--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -6110,21 +6110,22 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O4" s="83" t="n">
-        <v>3</v>
+      <c r="O4" s="83">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="P4" s="84" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="85" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" s="86" t="inlineStr">
-        <is>
-          <t>1-5</t>
-        </is>
+      <c r="Q4" s="85">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
+      </c>
+      <c r="R4" s="86">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="S4" s="331" t="n">
         <v>45139</v>
@@ -6168,21 +6169,22 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I5" s="22" t="n">
-        <v>1</v>
+      <c r="I5" s="22">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J5" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="55" t="inlineStr">
-        <is>
-          <t>2-4</t>
-        </is>
+      <c r="K5" s="23">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="L5" s="55">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="M5" s="330" t="n">
         <v>45109</v>
@@ -6192,21 +6194,22 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O5" s="83" t="n">
-        <v>2</v>
+      <c r="O5" s="83">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="P5" s="84" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q5" s="85" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" s="86" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+      <c r="Q5" s="85">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="R5" s="86">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="S5" s="331" t="n">
         <v>45140</v>
@@ -6250,21 +6253,22 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I6" s="22" t="n">
-        <v>2</v>
+      <c r="I6" s="22">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="J6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K6" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="55" t="inlineStr">
-        <is>
-          <t>1-6</t>
-        </is>
+      <c r="K6" s="23">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
+      </c>
+      <c r="L6" s="55">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="M6" s="330" t="n">
         <v>45110</v>
@@ -6324,21 +6328,22 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I7" s="22" t="n">
-        <v>4</v>
+      <c r="I7" s="22">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="J7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="55" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
+      <c r="K7" s="23">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L7" s="55">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="M7" s="330" t="n">
         <v>45111</v>
@@ -6662,21 +6667,22 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I12" s="22" t="n">
-        <v>1</v>
+      <c r="I12" s="22">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K12" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="55" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
+      <c r="K12" s="23">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
+      </c>
+      <c r="L12" s="55">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="M12" s="330" t="n">
         <v>45116</v>
@@ -6736,21 +6742,22 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I13" s="22" t="n">
-        <v>3</v>
+      <c r="I13" s="22">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="J13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" s="55" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
+      <c r="K13" s="23">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L13" s="55">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="M13" s="330" t="n">
         <v>45117</v>
@@ -6810,21 +6817,22 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I14" s="22" t="n">
-        <v>4</v>
+      <c r="I14" s="22">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="J14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="55" t="inlineStr">
-        <is>
-          <t>3-5</t>
-        </is>
+      <c r="K14" s="23">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="L14" s="55">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="M14" s="330" t="n">
         <v>45118</v>
@@ -7578,17 +7586,18 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I26" s="83" t="n">
-        <v>2</v>
+      <c r="I26" s="83">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="J26" s="84" t="n"/>
-      <c r="K26" s="85" t="n">
-        <v>5</v>
-      </c>
-      <c r="L26" s="86" t="inlineStr">
-        <is>
-          <t>4-6</t>
-        </is>
+      <c r="K26" s="85">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L26" s="86">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="M26" s="330" t="n">
         <v>45130</v>
@@ -7644,17 +7653,18 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I27" s="83" t="n">
-        <v>1</v>
+      <c r="I27" s="83">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J27" s="84" t="n"/>
-      <c r="K27" s="85" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="86" t="inlineStr">
-        <is>
-          <t>2-5</t>
-        </is>
+      <c r="K27" s="85">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
+      </c>
+      <c r="L27" s="86">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="M27" s="330" t="n">
         <v>45131</v>
@@ -7710,17 +7720,18 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I28" s="83" t="n">
-        <v>3</v>
+      <c r="I28" s="83">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="J28" s="84" t="n"/>
-      <c r="K28" s="85" t="n">
-        <v>6</v>
-      </c>
-      <c r="L28" s="86" t="inlineStr">
-        <is>
-          <t>1-4</t>
-        </is>
+      <c r="K28" s="85">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="L28" s="86">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="M28" s="330" t="n">
         <v>45132</v>
@@ -7760,21 +7771,22 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C29" s="22" t="n">
-        <v>1</v>
+      <c r="C29" s="22">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="D29" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="55" t="inlineStr">
-        <is>
-          <t>2-6</t>
-        </is>
+      <c r="E29" s="23">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
+      </c>
+      <c r="F29" s="55">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="G29" s="330" t="n">
         <v>45103</v>
@@ -7826,21 +7838,22 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C30" s="65" t="n">
-        <v>5</v>
+      <c r="C30" s="65">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="D30" s="66" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" s="55" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
+      <c r="E30" s="67">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="F30" s="55">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="G30" s="330" t="n">
         <v>45104</v>
@@ -7892,21 +7905,22 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n">
-        <v>2</v>
+      <c r="C31" s="22">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="D31" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E31" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F31" s="55" t="inlineStr">
-        <is>
-          <t>5-6</t>
-        </is>
+      <c r="E31" s="23">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
+      </c>
+      <c r="F31" s="55">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="G31" s="330" t="n">
         <v>45105</v>
@@ -8032,17 +8046,18 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I33" s="87" t="n">
-        <v>1</v>
+      <c r="I33" s="87">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J33" s="88" t="n"/>
-      <c r="K33" s="89" t="n">
-        <v>5</v>
-      </c>
-      <c r="L33" s="90" t="inlineStr">
-        <is>
-          <t>3-6</t>
-        </is>
+      <c r="K33" s="89">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L33" s="90">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="M33" s="330" t="n">
         <v>45137</v>
@@ -8664,21 +8679,22 @@
         <f>日程表１!N4</f>
         <v/>
       </c>
-      <c r="O4" s="26" t="n">
-        <v>3</v>
+      <c r="O4" s="26">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="P4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" s="29" t="inlineStr">
-        <is>
-          <t>1-5</t>
-        </is>
+      <c r="Q4" s="28">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
+      </c>
+      <c r="R4" s="29">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="S4" s="338">
         <f>日程表１!S5</f>
@@ -8722,21 +8738,22 @@
         <f>日程表１!H5</f>
         <v/>
       </c>
-      <c r="I5" s="31" t="n">
-        <v>1</v>
+      <c r="I5" s="31">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="29" t="inlineStr">
-        <is>
-          <t>2-4</t>
-        </is>
+      <c r="K5" s="32">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="L5" s="29">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="M5" s="338">
         <f>日程表１!M5</f>
@@ -8746,21 +8763,22 @@
         <f>日程表１!N5</f>
         <v/>
       </c>
-      <c r="O5" s="31" t="n">
-        <v>2</v>
+      <c r="O5" s="31">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="P5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q5" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" s="29" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+      <c r="Q5" s="32">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="R5" s="29">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="S5" s="338">
         <f>日程表１!S6</f>
@@ -8804,21 +8822,22 @@
         <f>日程表１!H6</f>
         <v/>
       </c>
-      <c r="I6" s="31" t="n">
-        <v>2</v>
+      <c r="I6" s="31">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="J6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K6" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="29" t="inlineStr">
-        <is>
-          <t>1-6</t>
-        </is>
+      <c r="K6" s="32">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
+      </c>
+      <c r="L6" s="29">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="M6" s="338">
         <f>日程表１!M6</f>
@@ -8878,21 +8897,22 @@
         <f>日程表１!H7</f>
         <v/>
       </c>
-      <c r="I7" s="31" t="n">
-        <v>4</v>
+      <c r="I7" s="31">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="J7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="29" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
+      <c r="K7" s="32">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L7" s="29">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="M7" s="338">
         <f>日程表１!M7</f>
@@ -9216,21 +9236,22 @@
         <f>日程表１!H12</f>
         <v/>
       </c>
-      <c r="I12" s="31" t="n">
-        <v>1</v>
+      <c r="I12" s="31">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K12" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="29" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
+      <c r="K12" s="32">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
+      </c>
+      <c r="L12" s="29">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="M12" s="338">
         <f>日程表１!M12</f>
@@ -9290,21 +9311,22 @@
         <f>日程表１!H13</f>
         <v/>
       </c>
-      <c r="I13" s="31" t="n">
-        <v>3</v>
+      <c r="I13" s="31">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="J13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" s="29" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
+      <c r="K13" s="32">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L13" s="29">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="M13" s="338">
         <f>日程表１!M13</f>
@@ -9364,21 +9386,22 @@
         <f>日程表１!H14</f>
         <v/>
       </c>
-      <c r="I14" s="31" t="n">
-        <v>4</v>
+      <c r="I14" s="31">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="J14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="29" t="inlineStr">
-        <is>
-          <t>3-5</t>
-        </is>
+      <c r="K14" s="32">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="L14" s="29">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="M14" s="338">
         <f>日程表１!M14</f>
@@ -10092,21 +10115,22 @@
         <f>日程表１!H26</f>
         <v/>
       </c>
-      <c r="I26" s="31" t="n">
-        <v>2</v>
+      <c r="I26" s="31">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="J26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K26" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L26" s="29" t="inlineStr">
-        <is>
-          <t>4-6</t>
-        </is>
+      <c r="K26" s="32">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L26" s="29">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="M26" s="338">
         <f>日程表１!M26</f>
@@ -10161,21 +10185,22 @@
         <f>日程表１!H27</f>
         <v/>
       </c>
-      <c r="I27" s="31" t="n">
-        <v>1</v>
+      <c r="I27" s="31">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K27" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="29" t="inlineStr">
-        <is>
-          <t>2-5</t>
-        </is>
+      <c r="K27" s="32">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
+      </c>
+      <c r="L27" s="29">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="M27" s="338">
         <f>日程表１!M27</f>
@@ -10230,21 +10255,22 @@
         <f>日程表１!H28</f>
         <v/>
       </c>
-      <c r="I28" s="31" t="n">
-        <v>3</v>
+      <c r="I28" s="31">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="J28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K28" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L28" s="29" t="inlineStr">
-        <is>
-          <t>1-4</t>
-        </is>
+      <c r="K28" s="32">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="L28" s="29">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
       </c>
       <c r="M28" s="339">
         <f>日程表１!M28</f>
@@ -10283,21 +10309,22 @@
         <f>日程表１!B29</f>
         <v/>
       </c>
-      <c r="C29" s="31" t="n">
-        <v>1</v>
+      <c r="C29" s="31">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="D29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="29" t="inlineStr">
-        <is>
-          <t>2-6</t>
-        </is>
+      <c r="E29" s="32">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
+      </c>
+      <c r="F29" s="29">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="G29" s="338">
         <f>日程表１!G29</f>
@@ -10347,21 +10374,22 @@
         <f>日程表１!B30</f>
         <v/>
       </c>
-      <c r="C30" s="31" t="n">
-        <v>5</v>
+      <c r="C30" s="31">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
       </c>
       <c r="D30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" s="29" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
+      <c r="E30" s="32">
+        <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
+      </c>
+      <c r="F30" s="29">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
+        <v/>
       </c>
       <c r="G30" s="338">
         <f>日程表１!G30</f>
@@ -10411,21 +10439,22 @@
         <f>日程表１!B31</f>
         <v/>
       </c>
-      <c r="C31" s="31" t="n">
-        <v>2</v>
+      <c r="C31" s="31">
+        <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
+        <v/>
       </c>
       <c r="D31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E31" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F31" s="29" t="inlineStr">
-        <is>
-          <t>5-6</t>
-        </is>
+      <c r="E31" s="32">
+        <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
+        <v/>
+      </c>
+      <c r="F31" s="29">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="G31" s="338">
         <f>日程表１!G31</f>
@@ -10547,21 +10576,22 @@
         <f>日程表１!H33</f>
         <v/>
       </c>
-      <c r="I33" s="31" t="n">
-        <v>1</v>
+      <c r="I33" s="31">
+        <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
+        <v/>
       </c>
       <c r="J33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K33" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L33" s="29" t="inlineStr">
-        <is>
-          <t>3-6</t>
-        </is>
+      <c r="K33" s="32">
+        <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
+        <v/>
+      </c>
+      <c r="L33" s="29">
+        <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
+        <v/>
       </c>
       <c r="M33" s="338">
         <f>日程表１!M33</f>

--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="メイリオ"/>
       <charset val="128"/>
@@ -232,6 +232,11 @@
       <b val="1"/>
       <sz val="24"/>
     </font>
+    <font>
+      <name val="メイリオ"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1296,7 +1301,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="340">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2351,15 +2356,98 @@
     <xf numFmtId="165" fontId="17" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="37" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2368,6 +2456,21 @@
     </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5901,20 +6004,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="18" zeroHeight="1"/>
   <cols>
     <col width="2.44140625" customWidth="1" style="17" min="1" max="2"/>
-    <col width="2.44140625" customWidth="1" style="49" min="3" max="5"/>
-    <col width="5.21875" customWidth="1" style="17" min="6" max="6"/>
+    <col width="8" customWidth="1" style="49" min="3" max="5"/>
+    <col width="2.5" customWidth="1" style="257" min="4" max="4"/>
+    <col width="11" customWidth="1" style="17" min="6" max="6"/>
     <col width="2.44140625" customWidth="1" style="17" min="7" max="11"/>
-    <col width="5.21875" customWidth="1" style="17" min="12" max="12"/>
+    <col width="8" customWidth="1" style="257" min="9" max="9"/>
+    <col width="2.5" customWidth="1" style="257" min="10" max="10"/>
+    <col width="11" customWidth="1" style="17" min="12" max="12"/>
     <col width="2.44140625" customWidth="1" style="17" min="13" max="17"/>
-    <col width="5.21875" customWidth="1" style="17" min="18" max="18"/>
+    <col width="8" customWidth="1" style="257" min="15" max="15"/>
+    <col width="2.5" customWidth="1" style="257" min="16" max="16"/>
+    <col width="11" customWidth="1" style="17" min="18" max="18"/>
     <col width="2.44140625" customWidth="1" style="17" min="19" max="23"/>
-    <col width="5.21875" customWidth="1" style="17" min="24" max="24"/>
+    <col width="8" customWidth="1" style="257" min="21" max="21"/>
+    <col width="2.5" customWidth="1" style="257" min="22" max="22"/>
+    <col width="11" customWidth="1" style="17" min="24" max="24"/>
     <col width="0.6640625" customWidth="1" style="17" min="25" max="25"/>
     <col hidden="1" width="8.88671875" customWidth="1" style="17" min="26" max="16384"/>
   </cols>
@@ -6078,14 +6188,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n"/>
+      <c r="C4" s="331" t="n"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="55" t="n"/>
+      <c r="E4" s="332" t="n"/>
+      <c r="F4" s="333" t="n"/>
       <c r="G4" s="330" t="n">
         <v>45078</v>
       </c>
@@ -6094,14 +6204,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I4" s="46" t="n"/>
+      <c r="I4" s="334" t="n"/>
       <c r="J4" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="48" t="n"/>
-      <c r="L4" s="55" t="n"/>
+      <c r="K4" s="335" t="n"/>
+      <c r="L4" s="333" t="n"/>
       <c r="M4" s="330" t="n">
         <v>45108</v>
       </c>
@@ -6110,7 +6220,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O4" s="83">
+      <c r="O4" s="336">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6119,15 +6229,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="85">
+      <c r="Q4" s="337">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="86">
+      <c r="R4" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="331" t="n">
+      <c r="S4" s="339" t="n">
         <v>45139</v>
       </c>
       <c r="T4" s="69" t="inlineStr">
@@ -6135,14 +6245,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U4" s="19" t="n"/>
+      <c r="U4" s="331" t="n"/>
       <c r="V4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="21" t="n"/>
-      <c r="X4" s="55" t="n"/>
+      <c r="W4" s="332" t="n"/>
+      <c r="X4" s="333" t="n"/>
     </row>
     <row r="5" ht="16.15" customHeight="1" s="257">
       <c r="A5" s="330" t="n">
@@ -6153,14 +6263,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n"/>
+      <c r="C5" s="340" t="n"/>
       <c r="D5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="55" t="n"/>
+      <c r="E5" s="341" t="n"/>
+      <c r="F5" s="333" t="n"/>
       <c r="G5" s="330" t="n">
         <v>45079</v>
       </c>
@@ -6169,7 +6279,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -6178,11 +6288,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="55">
+      <c r="L5" s="333">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6194,7 +6304,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O5" s="83">
+      <c r="O5" s="336">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -6203,15 +6313,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q5" s="85">
+      <c r="Q5" s="337">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="86">
+      <c r="R5" s="338">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="331" t="n">
+      <c r="S5" s="339" t="n">
         <v>45140</v>
       </c>
       <c r="T5" s="69" t="inlineStr">
@@ -6219,14 +6329,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U5" s="22" t="n"/>
+      <c r="U5" s="340" t="n"/>
       <c r="V5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="23" t="n"/>
-      <c r="X5" s="55" t="n"/>
+      <c r="W5" s="341" t="n"/>
+      <c r="X5" s="333" t="n"/>
     </row>
     <row r="6" ht="16.15" customHeight="1" s="257">
       <c r="A6" s="330" t="n">
@@ -6237,14 +6347,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n"/>
+      <c r="C6" s="340" t="n"/>
       <c r="D6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="55" t="n"/>
+      <c r="E6" s="341" t="n"/>
+      <c r="F6" s="333" t="n"/>
       <c r="G6" s="330" t="n">
         <v>45080</v>
       </c>
@@ -6253,7 +6363,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -6262,11 +6372,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="341">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="333">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -6278,15 +6388,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O6" s="83" t="n"/>
+      <c r="O6" s="336" t="n"/>
       <c r="P6" s="84" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="85" t="n"/>
-      <c r="R6" s="86" t="n"/>
-      <c r="S6" s="331" t="n">
+      <c r="Q6" s="337" t="n"/>
+      <c r="R6" s="338" t="n"/>
+      <c r="S6" s="339" t="n">
         <v>45141</v>
       </c>
       <c r="T6" s="69" t="inlineStr">
@@ -6294,14 +6404,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U6" s="22" t="n"/>
+      <c r="U6" s="340" t="n"/>
       <c r="V6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="23" t="n"/>
-      <c r="X6" s="55" t="n"/>
+      <c r="W6" s="341" t="n"/>
+      <c r="X6" s="333" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" s="257">
       <c r="A7" s="330" t="n">
@@ -6312,14 +6422,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n"/>
+      <c r="C7" s="340" t="n"/>
       <c r="D7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="55" t="n"/>
+      <c r="E7" s="341" t="n"/>
+      <c r="F7" s="333" t="n"/>
       <c r="G7" s="330" t="n">
         <v>45081</v>
       </c>
@@ -6328,7 +6438,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="340">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6337,11 +6447,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="341">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="55">
+      <c r="L7" s="333">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6353,15 +6463,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O7" s="83" t="n"/>
+      <c r="O7" s="336" t="n"/>
       <c r="P7" s="84" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="85" t="n"/>
-      <c r="R7" s="86" t="n"/>
-      <c r="S7" s="331" t="n">
+      <c r="Q7" s="337" t="n"/>
+      <c r="R7" s="338" t="n"/>
+      <c r="S7" s="339" t="n">
         <v>45142</v>
       </c>
       <c r="T7" s="69" t="inlineStr">
@@ -6369,14 +6479,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U7" s="22" t="n"/>
+      <c r="U7" s="340" t="n"/>
       <c r="V7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="23" t="n"/>
-      <c r="X7" s="55" t="n"/>
+      <c r="W7" s="341" t="n"/>
+      <c r="X7" s="333" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" s="257">
       <c r="A8" s="330" t="n">
@@ -6387,14 +6497,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n"/>
+      <c r="C8" s="340" t="n"/>
       <c r="D8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="23" t="n"/>
-      <c r="F8" s="55" t="n"/>
+      <c r="E8" s="341" t="n"/>
+      <c r="F8" s="333" t="n"/>
       <c r="G8" s="330" t="n">
         <v>45082</v>
       </c>
@@ -6403,14 +6513,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I8" s="65" t="n"/>
+      <c r="I8" s="342" t="n"/>
       <c r="J8" s="66" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="67" t="n"/>
-      <c r="L8" s="55" t="n"/>
+      <c r="K8" s="343" t="n"/>
+      <c r="L8" s="333" t="n"/>
       <c r="M8" s="330" t="n">
         <v>45112</v>
       </c>
@@ -6419,15 +6529,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O8" s="83" t="n"/>
+      <c r="O8" s="336" t="n"/>
       <c r="P8" s="84" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="85" t="n"/>
-      <c r="R8" s="86" t="n"/>
-      <c r="S8" s="331" t="n">
+      <c r="Q8" s="337" t="n"/>
+      <c r="R8" s="338" t="n"/>
+      <c r="S8" s="339" t="n">
         <v>45143</v>
       </c>
       <c r="T8" s="69" t="inlineStr">
@@ -6435,14 +6545,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U8" s="22" t="n"/>
+      <c r="U8" s="340" t="n"/>
       <c r="V8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="23" t="n"/>
-      <c r="X8" s="55" t="n"/>
+      <c r="W8" s="341" t="n"/>
+      <c r="X8" s="333" t="n"/>
     </row>
     <row r="9" ht="16.15" customHeight="1" s="257">
       <c r="A9" s="330" t="n">
@@ -6453,14 +6563,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n"/>
+      <c r="C9" s="340" t="n"/>
       <c r="D9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="55" t="n"/>
+      <c r="E9" s="341" t="n"/>
+      <c r="F9" s="333" t="n"/>
       <c r="G9" s="330" t="n">
         <v>45083</v>
       </c>
@@ -6469,14 +6579,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I9" s="22" t="n"/>
+      <c r="I9" s="340" t="n"/>
       <c r="J9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="23" t="n"/>
-      <c r="L9" s="55" t="n"/>
+      <c r="K9" s="341" t="n"/>
+      <c r="L9" s="333" t="n"/>
       <c r="M9" s="330" t="n">
         <v>45113</v>
       </c>
@@ -6485,15 +6595,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O9" s="83" t="n"/>
+      <c r="O9" s="336" t="n"/>
       <c r="P9" s="84" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="85" t="n"/>
-      <c r="R9" s="86" t="n"/>
-      <c r="S9" s="331" t="n">
+      <c r="Q9" s="337" t="n"/>
+      <c r="R9" s="338" t="n"/>
+      <c r="S9" s="339" t="n">
         <v>45144</v>
       </c>
       <c r="T9" s="69" t="inlineStr">
@@ -6501,14 +6611,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U9" s="22" t="n"/>
+      <c r="U9" s="340" t="n"/>
       <c r="V9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="23" t="n"/>
-      <c r="X9" s="55" t="n"/>
+      <c r="W9" s="341" t="n"/>
+      <c r="X9" s="333" t="n"/>
     </row>
     <row r="10" ht="16.15" customHeight="1" s="257">
       <c r="A10" s="330" t="n">
@@ -6519,14 +6629,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n"/>
+      <c r="C10" s="340" t="n"/>
       <c r="D10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="55" t="n"/>
+      <c r="E10" s="341" t="n"/>
+      <c r="F10" s="333" t="n"/>
       <c r="G10" s="330" t="n">
         <v>45084</v>
       </c>
@@ -6535,14 +6645,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I10" s="22" t="n"/>
+      <c r="I10" s="340" t="n"/>
       <c r="J10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="23" t="n"/>
-      <c r="L10" s="55" t="n"/>
+      <c r="K10" s="341" t="n"/>
+      <c r="L10" s="333" t="n"/>
       <c r="M10" s="330" t="n">
         <v>45114</v>
       </c>
@@ -6551,15 +6661,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O10" s="22" t="n"/>
+      <c r="O10" s="340" t="n"/>
       <c r="P10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="n"/>
-      <c r="R10" s="55" t="n"/>
-      <c r="S10" s="331" t="n">
+      <c r="Q10" s="341" t="n"/>
+      <c r="R10" s="333" t="n"/>
+      <c r="S10" s="339" t="n">
         <v>45145</v>
       </c>
       <c r="T10" s="69" t="inlineStr">
@@ -6567,14 +6677,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U10" s="22" t="n"/>
+      <c r="U10" s="340" t="n"/>
       <c r="V10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="23" t="n"/>
-      <c r="X10" s="55" t="n"/>
+      <c r="W10" s="341" t="n"/>
+      <c r="X10" s="333" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" s="257">
       <c r="A11" s="330" t="n">
@@ -6585,14 +6695,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C11" s="46" t="n"/>
+      <c r="C11" s="334" t="n"/>
       <c r="D11" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="48" t="n"/>
-      <c r="F11" s="55" t="n"/>
+      <c r="E11" s="335" t="n"/>
+      <c r="F11" s="333" t="n"/>
       <c r="G11" s="330" t="n">
         <v>45085</v>
       </c>
@@ -6601,14 +6711,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I11" s="22" t="n"/>
+      <c r="I11" s="340" t="n"/>
       <c r="J11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="55" t="n"/>
+      <c r="K11" s="341" t="n"/>
+      <c r="L11" s="333" t="n"/>
       <c r="M11" s="330" t="n">
         <v>45115</v>
       </c>
@@ -6617,15 +6727,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O11" s="22" t="n"/>
+      <c r="O11" s="340" t="n"/>
       <c r="P11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="23" t="n"/>
-      <c r="R11" s="55" t="n"/>
-      <c r="S11" s="331" t="n">
+      <c r="Q11" s="341" t="n"/>
+      <c r="R11" s="333" t="n"/>
+      <c r="S11" s="339" t="n">
         <v>45146</v>
       </c>
       <c r="T11" s="69" t="inlineStr">
@@ -6633,14 +6743,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U11" s="22" t="n"/>
+      <c r="U11" s="340" t="n"/>
       <c r="V11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="23" t="n"/>
-      <c r="X11" s="55" t="n"/>
+      <c r="W11" s="341" t="n"/>
+      <c r="X11" s="333" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" s="257">
       <c r="A12" s="330" t="n">
@@ -6651,14 +6761,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
+      <c r="C12" s="334" t="n"/>
       <c r="D12" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="48" t="n"/>
-      <c r="F12" s="55" t="n"/>
+      <c r="E12" s="335" t="n"/>
+      <c r="F12" s="333" t="n"/>
       <c r="G12" s="330" t="n">
         <v>45086</v>
       </c>
@@ -6667,7 +6777,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -6676,11 +6786,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="341">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="55">
+      <c r="L12" s="333">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -6692,15 +6802,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O12" s="65" t="n"/>
+      <c r="O12" s="342" t="n"/>
       <c r="P12" s="66" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="67" t="n"/>
-      <c r="R12" s="55" t="n"/>
-      <c r="S12" s="331" t="n">
+      <c r="Q12" s="343" t="n"/>
+      <c r="R12" s="333" t="n"/>
+      <c r="S12" s="339" t="n">
         <v>45147</v>
       </c>
       <c r="T12" s="69" t="inlineStr">
@@ -6708,14 +6818,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U12" s="22" t="n"/>
+      <c r="U12" s="340" t="n"/>
       <c r="V12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="23" t="n"/>
-      <c r="X12" s="55" t="n"/>
+      <c r="W12" s="341" t="n"/>
+      <c r="X12" s="333" t="n"/>
     </row>
     <row r="13" ht="16.15" customHeight="1" s="257">
       <c r="A13" s="330" t="n">
@@ -6726,14 +6836,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C13" s="46" t="n"/>
+      <c r="C13" s="334" t="n"/>
       <c r="D13" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="55" t="n"/>
+      <c r="E13" s="335" t="n"/>
+      <c r="F13" s="333" t="n"/>
       <c r="G13" s="330" t="n">
         <v>45087</v>
       </c>
@@ -6742,7 +6852,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="340">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6751,11 +6861,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="341">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="55">
+      <c r="L13" s="333">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -6767,15 +6877,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O13" s="22" t="n"/>
+      <c r="O13" s="340" t="n"/>
       <c r="P13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="23" t="n"/>
-      <c r="R13" s="55" t="n"/>
-      <c r="S13" s="331" t="n">
+      <c r="Q13" s="341" t="n"/>
+      <c r="R13" s="333" t="n"/>
+      <c r="S13" s="339" t="n">
         <v>45148</v>
       </c>
       <c r="T13" s="69" t="inlineStr">
@@ -6783,14 +6893,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U13" s="22" t="n"/>
+      <c r="U13" s="340" t="n"/>
       <c r="V13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="23" t="n"/>
-      <c r="X13" s="55" t="n"/>
+      <c r="W13" s="341" t="n"/>
+      <c r="X13" s="333" t="n"/>
     </row>
     <row r="14" ht="16.15" customHeight="1" s="257">
       <c r="A14" s="330" t="n">
@@ -6801,14 +6911,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C14" s="46" t="n"/>
+      <c r="C14" s="334" t="n"/>
       <c r="D14" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="48" t="n"/>
-      <c r="F14" s="55" t="n"/>
+      <c r="E14" s="335" t="n"/>
+      <c r="F14" s="333" t="n"/>
       <c r="G14" s="330" t="n">
         <v>45088</v>
       </c>
@@ -6817,7 +6927,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="340">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6826,11 +6936,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="55">
+      <c r="L14" s="333">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -6842,15 +6952,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O14" s="22" t="n"/>
+      <c r="O14" s="340" t="n"/>
       <c r="P14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="23" t="n"/>
-      <c r="R14" s="55" t="n"/>
-      <c r="S14" s="331" t="n">
+      <c r="Q14" s="341" t="n"/>
+      <c r="R14" s="333" t="n"/>
+      <c r="S14" s="339" t="n">
         <v>45149</v>
       </c>
       <c r="T14" s="69" t="inlineStr">
@@ -6858,14 +6968,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U14" s="22" t="n"/>
+      <c r="U14" s="340" t="n"/>
       <c r="V14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W14" s="23" t="n"/>
-      <c r="X14" s="55" t="n"/>
+      <c r="W14" s="341" t="n"/>
+      <c r="X14" s="333" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" s="257">
       <c r="A15" s="330" t="n">
@@ -6876,14 +6986,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C15" s="46" t="n"/>
+      <c r="C15" s="334" t="n"/>
       <c r="D15" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="48" t="n"/>
-      <c r="F15" s="55" t="n"/>
+      <c r="E15" s="335" t="n"/>
+      <c r="F15" s="333" t="n"/>
       <c r="G15" s="330" t="n">
         <v>45089</v>
       </c>
@@ -6892,14 +7002,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I15" s="65" t="n"/>
+      <c r="I15" s="342" t="n"/>
       <c r="J15" s="66" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="67" t="n"/>
-      <c r="L15" s="55" t="n"/>
+      <c r="K15" s="343" t="n"/>
+      <c r="L15" s="333" t="n"/>
       <c r="M15" s="330" t="n">
         <v>45119</v>
       </c>
@@ -6908,15 +7018,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O15" s="22" t="n"/>
+      <c r="O15" s="340" t="n"/>
       <c r="P15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="55" t="n"/>
-      <c r="S15" s="331" t="n">
+      <c r="Q15" s="341" t="n"/>
+      <c r="R15" s="333" t="n"/>
+      <c r="S15" s="339" t="n">
         <v>45150</v>
       </c>
       <c r="T15" s="69" t="inlineStr">
@@ -6924,14 +7034,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U15" s="22" t="n"/>
+      <c r="U15" s="340" t="n"/>
       <c r="V15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W15" s="23" t="n"/>
-      <c r="X15" s="55" t="n"/>
+      <c r="W15" s="341" t="n"/>
+      <c r="X15" s="333" t="n"/>
     </row>
     <row r="16" ht="16.15" customHeight="1" s="257">
       <c r="A16" s="330" t="n">
@@ -6942,14 +7052,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C16" s="65" t="n"/>
+      <c r="C16" s="342" t="n"/>
       <c r="D16" s="66" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="67" t="n"/>
-      <c r="F16" s="55" t="n"/>
+      <c r="E16" s="343" t="n"/>
+      <c r="F16" s="333" t="n"/>
       <c r="G16" s="330" t="n">
         <v>45090</v>
       </c>
@@ -6958,14 +7068,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I16" s="22" t="n"/>
+      <c r="I16" s="340" t="n"/>
       <c r="J16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="23" t="n"/>
-      <c r="L16" s="55" t="n"/>
+      <c r="K16" s="341" t="n"/>
+      <c r="L16" s="333" t="n"/>
       <c r="M16" s="330" t="n">
         <v>45120</v>
       </c>
@@ -6974,15 +7084,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O16" s="22" t="n"/>
+      <c r="O16" s="340" t="n"/>
       <c r="P16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="23" t="n"/>
-      <c r="R16" s="55" t="n"/>
-      <c r="S16" s="331" t="n">
+      <c r="Q16" s="341" t="n"/>
+      <c r="R16" s="333" t="n"/>
+      <c r="S16" s="339" t="n">
         <v>45151</v>
       </c>
       <c r="T16" s="69" t="inlineStr">
@@ -6990,14 +7100,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U16" s="22" t="n"/>
+      <c r="U16" s="340" t="n"/>
       <c r="V16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W16" s="23" t="n"/>
-      <c r="X16" s="55" t="n"/>
+      <c r="W16" s="341" t="n"/>
+      <c r="X16" s="333" t="n"/>
     </row>
     <row r="17" ht="16.15" customHeight="1" s="257">
       <c r="A17" s="330" t="n">
@@ -7008,14 +7118,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C17" s="46" t="n"/>
+      <c r="C17" s="334" t="n"/>
       <c r="D17" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="55" t="n"/>
+      <c r="E17" s="335" t="n"/>
+      <c r="F17" s="333" t="n"/>
       <c r="G17" s="330" t="n">
         <v>45091</v>
       </c>
@@ -7024,14 +7134,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I17" s="22" t="n"/>
+      <c r="I17" s="340" t="n"/>
       <c r="J17" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="23" t="n"/>
-      <c r="L17" s="55" t="n"/>
+      <c r="K17" s="341" t="n"/>
+      <c r="L17" s="333" t="n"/>
       <c r="M17" s="330" t="n">
         <v>45121</v>
       </c>
@@ -7040,15 +7150,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O17" s="22" t="n"/>
+      <c r="O17" s="340" t="n"/>
       <c r="P17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="23" t="n"/>
-      <c r="R17" s="55" t="n"/>
-      <c r="S17" s="331" t="n">
+      <c r="Q17" s="341" t="n"/>
+      <c r="R17" s="333" t="n"/>
+      <c r="S17" s="339" t="n">
         <v>45152</v>
       </c>
       <c r="T17" s="69" t="inlineStr">
@@ -7056,14 +7166,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U17" s="22" t="n"/>
+      <c r="U17" s="340" t="n"/>
       <c r="V17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W17" s="23" t="n"/>
-      <c r="X17" s="55" t="n"/>
+      <c r="W17" s="341" t="n"/>
+      <c r="X17" s="333" t="n"/>
     </row>
     <row r="18" ht="16.15" customHeight="1" s="257">
       <c r="A18" s="330" t="n">
@@ -7074,14 +7184,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C18" s="46" t="n"/>
+      <c r="C18" s="334" t="n"/>
       <c r="D18" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="48" t="n"/>
-      <c r="F18" s="55" t="n"/>
+      <c r="E18" s="335" t="n"/>
+      <c r="F18" s="333" t="n"/>
       <c r="G18" s="330" t="n">
         <v>45092</v>
       </c>
@@ -7090,14 +7200,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I18" s="22" t="n"/>
+      <c r="I18" s="340" t="n"/>
       <c r="J18" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="23" t="n"/>
-      <c r="L18" s="55" t="n"/>
+      <c r="K18" s="341" t="n"/>
+      <c r="L18" s="333" t="n"/>
       <c r="M18" s="330" t="n">
         <v>45122</v>
       </c>
@@ -7106,15 +7216,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O18" s="22" t="n"/>
+      <c r="O18" s="340" t="n"/>
       <c r="P18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="23" t="n"/>
-      <c r="R18" s="68" t="n"/>
-      <c r="S18" s="331" t="n">
+      <c r="Q18" s="341" t="n"/>
+      <c r="R18" s="344" t="n"/>
+      <c r="S18" s="339" t="n">
         <v>45153</v>
       </c>
       <c r="T18" s="69" t="inlineStr">
@@ -7122,14 +7232,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U18" s="22" t="n"/>
+      <c r="U18" s="340" t="n"/>
       <c r="V18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W18" s="23" t="n"/>
-      <c r="X18" s="55" t="n"/>
+      <c r="W18" s="341" t="n"/>
+      <c r="X18" s="333" t="n"/>
     </row>
     <row r="19" ht="16.15" customHeight="1" s="257">
       <c r="A19" s="330" t="n">
@@ -7140,14 +7250,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C19" s="46" t="n"/>
+      <c r="C19" s="334" t="n"/>
       <c r="D19" s="47" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="48" t="n"/>
-      <c r="F19" s="55" t="n"/>
+      <c r="E19" s="335" t="n"/>
+      <c r="F19" s="333" t="n"/>
       <c r="G19" s="330" t="n">
         <v>45093</v>
       </c>
@@ -7156,14 +7266,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="340" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="50" t="n"/>
-      <c r="K19" s="23" t="n"/>
-      <c r="L19" s="55" t="n"/>
+      <c r="K19" s="341" t="n"/>
+      <c r="L19" s="333" t="n"/>
       <c r="M19" s="330" t="n">
         <v>45123</v>
       </c>
@@ -7172,15 +7282,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O19" s="22" t="n"/>
+      <c r="O19" s="340" t="n"/>
       <c r="P19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="23" t="n"/>
-      <c r="R19" s="68" t="n"/>
-      <c r="S19" s="331" t="n">
+      <c r="Q19" s="341" t="n"/>
+      <c r="R19" s="344" t="n"/>
+      <c r="S19" s="339" t="n">
         <v>45154</v>
       </c>
       <c r="T19" s="69" t="inlineStr">
@@ -7188,14 +7298,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U19" s="22" t="n"/>
+      <c r="U19" s="340" t="n"/>
       <c r="V19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W19" s="23" t="n"/>
-      <c r="X19" s="55" t="n"/>
+      <c r="W19" s="341" t="n"/>
+      <c r="X19" s="333" t="n"/>
     </row>
     <row r="20" ht="16.15" customHeight="1" s="257">
       <c r="A20" s="330" t="n">
@@ -7206,14 +7316,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C20" s="22" t="n"/>
+      <c r="C20" s="340" t="n"/>
       <c r="D20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="55" t="n"/>
+      <c r="E20" s="341" t="n"/>
+      <c r="F20" s="333" t="n"/>
       <c r="G20" s="330" t="n">
         <v>45094</v>
       </c>
@@ -7222,14 +7332,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I20" s="83" t="inlineStr">
+      <c r="I20" s="336" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="84" t="n"/>
-      <c r="K20" s="85" t="n"/>
-      <c r="L20" s="86" t="n"/>
+      <c r="K20" s="337" t="n"/>
+      <c r="L20" s="338" t="n"/>
       <c r="M20" s="330" t="n">
         <v>45124</v>
       </c>
@@ -7238,15 +7348,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O20" s="22" t="n"/>
+      <c r="O20" s="340" t="n"/>
       <c r="P20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="23" t="n"/>
-      <c r="R20" s="68" t="n"/>
-      <c r="S20" s="331" t="n">
+      <c r="Q20" s="341" t="n"/>
+      <c r="R20" s="344" t="n"/>
+      <c r="S20" s="339" t="n">
         <v>45155</v>
       </c>
       <c r="T20" s="69" t="inlineStr">
@@ -7254,14 +7364,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U20" s="22" t="n"/>
+      <c r="U20" s="340" t="n"/>
       <c r="V20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W20" s="23" t="n"/>
-      <c r="X20" s="55" t="n"/>
+      <c r="W20" s="341" t="n"/>
+      <c r="X20" s="333" t="n"/>
     </row>
     <row r="21" ht="16.15" customHeight="1" s="257" thickBot="1">
       <c r="A21" s="330" t="n">
@@ -7272,14 +7382,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C21" s="22" t="n"/>
+      <c r="C21" s="340" t="n"/>
       <c r="D21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="55" t="n"/>
+      <c r="E21" s="341" t="n"/>
+      <c r="F21" s="333" t="n"/>
       <c r="G21" s="330" t="n">
         <v>45095</v>
       </c>
@@ -7288,14 +7398,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I21" s="83" t="inlineStr">
+      <c r="I21" s="336" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="84" t="n"/>
-      <c r="K21" s="85" t="n"/>
-      <c r="L21" s="86" t="n"/>
+      <c r="K21" s="337" t="n"/>
+      <c r="L21" s="338" t="n"/>
       <c r="M21" s="330" t="n">
         <v>45125</v>
       </c>
@@ -7304,15 +7414,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O21" s="22" t="n"/>
+      <c r="O21" s="340" t="n"/>
       <c r="P21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="23" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="332" t="n">
+      <c r="Q21" s="341" t="n"/>
+      <c r="R21" s="333" t="n"/>
+      <c r="S21" s="345" t="n">
         <v>45156</v>
       </c>
       <c r="T21" s="71" t="inlineStr">
@@ -7320,14 +7430,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U21" s="59" t="n"/>
+      <c r="U21" s="346" t="n"/>
       <c r="V21" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W21" s="61" t="n"/>
-      <c r="X21" s="57" t="n"/>
+      <c r="W21" s="347" t="n"/>
+      <c r="X21" s="348" t="n"/>
     </row>
     <row r="22" ht="16.15" customHeight="1" s="257" thickBot="1">
       <c r="A22" s="330" t="n">
@@ -7338,14 +7448,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C22" s="22" t="n"/>
+      <c r="C22" s="340" t="n"/>
       <c r="D22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="55" t="n"/>
+      <c r="E22" s="341" t="n"/>
+      <c r="F22" s="333" t="n"/>
       <c r="G22" s="330" t="n">
         <v>45096</v>
       </c>
@@ -7354,10 +7464,10 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I22" s="83" t="n"/>
+      <c r="I22" s="336" t="n"/>
       <c r="J22" s="84" t="n"/>
-      <c r="K22" s="85" t="n"/>
-      <c r="L22" s="86" t="n"/>
+      <c r="K22" s="337" t="n"/>
+      <c r="L22" s="338" t="n"/>
       <c r="M22" s="330" t="n">
         <v>45126</v>
       </c>
@@ -7366,24 +7476,24 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O22" s="22" t="n"/>
+      <c r="O22" s="340" t="n"/>
       <c r="P22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="23" t="n"/>
-      <c r="R22" s="55" t="n"/>
+      <c r="Q22" s="341" t="n"/>
+      <c r="R22" s="333" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="U22" s="24" t="n"/>
+      <c r="U22" s="349" t="n"/>
       <c r="V22" s="238" t="n"/>
-      <c r="W22" s="238" t="n"/>
-      <c r="X22" s="238" t="n"/>
+      <c r="W22" s="350" t="n"/>
+      <c r="X22" s="350" t="n"/>
     </row>
     <row r="23" ht="16.15" customHeight="1" s="257">
       <c r="A23" s="330" t="n">
@@ -7394,14 +7504,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C23" s="65" t="n"/>
+      <c r="C23" s="342" t="n"/>
       <c r="D23" s="66" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="67" t="n"/>
-      <c r="F23" s="55" t="n"/>
+      <c r="E23" s="343" t="n"/>
+      <c r="F23" s="333" t="n"/>
       <c r="G23" s="330" t="n">
         <v>45097</v>
       </c>
@@ -7410,10 +7520,10 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I23" s="83" t="n"/>
+      <c r="I23" s="336" t="n"/>
       <c r="J23" s="84" t="n"/>
-      <c r="K23" s="85" t="n"/>
-      <c r="L23" s="86" t="n"/>
+      <c r="K23" s="337" t="n"/>
+      <c r="L23" s="338" t="n"/>
       <c r="M23" s="330" t="n">
         <v>45127</v>
       </c>
@@ -7422,14 +7532,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O23" s="22" t="n"/>
+      <c r="O23" s="340" t="n"/>
       <c r="P23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="23" t="n"/>
-      <c r="R23" s="55" t="n"/>
+      <c r="Q23" s="341" t="n"/>
+      <c r="R23" s="333" t="n"/>
       <c r="S23" s="76" t="inlineStr">
         <is>
           <t>NO.</t>
@@ -7443,7 +7553,7 @@
       <c r="U23" s="328" t="n"/>
       <c r="V23" s="328" t="n"/>
       <c r="W23" s="328" t="n"/>
-      <c r="X23" s="333" t="n"/>
+      <c r="X23" s="351" t="n"/>
     </row>
     <row r="24" ht="16.15" customHeight="1" s="257">
       <c r="A24" s="330" t="n">
@@ -7454,14 +7564,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n"/>
+      <c r="C24" s="340" t="n"/>
       <c r="D24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="55" t="n"/>
+      <c r="E24" s="341" t="n"/>
+      <c r="F24" s="333" t="n"/>
       <c r="G24" s="330" t="n">
         <v>45098</v>
       </c>
@@ -7470,10 +7580,10 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I24" s="83" t="n"/>
+      <c r="I24" s="336" t="n"/>
       <c r="J24" s="84" t="n"/>
-      <c r="K24" s="85" t="n"/>
-      <c r="L24" s="86" t="n"/>
+      <c r="K24" s="337" t="n"/>
+      <c r="L24" s="338" t="n"/>
       <c r="M24" s="330" t="n">
         <v>45128</v>
       </c>
@@ -7482,14 +7592,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O24" s="22" t="n"/>
+      <c r="O24" s="340" t="n"/>
       <c r="P24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="23" t="n"/>
-      <c r="R24" s="55" t="n"/>
+      <c r="Q24" s="341" t="n"/>
+      <c r="R24" s="333" t="n"/>
       <c r="S24" s="73" t="n">
         <v>1</v>
       </c>
@@ -7512,14 +7622,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C25" s="22" t="n"/>
+      <c r="C25" s="340" t="n"/>
       <c r="D25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="55" t="n"/>
+      <c r="E25" s="341" t="n"/>
+      <c r="F25" s="333" t="n"/>
       <c r="G25" s="330" t="n">
         <v>45099</v>
       </c>
@@ -7528,10 +7638,10 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I25" s="83" t="n"/>
+      <c r="I25" s="336" t="n"/>
       <c r="J25" s="84" t="n"/>
-      <c r="K25" s="85" t="n"/>
-      <c r="L25" s="86" t="n"/>
+      <c r="K25" s="337" t="n"/>
+      <c r="L25" s="338" t="n"/>
       <c r="M25" s="330" t="n">
         <v>45129</v>
       </c>
@@ -7540,14 +7650,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O25" s="22" t="n"/>
+      <c r="O25" s="340" t="n"/>
       <c r="P25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="23" t="n"/>
-      <c r="R25" s="55" t="n"/>
+      <c r="Q25" s="341" t="n"/>
+      <c r="R25" s="333" t="n"/>
       <c r="S25" s="73" t="n">
         <v>2</v>
       </c>
@@ -7570,14 +7680,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
+      <c r="C26" s="340" t="n"/>
       <c r="D26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="55" t="n"/>
+      <c r="E26" s="341" t="n"/>
+      <c r="F26" s="333" t="n"/>
       <c r="G26" s="330" t="n">
         <v>45100</v>
       </c>
@@ -7586,16 +7696,16 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I26" s="83">
+      <c r="I26" s="336">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
       <c r="J26" s="84" t="n"/>
-      <c r="K26" s="85">
+      <c r="K26" s="337">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="86">
+      <c r="L26" s="338">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -7607,14 +7717,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O26" s="22" t="n"/>
+      <c r="O26" s="340" t="n"/>
       <c r="P26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="23" t="n"/>
-      <c r="R26" s="55" t="n"/>
+      <c r="Q26" s="341" t="n"/>
+      <c r="R26" s="333" t="n"/>
       <c r="S26" s="73" t="n">
         <v>3</v>
       </c>
@@ -7637,14 +7747,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
+      <c r="C27" s="340" t="n"/>
       <c r="D27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="55" t="n"/>
+      <c r="E27" s="341" t="n"/>
+      <c r="F27" s="333" t="n"/>
       <c r="G27" s="330" t="n">
         <v>45101</v>
       </c>
@@ -7653,16 +7763,16 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I27" s="83">
+      <c r="I27" s="336">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J27" s="84" t="n"/>
-      <c r="K27" s="85">
+      <c r="K27" s="337">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="86">
+      <c r="L27" s="338">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -7674,14 +7784,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O27" s="22" t="n"/>
+      <c r="O27" s="340" t="n"/>
       <c r="P27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="23" t="n"/>
-      <c r="R27" s="55" t="n"/>
+      <c r="Q27" s="341" t="n"/>
+      <c r="R27" s="333" t="n"/>
       <c r="S27" s="73" t="n">
         <v>4</v>
       </c>
@@ -7704,14 +7814,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C28" s="22" t="n"/>
+      <c r="C28" s="340" t="n"/>
       <c r="D28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="55" t="n"/>
+      <c r="E28" s="341" t="n"/>
+      <c r="F28" s="333" t="n"/>
       <c r="G28" s="330" t="n">
         <v>45102</v>
       </c>
@@ -7720,16 +7830,16 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I28" s="83">
+      <c r="I28" s="336">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
       <c r="J28" s="84" t="n"/>
-      <c r="K28" s="85">
+      <c r="K28" s="337">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="86">
+      <c r="L28" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -7741,14 +7851,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O28" s="22" t="n"/>
+      <c r="O28" s="340" t="n"/>
       <c r="P28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="23" t="n"/>
-      <c r="R28" s="55" t="n"/>
+      <c r="Q28" s="341" t="n"/>
+      <c r="R28" s="333" t="n"/>
       <c r="S28" s="73" t="n">
         <v>5</v>
       </c>
@@ -7771,7 +7881,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -7780,11 +7890,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="341">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="55">
+      <c r="F29" s="333">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -7796,10 +7906,10 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I29" s="83" t="n"/>
+      <c r="I29" s="336" t="n"/>
       <c r="J29" s="84" t="n"/>
-      <c r="K29" s="85" t="n"/>
-      <c r="L29" s="86" t="n"/>
+      <c r="K29" s="337" t="n"/>
+      <c r="L29" s="338" t="n"/>
       <c r="M29" s="330" t="n">
         <v>45133</v>
       </c>
@@ -7808,14 +7918,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O29" s="22" t="n"/>
+      <c r="O29" s="340" t="n"/>
       <c r="P29" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="23" t="n"/>
-      <c r="R29" s="55" t="n"/>
+      <c r="Q29" s="341" t="n"/>
+      <c r="R29" s="333" t="n"/>
       <c r="S29" s="73" t="n">
         <v>6</v>
       </c>
@@ -7838,7 +7948,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C30" s="65">
+      <c r="C30" s="342">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -7847,11 +7957,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="67">
+      <c r="E30" s="343">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="55">
+      <c r="F30" s="333">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -7863,10 +7973,10 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I30" s="83" t="n"/>
+      <c r="I30" s="336" t="n"/>
       <c r="J30" s="84" t="n"/>
-      <c r="K30" s="85" t="n"/>
-      <c r="L30" s="86" t="n"/>
+      <c r="K30" s="337" t="n"/>
+      <c r="L30" s="338" t="n"/>
       <c r="M30" s="330" t="n">
         <v>45134</v>
       </c>
@@ -7875,14 +7985,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O30" s="22" t="n"/>
+      <c r="O30" s="340" t="n"/>
       <c r="P30" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="23" t="n"/>
-      <c r="R30" s="55" t="n"/>
+      <c r="Q30" s="341" t="n"/>
+      <c r="R30" s="333" t="n"/>
       <c r="S30" s="73" t="n">
         <v>7</v>
       </c>
@@ -7905,7 +8015,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -7914,11 +8024,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="341">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="55">
+      <c r="F31" s="333">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -7930,10 +8040,10 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I31" s="83" t="n"/>
+      <c r="I31" s="336" t="n"/>
       <c r="J31" s="84" t="n"/>
-      <c r="K31" s="85" t="n"/>
-      <c r="L31" s="86" t="n"/>
+      <c r="K31" s="337" t="n"/>
+      <c r="L31" s="338" t="n"/>
       <c r="M31" s="330" t="n">
         <v>45135</v>
       </c>
@@ -7942,14 +8052,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O31" s="22" t="n"/>
+      <c r="O31" s="340" t="n"/>
       <c r="P31" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="23" t="n"/>
-      <c r="R31" s="55" t="n"/>
+      <c r="Q31" s="341" t="n"/>
+      <c r="R31" s="333" t="n"/>
       <c r="S31" s="73" t="n">
         <v>8</v>
       </c>
@@ -7972,14 +8082,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
+      <c r="C32" s="340" t="n"/>
       <c r="D32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="23" t="n"/>
-      <c r="F32" s="55" t="n"/>
+      <c r="E32" s="341" t="n"/>
+      <c r="F32" s="333" t="n"/>
       <c r="G32" s="330" t="n">
         <v>45106</v>
       </c>
@@ -7988,10 +8098,10 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I32" s="83" t="n"/>
+      <c r="I32" s="336" t="n"/>
       <c r="J32" s="84" t="n"/>
-      <c r="K32" s="85" t="n"/>
-      <c r="L32" s="86" t="n"/>
+      <c r="K32" s="337" t="n"/>
+      <c r="L32" s="338" t="n"/>
       <c r="M32" s="330" t="n">
         <v>45136</v>
       </c>
@@ -8000,14 +8110,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O32" s="22" t="n"/>
+      <c r="O32" s="340" t="n"/>
       <c r="P32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="23" t="n"/>
-      <c r="R32" s="55" t="n"/>
+      <c r="Q32" s="341" t="n"/>
+      <c r="R32" s="333" t="n"/>
       <c r="S32" s="73" t="n">
         <v>9</v>
       </c>
@@ -8030,15 +8140,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n"/>
+      <c r="C33" s="340" t="n"/>
       <c r="D33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="55" t="n"/>
-      <c r="G33" s="334" t="n">
+      <c r="E33" s="341" t="n"/>
+      <c r="F33" s="333" t="n"/>
+      <c r="G33" s="352" t="n">
         <v>45107</v>
       </c>
       <c r="H33" s="82" t="inlineStr">
@@ -8046,16 +8156,16 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I33" s="87">
+      <c r="I33" s="353">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J33" s="88" t="n"/>
-      <c r="K33" s="89">
+      <c r="K33" s="354">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="90">
+      <c r="L33" s="355">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -8067,14 +8177,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O33" s="22" t="n"/>
+      <c r="O33" s="340" t="n"/>
       <c r="P33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="23" t="n"/>
-      <c r="R33" s="55" t="n"/>
+      <c r="Q33" s="341" t="n"/>
+      <c r="R33" s="333" t="n"/>
       <c r="S33" s="77" t="n">
         <v>10</v>
       </c>
@@ -8083,13 +8193,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U33" s="335" t="n"/>
-      <c r="V33" s="335" t="n"/>
-      <c r="W33" s="335" t="n"/>
-      <c r="X33" s="336" t="n"/>
+      <c r="U33" s="356" t="n"/>
+      <c r="V33" s="356" t="n"/>
+      <c r="W33" s="356" t="n"/>
+      <c r="X33" s="357" t="n"/>
     </row>
     <row r="34" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A34" s="334" t="n">
+      <c r="A34" s="352" t="n">
         <v>45077</v>
       </c>
       <c r="B34" s="71" t="inlineStr">
@@ -8097,20 +8207,20 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C34" s="59" t="n"/>
+      <c r="C34" s="346" t="n"/>
       <c r="D34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="61" t="n"/>
-      <c r="F34" s="57" t="n"/>
-      <c r="G34" s="337" t="n"/>
-      <c r="I34" s="24" t="n"/>
+      <c r="E34" s="347" t="n"/>
+      <c r="F34" s="348" t="n"/>
+      <c r="G34" s="358" t="n"/>
+      <c r="I34" s="349" t="n"/>
       <c r="J34" s="238" t="n"/>
-      <c r="K34" s="24" t="n"/>
-      <c r="L34" s="24" t="n"/>
-      <c r="M34" s="334" t="n">
+      <c r="K34" s="349" t="n"/>
+      <c r="L34" s="349" t="n"/>
+      <c r="M34" s="352" t="n">
         <v>45138</v>
       </c>
       <c r="N34" s="71" t="inlineStr">
@@ -8118,14 +8228,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O34" s="59" t="n"/>
+      <c r="O34" s="346" t="n"/>
       <c r="P34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="61" t="n"/>
-      <c r="R34" s="57" t="n"/>
+      <c r="Q34" s="347" t="n"/>
+      <c r="R34" s="348" t="n"/>
       <c r="S34" s="238" t="n"/>
       <c r="T34" s="238" t="inlineStr">
         <is>
@@ -8423,8 +8533,8 @@
       <formula>NOT(ISERROR(SEARCH("土",X3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="360" verticalDpi="360"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1" horizontalDpi="360" verticalDpi="360"/>
 </worksheet>
 </file>
 
@@ -8467,22 +8577,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="18" zeroHeight="1"/>
   <cols>
     <col width="2.44140625" customWidth="1" style="17" min="1" max="1"/>
     <col width="2" customWidth="1" style="17" min="2" max="5"/>
-    <col width="5.21875" customWidth="1" style="17" min="6" max="6"/>
+    <col width="8" customWidth="1" style="257" min="3" max="3"/>
+    <col width="2.5" customWidth="1" style="257" min="4" max="4"/>
+    <col width="11" customWidth="1" style="17" min="6" max="6"/>
     <col width="2" customWidth="1" style="17" min="7" max="8"/>
-    <col width="2" customWidth="1" style="18" min="9" max="9"/>
-    <col width="2" customWidth="1" style="17" min="10" max="11"/>
-    <col width="5.21875" customWidth="1" style="17" min="12" max="12"/>
+    <col width="8" customWidth="1" style="18" min="9" max="9"/>
+    <col width="2.5" customWidth="1" style="17" min="10" max="11"/>
+    <col width="11" customWidth="1" style="17" min="12" max="12"/>
     <col width="2" customWidth="1" style="17" min="13" max="17"/>
-    <col width="5.21875" customWidth="1" style="17" min="18" max="18"/>
+    <col width="8" customWidth="1" style="257" min="15" max="15"/>
+    <col width="2.5" customWidth="1" style="257" min="16" max="16"/>
+    <col width="11" customWidth="1" style="17" min="18" max="18"/>
     <col width="2" customWidth="1" style="17" min="19" max="23"/>
-    <col width="5.21875" customWidth="1" style="17" min="24" max="24"/>
+    <col width="8" customWidth="1" style="257" min="21" max="21"/>
+    <col width="2.5" customWidth="1" style="257" min="22" max="22"/>
+    <col width="11" customWidth="1" style="17" min="24" max="24"/>
     <col width="0.6640625" customWidth="1" style="17" min="25" max="25"/>
     <col hidden="1" width="7.77734375" customWidth="1" style="17" min="26" max="16384"/>
   </cols>
@@ -8639,7 +8755,7 @@
       </c>
     </row>
     <row r="4" ht="20.45" customHeight="1" s="257">
-      <c r="A4" s="338">
+      <c r="A4" s="359">
         <f>日程表１!A4</f>
         <v/>
       </c>
@@ -8647,15 +8763,15 @@
         <f>日程表１!B4</f>
         <v/>
       </c>
-      <c r="C4" s="26" t="n"/>
+      <c r="C4" s="331" t="n"/>
       <c r="D4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="28" t="n"/>
-      <c r="F4" s="29" t="n"/>
-      <c r="G4" s="338">
+      <c r="E4" s="332" t="n"/>
+      <c r="F4" s="360" t="n"/>
+      <c r="G4" s="359">
         <f>日程表１!G4</f>
         <v/>
       </c>
@@ -8663,15 +8779,15 @@
         <f>日程表１!H4</f>
         <v/>
       </c>
-      <c r="I4" s="26" t="n"/>
+      <c r="I4" s="331" t="n"/>
       <c r="J4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="28" t="n"/>
-      <c r="L4" s="29" t="n"/>
-      <c r="M4" s="338">
+      <c r="K4" s="332" t="n"/>
+      <c r="L4" s="360" t="n"/>
+      <c r="M4" s="359">
         <f>日程表１!M4</f>
         <v/>
       </c>
@@ -8679,7 +8795,7 @@
         <f>日程表１!N4</f>
         <v/>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="331">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -8688,15 +8804,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="332">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="360">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="338">
+      <c r="S4" s="359">
         <f>日程表１!S5</f>
         <v/>
       </c>
@@ -8704,17 +8820,17 @@
         <f>日程表１!T5</f>
         <v/>
       </c>
-      <c r="U4" s="26" t="n"/>
+      <c r="U4" s="331" t="n"/>
       <c r="V4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="30" t="n"/>
-      <c r="X4" s="251" t="n"/>
+      <c r="W4" s="361" t="n"/>
+      <c r="X4" s="362" t="n"/>
     </row>
     <row r="5" ht="20.45" customHeight="1" s="257">
-      <c r="A5" s="338">
+      <c r="A5" s="359">
         <f>日程表１!A5</f>
         <v/>
       </c>
@@ -8722,15 +8838,15 @@
         <f>日程表１!B5</f>
         <v/>
       </c>
-      <c r="C5" s="31" t="n"/>
+      <c r="C5" s="340" t="n"/>
       <c r="D5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="29" t="n"/>
-      <c r="G5" s="338">
+      <c r="E5" s="341" t="n"/>
+      <c r="F5" s="360" t="n"/>
+      <c r="G5" s="359">
         <f>日程表１!G5</f>
         <v/>
       </c>
@@ -8738,7 +8854,7 @@
         <f>日程表１!H5</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -8747,15 +8863,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="29">
+      <c r="L5" s="360">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="338">
+      <c r="M5" s="359">
         <f>日程表１!M5</f>
         <v/>
       </c>
@@ -8763,7 +8879,7 @@
         <f>日程表１!N5</f>
         <v/>
       </c>
-      <c r="O5" s="31">
+      <c r="O5" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -8772,15 +8888,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q5" s="32">
+      <c r="Q5" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="360">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="338">
+      <c r="S5" s="359">
         <f>日程表１!S6</f>
         <v/>
       </c>
@@ -8788,17 +8904,17 @@
         <f>日程表１!T6</f>
         <v/>
       </c>
-      <c r="U5" s="31" t="n"/>
+      <c r="U5" s="340" t="n"/>
       <c r="V5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="33" t="n"/>
-      <c r="X5" s="251" t="n"/>
+      <c r="W5" s="363" t="n"/>
+      <c r="X5" s="362" t="n"/>
     </row>
     <row r="6" ht="20.45" customHeight="1" s="257">
-      <c r="A6" s="338">
+      <c r="A6" s="359">
         <f>日程表１!A6</f>
         <v/>
       </c>
@@ -8806,15 +8922,15 @@
         <f>日程表１!B6</f>
         <v/>
       </c>
-      <c r="C6" s="31" t="n"/>
+      <c r="C6" s="340" t="n"/>
       <c r="D6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="338">
+      <c r="E6" s="341" t="n"/>
+      <c r="F6" s="360" t="n"/>
+      <c r="G6" s="359">
         <f>日程表１!G6</f>
         <v/>
       </c>
@@ -8822,7 +8938,7 @@
         <f>日程表１!H6</f>
         <v/>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -8831,15 +8947,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="341">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="360">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="338">
+      <c r="M6" s="359">
         <f>日程表１!M6</f>
         <v/>
       </c>
@@ -8847,15 +8963,15 @@
         <f>日程表１!N6</f>
         <v/>
       </c>
-      <c r="O6" s="31" t="n"/>
+      <c r="O6" s="340" t="n"/>
       <c r="P6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="32" t="n"/>
-      <c r="R6" s="29" t="n"/>
-      <c r="S6" s="338">
+      <c r="Q6" s="341" t="n"/>
+      <c r="R6" s="360" t="n"/>
+      <c r="S6" s="359">
         <f>日程表１!S7</f>
         <v/>
       </c>
@@ -8863,17 +8979,17 @@
         <f>日程表１!T7</f>
         <v/>
       </c>
-      <c r="U6" s="31" t="n"/>
+      <c r="U6" s="340" t="n"/>
       <c r="V6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="33" t="n"/>
-      <c r="X6" s="251" t="n"/>
+      <c r="W6" s="363" t="n"/>
+      <c r="X6" s="362" t="n"/>
     </row>
     <row r="7" ht="20.45" customHeight="1" s="257">
-      <c r="A7" s="338">
+      <c r="A7" s="359">
         <f>日程表１!A7</f>
         <v/>
       </c>
@@ -8881,15 +8997,15 @@
         <f>日程表１!B7</f>
         <v/>
       </c>
-      <c r="C7" s="31" t="n"/>
+      <c r="C7" s="340" t="n"/>
       <c r="D7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="29" t="n"/>
-      <c r="G7" s="338">
+      <c r="E7" s="341" t="n"/>
+      <c r="F7" s="360" t="n"/>
+      <c r="G7" s="359">
         <f>日程表１!G7</f>
         <v/>
       </c>
@@ -8897,7 +9013,7 @@
         <f>日程表１!H7</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="340">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -8906,15 +9022,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="341">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="360">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="338">
+      <c r="M7" s="359">
         <f>日程表１!M7</f>
         <v/>
       </c>
@@ -8922,15 +9038,15 @@
         <f>日程表１!N7</f>
         <v/>
       </c>
-      <c r="O7" s="31" t="n"/>
+      <c r="O7" s="340" t="n"/>
       <c r="P7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="32" t="n"/>
-      <c r="R7" s="29" t="n"/>
-      <c r="S7" s="338">
+      <c r="Q7" s="341" t="n"/>
+      <c r="R7" s="360" t="n"/>
+      <c r="S7" s="359">
         <f>日程表１!S8</f>
         <v/>
       </c>
@@ -8938,17 +9054,17 @@
         <f>日程表１!T8</f>
         <v/>
       </c>
-      <c r="U7" s="31" t="n"/>
+      <c r="U7" s="340" t="n"/>
       <c r="V7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="33" t="n"/>
-      <c r="X7" s="251" t="n"/>
+      <c r="W7" s="363" t="n"/>
+      <c r="X7" s="362" t="n"/>
     </row>
     <row r="8" ht="20.45" customHeight="1" s="257">
-      <c r="A8" s="338">
+      <c r="A8" s="359">
         <f>日程表１!A8</f>
         <v/>
       </c>
@@ -8956,15 +9072,15 @@
         <f>日程表１!B8</f>
         <v/>
       </c>
-      <c r="C8" s="31" t="n"/>
+      <c r="C8" s="340" t="n"/>
       <c r="D8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="338">
+      <c r="E8" s="341" t="n"/>
+      <c r="F8" s="360" t="n"/>
+      <c r="G8" s="359">
         <f>日程表１!G8</f>
         <v/>
       </c>
@@ -8972,15 +9088,15 @@
         <f>日程表１!H8</f>
         <v/>
       </c>
-      <c r="I8" s="43" t="n"/>
+      <c r="I8" s="342" t="n"/>
       <c r="J8" s="44" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="45" t="n"/>
-      <c r="L8" s="29" t="n"/>
-      <c r="M8" s="338">
+      <c r="K8" s="343" t="n"/>
+      <c r="L8" s="360" t="n"/>
+      <c r="M8" s="359">
         <f>日程表１!M8</f>
         <v/>
       </c>
@@ -8988,15 +9104,15 @@
         <f>日程表１!N8</f>
         <v/>
       </c>
-      <c r="O8" s="31" t="n"/>
+      <c r="O8" s="340" t="n"/>
       <c r="P8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="32" t="n"/>
-      <c r="R8" s="29" t="n"/>
-      <c r="S8" s="338">
+      <c r="Q8" s="341" t="n"/>
+      <c r="R8" s="360" t="n"/>
+      <c r="S8" s="359">
         <f>日程表１!S9</f>
         <v/>
       </c>
@@ -9004,17 +9120,17 @@
         <f>日程表１!T9</f>
         <v/>
       </c>
-      <c r="U8" s="31" t="n"/>
+      <c r="U8" s="340" t="n"/>
       <c r="V8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="33" t="n"/>
-      <c r="X8" s="251" t="n"/>
+      <c r="W8" s="363" t="n"/>
+      <c r="X8" s="362" t="n"/>
     </row>
     <row r="9" ht="20.45" customHeight="1" s="257">
-      <c r="A9" s="338">
+      <c r="A9" s="359">
         <f>日程表１!A9</f>
         <v/>
       </c>
@@ -9022,15 +9138,15 @@
         <f>日程表１!B9</f>
         <v/>
       </c>
-      <c r="C9" s="31" t="n"/>
+      <c r="C9" s="340" t="n"/>
       <c r="D9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="338">
+      <c r="E9" s="341" t="n"/>
+      <c r="F9" s="360" t="n"/>
+      <c r="G9" s="359">
         <f>日程表１!G9</f>
         <v/>
       </c>
@@ -9038,15 +9154,15 @@
         <f>日程表１!H9</f>
         <v/>
       </c>
-      <c r="I9" s="31" t="n"/>
+      <c r="I9" s="340" t="n"/>
       <c r="J9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="29" t="n"/>
-      <c r="M9" s="338">
+      <c r="K9" s="341" t="n"/>
+      <c r="L9" s="360" t="n"/>
+      <c r="M9" s="359">
         <f>日程表１!M9</f>
         <v/>
       </c>
@@ -9054,15 +9170,15 @@
         <f>日程表１!N9</f>
         <v/>
       </c>
-      <c r="O9" s="31" t="n"/>
+      <c r="O9" s="340" t="n"/>
       <c r="P9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="32" t="n"/>
-      <c r="R9" s="29" t="n"/>
-      <c r="S9" s="338">
+      <c r="Q9" s="341" t="n"/>
+      <c r="R9" s="360" t="n"/>
+      <c r="S9" s="359">
         <f>日程表１!S10</f>
         <v/>
       </c>
@@ -9070,17 +9186,17 @@
         <f>日程表１!T10</f>
         <v/>
       </c>
-      <c r="U9" s="31" t="n"/>
+      <c r="U9" s="340" t="n"/>
       <c r="V9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="33" t="n"/>
-      <c r="X9" s="251" t="n"/>
+      <c r="W9" s="363" t="n"/>
+      <c r="X9" s="362" t="n"/>
     </row>
     <row r="10" ht="20.45" customHeight="1" s="257">
-      <c r="A10" s="338">
+      <c r="A10" s="359">
         <f>日程表１!A10</f>
         <v/>
       </c>
@@ -9088,15 +9204,15 @@
         <f>日程表１!B10</f>
         <v/>
       </c>
-      <c r="C10" s="31" t="n"/>
+      <c r="C10" s="340" t="n"/>
       <c r="D10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="338">
+      <c r="E10" s="341" t="n"/>
+      <c r="F10" s="360" t="n"/>
+      <c r="G10" s="359">
         <f>日程表１!G10</f>
         <v/>
       </c>
@@ -9104,15 +9220,15 @@
         <f>日程表１!H10</f>
         <v/>
       </c>
-      <c r="I10" s="31" t="n"/>
+      <c r="I10" s="340" t="n"/>
       <c r="J10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="338">
+      <c r="K10" s="341" t="n"/>
+      <c r="L10" s="360" t="n"/>
+      <c r="M10" s="359">
         <f>日程表１!M10</f>
         <v/>
       </c>
@@ -9120,15 +9236,15 @@
         <f>日程表１!N10</f>
         <v/>
       </c>
-      <c r="O10" s="31" t="n"/>
+      <c r="O10" s="340" t="n"/>
       <c r="P10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="32" t="n"/>
-      <c r="R10" s="29" t="n"/>
-      <c r="S10" s="338">
+      <c r="Q10" s="341" t="n"/>
+      <c r="R10" s="360" t="n"/>
+      <c r="S10" s="359">
         <f>日程表１!S11</f>
         <v/>
       </c>
@@ -9136,17 +9252,17 @@
         <f>日程表１!T11</f>
         <v/>
       </c>
-      <c r="U10" s="31" t="n"/>
+      <c r="U10" s="340" t="n"/>
       <c r="V10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="33" t="n"/>
-      <c r="X10" s="251" t="n"/>
+      <c r="W10" s="363" t="n"/>
+      <c r="X10" s="362" t="n"/>
     </row>
     <row r="11" ht="20.45" customHeight="1" s="257">
-      <c r="A11" s="338">
+      <c r="A11" s="359">
         <f>日程表１!A11</f>
         <v/>
       </c>
@@ -9154,15 +9270,15 @@
         <f>日程表１!B11</f>
         <v/>
       </c>
-      <c r="C11" s="43" t="n"/>
+      <c r="C11" s="342" t="n"/>
       <c r="D11" s="44" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="338">
+      <c r="E11" s="343" t="n"/>
+      <c r="F11" s="360" t="n"/>
+      <c r="G11" s="359">
         <f>日程表１!G11</f>
         <v/>
       </c>
@@ -9170,15 +9286,15 @@
         <f>日程表１!H11</f>
         <v/>
       </c>
-      <c r="I11" s="31" t="n"/>
+      <c r="I11" s="340" t="n"/>
       <c r="J11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="29" t="n"/>
-      <c r="M11" s="338">
+      <c r="K11" s="341" t="n"/>
+      <c r="L11" s="360" t="n"/>
+      <c r="M11" s="359">
         <f>日程表１!M11</f>
         <v/>
       </c>
@@ -9186,15 +9302,15 @@
         <f>日程表１!N11</f>
         <v/>
       </c>
-      <c r="O11" s="31" t="n"/>
+      <c r="O11" s="340" t="n"/>
       <c r="P11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="32" t="n"/>
-      <c r="R11" s="29" t="n"/>
-      <c r="S11" s="338">
+      <c r="Q11" s="341" t="n"/>
+      <c r="R11" s="360" t="n"/>
+      <c r="S11" s="359">
         <f>日程表１!S12</f>
         <v/>
       </c>
@@ -9202,17 +9318,17 @@
         <f>日程表１!T12</f>
         <v/>
       </c>
-      <c r="U11" s="31" t="n"/>
+      <c r="U11" s="340" t="n"/>
       <c r="V11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="33" t="n"/>
-      <c r="X11" s="251" t="n"/>
+      <c r="W11" s="363" t="n"/>
+      <c r="X11" s="362" t="n"/>
     </row>
     <row r="12" ht="20.45" customHeight="1" s="257">
-      <c r="A12" s="338">
+      <c r="A12" s="359">
         <f>日程表１!A12</f>
         <v/>
       </c>
@@ -9220,15 +9336,15 @@
         <f>日程表１!B12</f>
         <v/>
       </c>
-      <c r="C12" s="31" t="n"/>
+      <c r="C12" s="340" t="n"/>
       <c r="D12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="338">
+      <c r="E12" s="341" t="n"/>
+      <c r="F12" s="360" t="n"/>
+      <c r="G12" s="359">
         <f>日程表１!G12</f>
         <v/>
       </c>
@@ -9236,7 +9352,7 @@
         <f>日程表１!H12</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -9245,15 +9361,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="341">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="29">
+      <c r="L12" s="360">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="338">
+      <c r="M12" s="359">
         <f>日程表１!M12</f>
         <v/>
       </c>
@@ -9261,15 +9377,15 @@
         <f>日程表１!N12</f>
         <v/>
       </c>
-      <c r="O12" s="31" t="n"/>
+      <c r="O12" s="340" t="n"/>
       <c r="P12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="32" t="n"/>
-      <c r="R12" s="29" t="n"/>
-      <c r="S12" s="338">
+      <c r="Q12" s="341" t="n"/>
+      <c r="R12" s="360" t="n"/>
+      <c r="S12" s="359">
         <f>日程表１!S13</f>
         <v/>
       </c>
@@ -9277,17 +9393,17 @@
         <f>日程表１!T13</f>
         <v/>
       </c>
-      <c r="U12" s="31" t="n"/>
+      <c r="U12" s="340" t="n"/>
       <c r="V12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="33" t="n"/>
-      <c r="X12" s="251" t="n"/>
+      <c r="W12" s="363" t="n"/>
+      <c r="X12" s="362" t="n"/>
     </row>
     <row r="13" ht="20.45" customHeight="1" s="257">
-      <c r="A13" s="338">
+      <c r="A13" s="359">
         <f>日程表１!A13</f>
         <v/>
       </c>
@@ -9295,15 +9411,15 @@
         <f>日程表１!B13</f>
         <v/>
       </c>
-      <c r="C13" s="31" t="n"/>
+      <c r="C13" s="340" t="n"/>
       <c r="D13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="338">
+      <c r="E13" s="341" t="n"/>
+      <c r="F13" s="360" t="n"/>
+      <c r="G13" s="359">
         <f>日程表１!G13</f>
         <v/>
       </c>
@@ -9311,7 +9427,7 @@
         <f>日程表１!H13</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="340">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -9320,15 +9436,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="341">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="360">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="338">
+      <c r="M13" s="359">
         <f>日程表１!M13</f>
         <v/>
       </c>
@@ -9336,15 +9452,15 @@
         <f>日程表１!N13</f>
         <v/>
       </c>
-      <c r="O13" s="31" t="n"/>
+      <c r="O13" s="340" t="n"/>
       <c r="P13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="32" t="n"/>
-      <c r="R13" s="29" t="n"/>
-      <c r="S13" s="338" t="n">
+      <c r="Q13" s="341" t="n"/>
+      <c r="R13" s="360" t="n"/>
+      <c r="S13" s="359" t="n">
         <v>10</v>
       </c>
       <c r="T13" s="29" t="inlineStr">
@@ -9352,17 +9468,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U13" s="31" t="n"/>
+      <c r="U13" s="340" t="n"/>
       <c r="V13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="33" t="n"/>
-      <c r="X13" s="251" t="n"/>
+      <c r="W13" s="363" t="n"/>
+      <c r="X13" s="362" t="n"/>
     </row>
     <row r="14" ht="20.45" customHeight="1" s="257">
-      <c r="A14" s="338">
+      <c r="A14" s="359">
         <f>日程表１!A14</f>
         <v/>
       </c>
@@ -9370,15 +9486,15 @@
         <f>日程表１!B14</f>
         <v/>
       </c>
-      <c r="C14" s="31" t="n"/>
+      <c r="C14" s="340" t="n"/>
       <c r="D14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="338">
+      <c r="E14" s="341" t="n"/>
+      <c r="F14" s="360" t="n"/>
+      <c r="G14" s="359">
         <f>日程表１!G14</f>
         <v/>
       </c>
@@ -9386,7 +9502,7 @@
         <f>日程表１!H14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="340">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9395,15 +9511,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="360">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="338">
+      <c r="M14" s="359">
         <f>日程表１!M14</f>
         <v/>
       </c>
@@ -9411,23 +9527,23 @@
         <f>日程表１!N14</f>
         <v/>
       </c>
-      <c r="O14" s="31" t="n"/>
+      <c r="O14" s="340" t="n"/>
       <c r="P14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="32" t="n"/>
-      <c r="R14" s="29" t="n"/>
+      <c r="Q14" s="341" t="n"/>
+      <c r="R14" s="360" t="n"/>
       <c r="S14" s="256" t="n"/>
       <c r="T14" s="256" t="n"/>
-      <c r="U14" s="256" t="n"/>
+      <c r="U14" s="349" t="n"/>
       <c r="V14" s="255" t="n"/>
-      <c r="W14" s="255" t="n"/>
-      <c r="X14" s="255" t="n"/>
+      <c r="W14" s="350" t="n"/>
+      <c r="X14" s="350" t="n"/>
     </row>
     <row r="15" ht="20.45" customHeight="1" s="257">
-      <c r="A15" s="338">
+      <c r="A15" s="359">
         <f>日程表１!A15</f>
         <v/>
       </c>
@@ -9435,15 +9551,15 @@
         <f>日程表１!B15</f>
         <v/>
       </c>
-      <c r="C15" s="31" t="n"/>
+      <c r="C15" s="340" t="n"/>
       <c r="D15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="338">
+      <c r="E15" s="341" t="n"/>
+      <c r="F15" s="360" t="n"/>
+      <c r="G15" s="359">
         <f>日程表１!G15</f>
         <v/>
       </c>
@@ -9451,15 +9567,15 @@
         <f>日程表１!H15</f>
         <v/>
       </c>
-      <c r="I15" s="31" t="n"/>
+      <c r="I15" s="340" t="n"/>
       <c r="J15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="338">
+      <c r="K15" s="341" t="n"/>
+      <c r="L15" s="360" t="n"/>
+      <c r="M15" s="359">
         <f>日程表１!M15</f>
         <v/>
       </c>
@@ -9467,23 +9583,23 @@
         <f>日程表１!N15</f>
         <v/>
       </c>
-      <c r="O15" s="31" t="n"/>
+      <c r="O15" s="340" t="n"/>
       <c r="P15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="32" t="n"/>
-      <c r="R15" s="29" t="n"/>
+      <c r="Q15" s="341" t="n"/>
+      <c r="R15" s="360" t="n"/>
       <c r="S15" s="256" t="n"/>
       <c r="T15" s="256" t="n"/>
-      <c r="U15" s="256" t="n"/>
+      <c r="U15" s="349" t="n"/>
       <c r="V15" s="255" t="n"/>
-      <c r="W15" s="255" t="n"/>
-      <c r="X15" s="255" t="n"/>
+      <c r="W15" s="350" t="n"/>
+      <c r="X15" s="350" t="n"/>
     </row>
     <row r="16" ht="20.45" customHeight="1" s="257">
-      <c r="A16" s="338">
+      <c r="A16" s="359">
         <f>日程表１!A16</f>
         <v/>
       </c>
@@ -9491,15 +9607,15 @@
         <f>日程表１!B16</f>
         <v/>
       </c>
-      <c r="C16" s="31" t="n"/>
+      <c r="C16" s="340" t="n"/>
       <c r="D16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="338">
+      <c r="E16" s="341" t="n"/>
+      <c r="F16" s="360" t="n"/>
+      <c r="G16" s="359">
         <f>日程表１!G16</f>
         <v/>
       </c>
@@ -9507,15 +9623,15 @@
         <f>日程表１!H16</f>
         <v/>
       </c>
-      <c r="I16" s="31" t="n"/>
+      <c r="I16" s="340" t="n"/>
       <c r="J16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="29" t="n"/>
-      <c r="M16" s="338">
+      <c r="K16" s="341" t="n"/>
+      <c r="L16" s="360" t="n"/>
+      <c r="M16" s="359">
         <f>日程表１!M16</f>
         <v/>
       </c>
@@ -9523,23 +9639,23 @@
         <f>日程表１!N16</f>
         <v/>
       </c>
-      <c r="O16" s="31" t="n"/>
+      <c r="O16" s="340" t="n"/>
       <c r="P16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="29" t="n"/>
+      <c r="Q16" s="341" t="n"/>
+      <c r="R16" s="360" t="n"/>
       <c r="S16" s="256" t="n"/>
       <c r="T16" s="256" t="n"/>
-      <c r="U16" s="256" t="n"/>
+      <c r="U16" s="349" t="n"/>
       <c r="V16" s="255" t="n"/>
-      <c r="W16" s="255" t="n"/>
-      <c r="X16" s="255" t="n"/>
+      <c r="W16" s="350" t="n"/>
+      <c r="X16" s="350" t="n"/>
     </row>
     <row r="17" ht="20.45" customHeight="1" s="257">
-      <c r="A17" s="338">
+      <c r="A17" s="359">
         <f>日程表１!A17</f>
         <v/>
       </c>
@@ -9547,15 +9663,15 @@
         <f>日程表１!B17</f>
         <v/>
       </c>
-      <c r="C17" s="31" t="n"/>
+      <c r="C17" s="340" t="n"/>
       <c r="D17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="338">
+      <c r="E17" s="341" t="n"/>
+      <c r="F17" s="360" t="n"/>
+      <c r="G17" s="359">
         <f>日程表１!G17</f>
         <v/>
       </c>
@@ -9563,15 +9679,15 @@
         <f>日程表１!H17</f>
         <v/>
       </c>
-      <c r="I17" s="31" t="n"/>
+      <c r="I17" s="340" t="n"/>
       <c r="J17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="338">
+      <c r="K17" s="341" t="n"/>
+      <c r="L17" s="360" t="n"/>
+      <c r="M17" s="359">
         <f>日程表１!M17</f>
         <v/>
       </c>
@@ -9579,14 +9695,14 @@
         <f>日程表１!N17</f>
         <v/>
       </c>
-      <c r="O17" s="31" t="n"/>
+      <c r="O17" s="340" t="n"/>
       <c r="P17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="29" t="n"/>
+      <c r="Q17" s="341" t="n"/>
+      <c r="R17" s="360" t="n"/>
       <c r="S17" s="254" t="inlineStr">
         <is>
           <t>NO.</t>
@@ -9603,7 +9719,7 @@
       <c r="X17" s="279" t="n"/>
     </row>
     <row r="18" ht="20.45" customHeight="1" s="257">
-      <c r="A18" s="338">
+      <c r="A18" s="359">
         <f>日程表１!A18</f>
         <v/>
       </c>
@@ -9611,15 +9727,15 @@
         <f>日程表１!B18</f>
         <v/>
       </c>
-      <c r="C18" s="43" t="n"/>
+      <c r="C18" s="342" t="n"/>
       <c r="D18" s="44" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="29" t="n"/>
-      <c r="G18" s="338">
+      <c r="E18" s="343" t="n"/>
+      <c r="F18" s="360" t="n"/>
+      <c r="G18" s="359">
         <f>日程表１!G18</f>
         <v/>
       </c>
@@ -9627,15 +9743,15 @@
         <f>日程表１!H18</f>
         <v/>
       </c>
-      <c r="I18" s="31" t="n"/>
+      <c r="I18" s="340" t="n"/>
       <c r="J18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="29" t="n"/>
-      <c r="M18" s="338">
+      <c r="K18" s="341" t="n"/>
+      <c r="L18" s="360" t="n"/>
+      <c r="M18" s="359">
         <f>日程表１!M18</f>
         <v/>
       </c>
@@ -9643,14 +9759,14 @@
         <f>日程表１!N18</f>
         <v/>
       </c>
-      <c r="O18" s="31" t="n"/>
+      <c r="O18" s="340" t="n"/>
       <c r="P18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="32" t="n"/>
-      <c r="R18" s="29" t="n"/>
+      <c r="Q18" s="341" t="n"/>
+      <c r="R18" s="360" t="n"/>
       <c r="S18" s="254" t="n">
         <v>1</v>
       </c>
@@ -9664,7 +9780,7 @@
       <c r="X18" s="279" t="n"/>
     </row>
     <row r="19" ht="20.45" customHeight="1" s="257">
-      <c r="A19" s="338">
+      <c r="A19" s="359">
         <f>日程表１!A19</f>
         <v/>
       </c>
@@ -9672,15 +9788,15 @@
         <f>日程表１!B19</f>
         <v/>
       </c>
-      <c r="C19" s="31" t="n"/>
+      <c r="C19" s="340" t="n"/>
       <c r="D19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="29" t="n"/>
-      <c r="G19" s="338">
+      <c r="E19" s="341" t="n"/>
+      <c r="F19" s="360" t="n"/>
+      <c r="G19" s="359">
         <f>日程表１!G19</f>
         <v/>
       </c>
@@ -9688,15 +9804,15 @@
         <f>日程表１!H19</f>
         <v/>
       </c>
-      <c r="I19" s="31" t="inlineStr">
+      <c r="I19" s="340" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="253" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="29" t="n"/>
-      <c r="M19" s="338">
+      <c r="K19" s="341" t="n"/>
+      <c r="L19" s="360" t="n"/>
+      <c r="M19" s="359">
         <f>日程表１!M19</f>
         <v/>
       </c>
@@ -9704,14 +9820,14 @@
         <f>日程表１!N19</f>
         <v/>
       </c>
-      <c r="O19" s="31" t="n"/>
+      <c r="O19" s="340" t="n"/>
       <c r="P19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="32" t="n"/>
-      <c r="R19" s="29" t="n"/>
+      <c r="Q19" s="341" t="n"/>
+      <c r="R19" s="360" t="n"/>
       <c r="S19" s="254" t="n">
         <v>2</v>
       </c>
@@ -9725,7 +9841,7 @@
       <c r="X19" s="279" t="n"/>
     </row>
     <row r="20" ht="20.45" customHeight="1" s="257">
-      <c r="A20" s="339">
+      <c r="A20" s="364">
         <f>日程表１!A20</f>
         <v/>
       </c>
@@ -9733,15 +9849,15 @@
         <f>日程表１!B20</f>
         <v/>
       </c>
-      <c r="C20" s="31" t="n"/>
+      <c r="C20" s="340" t="n"/>
       <c r="D20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="339">
+      <c r="E20" s="341" t="n"/>
+      <c r="F20" s="360" t="n"/>
+      <c r="G20" s="364">
         <f>日程表１!G20</f>
         <v/>
       </c>
@@ -9749,15 +9865,15 @@
         <f>日程表１!H20</f>
         <v/>
       </c>
-      <c r="I20" s="31" t="inlineStr">
+      <c r="I20" s="340" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="253" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="29" t="n"/>
-      <c r="M20" s="339">
+      <c r="K20" s="341" t="n"/>
+      <c r="L20" s="360" t="n"/>
+      <c r="M20" s="364">
         <f>日程表１!M20</f>
         <v/>
       </c>
@@ -9765,14 +9881,14 @@
         <f>日程表１!N20</f>
         <v/>
       </c>
-      <c r="O20" s="31" t="n"/>
+      <c r="O20" s="340" t="n"/>
       <c r="P20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="32" t="n"/>
-      <c r="R20" s="29" t="n"/>
+      <c r="Q20" s="341" t="n"/>
+      <c r="R20" s="360" t="n"/>
       <c r="S20" s="254" t="n">
         <v>3</v>
       </c>
@@ -9786,7 +9902,7 @@
       <c r="X20" s="279" t="n"/>
     </row>
     <row r="21" ht="20.45" customHeight="1" s="257">
-      <c r="A21" s="338">
+      <c r="A21" s="359">
         <f>日程表１!A21</f>
         <v/>
       </c>
@@ -9794,15 +9910,15 @@
         <f>日程表１!B21</f>
         <v/>
       </c>
-      <c r="C21" s="31" t="n"/>
+      <c r="C21" s="340" t="n"/>
       <c r="D21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="338">
+      <c r="E21" s="341" t="n"/>
+      <c r="F21" s="360" t="n"/>
+      <c r="G21" s="359">
         <f>日程表１!G21</f>
         <v/>
       </c>
@@ -9810,15 +9926,15 @@
         <f>日程表１!H21</f>
         <v/>
       </c>
-      <c r="I21" s="31" t="inlineStr">
+      <c r="I21" s="340" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="253" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="29" t="n"/>
-      <c r="M21" s="338">
+      <c r="K21" s="341" t="n"/>
+      <c r="L21" s="360" t="n"/>
+      <c r="M21" s="359">
         <f>日程表１!M21</f>
         <v/>
       </c>
@@ -9826,14 +9942,14 @@
         <f>日程表１!N21</f>
         <v/>
       </c>
-      <c r="O21" s="31" t="n"/>
+      <c r="O21" s="340" t="n"/>
       <c r="P21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="29" t="n"/>
+      <c r="Q21" s="341" t="n"/>
+      <c r="R21" s="360" t="n"/>
       <c r="S21" s="254" t="n">
         <v>4</v>
       </c>
@@ -9847,7 +9963,7 @@
       <c r="X21" s="279" t="n"/>
     </row>
     <row r="22" ht="20.45" customHeight="1" s="257">
-      <c r="A22" s="338">
+      <c r="A22" s="359">
         <f>日程表１!A22</f>
         <v/>
       </c>
@@ -9855,15 +9971,15 @@
         <f>日程表１!B22</f>
         <v/>
       </c>
-      <c r="C22" s="31" t="n"/>
+      <c r="C22" s="340" t="n"/>
       <c r="D22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="29" t="n"/>
-      <c r="G22" s="338">
+      <c r="E22" s="341" t="n"/>
+      <c r="F22" s="360" t="n"/>
+      <c r="G22" s="359">
         <f>日程表１!G22</f>
         <v/>
       </c>
@@ -9871,15 +9987,15 @@
         <f>日程表１!H22</f>
         <v/>
       </c>
-      <c r="I22" s="31" t="n"/>
+      <c r="I22" s="340" t="n"/>
       <c r="J22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="29" t="n"/>
-      <c r="M22" s="338">
+      <c r="K22" s="341" t="n"/>
+      <c r="L22" s="360" t="n"/>
+      <c r="M22" s="359">
         <f>日程表１!M22</f>
         <v/>
       </c>
@@ -9887,14 +10003,14 @@
         <f>日程表１!N22</f>
         <v/>
       </c>
-      <c r="O22" s="31" t="n"/>
+      <c r="O22" s="340" t="n"/>
       <c r="P22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="32" t="n"/>
-      <c r="R22" s="29" t="n"/>
+      <c r="Q22" s="341" t="n"/>
+      <c r="R22" s="360" t="n"/>
       <c r="S22" s="254" t="n">
         <v>5</v>
       </c>
@@ -9908,7 +10024,7 @@
       <c r="X22" s="279" t="n"/>
     </row>
     <row r="23" ht="20.45" customHeight="1" s="257">
-      <c r="A23" s="338">
+      <c r="A23" s="359">
         <f>日程表１!A23</f>
         <v/>
       </c>
@@ -9916,15 +10032,15 @@
         <f>日程表１!B23</f>
         <v/>
       </c>
-      <c r="C23" s="31" t="n"/>
+      <c r="C23" s="340" t="n"/>
       <c r="D23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="29" t="n"/>
-      <c r="G23" s="338">
+      <c r="E23" s="341" t="n"/>
+      <c r="F23" s="360" t="n"/>
+      <c r="G23" s="359">
         <f>日程表１!G23</f>
         <v/>
       </c>
@@ -9932,15 +10048,15 @@
         <f>日程表１!H23</f>
         <v/>
       </c>
-      <c r="I23" s="31" t="n"/>
+      <c r="I23" s="340" t="n"/>
       <c r="J23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="29" t="n"/>
-      <c r="M23" s="338">
+      <c r="K23" s="341" t="n"/>
+      <c r="L23" s="360" t="n"/>
+      <c r="M23" s="359">
         <f>日程表１!M23</f>
         <v/>
       </c>
@@ -9948,14 +10064,14 @@
         <f>日程表１!N23</f>
         <v/>
       </c>
-      <c r="O23" s="31" t="n"/>
+      <c r="O23" s="340" t="n"/>
       <c r="P23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="29" t="n"/>
+      <c r="Q23" s="341" t="n"/>
+      <c r="R23" s="360" t="n"/>
       <c r="S23" s="254" t="n">
         <v>6</v>
       </c>
@@ -9969,7 +10085,7 @@
       <c r="X23" s="279" t="n"/>
     </row>
     <row r="24" ht="20.45" customHeight="1" s="257">
-      <c r="A24" s="338">
+      <c r="A24" s="359">
         <f>日程表１!A24</f>
         <v/>
       </c>
@@ -9977,15 +10093,15 @@
         <f>日程表１!B24</f>
         <v/>
       </c>
-      <c r="C24" s="31" t="n"/>
+      <c r="C24" s="340" t="n"/>
       <c r="D24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="29" t="n"/>
-      <c r="G24" s="338">
+      <c r="E24" s="341" t="n"/>
+      <c r="F24" s="360" t="n"/>
+      <c r="G24" s="359">
         <f>日程表１!G24</f>
         <v/>
       </c>
@@ -9993,15 +10109,15 @@
         <f>日程表１!H24</f>
         <v/>
       </c>
-      <c r="I24" s="31" t="n"/>
+      <c r="I24" s="340" t="n"/>
       <c r="J24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="29" t="n"/>
-      <c r="M24" s="338">
+      <c r="K24" s="341" t="n"/>
+      <c r="L24" s="360" t="n"/>
+      <c r="M24" s="359">
         <f>日程表１!M24</f>
         <v/>
       </c>
@@ -10009,14 +10125,14 @@
         <f>日程表１!N24</f>
         <v/>
       </c>
-      <c r="O24" s="31" t="n"/>
+      <c r="O24" s="340" t="n"/>
       <c r="P24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="32" t="n"/>
-      <c r="R24" s="29" t="n"/>
+      <c r="Q24" s="341" t="n"/>
+      <c r="R24" s="360" t="n"/>
       <c r="S24" s="254" t="n">
         <v>7</v>
       </c>
@@ -10030,7 +10146,7 @@
       <c r="X24" s="279" t="n"/>
     </row>
     <row r="25" ht="20.45" customHeight="1" s="257">
-      <c r="A25" s="338">
+      <c r="A25" s="359">
         <f>日程表１!A25</f>
         <v/>
       </c>
@@ -10038,15 +10154,15 @@
         <f>日程表１!B25</f>
         <v/>
       </c>
-      <c r="C25" s="43" t="n"/>
+      <c r="C25" s="342" t="n"/>
       <c r="D25" s="44" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="45" t="n"/>
-      <c r="F25" s="29" t="n"/>
-      <c r="G25" s="338">
+      <c r="E25" s="343" t="n"/>
+      <c r="F25" s="360" t="n"/>
+      <c r="G25" s="359">
         <f>日程表１!G25</f>
         <v/>
       </c>
@@ -10054,15 +10170,15 @@
         <f>日程表１!H25</f>
         <v/>
       </c>
-      <c r="I25" s="31" t="n"/>
+      <c r="I25" s="340" t="n"/>
       <c r="J25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="29" t="n"/>
-      <c r="M25" s="338">
+      <c r="K25" s="341" t="n"/>
+      <c r="L25" s="360" t="n"/>
+      <c r="M25" s="359">
         <f>日程表１!M25</f>
         <v/>
       </c>
@@ -10070,14 +10186,14 @@
         <f>日程表１!N25</f>
         <v/>
       </c>
-      <c r="O25" s="31" t="n"/>
+      <c r="O25" s="340" t="n"/>
       <c r="P25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="32" t="n"/>
-      <c r="R25" s="29" t="n"/>
+      <c r="Q25" s="341" t="n"/>
+      <c r="R25" s="360" t="n"/>
       <c r="S25" s="254" t="n">
         <v>8</v>
       </c>
@@ -10091,7 +10207,7 @@
       <c r="X25" s="279" t="n"/>
     </row>
     <row r="26" ht="20.45" customHeight="1" s="257">
-      <c r="A26" s="338">
+      <c r="A26" s="359">
         <f>日程表１!A26</f>
         <v/>
       </c>
@@ -10099,15 +10215,15 @@
         <f>日程表１!B26</f>
         <v/>
       </c>
-      <c r="C26" s="31" t="n"/>
+      <c r="C26" s="340" t="n"/>
       <c r="D26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="29" t="n"/>
-      <c r="G26" s="338">
+      <c r="E26" s="341" t="n"/>
+      <c r="F26" s="360" t="n"/>
+      <c r="G26" s="359">
         <f>日程表１!G26</f>
         <v/>
       </c>
@@ -10115,7 +10231,7 @@
         <f>日程表１!H26</f>
         <v/>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -10124,15 +10240,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K26" s="32">
+      <c r="K26" s="341">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="360">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="338">
+      <c r="M26" s="359">
         <f>日程表１!M26</f>
         <v/>
       </c>
@@ -10140,14 +10256,14 @@
         <f>日程表１!N26</f>
         <v/>
       </c>
-      <c r="O26" s="31" t="n"/>
+      <c r="O26" s="340" t="n"/>
       <c r="P26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="29" t="n"/>
+      <c r="Q26" s="341" t="n"/>
+      <c r="R26" s="360" t="n"/>
       <c r="S26" s="254" t="n">
         <v>9</v>
       </c>
@@ -10161,7 +10277,7 @@
       <c r="X26" s="279" t="n"/>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="257">
-      <c r="A27" s="338">
+      <c r="A27" s="359">
         <f>日程表１!A27</f>
         <v/>
       </c>
@@ -10169,15 +10285,15 @@
         <f>日程表１!B27</f>
         <v/>
       </c>
-      <c r="C27" s="31" t="n"/>
+      <c r="C27" s="340" t="n"/>
       <c r="D27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="338">
+      <c r="E27" s="341" t="n"/>
+      <c r="F27" s="360" t="n"/>
+      <c r="G27" s="359">
         <f>日程表１!G27</f>
         <v/>
       </c>
@@ -10185,7 +10301,7 @@
         <f>日程表１!H27</f>
         <v/>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10194,15 +10310,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="341">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="360">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="338">
+      <c r="M27" s="359">
         <f>日程表１!M27</f>
         <v/>
       </c>
@@ -10210,14 +10326,14 @@
         <f>日程表１!N27</f>
         <v/>
       </c>
-      <c r="O27" s="31" t="n"/>
+      <c r="O27" s="340" t="n"/>
       <c r="P27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="32" t="n"/>
-      <c r="R27" s="29" t="n"/>
+      <c r="Q27" s="341" t="n"/>
+      <c r="R27" s="360" t="n"/>
       <c r="S27" s="254" t="n">
         <v>10</v>
       </c>
@@ -10231,7 +10347,7 @@
       <c r="X27" s="279" t="n"/>
     </row>
     <row r="28" ht="20.45" customHeight="1" s="257">
-      <c r="A28" s="339">
+      <c r="A28" s="364">
         <f>日程表１!A28</f>
         <v/>
       </c>
@@ -10239,15 +10355,15 @@
         <f>日程表１!B28</f>
         <v/>
       </c>
-      <c r="C28" s="31" t="n"/>
+      <c r="C28" s="340" t="n"/>
       <c r="D28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="29" t="n"/>
-      <c r="G28" s="339">
+      <c r="E28" s="341" t="n"/>
+      <c r="F28" s="360" t="n"/>
+      <c r="G28" s="364">
         <f>日程表１!G28</f>
         <v/>
       </c>
@@ -10255,7 +10371,7 @@
         <f>日程表１!H28</f>
         <v/>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="340">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -10264,15 +10380,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="29">
+      <c r="L28" s="360">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="339">
+      <c r="M28" s="364">
         <f>日程表１!M28</f>
         <v/>
       </c>
@@ -10280,14 +10396,14 @@
         <f>日程表１!N28</f>
         <v/>
       </c>
-      <c r="O28" s="31" t="n"/>
+      <c r="O28" s="340" t="n"/>
       <c r="P28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="32" t="n"/>
-      <c r="R28" s="29" t="n"/>
+      <c r="Q28" s="341" t="n"/>
+      <c r="R28" s="360" t="n"/>
       <c r="S28" s="254" t="n">
         <v>11</v>
       </c>
@@ -10301,7 +10417,7 @@
       <c r="X28" s="279" t="n"/>
     </row>
     <row r="29" ht="20.45" customHeight="1" s="257">
-      <c r="A29" s="338">
+      <c r="A29" s="359">
         <f>日程表１!A29</f>
         <v/>
       </c>
@@ -10309,7 +10425,7 @@
         <f>日程表１!B29</f>
         <v/>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10318,15 +10434,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="341">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="360">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="338">
+      <c r="G29" s="359">
         <f>日程表１!G29</f>
         <v/>
       </c>
@@ -10334,15 +10450,15 @@
         <f>日程表１!H29</f>
         <v/>
       </c>
-      <c r="I29" s="31" t="n"/>
+      <c r="I29" s="340" t="n"/>
       <c r="J29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K29" s="32" t="n"/>
-      <c r="L29" s="29" t="n"/>
-      <c r="M29" s="338">
+      <c r="K29" s="341" t="n"/>
+      <c r="L29" s="360" t="n"/>
+      <c r="M29" s="359">
         <f>日程表１!M29</f>
         <v/>
       </c>
@@ -10350,23 +10466,23 @@
         <f>日程表１!N29</f>
         <v/>
       </c>
-      <c r="O29" s="31" t="n"/>
+      <c r="O29" s="340" t="n"/>
       <c r="P29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="32" t="n"/>
-      <c r="R29" s="29" t="n"/>
+      <c r="Q29" s="341" t="n"/>
+      <c r="R29" s="360" t="n"/>
       <c r="S29" s="255" t="n"/>
       <c r="T29" s="255" t="n"/>
-      <c r="U29" s="255" t="n"/>
+      <c r="U29" s="350" t="n"/>
       <c r="V29" s="255" t="n"/>
-      <c r="W29" s="255" t="n"/>
-      <c r="X29" s="255" t="n"/>
+      <c r="W29" s="350" t="n"/>
+      <c r="X29" s="350" t="n"/>
     </row>
     <row r="30" ht="20.45" customHeight="1" s="257">
-      <c r="A30" s="338">
+      <c r="A30" s="359">
         <f>日程表１!A30</f>
         <v/>
       </c>
@@ -10374,7 +10490,7 @@
         <f>日程表１!B30</f>
         <v/>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="340">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -10383,15 +10499,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="360">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="338">
+      <c r="G30" s="359">
         <f>日程表１!G30</f>
         <v/>
       </c>
@@ -10399,15 +10515,15 @@
         <f>日程表１!H30</f>
         <v/>
       </c>
-      <c r="I30" s="31" t="n"/>
+      <c r="I30" s="340" t="n"/>
       <c r="J30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="29" t="n"/>
-      <c r="M30" s="338">
+      <c r="K30" s="341" t="n"/>
+      <c r="L30" s="360" t="n"/>
+      <c r="M30" s="359">
         <f>日程表１!M30</f>
         <v/>
       </c>
@@ -10415,23 +10531,23 @@
         <f>日程表１!N30</f>
         <v/>
       </c>
-      <c r="O30" s="31" t="n"/>
+      <c r="O30" s="340" t="n"/>
       <c r="P30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="32" t="n"/>
-      <c r="R30" s="29" t="n"/>
+      <c r="Q30" s="341" t="n"/>
+      <c r="R30" s="360" t="n"/>
       <c r="S30" s="255" t="n"/>
       <c r="T30" s="255" t="n"/>
-      <c r="U30" s="255" t="n"/>
+      <c r="U30" s="350" t="n"/>
       <c r="V30" s="255" t="n"/>
-      <c r="W30" s="255" t="n"/>
-      <c r="X30" s="255" t="n"/>
+      <c r="W30" s="350" t="n"/>
+      <c r="X30" s="350" t="n"/>
     </row>
     <row r="31" ht="20.45" customHeight="1" s="257">
-      <c r="A31" s="338">
+      <c r="A31" s="359">
         <f>日程表１!A31</f>
         <v/>
       </c>
@@ -10439,7 +10555,7 @@
         <f>日程表１!B31</f>
         <v/>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
@@ -10448,15 +10564,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="341">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="360">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="338">
+      <c r="G31" s="359">
         <f>日程表１!G31</f>
         <v/>
       </c>
@@ -10464,15 +10580,15 @@
         <f>日程表１!H31</f>
         <v/>
       </c>
-      <c r="I31" s="31" t="n"/>
+      <c r="I31" s="340" t="n"/>
       <c r="J31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="29" t="n"/>
-      <c r="M31" s="338">
+      <c r="K31" s="341" t="n"/>
+      <c r="L31" s="360" t="n"/>
+      <c r="M31" s="359">
         <f>日程表１!M31</f>
         <v/>
       </c>
@@ -10480,23 +10596,23 @@
         <f>日程表１!N31</f>
         <v/>
       </c>
-      <c r="O31" s="31" t="n"/>
+      <c r="O31" s="340" t="n"/>
       <c r="P31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="29" t="n"/>
+      <c r="Q31" s="341" t="n"/>
+      <c r="R31" s="360" t="n"/>
       <c r="S31" s="255" t="n"/>
       <c r="T31" s="255" t="n"/>
-      <c r="U31" s="255" t="n"/>
+      <c r="U31" s="350" t="n"/>
       <c r="V31" s="255" t="n"/>
-      <c r="W31" s="255" t="n"/>
-      <c r="X31" s="255" t="n"/>
+      <c r="W31" s="350" t="n"/>
+      <c r="X31" s="350" t="n"/>
     </row>
     <row r="32" ht="20.45" customHeight="1" s="257">
-      <c r="A32" s="338">
+      <c r="A32" s="359">
         <f>日程表１!A32</f>
         <v/>
       </c>
@@ -10504,15 +10620,15 @@
         <f>日程表１!B32</f>
         <v/>
       </c>
-      <c r="C32" s="43" t="n"/>
+      <c r="C32" s="342" t="n"/>
       <c r="D32" s="44" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="45" t="n"/>
-      <c r="F32" s="29" t="n"/>
-      <c r="G32" s="338">
+      <c r="E32" s="343" t="n"/>
+      <c r="F32" s="360" t="n"/>
+      <c r="G32" s="359">
         <f>日程表１!G32</f>
         <v/>
       </c>
@@ -10520,15 +10636,15 @@
         <f>日程表１!H32</f>
         <v/>
       </c>
-      <c r="I32" s="31" t="n"/>
+      <c r="I32" s="340" t="n"/>
       <c r="J32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K32" s="32" t="n"/>
-      <c r="L32" s="29" t="n"/>
-      <c r="M32" s="338">
+      <c r="K32" s="341" t="n"/>
+      <c r="L32" s="360" t="n"/>
+      <c r="M32" s="359">
         <f>日程表１!M32</f>
         <v/>
       </c>
@@ -10536,23 +10652,23 @@
         <f>日程表１!N32</f>
         <v/>
       </c>
-      <c r="O32" s="31" t="n"/>
+      <c r="O32" s="340" t="n"/>
       <c r="P32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="32" t="n"/>
-      <c r="R32" s="29" t="n"/>
+      <c r="Q32" s="341" t="n"/>
+      <c r="R32" s="360" t="n"/>
       <c r="S32" s="255" t="n"/>
       <c r="T32" s="255" t="n"/>
-      <c r="U32" s="255" t="n"/>
+      <c r="U32" s="350" t="n"/>
       <c r="V32" s="255" t="n"/>
-      <c r="W32" s="255" t="n"/>
-      <c r="X32" s="255" t="n"/>
+      <c r="W32" s="350" t="n"/>
+      <c r="X32" s="350" t="n"/>
     </row>
     <row r="33" ht="20.45" customHeight="1" s="257">
-      <c r="A33" s="338">
+      <c r="A33" s="359">
         <f>日程表１!A33</f>
         <v/>
       </c>
@@ -10560,15 +10676,15 @@
         <f>日程表１!B33</f>
         <v/>
       </c>
-      <c r="C33" s="31" t="n"/>
+      <c r="C33" s="340" t="n"/>
       <c r="D33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="29" t="n"/>
-      <c r="G33" s="338">
+      <c r="E33" s="341" t="n"/>
+      <c r="F33" s="360" t="n"/>
+      <c r="G33" s="359">
         <f>日程表１!G33</f>
         <v/>
       </c>
@@ -10576,7 +10692,7 @@
         <f>日程表１!H33</f>
         <v/>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10585,15 +10701,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="341">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="29">
+      <c r="L33" s="360">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="338">
+      <c r="M33" s="359">
         <f>日程表１!M33</f>
         <v/>
       </c>
@@ -10601,23 +10717,23 @@
         <f>日程表１!N33</f>
         <v/>
       </c>
-      <c r="O33" s="31" t="n"/>
+      <c r="O33" s="340" t="n"/>
       <c r="P33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="32" t="n"/>
-      <c r="R33" s="29" t="n"/>
+      <c r="Q33" s="341" t="n"/>
+      <c r="R33" s="360" t="n"/>
       <c r="S33" s="255" t="n"/>
       <c r="T33" s="255" t="n"/>
-      <c r="U33" s="255" t="n"/>
+      <c r="U33" s="350" t="n"/>
       <c r="V33" s="255" t="n"/>
-      <c r="W33" s="255" t="n"/>
-      <c r="X33" s="255" t="n"/>
+      <c r="W33" s="350" t="n"/>
+      <c r="X33" s="350" t="n"/>
     </row>
     <row r="34" ht="20.45" customHeight="1" s="257">
-      <c r="A34" s="338">
+      <c r="A34" s="359">
         <f>日程表１!A34</f>
         <v/>
       </c>
@@ -10625,25 +10741,25 @@
         <f>日程表１!B34</f>
         <v/>
       </c>
-      <c r="C34" s="31" t="n"/>
+      <c r="C34" s="340" t="n"/>
       <c r="D34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="256" t="n"/>
-      <c r="G34" s="338" t="n"/>
+      <c r="E34" s="363" t="n"/>
+      <c r="F34" s="349" t="n"/>
+      <c r="G34" s="359" t="n"/>
       <c r="H34" s="256" t="n"/>
-      <c r="I34" s="31" t="n"/>
+      <c r="I34" s="340" t="n"/>
       <c r="J34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K34" s="32" t="n"/>
-      <c r="L34" s="29" t="n"/>
-      <c r="M34" s="338">
+      <c r="K34" s="341" t="n"/>
+      <c r="L34" s="360" t="n"/>
+      <c r="M34" s="359">
         <f>日程表１!M34</f>
         <v/>
       </c>
@@ -10651,20 +10767,20 @@
         <f>日程表１!N34</f>
         <v/>
       </c>
-      <c r="O34" s="31" t="n"/>
+      <c r="O34" s="340" t="n"/>
       <c r="P34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="32" t="n"/>
-      <c r="R34" s="29" t="n"/>
+      <c r="Q34" s="341" t="n"/>
+      <c r="R34" s="360" t="n"/>
       <c r="S34" s="255" t="n"/>
       <c r="T34" s="255" t="n"/>
-      <c r="U34" s="255" t="n"/>
+      <c r="U34" s="350" t="n"/>
       <c r="V34" s="255" t="n"/>
-      <c r="W34" s="255" t="n"/>
-      <c r="X34" s="255" t="n"/>
+      <c r="W34" s="350" t="n"/>
+      <c r="X34" s="350" t="n"/>
     </row>
     <row r="35" ht="3" customHeight="1" s="257"/>
   </sheetData>
@@ -10704,7 +10820,7 @@
       <formula>"土"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="360" verticalDpi="360"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1" horizontalDpi="360" verticalDpi="360"/>
 </worksheet>
 </file>
--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -238,7 +238,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -305,6 +305,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="lightTrellis">
+        <fgColor rgb="00D97706"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="80">
     <border>
@@ -1301,7 +1307,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="365">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2399,17 +2405,29 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2467,6 +2485,20 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -6296,28 +6328,28 @@
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="330" t="n">
+      <c r="M5" s="342" t="n">
         <v>45109</v>
       </c>
-      <c r="N5" s="69" t="inlineStr">
+      <c r="N5" s="343" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="O5" s="336">
+      <c r="O5" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="84" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="337">
+      <c r="P5" s="345" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="346">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="338">
+      <c r="R5" s="347">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6355,28 +6387,28 @@
       </c>
       <c r="E6" s="341" t="n"/>
       <c r="F6" s="333" t="n"/>
-      <c r="G6" s="330" t="n">
+      <c r="G6" s="342" t="n">
         <v>45080</v>
       </c>
-      <c r="H6" s="70" t="inlineStr">
+      <c r="H6" s="348" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I6" s="340">
+      <c r="I6" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="50" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="341">
+      <c r="J6" s="345" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="346">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="333">
+      <c r="L6" s="347">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -6513,13 +6545,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I8" s="342" t="n"/>
-      <c r="J8" s="66" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K8" s="343" t="n"/>
+      <c r="I8" s="340" t="n"/>
+      <c r="J8" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K8" s="341" t="n"/>
       <c r="L8" s="333" t="n"/>
       <c r="M8" s="330" t="n">
         <v>45112</v>
@@ -6769,28 +6801,28 @@
       </c>
       <c r="E12" s="335" t="n"/>
       <c r="F12" s="333" t="n"/>
-      <c r="G12" s="330" t="n">
+      <c r="G12" s="342" t="n">
         <v>45086</v>
       </c>
-      <c r="H12" s="70" t="inlineStr">
+      <c r="H12" s="348" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I12" s="340">
+      <c r="I12" s="344">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="50" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="341">
+      <c r="J12" s="345" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="346">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="333">
+      <c r="L12" s="347">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -6802,13 +6834,13 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O12" s="342" t="n"/>
-      <c r="P12" s="66" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q12" s="343" t="n"/>
+      <c r="O12" s="340" t="n"/>
+      <c r="P12" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q12" s="341" t="n"/>
       <c r="R12" s="333" t="n"/>
       <c r="S12" s="339" t="n">
         <v>45147</v>
@@ -7002,13 +7034,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I15" s="342" t="n"/>
-      <c r="J15" s="66" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K15" s="343" t="n"/>
+      <c r="I15" s="340" t="n"/>
+      <c r="J15" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K15" s="341" t="n"/>
       <c r="L15" s="333" t="n"/>
       <c r="M15" s="330" t="n">
         <v>45119</v>
@@ -7052,13 +7084,13 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C16" s="342" t="n"/>
-      <c r="D16" s="66" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E16" s="343" t="n"/>
+      <c r="C16" s="340" t="n"/>
+      <c r="D16" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E16" s="341" t="n"/>
       <c r="F16" s="333" t="n"/>
       <c r="G16" s="330" t="n">
         <v>45090</v>
@@ -7223,7 +7255,7 @@
         </is>
       </c>
       <c r="Q18" s="341" t="n"/>
-      <c r="R18" s="344" t="n"/>
+      <c r="R18" s="333" t="n"/>
       <c r="S18" s="339" t="n">
         <v>45153</v>
       </c>
@@ -7289,7 +7321,7 @@
         </is>
       </c>
       <c r="Q19" s="341" t="n"/>
-      <c r="R19" s="344" t="n"/>
+      <c r="R19" s="333" t="n"/>
       <c r="S19" s="339" t="n">
         <v>45154</v>
       </c>
@@ -7355,7 +7387,7 @@
         </is>
       </c>
       <c r="Q20" s="341" t="n"/>
-      <c r="R20" s="344" t="n"/>
+      <c r="R20" s="333" t="n"/>
       <c r="S20" s="339" t="n">
         <v>45155</v>
       </c>
@@ -7422,7 +7454,7 @@
       </c>
       <c r="Q21" s="341" t="n"/>
       <c r="R21" s="333" t="n"/>
-      <c r="S21" s="345" t="n">
+      <c r="S21" s="349" t="n">
         <v>45156</v>
       </c>
       <c r="T21" s="71" t="inlineStr">
@@ -7430,14 +7462,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U21" s="346" t="n"/>
+      <c r="U21" s="350" t="n"/>
       <c r="V21" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W21" s="347" t="n"/>
-      <c r="X21" s="348" t="n"/>
+      <c r="W21" s="351" t="n"/>
+      <c r="X21" s="352" t="n"/>
     </row>
     <row r="22" ht="16.15" customHeight="1" s="257" thickBot="1">
       <c r="A22" s="330" t="n">
@@ -7490,10 +7522,10 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U22" s="349" t="n"/>
+      <c r="U22" s="353" t="n"/>
       <c r="V22" s="238" t="n"/>
-      <c r="W22" s="350" t="n"/>
-      <c r="X22" s="350" t="n"/>
+      <c r="W22" s="354" t="n"/>
+      <c r="X22" s="354" t="n"/>
     </row>
     <row r="23" ht="16.15" customHeight="1" s="257">
       <c r="A23" s="330" t="n">
@@ -7504,13 +7536,13 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C23" s="342" t="n"/>
-      <c r="D23" s="66" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E23" s="343" t="n"/>
+      <c r="C23" s="340" t="n"/>
+      <c r="D23" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E23" s="341" t="n"/>
       <c r="F23" s="333" t="n"/>
       <c r="G23" s="330" t="n">
         <v>45097</v>
@@ -7553,7 +7585,7 @@
       <c r="U23" s="328" t="n"/>
       <c r="V23" s="328" t="n"/>
       <c r="W23" s="328" t="n"/>
-      <c r="X23" s="351" t="n"/>
+      <c r="X23" s="355" t="n"/>
     </row>
     <row r="24" ht="16.15" customHeight="1" s="257">
       <c r="A24" s="330" t="n">
@@ -7688,24 +7720,24 @@
       </c>
       <c r="E26" s="341" t="n"/>
       <c r="F26" s="333" t="n"/>
-      <c r="G26" s="330" t="n">
+      <c r="G26" s="342" t="n">
         <v>45100</v>
       </c>
-      <c r="H26" s="70" t="inlineStr">
+      <c r="H26" s="348" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I26" s="336">
+      <c r="I26" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="84" t="n"/>
-      <c r="K26" s="337">
+      <c r="J26" s="345" t="n"/>
+      <c r="K26" s="346">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="338">
+      <c r="L26" s="347">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -7948,16 +7980,16 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C30" s="342">
+      <c r="C30" s="340">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="D30" s="66" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E30" s="343">
+      <c r="D30" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E30" s="341">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -7996,7 +8028,7 @@
       <c r="S30" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="T30" s="247" t="inlineStr">
+      <c r="T30" s="236" t="inlineStr">
         <is>
           <t>木</t>
         </is>
@@ -8007,28 +8039,28 @@
       <c r="X30" s="279" t="n"/>
     </row>
     <row r="31" ht="16.15" customHeight="1" s="257">
-      <c r="A31" s="330" t="n">
+      <c r="A31" s="342" t="n">
         <v>45074</v>
       </c>
-      <c r="B31" s="69" t="inlineStr">
+      <c r="B31" s="343" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="C31" s="340">
+      <c r="C31" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="50" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="341">
+      <c r="D31" s="345" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="346">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="333">
+      <c r="F31" s="347">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -8148,7 +8180,7 @@
       </c>
       <c r="E33" s="341" t="n"/>
       <c r="F33" s="333" t="n"/>
-      <c r="G33" s="352" t="n">
+      <c r="G33" s="356" t="n">
         <v>45107</v>
       </c>
       <c r="H33" s="82" t="inlineStr">
@@ -8156,16 +8188,16 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I33" s="353">
+      <c r="I33" s="357">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J33" s="88" t="n"/>
-      <c r="K33" s="354">
+      <c r="K33" s="358">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="355">
+      <c r="L33" s="359">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
@@ -8193,13 +8225,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U33" s="356" t="n"/>
-      <c r="V33" s="356" t="n"/>
-      <c r="W33" s="356" t="n"/>
-      <c r="X33" s="357" t="n"/>
+      <c r="U33" s="360" t="n"/>
+      <c r="V33" s="360" t="n"/>
+      <c r="W33" s="360" t="n"/>
+      <c r="X33" s="361" t="n"/>
     </row>
     <row r="34" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A34" s="352" t="n">
+      <c r="A34" s="356" t="n">
         <v>45077</v>
       </c>
       <c r="B34" s="71" t="inlineStr">
@@ -8207,20 +8239,20 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C34" s="346" t="n"/>
+      <c r="C34" s="350" t="n"/>
       <c r="D34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="347" t="n"/>
-      <c r="F34" s="348" t="n"/>
-      <c r="G34" s="358" t="n"/>
-      <c r="I34" s="349" t="n"/>
+      <c r="E34" s="351" t="n"/>
+      <c r="F34" s="352" t="n"/>
+      <c r="G34" s="362" t="n"/>
+      <c r="I34" s="353" t="n"/>
       <c r="J34" s="238" t="n"/>
-      <c r="K34" s="349" t="n"/>
-      <c r="L34" s="349" t="n"/>
-      <c r="M34" s="352" t="n">
+      <c r="K34" s="353" t="n"/>
+      <c r="L34" s="353" t="n"/>
+      <c r="M34" s="356" t="n">
         <v>45138</v>
       </c>
       <c r="N34" s="71" t="inlineStr">
@@ -8228,14 +8260,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O34" s="346" t="n"/>
+      <c r="O34" s="350" t="n"/>
       <c r="P34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="347" t="n"/>
-      <c r="R34" s="348" t="n"/>
+      <c r="Q34" s="351" t="n"/>
+      <c r="R34" s="352" t="n"/>
       <c r="S34" s="238" t="n"/>
       <c r="T34" s="238" t="inlineStr">
         <is>
@@ -8755,7 +8787,7 @@
       </c>
     </row>
     <row r="4" ht="20.45" customHeight="1" s="257">
-      <c r="A4" s="359">
+      <c r="A4" s="363">
         <f>日程表１!A4</f>
         <v/>
       </c>
@@ -8770,8 +8802,8 @@
         </is>
       </c>
       <c r="E4" s="332" t="n"/>
-      <c r="F4" s="360" t="n"/>
-      <c r="G4" s="359">
+      <c r="F4" s="364" t="n"/>
+      <c r="G4" s="363">
         <f>日程表１!G4</f>
         <v/>
       </c>
@@ -8786,8 +8818,8 @@
         </is>
       </c>
       <c r="K4" s="332" t="n"/>
-      <c r="L4" s="360" t="n"/>
-      <c r="M4" s="359">
+      <c r="L4" s="364" t="n"/>
+      <c r="M4" s="363">
         <f>日程表１!M4</f>
         <v/>
       </c>
@@ -8808,11 +8840,11 @@
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="360">
+      <c r="R4" s="364">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="359">
+      <c r="S4" s="363">
         <f>日程表１!S5</f>
         <v/>
       </c>
@@ -8826,11 +8858,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="361" t="n"/>
-      <c r="X4" s="362" t="n"/>
+      <c r="W4" s="365" t="n"/>
+      <c r="X4" s="366" t="n"/>
     </row>
     <row r="5" ht="20.45" customHeight="1" s="257">
-      <c r="A5" s="359">
+      <c r="A5" s="363">
         <f>日程表１!A5</f>
         <v/>
       </c>
@@ -8845,8 +8877,8 @@
         </is>
       </c>
       <c r="E5" s="341" t="n"/>
-      <c r="F5" s="360" t="n"/>
-      <c r="G5" s="359">
+      <c r="F5" s="364" t="n"/>
+      <c r="G5" s="363">
         <f>日程表１!G5</f>
         <v/>
       </c>
@@ -8867,36 +8899,36 @@
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="360">
+      <c r="L5" s="364">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="359">
+      <c r="M5" s="367">
         <f>日程表１!M5</f>
         <v/>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="368">
         <f>日程表１!N5</f>
         <v/>
       </c>
-      <c r="O5" s="340">
+      <c r="O5" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="253" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="341">
+      <c r="P5" s="369" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="346">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="360">
+      <c r="R5" s="370">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="359">
+      <c r="S5" s="363">
         <f>日程表１!S6</f>
         <v/>
       </c>
@@ -8910,11 +8942,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="363" t="n"/>
-      <c r="X5" s="362" t="n"/>
+      <c r="W5" s="371" t="n"/>
+      <c r="X5" s="366" t="n"/>
     </row>
     <row r="6" ht="20.45" customHeight="1" s="257">
-      <c r="A6" s="359">
+      <c r="A6" s="363">
         <f>日程表１!A6</f>
         <v/>
       </c>
@@ -8929,33 +8961,33 @@
         </is>
       </c>
       <c r="E6" s="341" t="n"/>
-      <c r="F6" s="360" t="n"/>
-      <c r="G6" s="359">
+      <c r="F6" s="364" t="n"/>
+      <c r="G6" s="367">
         <f>日程表１!G6</f>
         <v/>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="368">
         <f>日程表１!H6</f>
         <v/>
       </c>
-      <c r="I6" s="340">
+      <c r="I6" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="253" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="341">
+      <c r="J6" s="369" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="346">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="360">
+      <c r="L6" s="370">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="359">
+      <c r="M6" s="363">
         <f>日程表１!M6</f>
         <v/>
       </c>
@@ -8970,8 +9002,8 @@
         </is>
       </c>
       <c r="Q6" s="341" t="n"/>
-      <c r="R6" s="360" t="n"/>
-      <c r="S6" s="359">
+      <c r="R6" s="364" t="n"/>
+      <c r="S6" s="363">
         <f>日程表１!S7</f>
         <v/>
       </c>
@@ -8985,11 +9017,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="363" t="n"/>
-      <c r="X6" s="362" t="n"/>
+      <c r="W6" s="371" t="n"/>
+      <c r="X6" s="366" t="n"/>
     </row>
     <row r="7" ht="20.45" customHeight="1" s="257">
-      <c r="A7" s="359">
+      <c r="A7" s="363">
         <f>日程表１!A7</f>
         <v/>
       </c>
@@ -9004,8 +9036,8 @@
         </is>
       </c>
       <c r="E7" s="341" t="n"/>
-      <c r="F7" s="360" t="n"/>
-      <c r="G7" s="359">
+      <c r="F7" s="364" t="n"/>
+      <c r="G7" s="363">
         <f>日程表１!G7</f>
         <v/>
       </c>
@@ -9026,11 +9058,11 @@
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="360">
+      <c r="L7" s="364">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="359">
+      <c r="M7" s="363">
         <f>日程表１!M7</f>
         <v/>
       </c>
@@ -9045,8 +9077,8 @@
         </is>
       </c>
       <c r="Q7" s="341" t="n"/>
-      <c r="R7" s="360" t="n"/>
-      <c r="S7" s="359">
+      <c r="R7" s="364" t="n"/>
+      <c r="S7" s="363">
         <f>日程表１!S8</f>
         <v/>
       </c>
@@ -9060,11 +9092,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="363" t="n"/>
-      <c r="X7" s="362" t="n"/>
+      <c r="W7" s="371" t="n"/>
+      <c r="X7" s="366" t="n"/>
     </row>
     <row r="8" ht="20.45" customHeight="1" s="257">
-      <c r="A8" s="359">
+      <c r="A8" s="363">
         <f>日程表１!A8</f>
         <v/>
       </c>
@@ -9079,8 +9111,8 @@
         </is>
       </c>
       <c r="E8" s="341" t="n"/>
-      <c r="F8" s="360" t="n"/>
-      <c r="G8" s="359">
+      <c r="F8" s="364" t="n"/>
+      <c r="G8" s="363">
         <f>日程表１!G8</f>
         <v/>
       </c>
@@ -9088,15 +9120,15 @@
         <f>日程表１!H8</f>
         <v/>
       </c>
-      <c r="I8" s="342" t="n"/>
-      <c r="J8" s="44" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K8" s="343" t="n"/>
-      <c r="L8" s="360" t="n"/>
-      <c r="M8" s="359">
+      <c r="I8" s="340" t="n"/>
+      <c r="J8" s="253" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K8" s="341" t="n"/>
+      <c r="L8" s="364" t="n"/>
+      <c r="M8" s="363">
         <f>日程表１!M8</f>
         <v/>
       </c>
@@ -9111,8 +9143,8 @@
         </is>
       </c>
       <c r="Q8" s="341" t="n"/>
-      <c r="R8" s="360" t="n"/>
-      <c r="S8" s="359">
+      <c r="R8" s="364" t="n"/>
+      <c r="S8" s="363">
         <f>日程表１!S9</f>
         <v/>
       </c>
@@ -9126,11 +9158,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="363" t="n"/>
-      <c r="X8" s="362" t="n"/>
+      <c r="W8" s="371" t="n"/>
+      <c r="X8" s="366" t="n"/>
     </row>
     <row r="9" ht="20.45" customHeight="1" s="257">
-      <c r="A9" s="359">
+      <c r="A9" s="363">
         <f>日程表１!A9</f>
         <v/>
       </c>
@@ -9145,8 +9177,8 @@
         </is>
       </c>
       <c r="E9" s="341" t="n"/>
-      <c r="F9" s="360" t="n"/>
-      <c r="G9" s="359">
+      <c r="F9" s="364" t="n"/>
+      <c r="G9" s="363">
         <f>日程表１!G9</f>
         <v/>
       </c>
@@ -9161,8 +9193,8 @@
         </is>
       </c>
       <c r="K9" s="341" t="n"/>
-      <c r="L9" s="360" t="n"/>
-      <c r="M9" s="359">
+      <c r="L9" s="364" t="n"/>
+      <c r="M9" s="363">
         <f>日程表１!M9</f>
         <v/>
       </c>
@@ -9177,8 +9209,8 @@
         </is>
       </c>
       <c r="Q9" s="341" t="n"/>
-      <c r="R9" s="360" t="n"/>
-      <c r="S9" s="359">
+      <c r="R9" s="364" t="n"/>
+      <c r="S9" s="363">
         <f>日程表１!S10</f>
         <v/>
       </c>
@@ -9192,11 +9224,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="363" t="n"/>
-      <c r="X9" s="362" t="n"/>
+      <c r="W9" s="371" t="n"/>
+      <c r="X9" s="366" t="n"/>
     </row>
     <row r="10" ht="20.45" customHeight="1" s="257">
-      <c r="A10" s="359">
+      <c r="A10" s="363">
         <f>日程表１!A10</f>
         <v/>
       </c>
@@ -9211,8 +9243,8 @@
         </is>
       </c>
       <c r="E10" s="341" t="n"/>
-      <c r="F10" s="360" t="n"/>
-      <c r="G10" s="359">
+      <c r="F10" s="364" t="n"/>
+      <c r="G10" s="363">
         <f>日程表１!G10</f>
         <v/>
       </c>
@@ -9227,8 +9259,8 @@
         </is>
       </c>
       <c r="K10" s="341" t="n"/>
-      <c r="L10" s="360" t="n"/>
-      <c r="M10" s="359">
+      <c r="L10" s="364" t="n"/>
+      <c r="M10" s="363">
         <f>日程表１!M10</f>
         <v/>
       </c>
@@ -9243,8 +9275,8 @@
         </is>
       </c>
       <c r="Q10" s="341" t="n"/>
-      <c r="R10" s="360" t="n"/>
-      <c r="S10" s="359">
+      <c r="R10" s="364" t="n"/>
+      <c r="S10" s="363">
         <f>日程表１!S11</f>
         <v/>
       </c>
@@ -9258,11 +9290,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="363" t="n"/>
-      <c r="X10" s="362" t="n"/>
+      <c r="W10" s="371" t="n"/>
+      <c r="X10" s="366" t="n"/>
     </row>
     <row r="11" ht="20.45" customHeight="1" s="257">
-      <c r="A11" s="359">
+      <c r="A11" s="363">
         <f>日程表１!A11</f>
         <v/>
       </c>
@@ -9270,15 +9302,15 @@
         <f>日程表１!B11</f>
         <v/>
       </c>
-      <c r="C11" s="342" t="n"/>
-      <c r="D11" s="44" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E11" s="343" t="n"/>
-      <c r="F11" s="360" t="n"/>
-      <c r="G11" s="359">
+      <c r="C11" s="340" t="n"/>
+      <c r="D11" s="253" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E11" s="341" t="n"/>
+      <c r="F11" s="364" t="n"/>
+      <c r="G11" s="363">
         <f>日程表１!G11</f>
         <v/>
       </c>
@@ -9293,8 +9325,8 @@
         </is>
       </c>
       <c r="K11" s="341" t="n"/>
-      <c r="L11" s="360" t="n"/>
-      <c r="M11" s="359">
+      <c r="L11" s="364" t="n"/>
+      <c r="M11" s="363">
         <f>日程表１!M11</f>
         <v/>
       </c>
@@ -9309,8 +9341,8 @@
         </is>
       </c>
       <c r="Q11" s="341" t="n"/>
-      <c r="R11" s="360" t="n"/>
-      <c r="S11" s="359">
+      <c r="R11" s="364" t="n"/>
+      <c r="S11" s="363">
         <f>日程表１!S12</f>
         <v/>
       </c>
@@ -9324,11 +9356,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="363" t="n"/>
-      <c r="X11" s="362" t="n"/>
+      <c r="W11" s="371" t="n"/>
+      <c r="X11" s="366" t="n"/>
     </row>
     <row r="12" ht="20.45" customHeight="1" s="257">
-      <c r="A12" s="359">
+      <c r="A12" s="363">
         <f>日程表１!A12</f>
         <v/>
       </c>
@@ -9343,33 +9375,33 @@
         </is>
       </c>
       <c r="E12" s="341" t="n"/>
-      <c r="F12" s="360" t="n"/>
-      <c r="G12" s="359">
+      <c r="F12" s="364" t="n"/>
+      <c r="G12" s="367">
         <f>日程表１!G12</f>
         <v/>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="368">
         <f>日程表１!H12</f>
         <v/>
       </c>
-      <c r="I12" s="340">
+      <c r="I12" s="344">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="253" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="341">
+      <c r="J12" s="369" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="346">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="360">
+      <c r="L12" s="370">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="359">
+      <c r="M12" s="363">
         <f>日程表１!M12</f>
         <v/>
       </c>
@@ -9384,8 +9416,8 @@
         </is>
       </c>
       <c r="Q12" s="341" t="n"/>
-      <c r="R12" s="360" t="n"/>
-      <c r="S12" s="359">
+      <c r="R12" s="364" t="n"/>
+      <c r="S12" s="363">
         <f>日程表１!S13</f>
         <v/>
       </c>
@@ -9399,11 +9431,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="363" t="n"/>
-      <c r="X12" s="362" t="n"/>
+      <c r="W12" s="371" t="n"/>
+      <c r="X12" s="366" t="n"/>
     </row>
     <row r="13" ht="20.45" customHeight="1" s="257">
-      <c r="A13" s="359">
+      <c r="A13" s="363">
         <f>日程表１!A13</f>
         <v/>
       </c>
@@ -9418,8 +9450,8 @@
         </is>
       </c>
       <c r="E13" s="341" t="n"/>
-      <c r="F13" s="360" t="n"/>
-      <c r="G13" s="359">
+      <c r="F13" s="364" t="n"/>
+      <c r="G13" s="363">
         <f>日程表１!G13</f>
         <v/>
       </c>
@@ -9440,11 +9472,11 @@
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="360">
+      <c r="L13" s="364">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="359">
+      <c r="M13" s="363">
         <f>日程表１!M13</f>
         <v/>
       </c>
@@ -9459,8 +9491,8 @@
         </is>
       </c>
       <c r="Q13" s="341" t="n"/>
-      <c r="R13" s="360" t="n"/>
-      <c r="S13" s="359" t="n">
+      <c r="R13" s="364" t="n"/>
+      <c r="S13" s="363" t="n">
         <v>10</v>
       </c>
       <c r="T13" s="29" t="inlineStr">
@@ -9474,11 +9506,11 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="363" t="n"/>
-      <c r="X13" s="362" t="n"/>
+      <c r="W13" s="371" t="n"/>
+      <c r="X13" s="366" t="n"/>
     </row>
     <row r="14" ht="20.45" customHeight="1" s="257">
-      <c r="A14" s="359">
+      <c r="A14" s="363">
         <f>日程表１!A14</f>
         <v/>
       </c>
@@ -9493,8 +9525,8 @@
         </is>
       </c>
       <c r="E14" s="341" t="n"/>
-      <c r="F14" s="360" t="n"/>
-      <c r="G14" s="359">
+      <c r="F14" s="364" t="n"/>
+      <c r="G14" s="363">
         <f>日程表１!G14</f>
         <v/>
       </c>
@@ -9515,11 +9547,11 @@
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="360">
+      <c r="L14" s="364">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="359">
+      <c r="M14" s="363">
         <f>日程表１!M14</f>
         <v/>
       </c>
@@ -9534,16 +9566,16 @@
         </is>
       </c>
       <c r="Q14" s="341" t="n"/>
-      <c r="R14" s="360" t="n"/>
+      <c r="R14" s="364" t="n"/>
       <c r="S14" s="256" t="n"/>
       <c r="T14" s="256" t="n"/>
-      <c r="U14" s="349" t="n"/>
+      <c r="U14" s="353" t="n"/>
       <c r="V14" s="255" t="n"/>
-      <c r="W14" s="350" t="n"/>
-      <c r="X14" s="350" t="n"/>
+      <c r="W14" s="354" t="n"/>
+      <c r="X14" s="354" t="n"/>
     </row>
     <row r="15" ht="20.45" customHeight="1" s="257">
-      <c r="A15" s="359">
+      <c r="A15" s="363">
         <f>日程表１!A15</f>
         <v/>
       </c>
@@ -9558,8 +9590,8 @@
         </is>
       </c>
       <c r="E15" s="341" t="n"/>
-      <c r="F15" s="360" t="n"/>
-      <c r="G15" s="359">
+      <c r="F15" s="364" t="n"/>
+      <c r="G15" s="363">
         <f>日程表１!G15</f>
         <v/>
       </c>
@@ -9574,8 +9606,8 @@
         </is>
       </c>
       <c r="K15" s="341" t="n"/>
-      <c r="L15" s="360" t="n"/>
-      <c r="M15" s="359">
+      <c r="L15" s="364" t="n"/>
+      <c r="M15" s="363">
         <f>日程表１!M15</f>
         <v/>
       </c>
@@ -9590,16 +9622,16 @@
         </is>
       </c>
       <c r="Q15" s="341" t="n"/>
-      <c r="R15" s="360" t="n"/>
+      <c r="R15" s="364" t="n"/>
       <c r="S15" s="256" t="n"/>
       <c r="T15" s="256" t="n"/>
-      <c r="U15" s="349" t="n"/>
+      <c r="U15" s="353" t="n"/>
       <c r="V15" s="255" t="n"/>
-      <c r="W15" s="350" t="n"/>
-      <c r="X15" s="350" t="n"/>
+      <c r="W15" s="354" t="n"/>
+      <c r="X15" s="354" t="n"/>
     </row>
     <row r="16" ht="20.45" customHeight="1" s="257">
-      <c r="A16" s="359">
+      <c r="A16" s="363">
         <f>日程表１!A16</f>
         <v/>
       </c>
@@ -9614,8 +9646,8 @@
         </is>
       </c>
       <c r="E16" s="341" t="n"/>
-      <c r="F16" s="360" t="n"/>
-      <c r="G16" s="359">
+      <c r="F16" s="364" t="n"/>
+      <c r="G16" s="363">
         <f>日程表１!G16</f>
         <v/>
       </c>
@@ -9630,8 +9662,8 @@
         </is>
       </c>
       <c r="K16" s="341" t="n"/>
-      <c r="L16" s="360" t="n"/>
-      <c r="M16" s="359">
+      <c r="L16" s="364" t="n"/>
+      <c r="M16" s="363">
         <f>日程表１!M16</f>
         <v/>
       </c>
@@ -9646,16 +9678,16 @@
         </is>
       </c>
       <c r="Q16" s="341" t="n"/>
-      <c r="R16" s="360" t="n"/>
+      <c r="R16" s="364" t="n"/>
       <c r="S16" s="256" t="n"/>
       <c r="T16" s="256" t="n"/>
-      <c r="U16" s="349" t="n"/>
+      <c r="U16" s="353" t="n"/>
       <c r="V16" s="255" t="n"/>
-      <c r="W16" s="350" t="n"/>
-      <c r="X16" s="350" t="n"/>
+      <c r="W16" s="354" t="n"/>
+      <c r="X16" s="354" t="n"/>
     </row>
     <row r="17" ht="20.45" customHeight="1" s="257">
-      <c r="A17" s="359">
+      <c r="A17" s="363">
         <f>日程表１!A17</f>
         <v/>
       </c>
@@ -9670,8 +9702,8 @@
         </is>
       </c>
       <c r="E17" s="341" t="n"/>
-      <c r="F17" s="360" t="n"/>
-      <c r="G17" s="359">
+      <c r="F17" s="364" t="n"/>
+      <c r="G17" s="363">
         <f>日程表１!G17</f>
         <v/>
       </c>
@@ -9686,8 +9718,8 @@
         </is>
       </c>
       <c r="K17" s="341" t="n"/>
-      <c r="L17" s="360" t="n"/>
-      <c r="M17" s="359">
+      <c r="L17" s="364" t="n"/>
+      <c r="M17" s="363">
         <f>日程表１!M17</f>
         <v/>
       </c>
@@ -9702,7 +9734,7 @@
         </is>
       </c>
       <c r="Q17" s="341" t="n"/>
-      <c r="R17" s="360" t="n"/>
+      <c r="R17" s="364" t="n"/>
       <c r="S17" s="254" t="inlineStr">
         <is>
           <t>NO.</t>
@@ -9719,7 +9751,7 @@
       <c r="X17" s="279" t="n"/>
     </row>
     <row r="18" ht="20.45" customHeight="1" s="257">
-      <c r="A18" s="359">
+      <c r="A18" s="363">
         <f>日程表１!A18</f>
         <v/>
       </c>
@@ -9727,15 +9759,15 @@
         <f>日程表１!B18</f>
         <v/>
       </c>
-      <c r="C18" s="342" t="n"/>
-      <c r="D18" s="44" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E18" s="343" t="n"/>
-      <c r="F18" s="360" t="n"/>
-      <c r="G18" s="359">
+      <c r="C18" s="340" t="n"/>
+      <c r="D18" s="253" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E18" s="341" t="n"/>
+      <c r="F18" s="364" t="n"/>
+      <c r="G18" s="363">
         <f>日程表１!G18</f>
         <v/>
       </c>
@@ -9750,8 +9782,8 @@
         </is>
       </c>
       <c r="K18" s="341" t="n"/>
-      <c r="L18" s="360" t="n"/>
-      <c r="M18" s="359">
+      <c r="L18" s="364" t="n"/>
+      <c r="M18" s="363">
         <f>日程表１!M18</f>
         <v/>
       </c>
@@ -9766,7 +9798,7 @@
         </is>
       </c>
       <c r="Q18" s="341" t="n"/>
-      <c r="R18" s="360" t="n"/>
+      <c r="R18" s="364" t="n"/>
       <c r="S18" s="254" t="n">
         <v>1</v>
       </c>
@@ -9780,7 +9812,7 @@
       <c r="X18" s="279" t="n"/>
     </row>
     <row r="19" ht="20.45" customHeight="1" s="257">
-      <c r="A19" s="359">
+      <c r="A19" s="363">
         <f>日程表１!A19</f>
         <v/>
       </c>
@@ -9795,8 +9827,8 @@
         </is>
       </c>
       <c r="E19" s="341" t="n"/>
-      <c r="F19" s="360" t="n"/>
-      <c r="G19" s="359">
+      <c r="F19" s="364" t="n"/>
+      <c r="G19" s="363">
         <f>日程表１!G19</f>
         <v/>
       </c>
@@ -9811,8 +9843,8 @@
       </c>
       <c r="J19" s="253" t="n"/>
       <c r="K19" s="341" t="n"/>
-      <c r="L19" s="360" t="n"/>
-      <c r="M19" s="359">
+      <c r="L19" s="364" t="n"/>
+      <c r="M19" s="363">
         <f>日程表１!M19</f>
         <v/>
       </c>
@@ -9827,7 +9859,7 @@
         </is>
       </c>
       <c r="Q19" s="341" t="n"/>
-      <c r="R19" s="360" t="n"/>
+      <c r="R19" s="364" t="n"/>
       <c r="S19" s="254" t="n">
         <v>2</v>
       </c>
@@ -9841,7 +9873,7 @@
       <c r="X19" s="279" t="n"/>
     </row>
     <row r="20" ht="20.45" customHeight="1" s="257">
-      <c r="A20" s="364">
+      <c r="A20" s="372">
         <f>日程表１!A20</f>
         <v/>
       </c>
@@ -9856,8 +9888,8 @@
         </is>
       </c>
       <c r="E20" s="341" t="n"/>
-      <c r="F20" s="360" t="n"/>
-      <c r="G20" s="364">
+      <c r="F20" s="364" t="n"/>
+      <c r="G20" s="372">
         <f>日程表１!G20</f>
         <v/>
       </c>
@@ -9872,8 +9904,8 @@
       </c>
       <c r="J20" s="253" t="n"/>
       <c r="K20" s="341" t="n"/>
-      <c r="L20" s="360" t="n"/>
-      <c r="M20" s="364">
+      <c r="L20" s="364" t="n"/>
+      <c r="M20" s="372">
         <f>日程表１!M20</f>
         <v/>
       </c>
@@ -9888,7 +9920,7 @@
         </is>
       </c>
       <c r="Q20" s="341" t="n"/>
-      <c r="R20" s="360" t="n"/>
+      <c r="R20" s="364" t="n"/>
       <c r="S20" s="254" t="n">
         <v>3</v>
       </c>
@@ -9902,7 +9934,7 @@
       <c r="X20" s="279" t="n"/>
     </row>
     <row r="21" ht="20.45" customHeight="1" s="257">
-      <c r="A21" s="359">
+      <c r="A21" s="363">
         <f>日程表１!A21</f>
         <v/>
       </c>
@@ -9917,8 +9949,8 @@
         </is>
       </c>
       <c r="E21" s="341" t="n"/>
-      <c r="F21" s="360" t="n"/>
-      <c r="G21" s="359">
+      <c r="F21" s="364" t="n"/>
+      <c r="G21" s="363">
         <f>日程表１!G21</f>
         <v/>
       </c>
@@ -9933,8 +9965,8 @@
       </c>
       <c r="J21" s="253" t="n"/>
       <c r="K21" s="341" t="n"/>
-      <c r="L21" s="360" t="n"/>
-      <c r="M21" s="359">
+      <c r="L21" s="364" t="n"/>
+      <c r="M21" s="363">
         <f>日程表１!M21</f>
         <v/>
       </c>
@@ -9949,7 +9981,7 @@
         </is>
       </c>
       <c r="Q21" s="341" t="n"/>
-      <c r="R21" s="360" t="n"/>
+      <c r="R21" s="364" t="n"/>
       <c r="S21" s="254" t="n">
         <v>4</v>
       </c>
@@ -9963,7 +9995,7 @@
       <c r="X21" s="279" t="n"/>
     </row>
     <row r="22" ht="20.45" customHeight="1" s="257">
-      <c r="A22" s="359">
+      <c r="A22" s="363">
         <f>日程表１!A22</f>
         <v/>
       </c>
@@ -9978,8 +10010,8 @@
         </is>
       </c>
       <c r="E22" s="341" t="n"/>
-      <c r="F22" s="360" t="n"/>
-      <c r="G22" s="359">
+      <c r="F22" s="364" t="n"/>
+      <c r="G22" s="363">
         <f>日程表１!G22</f>
         <v/>
       </c>
@@ -9994,8 +10026,8 @@
         </is>
       </c>
       <c r="K22" s="341" t="n"/>
-      <c r="L22" s="360" t="n"/>
-      <c r="M22" s="359">
+      <c r="L22" s="364" t="n"/>
+      <c r="M22" s="363">
         <f>日程表１!M22</f>
         <v/>
       </c>
@@ -10010,7 +10042,7 @@
         </is>
       </c>
       <c r="Q22" s="341" t="n"/>
-      <c r="R22" s="360" t="n"/>
+      <c r="R22" s="364" t="n"/>
       <c r="S22" s="254" t="n">
         <v>5</v>
       </c>
@@ -10024,7 +10056,7 @@
       <c r="X22" s="279" t="n"/>
     </row>
     <row r="23" ht="20.45" customHeight="1" s="257">
-      <c r="A23" s="359">
+      <c r="A23" s="363">
         <f>日程表１!A23</f>
         <v/>
       </c>
@@ -10039,8 +10071,8 @@
         </is>
       </c>
       <c r="E23" s="341" t="n"/>
-      <c r="F23" s="360" t="n"/>
-      <c r="G23" s="359">
+      <c r="F23" s="364" t="n"/>
+      <c r="G23" s="363">
         <f>日程表１!G23</f>
         <v/>
       </c>
@@ -10055,8 +10087,8 @@
         </is>
       </c>
       <c r="K23" s="341" t="n"/>
-      <c r="L23" s="360" t="n"/>
-      <c r="M23" s="359">
+      <c r="L23" s="364" t="n"/>
+      <c r="M23" s="363">
         <f>日程表１!M23</f>
         <v/>
       </c>
@@ -10071,7 +10103,7 @@
         </is>
       </c>
       <c r="Q23" s="341" t="n"/>
-      <c r="R23" s="360" t="n"/>
+      <c r="R23" s="364" t="n"/>
       <c r="S23" s="254" t="n">
         <v>6</v>
       </c>
@@ -10085,7 +10117,7 @@
       <c r="X23" s="279" t="n"/>
     </row>
     <row r="24" ht="20.45" customHeight="1" s="257">
-      <c r="A24" s="359">
+      <c r="A24" s="363">
         <f>日程表１!A24</f>
         <v/>
       </c>
@@ -10100,8 +10132,8 @@
         </is>
       </c>
       <c r="E24" s="341" t="n"/>
-      <c r="F24" s="360" t="n"/>
-      <c r="G24" s="359">
+      <c r="F24" s="364" t="n"/>
+      <c r="G24" s="363">
         <f>日程表１!G24</f>
         <v/>
       </c>
@@ -10116,8 +10148,8 @@
         </is>
       </c>
       <c r="K24" s="341" t="n"/>
-      <c r="L24" s="360" t="n"/>
-      <c r="M24" s="359">
+      <c r="L24" s="364" t="n"/>
+      <c r="M24" s="363">
         <f>日程表１!M24</f>
         <v/>
       </c>
@@ -10132,7 +10164,7 @@
         </is>
       </c>
       <c r="Q24" s="341" t="n"/>
-      <c r="R24" s="360" t="n"/>
+      <c r="R24" s="364" t="n"/>
       <c r="S24" s="254" t="n">
         <v>7</v>
       </c>
@@ -10146,7 +10178,7 @@
       <c r="X24" s="279" t="n"/>
     </row>
     <row r="25" ht="20.45" customHeight="1" s="257">
-      <c r="A25" s="359">
+      <c r="A25" s="363">
         <f>日程表１!A25</f>
         <v/>
       </c>
@@ -10154,15 +10186,15 @@
         <f>日程表１!B25</f>
         <v/>
       </c>
-      <c r="C25" s="342" t="n"/>
-      <c r="D25" s="44" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E25" s="343" t="n"/>
-      <c r="F25" s="360" t="n"/>
-      <c r="G25" s="359">
+      <c r="C25" s="340" t="n"/>
+      <c r="D25" s="253" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E25" s="341" t="n"/>
+      <c r="F25" s="364" t="n"/>
+      <c r="G25" s="363">
         <f>日程表１!G25</f>
         <v/>
       </c>
@@ -10177,8 +10209,8 @@
         </is>
       </c>
       <c r="K25" s="341" t="n"/>
-      <c r="L25" s="360" t="n"/>
-      <c r="M25" s="359">
+      <c r="L25" s="364" t="n"/>
+      <c r="M25" s="363">
         <f>日程表１!M25</f>
         <v/>
       </c>
@@ -10193,7 +10225,7 @@
         </is>
       </c>
       <c r="Q25" s="341" t="n"/>
-      <c r="R25" s="360" t="n"/>
+      <c r="R25" s="364" t="n"/>
       <c r="S25" s="254" t="n">
         <v>8</v>
       </c>
@@ -10207,7 +10239,7 @@
       <c r="X25" s="279" t="n"/>
     </row>
     <row r="26" ht="20.45" customHeight="1" s="257">
-      <c r="A26" s="359">
+      <c r="A26" s="363">
         <f>日程表１!A26</f>
         <v/>
       </c>
@@ -10222,33 +10254,33 @@
         </is>
       </c>
       <c r="E26" s="341" t="n"/>
-      <c r="F26" s="360" t="n"/>
-      <c r="G26" s="359">
+      <c r="F26" s="364" t="n"/>
+      <c r="G26" s="367">
         <f>日程表１!G26</f>
         <v/>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="368">
         <f>日程表１!H26</f>
         <v/>
       </c>
-      <c r="I26" s="340">
+      <c r="I26" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="253" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K26" s="341">
+      <c r="J26" s="369" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K26" s="346">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="360">
+      <c r="L26" s="370">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="359">
+      <c r="M26" s="363">
         <f>日程表１!M26</f>
         <v/>
       </c>
@@ -10263,7 +10295,7 @@
         </is>
       </c>
       <c r="Q26" s="341" t="n"/>
-      <c r="R26" s="360" t="n"/>
+      <c r="R26" s="364" t="n"/>
       <c r="S26" s="254" t="n">
         <v>9</v>
       </c>
@@ -10277,7 +10309,7 @@
       <c r="X26" s="279" t="n"/>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="257">
-      <c r="A27" s="359">
+      <c r="A27" s="363">
         <f>日程表１!A27</f>
         <v/>
       </c>
@@ -10292,8 +10324,8 @@
         </is>
       </c>
       <c r="E27" s="341" t="n"/>
-      <c r="F27" s="360" t="n"/>
-      <c r="G27" s="359">
+      <c r="F27" s="364" t="n"/>
+      <c r="G27" s="363">
         <f>日程表１!G27</f>
         <v/>
       </c>
@@ -10314,11 +10346,11 @@
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="360">
+      <c r="L27" s="364">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="359">
+      <c r="M27" s="363">
         <f>日程表１!M27</f>
         <v/>
       </c>
@@ -10333,7 +10365,7 @@
         </is>
       </c>
       <c r="Q27" s="341" t="n"/>
-      <c r="R27" s="360" t="n"/>
+      <c r="R27" s="364" t="n"/>
       <c r="S27" s="254" t="n">
         <v>10</v>
       </c>
@@ -10347,7 +10379,7 @@
       <c r="X27" s="279" t="n"/>
     </row>
     <row r="28" ht="20.45" customHeight="1" s="257">
-      <c r="A28" s="364">
+      <c r="A28" s="372">
         <f>日程表１!A28</f>
         <v/>
       </c>
@@ -10362,8 +10394,8 @@
         </is>
       </c>
       <c r="E28" s="341" t="n"/>
-      <c r="F28" s="360" t="n"/>
-      <c r="G28" s="364">
+      <c r="F28" s="364" t="n"/>
+      <c r="G28" s="372">
         <f>日程表１!G28</f>
         <v/>
       </c>
@@ -10384,11 +10416,11 @@
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="360">
+      <c r="L28" s="364">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="364">
+      <c r="M28" s="372">
         <f>日程表１!M28</f>
         <v/>
       </c>
@@ -10403,7 +10435,7 @@
         </is>
       </c>
       <c r="Q28" s="341" t="n"/>
-      <c r="R28" s="360" t="n"/>
+      <c r="R28" s="364" t="n"/>
       <c r="S28" s="254" t="n">
         <v>11</v>
       </c>
@@ -10417,7 +10449,7 @@
       <c r="X28" s="279" t="n"/>
     </row>
     <row r="29" ht="20.45" customHeight="1" s="257">
-      <c r="A29" s="359">
+      <c r="A29" s="363">
         <f>日程表１!A29</f>
         <v/>
       </c>
@@ -10438,11 +10470,11 @@
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="360">
+      <c r="F29" s="364">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="359">
+      <c r="G29" s="363">
         <f>日程表１!G29</f>
         <v/>
       </c>
@@ -10457,8 +10489,8 @@
         </is>
       </c>
       <c r="K29" s="341" t="n"/>
-      <c r="L29" s="360" t="n"/>
-      <c r="M29" s="359">
+      <c r="L29" s="364" t="n"/>
+      <c r="M29" s="363">
         <f>日程表１!M29</f>
         <v/>
       </c>
@@ -10473,16 +10505,16 @@
         </is>
       </c>
       <c r="Q29" s="341" t="n"/>
-      <c r="R29" s="360" t="n"/>
+      <c r="R29" s="364" t="n"/>
       <c r="S29" s="255" t="n"/>
       <c r="T29" s="255" t="n"/>
-      <c r="U29" s="350" t="n"/>
+      <c r="U29" s="354" t="n"/>
       <c r="V29" s="255" t="n"/>
-      <c r="W29" s="350" t="n"/>
-      <c r="X29" s="350" t="n"/>
+      <c r="W29" s="354" t="n"/>
+      <c r="X29" s="354" t="n"/>
     </row>
     <row r="30" ht="20.45" customHeight="1" s="257">
-      <c r="A30" s="359">
+      <c r="A30" s="363">
         <f>日程表１!A30</f>
         <v/>
       </c>
@@ -10503,11 +10535,11 @@
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="360">
+      <c r="F30" s="364">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="359">
+      <c r="G30" s="363">
         <f>日程表１!G30</f>
         <v/>
       </c>
@@ -10522,8 +10554,8 @@
         </is>
       </c>
       <c r="K30" s="341" t="n"/>
-      <c r="L30" s="360" t="n"/>
-      <c r="M30" s="359">
+      <c r="L30" s="364" t="n"/>
+      <c r="M30" s="363">
         <f>日程表１!M30</f>
         <v/>
       </c>
@@ -10538,41 +10570,41 @@
         </is>
       </c>
       <c r="Q30" s="341" t="n"/>
-      <c r="R30" s="360" t="n"/>
+      <c r="R30" s="364" t="n"/>
       <c r="S30" s="255" t="n"/>
       <c r="T30" s="255" t="n"/>
-      <c r="U30" s="350" t="n"/>
+      <c r="U30" s="354" t="n"/>
       <c r="V30" s="255" t="n"/>
-      <c r="W30" s="350" t="n"/>
-      <c r="X30" s="350" t="n"/>
+      <c r="W30" s="354" t="n"/>
+      <c r="X30" s="354" t="n"/>
     </row>
     <row r="31" ht="20.45" customHeight="1" s="257">
-      <c r="A31" s="359">
+      <c r="A31" s="367">
         <f>日程表１!A31</f>
         <v/>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="368">
         <f>日程表１!B31</f>
         <v/>
       </c>
-      <c r="C31" s="340">
+      <c r="C31" s="344">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="253" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="341">
+      <c r="D31" s="369" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="346">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="360">
+      <c r="F31" s="370">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="359">
+      <c r="G31" s="363">
         <f>日程表１!G31</f>
         <v/>
       </c>
@@ -10587,8 +10619,8 @@
         </is>
       </c>
       <c r="K31" s="341" t="n"/>
-      <c r="L31" s="360" t="n"/>
-      <c r="M31" s="359">
+      <c r="L31" s="364" t="n"/>
+      <c r="M31" s="363">
         <f>日程表１!M31</f>
         <v/>
       </c>
@@ -10603,16 +10635,16 @@
         </is>
       </c>
       <c r="Q31" s="341" t="n"/>
-      <c r="R31" s="360" t="n"/>
+      <c r="R31" s="364" t="n"/>
       <c r="S31" s="255" t="n"/>
       <c r="T31" s="255" t="n"/>
-      <c r="U31" s="350" t="n"/>
+      <c r="U31" s="354" t="n"/>
       <c r="V31" s="255" t="n"/>
-      <c r="W31" s="350" t="n"/>
-      <c r="X31" s="350" t="n"/>
+      <c r="W31" s="354" t="n"/>
+      <c r="X31" s="354" t="n"/>
     </row>
     <row r="32" ht="20.45" customHeight="1" s="257">
-      <c r="A32" s="359">
+      <c r="A32" s="363">
         <f>日程表１!A32</f>
         <v/>
       </c>
@@ -10620,15 +10652,15 @@
         <f>日程表１!B32</f>
         <v/>
       </c>
-      <c r="C32" s="342" t="n"/>
-      <c r="D32" s="44" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E32" s="343" t="n"/>
-      <c r="F32" s="360" t="n"/>
-      <c r="G32" s="359">
+      <c r="C32" s="340" t="n"/>
+      <c r="D32" s="253" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E32" s="341" t="n"/>
+      <c r="F32" s="364" t="n"/>
+      <c r="G32" s="363">
         <f>日程表１!G32</f>
         <v/>
       </c>
@@ -10643,8 +10675,8 @@
         </is>
       </c>
       <c r="K32" s="341" t="n"/>
-      <c r="L32" s="360" t="n"/>
-      <c r="M32" s="359">
+      <c r="L32" s="364" t="n"/>
+      <c r="M32" s="363">
         <f>日程表１!M32</f>
         <v/>
       </c>
@@ -10659,16 +10691,16 @@
         </is>
       </c>
       <c r="Q32" s="341" t="n"/>
-      <c r="R32" s="360" t="n"/>
+      <c r="R32" s="364" t="n"/>
       <c r="S32" s="255" t="n"/>
       <c r="T32" s="255" t="n"/>
-      <c r="U32" s="350" t="n"/>
+      <c r="U32" s="354" t="n"/>
       <c r="V32" s="255" t="n"/>
-      <c r="W32" s="350" t="n"/>
-      <c r="X32" s="350" t="n"/>
+      <c r="W32" s="354" t="n"/>
+      <c r="X32" s="354" t="n"/>
     </row>
     <row r="33" ht="20.45" customHeight="1" s="257">
-      <c r="A33" s="359">
+      <c r="A33" s="363">
         <f>日程表１!A33</f>
         <v/>
       </c>
@@ -10683,8 +10715,8 @@
         </is>
       </c>
       <c r="E33" s="341" t="n"/>
-      <c r="F33" s="360" t="n"/>
-      <c r="G33" s="359">
+      <c r="F33" s="364" t="n"/>
+      <c r="G33" s="363">
         <f>日程表１!G33</f>
         <v/>
       </c>
@@ -10705,11 +10737,11 @@
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="360">
+      <c r="L33" s="364">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="359">
+      <c r="M33" s="363">
         <f>日程表１!M33</f>
         <v/>
       </c>
@@ -10724,16 +10756,16 @@
         </is>
       </c>
       <c r="Q33" s="341" t="n"/>
-      <c r="R33" s="360" t="n"/>
+      <c r="R33" s="364" t="n"/>
       <c r="S33" s="255" t="n"/>
       <c r="T33" s="255" t="n"/>
-      <c r="U33" s="350" t="n"/>
+      <c r="U33" s="354" t="n"/>
       <c r="V33" s="255" t="n"/>
-      <c r="W33" s="350" t="n"/>
-      <c r="X33" s="350" t="n"/>
+      <c r="W33" s="354" t="n"/>
+      <c r="X33" s="354" t="n"/>
     </row>
     <row r="34" ht="20.45" customHeight="1" s="257">
-      <c r="A34" s="359">
+      <c r="A34" s="363">
         <f>日程表１!A34</f>
         <v/>
       </c>
@@ -10747,9 +10779,9 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="363" t="n"/>
-      <c r="F34" s="349" t="n"/>
-      <c r="G34" s="359" t="n"/>
+      <c r="E34" s="371" t="n"/>
+      <c r="F34" s="353" t="n"/>
+      <c r="G34" s="363" t="n"/>
       <c r="H34" s="256" t="n"/>
       <c r="I34" s="340" t="n"/>
       <c r="J34" s="253" t="inlineStr">
@@ -10758,8 +10790,8 @@
         </is>
       </c>
       <c r="K34" s="341" t="n"/>
-      <c r="L34" s="360" t="n"/>
-      <c r="M34" s="359">
+      <c r="L34" s="364" t="n"/>
+      <c r="M34" s="363">
         <f>日程表１!M34</f>
         <v/>
       </c>
@@ -10774,13 +10806,13 @@
         </is>
       </c>
       <c r="Q34" s="341" t="n"/>
-      <c r="R34" s="360" t="n"/>
+      <c r="R34" s="364" t="n"/>
       <c r="S34" s="255" t="n"/>
       <c r="T34" s="255" t="n"/>
-      <c r="U34" s="350" t="n"/>
+      <c r="U34" s="354" t="n"/>
       <c r="V34" s="255" t="n"/>
-      <c r="W34" s="350" t="n"/>
-      <c r="X34" s="350" t="n"/>
+      <c r="W34" s="354" t="n"/>
+      <c r="X34" s="354" t="n"/>
     </row>
     <row r="35" ht="3" customHeight="1" s="257"/>
   </sheetData>

--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -306,9 +306,9 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="lightTrellis">
-        <fgColor rgb="00D97706"/>
-        <bgColor rgb="00FFFFFF"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>

--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="メイリオ"/>
       <charset val="128"/>
@@ -234,6 +234,11 @@
     </font>
     <font>
       <name val="メイリオ"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
       <color theme="1"/>
       <sz val="8"/>
     </font>
@@ -1307,7 +1312,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="367">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2171,6 +2176,9 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2362,110 +2370,84 @@
     <xf numFmtId="165" fontId="17" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="37" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2475,15 +2457,15 @@
     <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2496,16 +2478,13 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2849,7 +2828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:BA27"/>
+  <dimension ref="A1:BA27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col width="2.5546875" customWidth="1" style="1" min="1" max="1"/>
@@ -2874,7 +2853,13 @@
     <col hidden="1" width="4.6640625" customWidth="1" style="1" min="61" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="257"/>
+    <row r="1" ht="25" customHeight="1" s="257">
+      <c r="A1" s="258" t="inlineStr">
+        <is>
+          <t>令和8年 朝野球リーグ勝敗表</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="48.75" customHeight="1" s="257">
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
@@ -2898,58 +2883,58 @@
       <c r="E4" s="235" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="258" t="n"/>
-      <c r="G4" s="258" t="n"/>
+      <c r="F4" s="259" t="n"/>
+      <c r="G4" s="259" t="n"/>
       <c r="H4" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="258" t="n"/>
-      <c r="J4" s="258" t="n"/>
+      <c r="I4" s="259" t="n"/>
+      <c r="J4" s="259" t="n"/>
       <c r="K4" s="235" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="258" t="n"/>
-      <c r="M4" s="258" t="n"/>
+      <c r="L4" s="259" t="n"/>
+      <c r="M4" s="259" t="n"/>
       <c r="N4" s="235" t="n">
         <v>4</v>
       </c>
-      <c r="O4" s="258" t="n"/>
-      <c r="P4" s="258" t="n"/>
+      <c r="O4" s="259" t="n"/>
+      <c r="P4" s="259" t="n"/>
       <c r="Q4" s="235" t="n">
         <v>5</v>
       </c>
-      <c r="R4" s="258" t="n"/>
-      <c r="S4" s="258" t="n"/>
+      <c r="R4" s="259" t="n"/>
+      <c r="S4" s="259" t="n"/>
       <c r="T4" s="235" t="n">
         <v>6</v>
       </c>
-      <c r="U4" s="258" t="n"/>
-      <c r="V4" s="258" t="n"/>
+      <c r="U4" s="259" t="n"/>
+      <c r="V4" s="259" t="n"/>
       <c r="W4" s="235" t="n">
         <v>7</v>
       </c>
-      <c r="X4" s="258" t="n"/>
-      <c r="Y4" s="258" t="n"/>
+      <c r="X4" s="259" t="n"/>
+      <c r="Y4" s="259" t="n"/>
       <c r="Z4" s="235" t="n">
         <v>8</v>
       </c>
-      <c r="AA4" s="258" t="n"/>
-      <c r="AB4" s="258" t="n"/>
+      <c r="AA4" s="259" t="n"/>
+      <c r="AB4" s="259" t="n"/>
       <c r="AC4" s="235" t="n">
         <v>9</v>
       </c>
-      <c r="AD4" s="258" t="n"/>
-      <c r="AE4" s="258" t="n"/>
+      <c r="AD4" s="259" t="n"/>
+      <c r="AE4" s="259" t="n"/>
       <c r="AF4" s="235" t="n">
         <v>10</v>
       </c>
-      <c r="AG4" s="258" t="n"/>
-      <c r="AH4" s="258" t="n"/>
+      <c r="AG4" s="259" t="n"/>
+      <c r="AH4" s="259" t="n"/>
       <c r="AI4" s="235" t="n">
         <v>11</v>
       </c>
-      <c r="AJ4" s="258" t="n"/>
-      <c r="AK4" s="258" t="n"/>
+      <c r="AJ4" s="259" t="n"/>
+      <c r="AK4" s="259" t="n"/>
     </row>
     <row r="5" ht="57" customHeight="1" s="257" thickBot="1">
       <c r="B5" s="108" t="inlineStr">
@@ -2957,74 +2942,74 @@
           <t>チーム名</t>
         </is>
       </c>
-      <c r="C5" s="259" t="n"/>
-      <c r="D5" s="260" t="n"/>
+      <c r="C5" s="260" t="n"/>
+      <c r="D5" s="261" t="n"/>
       <c r="E5" s="106">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F5" s="259" t="n"/>
-      <c r="G5" s="260" t="n"/>
+      <c r="F5" s="260" t="n"/>
+      <c r="G5" s="261" t="n"/>
       <c r="H5" s="107">
         <f>C8</f>
         <v/>
       </c>
-      <c r="I5" s="259" t="n"/>
-      <c r="J5" s="260" t="n"/>
+      <c r="I5" s="260" t="n"/>
+      <c r="J5" s="261" t="n"/>
       <c r="K5" s="107">
         <f>C10</f>
         <v/>
       </c>
-      <c r="L5" s="259" t="n"/>
-      <c r="M5" s="260" t="n"/>
+      <c r="L5" s="260" t="n"/>
+      <c r="M5" s="261" t="n"/>
       <c r="N5" s="107">
         <f>C12</f>
         <v/>
       </c>
-      <c r="O5" s="259" t="n"/>
-      <c r="P5" s="260" t="n"/>
+      <c r="O5" s="260" t="n"/>
+      <c r="P5" s="261" t="n"/>
       <c r="Q5" s="107">
         <f>C14</f>
         <v/>
       </c>
-      <c r="R5" s="259" t="n"/>
-      <c r="S5" s="260" t="n"/>
+      <c r="R5" s="260" t="n"/>
+      <c r="S5" s="261" t="n"/>
       <c r="T5" s="107">
         <f>C16</f>
         <v/>
       </c>
-      <c r="U5" s="259" t="n"/>
-      <c r="V5" s="260" t="n"/>
+      <c r="U5" s="260" t="n"/>
+      <c r="V5" s="261" t="n"/>
       <c r="W5" s="107">
         <f>C18</f>
         <v/>
       </c>
-      <c r="X5" s="259" t="n"/>
-      <c r="Y5" s="260" t="n"/>
+      <c r="X5" s="260" t="n"/>
+      <c r="Y5" s="261" t="n"/>
       <c r="Z5" s="107">
         <f>C20</f>
         <v/>
       </c>
-      <c r="AA5" s="259" t="n"/>
-      <c r="AB5" s="260" t="n"/>
+      <c r="AA5" s="260" t="n"/>
+      <c r="AB5" s="261" t="n"/>
       <c r="AC5" s="107">
         <f>C22</f>
         <v/>
       </c>
-      <c r="AD5" s="259" t="n"/>
-      <c r="AE5" s="260" t="n"/>
+      <c r="AD5" s="260" t="n"/>
+      <c r="AE5" s="261" t="n"/>
       <c r="AF5" s="107">
         <f>C24</f>
         <v/>
       </c>
-      <c r="AG5" s="259" t="n"/>
-      <c r="AH5" s="260" t="n"/>
+      <c r="AG5" s="260" t="n"/>
+      <c r="AH5" s="261" t="n"/>
       <c r="AI5" s="107">
         <f>C26</f>
         <v/>
       </c>
-      <c r="AJ5" s="259" t="n"/>
-      <c r="AK5" s="260" t="n"/>
+      <c r="AJ5" s="260" t="n"/>
+      <c r="AK5" s="261" t="n"/>
       <c r="AL5" s="34" t="inlineStr">
         <is>
           <t>勝</t>
@@ -3070,13 +3055,13 @@
           <t>チームナンバー</t>
         </is>
       </c>
-      <c r="AX5" s="261" t="n"/>
+      <c r="AX5" s="262" t="n"/>
       <c r="AZ5" s="100" t="inlineStr">
         <is>
           <t>チームリスト</t>
         </is>
       </c>
-      <c r="BA5" s="262" t="n"/>
+      <c r="BA5" s="263" t="n"/>
     </row>
     <row r="6" ht="46.9" customHeight="1" s="257">
       <c r="B6" s="130" t="n">
@@ -3086,94 +3071,94 @@
         <f>AX6</f>
         <v/>
       </c>
-      <c r="D6" s="263" t="n"/>
+      <c r="D6" s="264" t="n"/>
       <c r="E6" s="146" t="n"/>
-      <c r="G6" s="263" t="n"/>
-      <c r="H6" s="264">
+      <c r="G6" s="264" t="n"/>
+      <c r="H6" s="265">
         <f>IF(H7="","",IF(H7="☂","☂",IF(H7&gt;J7,"○",IF(H7=J7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I6" s="265" t="n"/>
-      <c r="J6" s="266" t="n"/>
-      <c r="K6" s="264">
+      <c r="I6" s="266" t="n"/>
+      <c r="J6" s="267" t="n"/>
+      <c r="K6" s="265">
         <f>IF(K7="","",IF(K7="☂","☂",IF(K7&gt;M7,"○",IF(K7=M7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L6" s="265" t="n"/>
-      <c r="M6" s="266" t="n"/>
-      <c r="N6" s="264">
+      <c r="L6" s="266" t="n"/>
+      <c r="M6" s="267" t="n"/>
+      <c r="N6" s="265">
         <f>IF(N7="","",IF(N7="☂","☂",IF(N7&gt;P7,"○",IF(N7=P7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O6" s="265" t="n"/>
-      <c r="P6" s="266" t="n"/>
-      <c r="Q6" s="264">
+      <c r="O6" s="266" t="n"/>
+      <c r="P6" s="267" t="n"/>
+      <c r="Q6" s="265">
         <f>IF(Q7="","",IF(Q7="☂","☂",IF(Q7&gt;S7,"○",IF(Q7=S7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R6" s="265" t="n"/>
-      <c r="S6" s="266" t="n"/>
-      <c r="T6" s="264">
+      <c r="R6" s="266" t="n"/>
+      <c r="S6" s="267" t="n"/>
+      <c r="T6" s="265">
         <f>IF(T7="","",IF(T7="☂","☂",IF(T7&gt;V7,"○",IF(T7=V7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U6" s="265" t="n"/>
-      <c r="V6" s="266" t="n"/>
-      <c r="W6" s="264">
+      <c r="U6" s="266" t="n"/>
+      <c r="V6" s="267" t="n"/>
+      <c r="W6" s="265">
         <f>IF(W7="","",IF(W7="☂","☂",IF(W7&gt;Y7,"○",IF(W7=Y7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X6" s="265" t="n"/>
-      <c r="Y6" s="266" t="n"/>
-      <c r="Z6" s="264">
+      <c r="X6" s="266" t="n"/>
+      <c r="Y6" s="267" t="n"/>
+      <c r="Z6" s="265">
         <f>IF(Z7="","",IF(Z7="☂","☂",IF(Z7&gt;AB7,"○",IF(Z7=AB7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA6" s="265" t="n"/>
-      <c r="AB6" s="266" t="n"/>
-      <c r="AC6" s="264">
+      <c r="AA6" s="266" t="n"/>
+      <c r="AB6" s="267" t="n"/>
+      <c r="AC6" s="265">
         <f>IF(AC7="","",IF(AC7="☂","☂",IF(AC7&gt;AE7,"○",IF(AC7=AE7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD6" s="265" t="n"/>
-      <c r="AE6" s="266" t="n"/>
-      <c r="AF6" s="264">
+      <c r="AD6" s="266" t="n"/>
+      <c r="AE6" s="267" t="n"/>
+      <c r="AF6" s="265">
         <f>IF(AF7="","",IF(AF7="☂","☂",IF(AF7&gt;AH7,"○",IF(AF7=AH7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG6" s="265" t="n"/>
-      <c r="AH6" s="266" t="n"/>
-      <c r="AI6" s="264">
+      <c r="AG6" s="266" t="n"/>
+      <c r="AH6" s="267" t="n"/>
+      <c r="AI6" s="265">
         <f>IF(AI7="","",IF(AI7="☂","☂",IF(AI7&gt;AK7,"○",IF(AI7=AK7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ6" s="265" t="n"/>
-      <c r="AK6" s="266" t="n"/>
-      <c r="AL6" s="267">
+      <c r="AJ6" s="266" t="n"/>
+      <c r="AK6" s="267" t="n"/>
+      <c r="AL6" s="268">
         <f>COUNTIF(E6:AK6,"○")</f>
         <v/>
       </c>
-      <c r="AM6" s="268">
+      <c r="AM6" s="269">
         <f>COUNTIF(E6:AK6,"△")</f>
         <v/>
       </c>
-      <c r="AN6" s="268">
+      <c r="AN6" s="269">
         <f>COUNTIF(E6:AK6,"×")</f>
         <v/>
       </c>
-      <c r="AO6" s="268">
+      <c r="AO6" s="269">
         <f>AL6*3+AM6*1</f>
         <v/>
       </c>
-      <c r="AP6" s="269">
+      <c r="AP6" s="270">
         <f>SUM(J7,M7,P7,S7,V7,Y7,AB7,AK7)</f>
         <v/>
       </c>
-      <c r="AQ6" s="268">
+      <c r="AQ6" s="269">
         <f>SUM(H7,K7,N7,Q7,T7,W7,Z7,AI7)</f>
         <v/>
       </c>
-      <c r="AR6" s="270">
+      <c r="AR6" s="271">
         <f>$AY$21-AL6-AM6-AN6</f>
         <v/>
       </c>
@@ -3201,13 +3186,13 @@
       </c>
     </row>
     <row r="7" ht="46.9" customHeight="1" s="257">
-      <c r="B7" s="271" t="n"/>
-      <c r="C7" s="272" t="n"/>
-      <c r="D7" s="273" t="n"/>
-      <c r="E7" s="262" t="n"/>
-      <c r="F7" s="262" t="n"/>
-      <c r="G7" s="273" t="n"/>
-      <c r="H7" s="274">
+      <c r="B7" s="272" t="n"/>
+      <c r="C7" s="273" t="n"/>
+      <c r="D7" s="274" t="n"/>
+      <c r="E7" s="263" t="n"/>
+      <c r="F7" s="263" t="n"/>
+      <c r="G7" s="274" t="n"/>
+      <c r="H7" s="275">
         <f>IF(G9="","",G9)</f>
         <v/>
       </c>
@@ -3216,11 +3201,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="274">
+      <c r="J7" s="275">
         <f>IF(E9="","",E9)</f>
         <v/>
       </c>
-      <c r="K7" s="274">
+      <c r="K7" s="275">
         <f>IF(G11="","",G11)</f>
         <v/>
       </c>
@@ -3229,11 +3214,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M7" s="274">
+      <c r="M7" s="275">
         <f>IF(E11="","",E11)</f>
         <v/>
       </c>
-      <c r="N7" s="274">
+      <c r="N7" s="275">
         <f>IF(G13="","",G13)</f>
         <v/>
       </c>
@@ -3242,11 +3227,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P7" s="274">
+      <c r="P7" s="275">
         <f>IF(E13="","",E13)</f>
         <v/>
       </c>
-      <c r="Q7" s="274">
+      <c r="Q7" s="275">
         <f>IF(G15="","",G15)</f>
         <v/>
       </c>
@@ -3255,11 +3240,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S7" s="274">
+      <c r="S7" s="275">
         <f>IF(E15="","",E15)</f>
         <v/>
       </c>
-      <c r="T7" s="274">
+      <c r="T7" s="275">
         <f>IF(G17="","",G17)</f>
         <v/>
       </c>
@@ -3268,11 +3253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V7" s="274">
+      <c r="V7" s="275">
         <f>IF(E17="","",E17)</f>
         <v/>
       </c>
-      <c r="W7" s="274">
+      <c r="W7" s="275">
         <f>IF(G19="","",G19)</f>
         <v/>
       </c>
@@ -3281,11 +3266,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y7" s="274">
+      <c r="Y7" s="275">
         <f>IF(E19="","",E19)</f>
         <v/>
       </c>
-      <c r="Z7" s="274">
+      <c r="Z7" s="275">
         <f>IF(G21="","",G21)</f>
         <v/>
       </c>
@@ -3294,11 +3279,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AB7" s="274">
+      <c r="AB7" s="275">
         <f>IF(E21="","",E21)</f>
         <v/>
       </c>
-      <c r="AC7" s="274">
+      <c r="AC7" s="275">
         <f>IF(G23="","",G23)</f>
         <v/>
       </c>
@@ -3307,11 +3292,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AE7" s="274">
+      <c r="AE7" s="275">
         <f>IF(E23="","",E23)</f>
         <v/>
       </c>
-      <c r="AF7" s="274">
+      <c r="AF7" s="275">
         <f>IF(G25="","",G25)</f>
         <v/>
       </c>
@@ -3320,11 +3305,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AH7" s="274">
+      <c r="AH7" s="275">
         <f>IF(E25="","",E25)</f>
         <v/>
       </c>
-      <c r="AI7" s="274">
+      <c r="AI7" s="275">
         <f>IF(G27="","",G27)</f>
         <v/>
       </c>
@@ -3333,21 +3318,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AK7" s="274">
+      <c r="AK7" s="275">
         <f>IF(E27="","",G27)</f>
         <v/>
       </c>
-      <c r="AL7" s="271" t="n"/>
-      <c r="AM7" s="275" t="n"/>
-      <c r="AN7" s="275" t="n"/>
-      <c r="AO7" s="275" t="n"/>
-      <c r="AP7" s="272" t="n"/>
-      <c r="AQ7" s="275" t="n"/>
-      <c r="AR7" s="275" t="n"/>
-      <c r="AS7" s="276" t="n"/>
-      <c r="AV7" s="275" t="n"/>
-      <c r="AW7" s="277" t="n"/>
-      <c r="AX7" s="275" t="n"/>
+      <c r="AL7" s="272" t="n"/>
+      <c r="AM7" s="276" t="n"/>
+      <c r="AN7" s="276" t="n"/>
+      <c r="AO7" s="276" t="n"/>
+      <c r="AP7" s="273" t="n"/>
+      <c r="AQ7" s="276" t="n"/>
+      <c r="AR7" s="276" t="n"/>
+      <c r="AS7" s="277" t="n"/>
+      <c r="AV7" s="276" t="n"/>
+      <c r="AW7" s="278" t="n"/>
+      <c r="AX7" s="276" t="n"/>
       <c r="AZ7" s="5" t="n">
         <v>2</v>
       </c>
@@ -3365,99 +3350,99 @@
         <f>AX8</f>
         <v/>
       </c>
-      <c r="D8" s="263" t="n"/>
+      <c r="D8" s="264" t="n"/>
       <c r="E8" s="122">
         <f>IF(E9="","",IF(E9="☂","☂",IF(E9&gt;G9,"○",IF(E9=G9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F8" s="278" t="n"/>
-      <c r="G8" s="279" t="n"/>
-      <c r="H8" s="280" t="n"/>
-      <c r="I8" s="281" t="n"/>
-      <c r="J8" s="261" t="n"/>
-      <c r="K8" s="282">
+      <c r="F8" s="279" t="n"/>
+      <c r="G8" s="280" t="n"/>
+      <c r="H8" s="281" t="n"/>
+      <c r="I8" s="282" t="n"/>
+      <c r="J8" s="262" t="n"/>
+      <c r="K8" s="283">
         <f>IF(K9="","",IF(K9="☂","☂",IF(K9&gt;M9,"○",IF(K9=M9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L8" s="283" t="n"/>
-      <c r="M8" s="284" t="n"/>
-      <c r="N8" s="282">
+      <c r="L8" s="284" t="n"/>
+      <c r="M8" s="285" t="n"/>
+      <c r="N8" s="283">
         <f>IF(N9="","",IF(N9="☂","☂",IF(N9&gt;P9,"○",IF(N9=P9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O8" s="283" t="n"/>
-      <c r="P8" s="284" t="n"/>
-      <c r="Q8" s="282">
+      <c r="O8" s="284" t="n"/>
+      <c r="P8" s="285" t="n"/>
+      <c r="Q8" s="283">
         <f>IF(Q9="","",IF(Q9="☂","☂",IF(Q9&gt;S9,"○",IF(Q9=S9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R8" s="283" t="n"/>
-      <c r="S8" s="284" t="n"/>
-      <c r="T8" s="282">
+      <c r="R8" s="284" t="n"/>
+      <c r="S8" s="285" t="n"/>
+      <c r="T8" s="283">
         <f>IF(T9="","",IF(T9="☂","☂",IF(T9&gt;V9,"○",IF(T9=V9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U8" s="283" t="n"/>
-      <c r="V8" s="284" t="n"/>
-      <c r="W8" s="282">
+      <c r="U8" s="284" t="n"/>
+      <c r="V8" s="285" t="n"/>
+      <c r="W8" s="283">
         <f>IF(W9="","",IF(W9="☂","☂",IF(W9&gt;Y9,"○",IF(W9=Y9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X8" s="283" t="n"/>
-      <c r="Y8" s="284" t="n"/>
-      <c r="Z8" s="282">
+      <c r="X8" s="284" t="n"/>
+      <c r="Y8" s="285" t="n"/>
+      <c r="Z8" s="283">
         <f>IF(Z9="","",IF(Z9="☂","☂",IF(Z9&gt;AB9,"○",IF(Z9=AB9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA8" s="283" t="n"/>
-      <c r="AB8" s="284" t="n"/>
-      <c r="AC8" s="282">
+      <c r="AA8" s="284" t="n"/>
+      <c r="AB8" s="285" t="n"/>
+      <c r="AC8" s="283">
         <f>IF(AC9="","",IF(AC9="☂","☂",IF(AC9&gt;AE9,"○",IF(AC9=AE9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD8" s="283" t="n"/>
-      <c r="AE8" s="284" t="n"/>
-      <c r="AF8" s="282">
+      <c r="AD8" s="284" t="n"/>
+      <c r="AE8" s="285" t="n"/>
+      <c r="AF8" s="283">
         <f>IF(AF9="","",IF(AF9="☂","☂",IF(AF9&gt;AH9,"○",IF(AF9=AH9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG8" s="283" t="n"/>
-      <c r="AH8" s="284" t="n"/>
-      <c r="AI8" s="282">
+      <c r="AG8" s="284" t="n"/>
+      <c r="AH8" s="285" t="n"/>
+      <c r="AI8" s="283">
         <f>IF(AI9="","",IF(AI9="☂","☂",IF(AI9&gt;AK9,"○",IF(AI9=AK9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ8" s="283" t="n"/>
-      <c r="AK8" s="284" t="n"/>
-      <c r="AL8" s="285">
+      <c r="AJ8" s="284" t="n"/>
+      <c r="AK8" s="285" t="n"/>
+      <c r="AL8" s="286">
         <f>COUNTIF(E8:AK8,"○")</f>
         <v/>
       </c>
-      <c r="AM8" s="286">
+      <c r="AM8" s="287">
         <f>COUNTIF(E8:AK8,"△")</f>
         <v/>
       </c>
-      <c r="AN8" s="286">
+      <c r="AN8" s="287">
         <f>COUNTIF(E8:AK8,"×")</f>
         <v/>
       </c>
-      <c r="AO8" s="286">
+      <c r="AO8" s="287">
         <f>AL8*3+AM8*1</f>
         <v/>
       </c>
-      <c r="AP8" s="286">
+      <c r="AP8" s="287">
         <f>SUM(G9,M9,P9,S9,V9,Y9,AB9,AK9)</f>
         <v/>
       </c>
-      <c r="AQ8" s="286">
+      <c r="AQ8" s="287">
         <f>SUM(E9,K9,N9,Q9,T9,W9,Z9,AI9)</f>
         <v/>
       </c>
-      <c r="AR8" s="286">
+      <c r="AR8" s="287">
         <f>$AY$21-AL8-AM8-AN8</f>
         <v/>
       </c>
-      <c r="AS8" s="287">
+      <c r="AS8" s="288">
         <f>IFERROR(_xlfn.RANK.EQ(AO8,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3481,9 +3466,9 @@
       </c>
     </row>
     <row r="9" ht="46.9" customHeight="1" s="257">
-      <c r="B9" s="271" t="n"/>
-      <c r="C9" s="272" t="n"/>
-      <c r="D9" s="273" t="n"/>
+      <c r="B9" s="272" t="n"/>
+      <c r="C9" s="273" t="n"/>
+      <c r="D9" s="274" t="n"/>
       <c r="E9" s="62" t="n"/>
       <c r="F9" s="123" t="inlineStr">
         <is>
@@ -3491,9 +3476,9 @@
         </is>
       </c>
       <c r="G9" s="63" t="n"/>
-      <c r="H9" s="272" t="n"/>
-      <c r="I9" s="262" t="n"/>
-      <c r="J9" s="273" t="n"/>
+      <c r="H9" s="273" t="n"/>
+      <c r="I9" s="263" t="n"/>
+      <c r="J9" s="274" t="n"/>
       <c r="K9" s="123">
         <f>IF(J11="","",J11)</f>
         <v/>
@@ -3611,17 +3596,17 @@
         <f>IF(H27="","",H27)</f>
         <v/>
       </c>
-      <c r="AL9" s="271" t="n"/>
-      <c r="AM9" s="275" t="n"/>
-      <c r="AN9" s="275" t="n"/>
-      <c r="AO9" s="275" t="n"/>
-      <c r="AP9" s="275" t="n"/>
-      <c r="AQ9" s="275" t="n"/>
-      <c r="AR9" s="275" t="n"/>
-      <c r="AS9" s="288" t="n"/>
-      <c r="AV9" s="275" t="n"/>
-      <c r="AW9" s="277" t="n"/>
-      <c r="AX9" s="275" t="n"/>
+      <c r="AL9" s="272" t="n"/>
+      <c r="AM9" s="276" t="n"/>
+      <c r="AN9" s="276" t="n"/>
+      <c r="AO9" s="276" t="n"/>
+      <c r="AP9" s="276" t="n"/>
+      <c r="AQ9" s="276" t="n"/>
+      <c r="AR9" s="276" t="n"/>
+      <c r="AS9" s="289" t="n"/>
+      <c r="AV9" s="276" t="n"/>
+      <c r="AW9" s="278" t="n"/>
+      <c r="AX9" s="276" t="n"/>
       <c r="AZ9" s="5" t="n">
         <v>4</v>
       </c>
@@ -3639,99 +3624,99 @@
         <f>AX10</f>
         <v/>
       </c>
-      <c r="D10" s="263" t="n"/>
-      <c r="E10" s="289">
+      <c r="D10" s="264" t="n"/>
+      <c r="E10" s="290">
         <f>IF(E11="","",IF(E11="☂","☂",IF(E11&gt;G11,"○",IF(E11=G11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F10" s="278" t="n"/>
-      <c r="G10" s="279" t="n"/>
+      <c r="F10" s="279" t="n"/>
+      <c r="G10" s="280" t="n"/>
       <c r="H10" s="8">
         <f>IF(H11="","",IF(H11="☂","☂",IF(H11&gt;J11,"○",IF(H11=J11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I10" s="278" t="n"/>
-      <c r="J10" s="279" t="n"/>
-      <c r="K10" s="290" t="n"/>
-      <c r="L10" s="281" t="n"/>
-      <c r="M10" s="261" t="n"/>
-      <c r="N10" s="291">
+      <c r="I10" s="279" t="n"/>
+      <c r="J10" s="280" t="n"/>
+      <c r="K10" s="291" t="n"/>
+      <c r="L10" s="282" t="n"/>
+      <c r="M10" s="262" t="n"/>
+      <c r="N10" s="292">
         <f>IF(N11="","",IF(N11="☂","☂",IF(N11&gt;P11,"○",IF(N11=P11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O10" s="283" t="n"/>
-      <c r="P10" s="284" t="n"/>
-      <c r="Q10" s="291">
+      <c r="O10" s="284" t="n"/>
+      <c r="P10" s="285" t="n"/>
+      <c r="Q10" s="292">
         <f>IF(Q11="","",IF(Q11="☂","☂",IF(Q11&gt;S11,"○",IF(Q11=S11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R10" s="283" t="n"/>
-      <c r="S10" s="284" t="n"/>
-      <c r="T10" s="291">
+      <c r="R10" s="284" t="n"/>
+      <c r="S10" s="285" t="n"/>
+      <c r="T10" s="292">
         <f>IF(T11="","",IF(T11="☂","☂",IF(T11&gt;V11,"○",IF(T11=V11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U10" s="283" t="n"/>
-      <c r="V10" s="284" t="n"/>
-      <c r="W10" s="291">
+      <c r="U10" s="284" t="n"/>
+      <c r="V10" s="285" t="n"/>
+      <c r="W10" s="292">
         <f>IF(W11="","",IF(W11="☂","☂",IF(W11&gt;Y11,"○",IF(W11=Y11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X10" s="283" t="n"/>
-      <c r="Y10" s="284" t="n"/>
-      <c r="Z10" s="291">
+      <c r="X10" s="284" t="n"/>
+      <c r="Y10" s="285" t="n"/>
+      <c r="Z10" s="292">
         <f>IF(Z11="","",IF(Z11="☂","☂",IF(Z11&gt;AB11,"○",IF(Z11=AB11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA10" s="283" t="n"/>
-      <c r="AB10" s="284" t="n"/>
-      <c r="AC10" s="291">
+      <c r="AA10" s="284" t="n"/>
+      <c r="AB10" s="285" t="n"/>
+      <c r="AC10" s="292">
         <f>IF(AC11="","",IF(AC11="☂","☂",IF(AC11&gt;AE11,"○",IF(AC11=AE11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD10" s="283" t="n"/>
-      <c r="AE10" s="284" t="n"/>
-      <c r="AF10" s="291">
+      <c r="AD10" s="284" t="n"/>
+      <c r="AE10" s="285" t="n"/>
+      <c r="AF10" s="292">
         <f>IF(AF11="","",IF(AF11="☂","☂",IF(AF11&gt;AH11,"○",IF(AF11=AH11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG10" s="283" t="n"/>
-      <c r="AH10" s="284" t="n"/>
-      <c r="AI10" s="291">
+      <c r="AG10" s="284" t="n"/>
+      <c r="AH10" s="285" t="n"/>
+      <c r="AI10" s="292">
         <f>IF(AI11="","",IF(AI11="☂","☂",IF(AI11&gt;AK11,"○",IF(AI11=AK11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ10" s="283" t="n"/>
-      <c r="AK10" s="284" t="n"/>
-      <c r="AL10" s="292">
+      <c r="AJ10" s="284" t="n"/>
+      <c r="AK10" s="285" t="n"/>
+      <c r="AL10" s="293">
         <f>COUNTIF(E10:AK10,"○")</f>
         <v/>
       </c>
-      <c r="AM10" s="293">
+      <c r="AM10" s="294">
         <f>COUNTIF(E10:AK10,"△")</f>
         <v/>
       </c>
-      <c r="AN10" s="293">
+      <c r="AN10" s="294">
         <f>COUNTIF(E10:AK10,"×")</f>
         <v/>
       </c>
-      <c r="AO10" s="293">
+      <c r="AO10" s="294">
         <f>AL10*3+AM10*1</f>
         <v/>
       </c>
-      <c r="AP10" s="293">
+      <c r="AP10" s="294">
         <f>SUM(G11,J11,M11,P11,S11,V11,Y11,AB11,AK11)</f>
         <v/>
       </c>
-      <c r="AQ10" s="293">
+      <c r="AQ10" s="294">
         <f>SUM(E11,H11,K11,N11,Q11,T11,W11,Z11,AI11)</f>
         <v/>
       </c>
-      <c r="AR10" s="293">
+      <c r="AR10" s="294">
         <f>$AY$21-AL10-AM10-AN10</f>
         <v/>
       </c>
-      <c r="AS10" s="287">
+      <c r="AS10" s="288">
         <f>IFERROR(_xlfn.RANK.EQ(AO10,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3755,9 +3740,9 @@
       </c>
     </row>
     <row r="11" ht="46.9" customHeight="1" s="257">
-      <c r="B11" s="271" t="n"/>
-      <c r="C11" s="272" t="n"/>
-      <c r="D11" s="273" t="n"/>
+      <c r="B11" s="272" t="n"/>
+      <c r="C11" s="273" t="n"/>
+      <c r="D11" s="274" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="10" t="n"/>
@@ -3768,9 +3753,9 @@
         </is>
       </c>
       <c r="J11" s="10" t="n"/>
-      <c r="K11" s="272" t="n"/>
-      <c r="L11" s="262" t="n"/>
-      <c r="M11" s="273" t="n"/>
+      <c r="K11" s="273" t="n"/>
+      <c r="L11" s="263" t="n"/>
+      <c r="M11" s="274" t="n"/>
       <c r="N11" s="8">
         <f>IF(M13="","",M13)</f>
         <v/>
@@ -3875,17 +3860,17 @@
         <f>IF(K27="","",K27)</f>
         <v/>
       </c>
-      <c r="AL11" s="271" t="n"/>
-      <c r="AM11" s="275" t="n"/>
-      <c r="AN11" s="275" t="n"/>
-      <c r="AO11" s="275" t="n"/>
-      <c r="AP11" s="275" t="n"/>
-      <c r="AQ11" s="275" t="n"/>
-      <c r="AR11" s="275" t="n"/>
-      <c r="AS11" s="288" t="n"/>
-      <c r="AV11" s="275" t="n"/>
-      <c r="AW11" s="277" t="n"/>
-      <c r="AX11" s="275" t="n"/>
+      <c r="AL11" s="272" t="n"/>
+      <c r="AM11" s="276" t="n"/>
+      <c r="AN11" s="276" t="n"/>
+      <c r="AO11" s="276" t="n"/>
+      <c r="AP11" s="276" t="n"/>
+      <c r="AQ11" s="276" t="n"/>
+      <c r="AR11" s="276" t="n"/>
+      <c r="AS11" s="289" t="n"/>
+      <c r="AV11" s="276" t="n"/>
+      <c r="AW11" s="278" t="n"/>
+      <c r="AX11" s="276" t="n"/>
       <c r="AZ11" s="5" t="n">
         <v>6</v>
       </c>
@@ -3903,99 +3888,99 @@
         <f>AX12</f>
         <v/>
       </c>
-      <c r="D12" s="263" t="n"/>
-      <c r="E12" s="294">
+      <c r="D12" s="264" t="n"/>
+      <c r="E12" s="295">
         <f>IF(E13="","",IF(E13="☂","☂",IF(E13&gt;G13,"○",IF(E13=G13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F12" s="278" t="n"/>
-      <c r="G12" s="279" t="n"/>
+      <c r="F12" s="279" t="n"/>
+      <c r="G12" s="280" t="n"/>
       <c r="H12" s="123">
         <f>IF(H13="","",IF(H13="☂","☂",IF(H13&gt;J13,"○",IF(H13=J13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I12" s="278" t="n"/>
-      <c r="J12" s="279" t="n"/>
+      <c r="I12" s="279" t="n"/>
+      <c r="J12" s="280" t="n"/>
       <c r="K12" s="123">
         <f>IF(K13="","",IF(K13="☂","☂",IF(K13&gt;M13,"○",IF(K13=M13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L12" s="278" t="n"/>
-      <c r="M12" s="279" t="n"/>
-      <c r="N12" s="280" t="n"/>
-      <c r="O12" s="281" t="n"/>
-      <c r="P12" s="261" t="n"/>
-      <c r="Q12" s="282">
+      <c r="L12" s="279" t="n"/>
+      <c r="M12" s="280" t="n"/>
+      <c r="N12" s="281" t="n"/>
+      <c r="O12" s="282" t="n"/>
+      <c r="P12" s="262" t="n"/>
+      <c r="Q12" s="283">
         <f>IF(Q13="","",IF(Q13="☂","☂",IF(Q13&gt;S13,"○",IF(Q13=S13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R12" s="283" t="n"/>
-      <c r="S12" s="284" t="n"/>
-      <c r="T12" s="282">
+      <c r="R12" s="284" t="n"/>
+      <c r="S12" s="285" t="n"/>
+      <c r="T12" s="283">
         <f>IF(T13="","",IF(T13="☂","☂",IF(T13&gt;V13,"○",IF(T13=V13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U12" s="283" t="n"/>
-      <c r="V12" s="284" t="n"/>
-      <c r="W12" s="282">
+      <c r="U12" s="284" t="n"/>
+      <c r="V12" s="285" t="n"/>
+      <c r="W12" s="283">
         <f>IF(W13="","",IF(W13="☂","☂",IF(W13&gt;Y13,"○",IF(W13=Y13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X12" s="283" t="n"/>
-      <c r="Y12" s="284" t="n"/>
-      <c r="Z12" s="282">
+      <c r="X12" s="284" t="n"/>
+      <c r="Y12" s="285" t="n"/>
+      <c r="Z12" s="283">
         <f>IF(Z13="","",IF(Z13="☂","☂",IF(Z13&gt;AB13,"○",IF(Z13=AB13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA12" s="283" t="n"/>
-      <c r="AB12" s="284" t="n"/>
-      <c r="AC12" s="282">
+      <c r="AA12" s="284" t="n"/>
+      <c r="AB12" s="285" t="n"/>
+      <c r="AC12" s="283">
         <f>IF(AC13="","",IF(AC13="☂","☂",IF(AC13&gt;AE13,"○",IF(AC13=AE13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD12" s="283" t="n"/>
-      <c r="AE12" s="284" t="n"/>
-      <c r="AF12" s="282">
+      <c r="AD12" s="284" t="n"/>
+      <c r="AE12" s="285" t="n"/>
+      <c r="AF12" s="283">
         <f>IF(AF13="","",IF(AF13="☂","☂",IF(AF13&gt;AH13,"○",IF(AF13=AH13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG12" s="283" t="n"/>
-      <c r="AH12" s="284" t="n"/>
-      <c r="AI12" s="282">
+      <c r="AG12" s="284" t="n"/>
+      <c r="AH12" s="285" t="n"/>
+      <c r="AI12" s="283">
         <f>IF(AI13="","",IF(AI13="☂","☂",IF(AI13&gt;AK13,"○",IF(AI13=AK13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ12" s="283" t="n"/>
-      <c r="AK12" s="284" t="n"/>
-      <c r="AL12" s="285">
+      <c r="AJ12" s="284" t="n"/>
+      <c r="AK12" s="285" t="n"/>
+      <c r="AL12" s="286">
         <f>COUNTIF(E12:AK12,"○")</f>
         <v/>
       </c>
-      <c r="AM12" s="286">
+      <c r="AM12" s="287">
         <f>COUNTIF(E12:AK12,"△")</f>
         <v/>
       </c>
-      <c r="AN12" s="286">
+      <c r="AN12" s="287">
         <f>COUNTIF(E12:AK12,"×")</f>
         <v/>
       </c>
-      <c r="AO12" s="286">
+      <c r="AO12" s="287">
         <f>AL12*3+AM12*1</f>
         <v/>
       </c>
-      <c r="AP12" s="286">
+      <c r="AP12" s="287">
         <f>SUM(G13,J13,M13,P13,S13,V13,Y13,AB13,AK13)</f>
         <v/>
       </c>
-      <c r="AQ12" s="286">
+      <c r="AQ12" s="287">
         <f>SUM(E13,H13,K13,N13,Q13,T13,W13,Z13,AI13)</f>
         <v/>
       </c>
-      <c r="AR12" s="286">
+      <c r="AR12" s="287">
         <f>$AY$21-AL12-AM12-AN12</f>
         <v/>
       </c>
-      <c r="AS12" s="295">
+      <c r="AS12" s="296">
         <f>IFERROR(_xlfn.RANK.EQ(AO12,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4015,9 +4000,9 @@
       <c r="BA12" s="6" t="n"/>
     </row>
     <row r="13" ht="46.9" customHeight="1" s="257">
-      <c r="B13" s="271" t="n"/>
-      <c r="C13" s="272" t="n"/>
-      <c r="D13" s="273" t="n"/>
+      <c r="B13" s="272" t="n"/>
+      <c r="C13" s="273" t="n"/>
+      <c r="D13" s="274" t="n"/>
       <c r="E13" s="63" t="n"/>
       <c r="F13" s="123" t="inlineStr">
         <is>
@@ -4039,9 +4024,9 @@
         </is>
       </c>
       <c r="M13" s="63" t="n"/>
-      <c r="N13" s="272" t="n"/>
-      <c r="O13" s="262" t="n"/>
-      <c r="P13" s="273" t="n"/>
+      <c r="N13" s="273" t="n"/>
+      <c r="O13" s="263" t="n"/>
+      <c r="P13" s="274" t="n"/>
       <c r="Q13" s="123">
         <f>IF(P15="","",P15)</f>
         <v/>
@@ -4133,17 +4118,17 @@
         <f>IF(N27="","",N27)</f>
         <v/>
       </c>
-      <c r="AL13" s="271" t="n"/>
-      <c r="AM13" s="275" t="n"/>
-      <c r="AN13" s="275" t="n"/>
-      <c r="AO13" s="275" t="n"/>
-      <c r="AP13" s="275" t="n"/>
-      <c r="AQ13" s="275" t="n"/>
-      <c r="AR13" s="275" t="n"/>
-      <c r="AS13" s="288" t="n"/>
-      <c r="AV13" s="275" t="n"/>
-      <c r="AW13" s="277" t="n"/>
-      <c r="AX13" s="275" t="n"/>
+      <c r="AL13" s="272" t="n"/>
+      <c r="AM13" s="276" t="n"/>
+      <c r="AN13" s="276" t="n"/>
+      <c r="AO13" s="276" t="n"/>
+      <c r="AP13" s="276" t="n"/>
+      <c r="AQ13" s="276" t="n"/>
+      <c r="AR13" s="276" t="n"/>
+      <c r="AS13" s="289" t="n"/>
+      <c r="AV13" s="276" t="n"/>
+      <c r="AW13" s="278" t="n"/>
+      <c r="AX13" s="276" t="n"/>
       <c r="AZ13" s="5" t="n">
         <v>8</v>
       </c>
@@ -4157,99 +4142,99 @@
         <f>AX14</f>
         <v/>
       </c>
-      <c r="D14" s="263" t="n"/>
-      <c r="E14" s="289">
+      <c r="D14" s="264" t="n"/>
+      <c r="E14" s="290">
         <f>IF(E15="","",IF(E15="☂","☂",IF(E15&gt;G15,"○",IF(E15=G15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F14" s="278" t="n"/>
-      <c r="G14" s="279" t="n"/>
+      <c r="F14" s="279" t="n"/>
+      <c r="G14" s="280" t="n"/>
       <c r="H14" s="8">
         <f>IF(H15="","",IF(H15="☂","☂",IF(H15&gt;J15,"○",IF(H15=J15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I14" s="278" t="n"/>
-      <c r="J14" s="279" t="n"/>
+      <c r="I14" s="279" t="n"/>
+      <c r="J14" s="280" t="n"/>
       <c r="K14" s="8">
         <f>IF(K15="","",IF(K15="☂","☂",IF(K15&gt;M15,"○",IF(K15=M15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L14" s="278" t="n"/>
-      <c r="M14" s="279" t="n"/>
-      <c r="N14" s="296">
+      <c r="L14" s="279" t="n"/>
+      <c r="M14" s="280" t="n"/>
+      <c r="N14" s="297">
         <f>IF(N15="","",IF(N15="☂","☂",IF(N15&gt;P15,"○",IF(N15=P15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O14" s="297" t="n"/>
-      <c r="P14" s="298" t="n"/>
-      <c r="Q14" s="290" t="n"/>
-      <c r="R14" s="281" t="n"/>
-      <c r="S14" s="261" t="n"/>
-      <c r="T14" s="291">
+      <c r="O14" s="298" t="n"/>
+      <c r="P14" s="299" t="n"/>
+      <c r="Q14" s="291" t="n"/>
+      <c r="R14" s="282" t="n"/>
+      <c r="S14" s="262" t="n"/>
+      <c r="T14" s="292">
         <f>IF(T15="","",IF(T15="☂","☂",IF(T15&gt;V15,"○",IF(T15=V15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U14" s="283" t="n"/>
-      <c r="V14" s="284" t="n"/>
-      <c r="W14" s="291">
+      <c r="U14" s="284" t="n"/>
+      <c r="V14" s="285" t="n"/>
+      <c r="W14" s="292">
         <f>IF(W15="","",IF(W15="☂","☂",IF(W15&gt;Y15,"○",IF(W15=Y15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X14" s="283" t="n"/>
-      <c r="Y14" s="284" t="n"/>
-      <c r="Z14" s="291">
+      <c r="X14" s="284" t="n"/>
+      <c r="Y14" s="285" t="n"/>
+      <c r="Z14" s="292">
         <f>IF(Z15="","",IF(Z15="☂","☂",IF(Z15&gt;AB15,"○",IF(Z15=AB15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA14" s="283" t="n"/>
-      <c r="AB14" s="284" t="n"/>
-      <c r="AC14" s="291">
+      <c r="AA14" s="284" t="n"/>
+      <c r="AB14" s="285" t="n"/>
+      <c r="AC14" s="292">
         <f>IF(AC15="","",IF(AC15="☂","☂",IF(AC15&gt;AE15,"○",IF(AC15=AE15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD14" s="283" t="n"/>
-      <c r="AE14" s="284" t="n"/>
-      <c r="AF14" s="291">
+      <c r="AD14" s="284" t="n"/>
+      <c r="AE14" s="285" t="n"/>
+      <c r="AF14" s="292">
         <f>IF(AF15="","",IF(AF15="☂","☂",IF(AF15&gt;AH15,"○",IF(AF15=AH15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG14" s="283" t="n"/>
-      <c r="AH14" s="284" t="n"/>
-      <c r="AI14" s="291">
+      <c r="AG14" s="284" t="n"/>
+      <c r="AH14" s="285" t="n"/>
+      <c r="AI14" s="292">
         <f>IF(AI15="","",IF(AI15="☂","☂",IF(AI15&gt;AK15,"○",IF(AI15=AK15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ14" s="283" t="n"/>
-      <c r="AK14" s="284" t="n"/>
-      <c r="AL14" s="292">
+      <c r="AJ14" s="284" t="n"/>
+      <c r="AK14" s="285" t="n"/>
+      <c r="AL14" s="293">
         <f>COUNTIF(E14:AK14,"○")</f>
         <v/>
       </c>
-      <c r="AM14" s="293">
+      <c r="AM14" s="294">
         <f>COUNTIF(E14:AK14,"△")</f>
         <v/>
       </c>
-      <c r="AN14" s="293">
+      <c r="AN14" s="294">
         <f>COUNTIF(E14:AK14,"×")</f>
         <v/>
       </c>
-      <c r="AO14" s="293">
+      <c r="AO14" s="294">
         <f>AL14*3+AM14*1</f>
         <v/>
       </c>
-      <c r="AP14" s="293">
+      <c r="AP14" s="294">
         <f>SUM(G15,J15,M15,P15,S15,V15,Y15,AB15,AK15)</f>
         <v/>
       </c>
-      <c r="AQ14" s="293">
+      <c r="AQ14" s="294">
         <f>SUM(E15,H15,K15,N15,Q15,T15,W15,Z15,AI15)</f>
         <v/>
       </c>
-      <c r="AR14" s="293">
+      <c r="AR14" s="294">
         <f>$AY$21-AL14-AM14-AN14</f>
         <v/>
       </c>
-      <c r="AS14" s="287">
+      <c r="AS14" s="288">
         <f>IFERROR(_xlfn.RANK.EQ(AO14,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4269,9 +4254,9 @@
       <c r="BA14" s="6" t="n"/>
     </row>
     <row r="15" ht="46.9" customHeight="1" s="257">
-      <c r="B15" s="271" t="n"/>
-      <c r="C15" s="272" t="n"/>
-      <c r="D15" s="273" t="n"/>
+      <c r="B15" s="272" t="n"/>
+      <c r="C15" s="273" t="n"/>
+      <c r="D15" s="274" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -4300,9 +4285,9 @@
         </is>
       </c>
       <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="272" t="n"/>
-      <c r="R15" s="262" t="n"/>
-      <c r="S15" s="273" t="n"/>
+      <c r="Q15" s="273" t="n"/>
+      <c r="R15" s="263" t="n"/>
+      <c r="S15" s="274" t="n"/>
       <c r="T15" s="8">
         <f>IF(S17="","",S17)</f>
         <v/>
@@ -4381,17 +4366,17 @@
         <f>IF(Q27="","",Q27)</f>
         <v/>
       </c>
-      <c r="AL15" s="271" t="n"/>
-      <c r="AM15" s="275" t="n"/>
-      <c r="AN15" s="275" t="n"/>
-      <c r="AO15" s="275" t="n"/>
-      <c r="AP15" s="275" t="n"/>
-      <c r="AQ15" s="275" t="n"/>
-      <c r="AR15" s="275" t="n"/>
-      <c r="AS15" s="288" t="n"/>
-      <c r="AV15" s="275" t="n"/>
-      <c r="AW15" s="277" t="n"/>
-      <c r="AX15" s="275" t="n"/>
+      <c r="AL15" s="272" t="n"/>
+      <c r="AM15" s="276" t="n"/>
+      <c r="AN15" s="276" t="n"/>
+      <c r="AO15" s="276" t="n"/>
+      <c r="AP15" s="276" t="n"/>
+      <c r="AQ15" s="276" t="n"/>
+      <c r="AR15" s="276" t="n"/>
+      <c r="AS15" s="289" t="n"/>
+      <c r="AV15" s="276" t="n"/>
+      <c r="AW15" s="278" t="n"/>
+      <c r="AX15" s="276" t="n"/>
       <c r="AZ15" s="5" t="n">
         <v>10</v>
       </c>
@@ -4405,99 +4390,99 @@
         <f>AX16</f>
         <v/>
       </c>
-      <c r="D16" s="263" t="n"/>
-      <c r="E16" s="294">
+      <c r="D16" s="264" t="n"/>
+      <c r="E16" s="295">
         <f>IF(E17="","",IF(E17="☂","☂",IF(E17&gt;G17,"○",IF(E17=G17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F16" s="278" t="n"/>
-      <c r="G16" s="279" t="n"/>
+      <c r="F16" s="279" t="n"/>
+      <c r="G16" s="280" t="n"/>
       <c r="H16" s="123">
         <f>IF(H17="","",IF(H17="☂","☂",IF(H17&gt;J17,"○",IF(H17=J17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I16" s="278" t="n"/>
-      <c r="J16" s="279" t="n"/>
+      <c r="I16" s="279" t="n"/>
+      <c r="J16" s="280" t="n"/>
       <c r="K16" s="123">
         <f>IF(K17="","",IF(K17="☂","☂",IF(K17&gt;M17,"○",IF(K17=M17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L16" s="278" t="n"/>
-      <c r="M16" s="279" t="n"/>
-      <c r="N16" s="299">
+      <c r="L16" s="279" t="n"/>
+      <c r="M16" s="280" t="n"/>
+      <c r="N16" s="300">
         <f>IF(N17="","",IF(N17="☂","☂",IF(N17&gt;P17,"○",IF(N17=P17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O16" s="297" t="n"/>
-      <c r="P16" s="298" t="n"/>
-      <c r="Q16" s="299">
+      <c r="O16" s="298" t="n"/>
+      <c r="P16" s="299" t="n"/>
+      <c r="Q16" s="300">
         <f>IF(Q17="","",IF(Q17="☂","☂",IF(Q17&gt;S17,"○",IF(Q17=S17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R16" s="297" t="n"/>
-      <c r="S16" s="298" t="n"/>
-      <c r="T16" s="280" t="n"/>
-      <c r="U16" s="281" t="n"/>
-      <c r="V16" s="261" t="n"/>
-      <c r="W16" s="282">
+      <c r="R16" s="298" t="n"/>
+      <c r="S16" s="299" t="n"/>
+      <c r="T16" s="281" t="n"/>
+      <c r="U16" s="282" t="n"/>
+      <c r="V16" s="262" t="n"/>
+      <c r="W16" s="283">
         <f>IF(W17="","",IF(W17="☂","☂",IF(W17&gt;Y17,"○",IF(W17=Y17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X16" s="283" t="n"/>
-      <c r="Y16" s="284" t="n"/>
-      <c r="Z16" s="282">
+      <c r="X16" s="284" t="n"/>
+      <c r="Y16" s="285" t="n"/>
+      <c r="Z16" s="283">
         <f>IF(Z17="","",IF(Z17="☂","☂",IF(Z17&gt;AB17,"○",IF(Z17=AB17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA16" s="283" t="n"/>
-      <c r="AB16" s="284" t="n"/>
-      <c r="AC16" s="282">
+      <c r="AA16" s="284" t="n"/>
+      <c r="AB16" s="285" t="n"/>
+      <c r="AC16" s="283">
         <f>IF(AC17="","",IF(AC17="☂","☂",IF(AC17&gt;AE17,"○",IF(AC17=AE17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD16" s="283" t="n"/>
-      <c r="AE16" s="284" t="n"/>
-      <c r="AF16" s="282">
+      <c r="AD16" s="284" t="n"/>
+      <c r="AE16" s="285" t="n"/>
+      <c r="AF16" s="283">
         <f>IF(AF17="","",IF(AF17="☂","☂",IF(AF17&gt;AH17,"○",IF(AF17=AH17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG16" s="283" t="n"/>
-      <c r="AH16" s="284" t="n"/>
-      <c r="AI16" s="282">
+      <c r="AG16" s="284" t="n"/>
+      <c r="AH16" s="285" t="n"/>
+      <c r="AI16" s="283">
         <f>IF(AI17="","",IF(AI17="☂","☂",IF(AI17&gt;AK17,"○",IF(AI17=AK17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ16" s="283" t="n"/>
-      <c r="AK16" s="284" t="n"/>
-      <c r="AL16" s="285">
+      <c r="AJ16" s="284" t="n"/>
+      <c r="AK16" s="285" t="n"/>
+      <c r="AL16" s="286">
         <f>COUNTIF(E16:AK16,"○")</f>
         <v/>
       </c>
-      <c r="AM16" s="286">
+      <c r="AM16" s="287">
         <f>COUNTIF(E16:AK16,"△")</f>
         <v/>
       </c>
-      <c r="AN16" s="286">
+      <c r="AN16" s="287">
         <f>COUNTIF(E16:AK16,"×")</f>
         <v/>
       </c>
-      <c r="AO16" s="286">
+      <c r="AO16" s="287">
         <f>AL16*3+AM16*1</f>
         <v/>
       </c>
-      <c r="AP16" s="286">
+      <c r="AP16" s="287">
         <f>SUM(G17,J17,M17,P17,S17,V17,Y17,AB17,AK17)</f>
         <v/>
       </c>
-      <c r="AQ16" s="286">
+      <c r="AQ16" s="287">
         <f>SUM(E17,H17,K17,N17,Q17,T17,W17,Z17,AI17)</f>
         <v/>
       </c>
-      <c r="AR16" s="286">
+      <c r="AR16" s="287">
         <f>$AY$21-AL16-AM16-AN16</f>
         <v/>
       </c>
-      <c r="AS16" s="300">
+      <c r="AS16" s="301">
         <f>IFERROR(_xlfn.RANK.EQ(AO16,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4517,9 +4502,9 @@
       <c r="BA16" s="6" t="n"/>
     </row>
     <row r="17" ht="46.9" customHeight="1" s="257">
-      <c r="B17" s="271" t="n"/>
-      <c r="C17" s="272" t="n"/>
-      <c r="D17" s="273" t="n"/>
+      <c r="B17" s="272" t="n"/>
+      <c r="C17" s="273" t="n"/>
+      <c r="D17" s="274" t="n"/>
       <c r="E17" s="63" t="n"/>
       <c r="F17" s="123" t="inlineStr">
         <is>
@@ -4555,9 +4540,9 @@
         </is>
       </c>
       <c r="S17" s="63" t="n"/>
-      <c r="T17" s="272" t="n"/>
-      <c r="U17" s="262" t="n"/>
-      <c r="V17" s="273" t="n"/>
+      <c r="T17" s="273" t="n"/>
+      <c r="U17" s="263" t="n"/>
+      <c r="V17" s="274" t="n"/>
       <c r="W17" s="123">
         <f>IF(V19="","",V19)</f>
         <v/>
@@ -4623,17 +4608,17 @@
         <f>IF(T27="","",T27)</f>
         <v/>
       </c>
-      <c r="AL17" s="271" t="n"/>
-      <c r="AM17" s="275" t="n"/>
-      <c r="AN17" s="275" t="n"/>
-      <c r="AO17" s="275" t="n"/>
-      <c r="AP17" s="275" t="n"/>
-      <c r="AQ17" s="275" t="n"/>
-      <c r="AR17" s="275" t="n"/>
-      <c r="AS17" s="288" t="n"/>
-      <c r="AV17" s="275" t="n"/>
-      <c r="AW17" s="277" t="n"/>
-      <c r="AX17" s="275" t="n"/>
+      <c r="AL17" s="272" t="n"/>
+      <c r="AM17" s="276" t="n"/>
+      <c r="AN17" s="276" t="n"/>
+      <c r="AO17" s="276" t="n"/>
+      <c r="AP17" s="276" t="n"/>
+      <c r="AQ17" s="276" t="n"/>
+      <c r="AR17" s="276" t="n"/>
+      <c r="AS17" s="289" t="n"/>
+      <c r="AV17" s="276" t="n"/>
+      <c r="AW17" s="278" t="n"/>
+      <c r="AX17" s="276" t="n"/>
       <c r="AZ17" s="5" t="n">
         <v>12</v>
       </c>
@@ -4647,99 +4632,99 @@
         <f>AX18</f>
         <v/>
       </c>
-      <c r="D18" s="263" t="n"/>
-      <c r="E18" s="289">
+      <c r="D18" s="264" t="n"/>
+      <c r="E18" s="290">
         <f>IF(E19="","",IF(E19="☂","☂",IF(E19&gt;G19,"○",IF(E19=G19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F18" s="278" t="n"/>
-      <c r="G18" s="279" t="n"/>
+      <c r="F18" s="279" t="n"/>
+      <c r="G18" s="280" t="n"/>
       <c r="H18" s="8">
         <f>IF(H19="","",IF(H19="☂","☂",IF(H19&gt;J19,"○",IF(H19=J19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I18" s="278" t="n"/>
-      <c r="J18" s="279" t="n"/>
+      <c r="I18" s="279" t="n"/>
+      <c r="J18" s="280" t="n"/>
       <c r="K18" s="8">
         <f>IF(K19="","",IF(K19="☂","☂",IF(K19&gt;M19,"○",IF(K19=M19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L18" s="278" t="n"/>
-      <c r="M18" s="279" t="n"/>
-      <c r="N18" s="296">
+      <c r="L18" s="279" t="n"/>
+      <c r="M18" s="280" t="n"/>
+      <c r="N18" s="297">
         <f>IF(N19="","",IF(N19="☂","☂",IF(N19&gt;P19,"○",IF(N19=P19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O18" s="297" t="n"/>
-      <c r="P18" s="298" t="n"/>
-      <c r="Q18" s="296">
+      <c r="O18" s="298" t="n"/>
+      <c r="P18" s="299" t="n"/>
+      <c r="Q18" s="297">
         <f>IF(Q19="","",IF(Q19="☂","☂",IF(Q19&gt;S19,"○",IF(Q19=S19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R18" s="297" t="n"/>
-      <c r="S18" s="298" t="n"/>
-      <c r="T18" s="296">
+      <c r="R18" s="298" t="n"/>
+      <c r="S18" s="299" t="n"/>
+      <c r="T18" s="297">
         <f>IF(T19="","",IF(T19="☂","☂",IF(T19&gt;V19,"○",IF(T19=V19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U18" s="297" t="n"/>
-      <c r="V18" s="298" t="n"/>
-      <c r="W18" s="290" t="n"/>
-      <c r="X18" s="281" t="n"/>
-      <c r="Y18" s="261" t="n"/>
-      <c r="Z18" s="291">
+      <c r="U18" s="298" t="n"/>
+      <c r="V18" s="299" t="n"/>
+      <c r="W18" s="291" t="n"/>
+      <c r="X18" s="282" t="n"/>
+      <c r="Y18" s="262" t="n"/>
+      <c r="Z18" s="292">
         <f>IF(Z19="","",IF(Z19="☂","☂",IF(Z19&gt;AB19,"○",IF(Z19=AB19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA18" s="283" t="n"/>
-      <c r="AB18" s="284" t="n"/>
-      <c r="AC18" s="291">
+      <c r="AA18" s="284" t="n"/>
+      <c r="AB18" s="285" t="n"/>
+      <c r="AC18" s="292">
         <f>IF(AC19="","",IF(AC19="☂","☂",IF(AC19&gt;AE19,"○",IF(AC19=AE19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD18" s="283" t="n"/>
-      <c r="AE18" s="284" t="n"/>
-      <c r="AF18" s="291">
+      <c r="AD18" s="284" t="n"/>
+      <c r="AE18" s="285" t="n"/>
+      <c r="AF18" s="292">
         <f>IF(AF19="","",IF(AF19="☂","☂",IF(AF19&gt;AH19,"○",IF(AF19=AH19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG18" s="283" t="n"/>
-      <c r="AH18" s="284" t="n"/>
-      <c r="AI18" s="291">
+      <c r="AG18" s="284" t="n"/>
+      <c r="AH18" s="285" t="n"/>
+      <c r="AI18" s="292">
         <f>IF(AI19="","",IF(AI19="☂","☂",IF(AI19&gt;AK19,"○",IF(AI19=AK19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ18" s="283" t="n"/>
-      <c r="AK18" s="284" t="n"/>
-      <c r="AL18" s="292">
+      <c r="AJ18" s="284" t="n"/>
+      <c r="AK18" s="285" t="n"/>
+      <c r="AL18" s="293">
         <f>COUNTIF(E18:AK18,"○")</f>
         <v/>
       </c>
-      <c r="AM18" s="293">
+      <c r="AM18" s="294">
         <f>COUNTIF(E18:AK18,"△")</f>
         <v/>
       </c>
-      <c r="AN18" s="293">
+      <c r="AN18" s="294">
         <f>COUNTIF(E18:AK18,"×")</f>
         <v/>
       </c>
-      <c r="AO18" s="293">
+      <c r="AO18" s="294">
         <f>AL18*3+AM18*1</f>
         <v/>
       </c>
-      <c r="AP18" s="293">
+      <c r="AP18" s="294">
         <f>SUM(G19,J19,M19,P19,S19,V19,Y19,AB19,AK19)</f>
         <v/>
       </c>
-      <c r="AQ18" s="293">
+      <c r="AQ18" s="294">
         <f>SUM(E19,H19,K19,N19,Q19,T19,W19,Z19,AI19)</f>
         <v/>
       </c>
-      <c r="AR18" s="293">
+      <c r="AR18" s="294">
         <f>$AY$21-AL18-AM18-AN18</f>
         <v/>
       </c>
-      <c r="AS18" s="287">
+      <c r="AS18" s="288">
         <f>IFERROR(_xlfn.RANK.EQ(AO18,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4757,9 +4742,9 @@
       <c r="BA18" s="6" t="n"/>
     </row>
     <row r="19" ht="46.9" customHeight="1" s="257">
-      <c r="B19" s="271" t="n"/>
-      <c r="C19" s="272" t="n"/>
-      <c r="D19" s="273" t="n"/>
+      <c r="B19" s="272" t="n"/>
+      <c r="C19" s="273" t="n"/>
+      <c r="D19" s="274" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -4802,9 +4787,9 @@
         </is>
       </c>
       <c r="V19" s="10" t="n"/>
-      <c r="W19" s="272" t="n"/>
-      <c r="X19" s="262" t="n"/>
-      <c r="Y19" s="273" t="n"/>
+      <c r="W19" s="273" t="n"/>
+      <c r="X19" s="263" t="n"/>
+      <c r="Y19" s="274" t="n"/>
       <c r="Z19" s="8">
         <f>IF(Y21="","",Y21)</f>
         <v/>
@@ -4857,17 +4842,17 @@
         <f>IF(W27="","",W27)</f>
         <v/>
       </c>
-      <c r="AL19" s="271" t="n"/>
-      <c r="AM19" s="275" t="n"/>
-      <c r="AN19" s="275" t="n"/>
-      <c r="AO19" s="275" t="n"/>
-      <c r="AP19" s="275" t="n"/>
-      <c r="AQ19" s="275" t="n"/>
-      <c r="AR19" s="275" t="n"/>
-      <c r="AS19" s="288" t="n"/>
-      <c r="AV19" s="275" t="n"/>
-      <c r="AW19" s="277" t="n"/>
-      <c r="AX19" s="275" t="n"/>
+      <c r="AL19" s="272" t="n"/>
+      <c r="AM19" s="276" t="n"/>
+      <c r="AN19" s="276" t="n"/>
+      <c r="AO19" s="276" t="n"/>
+      <c r="AP19" s="276" t="n"/>
+      <c r="AQ19" s="276" t="n"/>
+      <c r="AR19" s="276" t="n"/>
+      <c r="AS19" s="289" t="n"/>
+      <c r="AV19" s="276" t="n"/>
+      <c r="AW19" s="278" t="n"/>
+      <c r="AX19" s="276" t="n"/>
       <c r="AZ19" s="5" t="n">
         <v>14</v>
       </c>
@@ -4881,99 +4866,99 @@
         <f>AX20</f>
         <v/>
       </c>
-      <c r="D20" s="263" t="n"/>
+      <c r="D20" s="264" t="n"/>
       <c r="E20" s="122">
         <f>IF(E21="","",IF(E21="☂","☂",IF(E21&gt;G21,"○",IF(E21=G21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F20" s="278" t="n"/>
-      <c r="G20" s="279" t="n"/>
+      <c r="F20" s="279" t="n"/>
+      <c r="G20" s="280" t="n"/>
       <c r="H20" s="123">
         <f>IF(H21="","",IF(H21="☂","☂",IF(H21&gt;J21,"○",IF(H21=J21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I20" s="278" t="n"/>
-      <c r="J20" s="279" t="n"/>
+      <c r="I20" s="279" t="n"/>
+      <c r="J20" s="280" t="n"/>
       <c r="K20" s="123">
         <f>IF(K21="","",IF(K21="☂","☂",IF(K21&gt;M21,"○",IF(K21=M21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L20" s="278" t="n"/>
-      <c r="M20" s="279" t="n"/>
-      <c r="N20" s="299">
+      <c r="L20" s="279" t="n"/>
+      <c r="M20" s="280" t="n"/>
+      <c r="N20" s="300">
         <f>IF(N21="","",IF(N21="☂","☂",IF(N21&gt;P21,"○",IF(N21=P21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O20" s="297" t="n"/>
-      <c r="P20" s="298" t="n"/>
-      <c r="Q20" s="299">
+      <c r="O20" s="298" t="n"/>
+      <c r="P20" s="299" t="n"/>
+      <c r="Q20" s="300">
         <f>IF(Q21="","",IF(Q21="☂","☂",IF(Q21&gt;S21,"○",IF(Q21=S21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R20" s="297" t="n"/>
-      <c r="S20" s="298" t="n"/>
-      <c r="T20" s="299">
+      <c r="R20" s="298" t="n"/>
+      <c r="S20" s="299" t="n"/>
+      <c r="T20" s="300">
         <f>IF(T21="","",IF(T21="☂","☂",IF(T21&gt;V21,"○",IF(T21=V21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U20" s="297" t="n"/>
-      <c r="V20" s="298" t="n"/>
-      <c r="W20" s="299">
+      <c r="U20" s="298" t="n"/>
+      <c r="V20" s="299" t="n"/>
+      <c r="W20" s="300">
         <f>IF(W21="","",IF(W21="☂","☂",IF(W21&gt;Y21,"○",IF(W21=Y21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X20" s="297" t="n"/>
-      <c r="Y20" s="298" t="n"/>
-      <c r="Z20" s="280" t="n"/>
-      <c r="AA20" s="281" t="n"/>
-      <c r="AB20" s="261" t="n"/>
-      <c r="AC20" s="282">
+      <c r="X20" s="298" t="n"/>
+      <c r="Y20" s="299" t="n"/>
+      <c r="Z20" s="281" t="n"/>
+      <c r="AA20" s="282" t="n"/>
+      <c r="AB20" s="262" t="n"/>
+      <c r="AC20" s="283">
         <f>IF(AC21="","",IF(AC21="☂","☂",IF(AC21&gt;AE21,"○",IF(AC21=AE21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD20" s="283" t="n"/>
-      <c r="AE20" s="284" t="n"/>
-      <c r="AF20" s="282">
+      <c r="AD20" s="284" t="n"/>
+      <c r="AE20" s="285" t="n"/>
+      <c r="AF20" s="283">
         <f>IF(AF21="","",IF(AF21="☂","☂",IF(AF21&gt;AH21,"○",IF(AF21=AH21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG20" s="283" t="n"/>
-      <c r="AH20" s="284" t="n"/>
-      <c r="AI20" s="282">
+      <c r="AG20" s="284" t="n"/>
+      <c r="AH20" s="285" t="n"/>
+      <c r="AI20" s="283">
         <f>IF(AI21="","",IF(AI21="☂","☂",IF(AI21&gt;AK21,"○",IF(AI21=AK21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ20" s="283" t="n"/>
-      <c r="AK20" s="284" t="n"/>
-      <c r="AL20" s="285">
+      <c r="AJ20" s="284" t="n"/>
+      <c r="AK20" s="285" t="n"/>
+      <c r="AL20" s="286">
         <f>COUNTIF(E20:AK20,"○")</f>
         <v/>
       </c>
-      <c r="AM20" s="286">
+      <c r="AM20" s="287">
         <f>COUNTIF(E20:AK20,"△")</f>
         <v/>
       </c>
-      <c r="AN20" s="286">
+      <c r="AN20" s="287">
         <f>COUNTIF(E20:AK20,"×")</f>
         <v/>
       </c>
-      <c r="AO20" s="286">
+      <c r="AO20" s="287">
         <f>AL20*3+AM20*1</f>
         <v/>
       </c>
-      <c r="AP20" s="286">
+      <c r="AP20" s="287">
         <f>SUM(G21,J21,M21,P21,S21,V21,Y21,AB21,AK21)</f>
         <v/>
       </c>
-      <c r="AQ20" s="286">
+      <c r="AQ20" s="287">
         <f>SUM(E21,H21,K21,N21,Q21,T21,W21,Z21,AI21)</f>
         <v/>
       </c>
-      <c r="AR20" s="286">
+      <c r="AR20" s="287">
         <f>$AY$21-AL20-AM20-AN20</f>
         <v/>
       </c>
-      <c r="AS20" s="287">
+      <c r="AS20" s="288">
         <f>IFERROR(_xlfn.RANK.EQ(AO20,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4991,9 +4976,9 @@
       <c r="BA20" s="6" t="n"/>
     </row>
     <row r="21" ht="46.9" customHeight="1" s="257">
-      <c r="B21" s="301" t="n"/>
-      <c r="C21" s="272" t="n"/>
-      <c r="D21" s="273" t="n"/>
+      <c r="B21" s="302" t="n"/>
+      <c r="C21" s="273" t="n"/>
+      <c r="D21" s="274" t="n"/>
       <c r="E21" s="62" t="n"/>
       <c r="F21" s="123" t="inlineStr">
         <is>
@@ -5043,9 +5028,9 @@
         </is>
       </c>
       <c r="Y21" s="63" t="n"/>
-      <c r="Z21" s="272" t="n"/>
-      <c r="AA21" s="262" t="n"/>
-      <c r="AB21" s="273" t="n"/>
+      <c r="Z21" s="273" t="n"/>
+      <c r="AA21" s="263" t="n"/>
+      <c r="AB21" s="274" t="n"/>
       <c r="AC21" s="123">
         <f>IF(AB23="","",AB23)</f>
         <v/>
@@ -5085,17 +5070,17 @@
         <f>IF(Z27="","",Z27)</f>
         <v/>
       </c>
-      <c r="AL21" s="271" t="n"/>
-      <c r="AM21" s="275" t="n"/>
-      <c r="AN21" s="275" t="n"/>
-      <c r="AO21" s="275" t="n"/>
-      <c r="AP21" s="275" t="n"/>
-      <c r="AQ21" s="275" t="n"/>
-      <c r="AR21" s="275" t="n"/>
-      <c r="AS21" s="288" t="n"/>
-      <c r="AV21" s="275" t="n"/>
-      <c r="AW21" s="277" t="n"/>
-      <c r="AX21" s="275" t="n"/>
+      <c r="AL21" s="272" t="n"/>
+      <c r="AM21" s="276" t="n"/>
+      <c r="AN21" s="276" t="n"/>
+      <c r="AO21" s="276" t="n"/>
+      <c r="AP21" s="276" t="n"/>
+      <c r="AQ21" s="276" t="n"/>
+      <c r="AR21" s="276" t="n"/>
+      <c r="AS21" s="289" t="n"/>
+      <c r="AV21" s="276" t="n"/>
+      <c r="AW21" s="278" t="n"/>
+      <c r="AX21" s="276" t="n"/>
       <c r="AY21" s="1">
         <f>COUNTA(AW6:AW21)</f>
         <v/>
@@ -5109,99 +5094,99 @@
         <f>AX22</f>
         <v/>
       </c>
-      <c r="D22" s="263" t="n"/>
-      <c r="E22" s="289">
+      <c r="D22" s="264" t="n"/>
+      <c r="E22" s="290">
         <f>IF(E23="","",IF(E23="☂","☂",IF(E23&gt;G23,"○",IF(E23=G23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F22" s="278" t="n"/>
-      <c r="G22" s="279" t="n"/>
+      <c r="F22" s="279" t="n"/>
+      <c r="G22" s="280" t="n"/>
       <c r="H22" s="8">
         <f>IF(H23="","",IF(H23="☂","☂",IF(H23&gt;J23,"○",IF(H23=J23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I22" s="278" t="n"/>
-      <c r="J22" s="279" t="n"/>
+      <c r="I22" s="279" t="n"/>
+      <c r="J22" s="280" t="n"/>
       <c r="K22" s="8">
         <f>IF(K23="","",IF(K23="☂","☂",IF(K23&gt;M23,"○",IF(K23=M23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L22" s="278" t="n"/>
-      <c r="M22" s="279" t="n"/>
-      <c r="N22" s="296">
+      <c r="L22" s="279" t="n"/>
+      <c r="M22" s="280" t="n"/>
+      <c r="N22" s="297">
         <f>IF(N23="","",IF(N23="☂","☂",IF(N23&gt;P23,"○",IF(N23=P23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O22" s="297" t="n"/>
-      <c r="P22" s="298" t="n"/>
-      <c r="Q22" s="296">
+      <c r="O22" s="298" t="n"/>
+      <c r="P22" s="299" t="n"/>
+      <c r="Q22" s="297">
         <f>IF(Q23="","",IF(Q23="☂","☂",IF(Q23&gt;S23,"○",IF(Q23=S23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R22" s="297" t="n"/>
-      <c r="S22" s="298" t="n"/>
-      <c r="T22" s="296">
+      <c r="R22" s="298" t="n"/>
+      <c r="S22" s="299" t="n"/>
+      <c r="T22" s="297">
         <f>IF(T23="","",IF(T23="☂","☂",IF(T23&gt;V23,"○",IF(T23=V23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U22" s="297" t="n"/>
-      <c r="V22" s="298" t="n"/>
-      <c r="W22" s="296">
+      <c r="U22" s="298" t="n"/>
+      <c r="V22" s="299" t="n"/>
+      <c r="W22" s="297">
         <f>IF(W23="","",IF(W23="☂","☂",IF(W23&gt;Y23,"○",IF(W23=Y23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X22" s="297" t="n"/>
-      <c r="Y22" s="298" t="n"/>
-      <c r="Z22" s="296">
+      <c r="X22" s="298" t="n"/>
+      <c r="Y22" s="299" t="n"/>
+      <c r="Z22" s="297">
         <f>IF(Z23="","",IF(Z23="☂","☂",IF(Z23&gt;AB23,"○",IF(Z23=AB23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA22" s="297" t="n"/>
-      <c r="AB22" s="298" t="n"/>
-      <c r="AC22" s="302" t="n"/>
-      <c r="AD22" s="303" t="n"/>
-      <c r="AE22" s="304" t="n"/>
-      <c r="AF22" s="296">
+      <c r="AA22" s="298" t="n"/>
+      <c r="AB22" s="299" t="n"/>
+      <c r="AC22" s="303" t="n"/>
+      <c r="AD22" s="304" t="n"/>
+      <c r="AE22" s="305" t="n"/>
+      <c r="AF22" s="297">
         <f>IF(AF23="","",IF(AF23="☂","☂",IF(AF23&gt;AH23,"○",IF(AF23=AH23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG22" s="297" t="n"/>
-      <c r="AH22" s="298" t="n"/>
-      <c r="AI22" s="305">
+      <c r="AG22" s="298" t="n"/>
+      <c r="AH22" s="299" t="n"/>
+      <c r="AI22" s="306">
         <f>IF(AI23="","",IF(AI23="☂","☂",IF(AI23&gt;AK23,"○",IF(AI23=AK23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ22" s="283" t="n"/>
-      <c r="AK22" s="284" t="n"/>
-      <c r="AL22" s="292">
+      <c r="AJ22" s="284" t="n"/>
+      <c r="AK22" s="285" t="n"/>
+      <c r="AL22" s="293">
         <f>COUNTIF(E22:AK22,"○")</f>
         <v/>
       </c>
-      <c r="AM22" s="293">
+      <c r="AM22" s="294">
         <f>COUNTIF(E22:AK22,"△")</f>
         <v/>
       </c>
-      <c r="AN22" s="293">
+      <c r="AN22" s="294">
         <f>COUNTIF(E22:AK22,"×")</f>
         <v/>
       </c>
-      <c r="AO22" s="293">
+      <c r="AO22" s="294">
         <f>AL22*3+AM22*1</f>
         <v/>
       </c>
-      <c r="AP22" s="293">
+      <c r="AP22" s="294">
         <f>SUM(G23,M23,P23,S23,V23,Y23,AB23,AK23)</f>
         <v/>
       </c>
-      <c r="AQ22" s="293">
+      <c r="AQ22" s="294">
         <f>SUM(E23,K23,N23,Q23,T23,W23,Z23,AI23)</f>
         <v/>
       </c>
-      <c r="AR22" s="293">
+      <c r="AR22" s="294">
         <f>10-AL22-AM22-AN22</f>
         <v/>
       </c>
-      <c r="AS22" s="287">
+      <c r="AS22" s="288">
         <f>IFERROR(_xlfn.RANK.EQ(AO22,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5215,9 +5200,9 @@
       </c>
     </row>
     <row r="23" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="B23" s="271" t="n"/>
-      <c r="C23" s="272" t="n"/>
-      <c r="D23" s="273" t="n"/>
+      <c r="B23" s="272" t="n"/>
+      <c r="C23" s="273" t="n"/>
+      <c r="D23" s="274" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
@@ -5274,10 +5259,10 @@
         </is>
       </c>
       <c r="AB23" s="10" t="n"/>
-      <c r="AC23" s="306" t="n"/>
-      <c r="AD23" s="283" t="n"/>
-      <c r="AE23" s="284" t="n"/>
-      <c r="AF23" s="274">
+      <c r="AC23" s="307" t="n"/>
+      <c r="AD23" s="284" t="n"/>
+      <c r="AE23" s="285" t="n"/>
+      <c r="AF23" s="275">
         <f>IF(AE25="","",AE25)</f>
         <v/>
       </c>
@@ -5286,7 +5271,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AH23" s="274">
+      <c r="AH23" s="275">
         <f>IF(AC25="","",AC25)</f>
         <v/>
       </c>
@@ -5303,17 +5288,17 @@
         <f>IF(AC27="","",AC27)</f>
         <v/>
       </c>
-      <c r="AL23" s="271" t="n"/>
-      <c r="AM23" s="275" t="n"/>
-      <c r="AN23" s="275" t="n"/>
-      <c r="AO23" s="275" t="n"/>
-      <c r="AP23" s="275" t="n"/>
-      <c r="AQ23" s="275" t="n"/>
-      <c r="AR23" s="275" t="n"/>
-      <c r="AS23" s="288" t="n"/>
-      <c r="AV23" s="275" t="n"/>
-      <c r="AW23" s="277" t="n"/>
-      <c r="AX23" s="275" t="n"/>
+      <c r="AL23" s="272" t="n"/>
+      <c r="AM23" s="276" t="n"/>
+      <c r="AN23" s="276" t="n"/>
+      <c r="AO23" s="276" t="n"/>
+      <c r="AP23" s="276" t="n"/>
+      <c r="AQ23" s="276" t="n"/>
+      <c r="AR23" s="276" t="n"/>
+      <c r="AS23" s="289" t="n"/>
+      <c r="AV23" s="276" t="n"/>
+      <c r="AW23" s="278" t="n"/>
+      <c r="AX23" s="276" t="n"/>
     </row>
     <row r="24" hidden="1" ht="33.6" customHeight="1" s="257">
       <c r="B24" s="174" t="n">
@@ -5323,99 +5308,99 @@
         <f>AX24</f>
         <v/>
       </c>
-      <c r="D24" s="263" t="n"/>
-      <c r="E24" s="307">
+      <c r="D24" s="264" t="n"/>
+      <c r="E24" s="308">
         <f>IF(E25="","",IF(E25="☂","☂",IF(E25&gt;G25,"○",IF(E25=G25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F24" s="278" t="n"/>
-      <c r="G24" s="279" t="n"/>
+      <c r="F24" s="279" t="n"/>
+      <c r="G24" s="280" t="n"/>
       <c r="H24" s="39">
         <f>IF(H25="","",IF(H25="☂","☂",IF(H25&gt;J25,"○",IF(H25=J25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I24" s="278" t="n"/>
-      <c r="J24" s="279" t="n"/>
+      <c r="I24" s="279" t="n"/>
+      <c r="J24" s="280" t="n"/>
       <c r="K24" s="39">
         <f>IF(K25="","",IF(K25="☂","☂",IF(K25&gt;M25,"○",IF(K25=M25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L24" s="278" t="n"/>
-      <c r="M24" s="279" t="n"/>
-      <c r="N24" s="308">
+      <c r="L24" s="279" t="n"/>
+      <c r="M24" s="280" t="n"/>
+      <c r="N24" s="309">
         <f>IF(N25="","",IF(N25="☂","☂",IF(N25&gt;P25,"○",IF(N25=P25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O24" s="297" t="n"/>
-      <c r="P24" s="298" t="n"/>
-      <c r="Q24" s="308">
+      <c r="O24" s="298" t="n"/>
+      <c r="P24" s="299" t="n"/>
+      <c r="Q24" s="309">
         <f>IF(Q25="","",IF(Q25="☂","☂",IF(Q25&gt;S25,"○",IF(Q25=S25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R24" s="297" t="n"/>
-      <c r="S24" s="298" t="n"/>
-      <c r="T24" s="308">
+      <c r="R24" s="298" t="n"/>
+      <c r="S24" s="299" t="n"/>
+      <c r="T24" s="309">
         <f>IF(T25="","",IF(T25="☂","☂",IF(T25&gt;V25,"○",IF(T25=V25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U24" s="297" t="n"/>
-      <c r="V24" s="298" t="n"/>
-      <c r="W24" s="308">
+      <c r="U24" s="298" t="n"/>
+      <c r="V24" s="299" t="n"/>
+      <c r="W24" s="309">
         <f>IF(W25="","",IF(W25="☂","☂",IF(W25&gt;Y25,"○",IF(W25=Y25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X24" s="297" t="n"/>
-      <c r="Y24" s="298" t="n"/>
-      <c r="Z24" s="308">
+      <c r="X24" s="298" t="n"/>
+      <c r="Y24" s="299" t="n"/>
+      <c r="Z24" s="309">
         <f>IF(Z25="","",IF(Z25="☂","☂",IF(Z25&gt;AB25,"○",IF(Z25=AB25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA24" s="297" t="n"/>
-      <c r="AB24" s="298" t="n"/>
-      <c r="AC24" s="308">
+      <c r="AA24" s="298" t="n"/>
+      <c r="AB24" s="299" t="n"/>
+      <c r="AC24" s="309">
         <f>IF(AC25="","",IF(AC25="☂","☂",IF(AC25&gt;AE25,"○",IF(AC25=AE25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD24" s="297" t="n"/>
-      <c r="AE24" s="298" t="n"/>
-      <c r="AF24" s="309" t="n"/>
-      <c r="AG24" s="303" t="n"/>
-      <c r="AH24" s="304" t="n"/>
-      <c r="AI24" s="308">
+      <c r="AD24" s="298" t="n"/>
+      <c r="AE24" s="299" t="n"/>
+      <c r="AF24" s="310" t="n"/>
+      <c r="AG24" s="304" t="n"/>
+      <c r="AH24" s="305" t="n"/>
+      <c r="AI24" s="309">
         <f>IF(AI25="","",IF(AI25="☂","☂",IF(AI25&gt;AK25,"○",IF(AI25=AK25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ24" s="297" t="n"/>
-      <c r="AK24" s="298" t="n"/>
-      <c r="AL24" s="310">
+      <c r="AJ24" s="298" t="n"/>
+      <c r="AK24" s="299" t="n"/>
+      <c r="AL24" s="311">
         <f>COUNTIF(E24:AK24,"○")</f>
         <v/>
       </c>
-      <c r="AM24" s="311">
+      <c r="AM24" s="312">
         <f>COUNTIF(E24:AK24,"△")</f>
         <v/>
       </c>
-      <c r="AN24" s="311">
+      <c r="AN24" s="312">
         <f>COUNTIF(E24:AK24,"×")</f>
         <v/>
       </c>
-      <c r="AO24" s="311">
+      <c r="AO24" s="312">
         <f>AL24*3+AM24*1</f>
         <v/>
       </c>
-      <c r="AP24" s="311">
+      <c r="AP24" s="312">
         <f>SUM(G25,M25,P25,S25,V25,Y25,AB25,AK25)</f>
         <v/>
       </c>
-      <c r="AQ24" s="311">
+      <c r="AQ24" s="312">
         <f>SUM(E25,K25,N25,Q25,T25,W25,Z25,AI25)</f>
         <v/>
       </c>
-      <c r="AR24" s="311">
+      <c r="AR24" s="312">
         <f>10-AL24-AM24-AN24</f>
         <v/>
       </c>
-      <c r="AS24" s="287">
+      <c r="AS24" s="288">
         <f>IFERROR(_xlfn.RANK.EQ(AO24,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5429,9 +5414,9 @@
       </c>
     </row>
     <row r="25" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="B25" s="271" t="n"/>
-      <c r="C25" s="272" t="n"/>
-      <c r="D25" s="273" t="n"/>
+      <c r="B25" s="272" t="n"/>
+      <c r="C25" s="273" t="n"/>
+      <c r="D25" s="274" t="n"/>
       <c r="E25" s="41" t="n"/>
       <c r="F25" s="39" t="inlineStr">
         <is>
@@ -5495,9 +5480,9 @@
         </is>
       </c>
       <c r="AE25" s="40" t="n"/>
-      <c r="AF25" s="312" t="n"/>
-      <c r="AG25" s="313" t="n"/>
-      <c r="AH25" s="314" t="n"/>
+      <c r="AF25" s="313" t="n"/>
+      <c r="AG25" s="314" t="n"/>
+      <c r="AH25" s="315" t="n"/>
       <c r="AI25" s="40">
         <f>IF(AH27="","",AH27)</f>
         <v/>
@@ -5511,17 +5496,17 @@
         <f>IF(AF27="","",AF27)</f>
         <v/>
       </c>
-      <c r="AL25" s="271" t="n"/>
-      <c r="AM25" s="275" t="n"/>
-      <c r="AN25" s="275" t="n"/>
-      <c r="AO25" s="275" t="n"/>
-      <c r="AP25" s="275" t="n"/>
-      <c r="AQ25" s="275" t="n"/>
-      <c r="AR25" s="275" t="n"/>
-      <c r="AS25" s="288" t="n"/>
-      <c r="AV25" s="275" t="n"/>
-      <c r="AW25" s="277" t="n"/>
-      <c r="AX25" s="275" t="n"/>
+      <c r="AL25" s="272" t="n"/>
+      <c r="AM25" s="276" t="n"/>
+      <c r="AN25" s="276" t="n"/>
+      <c r="AO25" s="276" t="n"/>
+      <c r="AP25" s="276" t="n"/>
+      <c r="AQ25" s="276" t="n"/>
+      <c r="AR25" s="276" t="n"/>
+      <c r="AS25" s="289" t="n"/>
+      <c r="AV25" s="276" t="n"/>
+      <c r="AW25" s="278" t="n"/>
+      <c r="AX25" s="276" t="n"/>
     </row>
     <row r="26" hidden="1" ht="33.6" customHeight="1" s="257">
       <c r="B26" s="131" t="n">
@@ -5531,87 +5516,87 @@
         <f>AX26</f>
         <v/>
       </c>
-      <c r="D26" s="263" t="n"/>
-      <c r="E26" s="315">
+      <c r="D26" s="264" t="n"/>
+      <c r="E26" s="316">
         <f>IF(E27="","",IF(E27="☂","☂",IF(E27&gt;G27,"○",IF(E27=G27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F26" s="278" t="n"/>
-      <c r="G26" s="279" t="n"/>
+      <c r="F26" s="279" t="n"/>
+      <c r="G26" s="280" t="n"/>
       <c r="H26" s="16">
         <f>IF(H27="","",IF(H27="☂","☂",IF(H27&gt;J27,"○",IF(H27=J27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I26" s="278" t="n"/>
-      <c r="J26" s="279" t="n"/>
+      <c r="I26" s="279" t="n"/>
+      <c r="J26" s="280" t="n"/>
       <c r="K26" s="16">
         <f>IF(K27="","",IF(K27="☂","☂",IF(K27&gt;M27,"○",IF(K27=M27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L26" s="278" t="n"/>
-      <c r="M26" s="279" t="n"/>
-      <c r="N26" s="316">
+      <c r="L26" s="279" t="n"/>
+      <c r="M26" s="280" t="n"/>
+      <c r="N26" s="317">
         <f>IF(N27="","",IF(N27="☂","☂",IF(N27&gt;P27,"○",IF(N27=P27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O26" s="297" t="n"/>
-      <c r="P26" s="298" t="n"/>
-      <c r="Q26" s="316">
+      <c r="O26" s="298" t="n"/>
+      <c r="P26" s="299" t="n"/>
+      <c r="Q26" s="317">
         <f>IF(Q27="","",IF(Q27="☂","☂",IF(Q27&gt;S27,"○",IF(Q27=S27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R26" s="297" t="n"/>
-      <c r="S26" s="298" t="n"/>
-      <c r="T26" s="316">
+      <c r="R26" s="298" t="n"/>
+      <c r="S26" s="299" t="n"/>
+      <c r="T26" s="317">
         <f>IF(T27="","",IF(T27="☂","☂",IF(T27&gt;V27,"○",IF(T27=V27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U26" s="297" t="n"/>
-      <c r="V26" s="298" t="n"/>
-      <c r="W26" s="316">
+      <c r="U26" s="298" t="n"/>
+      <c r="V26" s="299" t="n"/>
+      <c r="W26" s="317">
         <f>IF(W27="","",IF(W27="☂","☂",IF(W27&gt;Y27,"○",IF(W27=Y27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X26" s="297" t="n"/>
-      <c r="Y26" s="298" t="n"/>
-      <c r="Z26" s="316">
+      <c r="X26" s="298" t="n"/>
+      <c r="Y26" s="299" t="n"/>
+      <c r="Z26" s="317">
         <f>IF(Z27="","",IF(Z27="☂","☂",IF(Z27&gt;AB27,"○",IF(Z27=AB27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA26" s="297" t="n"/>
-      <c r="AB26" s="298" t="n"/>
-      <c r="AC26" s="316">
+      <c r="AA26" s="298" t="n"/>
+      <c r="AB26" s="299" t="n"/>
+      <c r="AC26" s="317">
         <f>IF(AC27="","",IF(AC27="☂","☂",IF(AC27&gt;AE27,"○",IF(AC27=AE27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD26" s="297" t="n"/>
-      <c r="AE26" s="298" t="n"/>
-      <c r="AF26" s="316">
+      <c r="AD26" s="298" t="n"/>
+      <c r="AE26" s="299" t="n"/>
+      <c r="AF26" s="317">
         <f>IF(AF27="","",IF(AF27="☂","☂",IF(AF27&gt;AH27,"○",IF(AF27=AH27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG26" s="297" t="n"/>
-      <c r="AH26" s="298" t="n"/>
-      <c r="AI26" s="317" t="n"/>
-      <c r="AJ26" s="313" t="n"/>
-      <c r="AK26" s="318" t="n"/>
-      <c r="AL26" s="292">
+      <c r="AG26" s="298" t="n"/>
+      <c r="AH26" s="299" t="n"/>
+      <c r="AI26" s="318" t="n"/>
+      <c r="AJ26" s="314" t="n"/>
+      <c r="AK26" s="319" t="n"/>
+      <c r="AL26" s="293">
         <f>COUNTIF(E26:AK26,"○")</f>
         <v/>
       </c>
-      <c r="AM26" s="293">
+      <c r="AM26" s="294">
         <f>COUNTIF(E26:AK26,"△")</f>
         <v/>
       </c>
-      <c r="AN26" s="293">
+      <c r="AN26" s="294">
         <f>COUNTIF(E26:AK26,"×")</f>
         <v/>
       </c>
-      <c r="AO26" s="293">
+      <c r="AO26" s="294">
         <f>AL26*3+AM26*1</f>
         <v/>
       </c>
-      <c r="AP26" s="293">
+      <c r="AP26" s="294">
         <f>SUM(G27,M27,P27,S27,V27,Y27,AB27,AK27)</f>
         <v/>
       </c>
@@ -5623,7 +5608,7 @@
         <f>10-AL26-AM26-AN26</f>
         <v/>
       </c>
-      <c r="AS26" s="319">
+      <c r="AS26" s="320">
         <f>IFERROR(_xlfn.RANK.EQ(AO26,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5637,9 +5622,9 @@
       </c>
     </row>
     <row r="27" hidden="1" ht="33.6" customHeight="1" s="257" thickBot="1">
-      <c r="B27" s="271" t="n"/>
-      <c r="C27" s="272" t="n"/>
-      <c r="D27" s="273" t="n"/>
+      <c r="B27" s="272" t="n"/>
+      <c r="C27" s="273" t="n"/>
+      <c r="D27" s="274" t="n"/>
       <c r="E27" s="13" t="n"/>
       <c r="F27" s="14" t="inlineStr">
         <is>
@@ -5703,31 +5688,31 @@
         </is>
       </c>
       <c r="AE27" s="13" t="n"/>
-      <c r="AF27" s="320" t="n"/>
+      <c r="AF27" s="321" t="n"/>
       <c r="AG27" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH27" s="320" t="n"/>
-      <c r="AI27" s="321" t="n"/>
-      <c r="AJ27" s="322" t="n"/>
-      <c r="AK27" s="323" t="n"/>
-      <c r="AL27" s="271" t="n"/>
-      <c r="AM27" s="275" t="n"/>
-      <c r="AN27" s="275" t="n"/>
-      <c r="AO27" s="275" t="n"/>
-      <c r="AP27" s="275" t="n"/>
-      <c r="AQ27" s="324" t="n"/>
-      <c r="AR27" s="324" t="n"/>
-      <c r="AS27" s="325" t="n"/>
-      <c r="AV27" s="275" t="n"/>
-      <c r="AW27" s="277" t="n"/>
-      <c r="AX27" s="275" t="n"/>
+      <c r="AH27" s="321" t="n"/>
+      <c r="AI27" s="322" t="n"/>
+      <c r="AJ27" s="323" t="n"/>
+      <c r="AK27" s="324" t="n"/>
+      <c r="AL27" s="272" t="n"/>
+      <c r="AM27" s="276" t="n"/>
+      <c r="AN27" s="276" t="n"/>
+      <c r="AO27" s="276" t="n"/>
+      <c r="AP27" s="276" t="n"/>
+      <c r="AQ27" s="325" t="n"/>
+      <c r="AR27" s="325" t="n"/>
+      <c r="AS27" s="326" t="n"/>
+      <c r="AV27" s="276" t="n"/>
+      <c r="AW27" s="278" t="n"/>
+      <c r="AX27" s="276" t="n"/>
     </row>
     <row r="28" ht="6.75" customHeight="1" s="257"/>
   </sheetData>
-  <mergeCells count="289">
+  <mergeCells count="290">
     <mergeCell ref="AP18:AP19"/>
     <mergeCell ref="AC5:AE5"/>
     <mergeCell ref="B12:B13"/>
@@ -5766,6 +5751,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW26:AW27"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A1:S1"/>
     <mergeCell ref="AS16:AS17"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="N4:P4"/>
@@ -6070,8 +6056,8 @@
       <c r="T1" s="240" t="n">
         <v>2026</v>
       </c>
-      <c r="U1" s="326" t="n"/>
-      <c r="V1" s="326" t="n"/>
+      <c r="U1" s="327" t="n"/>
+      <c r="V1" s="327" t="n"/>
       <c r="W1" s="238" t="inlineStr">
         <is>
           <t>年</t>
@@ -6080,46 +6066,46 @@
       <c r="X1" s="238" t="n"/>
     </row>
     <row r="2" ht="16.15" customHeight="1" s="257">
-      <c r="A2" s="327" t="inlineStr">
+      <c r="A2" s="328" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="328" t="n"/>
-      <c r="C2" s="328" t="n"/>
-      <c r="D2" s="328" t="n"/>
-      <c r="E2" s="328" t="n"/>
-      <c r="F2" s="329" t="n"/>
-      <c r="G2" s="327" t="inlineStr">
+      <c r="B2" s="329" t="n"/>
+      <c r="C2" s="329" t="n"/>
+      <c r="D2" s="329" t="n"/>
+      <c r="E2" s="329" t="n"/>
+      <c r="F2" s="330" t="n"/>
+      <c r="G2" s="328" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="328" t="n"/>
-      <c r="I2" s="328" t="n"/>
-      <c r="J2" s="328" t="n"/>
-      <c r="K2" s="328" t="n"/>
-      <c r="L2" s="329" t="n"/>
-      <c r="M2" s="327" t="inlineStr">
+      <c r="H2" s="329" t="n"/>
+      <c r="I2" s="329" t="n"/>
+      <c r="J2" s="329" t="n"/>
+      <c r="K2" s="329" t="n"/>
+      <c r="L2" s="330" t="n"/>
+      <c r="M2" s="328" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="328" t="n"/>
-      <c r="O2" s="328" t="n"/>
-      <c r="P2" s="328" t="n"/>
-      <c r="Q2" s="328" t="n"/>
-      <c r="R2" s="329" t="n"/>
+      <c r="N2" s="329" t="n"/>
+      <c r="O2" s="329" t="n"/>
+      <c r="P2" s="329" t="n"/>
+      <c r="Q2" s="329" t="n"/>
+      <c r="R2" s="330" t="n"/>
       <c r="S2" s="246" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="328" t="n"/>
-      <c r="U2" s="328" t="n"/>
-      <c r="V2" s="328" t="n"/>
-      <c r="W2" s="328" t="n"/>
-      <c r="X2" s="329" t="n"/>
+      <c r="T2" s="329" t="n"/>
+      <c r="U2" s="329" t="n"/>
+      <c r="V2" s="329" t="n"/>
+      <c r="W2" s="329" t="n"/>
+      <c r="X2" s="330" t="n"/>
     </row>
     <row r="3" ht="16.15" customHeight="1" s="257">
       <c r="A3" s="53" t="inlineStr">
@@ -6137,8 +6123,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="278" t="n"/>
-      <c r="E3" s="279" t="n"/>
+      <c r="D3" s="279" t="n"/>
+      <c r="E3" s="280" t="n"/>
       <c r="F3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6159,8 +6145,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="278" t="n"/>
-      <c r="K3" s="279" t="n"/>
+      <c r="J3" s="279" t="n"/>
+      <c r="K3" s="280" t="n"/>
       <c r="L3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6181,8 +6167,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="278" t="n"/>
-      <c r="Q3" s="279" t="n"/>
+      <c r="P3" s="279" t="n"/>
+      <c r="Q3" s="280" t="n"/>
       <c r="R3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6203,8 +6189,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="278" t="n"/>
-      <c r="W3" s="279" t="n"/>
+      <c r="V3" s="279" t="n"/>
+      <c r="W3" s="280" t="n"/>
       <c r="X3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6212,7 +6198,7 @@
       </c>
     </row>
     <row r="4" ht="16.15" customHeight="1" s="257">
-      <c r="A4" s="330" t="n">
+      <c r="A4" s="331" t="n">
         <v>45047</v>
       </c>
       <c r="B4" s="69" t="inlineStr">
@@ -6220,15 +6206,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C4" s="331" t="n"/>
+      <c r="C4" s="332" t="n"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="332" t="n"/>
-      <c r="F4" s="333" t="n"/>
-      <c r="G4" s="330" t="n">
+      <c r="E4" s="333" t="n"/>
+      <c r="F4" s="334" t="n"/>
+      <c r="G4" s="331" t="n">
         <v>45078</v>
       </c>
       <c r="H4" s="70" t="inlineStr">
@@ -6236,15 +6222,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I4" s="334" t="n"/>
-      <c r="J4" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K4" s="335" t="n"/>
-      <c r="L4" s="333" t="n"/>
-      <c r="M4" s="330" t="n">
+      <c r="I4" s="335" t="n"/>
+      <c r="J4" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K4" s="336" t="n"/>
+      <c r="L4" s="334" t="n"/>
+      <c r="M4" s="331" t="n">
         <v>45108</v>
       </c>
       <c r="N4" s="69" t="inlineStr">
@@ -6252,24 +6238,24 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O4" s="336">
+      <c r="O4" s="335">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="P4" s="84" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q4" s="337">
+      <c r="P4" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q4" s="336">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="338">
+      <c r="R4" s="334">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="339" t="n">
+      <c r="S4" s="337" t="n">
         <v>45139</v>
       </c>
       <c r="T4" s="69" t="inlineStr">
@@ -6277,17 +6263,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U4" s="331" t="n"/>
+      <c r="U4" s="332" t="n"/>
       <c r="V4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="332" t="n"/>
-      <c r="X4" s="333" t="n"/>
+      <c r="W4" s="333" t="n"/>
+      <c r="X4" s="334" t="n"/>
     </row>
     <row r="5" ht="16.15" customHeight="1" s="257">
-      <c r="A5" s="330" t="n">
+      <c r="A5" s="331" t="n">
         <v>45048</v>
       </c>
       <c r="B5" s="69" t="inlineStr">
@@ -6295,15 +6281,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C5" s="340" t="n"/>
+      <c r="C5" s="335" t="n"/>
       <c r="D5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="341" t="n"/>
-      <c r="F5" s="333" t="n"/>
-      <c r="G5" s="330" t="n">
+      <c r="E5" s="336" t="n"/>
+      <c r="F5" s="334" t="n"/>
+      <c r="G5" s="331" t="n">
         <v>45079</v>
       </c>
       <c r="H5" s="70" t="inlineStr">
@@ -6311,49 +6297,49 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I5" s="340">
+      <c r="I5" s="335">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J5" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K5" s="341">
+      <c r="J5" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K5" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="333">
+      <c r="L5" s="334">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="342" t="n">
+      <c r="M5" s="338" t="n">
         <v>45109</v>
       </c>
-      <c r="N5" s="343" t="inlineStr">
+      <c r="N5" s="339" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="O5" s="344">
+      <c r="O5" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="345" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="346">
+      <c r="P5" s="341" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="342">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="347">
+      <c r="R5" s="343">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="339" t="n">
+      <c r="S5" s="337" t="n">
         <v>45140</v>
       </c>
       <c r="T5" s="69" t="inlineStr">
@@ -6361,17 +6347,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U5" s="340" t="n"/>
+      <c r="U5" s="335" t="n"/>
       <c r="V5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="341" t="n"/>
-      <c r="X5" s="333" t="n"/>
+      <c r="W5" s="336" t="n"/>
+      <c r="X5" s="334" t="n"/>
     </row>
     <row r="6" ht="16.15" customHeight="1" s="257">
-      <c r="A6" s="330" t="n">
+      <c r="A6" s="331" t="n">
         <v>45049</v>
       </c>
       <c r="B6" s="69" t="inlineStr">
@@ -6379,40 +6365,40 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C6" s="340" t="n"/>
+      <c r="C6" s="335" t="n"/>
       <c r="D6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="341" t="n"/>
-      <c r="F6" s="333" t="n"/>
-      <c r="G6" s="342" t="n">
+      <c r="E6" s="336" t="n"/>
+      <c r="F6" s="334" t="n"/>
+      <c r="G6" s="338" t="n">
         <v>45080</v>
       </c>
-      <c r="H6" s="348" t="inlineStr">
+      <c r="H6" s="344" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I6" s="344">
+      <c r="I6" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="345" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="346">
+      <c r="J6" s="341" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="342">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="347">
+      <c r="L6" s="343">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="330" t="n">
+      <c r="M6" s="331" t="n">
         <v>45110</v>
       </c>
       <c r="N6" s="69" t="inlineStr">
@@ -6420,15 +6406,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O6" s="336" t="n"/>
-      <c r="P6" s="84" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q6" s="337" t="n"/>
-      <c r="R6" s="338" t="n"/>
-      <c r="S6" s="339" t="n">
+      <c r="O6" s="335" t="n"/>
+      <c r="P6" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q6" s="336" t="n"/>
+      <c r="R6" s="334" t="n"/>
+      <c r="S6" s="337" t="n">
         <v>45141</v>
       </c>
       <c r="T6" s="69" t="inlineStr">
@@ -6436,17 +6422,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U6" s="340" t="n"/>
+      <c r="U6" s="335" t="n"/>
       <c r="V6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="341" t="n"/>
-      <c r="X6" s="333" t="n"/>
+      <c r="W6" s="336" t="n"/>
+      <c r="X6" s="334" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" s="257">
-      <c r="A7" s="330" t="n">
+      <c r="A7" s="331" t="n">
         <v>45050</v>
       </c>
       <c r="B7" s="69" t="inlineStr">
@@ -6454,15 +6440,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C7" s="340" t="n"/>
+      <c r="C7" s="335" t="n"/>
       <c r="D7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="341" t="n"/>
-      <c r="F7" s="333" t="n"/>
-      <c r="G7" s="330" t="n">
+      <c r="E7" s="336" t="n"/>
+      <c r="F7" s="334" t="n"/>
+      <c r="G7" s="331" t="n">
         <v>45081</v>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -6470,7 +6456,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I7" s="340">
+      <c r="I7" s="335">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6479,15 +6465,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="341">
+      <c r="K7" s="336">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="333">
+      <c r="L7" s="334">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="330" t="n">
+      <c r="M7" s="331" t="n">
         <v>45111</v>
       </c>
       <c r="N7" s="69" t="inlineStr">
@@ -6495,15 +6481,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O7" s="336" t="n"/>
-      <c r="P7" s="84" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q7" s="337" t="n"/>
-      <c r="R7" s="338" t="n"/>
-      <c r="S7" s="339" t="n">
+      <c r="O7" s="335" t="n"/>
+      <c r="P7" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q7" s="336" t="n"/>
+      <c r="R7" s="334" t="n"/>
+      <c r="S7" s="337" t="n">
         <v>45142</v>
       </c>
       <c r="T7" s="69" t="inlineStr">
@@ -6511,17 +6497,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U7" s="340" t="n"/>
+      <c r="U7" s="335" t="n"/>
       <c r="V7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="341" t="n"/>
-      <c r="X7" s="333" t="n"/>
+      <c r="W7" s="336" t="n"/>
+      <c r="X7" s="334" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" s="257">
-      <c r="A8" s="330" t="n">
+      <c r="A8" s="331" t="n">
         <v>45051</v>
       </c>
       <c r="B8" s="69" t="inlineStr">
@@ -6529,15 +6515,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C8" s="340" t="n"/>
+      <c r="C8" s="335" t="n"/>
       <c r="D8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="341" t="n"/>
-      <c r="F8" s="333" t="n"/>
-      <c r="G8" s="330" t="n">
+      <c r="E8" s="336" t="n"/>
+      <c r="F8" s="334" t="n"/>
+      <c r="G8" s="331" t="n">
         <v>45082</v>
       </c>
       <c r="H8" s="70" t="inlineStr">
@@ -6545,15 +6531,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I8" s="340" t="n"/>
+      <c r="I8" s="335" t="n"/>
       <c r="J8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="341" t="n"/>
-      <c r="L8" s="333" t="n"/>
-      <c r="M8" s="330" t="n">
+      <c r="K8" s="336" t="n"/>
+      <c r="L8" s="334" t="n"/>
+      <c r="M8" s="331" t="n">
         <v>45112</v>
       </c>
       <c r="N8" s="69" t="inlineStr">
@@ -6561,15 +6547,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O8" s="336" t="n"/>
-      <c r="P8" s="84" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q8" s="337" t="n"/>
-      <c r="R8" s="338" t="n"/>
-      <c r="S8" s="339" t="n">
+      <c r="O8" s="335" t="n"/>
+      <c r="P8" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q8" s="336" t="n"/>
+      <c r="R8" s="334" t="n"/>
+      <c r="S8" s="337" t="n">
         <v>45143</v>
       </c>
       <c r="T8" s="69" t="inlineStr">
@@ -6577,17 +6563,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U8" s="340" t="n"/>
+      <c r="U8" s="335" t="n"/>
       <c r="V8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="341" t="n"/>
-      <c r="X8" s="333" t="n"/>
+      <c r="W8" s="336" t="n"/>
+      <c r="X8" s="334" t="n"/>
     </row>
     <row r="9" ht="16.15" customHeight="1" s="257">
-      <c r="A9" s="330" t="n">
+      <c r="A9" s="331" t="n">
         <v>45052</v>
       </c>
       <c r="B9" s="69" t="inlineStr">
@@ -6595,15 +6581,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C9" s="340" t="n"/>
+      <c r="C9" s="335" t="n"/>
       <c r="D9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="341" t="n"/>
-      <c r="F9" s="333" t="n"/>
-      <c r="G9" s="330" t="n">
+      <c r="E9" s="336" t="n"/>
+      <c r="F9" s="334" t="n"/>
+      <c r="G9" s="331" t="n">
         <v>45083</v>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -6611,15 +6597,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I9" s="340" t="n"/>
+      <c r="I9" s="335" t="n"/>
       <c r="J9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="341" t="n"/>
-      <c r="L9" s="333" t="n"/>
-      <c r="M9" s="330" t="n">
+      <c r="K9" s="336" t="n"/>
+      <c r="L9" s="334" t="n"/>
+      <c r="M9" s="331" t="n">
         <v>45113</v>
       </c>
       <c r="N9" s="69" t="inlineStr">
@@ -6627,15 +6613,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O9" s="336" t="n"/>
-      <c r="P9" s="84" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q9" s="337" t="n"/>
-      <c r="R9" s="338" t="n"/>
-      <c r="S9" s="339" t="n">
+      <c r="O9" s="335" t="n"/>
+      <c r="P9" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q9" s="336" t="n"/>
+      <c r="R9" s="334" t="n"/>
+      <c r="S9" s="337" t="n">
         <v>45144</v>
       </c>
       <c r="T9" s="69" t="inlineStr">
@@ -6643,17 +6629,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U9" s="340" t="n"/>
+      <c r="U9" s="335" t="n"/>
       <c r="V9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="341" t="n"/>
-      <c r="X9" s="333" t="n"/>
+      <c r="W9" s="336" t="n"/>
+      <c r="X9" s="334" t="n"/>
     </row>
     <row r="10" ht="16.15" customHeight="1" s="257">
-      <c r="A10" s="330" t="n">
+      <c r="A10" s="331" t="n">
         <v>45053</v>
       </c>
       <c r="B10" s="69" t="inlineStr">
@@ -6661,15 +6647,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C10" s="340" t="n"/>
+      <c r="C10" s="335" t="n"/>
       <c r="D10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="341" t="n"/>
-      <c r="F10" s="333" t="n"/>
-      <c r="G10" s="330" t="n">
+      <c r="E10" s="336" t="n"/>
+      <c r="F10" s="334" t="n"/>
+      <c r="G10" s="331" t="n">
         <v>45084</v>
       </c>
       <c r="H10" s="70" t="inlineStr">
@@ -6677,15 +6663,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I10" s="340" t="n"/>
+      <c r="I10" s="335" t="n"/>
       <c r="J10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="341" t="n"/>
-      <c r="L10" s="333" t="n"/>
-      <c r="M10" s="330" t="n">
+      <c r="K10" s="336" t="n"/>
+      <c r="L10" s="334" t="n"/>
+      <c r="M10" s="331" t="n">
         <v>45114</v>
       </c>
       <c r="N10" s="69" t="inlineStr">
@@ -6693,15 +6679,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O10" s="340" t="n"/>
+      <c r="O10" s="335" t="n"/>
       <c r="P10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="341" t="n"/>
-      <c r="R10" s="333" t="n"/>
-      <c r="S10" s="339" t="n">
+      <c r="Q10" s="336" t="n"/>
+      <c r="R10" s="334" t="n"/>
+      <c r="S10" s="337" t="n">
         <v>45145</v>
       </c>
       <c r="T10" s="69" t="inlineStr">
@@ -6709,17 +6695,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U10" s="340" t="n"/>
+      <c r="U10" s="335" t="n"/>
       <c r="V10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="341" t="n"/>
-      <c r="X10" s="333" t="n"/>
+      <c r="W10" s="336" t="n"/>
+      <c r="X10" s="334" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" s="257">
-      <c r="A11" s="330" t="n">
+      <c r="A11" s="331" t="n">
         <v>45054</v>
       </c>
       <c r="B11" s="69" t="inlineStr">
@@ -6727,15 +6713,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C11" s="334" t="n"/>
-      <c r="D11" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E11" s="335" t="n"/>
-      <c r="F11" s="333" t="n"/>
-      <c r="G11" s="330" t="n">
+      <c r="C11" s="335" t="n"/>
+      <c r="D11" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E11" s="336" t="n"/>
+      <c r="F11" s="334" t="n"/>
+      <c r="G11" s="331" t="n">
         <v>45085</v>
       </c>
       <c r="H11" s="70" t="inlineStr">
@@ -6743,15 +6729,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I11" s="340" t="n"/>
+      <c r="I11" s="335" t="n"/>
       <c r="J11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="341" t="n"/>
-      <c r="L11" s="333" t="n"/>
-      <c r="M11" s="330" t="n">
+      <c r="K11" s="336" t="n"/>
+      <c r="L11" s="334" t="n"/>
+      <c r="M11" s="331" t="n">
         <v>45115</v>
       </c>
       <c r="N11" s="69" t="inlineStr">
@@ -6759,15 +6745,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O11" s="340" t="n"/>
+      <c r="O11" s="335" t="n"/>
       <c r="P11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="341" t="n"/>
-      <c r="R11" s="333" t="n"/>
-      <c r="S11" s="339" t="n">
+      <c r="Q11" s="336" t="n"/>
+      <c r="R11" s="334" t="n"/>
+      <c r="S11" s="337" t="n">
         <v>45146</v>
       </c>
       <c r="T11" s="69" t="inlineStr">
@@ -6775,17 +6761,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U11" s="340" t="n"/>
+      <c r="U11" s="335" t="n"/>
       <c r="V11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="341" t="n"/>
-      <c r="X11" s="333" t="n"/>
+      <c r="W11" s="336" t="n"/>
+      <c r="X11" s="334" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" s="257">
-      <c r="A12" s="330" t="n">
+      <c r="A12" s="331" t="n">
         <v>45055</v>
       </c>
       <c r="B12" s="69" t="inlineStr">
@@ -6793,40 +6779,40 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C12" s="334" t="n"/>
-      <c r="D12" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E12" s="335" t="n"/>
-      <c r="F12" s="333" t="n"/>
-      <c r="G12" s="342" t="n">
+      <c r="C12" s="335" t="n"/>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E12" s="336" t="n"/>
+      <c r="F12" s="334" t="n"/>
+      <c r="G12" s="338" t="n">
         <v>45086</v>
       </c>
-      <c r="H12" s="348" t="inlineStr">
+      <c r="H12" s="344" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I12" s="344">
+      <c r="I12" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="345" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="346">
+      <c r="J12" s="341" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="342">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="347">
+      <c r="L12" s="343">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="330" t="n">
+      <c r="M12" s="331" t="n">
         <v>45116</v>
       </c>
       <c r="N12" s="69" t="inlineStr">
@@ -6834,15 +6820,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O12" s="340" t="n"/>
+      <c r="O12" s="335" t="n"/>
       <c r="P12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="341" t="n"/>
-      <c r="R12" s="333" t="n"/>
-      <c r="S12" s="339" t="n">
+      <c r="Q12" s="336" t="n"/>
+      <c r="R12" s="334" t="n"/>
+      <c r="S12" s="337" t="n">
         <v>45147</v>
       </c>
       <c r="T12" s="69" t="inlineStr">
@@ -6850,17 +6836,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U12" s="340" t="n"/>
+      <c r="U12" s="335" t="n"/>
       <c r="V12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="341" t="n"/>
-      <c r="X12" s="333" t="n"/>
+      <c r="W12" s="336" t="n"/>
+      <c r="X12" s="334" t="n"/>
     </row>
     <row r="13" ht="16.15" customHeight="1" s="257">
-      <c r="A13" s="330" t="n">
+      <c r="A13" s="331" t="n">
         <v>45056</v>
       </c>
       <c r="B13" s="69" t="inlineStr">
@@ -6868,15 +6854,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C13" s="334" t="n"/>
-      <c r="D13" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E13" s="335" t="n"/>
-      <c r="F13" s="333" t="n"/>
-      <c r="G13" s="330" t="n">
+      <c r="C13" s="335" t="n"/>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E13" s="336" t="n"/>
+      <c r="F13" s="334" t="n"/>
+      <c r="G13" s="331" t="n">
         <v>45087</v>
       </c>
       <c r="H13" s="70" t="inlineStr">
@@ -6884,7 +6870,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I13" s="340">
+      <c r="I13" s="335">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6893,15 +6879,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="341">
+      <c r="K13" s="336">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="333">
+      <c r="L13" s="334">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="330" t="n">
+      <c r="M13" s="331" t="n">
         <v>45117</v>
       </c>
       <c r="N13" s="69" t="inlineStr">
@@ -6909,15 +6895,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O13" s="340" t="n"/>
+      <c r="O13" s="335" t="n"/>
       <c r="P13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="341" t="n"/>
-      <c r="R13" s="333" t="n"/>
-      <c r="S13" s="339" t="n">
+      <c r="Q13" s="336" t="n"/>
+      <c r="R13" s="334" t="n"/>
+      <c r="S13" s="337" t="n">
         <v>45148</v>
       </c>
       <c r="T13" s="69" t="inlineStr">
@@ -6925,17 +6911,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U13" s="340" t="n"/>
+      <c r="U13" s="335" t="n"/>
       <c r="V13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="341" t="n"/>
-      <c r="X13" s="333" t="n"/>
+      <c r="W13" s="336" t="n"/>
+      <c r="X13" s="334" t="n"/>
     </row>
     <row r="14" ht="16.15" customHeight="1" s="257">
-      <c r="A14" s="330" t="n">
+      <c r="A14" s="331" t="n">
         <v>45057</v>
       </c>
       <c r="B14" s="69" t="inlineStr">
@@ -6943,15 +6929,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C14" s="334" t="n"/>
-      <c r="D14" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E14" s="335" t="n"/>
-      <c r="F14" s="333" t="n"/>
-      <c r="G14" s="330" t="n">
+      <c r="C14" s="335" t="n"/>
+      <c r="D14" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E14" s="336" t="n"/>
+      <c r="F14" s="334" t="n"/>
+      <c r="G14" s="331" t="n">
         <v>45088</v>
       </c>
       <c r="H14" s="70" t="inlineStr">
@@ -6959,7 +6945,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I14" s="340">
+      <c r="I14" s="335">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6968,15 +6954,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="341">
+      <c r="K14" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="333">
+      <c r="L14" s="334">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="330" t="n">
+      <c r="M14" s="331" t="n">
         <v>45118</v>
       </c>
       <c r="N14" s="69" t="inlineStr">
@@ -6984,15 +6970,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O14" s="340" t="n"/>
+      <c r="O14" s="335" t="n"/>
       <c r="P14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="341" t="n"/>
-      <c r="R14" s="333" t="n"/>
-      <c r="S14" s="339" t="n">
+      <c r="Q14" s="336" t="n"/>
+      <c r="R14" s="334" t="n"/>
+      <c r="S14" s="337" t="n">
         <v>45149</v>
       </c>
       <c r="T14" s="69" t="inlineStr">
@@ -7000,17 +6986,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U14" s="340" t="n"/>
+      <c r="U14" s="335" t="n"/>
       <c r="V14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W14" s="341" t="n"/>
-      <c r="X14" s="333" t="n"/>
+      <c r="W14" s="336" t="n"/>
+      <c r="X14" s="334" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" s="257">
-      <c r="A15" s="330" t="n">
+      <c r="A15" s="331" t="n">
         <v>45058</v>
       </c>
       <c r="B15" s="69" t="inlineStr">
@@ -7018,15 +7004,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C15" s="334" t="n"/>
-      <c r="D15" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E15" s="335" t="n"/>
-      <c r="F15" s="333" t="n"/>
-      <c r="G15" s="330" t="n">
+      <c r="C15" s="335" t="n"/>
+      <c r="D15" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E15" s="336" t="n"/>
+      <c r="F15" s="334" t="n"/>
+      <c r="G15" s="331" t="n">
         <v>45089</v>
       </c>
       <c r="H15" s="70" t="inlineStr">
@@ -7034,15 +7020,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I15" s="340" t="n"/>
+      <c r="I15" s="335" t="n"/>
       <c r="J15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="341" t="n"/>
-      <c r="L15" s="333" t="n"/>
-      <c r="M15" s="330" t="n">
+      <c r="K15" s="336" t="n"/>
+      <c r="L15" s="334" t="n"/>
+      <c r="M15" s="331" t="n">
         <v>45119</v>
       </c>
       <c r="N15" s="69" t="inlineStr">
@@ -7050,15 +7036,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O15" s="340" t="n"/>
+      <c r="O15" s="335" t="n"/>
       <c r="P15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="341" t="n"/>
-      <c r="R15" s="333" t="n"/>
-      <c r="S15" s="339" t="n">
+      <c r="Q15" s="336" t="n"/>
+      <c r="R15" s="334" t="n"/>
+      <c r="S15" s="337" t="n">
         <v>45150</v>
       </c>
       <c r="T15" s="69" t="inlineStr">
@@ -7066,17 +7052,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U15" s="340" t="n"/>
+      <c r="U15" s="335" t="n"/>
       <c r="V15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W15" s="341" t="n"/>
-      <c r="X15" s="333" t="n"/>
+      <c r="W15" s="336" t="n"/>
+      <c r="X15" s="334" t="n"/>
     </row>
     <row r="16" ht="16.15" customHeight="1" s="257">
-      <c r="A16" s="330" t="n">
+      <c r="A16" s="331" t="n">
         <v>45059</v>
       </c>
       <c r="B16" s="69" t="inlineStr">
@@ -7084,15 +7070,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C16" s="340" t="n"/>
+      <c r="C16" s="335" t="n"/>
       <c r="D16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="341" t="n"/>
-      <c r="F16" s="333" t="n"/>
-      <c r="G16" s="330" t="n">
+      <c r="E16" s="336" t="n"/>
+      <c r="F16" s="334" t="n"/>
+      <c r="G16" s="331" t="n">
         <v>45090</v>
       </c>
       <c r="H16" s="70" t="inlineStr">
@@ -7100,15 +7086,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I16" s="340" t="n"/>
+      <c r="I16" s="335" t="n"/>
       <c r="J16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="341" t="n"/>
-      <c r="L16" s="333" t="n"/>
-      <c r="M16" s="330" t="n">
+      <c r="K16" s="336" t="n"/>
+      <c r="L16" s="334" t="n"/>
+      <c r="M16" s="331" t="n">
         <v>45120</v>
       </c>
       <c r="N16" s="69" t="inlineStr">
@@ -7116,15 +7102,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O16" s="340" t="n"/>
+      <c r="O16" s="335" t="n"/>
       <c r="P16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="341" t="n"/>
-      <c r="R16" s="333" t="n"/>
-      <c r="S16" s="339" t="n">
+      <c r="Q16" s="336" t="n"/>
+      <c r="R16" s="334" t="n"/>
+      <c r="S16" s="337" t="n">
         <v>45151</v>
       </c>
       <c r="T16" s="69" t="inlineStr">
@@ -7132,17 +7118,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U16" s="340" t="n"/>
+      <c r="U16" s="335" t="n"/>
       <c r="V16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W16" s="341" t="n"/>
-      <c r="X16" s="333" t="n"/>
+      <c r="W16" s="336" t="n"/>
+      <c r="X16" s="334" t="n"/>
     </row>
     <row r="17" ht="16.15" customHeight="1" s="257">
-      <c r="A17" s="330" t="n">
+      <c r="A17" s="331" t="n">
         <v>45060</v>
       </c>
       <c r="B17" s="69" t="inlineStr">
@@ -7150,15 +7136,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C17" s="334" t="n"/>
-      <c r="D17" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E17" s="335" t="n"/>
-      <c r="F17" s="333" t="n"/>
-      <c r="G17" s="330" t="n">
+      <c r="C17" s="335" t="n"/>
+      <c r="D17" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E17" s="336" t="n"/>
+      <c r="F17" s="334" t="n"/>
+      <c r="G17" s="331" t="n">
         <v>45091</v>
       </c>
       <c r="H17" s="70" t="inlineStr">
@@ -7166,15 +7152,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I17" s="340" t="n"/>
-      <c r="J17" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K17" s="341" t="n"/>
-      <c r="L17" s="333" t="n"/>
-      <c r="M17" s="330" t="n">
+      <c r="I17" s="335" t="n"/>
+      <c r="J17" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K17" s="336" t="n"/>
+      <c r="L17" s="334" t="n"/>
+      <c r="M17" s="331" t="n">
         <v>45121</v>
       </c>
       <c r="N17" s="69" t="inlineStr">
@@ -7182,15 +7168,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O17" s="340" t="n"/>
+      <c r="O17" s="335" t="n"/>
       <c r="P17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="341" t="n"/>
-      <c r="R17" s="333" t="n"/>
-      <c r="S17" s="339" t="n">
+      <c r="Q17" s="336" t="n"/>
+      <c r="R17" s="334" t="n"/>
+      <c r="S17" s="337" t="n">
         <v>45152</v>
       </c>
       <c r="T17" s="69" t="inlineStr">
@@ -7198,17 +7184,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U17" s="340" t="n"/>
+      <c r="U17" s="335" t="n"/>
       <c r="V17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W17" s="341" t="n"/>
-      <c r="X17" s="333" t="n"/>
+      <c r="W17" s="336" t="n"/>
+      <c r="X17" s="334" t="n"/>
     </row>
     <row r="18" ht="16.15" customHeight="1" s="257">
-      <c r="A18" s="330" t="n">
+      <c r="A18" s="331" t="n">
         <v>45061</v>
       </c>
       <c r="B18" s="69" t="inlineStr">
@@ -7216,15 +7202,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C18" s="334" t="n"/>
-      <c r="D18" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E18" s="335" t="n"/>
-      <c r="F18" s="333" t="n"/>
-      <c r="G18" s="330" t="n">
+      <c r="C18" s="335" t="n"/>
+      <c r="D18" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E18" s="336" t="n"/>
+      <c r="F18" s="334" t="n"/>
+      <c r="G18" s="331" t="n">
         <v>45092</v>
       </c>
       <c r="H18" s="70" t="inlineStr">
@@ -7232,15 +7218,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I18" s="340" t="n"/>
-      <c r="J18" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K18" s="341" t="n"/>
-      <c r="L18" s="333" t="n"/>
-      <c r="M18" s="330" t="n">
+      <c r="I18" s="335" t="n"/>
+      <c r="J18" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K18" s="336" t="n"/>
+      <c r="L18" s="334" t="n"/>
+      <c r="M18" s="331" t="n">
         <v>45122</v>
       </c>
       <c r="N18" s="69" t="inlineStr">
@@ -7248,15 +7234,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O18" s="340" t="n"/>
+      <c r="O18" s="335" t="n"/>
       <c r="P18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="341" t="n"/>
-      <c r="R18" s="333" t="n"/>
-      <c r="S18" s="339" t="n">
+      <c r="Q18" s="336" t="n"/>
+      <c r="R18" s="334" t="n"/>
+      <c r="S18" s="337" t="n">
         <v>45153</v>
       </c>
       <c r="T18" s="69" t="inlineStr">
@@ -7264,17 +7250,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U18" s="340" t="n"/>
+      <c r="U18" s="335" t="n"/>
       <c r="V18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W18" s="341" t="n"/>
-      <c r="X18" s="333" t="n"/>
+      <c r="W18" s="336" t="n"/>
+      <c r="X18" s="334" t="n"/>
     </row>
     <row r="19" ht="16.15" customHeight="1" s="257">
-      <c r="A19" s="330" t="n">
+      <c r="A19" s="331" t="n">
         <v>45062</v>
       </c>
       <c r="B19" s="69" t="inlineStr">
@@ -7282,15 +7268,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C19" s="334" t="n"/>
-      <c r="D19" s="47" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E19" s="335" t="n"/>
-      <c r="F19" s="333" t="n"/>
-      <c r="G19" s="330" t="n">
+      <c r="C19" s="335" t="n"/>
+      <c r="D19" s="50" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E19" s="336" t="n"/>
+      <c r="F19" s="334" t="n"/>
+      <c r="G19" s="331" t="n">
         <v>45093</v>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -7298,15 +7284,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I19" s="340" t="inlineStr">
+      <c r="I19" s="335" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="50" t="n"/>
-      <c r="K19" s="341" t="n"/>
-      <c r="L19" s="333" t="n"/>
-      <c r="M19" s="330" t="n">
+      <c r="K19" s="336" t="n"/>
+      <c r="L19" s="334" t="n"/>
+      <c r="M19" s="331" t="n">
         <v>45123</v>
       </c>
       <c r="N19" s="69" t="inlineStr">
@@ -7314,15 +7300,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O19" s="340" t="n"/>
+      <c r="O19" s="335" t="n"/>
       <c r="P19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="341" t="n"/>
-      <c r="R19" s="333" t="n"/>
-      <c r="S19" s="339" t="n">
+      <c r="Q19" s="336" t="n"/>
+      <c r="R19" s="334" t="n"/>
+      <c r="S19" s="337" t="n">
         <v>45154</v>
       </c>
       <c r="T19" s="69" t="inlineStr">
@@ -7330,17 +7316,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U19" s="340" t="n"/>
+      <c r="U19" s="335" t="n"/>
       <c r="V19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W19" s="341" t="n"/>
-      <c r="X19" s="333" t="n"/>
+      <c r="W19" s="336" t="n"/>
+      <c r="X19" s="334" t="n"/>
     </row>
     <row r="20" ht="16.15" customHeight="1" s="257">
-      <c r="A20" s="330" t="n">
+      <c r="A20" s="331" t="n">
         <v>45063</v>
       </c>
       <c r="B20" s="69" t="inlineStr">
@@ -7348,15 +7334,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C20" s="340" t="n"/>
+      <c r="C20" s="335" t="n"/>
       <c r="D20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="341" t="n"/>
-      <c r="F20" s="333" t="n"/>
-      <c r="G20" s="330" t="n">
+      <c r="E20" s="336" t="n"/>
+      <c r="F20" s="334" t="n"/>
+      <c r="G20" s="331" t="n">
         <v>45094</v>
       </c>
       <c r="H20" s="70" t="inlineStr">
@@ -7364,15 +7350,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I20" s="336" t="inlineStr">
+      <c r="I20" s="335" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
-      <c r="J20" s="84" t="n"/>
-      <c r="K20" s="337" t="n"/>
-      <c r="L20" s="338" t="n"/>
-      <c r="M20" s="330" t="n">
+      <c r="J20" s="50" t="n"/>
+      <c r="K20" s="336" t="n"/>
+      <c r="L20" s="334" t="n"/>
+      <c r="M20" s="331" t="n">
         <v>45124</v>
       </c>
       <c r="N20" s="69" t="inlineStr">
@@ -7380,15 +7366,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O20" s="340" t="n"/>
+      <c r="O20" s="335" t="n"/>
       <c r="P20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="341" t="n"/>
-      <c r="R20" s="333" t="n"/>
-      <c r="S20" s="339" t="n">
+      <c r="Q20" s="336" t="n"/>
+      <c r="R20" s="334" t="n"/>
+      <c r="S20" s="337" t="n">
         <v>45155</v>
       </c>
       <c r="T20" s="69" t="inlineStr">
@@ -7396,17 +7382,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U20" s="340" t="n"/>
+      <c r="U20" s="335" t="n"/>
       <c r="V20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W20" s="341" t="n"/>
-      <c r="X20" s="333" t="n"/>
+      <c r="W20" s="336" t="n"/>
+      <c r="X20" s="334" t="n"/>
     </row>
     <row r="21" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A21" s="330" t="n">
+      <c r="A21" s="331" t="n">
         <v>45064</v>
       </c>
       <c r="B21" s="69" t="inlineStr">
@@ -7414,15 +7400,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C21" s="340" t="n"/>
+      <c r="C21" s="335" t="n"/>
       <c r="D21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="341" t="n"/>
-      <c r="F21" s="333" t="n"/>
-      <c r="G21" s="330" t="n">
+      <c r="E21" s="336" t="n"/>
+      <c r="F21" s="334" t="n"/>
+      <c r="G21" s="331" t="n">
         <v>45095</v>
       </c>
       <c r="H21" s="70" t="inlineStr">
@@ -7430,15 +7416,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I21" s="336" t="inlineStr">
+      <c r="I21" s="335" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
-      <c r="J21" s="84" t="n"/>
-      <c r="K21" s="337" t="n"/>
-      <c r="L21" s="338" t="n"/>
-      <c r="M21" s="330" t="n">
+      <c r="J21" s="50" t="n"/>
+      <c r="K21" s="336" t="n"/>
+      <c r="L21" s="334" t="n"/>
+      <c r="M21" s="331" t="n">
         <v>45125</v>
       </c>
       <c r="N21" s="69" t="inlineStr">
@@ -7446,15 +7432,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O21" s="340" t="n"/>
+      <c r="O21" s="335" t="n"/>
       <c r="P21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="341" t="n"/>
-      <c r="R21" s="333" t="n"/>
-      <c r="S21" s="349" t="n">
+      <c r="Q21" s="336" t="n"/>
+      <c r="R21" s="334" t="n"/>
+      <c r="S21" s="345" t="n">
         <v>45156</v>
       </c>
       <c r="T21" s="71" t="inlineStr">
@@ -7462,17 +7448,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U21" s="350" t="n"/>
+      <c r="U21" s="346" t="n"/>
       <c r="V21" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W21" s="351" t="n"/>
-      <c r="X21" s="352" t="n"/>
+      <c r="W21" s="347" t="n"/>
+      <c r="X21" s="348" t="n"/>
     </row>
     <row r="22" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A22" s="330" t="n">
+      <c r="A22" s="331" t="n">
         <v>45065</v>
       </c>
       <c r="B22" s="69" t="inlineStr">
@@ -7480,15 +7466,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C22" s="340" t="n"/>
+      <c r="C22" s="335" t="n"/>
       <c r="D22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="341" t="n"/>
-      <c r="F22" s="333" t="n"/>
-      <c r="G22" s="330" t="n">
+      <c r="E22" s="336" t="n"/>
+      <c r="F22" s="334" t="n"/>
+      <c r="G22" s="331" t="n">
         <v>45096</v>
       </c>
       <c r="H22" s="70" t="inlineStr">
@@ -7496,11 +7482,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I22" s="336" t="n"/>
-      <c r="J22" s="84" t="n"/>
-      <c r="K22" s="337" t="n"/>
-      <c r="L22" s="338" t="n"/>
-      <c r="M22" s="330" t="n">
+      <c r="I22" s="335" t="n"/>
+      <c r="J22" s="50" t="n"/>
+      <c r="K22" s="336" t="n"/>
+      <c r="L22" s="334" t="n"/>
+      <c r="M22" s="331" t="n">
         <v>45126</v>
       </c>
       <c r="N22" s="69" t="inlineStr">
@@ -7508,27 +7494,27 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O22" s="340" t="n"/>
+      <c r="O22" s="335" t="n"/>
       <c r="P22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="341" t="n"/>
-      <c r="R22" s="333" t="n"/>
+      <c r="Q22" s="336" t="n"/>
+      <c r="R22" s="334" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="U22" s="353" t="n"/>
+      <c r="U22" s="349" t="n"/>
       <c r="V22" s="238" t="n"/>
-      <c r="W22" s="354" t="n"/>
-      <c r="X22" s="354" t="n"/>
+      <c r="W22" s="350" t="n"/>
+      <c r="X22" s="350" t="n"/>
     </row>
     <row r="23" ht="16.15" customHeight="1" s="257">
-      <c r="A23" s="330" t="n">
+      <c r="A23" s="331" t="n">
         <v>45066</v>
       </c>
       <c r="B23" s="69" t="inlineStr">
@@ -7536,15 +7522,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C23" s="340" t="n"/>
+      <c r="C23" s="335" t="n"/>
       <c r="D23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="341" t="n"/>
-      <c r="F23" s="333" t="n"/>
-      <c r="G23" s="330" t="n">
+      <c r="E23" s="336" t="n"/>
+      <c r="F23" s="334" t="n"/>
+      <c r="G23" s="331" t="n">
         <v>45097</v>
       </c>
       <c r="H23" s="70" t="inlineStr">
@@ -7552,11 +7538,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I23" s="336" t="n"/>
-      <c r="J23" s="84" t="n"/>
-      <c r="K23" s="337" t="n"/>
-      <c r="L23" s="338" t="n"/>
-      <c r="M23" s="330" t="n">
+      <c r="I23" s="335" t="n"/>
+      <c r="J23" s="50" t="n"/>
+      <c r="K23" s="336" t="n"/>
+      <c r="L23" s="334" t="n"/>
+      <c r="M23" s="331" t="n">
         <v>45127</v>
       </c>
       <c r="N23" s="69" t="inlineStr">
@@ -7564,31 +7550,31 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O23" s="340" t="n"/>
+      <c r="O23" s="335" t="n"/>
       <c r="P23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="341" t="n"/>
-      <c r="R23" s="333" t="n"/>
-      <c r="S23" s="76" t="inlineStr">
+      <c r="Q23" s="336" t="n"/>
+      <c r="R23" s="334" t="n"/>
+      <c r="S23" s="351" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="T23" s="249" t="inlineStr">
+      <c r="T23" s="352" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="U23" s="328" t="n"/>
-      <c r="V23" s="328" t="n"/>
-      <c r="W23" s="328" t="n"/>
-      <c r="X23" s="355" t="n"/>
+      <c r="U23" s="329" t="n"/>
+      <c r="V23" s="329" t="n"/>
+      <c r="W23" s="329" t="n"/>
+      <c r="X23" s="353" t="n"/>
     </row>
     <row r="24" ht="16.15" customHeight="1" s="257">
-      <c r="A24" s="330" t="n">
+      <c r="A24" s="331" t="n">
         <v>45067</v>
       </c>
       <c r="B24" s="69" t="inlineStr">
@@ -7596,15 +7582,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C24" s="340" t="n"/>
+      <c r="C24" s="335" t="n"/>
       <c r="D24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="341" t="n"/>
-      <c r="F24" s="333" t="n"/>
-      <c r="G24" s="330" t="n">
+      <c r="E24" s="336" t="n"/>
+      <c r="F24" s="334" t="n"/>
+      <c r="G24" s="331" t="n">
         <v>45098</v>
       </c>
       <c r="H24" s="70" t="inlineStr">
@@ -7612,11 +7598,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I24" s="336" t="n"/>
-      <c r="J24" s="84" t="n"/>
-      <c r="K24" s="337" t="n"/>
-      <c r="L24" s="338" t="n"/>
-      <c r="M24" s="330" t="n">
+      <c r="I24" s="335" t="n"/>
+      <c r="J24" s="50" t="n"/>
+      <c r="K24" s="336" t="n"/>
+      <c r="L24" s="334" t="n"/>
+      <c r="M24" s="331" t="n">
         <v>45128</v>
       </c>
       <c r="N24" s="69" t="inlineStr">
@@ -7624,14 +7610,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O24" s="340" t="n"/>
+      <c r="O24" s="335" t="n"/>
       <c r="P24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="341" t="n"/>
-      <c r="R24" s="333" t="n"/>
+      <c r="Q24" s="336" t="n"/>
+      <c r="R24" s="334" t="n"/>
       <c r="S24" s="73" t="n">
         <v>1</v>
       </c>
@@ -7640,13 +7626,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U24" s="278" t="n"/>
-      <c r="V24" s="278" t="n"/>
-      <c r="W24" s="278" t="n"/>
-      <c r="X24" s="279" t="n"/>
+      <c r="U24" s="279" t="n"/>
+      <c r="V24" s="279" t="n"/>
+      <c r="W24" s="279" t="n"/>
+      <c r="X24" s="280" t="n"/>
     </row>
     <row r="25" ht="16.15" customHeight="1" s="257">
-      <c r="A25" s="330" t="n">
+      <c r="A25" s="331" t="n">
         <v>45068</v>
       </c>
       <c r="B25" s="69" t="inlineStr">
@@ -7654,15 +7640,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C25" s="340" t="n"/>
+      <c r="C25" s="335" t="n"/>
       <c r="D25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="341" t="n"/>
-      <c r="F25" s="333" t="n"/>
-      <c r="G25" s="330" t="n">
+      <c r="E25" s="336" t="n"/>
+      <c r="F25" s="334" t="n"/>
+      <c r="G25" s="331" t="n">
         <v>45099</v>
       </c>
       <c r="H25" s="70" t="inlineStr">
@@ -7670,11 +7656,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I25" s="336" t="n"/>
-      <c r="J25" s="84" t="n"/>
-      <c r="K25" s="337" t="n"/>
-      <c r="L25" s="338" t="n"/>
-      <c r="M25" s="330" t="n">
+      <c r="I25" s="335" t="n"/>
+      <c r="J25" s="50" t="n"/>
+      <c r="K25" s="336" t="n"/>
+      <c r="L25" s="334" t="n"/>
+      <c r="M25" s="331" t="n">
         <v>45129</v>
       </c>
       <c r="N25" s="69" t="inlineStr">
@@ -7682,14 +7668,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O25" s="340" t="n"/>
+      <c r="O25" s="335" t="n"/>
       <c r="P25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="341" t="n"/>
-      <c r="R25" s="333" t="n"/>
+      <c r="Q25" s="336" t="n"/>
+      <c r="R25" s="334" t="n"/>
       <c r="S25" s="73" t="n">
         <v>2</v>
       </c>
@@ -7698,13 +7684,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U25" s="278" t="n"/>
-      <c r="V25" s="278" t="n"/>
-      <c r="W25" s="278" t="n"/>
-      <c r="X25" s="279" t="n"/>
+      <c r="U25" s="279" t="n"/>
+      <c r="V25" s="279" t="n"/>
+      <c r="W25" s="279" t="n"/>
+      <c r="X25" s="280" t="n"/>
     </row>
     <row r="26" ht="16.15" customHeight="1" s="257">
-      <c r="A26" s="330" t="n">
+      <c r="A26" s="331" t="n">
         <v>45069</v>
       </c>
       <c r="B26" s="69" t="inlineStr">
@@ -7712,36 +7698,36 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C26" s="340" t="n"/>
+      <c r="C26" s="335" t="n"/>
       <c r="D26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="341" t="n"/>
-      <c r="F26" s="333" t="n"/>
-      <c r="G26" s="342" t="n">
+      <c r="E26" s="336" t="n"/>
+      <c r="F26" s="334" t="n"/>
+      <c r="G26" s="338" t="n">
         <v>45100</v>
       </c>
-      <c r="H26" s="348" t="inlineStr">
+      <c r="H26" s="344" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I26" s="344">
+      <c r="I26" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="345" t="n"/>
-      <c r="K26" s="346">
+      <c r="J26" s="341" t="n"/>
+      <c r="K26" s="342">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="347">
+      <c r="L26" s="343">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="330" t="n">
+      <c r="M26" s="331" t="n">
         <v>45130</v>
       </c>
       <c r="N26" s="69" t="inlineStr">
@@ -7749,14 +7735,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O26" s="340" t="n"/>
+      <c r="O26" s="335" t="n"/>
       <c r="P26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="341" t="n"/>
-      <c r="R26" s="333" t="n"/>
+      <c r="Q26" s="336" t="n"/>
+      <c r="R26" s="334" t="n"/>
       <c r="S26" s="73" t="n">
         <v>3</v>
       </c>
@@ -7765,13 +7751,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U26" s="278" t="n"/>
-      <c r="V26" s="278" t="n"/>
-      <c r="W26" s="278" t="n"/>
-      <c r="X26" s="279" t="n"/>
+      <c r="U26" s="279" t="n"/>
+      <c r="V26" s="279" t="n"/>
+      <c r="W26" s="279" t="n"/>
+      <c r="X26" s="280" t="n"/>
     </row>
     <row r="27" ht="16.15" customHeight="1" s="257">
-      <c r="A27" s="330" t="n">
+      <c r="A27" s="331" t="n">
         <v>45070</v>
       </c>
       <c r="B27" s="69" t="inlineStr">
@@ -7779,15 +7765,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C27" s="340" t="n"/>
+      <c r="C27" s="335" t="n"/>
       <c r="D27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="341" t="n"/>
-      <c r="F27" s="333" t="n"/>
-      <c r="G27" s="330" t="n">
+      <c r="E27" s="336" t="n"/>
+      <c r="F27" s="334" t="n"/>
+      <c r="G27" s="331" t="n">
         <v>45101</v>
       </c>
       <c r="H27" s="70" t="inlineStr">
@@ -7795,20 +7781,20 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I27" s="336">
+      <c r="I27" s="335">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J27" s="84" t="n"/>
-      <c r="K27" s="337">
+      <c r="J27" s="50" t="n"/>
+      <c r="K27" s="336">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="338">
+      <c r="L27" s="334">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="330" t="n">
+      <c r="M27" s="331" t="n">
         <v>45131</v>
       </c>
       <c r="N27" s="69" t="inlineStr">
@@ -7816,14 +7802,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O27" s="340" t="n"/>
+      <c r="O27" s="335" t="n"/>
       <c r="P27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="341" t="n"/>
-      <c r="R27" s="333" t="n"/>
+      <c r="Q27" s="336" t="n"/>
+      <c r="R27" s="334" t="n"/>
       <c r="S27" s="73" t="n">
         <v>4</v>
       </c>
@@ -7832,13 +7818,13 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U27" s="278" t="n"/>
-      <c r="V27" s="278" t="n"/>
-      <c r="W27" s="278" t="n"/>
-      <c r="X27" s="279" t="n"/>
+      <c r="U27" s="279" t="n"/>
+      <c r="V27" s="279" t="n"/>
+      <c r="W27" s="279" t="n"/>
+      <c r="X27" s="280" t="n"/>
     </row>
     <row r="28" ht="16.15" customHeight="1" s="257">
-      <c r="A28" s="330" t="n">
+      <c r="A28" s="331" t="n">
         <v>45071</v>
       </c>
       <c r="B28" s="69" t="inlineStr">
@@ -7846,15 +7832,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C28" s="340" t="n"/>
+      <c r="C28" s="335" t="n"/>
       <c r="D28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="341" t="n"/>
-      <c r="F28" s="333" t="n"/>
-      <c r="G28" s="330" t="n">
+      <c r="E28" s="336" t="n"/>
+      <c r="F28" s="334" t="n"/>
+      <c r="G28" s="331" t="n">
         <v>45102</v>
       </c>
       <c r="H28" s="70" t="inlineStr">
@@ -7862,20 +7848,20 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I28" s="336">
+      <c r="I28" s="335">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="J28" s="84" t="n"/>
-      <c r="K28" s="337">
+      <c r="J28" s="50" t="n"/>
+      <c r="K28" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="338">
+      <c r="L28" s="334">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="330" t="n">
+      <c r="M28" s="331" t="n">
         <v>45132</v>
       </c>
       <c r="N28" s="69" t="inlineStr">
@@ -7883,14 +7869,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O28" s="340" t="n"/>
+      <c r="O28" s="335" t="n"/>
       <c r="P28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="341" t="n"/>
-      <c r="R28" s="333" t="n"/>
+      <c r="Q28" s="336" t="n"/>
+      <c r="R28" s="334" t="n"/>
       <c r="S28" s="73" t="n">
         <v>5</v>
       </c>
@@ -7899,13 +7885,13 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U28" s="278" t="n"/>
-      <c r="V28" s="278" t="n"/>
-      <c r="W28" s="278" t="n"/>
-      <c r="X28" s="279" t="n"/>
+      <c r="U28" s="279" t="n"/>
+      <c r="V28" s="279" t="n"/>
+      <c r="W28" s="279" t="n"/>
+      <c r="X28" s="280" t="n"/>
     </row>
     <row r="29" ht="16.15" customHeight="1" s="257">
-      <c r="A29" s="330" t="n">
+      <c r="A29" s="331" t="n">
         <v>45072</v>
       </c>
       <c r="B29" s="69" t="inlineStr">
@@ -7913,7 +7899,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C29" s="340">
+      <c r="C29" s="335">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -7922,15 +7908,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="341">
+      <c r="E29" s="336">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="333">
+      <c r="F29" s="334">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="330" t="n">
+      <c r="G29" s="331" t="n">
         <v>45103</v>
       </c>
       <c r="H29" s="70" t="inlineStr">
@@ -7938,11 +7924,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I29" s="336" t="n"/>
-      <c r="J29" s="84" t="n"/>
-      <c r="K29" s="337" t="n"/>
-      <c r="L29" s="338" t="n"/>
-      <c r="M29" s="330" t="n">
+      <c r="I29" s="335" t="n"/>
+      <c r="J29" s="50" t="n"/>
+      <c r="K29" s="336" t="n"/>
+      <c r="L29" s="334" t="n"/>
+      <c r="M29" s="331" t="n">
         <v>45133</v>
       </c>
       <c r="N29" s="69" t="inlineStr">
@@ -7950,14 +7936,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O29" s="340" t="n"/>
+      <c r="O29" s="335" t="n"/>
       <c r="P29" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="341" t="n"/>
-      <c r="R29" s="333" t="n"/>
+      <c r="Q29" s="336" t="n"/>
+      <c r="R29" s="334" t="n"/>
       <c r="S29" s="73" t="n">
         <v>6</v>
       </c>
@@ -7966,13 +7952,13 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U29" s="278" t="n"/>
-      <c r="V29" s="278" t="n"/>
-      <c r="W29" s="278" t="n"/>
-      <c r="X29" s="279" t="n"/>
+      <c r="U29" s="279" t="n"/>
+      <c r="V29" s="279" t="n"/>
+      <c r="W29" s="279" t="n"/>
+      <c r="X29" s="280" t="n"/>
     </row>
     <row r="30" ht="16.15" customHeight="1" s="257">
-      <c r="A30" s="330" t="n">
+      <c r="A30" s="331" t="n">
         <v>45073</v>
       </c>
       <c r="B30" s="69" t="inlineStr">
@@ -7980,7 +7966,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C30" s="340">
+      <c r="C30" s="335">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -7989,15 +7975,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="341">
+      <c r="E30" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="333">
+      <c r="F30" s="334">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="330" t="n">
+      <c r="G30" s="331" t="n">
         <v>45104</v>
       </c>
       <c r="H30" s="70" t="inlineStr">
@@ -8005,11 +7991,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I30" s="336" t="n"/>
-      <c r="J30" s="84" t="n"/>
-      <c r="K30" s="337" t="n"/>
-      <c r="L30" s="338" t="n"/>
-      <c r="M30" s="330" t="n">
+      <c r="I30" s="335" t="n"/>
+      <c r="J30" s="50" t="n"/>
+      <c r="K30" s="336" t="n"/>
+      <c r="L30" s="334" t="n"/>
+      <c r="M30" s="331" t="n">
         <v>45134</v>
       </c>
       <c r="N30" s="69" t="inlineStr">
@@ -8017,14 +8003,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O30" s="340" t="n"/>
+      <c r="O30" s="335" t="n"/>
       <c r="P30" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="341" t="n"/>
-      <c r="R30" s="333" t="n"/>
+      <c r="Q30" s="336" t="n"/>
+      <c r="R30" s="334" t="n"/>
       <c r="S30" s="73" t="n">
         <v>7</v>
       </c>
@@ -8033,38 +8019,38 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U30" s="278" t="n"/>
-      <c r="V30" s="278" t="n"/>
-      <c r="W30" s="278" t="n"/>
-      <c r="X30" s="279" t="n"/>
+      <c r="U30" s="279" t="n"/>
+      <c r="V30" s="279" t="n"/>
+      <c r="W30" s="279" t="n"/>
+      <c r="X30" s="280" t="n"/>
     </row>
     <row r="31" ht="16.15" customHeight="1" s="257">
-      <c r="A31" s="342" t="n">
+      <c r="A31" s="338" t="n">
         <v>45074</v>
       </c>
-      <c r="B31" s="343" t="inlineStr">
+      <c r="B31" s="339" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="C31" s="344">
+      <c r="C31" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="345" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="346">
+      <c r="D31" s="341" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="342">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="347">
+      <c r="F31" s="343">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="330" t="n">
+      <c r="G31" s="331" t="n">
         <v>45105</v>
       </c>
       <c r="H31" s="70" t="inlineStr">
@@ -8072,11 +8058,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I31" s="336" t="n"/>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="337" t="n"/>
-      <c r="L31" s="338" t="n"/>
-      <c r="M31" s="330" t="n">
+      <c r="I31" s="335" t="n"/>
+      <c r="J31" s="50" t="n"/>
+      <c r="K31" s="336" t="n"/>
+      <c r="L31" s="334" t="n"/>
+      <c r="M31" s="331" t="n">
         <v>45135</v>
       </c>
       <c r="N31" s="69" t="inlineStr">
@@ -8084,14 +8070,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O31" s="340" t="n"/>
+      <c r="O31" s="335" t="n"/>
       <c r="P31" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="341" t="n"/>
-      <c r="R31" s="333" t="n"/>
+      <c r="Q31" s="336" t="n"/>
+      <c r="R31" s="334" t="n"/>
       <c r="S31" s="73" t="n">
         <v>8</v>
       </c>
@@ -8100,13 +8086,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U31" s="278" t="n"/>
-      <c r="V31" s="278" t="n"/>
-      <c r="W31" s="278" t="n"/>
-      <c r="X31" s="279" t="n"/>
+      <c r="U31" s="279" t="n"/>
+      <c r="V31" s="279" t="n"/>
+      <c r="W31" s="279" t="n"/>
+      <c r="X31" s="280" t="n"/>
     </row>
     <row r="32" ht="16.15" customHeight="1" s="257">
-      <c r="A32" s="330" t="n">
+      <c r="A32" s="331" t="n">
         <v>45075</v>
       </c>
       <c r="B32" s="69" t="inlineStr">
@@ -8114,15 +8100,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C32" s="340" t="n"/>
+      <c r="C32" s="335" t="n"/>
       <c r="D32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="341" t="n"/>
-      <c r="F32" s="333" t="n"/>
-      <c r="G32" s="330" t="n">
+      <c r="E32" s="336" t="n"/>
+      <c r="F32" s="334" t="n"/>
+      <c r="G32" s="331" t="n">
         <v>45106</v>
       </c>
       <c r="H32" s="70" t="inlineStr">
@@ -8130,11 +8116,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I32" s="336" t="n"/>
-      <c r="J32" s="84" t="n"/>
-      <c r="K32" s="337" t="n"/>
-      <c r="L32" s="338" t="n"/>
-      <c r="M32" s="330" t="n">
+      <c r="I32" s="335" t="n"/>
+      <c r="J32" s="50" t="n"/>
+      <c r="K32" s="336" t="n"/>
+      <c r="L32" s="334" t="n"/>
+      <c r="M32" s="331" t="n">
         <v>45136</v>
       </c>
       <c r="N32" s="69" t="inlineStr">
@@ -8142,14 +8128,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O32" s="340" t="n"/>
+      <c r="O32" s="335" t="n"/>
       <c r="P32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="341" t="n"/>
-      <c r="R32" s="333" t="n"/>
+      <c r="Q32" s="336" t="n"/>
+      <c r="R32" s="334" t="n"/>
       <c r="S32" s="73" t="n">
         <v>9</v>
       </c>
@@ -8158,13 +8144,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U32" s="278" t="n"/>
-      <c r="V32" s="278" t="n"/>
-      <c r="W32" s="278" t="n"/>
-      <c r="X32" s="279" t="n"/>
+      <c r="U32" s="279" t="n"/>
+      <c r="V32" s="279" t="n"/>
+      <c r="W32" s="279" t="n"/>
+      <c r="X32" s="280" t="n"/>
     </row>
     <row r="33" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A33" s="330" t="n">
+      <c r="A33" s="331" t="n">
         <v>45076</v>
       </c>
       <c r="B33" s="69" t="inlineStr">
@@ -8172,15 +8158,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C33" s="340" t="n"/>
+      <c r="C33" s="335" t="n"/>
       <c r="D33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="341" t="n"/>
-      <c r="F33" s="333" t="n"/>
-      <c r="G33" s="356" t="n">
+      <c r="E33" s="336" t="n"/>
+      <c r="F33" s="334" t="n"/>
+      <c r="G33" s="354" t="n">
         <v>45107</v>
       </c>
       <c r="H33" s="82" t="inlineStr">
@@ -8188,20 +8174,20 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I33" s="357">
+      <c r="I33" s="346">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J33" s="88" t="n"/>
-      <c r="K33" s="358">
+      <c r="J33" s="60" t="n"/>
+      <c r="K33" s="347">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="359">
+      <c r="L33" s="348">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="330" t="n">
+      <c r="M33" s="331" t="n">
         <v>45137</v>
       </c>
       <c r="N33" s="69" t="inlineStr">
@@ -8209,14 +8195,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O33" s="340" t="n"/>
+      <c r="O33" s="335" t="n"/>
       <c r="P33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="341" t="n"/>
-      <c r="R33" s="333" t="n"/>
+      <c r="Q33" s="336" t="n"/>
+      <c r="R33" s="334" t="n"/>
       <c r="S33" s="77" t="n">
         <v>10</v>
       </c>
@@ -8225,13 +8211,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U33" s="360" t="n"/>
-      <c r="V33" s="360" t="n"/>
-      <c r="W33" s="360" t="n"/>
-      <c r="X33" s="361" t="n"/>
+      <c r="U33" s="355" t="n"/>
+      <c r="V33" s="355" t="n"/>
+      <c r="W33" s="355" t="n"/>
+      <c r="X33" s="356" t="n"/>
     </row>
     <row r="34" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A34" s="356" t="n">
+      <c r="A34" s="354" t="n">
         <v>45077</v>
       </c>
       <c r="B34" s="71" t="inlineStr">
@@ -8239,20 +8225,20 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C34" s="350" t="n"/>
+      <c r="C34" s="346" t="n"/>
       <c r="D34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="351" t="n"/>
-      <c r="F34" s="352" t="n"/>
-      <c r="G34" s="362" t="n"/>
-      <c r="I34" s="353" t="n"/>
+      <c r="E34" s="347" t="n"/>
+      <c r="F34" s="348" t="n"/>
+      <c r="G34" s="357" t="n"/>
+      <c r="I34" s="349" t="n"/>
       <c r="J34" s="238" t="n"/>
-      <c r="K34" s="353" t="n"/>
-      <c r="L34" s="353" t="n"/>
-      <c r="M34" s="356" t="n">
+      <c r="K34" s="349" t="n"/>
+      <c r="L34" s="349" t="n"/>
+      <c r="M34" s="354" t="n">
         <v>45138</v>
       </c>
       <c r="N34" s="71" t="inlineStr">
@@ -8260,14 +8246,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O34" s="350" t="n"/>
+      <c r="O34" s="346" t="n"/>
       <c r="P34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="351" t="n"/>
-      <c r="R34" s="352" t="n"/>
+      <c r="Q34" s="347" t="n"/>
+      <c r="R34" s="348" t="n"/>
       <c r="S34" s="238" t="n"/>
       <c r="T34" s="238" t="inlineStr">
         <is>
@@ -8645,8 +8631,8 @@
         <f>日程表１!T1</f>
         <v/>
       </c>
-      <c r="U1" s="326" t="n"/>
-      <c r="V1" s="326" t="n"/>
+      <c r="U1" s="327" t="n"/>
+      <c r="V1" s="327" t="n"/>
       <c r="W1" s="255" t="inlineStr">
         <is>
           <t>年</t>
@@ -8660,41 +8646,41 @@
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="278" t="n"/>
-      <c r="C2" s="278" t="n"/>
-      <c r="D2" s="278" t="n"/>
-      <c r="E2" s="278" t="n"/>
-      <c r="F2" s="279" t="n"/>
+      <c r="B2" s="279" t="n"/>
+      <c r="C2" s="279" t="n"/>
+      <c r="D2" s="279" t="n"/>
+      <c r="E2" s="279" t="n"/>
+      <c r="F2" s="280" t="n"/>
       <c r="G2" s="251" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="278" t="n"/>
-      <c r="I2" s="278" t="n"/>
-      <c r="J2" s="278" t="n"/>
-      <c r="K2" s="278" t="n"/>
-      <c r="L2" s="279" t="n"/>
+      <c r="H2" s="279" t="n"/>
+      <c r="I2" s="279" t="n"/>
+      <c r="J2" s="279" t="n"/>
+      <c r="K2" s="279" t="n"/>
+      <c r="L2" s="280" t="n"/>
       <c r="M2" s="251" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="278" t="n"/>
-      <c r="O2" s="278" t="n"/>
-      <c r="P2" s="278" t="n"/>
-      <c r="Q2" s="278" t="n"/>
-      <c r="R2" s="279" t="n"/>
+      <c r="N2" s="279" t="n"/>
+      <c r="O2" s="279" t="n"/>
+      <c r="P2" s="279" t="n"/>
+      <c r="Q2" s="279" t="n"/>
+      <c r="R2" s="280" t="n"/>
       <c r="S2" s="251" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="278" t="n"/>
-      <c r="U2" s="278" t="n"/>
-      <c r="V2" s="278" t="n"/>
-      <c r="W2" s="278" t="n"/>
-      <c r="X2" s="279" t="n"/>
+      <c r="T2" s="279" t="n"/>
+      <c r="U2" s="279" t="n"/>
+      <c r="V2" s="279" t="n"/>
+      <c r="W2" s="279" t="n"/>
+      <c r="X2" s="280" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="251" t="inlineStr">
@@ -8712,8 +8698,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="278" t="n"/>
-      <c r="E3" s="279" t="n"/>
+      <c r="D3" s="279" t="n"/>
+      <c r="E3" s="280" t="n"/>
       <c r="F3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8734,8 +8720,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="278" t="n"/>
-      <c r="K3" s="279" t="n"/>
+      <c r="J3" s="279" t="n"/>
+      <c r="K3" s="280" t="n"/>
       <c r="L3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8756,8 +8742,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="278" t="n"/>
-      <c r="Q3" s="279" t="n"/>
+      <c r="P3" s="279" t="n"/>
+      <c r="Q3" s="280" t="n"/>
       <c r="R3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8778,8 +8764,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="278" t="n"/>
-      <c r="W3" s="279" t="n"/>
+      <c r="V3" s="279" t="n"/>
+      <c r="W3" s="280" t="n"/>
       <c r="X3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8787,7 +8773,7 @@
       </c>
     </row>
     <row r="4" ht="20.45" customHeight="1" s="257">
-      <c r="A4" s="363">
+      <c r="A4" s="358">
         <f>日程表１!A4</f>
         <v/>
       </c>
@@ -8795,15 +8781,15 @@
         <f>日程表１!B4</f>
         <v/>
       </c>
-      <c r="C4" s="331" t="n"/>
+      <c r="C4" s="332" t="n"/>
       <c r="D4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="332" t="n"/>
-      <c r="F4" s="364" t="n"/>
-      <c r="G4" s="363">
+      <c r="E4" s="333" t="n"/>
+      <c r="F4" s="359" t="n"/>
+      <c r="G4" s="358">
         <f>日程表１!G4</f>
         <v/>
       </c>
@@ -8811,15 +8797,15 @@
         <f>日程表１!H4</f>
         <v/>
       </c>
-      <c r="I4" s="331" t="n"/>
+      <c r="I4" s="332" t="n"/>
       <c r="J4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="332" t="n"/>
-      <c r="L4" s="364" t="n"/>
-      <c r="M4" s="363">
+      <c r="K4" s="333" t="n"/>
+      <c r="L4" s="359" t="n"/>
+      <c r="M4" s="358">
         <f>日程表１!M4</f>
         <v/>
       </c>
@@ -8827,7 +8813,7 @@
         <f>日程表１!N4</f>
         <v/>
       </c>
-      <c r="O4" s="331">
+      <c r="O4" s="332">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -8836,15 +8822,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="332">
+      <c r="Q4" s="333">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="364">
+      <c r="R4" s="359">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="363">
+      <c r="S4" s="358">
         <f>日程表１!S5</f>
         <v/>
       </c>
@@ -8852,17 +8838,17 @@
         <f>日程表１!T5</f>
         <v/>
       </c>
-      <c r="U4" s="331" t="n"/>
+      <c r="U4" s="332" t="n"/>
       <c r="V4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="365" t="n"/>
-      <c r="X4" s="366" t="n"/>
+      <c r="W4" s="360" t="n"/>
+      <c r="X4" s="361" t="n"/>
     </row>
     <row r="5" ht="20.45" customHeight="1" s="257">
-      <c r="A5" s="363">
+      <c r="A5" s="358">
         <f>日程表１!A5</f>
         <v/>
       </c>
@@ -8870,15 +8856,15 @@
         <f>日程表１!B5</f>
         <v/>
       </c>
-      <c r="C5" s="340" t="n"/>
+      <c r="C5" s="335" t="n"/>
       <c r="D5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="341" t="n"/>
-      <c r="F5" s="364" t="n"/>
-      <c r="G5" s="363">
+      <c r="E5" s="336" t="n"/>
+      <c r="F5" s="359" t="n"/>
+      <c r="G5" s="358">
         <f>日程表１!G5</f>
         <v/>
       </c>
@@ -8886,7 +8872,7 @@
         <f>日程表１!H5</f>
         <v/>
       </c>
-      <c r="I5" s="340">
+      <c r="I5" s="335">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -8895,40 +8881,40 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="341">
+      <c r="K5" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="364">
+      <c r="L5" s="359">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="367">
+      <c r="M5" s="362">
         <f>日程表１!M5</f>
         <v/>
       </c>
-      <c r="N5" s="368">
+      <c r="N5" s="363">
         <f>日程表１!N5</f>
         <v/>
       </c>
-      <c r="O5" s="344">
+      <c r="O5" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="369" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="346">
+      <c r="P5" s="364" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="342">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="370">
+      <c r="R5" s="365">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="363">
+      <c r="S5" s="358">
         <f>日程表１!S6</f>
         <v/>
       </c>
@@ -8936,17 +8922,17 @@
         <f>日程表１!T6</f>
         <v/>
       </c>
-      <c r="U5" s="340" t="n"/>
+      <c r="U5" s="335" t="n"/>
       <c r="V5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="371" t="n"/>
-      <c r="X5" s="366" t="n"/>
+      <c r="W5" s="366" t="n"/>
+      <c r="X5" s="361" t="n"/>
     </row>
     <row r="6" ht="20.45" customHeight="1" s="257">
-      <c r="A6" s="363">
+      <c r="A6" s="358">
         <f>日程表１!A6</f>
         <v/>
       </c>
@@ -8954,40 +8940,40 @@
         <f>日程表１!B6</f>
         <v/>
       </c>
-      <c r="C6" s="340" t="n"/>
+      <c r="C6" s="335" t="n"/>
       <c r="D6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="341" t="n"/>
-      <c r="F6" s="364" t="n"/>
-      <c r="G6" s="367">
+      <c r="E6" s="336" t="n"/>
+      <c r="F6" s="359" t="n"/>
+      <c r="G6" s="362">
         <f>日程表１!G6</f>
         <v/>
       </c>
-      <c r="H6" s="368">
+      <c r="H6" s="363">
         <f>日程表１!H6</f>
         <v/>
       </c>
-      <c r="I6" s="344">
+      <c r="I6" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="369" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="346">
+      <c r="J6" s="364" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="342">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="370">
+      <c r="L6" s="365">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="363">
+      <c r="M6" s="358">
         <f>日程表１!M6</f>
         <v/>
       </c>
@@ -8995,15 +8981,15 @@
         <f>日程表１!N6</f>
         <v/>
       </c>
-      <c r="O6" s="340" t="n"/>
+      <c r="O6" s="335" t="n"/>
       <c r="P6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="341" t="n"/>
-      <c r="R6" s="364" t="n"/>
-      <c r="S6" s="363">
+      <c r="Q6" s="336" t="n"/>
+      <c r="R6" s="359" t="n"/>
+      <c r="S6" s="358">
         <f>日程表１!S7</f>
         <v/>
       </c>
@@ -9011,17 +8997,17 @@
         <f>日程表１!T7</f>
         <v/>
       </c>
-      <c r="U6" s="340" t="n"/>
+      <c r="U6" s="335" t="n"/>
       <c r="V6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="371" t="n"/>
-      <c r="X6" s="366" t="n"/>
+      <c r="W6" s="366" t="n"/>
+      <c r="X6" s="361" t="n"/>
     </row>
     <row r="7" ht="20.45" customHeight="1" s="257">
-      <c r="A7" s="363">
+      <c r="A7" s="358">
         <f>日程表１!A7</f>
         <v/>
       </c>
@@ -9029,15 +9015,15 @@
         <f>日程表１!B7</f>
         <v/>
       </c>
-      <c r="C7" s="340" t="n"/>
+      <c r="C7" s="335" t="n"/>
       <c r="D7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="341" t="n"/>
-      <c r="F7" s="364" t="n"/>
-      <c r="G7" s="363">
+      <c r="E7" s="336" t="n"/>
+      <c r="F7" s="359" t="n"/>
+      <c r="G7" s="358">
         <f>日程表１!G7</f>
         <v/>
       </c>
@@ -9045,7 +9031,7 @@
         <f>日程表１!H7</f>
         <v/>
       </c>
-      <c r="I7" s="340">
+      <c r="I7" s="335">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9054,15 +9040,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="341">
+      <c r="K7" s="336">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="364">
+      <c r="L7" s="359">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="363">
+      <c r="M7" s="358">
         <f>日程表１!M7</f>
         <v/>
       </c>
@@ -9070,15 +9056,15 @@
         <f>日程表１!N7</f>
         <v/>
       </c>
-      <c r="O7" s="340" t="n"/>
+      <c r="O7" s="335" t="n"/>
       <c r="P7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="341" t="n"/>
-      <c r="R7" s="364" t="n"/>
-      <c r="S7" s="363">
+      <c r="Q7" s="336" t="n"/>
+      <c r="R7" s="359" t="n"/>
+      <c r="S7" s="358">
         <f>日程表１!S8</f>
         <v/>
       </c>
@@ -9086,17 +9072,17 @@
         <f>日程表１!T8</f>
         <v/>
       </c>
-      <c r="U7" s="340" t="n"/>
+      <c r="U7" s="335" t="n"/>
       <c r="V7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="371" t="n"/>
-      <c r="X7" s="366" t="n"/>
+      <c r="W7" s="366" t="n"/>
+      <c r="X7" s="361" t="n"/>
     </row>
     <row r="8" ht="20.45" customHeight="1" s="257">
-      <c r="A8" s="363">
+      <c r="A8" s="358">
         <f>日程表１!A8</f>
         <v/>
       </c>
@@ -9104,15 +9090,15 @@
         <f>日程表１!B8</f>
         <v/>
       </c>
-      <c r="C8" s="340" t="n"/>
+      <c r="C8" s="335" t="n"/>
       <c r="D8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="341" t="n"/>
-      <c r="F8" s="364" t="n"/>
-      <c r="G8" s="363">
+      <c r="E8" s="336" t="n"/>
+      <c r="F8" s="359" t="n"/>
+      <c r="G8" s="358">
         <f>日程表１!G8</f>
         <v/>
       </c>
@@ -9120,15 +9106,15 @@
         <f>日程表１!H8</f>
         <v/>
       </c>
-      <c r="I8" s="340" t="n"/>
+      <c r="I8" s="335" t="n"/>
       <c r="J8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="341" t="n"/>
-      <c r="L8" s="364" t="n"/>
-      <c r="M8" s="363">
+      <c r="K8" s="336" t="n"/>
+      <c r="L8" s="359" t="n"/>
+      <c r="M8" s="358">
         <f>日程表１!M8</f>
         <v/>
       </c>
@@ -9136,15 +9122,15 @@
         <f>日程表１!N8</f>
         <v/>
       </c>
-      <c r="O8" s="340" t="n"/>
+      <c r="O8" s="335" t="n"/>
       <c r="P8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="341" t="n"/>
-      <c r="R8" s="364" t="n"/>
-      <c r="S8" s="363">
+      <c r="Q8" s="336" t="n"/>
+      <c r="R8" s="359" t="n"/>
+      <c r="S8" s="358">
         <f>日程表１!S9</f>
         <v/>
       </c>
@@ -9152,17 +9138,17 @@
         <f>日程表１!T9</f>
         <v/>
       </c>
-      <c r="U8" s="340" t="n"/>
+      <c r="U8" s="335" t="n"/>
       <c r="V8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="371" t="n"/>
-      <c r="X8" s="366" t="n"/>
+      <c r="W8" s="366" t="n"/>
+      <c r="X8" s="361" t="n"/>
     </row>
     <row r="9" ht="20.45" customHeight="1" s="257">
-      <c r="A9" s="363">
+      <c r="A9" s="358">
         <f>日程表１!A9</f>
         <v/>
       </c>
@@ -9170,15 +9156,15 @@
         <f>日程表１!B9</f>
         <v/>
       </c>
-      <c r="C9" s="340" t="n"/>
+      <c r="C9" s="335" t="n"/>
       <c r="D9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="341" t="n"/>
-      <c r="F9" s="364" t="n"/>
-      <c r="G9" s="363">
+      <c r="E9" s="336" t="n"/>
+      <c r="F9" s="359" t="n"/>
+      <c r="G9" s="358">
         <f>日程表１!G9</f>
         <v/>
       </c>
@@ -9186,15 +9172,15 @@
         <f>日程表１!H9</f>
         <v/>
       </c>
-      <c r="I9" s="340" t="n"/>
+      <c r="I9" s="335" t="n"/>
       <c r="J9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="341" t="n"/>
-      <c r="L9" s="364" t="n"/>
-      <c r="M9" s="363">
+      <c r="K9" s="336" t="n"/>
+      <c r="L9" s="359" t="n"/>
+      <c r="M9" s="358">
         <f>日程表１!M9</f>
         <v/>
       </c>
@@ -9202,15 +9188,15 @@
         <f>日程表１!N9</f>
         <v/>
       </c>
-      <c r="O9" s="340" t="n"/>
+      <c r="O9" s="335" t="n"/>
       <c r="P9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="341" t="n"/>
-      <c r="R9" s="364" t="n"/>
-      <c r="S9" s="363">
+      <c r="Q9" s="336" t="n"/>
+      <c r="R9" s="359" t="n"/>
+      <c r="S9" s="358">
         <f>日程表１!S10</f>
         <v/>
       </c>
@@ -9218,17 +9204,17 @@
         <f>日程表１!T10</f>
         <v/>
       </c>
-      <c r="U9" s="340" t="n"/>
+      <c r="U9" s="335" t="n"/>
       <c r="V9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="371" t="n"/>
-      <c r="X9" s="366" t="n"/>
+      <c r="W9" s="366" t="n"/>
+      <c r="X9" s="361" t="n"/>
     </row>
     <row r="10" ht="20.45" customHeight="1" s="257">
-      <c r="A10" s="363">
+      <c r="A10" s="358">
         <f>日程表１!A10</f>
         <v/>
       </c>
@@ -9236,15 +9222,15 @@
         <f>日程表１!B10</f>
         <v/>
       </c>
-      <c r="C10" s="340" t="n"/>
+      <c r="C10" s="335" t="n"/>
       <c r="D10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="341" t="n"/>
-      <c r="F10" s="364" t="n"/>
-      <c r="G10" s="363">
+      <c r="E10" s="336" t="n"/>
+      <c r="F10" s="359" t="n"/>
+      <c r="G10" s="358">
         <f>日程表１!G10</f>
         <v/>
       </c>
@@ -9252,15 +9238,15 @@
         <f>日程表１!H10</f>
         <v/>
       </c>
-      <c r="I10" s="340" t="n"/>
+      <c r="I10" s="335" t="n"/>
       <c r="J10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="341" t="n"/>
-      <c r="L10" s="364" t="n"/>
-      <c r="M10" s="363">
+      <c r="K10" s="336" t="n"/>
+      <c r="L10" s="359" t="n"/>
+      <c r="M10" s="358">
         <f>日程表１!M10</f>
         <v/>
       </c>
@@ -9268,15 +9254,15 @@
         <f>日程表１!N10</f>
         <v/>
       </c>
-      <c r="O10" s="340" t="n"/>
+      <c r="O10" s="335" t="n"/>
       <c r="P10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="341" t="n"/>
-      <c r="R10" s="364" t="n"/>
-      <c r="S10" s="363">
+      <c r="Q10" s="336" t="n"/>
+      <c r="R10" s="359" t="n"/>
+      <c r="S10" s="358">
         <f>日程表１!S11</f>
         <v/>
       </c>
@@ -9284,17 +9270,17 @@
         <f>日程表１!T11</f>
         <v/>
       </c>
-      <c r="U10" s="340" t="n"/>
+      <c r="U10" s="335" t="n"/>
       <c r="V10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="371" t="n"/>
-      <c r="X10" s="366" t="n"/>
+      <c r="W10" s="366" t="n"/>
+      <c r="X10" s="361" t="n"/>
     </row>
     <row r="11" ht="20.45" customHeight="1" s="257">
-      <c r="A11" s="363">
+      <c r="A11" s="358">
         <f>日程表１!A11</f>
         <v/>
       </c>
@@ -9302,15 +9288,15 @@
         <f>日程表１!B11</f>
         <v/>
       </c>
-      <c r="C11" s="340" t="n"/>
+      <c r="C11" s="335" t="n"/>
       <c r="D11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="341" t="n"/>
-      <c r="F11" s="364" t="n"/>
-      <c r="G11" s="363">
+      <c r="E11" s="336" t="n"/>
+      <c r="F11" s="359" t="n"/>
+      <c r="G11" s="358">
         <f>日程表１!G11</f>
         <v/>
       </c>
@@ -9318,15 +9304,15 @@
         <f>日程表１!H11</f>
         <v/>
       </c>
-      <c r="I11" s="340" t="n"/>
+      <c r="I11" s="335" t="n"/>
       <c r="J11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="341" t="n"/>
-      <c r="L11" s="364" t="n"/>
-      <c r="M11" s="363">
+      <c r="K11" s="336" t="n"/>
+      <c r="L11" s="359" t="n"/>
+      <c r="M11" s="358">
         <f>日程表１!M11</f>
         <v/>
       </c>
@@ -9334,15 +9320,15 @@
         <f>日程表１!N11</f>
         <v/>
       </c>
-      <c r="O11" s="340" t="n"/>
+      <c r="O11" s="335" t="n"/>
       <c r="P11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="341" t="n"/>
-      <c r="R11" s="364" t="n"/>
-      <c r="S11" s="363">
+      <c r="Q11" s="336" t="n"/>
+      <c r="R11" s="359" t="n"/>
+      <c r="S11" s="358">
         <f>日程表１!S12</f>
         <v/>
       </c>
@@ -9350,17 +9336,17 @@
         <f>日程表１!T12</f>
         <v/>
       </c>
-      <c r="U11" s="340" t="n"/>
+      <c r="U11" s="335" t="n"/>
       <c r="V11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="371" t="n"/>
-      <c r="X11" s="366" t="n"/>
+      <c r="W11" s="366" t="n"/>
+      <c r="X11" s="361" t="n"/>
     </row>
     <row r="12" ht="20.45" customHeight="1" s="257">
-      <c r="A12" s="363">
+      <c r="A12" s="358">
         <f>日程表１!A12</f>
         <v/>
       </c>
@@ -9368,40 +9354,40 @@
         <f>日程表１!B12</f>
         <v/>
       </c>
-      <c r="C12" s="340" t="n"/>
+      <c r="C12" s="335" t="n"/>
       <c r="D12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="341" t="n"/>
-      <c r="F12" s="364" t="n"/>
-      <c r="G12" s="367">
+      <c r="E12" s="336" t="n"/>
+      <c r="F12" s="359" t="n"/>
+      <c r="G12" s="362">
         <f>日程表１!G12</f>
         <v/>
       </c>
-      <c r="H12" s="368">
+      <c r="H12" s="363">
         <f>日程表１!H12</f>
         <v/>
       </c>
-      <c r="I12" s="344">
+      <c r="I12" s="340">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="369" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="346">
+      <c r="J12" s="364" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="342">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="370">
+      <c r="L12" s="365">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="363">
+      <c r="M12" s="358">
         <f>日程表１!M12</f>
         <v/>
       </c>
@@ -9409,15 +9395,15 @@
         <f>日程表１!N12</f>
         <v/>
       </c>
-      <c r="O12" s="340" t="n"/>
+      <c r="O12" s="335" t="n"/>
       <c r="P12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="341" t="n"/>
-      <c r="R12" s="364" t="n"/>
-      <c r="S12" s="363">
+      <c r="Q12" s="336" t="n"/>
+      <c r="R12" s="359" t="n"/>
+      <c r="S12" s="358">
         <f>日程表１!S13</f>
         <v/>
       </c>
@@ -9425,17 +9411,17 @@
         <f>日程表１!T13</f>
         <v/>
       </c>
-      <c r="U12" s="340" t="n"/>
+      <c r="U12" s="335" t="n"/>
       <c r="V12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="371" t="n"/>
-      <c r="X12" s="366" t="n"/>
+      <c r="W12" s="366" t="n"/>
+      <c r="X12" s="361" t="n"/>
     </row>
     <row r="13" ht="20.45" customHeight="1" s="257">
-      <c r="A13" s="363">
+      <c r="A13" s="358">
         <f>日程表１!A13</f>
         <v/>
       </c>
@@ -9443,15 +9429,15 @@
         <f>日程表１!B13</f>
         <v/>
       </c>
-      <c r="C13" s="340" t="n"/>
+      <c r="C13" s="335" t="n"/>
       <c r="D13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="341" t="n"/>
-      <c r="F13" s="364" t="n"/>
-      <c r="G13" s="363">
+      <c r="E13" s="336" t="n"/>
+      <c r="F13" s="359" t="n"/>
+      <c r="G13" s="358">
         <f>日程表１!G13</f>
         <v/>
       </c>
@@ -9459,7 +9445,7 @@
         <f>日程表１!H13</f>
         <v/>
       </c>
-      <c r="I13" s="340">
+      <c r="I13" s="335">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -9468,15 +9454,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="341">
+      <c r="K13" s="336">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="364">
+      <c r="L13" s="359">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="363">
+      <c r="M13" s="358">
         <f>日程表１!M13</f>
         <v/>
       </c>
@@ -9484,15 +9470,15 @@
         <f>日程表１!N13</f>
         <v/>
       </c>
-      <c r="O13" s="340" t="n"/>
+      <c r="O13" s="335" t="n"/>
       <c r="P13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="341" t="n"/>
-      <c r="R13" s="364" t="n"/>
-      <c r="S13" s="363" t="n">
+      <c r="Q13" s="336" t="n"/>
+      <c r="R13" s="359" t="n"/>
+      <c r="S13" s="358" t="n">
         <v>10</v>
       </c>
       <c r="T13" s="29" t="inlineStr">
@@ -9500,17 +9486,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U13" s="340" t="n"/>
+      <c r="U13" s="335" t="n"/>
       <c r="V13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="371" t="n"/>
-      <c r="X13" s="366" t="n"/>
+      <c r="W13" s="366" t="n"/>
+      <c r="X13" s="361" t="n"/>
     </row>
     <row r="14" ht="20.45" customHeight="1" s="257">
-      <c r="A14" s="363">
+      <c r="A14" s="358">
         <f>日程表１!A14</f>
         <v/>
       </c>
@@ -9518,15 +9504,15 @@
         <f>日程表１!B14</f>
         <v/>
       </c>
-      <c r="C14" s="340" t="n"/>
+      <c r="C14" s="335" t="n"/>
       <c r="D14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="341" t="n"/>
-      <c r="F14" s="364" t="n"/>
-      <c r="G14" s="363">
+      <c r="E14" s="336" t="n"/>
+      <c r="F14" s="359" t="n"/>
+      <c r="G14" s="358">
         <f>日程表１!G14</f>
         <v/>
       </c>
@@ -9534,7 +9520,7 @@
         <f>日程表１!H14</f>
         <v/>
       </c>
-      <c r="I14" s="340">
+      <c r="I14" s="335">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9543,15 +9529,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="341">
+      <c r="K14" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="364">
+      <c r="L14" s="359">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="363">
+      <c r="M14" s="358">
         <f>日程表１!M14</f>
         <v/>
       </c>
@@ -9559,23 +9545,23 @@
         <f>日程表１!N14</f>
         <v/>
       </c>
-      <c r="O14" s="340" t="n"/>
+      <c r="O14" s="335" t="n"/>
       <c r="P14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="341" t="n"/>
-      <c r="R14" s="364" t="n"/>
+      <c r="Q14" s="336" t="n"/>
+      <c r="R14" s="359" t="n"/>
       <c r="S14" s="256" t="n"/>
       <c r="T14" s="256" t="n"/>
-      <c r="U14" s="353" t="n"/>
+      <c r="U14" s="349" t="n"/>
       <c r="V14" s="255" t="n"/>
-      <c r="W14" s="354" t="n"/>
-      <c r="X14" s="354" t="n"/>
+      <c r="W14" s="350" t="n"/>
+      <c r="X14" s="350" t="n"/>
     </row>
     <row r="15" ht="20.45" customHeight="1" s="257">
-      <c r="A15" s="363">
+      <c r="A15" s="358">
         <f>日程表１!A15</f>
         <v/>
       </c>
@@ -9583,15 +9569,15 @@
         <f>日程表１!B15</f>
         <v/>
       </c>
-      <c r="C15" s="340" t="n"/>
+      <c r="C15" s="335" t="n"/>
       <c r="D15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="341" t="n"/>
-      <c r="F15" s="364" t="n"/>
-      <c r="G15" s="363">
+      <c r="E15" s="336" t="n"/>
+      <c r="F15" s="359" t="n"/>
+      <c r="G15" s="358">
         <f>日程表１!G15</f>
         <v/>
       </c>
@@ -9599,15 +9585,15 @@
         <f>日程表１!H15</f>
         <v/>
       </c>
-      <c r="I15" s="340" t="n"/>
+      <c r="I15" s="335" t="n"/>
       <c r="J15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="341" t="n"/>
-      <c r="L15" s="364" t="n"/>
-      <c r="M15" s="363">
+      <c r="K15" s="336" t="n"/>
+      <c r="L15" s="359" t="n"/>
+      <c r="M15" s="358">
         <f>日程表１!M15</f>
         <v/>
       </c>
@@ -9615,23 +9601,23 @@
         <f>日程表１!N15</f>
         <v/>
       </c>
-      <c r="O15" s="340" t="n"/>
+      <c r="O15" s="335" t="n"/>
       <c r="P15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="341" t="n"/>
-      <c r="R15" s="364" t="n"/>
+      <c r="Q15" s="336" t="n"/>
+      <c r="R15" s="359" t="n"/>
       <c r="S15" s="256" t="n"/>
       <c r="T15" s="256" t="n"/>
-      <c r="U15" s="353" t="n"/>
+      <c r="U15" s="349" t="n"/>
       <c r="V15" s="255" t="n"/>
-      <c r="W15" s="354" t="n"/>
-      <c r="X15" s="354" t="n"/>
+      <c r="W15" s="350" t="n"/>
+      <c r="X15" s="350" t="n"/>
     </row>
     <row r="16" ht="20.45" customHeight="1" s="257">
-      <c r="A16" s="363">
+      <c r="A16" s="358">
         <f>日程表１!A16</f>
         <v/>
       </c>
@@ -9639,15 +9625,15 @@
         <f>日程表１!B16</f>
         <v/>
       </c>
-      <c r="C16" s="340" t="n"/>
+      <c r="C16" s="335" t="n"/>
       <c r="D16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="341" t="n"/>
-      <c r="F16" s="364" t="n"/>
-      <c r="G16" s="363">
+      <c r="E16" s="336" t="n"/>
+      <c r="F16" s="359" t="n"/>
+      <c r="G16" s="358">
         <f>日程表１!G16</f>
         <v/>
       </c>
@@ -9655,15 +9641,15 @@
         <f>日程表１!H16</f>
         <v/>
       </c>
-      <c r="I16" s="340" t="n"/>
+      <c r="I16" s="335" t="n"/>
       <c r="J16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="341" t="n"/>
-      <c r="L16" s="364" t="n"/>
-      <c r="M16" s="363">
+      <c r="K16" s="336" t="n"/>
+      <c r="L16" s="359" t="n"/>
+      <c r="M16" s="358">
         <f>日程表１!M16</f>
         <v/>
       </c>
@@ -9671,23 +9657,23 @@
         <f>日程表１!N16</f>
         <v/>
       </c>
-      <c r="O16" s="340" t="n"/>
+      <c r="O16" s="335" t="n"/>
       <c r="P16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="341" t="n"/>
-      <c r="R16" s="364" t="n"/>
+      <c r="Q16" s="336" t="n"/>
+      <c r="R16" s="359" t="n"/>
       <c r="S16" s="256" t="n"/>
       <c r="T16" s="256" t="n"/>
-      <c r="U16" s="353" t="n"/>
+      <c r="U16" s="349" t="n"/>
       <c r="V16" s="255" t="n"/>
-      <c r="W16" s="354" t="n"/>
-      <c r="X16" s="354" t="n"/>
+      <c r="W16" s="350" t="n"/>
+      <c r="X16" s="350" t="n"/>
     </row>
     <row r="17" ht="20.45" customHeight="1" s="257">
-      <c r="A17" s="363">
+      <c r="A17" s="358">
         <f>日程表１!A17</f>
         <v/>
       </c>
@@ -9695,15 +9681,15 @@
         <f>日程表１!B17</f>
         <v/>
       </c>
-      <c r="C17" s="340" t="n"/>
+      <c r="C17" s="335" t="n"/>
       <c r="D17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="341" t="n"/>
-      <c r="F17" s="364" t="n"/>
-      <c r="G17" s="363">
+      <c r="E17" s="336" t="n"/>
+      <c r="F17" s="359" t="n"/>
+      <c r="G17" s="358">
         <f>日程表１!G17</f>
         <v/>
       </c>
@@ -9711,15 +9697,15 @@
         <f>日程表１!H17</f>
         <v/>
       </c>
-      <c r="I17" s="340" t="n"/>
+      <c r="I17" s="335" t="n"/>
       <c r="J17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="341" t="n"/>
-      <c r="L17" s="364" t="n"/>
-      <c r="M17" s="363">
+      <c r="K17" s="336" t="n"/>
+      <c r="L17" s="359" t="n"/>
+      <c r="M17" s="358">
         <f>日程表１!M17</f>
         <v/>
       </c>
@@ -9727,14 +9713,14 @@
         <f>日程表１!N17</f>
         <v/>
       </c>
-      <c r="O17" s="340" t="n"/>
+      <c r="O17" s="335" t="n"/>
       <c r="P17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="341" t="n"/>
-      <c r="R17" s="364" t="n"/>
+      <c r="Q17" s="336" t="n"/>
+      <c r="R17" s="359" t="n"/>
       <c r="S17" s="254" t="inlineStr">
         <is>
           <t>NO.</t>
@@ -9745,13 +9731,13 @@
           <t>team</t>
         </is>
       </c>
-      <c r="U17" s="278" t="n"/>
-      <c r="V17" s="278" t="n"/>
-      <c r="W17" s="278" t="n"/>
-      <c r="X17" s="279" t="n"/>
+      <c r="U17" s="279" t="n"/>
+      <c r="V17" s="279" t="n"/>
+      <c r="W17" s="279" t="n"/>
+      <c r="X17" s="280" t="n"/>
     </row>
     <row r="18" ht="20.45" customHeight="1" s="257">
-      <c r="A18" s="363">
+      <c r="A18" s="358">
         <f>日程表１!A18</f>
         <v/>
       </c>
@@ -9759,15 +9745,15 @@
         <f>日程表１!B18</f>
         <v/>
       </c>
-      <c r="C18" s="340" t="n"/>
+      <c r="C18" s="335" t="n"/>
       <c r="D18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="341" t="n"/>
-      <c r="F18" s="364" t="n"/>
-      <c r="G18" s="363">
+      <c r="E18" s="336" t="n"/>
+      <c r="F18" s="359" t="n"/>
+      <c r="G18" s="358">
         <f>日程表１!G18</f>
         <v/>
       </c>
@@ -9775,15 +9761,15 @@
         <f>日程表１!H18</f>
         <v/>
       </c>
-      <c r="I18" s="340" t="n"/>
+      <c r="I18" s="335" t="n"/>
       <c r="J18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="341" t="n"/>
-      <c r="L18" s="364" t="n"/>
-      <c r="M18" s="363">
+      <c r="K18" s="336" t="n"/>
+      <c r="L18" s="359" t="n"/>
+      <c r="M18" s="358">
         <f>日程表１!M18</f>
         <v/>
       </c>
@@ -9791,14 +9777,14 @@
         <f>日程表１!N18</f>
         <v/>
       </c>
-      <c r="O18" s="340" t="n"/>
+      <c r="O18" s="335" t="n"/>
       <c r="P18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="341" t="n"/>
-      <c r="R18" s="364" t="n"/>
+      <c r="Q18" s="336" t="n"/>
+      <c r="R18" s="359" t="n"/>
       <c r="S18" s="254" t="n">
         <v>1</v>
       </c>
@@ -9806,13 +9792,13 @@
         <f>リーグ勝敗表!AX6</f>
         <v/>
       </c>
-      <c r="U18" s="278" t="n"/>
-      <c r="V18" s="278" t="n"/>
-      <c r="W18" s="278" t="n"/>
-      <c r="X18" s="279" t="n"/>
+      <c r="U18" s="279" t="n"/>
+      <c r="V18" s="279" t="n"/>
+      <c r="W18" s="279" t="n"/>
+      <c r="X18" s="280" t="n"/>
     </row>
     <row r="19" ht="20.45" customHeight="1" s="257">
-      <c r="A19" s="363">
+      <c r="A19" s="358">
         <f>日程表１!A19</f>
         <v/>
       </c>
@@ -9820,15 +9806,15 @@
         <f>日程表１!B19</f>
         <v/>
       </c>
-      <c r="C19" s="340" t="n"/>
+      <c r="C19" s="335" t="n"/>
       <c r="D19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="341" t="n"/>
-      <c r="F19" s="364" t="n"/>
-      <c r="G19" s="363">
+      <c r="E19" s="336" t="n"/>
+      <c r="F19" s="359" t="n"/>
+      <c r="G19" s="358">
         <f>日程表１!G19</f>
         <v/>
       </c>
@@ -9836,15 +9822,15 @@
         <f>日程表１!H19</f>
         <v/>
       </c>
-      <c r="I19" s="340" t="inlineStr">
+      <c r="I19" s="335" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="253" t="n"/>
-      <c r="K19" s="341" t="n"/>
-      <c r="L19" s="364" t="n"/>
-      <c r="M19" s="363">
+      <c r="K19" s="336" t="n"/>
+      <c r="L19" s="359" t="n"/>
+      <c r="M19" s="358">
         <f>日程表１!M19</f>
         <v/>
       </c>
@@ -9852,14 +9838,14 @@
         <f>日程表１!N19</f>
         <v/>
       </c>
-      <c r="O19" s="340" t="n"/>
+      <c r="O19" s="335" t="n"/>
       <c r="P19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="341" t="n"/>
-      <c r="R19" s="364" t="n"/>
+      <c r="Q19" s="336" t="n"/>
+      <c r="R19" s="359" t="n"/>
       <c r="S19" s="254" t="n">
         <v>2</v>
       </c>
@@ -9867,13 +9853,13 @@
         <f>リーグ勝敗表!AX8</f>
         <v/>
       </c>
-      <c r="U19" s="278" t="n"/>
-      <c r="V19" s="278" t="n"/>
-      <c r="W19" s="278" t="n"/>
-      <c r="X19" s="279" t="n"/>
+      <c r="U19" s="279" t="n"/>
+      <c r="V19" s="279" t="n"/>
+      <c r="W19" s="279" t="n"/>
+      <c r="X19" s="280" t="n"/>
     </row>
     <row r="20" ht="20.45" customHeight="1" s="257">
-      <c r="A20" s="372">
+      <c r="A20" s="358">
         <f>日程表１!A20</f>
         <v/>
       </c>
@@ -9881,15 +9867,15 @@
         <f>日程表１!B20</f>
         <v/>
       </c>
-      <c r="C20" s="340" t="n"/>
+      <c r="C20" s="335" t="n"/>
       <c r="D20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="341" t="n"/>
-      <c r="F20" s="364" t="n"/>
-      <c r="G20" s="372">
+      <c r="E20" s="336" t="n"/>
+      <c r="F20" s="359" t="n"/>
+      <c r="G20" s="358">
         <f>日程表１!G20</f>
         <v/>
       </c>
@@ -9897,15 +9883,15 @@
         <f>日程表１!H20</f>
         <v/>
       </c>
-      <c r="I20" s="340" t="inlineStr">
+      <c r="I20" s="335" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="253" t="n"/>
-      <c r="K20" s="341" t="n"/>
-      <c r="L20" s="364" t="n"/>
-      <c r="M20" s="372">
+      <c r="K20" s="336" t="n"/>
+      <c r="L20" s="359" t="n"/>
+      <c r="M20" s="358">
         <f>日程表１!M20</f>
         <v/>
       </c>
@@ -9913,14 +9899,14 @@
         <f>日程表１!N20</f>
         <v/>
       </c>
-      <c r="O20" s="340" t="n"/>
+      <c r="O20" s="335" t="n"/>
       <c r="P20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="341" t="n"/>
-      <c r="R20" s="364" t="n"/>
+      <c r="Q20" s="336" t="n"/>
+      <c r="R20" s="359" t="n"/>
       <c r="S20" s="254" t="n">
         <v>3</v>
       </c>
@@ -9928,13 +9914,13 @@
         <f>リーグ勝敗表!AX10</f>
         <v/>
       </c>
-      <c r="U20" s="278" t="n"/>
-      <c r="V20" s="278" t="n"/>
-      <c r="W20" s="278" t="n"/>
-      <c r="X20" s="279" t="n"/>
+      <c r="U20" s="279" t="n"/>
+      <c r="V20" s="279" t="n"/>
+      <c r="W20" s="279" t="n"/>
+      <c r="X20" s="280" t="n"/>
     </row>
     <row r="21" ht="20.45" customHeight="1" s="257">
-      <c r="A21" s="363">
+      <c r="A21" s="358">
         <f>日程表１!A21</f>
         <v/>
       </c>
@@ -9942,15 +9928,15 @@
         <f>日程表１!B21</f>
         <v/>
       </c>
-      <c r="C21" s="340" t="n"/>
+      <c r="C21" s="335" t="n"/>
       <c r="D21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="341" t="n"/>
-      <c r="F21" s="364" t="n"/>
-      <c r="G21" s="363">
+      <c r="E21" s="336" t="n"/>
+      <c r="F21" s="359" t="n"/>
+      <c r="G21" s="358">
         <f>日程表１!G21</f>
         <v/>
       </c>
@@ -9958,15 +9944,15 @@
         <f>日程表１!H21</f>
         <v/>
       </c>
-      <c r="I21" s="340" t="inlineStr">
+      <c r="I21" s="335" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="253" t="n"/>
-      <c r="K21" s="341" t="n"/>
-      <c r="L21" s="364" t="n"/>
-      <c r="M21" s="363">
+      <c r="K21" s="336" t="n"/>
+      <c r="L21" s="359" t="n"/>
+      <c r="M21" s="358">
         <f>日程表１!M21</f>
         <v/>
       </c>
@@ -9974,14 +9960,14 @@
         <f>日程表１!N21</f>
         <v/>
       </c>
-      <c r="O21" s="340" t="n"/>
+      <c r="O21" s="335" t="n"/>
       <c r="P21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="341" t="n"/>
-      <c r="R21" s="364" t="n"/>
+      <c r="Q21" s="336" t="n"/>
+      <c r="R21" s="359" t="n"/>
       <c r="S21" s="254" t="n">
         <v>4</v>
       </c>
@@ -9989,13 +9975,13 @@
         <f>リーグ勝敗表!AX12</f>
         <v/>
       </c>
-      <c r="U21" s="278" t="n"/>
-      <c r="V21" s="278" t="n"/>
-      <c r="W21" s="278" t="n"/>
-      <c r="X21" s="279" t="n"/>
+      <c r="U21" s="279" t="n"/>
+      <c r="V21" s="279" t="n"/>
+      <c r="W21" s="279" t="n"/>
+      <c r="X21" s="280" t="n"/>
     </row>
     <row r="22" ht="20.45" customHeight="1" s="257">
-      <c r="A22" s="363">
+      <c r="A22" s="358">
         <f>日程表１!A22</f>
         <v/>
       </c>
@@ -10003,15 +9989,15 @@
         <f>日程表１!B22</f>
         <v/>
       </c>
-      <c r="C22" s="340" t="n"/>
+      <c r="C22" s="335" t="n"/>
       <c r="D22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="341" t="n"/>
-      <c r="F22" s="364" t="n"/>
-      <c r="G22" s="363">
+      <c r="E22" s="336" t="n"/>
+      <c r="F22" s="359" t="n"/>
+      <c r="G22" s="358">
         <f>日程表１!G22</f>
         <v/>
       </c>
@@ -10019,15 +10005,15 @@
         <f>日程表１!H22</f>
         <v/>
       </c>
-      <c r="I22" s="340" t="n"/>
+      <c r="I22" s="335" t="n"/>
       <c r="J22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K22" s="341" t="n"/>
-      <c r="L22" s="364" t="n"/>
-      <c r="M22" s="363">
+      <c r="K22" s="336" t="n"/>
+      <c r="L22" s="359" t="n"/>
+      <c r="M22" s="358">
         <f>日程表１!M22</f>
         <v/>
       </c>
@@ -10035,14 +10021,14 @@
         <f>日程表１!N22</f>
         <v/>
       </c>
-      <c r="O22" s="340" t="n"/>
+      <c r="O22" s="335" t="n"/>
       <c r="P22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="341" t="n"/>
-      <c r="R22" s="364" t="n"/>
+      <c r="Q22" s="336" t="n"/>
+      <c r="R22" s="359" t="n"/>
       <c r="S22" s="254" t="n">
         <v>5</v>
       </c>
@@ -10050,13 +10036,13 @@
         <f>リーグ勝敗表!AX14</f>
         <v/>
       </c>
-      <c r="U22" s="278" t="n"/>
-      <c r="V22" s="278" t="n"/>
-      <c r="W22" s="278" t="n"/>
-      <c r="X22" s="279" t="n"/>
+      <c r="U22" s="279" t="n"/>
+      <c r="V22" s="279" t="n"/>
+      <c r="W22" s="279" t="n"/>
+      <c r="X22" s="280" t="n"/>
     </row>
     <row r="23" ht="20.45" customHeight="1" s="257">
-      <c r="A23" s="363">
+      <c r="A23" s="358">
         <f>日程表１!A23</f>
         <v/>
       </c>
@@ -10064,15 +10050,15 @@
         <f>日程表１!B23</f>
         <v/>
       </c>
-      <c r="C23" s="340" t="n"/>
+      <c r="C23" s="335" t="n"/>
       <c r="D23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="341" t="n"/>
-      <c r="F23" s="364" t="n"/>
-      <c r="G23" s="363">
+      <c r="E23" s="336" t="n"/>
+      <c r="F23" s="359" t="n"/>
+      <c r="G23" s="358">
         <f>日程表１!G23</f>
         <v/>
       </c>
@@ -10080,15 +10066,15 @@
         <f>日程表１!H23</f>
         <v/>
       </c>
-      <c r="I23" s="340" t="n"/>
+      <c r="I23" s="335" t="n"/>
       <c r="J23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K23" s="341" t="n"/>
-      <c r="L23" s="364" t="n"/>
-      <c r="M23" s="363">
+      <c r="K23" s="336" t="n"/>
+      <c r="L23" s="359" t="n"/>
+      <c r="M23" s="358">
         <f>日程表１!M23</f>
         <v/>
       </c>
@@ -10096,14 +10082,14 @@
         <f>日程表１!N23</f>
         <v/>
       </c>
-      <c r="O23" s="340" t="n"/>
+      <c r="O23" s="335" t="n"/>
       <c r="P23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="341" t="n"/>
-      <c r="R23" s="364" t="n"/>
+      <c r="Q23" s="336" t="n"/>
+      <c r="R23" s="359" t="n"/>
       <c r="S23" s="254" t="n">
         <v>6</v>
       </c>
@@ -10111,13 +10097,13 @@
         <f>リーグ勝敗表!AX16</f>
         <v/>
       </c>
-      <c r="U23" s="278" t="n"/>
-      <c r="V23" s="278" t="n"/>
-      <c r="W23" s="278" t="n"/>
-      <c r="X23" s="279" t="n"/>
+      <c r="U23" s="279" t="n"/>
+      <c r="V23" s="279" t="n"/>
+      <c r="W23" s="279" t="n"/>
+      <c r="X23" s="280" t="n"/>
     </row>
     <row r="24" ht="20.45" customHeight="1" s="257">
-      <c r="A24" s="363">
+      <c r="A24" s="358">
         <f>日程表１!A24</f>
         <v/>
       </c>
@@ -10125,15 +10111,15 @@
         <f>日程表１!B24</f>
         <v/>
       </c>
-      <c r="C24" s="340" t="n"/>
+      <c r="C24" s="335" t="n"/>
       <c r="D24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="341" t="n"/>
-      <c r="F24" s="364" t="n"/>
-      <c r="G24" s="363">
+      <c r="E24" s="336" t="n"/>
+      <c r="F24" s="359" t="n"/>
+      <c r="G24" s="358">
         <f>日程表１!G24</f>
         <v/>
       </c>
@@ -10141,15 +10127,15 @@
         <f>日程表１!H24</f>
         <v/>
       </c>
-      <c r="I24" s="340" t="n"/>
+      <c r="I24" s="335" t="n"/>
       <c r="J24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K24" s="341" t="n"/>
-      <c r="L24" s="364" t="n"/>
-      <c r="M24" s="363">
+      <c r="K24" s="336" t="n"/>
+      <c r="L24" s="359" t="n"/>
+      <c r="M24" s="358">
         <f>日程表１!M24</f>
         <v/>
       </c>
@@ -10157,14 +10143,14 @@
         <f>日程表１!N24</f>
         <v/>
       </c>
-      <c r="O24" s="340" t="n"/>
+      <c r="O24" s="335" t="n"/>
       <c r="P24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="341" t="n"/>
-      <c r="R24" s="364" t="n"/>
+      <c r="Q24" s="336" t="n"/>
+      <c r="R24" s="359" t="n"/>
       <c r="S24" s="254" t="n">
         <v>7</v>
       </c>
@@ -10172,13 +10158,13 @@
         <f>リーグ勝敗表!AX18</f>
         <v/>
       </c>
-      <c r="U24" s="278" t="n"/>
-      <c r="V24" s="278" t="n"/>
-      <c r="W24" s="278" t="n"/>
-      <c r="X24" s="279" t="n"/>
+      <c r="U24" s="279" t="n"/>
+      <c r="V24" s="279" t="n"/>
+      <c r="W24" s="279" t="n"/>
+      <c r="X24" s="280" t="n"/>
     </row>
     <row r="25" ht="20.45" customHeight="1" s="257">
-      <c r="A25" s="363">
+      <c r="A25" s="358">
         <f>日程表１!A25</f>
         <v/>
       </c>
@@ -10186,15 +10172,15 @@
         <f>日程表１!B25</f>
         <v/>
       </c>
-      <c r="C25" s="340" t="n"/>
+      <c r="C25" s="335" t="n"/>
       <c r="D25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="341" t="n"/>
-      <c r="F25" s="364" t="n"/>
-      <c r="G25" s="363">
+      <c r="E25" s="336" t="n"/>
+      <c r="F25" s="359" t="n"/>
+      <c r="G25" s="358">
         <f>日程表１!G25</f>
         <v/>
       </c>
@@ -10202,15 +10188,15 @@
         <f>日程表１!H25</f>
         <v/>
       </c>
-      <c r="I25" s="340" t="n"/>
+      <c r="I25" s="335" t="n"/>
       <c r="J25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K25" s="341" t="n"/>
-      <c r="L25" s="364" t="n"/>
-      <c r="M25" s="363">
+      <c r="K25" s="336" t="n"/>
+      <c r="L25" s="359" t="n"/>
+      <c r="M25" s="358">
         <f>日程表１!M25</f>
         <v/>
       </c>
@@ -10218,14 +10204,14 @@
         <f>日程表１!N25</f>
         <v/>
       </c>
-      <c r="O25" s="340" t="n"/>
+      <c r="O25" s="335" t="n"/>
       <c r="P25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="341" t="n"/>
-      <c r="R25" s="364" t="n"/>
+      <c r="Q25" s="336" t="n"/>
+      <c r="R25" s="359" t="n"/>
       <c r="S25" s="254" t="n">
         <v>8</v>
       </c>
@@ -10233,13 +10219,13 @@
         <f>リーグ勝敗表!AX20</f>
         <v/>
       </c>
-      <c r="U25" s="278" t="n"/>
-      <c r="V25" s="278" t="n"/>
-      <c r="W25" s="278" t="n"/>
-      <c r="X25" s="279" t="n"/>
+      <c r="U25" s="279" t="n"/>
+      <c r="V25" s="279" t="n"/>
+      <c r="W25" s="279" t="n"/>
+      <c r="X25" s="280" t="n"/>
     </row>
     <row r="26" ht="20.45" customHeight="1" s="257">
-      <c r="A26" s="363">
+      <c r="A26" s="358">
         <f>日程表１!A26</f>
         <v/>
       </c>
@@ -10247,40 +10233,40 @@
         <f>日程表１!B26</f>
         <v/>
       </c>
-      <c r="C26" s="340" t="n"/>
+      <c r="C26" s="335" t="n"/>
       <c r="D26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="341" t="n"/>
-      <c r="F26" s="364" t="n"/>
-      <c r="G26" s="367">
+      <c r="E26" s="336" t="n"/>
+      <c r="F26" s="359" t="n"/>
+      <c r="G26" s="362">
         <f>日程表１!G26</f>
         <v/>
       </c>
-      <c r="H26" s="368">
+      <c r="H26" s="363">
         <f>日程表１!H26</f>
         <v/>
       </c>
-      <c r="I26" s="344">
+      <c r="I26" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="369" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K26" s="346">
+      <c r="J26" s="364" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K26" s="342">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="370">
+      <c r="L26" s="365">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="363">
+      <c r="M26" s="358">
         <f>日程表１!M26</f>
         <v/>
       </c>
@@ -10288,14 +10274,14 @@
         <f>日程表１!N26</f>
         <v/>
       </c>
-      <c r="O26" s="340" t="n"/>
+      <c r="O26" s="335" t="n"/>
       <c r="P26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="341" t="n"/>
-      <c r="R26" s="364" t="n"/>
+      <c r="Q26" s="336" t="n"/>
+      <c r="R26" s="359" t="n"/>
       <c r="S26" s="254" t="n">
         <v>9</v>
       </c>
@@ -10303,13 +10289,13 @@
         <f>リーグ勝敗表!AX22</f>
         <v/>
       </c>
-      <c r="U26" s="278" t="n"/>
-      <c r="V26" s="278" t="n"/>
-      <c r="W26" s="278" t="n"/>
-      <c r="X26" s="279" t="n"/>
+      <c r="U26" s="279" t="n"/>
+      <c r="V26" s="279" t="n"/>
+      <c r="W26" s="279" t="n"/>
+      <c r="X26" s="280" t="n"/>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="257">
-      <c r="A27" s="363">
+      <c r="A27" s="358">
         <f>日程表１!A27</f>
         <v/>
       </c>
@@ -10317,15 +10303,15 @@
         <f>日程表１!B27</f>
         <v/>
       </c>
-      <c r="C27" s="340" t="n"/>
+      <c r="C27" s="335" t="n"/>
       <c r="D27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="341" t="n"/>
-      <c r="F27" s="364" t="n"/>
-      <c r="G27" s="363">
+      <c r="E27" s="336" t="n"/>
+      <c r="F27" s="359" t="n"/>
+      <c r="G27" s="358">
         <f>日程表１!G27</f>
         <v/>
       </c>
@@ -10333,7 +10319,7 @@
         <f>日程表１!H27</f>
         <v/>
       </c>
-      <c r="I27" s="340">
+      <c r="I27" s="335">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10342,15 +10328,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K27" s="341">
+      <c r="K27" s="336">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="364">
+      <c r="L27" s="359">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="363">
+      <c r="M27" s="358">
         <f>日程表１!M27</f>
         <v/>
       </c>
@@ -10358,14 +10344,14 @@
         <f>日程表１!N27</f>
         <v/>
       </c>
-      <c r="O27" s="340" t="n"/>
+      <c r="O27" s="335" t="n"/>
       <c r="P27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="341" t="n"/>
-      <c r="R27" s="364" t="n"/>
+      <c r="Q27" s="336" t="n"/>
+      <c r="R27" s="359" t="n"/>
       <c r="S27" s="254" t="n">
         <v>10</v>
       </c>
@@ -10373,13 +10359,13 @@
         <f>リーグ勝敗表!AX24</f>
         <v/>
       </c>
-      <c r="U27" s="278" t="n"/>
-      <c r="V27" s="278" t="n"/>
-      <c r="W27" s="278" t="n"/>
-      <c r="X27" s="279" t="n"/>
+      <c r="U27" s="279" t="n"/>
+      <c r="V27" s="279" t="n"/>
+      <c r="W27" s="279" t="n"/>
+      <c r="X27" s="280" t="n"/>
     </row>
     <row r="28" ht="20.45" customHeight="1" s="257">
-      <c r="A28" s="372">
+      <c r="A28" s="358">
         <f>日程表１!A28</f>
         <v/>
       </c>
@@ -10387,15 +10373,15 @@
         <f>日程表１!B28</f>
         <v/>
       </c>
-      <c r="C28" s="340" t="n"/>
+      <c r="C28" s="335" t="n"/>
       <c r="D28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="341" t="n"/>
-      <c r="F28" s="364" t="n"/>
-      <c r="G28" s="372">
+      <c r="E28" s="336" t="n"/>
+      <c r="F28" s="359" t="n"/>
+      <c r="G28" s="358">
         <f>日程表１!G28</f>
         <v/>
       </c>
@@ -10403,7 +10389,7 @@
         <f>日程表１!H28</f>
         <v/>
       </c>
-      <c r="I28" s="340">
+      <c r="I28" s="335">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -10412,15 +10398,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K28" s="341">
+      <c r="K28" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="364">
+      <c r="L28" s="359">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="372">
+      <c r="M28" s="358">
         <f>日程表１!M28</f>
         <v/>
       </c>
@@ -10428,14 +10414,14 @@
         <f>日程表１!N28</f>
         <v/>
       </c>
-      <c r="O28" s="340" t="n"/>
+      <c r="O28" s="335" t="n"/>
       <c r="P28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="341" t="n"/>
-      <c r="R28" s="364" t="n"/>
+      <c r="Q28" s="336" t="n"/>
+      <c r="R28" s="359" t="n"/>
       <c r="S28" s="254" t="n">
         <v>11</v>
       </c>
@@ -10443,13 +10429,13 @@
         <f>リーグ勝敗表!AX26</f>
         <v/>
       </c>
-      <c r="U28" s="278" t="n"/>
-      <c r="V28" s="278" t="n"/>
-      <c r="W28" s="278" t="n"/>
-      <c r="X28" s="279" t="n"/>
+      <c r="U28" s="279" t="n"/>
+      <c r="V28" s="279" t="n"/>
+      <c r="W28" s="279" t="n"/>
+      <c r="X28" s="280" t="n"/>
     </row>
     <row r="29" ht="20.45" customHeight="1" s="257">
-      <c r="A29" s="363">
+      <c r="A29" s="358">
         <f>日程表１!A29</f>
         <v/>
       </c>
@@ -10457,7 +10443,7 @@
         <f>日程表１!B29</f>
         <v/>
       </c>
-      <c r="C29" s="340">
+      <c r="C29" s="335">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10466,15 +10452,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="341">
+      <c r="E29" s="336">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="364">
+      <c r="F29" s="359">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="363">
+      <c r="G29" s="358">
         <f>日程表１!G29</f>
         <v/>
       </c>
@@ -10482,15 +10468,15 @@
         <f>日程表１!H29</f>
         <v/>
       </c>
-      <c r="I29" s="340" t="n"/>
+      <c r="I29" s="335" t="n"/>
       <c r="J29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K29" s="341" t="n"/>
-      <c r="L29" s="364" t="n"/>
-      <c r="M29" s="363">
+      <c r="K29" s="336" t="n"/>
+      <c r="L29" s="359" t="n"/>
+      <c r="M29" s="358">
         <f>日程表１!M29</f>
         <v/>
       </c>
@@ -10498,23 +10484,23 @@
         <f>日程表１!N29</f>
         <v/>
       </c>
-      <c r="O29" s="340" t="n"/>
+      <c r="O29" s="335" t="n"/>
       <c r="P29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="341" t="n"/>
-      <c r="R29" s="364" t="n"/>
+      <c r="Q29" s="336" t="n"/>
+      <c r="R29" s="359" t="n"/>
       <c r="S29" s="255" t="n"/>
       <c r="T29" s="255" t="n"/>
-      <c r="U29" s="354" t="n"/>
+      <c r="U29" s="350" t="n"/>
       <c r="V29" s="255" t="n"/>
-      <c r="W29" s="354" t="n"/>
-      <c r="X29" s="354" t="n"/>
+      <c r="W29" s="350" t="n"/>
+      <c r="X29" s="350" t="n"/>
     </row>
     <row r="30" ht="20.45" customHeight="1" s="257">
-      <c r="A30" s="363">
+      <c r="A30" s="358">
         <f>日程表１!A30</f>
         <v/>
       </c>
@@ -10522,7 +10508,7 @@
         <f>日程表１!B30</f>
         <v/>
       </c>
-      <c r="C30" s="340">
+      <c r="C30" s="335">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -10531,15 +10517,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="341">
+      <c r="E30" s="336">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="364">
+      <c r="F30" s="359">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="363">
+      <c r="G30" s="358">
         <f>日程表１!G30</f>
         <v/>
       </c>
@@ -10547,15 +10533,15 @@
         <f>日程表１!H30</f>
         <v/>
       </c>
-      <c r="I30" s="340" t="n"/>
+      <c r="I30" s="335" t="n"/>
       <c r="J30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K30" s="341" t="n"/>
-      <c r="L30" s="364" t="n"/>
-      <c r="M30" s="363">
+      <c r="K30" s="336" t="n"/>
+      <c r="L30" s="359" t="n"/>
+      <c r="M30" s="358">
         <f>日程表１!M30</f>
         <v/>
       </c>
@@ -10563,48 +10549,48 @@
         <f>日程表１!N30</f>
         <v/>
       </c>
-      <c r="O30" s="340" t="n"/>
+      <c r="O30" s="335" t="n"/>
       <c r="P30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="341" t="n"/>
-      <c r="R30" s="364" t="n"/>
+      <c r="Q30" s="336" t="n"/>
+      <c r="R30" s="359" t="n"/>
       <c r="S30" s="255" t="n"/>
       <c r="T30" s="255" t="n"/>
-      <c r="U30" s="354" t="n"/>
+      <c r="U30" s="350" t="n"/>
       <c r="V30" s="255" t="n"/>
-      <c r="W30" s="354" t="n"/>
-      <c r="X30" s="354" t="n"/>
+      <c r="W30" s="350" t="n"/>
+      <c r="X30" s="350" t="n"/>
     </row>
     <row r="31" ht="20.45" customHeight="1" s="257">
-      <c r="A31" s="367">
+      <c r="A31" s="362">
         <f>日程表１!A31</f>
         <v/>
       </c>
-      <c r="B31" s="368">
+      <c r="B31" s="363">
         <f>日程表１!B31</f>
         <v/>
       </c>
-      <c r="C31" s="344">
+      <c r="C31" s="340">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="369" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="346">
+      <c r="D31" s="364" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="342">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="370">
+      <c r="F31" s="365">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="363">
+      <c r="G31" s="358">
         <f>日程表１!G31</f>
         <v/>
       </c>
@@ -10612,15 +10598,15 @@
         <f>日程表１!H31</f>
         <v/>
       </c>
-      <c r="I31" s="340" t="n"/>
+      <c r="I31" s="335" t="n"/>
       <c r="J31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K31" s="341" t="n"/>
-      <c r="L31" s="364" t="n"/>
-      <c r="M31" s="363">
+      <c r="K31" s="336" t="n"/>
+      <c r="L31" s="359" t="n"/>
+      <c r="M31" s="358">
         <f>日程表１!M31</f>
         <v/>
       </c>
@@ -10628,23 +10614,23 @@
         <f>日程表１!N31</f>
         <v/>
       </c>
-      <c r="O31" s="340" t="n"/>
+      <c r="O31" s="335" t="n"/>
       <c r="P31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="341" t="n"/>
-      <c r="R31" s="364" t="n"/>
+      <c r="Q31" s="336" t="n"/>
+      <c r="R31" s="359" t="n"/>
       <c r="S31" s="255" t="n"/>
       <c r="T31" s="255" t="n"/>
-      <c r="U31" s="354" t="n"/>
+      <c r="U31" s="350" t="n"/>
       <c r="V31" s="255" t="n"/>
-      <c r="W31" s="354" t="n"/>
-      <c r="X31" s="354" t="n"/>
+      <c r="W31" s="350" t="n"/>
+      <c r="X31" s="350" t="n"/>
     </row>
     <row r="32" ht="20.45" customHeight="1" s="257">
-      <c r="A32" s="363">
+      <c r="A32" s="358">
         <f>日程表１!A32</f>
         <v/>
       </c>
@@ -10652,15 +10638,15 @@
         <f>日程表１!B32</f>
         <v/>
       </c>
-      <c r="C32" s="340" t="n"/>
+      <c r="C32" s="335" t="n"/>
       <c r="D32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="341" t="n"/>
-      <c r="F32" s="364" t="n"/>
-      <c r="G32" s="363">
+      <c r="E32" s="336" t="n"/>
+      <c r="F32" s="359" t="n"/>
+      <c r="G32" s="358">
         <f>日程表１!G32</f>
         <v/>
       </c>
@@ -10668,15 +10654,15 @@
         <f>日程表１!H32</f>
         <v/>
       </c>
-      <c r="I32" s="340" t="n"/>
+      <c r="I32" s="335" t="n"/>
       <c r="J32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K32" s="341" t="n"/>
-      <c r="L32" s="364" t="n"/>
-      <c r="M32" s="363">
+      <c r="K32" s="336" t="n"/>
+      <c r="L32" s="359" t="n"/>
+      <c r="M32" s="358">
         <f>日程表１!M32</f>
         <v/>
       </c>
@@ -10684,23 +10670,23 @@
         <f>日程表１!N32</f>
         <v/>
       </c>
-      <c r="O32" s="340" t="n"/>
+      <c r="O32" s="335" t="n"/>
       <c r="P32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="341" t="n"/>
-      <c r="R32" s="364" t="n"/>
+      <c r="Q32" s="336" t="n"/>
+      <c r="R32" s="359" t="n"/>
       <c r="S32" s="255" t="n"/>
       <c r="T32" s="255" t="n"/>
-      <c r="U32" s="354" t="n"/>
+      <c r="U32" s="350" t="n"/>
       <c r="V32" s="255" t="n"/>
-      <c r="W32" s="354" t="n"/>
-      <c r="X32" s="354" t="n"/>
+      <c r="W32" s="350" t="n"/>
+      <c r="X32" s="350" t="n"/>
     </row>
     <row r="33" ht="20.45" customHeight="1" s="257">
-      <c r="A33" s="363">
+      <c r="A33" s="358">
         <f>日程表１!A33</f>
         <v/>
       </c>
@@ -10708,15 +10694,15 @@
         <f>日程表１!B33</f>
         <v/>
       </c>
-      <c r="C33" s="340" t="n"/>
+      <c r="C33" s="335" t="n"/>
       <c r="D33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="341" t="n"/>
-      <c r="F33" s="364" t="n"/>
-      <c r="G33" s="363">
+      <c r="E33" s="336" t="n"/>
+      <c r="F33" s="359" t="n"/>
+      <c r="G33" s="358">
         <f>日程表１!G33</f>
         <v/>
       </c>
@@ -10724,7 +10710,7 @@
         <f>日程表１!H33</f>
         <v/>
       </c>
-      <c r="I33" s="340">
+      <c r="I33" s="335">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10733,15 +10719,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K33" s="341">
+      <c r="K33" s="336">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="364">
+      <c r="L33" s="359">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="363">
+      <c r="M33" s="358">
         <f>日程表１!M33</f>
         <v/>
       </c>
@@ -10749,23 +10735,23 @@
         <f>日程表１!N33</f>
         <v/>
       </c>
-      <c r="O33" s="340" t="n"/>
+      <c r="O33" s="335" t="n"/>
       <c r="P33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="341" t="n"/>
-      <c r="R33" s="364" t="n"/>
+      <c r="Q33" s="336" t="n"/>
+      <c r="R33" s="359" t="n"/>
       <c r="S33" s="255" t="n"/>
       <c r="T33" s="255" t="n"/>
-      <c r="U33" s="354" t="n"/>
+      <c r="U33" s="350" t="n"/>
       <c r="V33" s="255" t="n"/>
-      <c r="W33" s="354" t="n"/>
-      <c r="X33" s="354" t="n"/>
+      <c r="W33" s="350" t="n"/>
+      <c r="X33" s="350" t="n"/>
     </row>
     <row r="34" ht="20.45" customHeight="1" s="257">
-      <c r="A34" s="363">
+      <c r="A34" s="358">
         <f>日程表１!A34</f>
         <v/>
       </c>
@@ -10773,25 +10759,25 @@
         <f>日程表１!B34</f>
         <v/>
       </c>
-      <c r="C34" s="340" t="n"/>
+      <c r="C34" s="335" t="n"/>
       <c r="D34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="371" t="n"/>
-      <c r="F34" s="353" t="n"/>
-      <c r="G34" s="363" t="n"/>
+      <c r="E34" s="366" t="n"/>
+      <c r="F34" s="349" t="n"/>
+      <c r="G34" s="358" t="n"/>
       <c r="H34" s="256" t="n"/>
-      <c r="I34" s="340" t="n"/>
+      <c r="I34" s="335" t="n"/>
       <c r="J34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K34" s="341" t="n"/>
-      <c r="L34" s="364" t="n"/>
-      <c r="M34" s="363">
+      <c r="K34" s="336" t="n"/>
+      <c r="L34" s="359" t="n"/>
+      <c r="M34" s="358">
         <f>日程表１!M34</f>
         <v/>
       </c>
@@ -10799,20 +10785,20 @@
         <f>日程表１!N34</f>
         <v/>
       </c>
-      <c r="O34" s="340" t="n"/>
+      <c r="O34" s="335" t="n"/>
       <c r="P34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="341" t="n"/>
-      <c r="R34" s="364" t="n"/>
+      <c r="Q34" s="336" t="n"/>
+      <c r="R34" s="359" t="n"/>
       <c r="S34" s="255" t="n"/>
       <c r="T34" s="255" t="n"/>
-      <c r="U34" s="354" t="n"/>
+      <c r="U34" s="350" t="n"/>
       <c r="V34" s="255" t="n"/>
-      <c r="W34" s="354" t="n"/>
-      <c r="X34" s="354" t="n"/>
+      <c r="W34" s="350" t="n"/>
+      <c r="X34" s="350" t="n"/>
     </row>
     <row r="35" ht="3" customHeight="1" s="257"/>
   </sheetData>

--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="34">
     <font>
       <name val="メイリオ"/>
       <charset val="128"/>
@@ -242,8 +242,42 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <color rgb="001A252F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="001A252F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <color rgb="00D5D8DC"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -316,8 +350,53 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D1B2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B4F72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002471A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FBFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F3F4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="80">
+  <borders count="86">
     <border>
       <left/>
       <right/>
@@ -1306,13 +1385,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B2BABB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B2BABB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B2BABB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B2BABB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B2BABB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B2BABB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B2BABB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000D1B2A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000D1B2A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000D1B2A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B2BABB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B2BABB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000D1B2A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000D1B2A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B2BABB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B2BABB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B2BABB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000D1B2A"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="367">
+  <cellXfs count="380">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2176,16 +2333,41 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2195,22 +2377,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="17" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="17" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="17" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="31" fillId="18" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2218,13 +2403,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2234,41 +2419,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
@@ -2276,15 +2437,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="21" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2294,29 +2494,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="65" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="65" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
@@ -2327,24 +2517,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="74" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="74" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="21" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2853,199 +3051,288 @@
     <col hidden="1" width="4.6640625" customWidth="1" style="1" min="61" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" s="257">
+    <row r="1" ht="32" customHeight="1" s="257">
       <c r="A1" s="258" t="inlineStr">
         <is>
           <t>令和8年 朝野球リーグ勝敗表</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48.75" customHeight="1" s="257">
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+    <row r="2" ht="6" customHeight="1" s="257">
+      <c r="A2" s="259" t="n"/>
+      <c r="B2" s="260" t="n"/>
+      <c r="C2" s="260" t="n"/>
+      <c r="D2" s="260" t="n"/>
+      <c r="E2" s="260" t="n"/>
+      <c r="F2" s="260" t="n"/>
+      <c r="G2" s="260" t="n"/>
+      <c r="H2" s="260" t="n"/>
+      <c r="I2" s="260" t="n"/>
+      <c r="J2" s="260" t="n"/>
+      <c r="K2" s="260" t="n"/>
+      <c r="L2" s="260" t="n"/>
+      <c r="M2" s="260" t="n"/>
+      <c r="N2" s="260" t="n"/>
+      <c r="O2" s="260" t="n"/>
+      <c r="P2" s="260" t="n"/>
+      <c r="Q2" s="259" t="n"/>
+      <c r="R2" s="259" t="n"/>
+      <c r="S2" s="259" t="n"/>
+      <c r="T2" s="259" t="n"/>
+      <c r="U2" s="259" t="n"/>
+      <c r="V2" s="259" t="n"/>
+      <c r="W2" s="259" t="n"/>
+      <c r="X2" s="259" t="n"/>
+      <c r="Y2" s="259" t="n"/>
+      <c r="Z2" s="259" t="n"/>
+      <c r="AA2" s="259" t="n"/>
+      <c r="AB2" s="259" t="n"/>
+      <c r="AC2" s="259" t="n"/>
+      <c r="AD2" s="259" t="n"/>
+      <c r="AE2" s="259" t="n"/>
+      <c r="AF2" s="259" t="n"/>
+      <c r="AG2" s="259" t="n"/>
+      <c r="AH2" s="259" t="n"/>
+      <c r="AI2" s="259" t="n"/>
+      <c r="AJ2" s="259" t="n"/>
+      <c r="AK2" s="259" t="n"/>
+      <c r="AL2" s="259" t="n"/>
+      <c r="AM2" s="259" t="n"/>
+      <c r="AN2" s="259" t="n"/>
+      <c r="AO2" s="259" t="n"/>
+      <c r="AP2" s="259" t="n"/>
+      <c r="AQ2" s="259" t="n"/>
+      <c r="AR2" s="259" t="n"/>
+      <c r="AS2" s="259" t="n"/>
       <c r="AU2" s="255" t="n"/>
     </row>
-    <row r="3" ht="20.25" customHeight="1" s="257"/>
+    <row r="3" ht="6" customHeight="1" s="257">
+      <c r="A3" s="259" t="n"/>
+      <c r="B3" s="259" t="n"/>
+      <c r="C3" s="259" t="n"/>
+      <c r="D3" s="259" t="n"/>
+      <c r="E3" s="259" t="n"/>
+      <c r="F3" s="259" t="n"/>
+      <c r="G3" s="259" t="n"/>
+      <c r="H3" s="259" t="n"/>
+      <c r="I3" s="259" t="n"/>
+      <c r="J3" s="259" t="n"/>
+      <c r="K3" s="259" t="n"/>
+      <c r="L3" s="259" t="n"/>
+      <c r="M3" s="259" t="n"/>
+      <c r="N3" s="259" t="n"/>
+      <c r="O3" s="259" t="n"/>
+      <c r="P3" s="259" t="n"/>
+      <c r="Q3" s="259" t="n"/>
+      <c r="R3" s="259" t="n"/>
+      <c r="S3" s="259" t="n"/>
+      <c r="T3" s="259" t="n"/>
+      <c r="U3" s="259" t="n"/>
+      <c r="V3" s="259" t="n"/>
+      <c r="W3" s="259" t="n"/>
+      <c r="X3" s="259" t="n"/>
+      <c r="Y3" s="259" t="n"/>
+      <c r="Z3" s="259" t="n"/>
+      <c r="AA3" s="259" t="n"/>
+      <c r="AB3" s="259" t="n"/>
+      <c r="AC3" s="259" t="n"/>
+      <c r="AD3" s="259" t="n"/>
+      <c r="AE3" s="259" t="n"/>
+      <c r="AF3" s="259" t="n"/>
+      <c r="AG3" s="259" t="n"/>
+      <c r="AH3" s="259" t="n"/>
+      <c r="AI3" s="259" t="n"/>
+      <c r="AJ3" s="259" t="n"/>
+      <c r="AK3" s="259" t="n"/>
+      <c r="AL3" s="259" t="n"/>
+      <c r="AM3" s="259" t="n"/>
+      <c r="AN3" s="259" t="n"/>
+      <c r="AO3" s="259" t="n"/>
+      <c r="AP3" s="259" t="n"/>
+      <c r="AQ3" s="259" t="n"/>
+      <c r="AR3" s="259" t="n"/>
+      <c r="AS3" s="259" t="n"/>
+    </row>
     <row r="4" ht="20.25" customHeight="1" s="257" thickBot="1">
-      <c r="E4" s="235" t="n">
+      <c r="A4" s="261" t="n"/>
+      <c r="B4" s="261" t="n"/>
+      <c r="C4" s="261" t="n"/>
+      <c r="D4" s="261" t="n"/>
+      <c r="E4" s="262" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="259" t="n"/>
-      <c r="G4" s="259" t="n"/>
-      <c r="H4" s="235" t="n">
+      <c r="F4" s="263" t="n"/>
+      <c r="G4" s="263" t="n"/>
+      <c r="H4" s="262" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="259" t="n"/>
-      <c r="J4" s="259" t="n"/>
-      <c r="K4" s="235" t="n">
+      <c r="I4" s="263" t="n"/>
+      <c r="J4" s="263" t="n"/>
+      <c r="K4" s="262" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="259" t="n"/>
-      <c r="M4" s="259" t="n"/>
-      <c r="N4" s="235" t="n">
+      <c r="L4" s="263" t="n"/>
+      <c r="M4" s="263" t="n"/>
+      <c r="N4" s="262" t="n">
         <v>4</v>
       </c>
-      <c r="O4" s="259" t="n"/>
-      <c r="P4" s="259" t="n"/>
-      <c r="Q4" s="235" t="n">
+      <c r="O4" s="263" t="n"/>
+      <c r="P4" s="263" t="n"/>
+      <c r="Q4" s="262" t="n">
         <v>5</v>
       </c>
-      <c r="R4" s="259" t="n"/>
-      <c r="S4" s="259" t="n"/>
-      <c r="T4" s="235" t="n">
+      <c r="R4" s="263" t="n"/>
+      <c r="S4" s="263" t="n"/>
+      <c r="T4" s="262" t="n">
         <v>6</v>
       </c>
-      <c r="U4" s="259" t="n"/>
-      <c r="V4" s="259" t="n"/>
-      <c r="W4" s="235" t="n">
+      <c r="U4" s="263" t="n"/>
+      <c r="V4" s="263" t="n"/>
+      <c r="W4" s="262" t="n">
         <v>7</v>
       </c>
-      <c r="X4" s="259" t="n"/>
-      <c r="Y4" s="259" t="n"/>
-      <c r="Z4" s="235" t="n">
+      <c r="X4" s="263" t="n"/>
+      <c r="Y4" s="263" t="n"/>
+      <c r="Z4" s="262" t="n">
         <v>8</v>
       </c>
-      <c r="AA4" s="259" t="n"/>
-      <c r="AB4" s="259" t="n"/>
-      <c r="AC4" s="235" t="n">
+      <c r="AA4" s="263" t="n"/>
+      <c r="AB4" s="263" t="n"/>
+      <c r="AC4" s="262" t="n">
         <v>9</v>
       </c>
-      <c r="AD4" s="259" t="n"/>
-      <c r="AE4" s="259" t="n"/>
-      <c r="AF4" s="235" t="n">
+      <c r="AD4" s="263" t="n"/>
+      <c r="AE4" s="263" t="n"/>
+      <c r="AF4" s="262" t="n">
         <v>10</v>
       </c>
-      <c r="AG4" s="259" t="n"/>
-      <c r="AH4" s="259" t="n"/>
-      <c r="AI4" s="235" t="n">
+      <c r="AG4" s="263" t="n"/>
+      <c r="AH4" s="263" t="n"/>
+      <c r="AI4" s="262" t="n">
         <v>11</v>
       </c>
-      <c r="AJ4" s="259" t="n"/>
-      <c r="AK4" s="259" t="n"/>
+      <c r="AJ4" s="263" t="n"/>
+      <c r="AK4" s="263" t="n"/>
+      <c r="AL4" s="264" t="n"/>
+      <c r="AM4" s="261" t="n"/>
+      <c r="AN4" s="261" t="n"/>
+      <c r="AO4" s="261" t="n"/>
+      <c r="AP4" s="261" t="n"/>
+      <c r="AQ4" s="261" t="n"/>
+      <c r="AR4" s="261" t="n"/>
+      <c r="AS4" s="261" t="n"/>
     </row>
     <row r="5" ht="57" customHeight="1" s="257" thickBot="1">
-      <c r="B5" s="108" t="inlineStr">
+      <c r="A5" s="265" t="n"/>
+      <c r="B5" s="265" t="inlineStr">
         <is>
           <t>チーム名</t>
         </is>
       </c>
-      <c r="C5" s="260" t="n"/>
-      <c r="D5" s="261" t="n"/>
-      <c r="E5" s="106">
+      <c r="C5" s="266" t="n"/>
+      <c r="D5" s="267" t="n"/>
+      <c r="E5" s="265">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F5" s="260" t="n"/>
-      <c r="G5" s="261" t="n"/>
-      <c r="H5" s="107">
+      <c r="F5" s="266" t="n"/>
+      <c r="G5" s="267" t="n"/>
+      <c r="H5" s="265">
         <f>C8</f>
         <v/>
       </c>
-      <c r="I5" s="260" t="n"/>
-      <c r="J5" s="261" t="n"/>
-      <c r="K5" s="107">
+      <c r="I5" s="266" t="n"/>
+      <c r="J5" s="267" t="n"/>
+      <c r="K5" s="265">
         <f>C10</f>
         <v/>
       </c>
-      <c r="L5" s="260" t="n"/>
-      <c r="M5" s="261" t="n"/>
-      <c r="N5" s="107">
+      <c r="L5" s="266" t="n"/>
+      <c r="M5" s="267" t="n"/>
+      <c r="N5" s="265">
         <f>C12</f>
         <v/>
       </c>
-      <c r="O5" s="260" t="n"/>
-      <c r="P5" s="261" t="n"/>
-      <c r="Q5" s="107">
+      <c r="O5" s="266" t="n"/>
+      <c r="P5" s="267" t="n"/>
+      <c r="Q5" s="265">
         <f>C14</f>
         <v/>
       </c>
-      <c r="R5" s="260" t="n"/>
-      <c r="S5" s="261" t="n"/>
-      <c r="T5" s="107">
+      <c r="R5" s="266" t="n"/>
+      <c r="S5" s="267" t="n"/>
+      <c r="T5" s="265">
         <f>C16</f>
         <v/>
       </c>
-      <c r="U5" s="260" t="n"/>
-      <c r="V5" s="261" t="n"/>
-      <c r="W5" s="107">
+      <c r="U5" s="266" t="n"/>
+      <c r="V5" s="267" t="n"/>
+      <c r="W5" s="265">
         <f>C18</f>
         <v/>
       </c>
-      <c r="X5" s="260" t="n"/>
-      <c r="Y5" s="261" t="n"/>
-      <c r="Z5" s="107">
+      <c r="X5" s="266" t="n"/>
+      <c r="Y5" s="267" t="n"/>
+      <c r="Z5" s="265">
         <f>C20</f>
         <v/>
       </c>
-      <c r="AA5" s="260" t="n"/>
-      <c r="AB5" s="261" t="n"/>
-      <c r="AC5" s="107">
+      <c r="AA5" s="266" t="n"/>
+      <c r="AB5" s="267" t="n"/>
+      <c r="AC5" s="265">
         <f>C22</f>
         <v/>
       </c>
-      <c r="AD5" s="260" t="n"/>
-      <c r="AE5" s="261" t="n"/>
-      <c r="AF5" s="107">
+      <c r="AD5" s="266" t="n"/>
+      <c r="AE5" s="267" t="n"/>
+      <c r="AF5" s="265">
         <f>C24</f>
         <v/>
       </c>
-      <c r="AG5" s="260" t="n"/>
-      <c r="AH5" s="261" t="n"/>
-      <c r="AI5" s="107">
+      <c r="AG5" s="266" t="n"/>
+      <c r="AH5" s="267" t="n"/>
+      <c r="AI5" s="265">
         <f>C26</f>
         <v/>
       </c>
-      <c r="AJ5" s="260" t="n"/>
-      <c r="AK5" s="261" t="n"/>
-      <c r="AL5" s="34" t="inlineStr">
+      <c r="AJ5" s="266" t="n"/>
+      <c r="AK5" s="267" t="n"/>
+      <c r="AL5" s="268" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
       </c>
-      <c r="AM5" s="35" t="inlineStr">
+      <c r="AM5" s="265" t="inlineStr">
         <is>
           <t>分</t>
         </is>
       </c>
-      <c r="AN5" s="35" t="inlineStr">
+      <c r="AN5" s="265" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
       </c>
-      <c r="AO5" s="35" t="inlineStr">
+      <c r="AO5" s="265" t="inlineStr">
         <is>
           <t>勝点</t>
         </is>
       </c>
-      <c r="AP5" s="36" t="inlineStr">
+      <c r="AP5" s="265" t="inlineStr">
         <is>
           <t>失点</t>
         </is>
       </c>
-      <c r="AQ5" s="35" t="inlineStr">
+      <c r="AQ5" s="265" t="inlineStr">
         <is>
           <t>得点</t>
         </is>
       </c>
-      <c r="AR5" s="37" t="inlineStr">
+      <c r="AR5" s="265" t="inlineStr">
         <is>
           <t>残試</t>
         </is>
       </c>
-      <c r="AS5" s="7" t="inlineStr">
+      <c r="AS5" s="265" t="inlineStr">
         <is>
           <t>順位</t>
         </is>
@@ -3055,114 +3342,115 @@
           <t>チームナンバー</t>
         </is>
       </c>
-      <c r="AX5" s="262" t="n"/>
+      <c r="AX5" s="269" t="n"/>
       <c r="AZ5" s="100" t="inlineStr">
         <is>
           <t>チームリスト</t>
         </is>
       </c>
-      <c r="BA5" s="263" t="n"/>
+      <c r="BA5" s="270" t="n"/>
     </row>
     <row r="6" ht="46.9" customHeight="1" s="257">
-      <c r="B6" s="130" t="n">
+      <c r="A6" s="271" t="n"/>
+      <c r="B6" s="271" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="132">
+      <c r="C6" s="271">
         <f>AX6</f>
         <v/>
       </c>
-      <c r="D6" s="264" t="n"/>
-      <c r="E6" s="146" t="n"/>
-      <c r="G6" s="264" t="n"/>
-      <c r="H6" s="265">
+      <c r="D6" s="272" t="n"/>
+      <c r="E6" s="273" t="n"/>
+      <c r="G6" s="272" t="n"/>
+      <c r="H6" s="274">
         <f>IF(H7="","",IF(H7="☂","☂",IF(H7&gt;J7,"○",IF(H7=J7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I6" s="266" t="n"/>
-      <c r="J6" s="267" t="n"/>
-      <c r="K6" s="265">
+      <c r="I6" s="275" t="n"/>
+      <c r="J6" s="276" t="n"/>
+      <c r="K6" s="274">
         <f>IF(K7="","",IF(K7="☂","☂",IF(K7&gt;M7,"○",IF(K7=M7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L6" s="266" t="n"/>
-      <c r="M6" s="267" t="n"/>
-      <c r="N6" s="265">
+      <c r="L6" s="275" t="n"/>
+      <c r="M6" s="276" t="n"/>
+      <c r="N6" s="274">
         <f>IF(N7="","",IF(N7="☂","☂",IF(N7&gt;P7,"○",IF(N7=P7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O6" s="266" t="n"/>
-      <c r="P6" s="267" t="n"/>
-      <c r="Q6" s="265">
+      <c r="O6" s="275" t="n"/>
+      <c r="P6" s="276" t="n"/>
+      <c r="Q6" s="274">
         <f>IF(Q7="","",IF(Q7="☂","☂",IF(Q7&gt;S7,"○",IF(Q7=S7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R6" s="266" t="n"/>
-      <c r="S6" s="267" t="n"/>
-      <c r="T6" s="265">
+      <c r="R6" s="275" t="n"/>
+      <c r="S6" s="276" t="n"/>
+      <c r="T6" s="274">
         <f>IF(T7="","",IF(T7="☂","☂",IF(T7&gt;V7,"○",IF(T7=V7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U6" s="266" t="n"/>
-      <c r="V6" s="267" t="n"/>
-      <c r="W6" s="265">
+      <c r="U6" s="275" t="n"/>
+      <c r="V6" s="276" t="n"/>
+      <c r="W6" s="274">
         <f>IF(W7="","",IF(W7="☂","☂",IF(W7&gt;Y7,"○",IF(W7=Y7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X6" s="266" t="n"/>
-      <c r="Y6" s="267" t="n"/>
-      <c r="Z6" s="265">
+      <c r="X6" s="275" t="n"/>
+      <c r="Y6" s="276" t="n"/>
+      <c r="Z6" s="274">
         <f>IF(Z7="","",IF(Z7="☂","☂",IF(Z7&gt;AB7,"○",IF(Z7=AB7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA6" s="266" t="n"/>
-      <c r="AB6" s="267" t="n"/>
-      <c r="AC6" s="265">
+      <c r="AA6" s="275" t="n"/>
+      <c r="AB6" s="276" t="n"/>
+      <c r="AC6" s="274">
         <f>IF(AC7="","",IF(AC7="☂","☂",IF(AC7&gt;AE7,"○",IF(AC7=AE7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD6" s="266" t="n"/>
-      <c r="AE6" s="267" t="n"/>
-      <c r="AF6" s="265">
+      <c r="AD6" s="275" t="n"/>
+      <c r="AE6" s="276" t="n"/>
+      <c r="AF6" s="274">
         <f>IF(AF7="","",IF(AF7="☂","☂",IF(AF7&gt;AH7,"○",IF(AF7=AH7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG6" s="266" t="n"/>
-      <c r="AH6" s="267" t="n"/>
-      <c r="AI6" s="265">
+      <c r="AG6" s="275" t="n"/>
+      <c r="AH6" s="276" t="n"/>
+      <c r="AI6" s="274">
         <f>IF(AI7="","",IF(AI7="☂","☂",IF(AI7&gt;AK7,"○",IF(AI7=AK7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ6" s="266" t="n"/>
-      <c r="AK6" s="267" t="n"/>
-      <c r="AL6" s="268">
+      <c r="AJ6" s="275" t="n"/>
+      <c r="AK6" s="276" t="n"/>
+      <c r="AL6" s="277">
         <f>COUNTIF(E6:AK6,"○")</f>
         <v/>
       </c>
-      <c r="AM6" s="269">
+      <c r="AM6" s="278">
         <f>COUNTIF(E6:AK6,"△")</f>
         <v/>
       </c>
-      <c r="AN6" s="269">
+      <c r="AN6" s="278">
         <f>COUNTIF(E6:AK6,"×")</f>
         <v/>
       </c>
-      <c r="AO6" s="269">
+      <c r="AO6" s="279">
         <f>AL6*3+AM6*1</f>
         <v/>
       </c>
-      <c r="AP6" s="270">
+      <c r="AP6" s="278">
         <f>SUM(J7,M7,P7,S7,V7,Y7,AB7,AK7)</f>
         <v/>
       </c>
-      <c r="AQ6" s="269">
+      <c r="AQ6" s="278">
         <f>SUM(H7,K7,N7,Q7,T7,W7,Z7,AI7)</f>
         <v/>
       </c>
-      <c r="AR6" s="271">
+      <c r="AR6" s="278">
         <f>$AY$21-AL6-AM6-AN6</f>
         <v/>
       </c>
-      <c r="AS6" s="114">
+      <c r="AS6" s="280">
         <f>IFERROR(_xlfn.RANK.EQ(AO6,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3186,153 +3474,154 @@
       </c>
     </row>
     <row r="7" ht="46.9" customHeight="1" s="257">
-      <c r="B7" s="272" t="n"/>
-      <c r="C7" s="273" t="n"/>
-      <c r="D7" s="274" t="n"/>
-      <c r="E7" s="263" t="n"/>
-      <c r="F7" s="263" t="n"/>
-      <c r="G7" s="274" t="n"/>
-      <c r="H7" s="275">
+      <c r="A7" s="271" t="n"/>
+      <c r="B7" s="281" t="n"/>
+      <c r="C7" s="282" t="n"/>
+      <c r="D7" s="283" t="n"/>
+      <c r="E7" s="270" t="n"/>
+      <c r="F7" s="270" t="n"/>
+      <c r="G7" s="283" t="n"/>
+      <c r="H7" s="284">
         <f>IF(G9="","",G9)</f>
         <v/>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="275">
+      <c r="J7" s="284">
         <f>IF(E9="","",E9)</f>
         <v/>
       </c>
-      <c r="K7" s="275">
+      <c r="K7" s="284">
         <f>IF(G11="","",G11)</f>
         <v/>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M7" s="275">
+      <c r="M7" s="284">
         <f>IF(E11="","",E11)</f>
         <v/>
       </c>
-      <c r="N7" s="275">
+      <c r="N7" s="284">
         <f>IF(G13="","",G13)</f>
         <v/>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P7" s="275">
+      <c r="P7" s="284">
         <f>IF(E13="","",E13)</f>
         <v/>
       </c>
-      <c r="Q7" s="275">
+      <c r="Q7" s="284">
         <f>IF(G15="","",G15)</f>
         <v/>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="R7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S7" s="275">
+      <c r="S7" s="284">
         <f>IF(E15="","",E15)</f>
         <v/>
       </c>
-      <c r="T7" s="275">
+      <c r="T7" s="284">
         <f>IF(G17="","",G17)</f>
         <v/>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="U7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V7" s="275">
+      <c r="V7" s="284">
         <f>IF(E17="","",E17)</f>
         <v/>
       </c>
-      <c r="W7" s="275">
+      <c r="W7" s="284">
         <f>IF(G19="","",G19)</f>
         <v/>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="X7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y7" s="275">
+      <c r="Y7" s="284">
         <f>IF(E19="","",E19)</f>
         <v/>
       </c>
-      <c r="Z7" s="275">
+      <c r="Z7" s="284">
         <f>IF(G21="","",G21)</f>
         <v/>
       </c>
-      <c r="AA7" s="8" t="inlineStr">
+      <c r="AA7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB7" s="275">
+      <c r="AB7" s="284">
         <f>IF(E21="","",E21)</f>
         <v/>
       </c>
-      <c r="AC7" s="275">
+      <c r="AC7" s="284">
         <f>IF(G23="","",G23)</f>
         <v/>
       </c>
-      <c r="AD7" s="8" t="inlineStr">
+      <c r="AD7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE7" s="275">
+      <c r="AE7" s="284">
         <f>IF(E23="","",E23)</f>
         <v/>
       </c>
-      <c r="AF7" s="275">
+      <c r="AF7" s="284">
         <f>IF(G25="","",G25)</f>
         <v/>
       </c>
-      <c r="AG7" s="8" t="inlineStr">
+      <c r="AG7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH7" s="275">
+      <c r="AH7" s="284">
         <f>IF(E25="","",E25)</f>
         <v/>
       </c>
-      <c r="AI7" s="275">
+      <c r="AI7" s="284">
         <f>IF(G27="","",G27)</f>
         <v/>
       </c>
-      <c r="AJ7" s="8" t="inlineStr">
+      <c r="AJ7" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK7" s="275">
+      <c r="AK7" s="284">
         <f>IF(E27="","",G27)</f>
         <v/>
       </c>
-      <c r="AL7" s="272" t="n"/>
-      <c r="AM7" s="276" t="n"/>
-      <c r="AN7" s="276" t="n"/>
-      <c r="AO7" s="276" t="n"/>
-      <c r="AP7" s="273" t="n"/>
-      <c r="AQ7" s="276" t="n"/>
-      <c r="AR7" s="276" t="n"/>
-      <c r="AS7" s="277" t="n"/>
-      <c r="AV7" s="276" t="n"/>
-      <c r="AW7" s="278" t="n"/>
-      <c r="AX7" s="276" t="n"/>
+      <c r="AL7" s="281" t="n"/>
+      <c r="AM7" s="286" t="n"/>
+      <c r="AN7" s="286" t="n"/>
+      <c r="AO7" s="286" t="n"/>
+      <c r="AP7" s="282" t="n"/>
+      <c r="AQ7" s="286" t="n"/>
+      <c r="AR7" s="286" t="n"/>
+      <c r="AS7" s="287" t="n"/>
+      <c r="AV7" s="286" t="n"/>
+      <c r="AW7" s="288" t="n"/>
+      <c r="AX7" s="286" t="n"/>
       <c r="AZ7" s="5" t="n">
         <v>2</v>
       </c>
@@ -3343,106 +3632,107 @@
       </c>
     </row>
     <row r="8" ht="46.9" customHeight="1" s="257">
-      <c r="B8" s="117" t="n">
+      <c r="A8" s="271" t="n"/>
+      <c r="B8" s="271" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="118">
+      <c r="C8" s="271">
         <f>AX8</f>
         <v/>
       </c>
-      <c r="D8" s="264" t="n"/>
-      <c r="E8" s="122">
+      <c r="D8" s="272" t="n"/>
+      <c r="E8" s="289">
         <f>IF(E9="","",IF(E9="☂","☂",IF(E9&gt;G9,"○",IF(E9=G9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F8" s="279" t="n"/>
-      <c r="G8" s="280" t="n"/>
-      <c r="H8" s="281" t="n"/>
-      <c r="I8" s="282" t="n"/>
-      <c r="J8" s="262" t="n"/>
-      <c r="K8" s="283">
+      <c r="F8" s="290" t="n"/>
+      <c r="G8" s="291" t="n"/>
+      <c r="H8" s="289" t="n"/>
+      <c r="I8" s="292" t="n"/>
+      <c r="J8" s="269" t="n"/>
+      <c r="K8" s="293">
         <f>IF(K9="","",IF(K9="☂","☂",IF(K9&gt;M9,"○",IF(K9=M9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L8" s="284" t="n"/>
-      <c r="M8" s="285" t="n"/>
-      <c r="N8" s="283">
+      <c r="L8" s="294" t="n"/>
+      <c r="M8" s="295" t="n"/>
+      <c r="N8" s="293">
         <f>IF(N9="","",IF(N9="☂","☂",IF(N9&gt;P9,"○",IF(N9=P9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O8" s="284" t="n"/>
-      <c r="P8" s="285" t="n"/>
-      <c r="Q8" s="283">
+      <c r="O8" s="294" t="n"/>
+      <c r="P8" s="295" t="n"/>
+      <c r="Q8" s="293">
         <f>IF(Q9="","",IF(Q9="☂","☂",IF(Q9&gt;S9,"○",IF(Q9=S9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R8" s="284" t="n"/>
-      <c r="S8" s="285" t="n"/>
-      <c r="T8" s="283">
+      <c r="R8" s="294" t="n"/>
+      <c r="S8" s="295" t="n"/>
+      <c r="T8" s="293">
         <f>IF(T9="","",IF(T9="☂","☂",IF(T9&gt;V9,"○",IF(T9=V9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U8" s="284" t="n"/>
-      <c r="V8" s="285" t="n"/>
-      <c r="W8" s="283">
+      <c r="U8" s="294" t="n"/>
+      <c r="V8" s="295" t="n"/>
+      <c r="W8" s="293">
         <f>IF(W9="","",IF(W9="☂","☂",IF(W9&gt;Y9,"○",IF(W9=Y9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X8" s="284" t="n"/>
-      <c r="Y8" s="285" t="n"/>
-      <c r="Z8" s="283">
+      <c r="X8" s="294" t="n"/>
+      <c r="Y8" s="295" t="n"/>
+      <c r="Z8" s="293">
         <f>IF(Z9="","",IF(Z9="☂","☂",IF(Z9&gt;AB9,"○",IF(Z9=AB9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA8" s="284" t="n"/>
-      <c r="AB8" s="285" t="n"/>
-      <c r="AC8" s="283">
+      <c r="AA8" s="294" t="n"/>
+      <c r="AB8" s="295" t="n"/>
+      <c r="AC8" s="293">
         <f>IF(AC9="","",IF(AC9="☂","☂",IF(AC9&gt;AE9,"○",IF(AC9=AE9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD8" s="284" t="n"/>
-      <c r="AE8" s="285" t="n"/>
-      <c r="AF8" s="283">
+      <c r="AD8" s="294" t="n"/>
+      <c r="AE8" s="295" t="n"/>
+      <c r="AF8" s="293">
         <f>IF(AF9="","",IF(AF9="☂","☂",IF(AF9&gt;AH9,"○",IF(AF9=AH9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG8" s="284" t="n"/>
-      <c r="AH8" s="285" t="n"/>
-      <c r="AI8" s="283">
+      <c r="AG8" s="294" t="n"/>
+      <c r="AH8" s="295" t="n"/>
+      <c r="AI8" s="293">
         <f>IF(AI9="","",IF(AI9="☂","☂",IF(AI9&gt;AK9,"○",IF(AI9=AK9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ8" s="284" t="n"/>
-      <c r="AK8" s="285" t="n"/>
-      <c r="AL8" s="286">
+      <c r="AJ8" s="294" t="n"/>
+      <c r="AK8" s="295" t="n"/>
+      <c r="AL8" s="277">
         <f>COUNTIF(E8:AK8,"○")</f>
         <v/>
       </c>
-      <c r="AM8" s="287">
+      <c r="AM8" s="278">
         <f>COUNTIF(E8:AK8,"△")</f>
         <v/>
       </c>
-      <c r="AN8" s="287">
+      <c r="AN8" s="278">
         <f>COUNTIF(E8:AK8,"×")</f>
         <v/>
       </c>
-      <c r="AO8" s="287">
+      <c r="AO8" s="279">
         <f>AL8*3+AM8*1</f>
         <v/>
       </c>
-      <c r="AP8" s="287">
+      <c r="AP8" s="278">
         <f>SUM(G9,M9,P9,S9,V9,Y9,AB9,AK9)</f>
         <v/>
       </c>
-      <c r="AQ8" s="287">
+      <c r="AQ8" s="278">
         <f>SUM(E9,K9,N9,Q9,T9,W9,Z9,AI9)</f>
         <v/>
       </c>
-      <c r="AR8" s="287">
+      <c r="AR8" s="278">
         <f>$AY$21-AL8-AM8-AN8</f>
         <v/>
       </c>
-      <c r="AS8" s="288">
+      <c r="AS8" s="280">
         <f>IFERROR(_xlfn.RANK.EQ(AO8,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3466,147 +3756,148 @@
       </c>
     </row>
     <row r="9" ht="46.9" customHeight="1" s="257">
-      <c r="B9" s="272" t="n"/>
-      <c r="C9" s="273" t="n"/>
-      <c r="D9" s="274" t="n"/>
-      <c r="E9" s="62" t="n"/>
-      <c r="F9" s="123" t="inlineStr">
+      <c r="A9" s="271" t="n"/>
+      <c r="B9" s="281" t="n"/>
+      <c r="C9" s="282" t="n"/>
+      <c r="D9" s="283" t="n"/>
+      <c r="E9" s="296" t="n"/>
+      <c r="F9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="63" t="n"/>
-      <c r="H9" s="273" t="n"/>
-      <c r="I9" s="263" t="n"/>
-      <c r="J9" s="274" t="n"/>
-      <c r="K9" s="123">
+      <c r="G9" s="296" t="n"/>
+      <c r="H9" s="282" t="n"/>
+      <c r="I9" s="270" t="n"/>
+      <c r="J9" s="283" t="n"/>
+      <c r="K9" s="297">
         <f>IF(J11="","",J11)</f>
         <v/>
       </c>
-      <c r="L9" s="123" t="inlineStr">
+      <c r="L9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M9" s="123">
+      <c r="M9" s="297">
         <f>IF(H11="","",H11)</f>
         <v/>
       </c>
-      <c r="N9" s="123">
+      <c r="N9" s="297">
         <f>IF(J13="","",J13)</f>
         <v/>
       </c>
-      <c r="O9" s="123" t="inlineStr">
+      <c r="O9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P9" s="123">
+      <c r="P9" s="297">
         <f>IF(H13="","",H13)</f>
         <v/>
       </c>
-      <c r="Q9" s="123">
+      <c r="Q9" s="297">
         <f>IF(J15="","",J15)</f>
         <v/>
       </c>
-      <c r="R9" s="123" t="inlineStr">
+      <c r="R9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S9" s="123">
+      <c r="S9" s="297">
         <f>IF(H15="","",H15)</f>
         <v/>
       </c>
-      <c r="T9" s="123">
+      <c r="T9" s="297">
         <f>IF(J17="","",J17)</f>
         <v/>
       </c>
-      <c r="U9" s="123" t="inlineStr">
+      <c r="U9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V9" s="123">
+      <c r="V9" s="297">
         <f>IF(H17="","",H17)</f>
         <v/>
       </c>
-      <c r="W9" s="123">
+      <c r="W9" s="297">
         <f>IF(J19="","",J19)</f>
         <v/>
       </c>
-      <c r="X9" s="123" t="inlineStr">
+      <c r="X9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y9" s="123">
+      <c r="Y9" s="297">
         <f>IF(H19="","",H19)</f>
         <v/>
       </c>
-      <c r="Z9" s="123">
+      <c r="Z9" s="297">
         <f>IF(J21="","",J21)</f>
         <v/>
       </c>
-      <c r="AA9" s="123" t="inlineStr">
+      <c r="AA9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB9" s="123">
+      <c r="AB9" s="297">
         <f>IF(H21="","",H21)</f>
         <v/>
       </c>
-      <c r="AC9" s="123">
+      <c r="AC9" s="297">
         <f>IF(J23="","",J23)</f>
         <v/>
       </c>
-      <c r="AD9" s="123" t="inlineStr">
+      <c r="AD9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE9" s="123">
+      <c r="AE9" s="297">
         <f>IF(H23="","",H23)</f>
         <v/>
       </c>
-      <c r="AF9" s="123">
+      <c r="AF9" s="297">
         <f>IF(J25="","",J25)</f>
         <v/>
       </c>
-      <c r="AG9" s="123" t="inlineStr">
+      <c r="AG9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH9" s="123">
+      <c r="AH9" s="297">
         <f>IF(H25="","",H25)</f>
         <v/>
       </c>
-      <c r="AI9" s="123">
+      <c r="AI9" s="297">
         <f>IF(J27="","",J27)</f>
         <v/>
       </c>
-      <c r="AJ9" s="123" t="inlineStr">
+      <c r="AJ9" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK9" s="123">
+      <c r="AK9" s="297">
         <f>IF(H27="","",H27)</f>
         <v/>
       </c>
-      <c r="AL9" s="272" t="n"/>
-      <c r="AM9" s="276" t="n"/>
-      <c r="AN9" s="276" t="n"/>
-      <c r="AO9" s="276" t="n"/>
-      <c r="AP9" s="276" t="n"/>
-      <c r="AQ9" s="276" t="n"/>
-      <c r="AR9" s="276" t="n"/>
-      <c r="AS9" s="289" t="n"/>
-      <c r="AV9" s="276" t="n"/>
-      <c r="AW9" s="278" t="n"/>
-      <c r="AX9" s="276" t="n"/>
+      <c r="AL9" s="281" t="n"/>
+      <c r="AM9" s="286" t="n"/>
+      <c r="AN9" s="286" t="n"/>
+      <c r="AO9" s="286" t="n"/>
+      <c r="AP9" s="286" t="n"/>
+      <c r="AQ9" s="286" t="n"/>
+      <c r="AR9" s="286" t="n"/>
+      <c r="AS9" s="298" t="n"/>
+      <c r="AV9" s="286" t="n"/>
+      <c r="AW9" s="288" t="n"/>
+      <c r="AX9" s="286" t="n"/>
       <c r="AZ9" s="5" t="n">
         <v>4</v>
       </c>
@@ -3617,106 +3908,107 @@
       </c>
     </row>
     <row r="10" ht="46.9" customHeight="1" s="257">
-      <c r="B10" s="131" t="n">
+      <c r="A10" s="271" t="n"/>
+      <c r="B10" s="271" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="132">
+      <c r="C10" s="271">
         <f>AX10</f>
         <v/>
       </c>
-      <c r="D10" s="264" t="n"/>
-      <c r="E10" s="290">
+      <c r="D10" s="272" t="n"/>
+      <c r="E10" s="273">
         <f>IF(E11="","",IF(E11="☂","☂",IF(E11&gt;G11,"○",IF(E11=G11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F10" s="279" t="n"/>
-      <c r="G10" s="280" t="n"/>
-      <c r="H10" s="8">
+      <c r="F10" s="290" t="n"/>
+      <c r="G10" s="291" t="n"/>
+      <c r="H10" s="273">
         <f>IF(H11="","",IF(H11="☂","☂",IF(H11&gt;J11,"○",IF(H11=J11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I10" s="279" t="n"/>
-      <c r="J10" s="280" t="n"/>
-      <c r="K10" s="291" t="n"/>
-      <c r="L10" s="282" t="n"/>
-      <c r="M10" s="262" t="n"/>
-      <c r="N10" s="292">
+      <c r="I10" s="290" t="n"/>
+      <c r="J10" s="291" t="n"/>
+      <c r="K10" s="273" t="n"/>
+      <c r="L10" s="292" t="n"/>
+      <c r="M10" s="269" t="n"/>
+      <c r="N10" s="274">
         <f>IF(N11="","",IF(N11="☂","☂",IF(N11&gt;P11,"○",IF(N11=P11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O10" s="284" t="n"/>
-      <c r="P10" s="285" t="n"/>
-      <c r="Q10" s="292">
+      <c r="O10" s="294" t="n"/>
+      <c r="P10" s="295" t="n"/>
+      <c r="Q10" s="274">
         <f>IF(Q11="","",IF(Q11="☂","☂",IF(Q11&gt;S11,"○",IF(Q11=S11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R10" s="284" t="n"/>
-      <c r="S10" s="285" t="n"/>
-      <c r="T10" s="292">
+      <c r="R10" s="294" t="n"/>
+      <c r="S10" s="295" t="n"/>
+      <c r="T10" s="274">
         <f>IF(T11="","",IF(T11="☂","☂",IF(T11&gt;V11,"○",IF(T11=V11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U10" s="284" t="n"/>
-      <c r="V10" s="285" t="n"/>
-      <c r="W10" s="292">
+      <c r="U10" s="294" t="n"/>
+      <c r="V10" s="295" t="n"/>
+      <c r="W10" s="274">
         <f>IF(W11="","",IF(W11="☂","☂",IF(W11&gt;Y11,"○",IF(W11=Y11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X10" s="284" t="n"/>
-      <c r="Y10" s="285" t="n"/>
-      <c r="Z10" s="292">
+      <c r="X10" s="294" t="n"/>
+      <c r="Y10" s="295" t="n"/>
+      <c r="Z10" s="274">
         <f>IF(Z11="","",IF(Z11="☂","☂",IF(Z11&gt;AB11,"○",IF(Z11=AB11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA10" s="284" t="n"/>
-      <c r="AB10" s="285" t="n"/>
-      <c r="AC10" s="292">
+      <c r="AA10" s="294" t="n"/>
+      <c r="AB10" s="295" t="n"/>
+      <c r="AC10" s="274">
         <f>IF(AC11="","",IF(AC11="☂","☂",IF(AC11&gt;AE11,"○",IF(AC11=AE11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD10" s="284" t="n"/>
-      <c r="AE10" s="285" t="n"/>
-      <c r="AF10" s="292">
+      <c r="AD10" s="294" t="n"/>
+      <c r="AE10" s="295" t="n"/>
+      <c r="AF10" s="274">
         <f>IF(AF11="","",IF(AF11="☂","☂",IF(AF11&gt;AH11,"○",IF(AF11=AH11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG10" s="284" t="n"/>
-      <c r="AH10" s="285" t="n"/>
-      <c r="AI10" s="292">
+      <c r="AG10" s="294" t="n"/>
+      <c r="AH10" s="295" t="n"/>
+      <c r="AI10" s="274">
         <f>IF(AI11="","",IF(AI11="☂","☂",IF(AI11&gt;AK11,"○",IF(AI11=AK11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ10" s="284" t="n"/>
-      <c r="AK10" s="285" t="n"/>
-      <c r="AL10" s="293">
+      <c r="AJ10" s="294" t="n"/>
+      <c r="AK10" s="295" t="n"/>
+      <c r="AL10" s="277">
         <f>COUNTIF(E10:AK10,"○")</f>
         <v/>
       </c>
-      <c r="AM10" s="294">
+      <c r="AM10" s="278">
         <f>COUNTIF(E10:AK10,"△")</f>
         <v/>
       </c>
-      <c r="AN10" s="294">
+      <c r="AN10" s="278">
         <f>COUNTIF(E10:AK10,"×")</f>
         <v/>
       </c>
-      <c r="AO10" s="294">
+      <c r="AO10" s="279">
         <f>AL10*3+AM10*1</f>
         <v/>
       </c>
-      <c r="AP10" s="294">
+      <c r="AP10" s="278">
         <f>SUM(G11,J11,M11,P11,S11,V11,Y11,AB11,AK11)</f>
         <v/>
       </c>
-      <c r="AQ10" s="294">
+      <c r="AQ10" s="278">
         <f>SUM(E11,H11,K11,N11,Q11,T11,W11,Z11,AI11)</f>
         <v/>
       </c>
-      <c r="AR10" s="294">
+      <c r="AR10" s="278">
         <f>$AY$21-AL10-AM10-AN10</f>
         <v/>
       </c>
-      <c r="AS10" s="288">
+      <c r="AS10" s="280">
         <f>IFERROR(_xlfn.RANK.EQ(AO10,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3740,137 +4032,138 @@
       </c>
     </row>
     <row r="11" ht="46.9" customHeight="1" s="257">
-      <c r="B11" s="272" t="n"/>
-      <c r="C11" s="273" t="n"/>
-      <c r="D11" s="274" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="A11" s="271" t="n"/>
+      <c r="B11" s="281" t="n"/>
+      <c r="C11" s="282" t="n"/>
+      <c r="D11" s="283" t="n"/>
+      <c r="E11" s="299" t="n"/>
+      <c r="F11" s="285" t="n"/>
+      <c r="G11" s="299" t="n"/>
+      <c r="H11" s="299" t="n"/>
+      <c r="I11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="273" t="n"/>
-      <c r="L11" s="263" t="n"/>
-      <c r="M11" s="274" t="n"/>
-      <c r="N11" s="8">
+      <c r="J11" s="299" t="n"/>
+      <c r="K11" s="282" t="n"/>
+      <c r="L11" s="270" t="n"/>
+      <c r="M11" s="283" t="n"/>
+      <c r="N11" s="285">
         <f>IF(M13="","",M13)</f>
         <v/>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="285">
         <f>IF(K13="","",K13)</f>
         <v/>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="285">
         <f>IF(M15="","",M15)</f>
         <v/>
       </c>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="R11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="285">
         <f>IF(K15="","",K15)</f>
         <v/>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="285">
         <f>IF(M17="","",M17)</f>
         <v/>
       </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="U11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="285">
         <f>IF(K17="","",K17)</f>
         <v/>
       </c>
-      <c r="W11" s="8">
+      <c r="W11" s="285">
         <f>IF(M19="","",M19)</f>
         <v/>
       </c>
-      <c r="X11" s="8" t="inlineStr">
+      <c r="X11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y11" s="8">
+      <c r="Y11" s="285">
         <f>IF(K19="","",K19)</f>
         <v/>
       </c>
-      <c r="Z11" s="8">
+      <c r="Z11" s="285">
         <f>IF(M21="","",M21)</f>
         <v/>
       </c>
-      <c r="AA11" s="8" t="inlineStr">
+      <c r="AA11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB11" s="8">
+      <c r="AB11" s="285">
         <f>IF(K21="","",K21)</f>
         <v/>
       </c>
-      <c r="AC11" s="8">
+      <c r="AC11" s="285">
         <f>IF(M23="","",M23)</f>
         <v/>
       </c>
-      <c r="AD11" s="8" t="inlineStr">
+      <c r="AD11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE11" s="8">
+      <c r="AE11" s="285">
         <f>IF(K23="","",K23)</f>
         <v/>
       </c>
-      <c r="AF11" s="8">
+      <c r="AF11" s="285">
         <f>IF(M25="","",M25)</f>
         <v/>
       </c>
-      <c r="AG11" s="8" t="inlineStr">
+      <c r="AG11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH11" s="8">
+      <c r="AH11" s="285">
         <f>IF(K25="","",K25)</f>
         <v/>
       </c>
-      <c r="AI11" s="8">
+      <c r="AI11" s="285">
         <f>IF(M27="","",M27)</f>
         <v/>
       </c>
-      <c r="AJ11" s="8" t="inlineStr">
+      <c r="AJ11" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK11" s="8">
+      <c r="AK11" s="285">
         <f>IF(K27="","",K27)</f>
         <v/>
       </c>
-      <c r="AL11" s="272" t="n"/>
-      <c r="AM11" s="276" t="n"/>
-      <c r="AN11" s="276" t="n"/>
-      <c r="AO11" s="276" t="n"/>
-      <c r="AP11" s="276" t="n"/>
-      <c r="AQ11" s="276" t="n"/>
-      <c r="AR11" s="276" t="n"/>
-      <c r="AS11" s="289" t="n"/>
-      <c r="AV11" s="276" t="n"/>
-      <c r="AW11" s="278" t="n"/>
-      <c r="AX11" s="276" t="n"/>
+      <c r="AL11" s="281" t="n"/>
+      <c r="AM11" s="286" t="n"/>
+      <c r="AN11" s="286" t="n"/>
+      <c r="AO11" s="286" t="n"/>
+      <c r="AP11" s="286" t="n"/>
+      <c r="AQ11" s="286" t="n"/>
+      <c r="AR11" s="286" t="n"/>
+      <c r="AS11" s="298" t="n"/>
+      <c r="AV11" s="286" t="n"/>
+      <c r="AW11" s="288" t="n"/>
+      <c r="AX11" s="286" t="n"/>
       <c r="AZ11" s="5" t="n">
         <v>6</v>
       </c>
@@ -3881,106 +4174,107 @@
       </c>
     </row>
     <row r="12" ht="46.9" customHeight="1" s="257">
-      <c r="B12" s="117" t="n">
+      <c r="A12" s="271" t="n"/>
+      <c r="B12" s="271" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="118">
+      <c r="C12" s="271">
         <f>AX12</f>
         <v/>
       </c>
-      <c r="D12" s="264" t="n"/>
-      <c r="E12" s="295">
+      <c r="D12" s="272" t="n"/>
+      <c r="E12" s="289">
         <f>IF(E13="","",IF(E13="☂","☂",IF(E13&gt;G13,"○",IF(E13=G13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F12" s="279" t="n"/>
-      <c r="G12" s="280" t="n"/>
-      <c r="H12" s="123">
+      <c r="F12" s="290" t="n"/>
+      <c r="G12" s="291" t="n"/>
+      <c r="H12" s="289">
         <f>IF(H13="","",IF(H13="☂","☂",IF(H13&gt;J13,"○",IF(H13=J13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I12" s="279" t="n"/>
-      <c r="J12" s="280" t="n"/>
-      <c r="K12" s="123">
+      <c r="I12" s="290" t="n"/>
+      <c r="J12" s="291" t="n"/>
+      <c r="K12" s="289">
         <f>IF(K13="","",IF(K13="☂","☂",IF(K13&gt;M13,"○",IF(K13=M13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L12" s="279" t="n"/>
-      <c r="M12" s="280" t="n"/>
-      <c r="N12" s="281" t="n"/>
-      <c r="O12" s="282" t="n"/>
-      <c r="P12" s="262" t="n"/>
-      <c r="Q12" s="283">
+      <c r="L12" s="290" t="n"/>
+      <c r="M12" s="291" t="n"/>
+      <c r="N12" s="289" t="n"/>
+      <c r="O12" s="292" t="n"/>
+      <c r="P12" s="269" t="n"/>
+      <c r="Q12" s="293">
         <f>IF(Q13="","",IF(Q13="☂","☂",IF(Q13&gt;S13,"○",IF(Q13=S13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R12" s="284" t="n"/>
-      <c r="S12" s="285" t="n"/>
-      <c r="T12" s="283">
+      <c r="R12" s="294" t="n"/>
+      <c r="S12" s="295" t="n"/>
+      <c r="T12" s="293">
         <f>IF(T13="","",IF(T13="☂","☂",IF(T13&gt;V13,"○",IF(T13=V13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U12" s="284" t="n"/>
-      <c r="V12" s="285" t="n"/>
-      <c r="W12" s="283">
+      <c r="U12" s="294" t="n"/>
+      <c r="V12" s="295" t="n"/>
+      <c r="W12" s="293">
         <f>IF(W13="","",IF(W13="☂","☂",IF(W13&gt;Y13,"○",IF(W13=Y13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X12" s="284" t="n"/>
-      <c r="Y12" s="285" t="n"/>
-      <c r="Z12" s="283">
+      <c r="X12" s="294" t="n"/>
+      <c r="Y12" s="295" t="n"/>
+      <c r="Z12" s="293">
         <f>IF(Z13="","",IF(Z13="☂","☂",IF(Z13&gt;AB13,"○",IF(Z13=AB13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA12" s="284" t="n"/>
-      <c r="AB12" s="285" t="n"/>
-      <c r="AC12" s="283">
+      <c r="AA12" s="294" t="n"/>
+      <c r="AB12" s="295" t="n"/>
+      <c r="AC12" s="293">
         <f>IF(AC13="","",IF(AC13="☂","☂",IF(AC13&gt;AE13,"○",IF(AC13=AE13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD12" s="284" t="n"/>
-      <c r="AE12" s="285" t="n"/>
-      <c r="AF12" s="283">
+      <c r="AD12" s="294" t="n"/>
+      <c r="AE12" s="295" t="n"/>
+      <c r="AF12" s="293">
         <f>IF(AF13="","",IF(AF13="☂","☂",IF(AF13&gt;AH13,"○",IF(AF13=AH13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG12" s="284" t="n"/>
-      <c r="AH12" s="285" t="n"/>
-      <c r="AI12" s="283">
+      <c r="AG12" s="294" t="n"/>
+      <c r="AH12" s="295" t="n"/>
+      <c r="AI12" s="293">
         <f>IF(AI13="","",IF(AI13="☂","☂",IF(AI13&gt;AK13,"○",IF(AI13=AK13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ12" s="284" t="n"/>
-      <c r="AK12" s="285" t="n"/>
-      <c r="AL12" s="286">
+      <c r="AJ12" s="294" t="n"/>
+      <c r="AK12" s="295" t="n"/>
+      <c r="AL12" s="277">
         <f>COUNTIF(E12:AK12,"○")</f>
         <v/>
       </c>
-      <c r="AM12" s="287">
+      <c r="AM12" s="278">
         <f>COUNTIF(E12:AK12,"△")</f>
         <v/>
       </c>
-      <c r="AN12" s="287">
+      <c r="AN12" s="278">
         <f>COUNTIF(E12:AK12,"×")</f>
         <v/>
       </c>
-      <c r="AO12" s="287">
+      <c r="AO12" s="279">
         <f>AL12*3+AM12*1</f>
         <v/>
       </c>
-      <c r="AP12" s="287">
+      <c r="AP12" s="278">
         <f>SUM(G13,J13,M13,P13,S13,V13,Y13,AB13,AK13)</f>
         <v/>
       </c>
-      <c r="AQ12" s="287">
+      <c r="AQ12" s="278">
         <f>SUM(E13,H13,K13,N13,Q13,T13,W13,Z13,AI13)</f>
         <v/>
       </c>
-      <c r="AR12" s="287">
+      <c r="AR12" s="278">
         <f>$AY$21-AL12-AM12-AN12</f>
         <v/>
       </c>
-      <c r="AS12" s="296">
+      <c r="AS12" s="280">
         <f>IFERROR(_xlfn.RANK.EQ(AO12,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4000,241 +4294,243 @@
       <c r="BA12" s="6" t="n"/>
     </row>
     <row r="13" ht="46.9" customHeight="1" s="257">
-      <c r="B13" s="272" t="n"/>
-      <c r="C13" s="273" t="n"/>
-      <c r="D13" s="274" t="n"/>
-      <c r="E13" s="63" t="n"/>
-      <c r="F13" s="123" t="inlineStr">
+      <c r="A13" s="271" t="n"/>
+      <c r="B13" s="281" t="n"/>
+      <c r="C13" s="282" t="n"/>
+      <c r="D13" s="283" t="n"/>
+      <c r="E13" s="296" t="n"/>
+      <c r="F13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="64" t="n"/>
-      <c r="H13" s="63" t="n"/>
-      <c r="I13" s="123" t="inlineStr">
+      <c r="G13" s="296" t="n"/>
+      <c r="H13" s="296" t="n"/>
+      <c r="I13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="63" t="n"/>
-      <c r="K13" s="63" t="n"/>
-      <c r="L13" s="123" t="inlineStr">
+      <c r="J13" s="296" t="n"/>
+      <c r="K13" s="296" t="n"/>
+      <c r="L13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M13" s="63" t="n"/>
-      <c r="N13" s="273" t="n"/>
-      <c r="O13" s="263" t="n"/>
-      <c r="P13" s="274" t="n"/>
-      <c r="Q13" s="123">
+      <c r="M13" s="296" t="n"/>
+      <c r="N13" s="282" t="n"/>
+      <c r="O13" s="270" t="n"/>
+      <c r="P13" s="283" t="n"/>
+      <c r="Q13" s="297">
         <f>IF(P15="","",P15)</f>
         <v/>
       </c>
-      <c r="R13" s="123" t="inlineStr">
+      <c r="R13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S13" s="123">
+      <c r="S13" s="297">
         <f>IF(N15="","",N15)</f>
         <v/>
       </c>
-      <c r="T13" s="123">
+      <c r="T13" s="297">
         <f>IF(P17="","",P17)</f>
         <v/>
       </c>
-      <c r="U13" s="123" t="inlineStr">
+      <c r="U13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V13" s="123">
+      <c r="V13" s="297">
         <f>IF(N17="","",N17)</f>
         <v/>
       </c>
-      <c r="W13" s="123">
+      <c r="W13" s="297">
         <f>IF(P19="","",P19)</f>
         <v/>
       </c>
-      <c r="X13" s="123" t="inlineStr">
+      <c r="X13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y13" s="123">
+      <c r="Y13" s="297">
         <f>IF(N19="","",N19)</f>
         <v/>
       </c>
-      <c r="Z13" s="123">
+      <c r="Z13" s="297">
         <f>IF(P21="","",P21)</f>
         <v/>
       </c>
-      <c r="AA13" s="123" t="inlineStr">
+      <c r="AA13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB13" s="123">
+      <c r="AB13" s="297">
         <f>IF(N21="","",N21)</f>
         <v/>
       </c>
-      <c r="AC13" s="123">
+      <c r="AC13" s="297">
         <f>IF(P23="","",P23)</f>
         <v/>
       </c>
-      <c r="AD13" s="123" t="inlineStr">
+      <c r="AD13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE13" s="123">
+      <c r="AE13" s="297">
         <f>IF(N23="","",N23)</f>
         <v/>
       </c>
-      <c r="AF13" s="123">
+      <c r="AF13" s="297">
         <f>IF(P25="","",P25)</f>
         <v/>
       </c>
-      <c r="AG13" s="123" t="inlineStr">
+      <c r="AG13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH13" s="123">
+      <c r="AH13" s="297">
         <f>IF(N25="","",N25)</f>
         <v/>
       </c>
-      <c r="AI13" s="123">
+      <c r="AI13" s="297">
         <f>IF(P27="","",P27)</f>
         <v/>
       </c>
-      <c r="AJ13" s="123" t="inlineStr">
+      <c r="AJ13" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK13" s="123">
+      <c r="AK13" s="297">
         <f>IF(N27="","",N27)</f>
         <v/>
       </c>
-      <c r="AL13" s="272" t="n"/>
-      <c r="AM13" s="276" t="n"/>
-      <c r="AN13" s="276" t="n"/>
-      <c r="AO13" s="276" t="n"/>
-      <c r="AP13" s="276" t="n"/>
-      <c r="AQ13" s="276" t="n"/>
-      <c r="AR13" s="276" t="n"/>
-      <c r="AS13" s="289" t="n"/>
-      <c r="AV13" s="276" t="n"/>
-      <c r="AW13" s="278" t="n"/>
-      <c r="AX13" s="276" t="n"/>
+      <c r="AL13" s="281" t="n"/>
+      <c r="AM13" s="286" t="n"/>
+      <c r="AN13" s="286" t="n"/>
+      <c r="AO13" s="286" t="n"/>
+      <c r="AP13" s="286" t="n"/>
+      <c r="AQ13" s="286" t="n"/>
+      <c r="AR13" s="286" t="n"/>
+      <c r="AS13" s="298" t="n"/>
+      <c r="AV13" s="286" t="n"/>
+      <c r="AW13" s="288" t="n"/>
+      <c r="AX13" s="286" t="n"/>
       <c r="AZ13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="BA13" s="6" t="n"/>
     </row>
     <row r="14" ht="46.9" customHeight="1" s="257">
-      <c r="B14" s="131" t="n">
+      <c r="A14" s="271" t="n"/>
+      <c r="B14" s="271" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="132">
+      <c r="C14" s="271">
         <f>AX14</f>
         <v/>
       </c>
-      <c r="D14" s="264" t="n"/>
-      <c r="E14" s="290">
+      <c r="D14" s="272" t="n"/>
+      <c r="E14" s="273">
         <f>IF(E15="","",IF(E15="☂","☂",IF(E15&gt;G15,"○",IF(E15=G15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F14" s="279" t="n"/>
-      <c r="G14" s="280" t="n"/>
-      <c r="H14" s="8">
+      <c r="F14" s="290" t="n"/>
+      <c r="G14" s="291" t="n"/>
+      <c r="H14" s="273">
         <f>IF(H15="","",IF(H15="☂","☂",IF(H15&gt;J15,"○",IF(H15=J15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I14" s="279" t="n"/>
-      <c r="J14" s="280" t="n"/>
-      <c r="K14" s="8">
+      <c r="I14" s="290" t="n"/>
+      <c r="J14" s="291" t="n"/>
+      <c r="K14" s="273">
         <f>IF(K15="","",IF(K15="☂","☂",IF(K15&gt;M15,"○",IF(K15=M15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L14" s="279" t="n"/>
-      <c r="M14" s="280" t="n"/>
-      <c r="N14" s="297">
+      <c r="L14" s="290" t="n"/>
+      <c r="M14" s="291" t="n"/>
+      <c r="N14" s="274">
         <f>IF(N15="","",IF(N15="☂","☂",IF(N15&gt;P15,"○",IF(N15=P15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O14" s="298" t="n"/>
-      <c r="P14" s="299" t="n"/>
-      <c r="Q14" s="291" t="n"/>
-      <c r="R14" s="282" t="n"/>
-      <c r="S14" s="262" t="n"/>
-      <c r="T14" s="292">
+      <c r="O14" s="300" t="n"/>
+      <c r="P14" s="301" t="n"/>
+      <c r="Q14" s="273" t="n"/>
+      <c r="R14" s="292" t="n"/>
+      <c r="S14" s="269" t="n"/>
+      <c r="T14" s="274">
         <f>IF(T15="","",IF(T15="☂","☂",IF(T15&gt;V15,"○",IF(T15=V15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U14" s="284" t="n"/>
-      <c r="V14" s="285" t="n"/>
-      <c r="W14" s="292">
+      <c r="U14" s="294" t="n"/>
+      <c r="V14" s="295" t="n"/>
+      <c r="W14" s="274">
         <f>IF(W15="","",IF(W15="☂","☂",IF(W15&gt;Y15,"○",IF(W15=Y15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X14" s="284" t="n"/>
-      <c r="Y14" s="285" t="n"/>
-      <c r="Z14" s="292">
+      <c r="X14" s="294" t="n"/>
+      <c r="Y14" s="295" t="n"/>
+      <c r="Z14" s="274">
         <f>IF(Z15="","",IF(Z15="☂","☂",IF(Z15&gt;AB15,"○",IF(Z15=AB15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA14" s="284" t="n"/>
-      <c r="AB14" s="285" t="n"/>
-      <c r="AC14" s="292">
+      <c r="AA14" s="294" t="n"/>
+      <c r="AB14" s="295" t="n"/>
+      <c r="AC14" s="274">
         <f>IF(AC15="","",IF(AC15="☂","☂",IF(AC15&gt;AE15,"○",IF(AC15=AE15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD14" s="284" t="n"/>
-      <c r="AE14" s="285" t="n"/>
-      <c r="AF14" s="292">
+      <c r="AD14" s="294" t="n"/>
+      <c r="AE14" s="295" t="n"/>
+      <c r="AF14" s="274">
         <f>IF(AF15="","",IF(AF15="☂","☂",IF(AF15&gt;AH15,"○",IF(AF15=AH15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG14" s="284" t="n"/>
-      <c r="AH14" s="285" t="n"/>
-      <c r="AI14" s="292">
+      <c r="AG14" s="294" t="n"/>
+      <c r="AH14" s="295" t="n"/>
+      <c r="AI14" s="274">
         <f>IF(AI15="","",IF(AI15="☂","☂",IF(AI15&gt;AK15,"○",IF(AI15=AK15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ14" s="284" t="n"/>
-      <c r="AK14" s="285" t="n"/>
-      <c r="AL14" s="293">
+      <c r="AJ14" s="294" t="n"/>
+      <c r="AK14" s="295" t="n"/>
+      <c r="AL14" s="277">
         <f>COUNTIF(E14:AK14,"○")</f>
         <v/>
       </c>
-      <c r="AM14" s="294">
+      <c r="AM14" s="278">
         <f>COUNTIF(E14:AK14,"△")</f>
         <v/>
       </c>
-      <c r="AN14" s="294">
+      <c r="AN14" s="278">
         <f>COUNTIF(E14:AK14,"×")</f>
         <v/>
       </c>
-      <c r="AO14" s="294">
+      <c r="AO14" s="279">
         <f>AL14*3+AM14*1</f>
         <v/>
       </c>
-      <c r="AP14" s="294">
+      <c r="AP14" s="278">
         <f>SUM(G15,J15,M15,P15,S15,V15,Y15,AB15,AK15)</f>
         <v/>
       </c>
-      <c r="AQ14" s="294">
+      <c r="AQ14" s="278">
         <f>SUM(E15,H15,K15,N15,Q15,T15,W15,Z15,AI15)</f>
         <v/>
       </c>
-      <c r="AR14" s="294">
+      <c r="AR14" s="278">
         <f>$AY$21-AL14-AM14-AN14</f>
         <v/>
       </c>
-      <c r="AS14" s="288">
+      <c r="AS14" s="280">
         <f>IFERROR(_xlfn.RANK.EQ(AO14,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4254,235 +4550,237 @@
       <c r="BA14" s="6" t="n"/>
     </row>
     <row r="15" ht="46.9" customHeight="1" s="257">
-      <c r="B15" s="272" t="n"/>
-      <c r="C15" s="273" t="n"/>
-      <c r="D15" s="274" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="A15" s="271" t="n"/>
+      <c r="B15" s="281" t="n"/>
+      <c r="C15" s="282" t="n"/>
+      <c r="D15" s="283" t="n"/>
+      <c r="E15" s="299" t="n"/>
+      <c r="F15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="G15" s="299" t="n"/>
+      <c r="H15" s="299" t="n"/>
+      <c r="I15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="J15" s="299" t="n"/>
+      <c r="K15" s="299" t="n"/>
+      <c r="L15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="10" t="n"/>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="M15" s="299" t="n"/>
+      <c r="N15" s="299" t="n"/>
+      <c r="O15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="273" t="n"/>
-      <c r="R15" s="263" t="n"/>
-      <c r="S15" s="274" t="n"/>
-      <c r="T15" s="8">
+      <c r="P15" s="299" t="n"/>
+      <c r="Q15" s="282" t="n"/>
+      <c r="R15" s="270" t="n"/>
+      <c r="S15" s="283" t="n"/>
+      <c r="T15" s="285">
         <f>IF(S17="","",S17)</f>
         <v/>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="U15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V15" s="8">
+      <c r="V15" s="285">
         <f>IF(Q17="","",Q17)</f>
         <v/>
       </c>
-      <c r="W15" s="8">
+      <c r="W15" s="285">
         <f>IF(S19="","",S19)</f>
         <v/>
       </c>
-      <c r="X15" s="8" t="inlineStr">
+      <c r="X15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y15" s="8">
+      <c r="Y15" s="285">
         <f>IF(Q19="","",Q19)</f>
         <v/>
       </c>
-      <c r="Z15" s="8">
+      <c r="Z15" s="285">
         <f>IF(S21="","",S21)</f>
         <v/>
       </c>
-      <c r="AA15" s="8" t="inlineStr">
+      <c r="AA15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB15" s="8">
+      <c r="AB15" s="285">
         <f>IF(Q21="","",Q21)</f>
         <v/>
       </c>
-      <c r="AC15" s="8">
+      <c r="AC15" s="285">
         <f>IF(S23="","",S23)</f>
         <v/>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
+      <c r="AD15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE15" s="8">
+      <c r="AE15" s="285">
         <f>IF(Q31="","",Q31)</f>
         <v/>
       </c>
-      <c r="AF15" s="8">
+      <c r="AF15" s="285">
         <f>IF(S25="","",S25)</f>
         <v/>
       </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AG15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH15" s="8">
+      <c r="AH15" s="285">
         <f>IF(Q25="","",Q25)</f>
         <v/>
       </c>
-      <c r="AI15" s="8">
+      <c r="AI15" s="285">
         <f>IF(S27="","",S27)</f>
         <v/>
       </c>
-      <c r="AJ15" s="8" t="inlineStr">
+      <c r="AJ15" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK15" s="8">
+      <c r="AK15" s="285">
         <f>IF(Q27="","",Q27)</f>
         <v/>
       </c>
-      <c r="AL15" s="272" t="n"/>
-      <c r="AM15" s="276" t="n"/>
-      <c r="AN15" s="276" t="n"/>
-      <c r="AO15" s="276" t="n"/>
-      <c r="AP15" s="276" t="n"/>
-      <c r="AQ15" s="276" t="n"/>
-      <c r="AR15" s="276" t="n"/>
-      <c r="AS15" s="289" t="n"/>
-      <c r="AV15" s="276" t="n"/>
-      <c r="AW15" s="278" t="n"/>
-      <c r="AX15" s="276" t="n"/>
+      <c r="AL15" s="281" t="n"/>
+      <c r="AM15" s="286" t="n"/>
+      <c r="AN15" s="286" t="n"/>
+      <c r="AO15" s="286" t="n"/>
+      <c r="AP15" s="286" t="n"/>
+      <c r="AQ15" s="286" t="n"/>
+      <c r="AR15" s="286" t="n"/>
+      <c r="AS15" s="298" t="n"/>
+      <c r="AV15" s="286" t="n"/>
+      <c r="AW15" s="288" t="n"/>
+      <c r="AX15" s="286" t="n"/>
       <c r="AZ15" s="5" t="n">
         <v>10</v>
       </c>
       <c r="BA15" s="6" t="n"/>
     </row>
     <row r="16" ht="46.9" customHeight="1" s="257">
-      <c r="B16" s="117" t="n">
+      <c r="A16" s="271" t="n"/>
+      <c r="B16" s="271" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="118">
+      <c r="C16" s="271">
         <f>AX16</f>
         <v/>
       </c>
-      <c r="D16" s="264" t="n"/>
-      <c r="E16" s="295">
+      <c r="D16" s="272" t="n"/>
+      <c r="E16" s="289">
         <f>IF(E17="","",IF(E17="☂","☂",IF(E17&gt;G17,"○",IF(E17=G17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F16" s="279" t="n"/>
-      <c r="G16" s="280" t="n"/>
-      <c r="H16" s="123">
+      <c r="F16" s="290" t="n"/>
+      <c r="G16" s="291" t="n"/>
+      <c r="H16" s="289">
         <f>IF(H17="","",IF(H17="☂","☂",IF(H17&gt;J17,"○",IF(H17=J17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I16" s="279" t="n"/>
-      <c r="J16" s="280" t="n"/>
-      <c r="K16" s="123">
+      <c r="I16" s="290" t="n"/>
+      <c r="J16" s="291" t="n"/>
+      <c r="K16" s="289">
         <f>IF(K17="","",IF(K17="☂","☂",IF(K17&gt;M17,"○",IF(K17=M17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L16" s="279" t="n"/>
-      <c r="M16" s="280" t="n"/>
-      <c r="N16" s="300">
+      <c r="L16" s="290" t="n"/>
+      <c r="M16" s="291" t="n"/>
+      <c r="N16" s="293">
         <f>IF(N17="","",IF(N17="☂","☂",IF(N17&gt;P17,"○",IF(N17=P17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O16" s="298" t="n"/>
-      <c r="P16" s="299" t="n"/>
-      <c r="Q16" s="300">
+      <c r="O16" s="300" t="n"/>
+      <c r="P16" s="301" t="n"/>
+      <c r="Q16" s="293">
         <f>IF(Q17="","",IF(Q17="☂","☂",IF(Q17&gt;S17,"○",IF(Q17=S17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R16" s="298" t="n"/>
-      <c r="S16" s="299" t="n"/>
-      <c r="T16" s="281" t="n"/>
-      <c r="U16" s="282" t="n"/>
-      <c r="V16" s="262" t="n"/>
-      <c r="W16" s="283">
+      <c r="R16" s="300" t="n"/>
+      <c r="S16" s="301" t="n"/>
+      <c r="T16" s="289" t="n"/>
+      <c r="U16" s="292" t="n"/>
+      <c r="V16" s="269" t="n"/>
+      <c r="W16" s="293">
         <f>IF(W17="","",IF(W17="☂","☂",IF(W17&gt;Y17,"○",IF(W17=Y17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X16" s="284" t="n"/>
-      <c r="Y16" s="285" t="n"/>
-      <c r="Z16" s="283">
+      <c r="X16" s="294" t="n"/>
+      <c r="Y16" s="295" t="n"/>
+      <c r="Z16" s="293">
         <f>IF(Z17="","",IF(Z17="☂","☂",IF(Z17&gt;AB17,"○",IF(Z17=AB17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA16" s="284" t="n"/>
-      <c r="AB16" s="285" t="n"/>
-      <c r="AC16" s="283">
+      <c r="AA16" s="294" t="n"/>
+      <c r="AB16" s="295" t="n"/>
+      <c r="AC16" s="293">
         <f>IF(AC17="","",IF(AC17="☂","☂",IF(AC17&gt;AE17,"○",IF(AC17=AE17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD16" s="284" t="n"/>
-      <c r="AE16" s="285" t="n"/>
-      <c r="AF16" s="283">
+      <c r="AD16" s="294" t="n"/>
+      <c r="AE16" s="295" t="n"/>
+      <c r="AF16" s="293">
         <f>IF(AF17="","",IF(AF17="☂","☂",IF(AF17&gt;AH17,"○",IF(AF17=AH17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG16" s="284" t="n"/>
-      <c r="AH16" s="285" t="n"/>
-      <c r="AI16" s="283">
+      <c r="AG16" s="294" t="n"/>
+      <c r="AH16" s="295" t="n"/>
+      <c r="AI16" s="293">
         <f>IF(AI17="","",IF(AI17="☂","☂",IF(AI17&gt;AK17,"○",IF(AI17=AK17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ16" s="284" t="n"/>
-      <c r="AK16" s="285" t="n"/>
-      <c r="AL16" s="286">
+      <c r="AJ16" s="294" t="n"/>
+      <c r="AK16" s="295" t="n"/>
+      <c r="AL16" s="277">
         <f>COUNTIF(E16:AK16,"○")</f>
         <v/>
       </c>
-      <c r="AM16" s="287">
+      <c r="AM16" s="278">
         <f>COUNTIF(E16:AK16,"△")</f>
         <v/>
       </c>
-      <c r="AN16" s="287">
+      <c r="AN16" s="278">
         <f>COUNTIF(E16:AK16,"×")</f>
         <v/>
       </c>
-      <c r="AO16" s="287">
+      <c r="AO16" s="279">
         <f>AL16*3+AM16*1</f>
         <v/>
       </c>
-      <c r="AP16" s="287">
+      <c r="AP16" s="278">
         <f>SUM(G17,J17,M17,P17,S17,V17,Y17,AB17,AK17)</f>
         <v/>
       </c>
-      <c r="AQ16" s="287">
+      <c r="AQ16" s="278">
         <f>SUM(E17,H17,K17,N17,Q17,T17,W17,Z17,AI17)</f>
         <v/>
       </c>
-      <c r="AR16" s="287">
+      <c r="AR16" s="278">
         <f>$AY$21-AL16-AM16-AN16</f>
         <v/>
       </c>
-      <c r="AS16" s="301">
+      <c r="AS16" s="280">
         <f>IFERROR(_xlfn.RANK.EQ(AO16,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4502,229 +4800,231 @@
       <c r="BA16" s="6" t="n"/>
     </row>
     <row r="17" ht="46.9" customHeight="1" s="257">
-      <c r="B17" s="272" t="n"/>
-      <c r="C17" s="273" t="n"/>
-      <c r="D17" s="274" t="n"/>
-      <c r="E17" s="63" t="n"/>
-      <c r="F17" s="123" t="inlineStr">
+      <c r="A17" s="271" t="n"/>
+      <c r="B17" s="281" t="n"/>
+      <c r="C17" s="282" t="n"/>
+      <c r="D17" s="283" t="n"/>
+      <c r="E17" s="296" t="n"/>
+      <c r="F17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="64" t="n"/>
-      <c r="H17" s="63" t="n"/>
-      <c r="I17" s="123" t="inlineStr">
+      <c r="G17" s="296" t="n"/>
+      <c r="H17" s="296" t="n"/>
+      <c r="I17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="63" t="n"/>
-      <c r="K17" s="63" t="n"/>
-      <c r="L17" s="123" t="inlineStr">
+      <c r="J17" s="296" t="n"/>
+      <c r="K17" s="296" t="n"/>
+      <c r="L17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M17" s="63" t="n"/>
-      <c r="N17" s="63" t="n"/>
-      <c r="O17" s="123" t="inlineStr">
+      <c r="M17" s="296" t="n"/>
+      <c r="N17" s="296" t="n"/>
+      <c r="O17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="63" t="n"/>
-      <c r="Q17" s="63" t="n"/>
-      <c r="R17" s="123" t="inlineStr">
+      <c r="P17" s="296" t="n"/>
+      <c r="Q17" s="296" t="n"/>
+      <c r="R17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S17" s="63" t="n"/>
-      <c r="T17" s="273" t="n"/>
-      <c r="U17" s="263" t="n"/>
-      <c r="V17" s="274" t="n"/>
-      <c r="W17" s="123">
+      <c r="S17" s="296" t="n"/>
+      <c r="T17" s="282" t="n"/>
+      <c r="U17" s="270" t="n"/>
+      <c r="V17" s="283" t="n"/>
+      <c r="W17" s="297">
         <f>IF(V19="","",V19)</f>
         <v/>
       </c>
-      <c r="X17" s="123" t="inlineStr">
+      <c r="X17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y17" s="123">
+      <c r="Y17" s="297">
         <f>IF(T19="","",T19)</f>
         <v/>
       </c>
-      <c r="Z17" s="123">
+      <c r="Z17" s="297">
         <f>IF(V21="","",V21)</f>
         <v/>
       </c>
-      <c r="AA17" s="123" t="inlineStr">
+      <c r="AA17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB17" s="123">
+      <c r="AB17" s="297">
         <f>IF(T21="","",T21)</f>
         <v/>
       </c>
-      <c r="AC17" s="123">
+      <c r="AC17" s="297">
         <f>IF(V23="","",V23)</f>
         <v/>
       </c>
-      <c r="AD17" s="123" t="inlineStr">
+      <c r="AD17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE17" s="123">
+      <c r="AE17" s="297">
         <f>IF(T23="","",T23)</f>
         <v/>
       </c>
-      <c r="AF17" s="123">
+      <c r="AF17" s="297">
         <f>IF(V25="","",V25)</f>
         <v/>
       </c>
-      <c r="AG17" s="123" t="inlineStr">
+      <c r="AG17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH17" s="123">
+      <c r="AH17" s="297">
         <f>IF(T25="","",T25)</f>
         <v/>
       </c>
-      <c r="AI17" s="123">
+      <c r="AI17" s="297">
         <f>IF(V27="","",V27)</f>
         <v/>
       </c>
-      <c r="AJ17" s="123" t="inlineStr">
+      <c r="AJ17" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK17" s="123">
+      <c r="AK17" s="297">
         <f>IF(T27="","",T27)</f>
         <v/>
       </c>
-      <c r="AL17" s="272" t="n"/>
-      <c r="AM17" s="276" t="n"/>
-      <c r="AN17" s="276" t="n"/>
-      <c r="AO17" s="276" t="n"/>
-      <c r="AP17" s="276" t="n"/>
-      <c r="AQ17" s="276" t="n"/>
-      <c r="AR17" s="276" t="n"/>
-      <c r="AS17" s="289" t="n"/>
-      <c r="AV17" s="276" t="n"/>
-      <c r="AW17" s="278" t="n"/>
-      <c r="AX17" s="276" t="n"/>
+      <c r="AL17" s="281" t="n"/>
+      <c r="AM17" s="286" t="n"/>
+      <c r="AN17" s="286" t="n"/>
+      <c r="AO17" s="286" t="n"/>
+      <c r="AP17" s="286" t="n"/>
+      <c r="AQ17" s="286" t="n"/>
+      <c r="AR17" s="286" t="n"/>
+      <c r="AS17" s="298" t="n"/>
+      <c r="AV17" s="286" t="n"/>
+      <c r="AW17" s="288" t="n"/>
+      <c r="AX17" s="286" t="n"/>
       <c r="AZ17" s="5" t="n">
         <v>12</v>
       </c>
       <c r="BA17" s="6" t="n"/>
     </row>
     <row r="18" ht="46.9" customHeight="1" s="257">
-      <c r="B18" s="131" t="n">
+      <c r="A18" s="302" t="n"/>
+      <c r="B18" s="303" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="132">
+      <c r="C18" s="304">
         <f>AX18</f>
         <v/>
       </c>
-      <c r="D18" s="264" t="n"/>
-      <c r="E18" s="290">
+      <c r="D18" s="272" t="n"/>
+      <c r="E18" s="303">
         <f>IF(E19="","",IF(E19="☂","☂",IF(E19&gt;G19,"○",IF(E19=G19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F18" s="279" t="n"/>
-      <c r="G18" s="280" t="n"/>
-      <c r="H18" s="8">
+      <c r="F18" s="290" t="n"/>
+      <c r="G18" s="291" t="n"/>
+      <c r="H18" s="305">
         <f>IF(H19="","",IF(H19="☂","☂",IF(H19&gt;J19,"○",IF(H19=J19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I18" s="279" t="n"/>
-      <c r="J18" s="280" t="n"/>
-      <c r="K18" s="8">
+      <c r="I18" s="290" t="n"/>
+      <c r="J18" s="291" t="n"/>
+      <c r="K18" s="305">
         <f>IF(K19="","",IF(K19="☂","☂",IF(K19&gt;M19,"○",IF(K19=M19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L18" s="279" t="n"/>
-      <c r="M18" s="280" t="n"/>
-      <c r="N18" s="297">
+      <c r="L18" s="290" t="n"/>
+      <c r="M18" s="291" t="n"/>
+      <c r="N18" s="306">
         <f>IF(N19="","",IF(N19="☂","☂",IF(N19&gt;P19,"○",IF(N19=P19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O18" s="298" t="n"/>
-      <c r="P18" s="299" t="n"/>
-      <c r="Q18" s="297">
+      <c r="O18" s="300" t="n"/>
+      <c r="P18" s="301" t="n"/>
+      <c r="Q18" s="306">
         <f>IF(Q19="","",IF(Q19="☂","☂",IF(Q19&gt;S19,"○",IF(Q19=S19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R18" s="298" t="n"/>
-      <c r="S18" s="299" t="n"/>
-      <c r="T18" s="297">
+      <c r="R18" s="300" t="n"/>
+      <c r="S18" s="301" t="n"/>
+      <c r="T18" s="306">
         <f>IF(T19="","",IF(T19="☂","☂",IF(T19&gt;V19,"○",IF(T19=V19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U18" s="298" t="n"/>
-      <c r="V18" s="299" t="n"/>
-      <c r="W18" s="291" t="n"/>
-      <c r="X18" s="282" t="n"/>
-      <c r="Y18" s="262" t="n"/>
-      <c r="Z18" s="292">
+      <c r="U18" s="300" t="n"/>
+      <c r="V18" s="301" t="n"/>
+      <c r="W18" s="307" t="n"/>
+      <c r="X18" s="292" t="n"/>
+      <c r="Y18" s="269" t="n"/>
+      <c r="Z18" s="308">
         <f>IF(Z19="","",IF(Z19="☂","☂",IF(Z19&gt;AB19,"○",IF(Z19=AB19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA18" s="284" t="n"/>
-      <c r="AB18" s="285" t="n"/>
-      <c r="AC18" s="292">
+      <c r="AA18" s="294" t="n"/>
+      <c r="AB18" s="295" t="n"/>
+      <c r="AC18" s="308">
         <f>IF(AC19="","",IF(AC19="☂","☂",IF(AC19&gt;AE19,"○",IF(AC19=AE19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD18" s="284" t="n"/>
-      <c r="AE18" s="285" t="n"/>
-      <c r="AF18" s="292">
+      <c r="AD18" s="294" t="n"/>
+      <c r="AE18" s="295" t="n"/>
+      <c r="AF18" s="308">
         <f>IF(AF19="","",IF(AF19="☂","☂",IF(AF19&gt;AH19,"○",IF(AF19=AH19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG18" s="284" t="n"/>
-      <c r="AH18" s="285" t="n"/>
-      <c r="AI18" s="292">
+      <c r="AG18" s="294" t="n"/>
+      <c r="AH18" s="295" t="n"/>
+      <c r="AI18" s="308">
         <f>IF(AI19="","",IF(AI19="☂","☂",IF(AI19&gt;AK19,"○",IF(AI19=AK19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ18" s="284" t="n"/>
-      <c r="AK18" s="285" t="n"/>
-      <c r="AL18" s="293">
+      <c r="AJ18" s="294" t="n"/>
+      <c r="AK18" s="295" t="n"/>
+      <c r="AL18" s="309">
         <f>COUNTIF(E18:AK18,"○")</f>
         <v/>
       </c>
-      <c r="AM18" s="294">
+      <c r="AM18" s="310">
         <f>COUNTIF(E18:AK18,"△")</f>
         <v/>
       </c>
-      <c r="AN18" s="294">
+      <c r="AN18" s="310">
         <f>COUNTIF(E18:AK18,"×")</f>
         <v/>
       </c>
-      <c r="AO18" s="294">
+      <c r="AO18" s="310">
         <f>AL18*3+AM18*1</f>
         <v/>
       </c>
-      <c r="AP18" s="294">
+      <c r="AP18" s="310">
         <f>SUM(G19,J19,M19,P19,S19,V19,Y19,AB19,AK19)</f>
         <v/>
       </c>
-      <c r="AQ18" s="294">
+      <c r="AQ18" s="310">
         <f>SUM(E19,H19,K19,N19,Q19,T19,W19,Z19,AI19)</f>
         <v/>
       </c>
-      <c r="AR18" s="294">
+      <c r="AR18" s="310">
         <f>$AY$21-AL18-AM18-AN18</f>
         <v/>
       </c>
-      <c r="AS18" s="288">
+      <c r="AS18" s="311">
         <f>IFERROR(_xlfn.RANK.EQ(AO18,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4742,223 +5042,225 @@
       <c r="BA18" s="6" t="n"/>
     </row>
     <row r="19" ht="46.9" customHeight="1" s="257">
-      <c r="B19" s="272" t="n"/>
-      <c r="C19" s="273" t="n"/>
-      <c r="D19" s="274" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="A19" s="302" t="n"/>
+      <c r="B19" s="281" t="n"/>
+      <c r="C19" s="282" t="n"/>
+      <c r="D19" s="283" t="n"/>
+      <c r="E19" s="312" t="n"/>
+      <c r="F19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="G19" s="312" t="n"/>
+      <c r="H19" s="312" t="n"/>
+      <c r="I19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="J19" s="312" t="n"/>
+      <c r="K19" s="312" t="n"/>
+      <c r="L19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="M19" s="312" t="n"/>
+      <c r="N19" s="312" t="n"/>
+      <c r="O19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="P19" s="312" t="n"/>
+      <c r="Q19" s="312" t="n"/>
+      <c r="R19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="S19" s="312" t="n"/>
+      <c r="T19" s="312" t="n"/>
+      <c r="U19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V19" s="10" t="n"/>
-      <c r="W19" s="273" t="n"/>
-      <c r="X19" s="263" t="n"/>
-      <c r="Y19" s="274" t="n"/>
-      <c r="Z19" s="8">
+      <c r="V19" s="312" t="n"/>
+      <c r="W19" s="282" t="n"/>
+      <c r="X19" s="270" t="n"/>
+      <c r="Y19" s="283" t="n"/>
+      <c r="Z19" s="305">
         <f>IF(Y21="","",Y21)</f>
         <v/>
       </c>
-      <c r="AA19" s="8" t="inlineStr">
+      <c r="AA19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB19" s="8">
+      <c r="AB19" s="305">
         <f>IF(W21="","",W21)</f>
         <v/>
       </c>
-      <c r="AC19" s="8">
+      <c r="AC19" s="305">
         <f>IF(Y23="","",Y23)</f>
         <v/>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
+      <c r="AD19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE19" s="8">
+      <c r="AE19" s="305">
         <f>IF(W23="","",W23)</f>
         <v/>
       </c>
-      <c r="AF19" s="8">
+      <c r="AF19" s="305">
         <f>IF(Y25="","",Y25)</f>
         <v/>
       </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AG19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH19" s="8">
+      <c r="AH19" s="305">
         <f>IF(W25="","",W25)</f>
         <v/>
       </c>
-      <c r="AI19" s="8">
+      <c r="AI19" s="305">
         <f>IF(Y27="","",Y27)</f>
         <v/>
       </c>
-      <c r="AJ19" s="8" t="inlineStr">
+      <c r="AJ19" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK19" s="8">
+      <c r="AK19" s="305">
         <f>IF(W27="","",W27)</f>
         <v/>
       </c>
-      <c r="AL19" s="272" t="n"/>
-      <c r="AM19" s="276" t="n"/>
-      <c r="AN19" s="276" t="n"/>
-      <c r="AO19" s="276" t="n"/>
-      <c r="AP19" s="276" t="n"/>
-      <c r="AQ19" s="276" t="n"/>
-      <c r="AR19" s="276" t="n"/>
-      <c r="AS19" s="289" t="n"/>
-      <c r="AV19" s="276" t="n"/>
-      <c r="AW19" s="278" t="n"/>
-      <c r="AX19" s="276" t="n"/>
+      <c r="AL19" s="281" t="n"/>
+      <c r="AM19" s="286" t="n"/>
+      <c r="AN19" s="286" t="n"/>
+      <c r="AO19" s="286" t="n"/>
+      <c r="AP19" s="286" t="n"/>
+      <c r="AQ19" s="286" t="n"/>
+      <c r="AR19" s="286" t="n"/>
+      <c r="AS19" s="298" t="n"/>
+      <c r="AV19" s="286" t="n"/>
+      <c r="AW19" s="288" t="n"/>
+      <c r="AX19" s="286" t="n"/>
       <c r="AZ19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="BA19" s="6" t="n"/>
     </row>
     <row r="20" ht="46.9" customHeight="1" s="257">
-      <c r="B20" s="179" t="n">
+      <c r="A20" s="302" t="n"/>
+      <c r="B20" s="313" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="118">
+      <c r="C20" s="304">
         <f>AX20</f>
         <v/>
       </c>
-      <c r="D20" s="264" t="n"/>
-      <c r="E20" s="122">
+      <c r="D20" s="272" t="n"/>
+      <c r="E20" s="314">
         <f>IF(E21="","",IF(E21="☂","☂",IF(E21&gt;G21,"○",IF(E21=G21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F20" s="279" t="n"/>
-      <c r="G20" s="280" t="n"/>
-      <c r="H20" s="123">
+      <c r="F20" s="290" t="n"/>
+      <c r="G20" s="291" t="n"/>
+      <c r="H20" s="305">
         <f>IF(H21="","",IF(H21="☂","☂",IF(H21&gt;J21,"○",IF(H21=J21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I20" s="279" t="n"/>
-      <c r="J20" s="280" t="n"/>
-      <c r="K20" s="123">
+      <c r="I20" s="290" t="n"/>
+      <c r="J20" s="291" t="n"/>
+      <c r="K20" s="305">
         <f>IF(K21="","",IF(K21="☂","☂",IF(K21&gt;M21,"○",IF(K21=M21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L20" s="279" t="n"/>
-      <c r="M20" s="280" t="n"/>
-      <c r="N20" s="300">
+      <c r="L20" s="290" t="n"/>
+      <c r="M20" s="291" t="n"/>
+      <c r="N20" s="306">
         <f>IF(N21="","",IF(N21="☂","☂",IF(N21&gt;P21,"○",IF(N21=P21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O20" s="298" t="n"/>
-      <c r="P20" s="299" t="n"/>
-      <c r="Q20" s="300">
+      <c r="O20" s="300" t="n"/>
+      <c r="P20" s="301" t="n"/>
+      <c r="Q20" s="306">
         <f>IF(Q21="","",IF(Q21="☂","☂",IF(Q21&gt;S21,"○",IF(Q21=S21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R20" s="298" t="n"/>
-      <c r="S20" s="299" t="n"/>
-      <c r="T20" s="300">
+      <c r="R20" s="300" t="n"/>
+      <c r="S20" s="301" t="n"/>
+      <c r="T20" s="306">
         <f>IF(T21="","",IF(T21="☂","☂",IF(T21&gt;V21,"○",IF(T21=V21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U20" s="298" t="n"/>
-      <c r="V20" s="299" t="n"/>
-      <c r="W20" s="300">
+      <c r="U20" s="300" t="n"/>
+      <c r="V20" s="301" t="n"/>
+      <c r="W20" s="306">
         <f>IF(W21="","",IF(W21="☂","☂",IF(W21&gt;Y21,"○",IF(W21=Y21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X20" s="298" t="n"/>
-      <c r="Y20" s="299" t="n"/>
-      <c r="Z20" s="281" t="n"/>
-      <c r="AA20" s="282" t="n"/>
-      <c r="AB20" s="262" t="n"/>
-      <c r="AC20" s="283">
+      <c r="X20" s="300" t="n"/>
+      <c r="Y20" s="301" t="n"/>
+      <c r="Z20" s="307" t="n"/>
+      <c r="AA20" s="292" t="n"/>
+      <c r="AB20" s="269" t="n"/>
+      <c r="AC20" s="308">
         <f>IF(AC21="","",IF(AC21="☂","☂",IF(AC21&gt;AE21,"○",IF(AC21=AE21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD20" s="284" t="n"/>
-      <c r="AE20" s="285" t="n"/>
-      <c r="AF20" s="283">
+      <c r="AD20" s="294" t="n"/>
+      <c r="AE20" s="295" t="n"/>
+      <c r="AF20" s="308">
         <f>IF(AF21="","",IF(AF21="☂","☂",IF(AF21&gt;AH21,"○",IF(AF21=AH21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG20" s="284" t="n"/>
-      <c r="AH20" s="285" t="n"/>
-      <c r="AI20" s="283">
+      <c r="AG20" s="294" t="n"/>
+      <c r="AH20" s="295" t="n"/>
+      <c r="AI20" s="308">
         <f>IF(AI21="","",IF(AI21="☂","☂",IF(AI21&gt;AK21,"○",IF(AI21=AK21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ20" s="284" t="n"/>
-      <c r="AK20" s="285" t="n"/>
-      <c r="AL20" s="286">
+      <c r="AJ20" s="294" t="n"/>
+      <c r="AK20" s="295" t="n"/>
+      <c r="AL20" s="309">
         <f>COUNTIF(E20:AK20,"○")</f>
         <v/>
       </c>
-      <c r="AM20" s="287">
+      <c r="AM20" s="310">
         <f>COUNTIF(E20:AK20,"△")</f>
         <v/>
       </c>
-      <c r="AN20" s="287">
+      <c r="AN20" s="310">
         <f>COUNTIF(E20:AK20,"×")</f>
         <v/>
       </c>
-      <c r="AO20" s="287">
+      <c r="AO20" s="310">
         <f>AL20*3+AM20*1</f>
         <v/>
       </c>
-      <c r="AP20" s="287">
+      <c r="AP20" s="310">
         <f>SUM(G21,J21,M21,P21,S21,V21,Y21,AB21,AK21)</f>
         <v/>
       </c>
-      <c r="AQ20" s="287">
+      <c r="AQ20" s="310">
         <f>SUM(E21,H21,K21,N21,Q21,T21,W21,Z21,AI21)</f>
         <v/>
       </c>
-      <c r="AR20" s="287">
+      <c r="AR20" s="310">
         <f>$AY$21-AL20-AM20-AN20</f>
         <v/>
       </c>
-      <c r="AS20" s="288">
+      <c r="AS20" s="311">
         <f>IFERROR(_xlfn.RANK.EQ(AO20,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4976,217 +5278,219 @@
       <c r="BA20" s="6" t="n"/>
     </row>
     <row r="21" ht="46.9" customHeight="1" s="257">
-      <c r="B21" s="302" t="n"/>
-      <c r="C21" s="273" t="n"/>
-      <c r="D21" s="274" t="n"/>
-      <c r="E21" s="62" t="n"/>
-      <c r="F21" s="123" t="inlineStr">
+      <c r="A21" s="302" t="n"/>
+      <c r="B21" s="315" t="n"/>
+      <c r="C21" s="282" t="n"/>
+      <c r="D21" s="283" t="n"/>
+      <c r="E21" s="316" t="n"/>
+      <c r="F21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="63" t="n"/>
-      <c r="H21" s="63" t="n"/>
-      <c r="I21" s="123" t="inlineStr">
+      <c r="G21" s="312" t="n"/>
+      <c r="H21" s="312" t="n"/>
+      <c r="I21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J21" s="63" t="n"/>
-      <c r="K21" s="63" t="n"/>
-      <c r="L21" s="123" t="inlineStr">
+      <c r="J21" s="312" t="n"/>
+      <c r="K21" s="312" t="n"/>
+      <c r="L21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="63" t="n"/>
-      <c r="N21" s="63" t="n"/>
-      <c r="O21" s="123" t="inlineStr">
+      <c r="M21" s="312" t="n"/>
+      <c r="N21" s="312" t="n"/>
+      <c r="O21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="63" t="n"/>
-      <c r="Q21" s="63" t="n"/>
-      <c r="R21" s="123" t="inlineStr">
+      <c r="P21" s="312" t="n"/>
+      <c r="Q21" s="312" t="n"/>
+      <c r="R21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S21" s="63" t="n"/>
-      <c r="T21" s="63" t="n"/>
-      <c r="U21" s="123" t="inlineStr">
+      <c r="S21" s="312" t="n"/>
+      <c r="T21" s="312" t="n"/>
+      <c r="U21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V21" s="63" t="n"/>
-      <c r="W21" s="63" t="n"/>
-      <c r="X21" s="123" t="inlineStr">
+      <c r="V21" s="312" t="n"/>
+      <c r="W21" s="312" t="n"/>
+      <c r="X21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y21" s="63" t="n"/>
-      <c r="Z21" s="273" t="n"/>
-      <c r="AA21" s="263" t="n"/>
-      <c r="AB21" s="274" t="n"/>
-      <c r="AC21" s="123">
+      <c r="Y21" s="312" t="n"/>
+      <c r="Z21" s="282" t="n"/>
+      <c r="AA21" s="270" t="n"/>
+      <c r="AB21" s="283" t="n"/>
+      <c r="AC21" s="305">
         <f>IF(AB23="","",AB23)</f>
         <v/>
       </c>
-      <c r="AD21" s="123" t="inlineStr">
+      <c r="AD21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE21" s="123">
+      <c r="AE21" s="305">
         <f>IF(Z23="","",Z23)</f>
         <v/>
       </c>
-      <c r="AF21" s="123">
+      <c r="AF21" s="305">
         <f>IF(AB25="","",AB25)</f>
         <v/>
       </c>
-      <c r="AG21" s="123" t="inlineStr">
+      <c r="AG21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH21" s="123">
+      <c r="AH21" s="305">
         <f>IF(Z25="","",Z25)</f>
         <v/>
       </c>
-      <c r="AI21" s="123">
+      <c r="AI21" s="305">
         <f>IF(AB27="","",AB27)</f>
         <v/>
       </c>
-      <c r="AJ21" s="123" t="inlineStr">
+      <c r="AJ21" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK21" s="123">
+      <c r="AK21" s="305">
         <f>IF(Z27="","",Z27)</f>
         <v/>
       </c>
-      <c r="AL21" s="272" t="n"/>
-      <c r="AM21" s="276" t="n"/>
-      <c r="AN21" s="276" t="n"/>
-      <c r="AO21" s="276" t="n"/>
-      <c r="AP21" s="276" t="n"/>
-      <c r="AQ21" s="276" t="n"/>
-      <c r="AR21" s="276" t="n"/>
-      <c r="AS21" s="289" t="n"/>
-      <c r="AV21" s="276" t="n"/>
-      <c r="AW21" s="278" t="n"/>
-      <c r="AX21" s="276" t="n"/>
+      <c r="AL21" s="281" t="n"/>
+      <c r="AM21" s="286" t="n"/>
+      <c r="AN21" s="286" t="n"/>
+      <c r="AO21" s="286" t="n"/>
+      <c r="AP21" s="286" t="n"/>
+      <c r="AQ21" s="286" t="n"/>
+      <c r="AR21" s="286" t="n"/>
+      <c r="AS21" s="298" t="n"/>
+      <c r="AV21" s="286" t="n"/>
+      <c r="AW21" s="288" t="n"/>
+      <c r="AX21" s="286" t="n"/>
       <c r="AY21" s="1">
         <f>COUNTA(AW6:AW21)</f>
         <v/>
       </c>
     </row>
     <row r="22" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="B22" s="131" t="n">
+      <c r="A22" s="302" t="n"/>
+      <c r="B22" s="303" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="132">
+      <c r="C22" s="304">
         <f>AX22</f>
         <v/>
       </c>
-      <c r="D22" s="264" t="n"/>
-      <c r="E22" s="290">
+      <c r="D22" s="272" t="n"/>
+      <c r="E22" s="303">
         <f>IF(E23="","",IF(E23="☂","☂",IF(E23&gt;G23,"○",IF(E23=G23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F22" s="279" t="n"/>
-      <c r="G22" s="280" t="n"/>
-      <c r="H22" s="8">
+      <c r="F22" s="290" t="n"/>
+      <c r="G22" s="291" t="n"/>
+      <c r="H22" s="305">
         <f>IF(H23="","",IF(H23="☂","☂",IF(H23&gt;J23,"○",IF(H23=J23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I22" s="279" t="n"/>
-      <c r="J22" s="280" t="n"/>
-      <c r="K22" s="8">
+      <c r="I22" s="290" t="n"/>
+      <c r="J22" s="291" t="n"/>
+      <c r="K22" s="305">
         <f>IF(K23="","",IF(K23="☂","☂",IF(K23&gt;M23,"○",IF(K23=M23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L22" s="279" t="n"/>
-      <c r="M22" s="280" t="n"/>
-      <c r="N22" s="297">
+      <c r="L22" s="290" t="n"/>
+      <c r="M22" s="291" t="n"/>
+      <c r="N22" s="306">
         <f>IF(N23="","",IF(N23="☂","☂",IF(N23&gt;P23,"○",IF(N23=P23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O22" s="298" t="n"/>
-      <c r="P22" s="299" t="n"/>
-      <c r="Q22" s="297">
+      <c r="O22" s="300" t="n"/>
+      <c r="P22" s="301" t="n"/>
+      <c r="Q22" s="306">
         <f>IF(Q23="","",IF(Q23="☂","☂",IF(Q23&gt;S23,"○",IF(Q23=S23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R22" s="298" t="n"/>
-      <c r="S22" s="299" t="n"/>
-      <c r="T22" s="297">
+      <c r="R22" s="300" t="n"/>
+      <c r="S22" s="301" t="n"/>
+      <c r="T22" s="306">
         <f>IF(T23="","",IF(T23="☂","☂",IF(T23&gt;V23,"○",IF(T23=V23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U22" s="298" t="n"/>
-      <c r="V22" s="299" t="n"/>
-      <c r="W22" s="297">
+      <c r="U22" s="300" t="n"/>
+      <c r="V22" s="301" t="n"/>
+      <c r="W22" s="306">
         <f>IF(W23="","",IF(W23="☂","☂",IF(W23&gt;Y23,"○",IF(W23=Y23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X22" s="298" t="n"/>
-      <c r="Y22" s="299" t="n"/>
-      <c r="Z22" s="297">
+      <c r="X22" s="300" t="n"/>
+      <c r="Y22" s="301" t="n"/>
+      <c r="Z22" s="306">
         <f>IF(Z23="","",IF(Z23="☂","☂",IF(Z23&gt;AB23,"○",IF(Z23=AB23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA22" s="298" t="n"/>
-      <c r="AB22" s="299" t="n"/>
-      <c r="AC22" s="303" t="n"/>
-      <c r="AD22" s="304" t="n"/>
-      <c r="AE22" s="305" t="n"/>
-      <c r="AF22" s="297">
+      <c r="AA22" s="300" t="n"/>
+      <c r="AB22" s="301" t="n"/>
+      <c r="AC22" s="317" t="n"/>
+      <c r="AD22" s="318" t="n"/>
+      <c r="AE22" s="319" t="n"/>
+      <c r="AF22" s="306">
         <f>IF(AF23="","",IF(AF23="☂","☂",IF(AF23&gt;AH23,"○",IF(AF23=AH23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG22" s="298" t="n"/>
-      <c r="AH22" s="299" t="n"/>
-      <c r="AI22" s="306">
+      <c r="AG22" s="300" t="n"/>
+      <c r="AH22" s="301" t="n"/>
+      <c r="AI22" s="308">
         <f>IF(AI23="","",IF(AI23="☂","☂",IF(AI23&gt;AK23,"○",IF(AI23=AK23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ22" s="284" t="n"/>
-      <c r="AK22" s="285" t="n"/>
-      <c r="AL22" s="293">
+      <c r="AJ22" s="294" t="n"/>
+      <c r="AK22" s="295" t="n"/>
+      <c r="AL22" s="309">
         <f>COUNTIF(E22:AK22,"○")</f>
         <v/>
       </c>
-      <c r="AM22" s="294">
+      <c r="AM22" s="310">
         <f>COUNTIF(E22:AK22,"△")</f>
         <v/>
       </c>
-      <c r="AN22" s="294">
+      <c r="AN22" s="310">
         <f>COUNTIF(E22:AK22,"×")</f>
         <v/>
       </c>
-      <c r="AO22" s="294">
+      <c r="AO22" s="310">
         <f>AL22*3+AM22*1</f>
         <v/>
       </c>
-      <c r="AP22" s="294">
+      <c r="AP22" s="310">
         <f>SUM(G23,M23,P23,S23,V23,Y23,AB23,AK23)</f>
         <v/>
       </c>
-      <c r="AQ22" s="294">
+      <c r="AQ22" s="310">
         <f>SUM(E23,K23,N23,Q23,T23,W23,Z23,AI23)</f>
         <v/>
       </c>
-      <c r="AR22" s="294">
+      <c r="AR22" s="310">
         <f>10-AL22-AM22-AN22</f>
         <v/>
       </c>
-      <c r="AS22" s="288">
+      <c r="AS22" s="311">
         <f>IFERROR(_xlfn.RANK.EQ(AO22,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5200,207 +5504,209 @@
       </c>
     </row>
     <row r="23" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="B23" s="272" t="n"/>
-      <c r="C23" s="273" t="n"/>
-      <c r="D23" s="274" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="A23" s="302" t="n"/>
+      <c r="B23" s="281" t="n"/>
+      <c r="C23" s="282" t="n"/>
+      <c r="D23" s="283" t="n"/>
+      <c r="E23" s="316" t="n"/>
+      <c r="F23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="G23" s="312" t="n"/>
+      <c r="H23" s="312" t="n"/>
+      <c r="I23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="J23" s="312" t="n"/>
+      <c r="K23" s="312" t="n"/>
+      <c r="L23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="10" t="n"/>
-      <c r="N23" s="10" t="n"/>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="M23" s="312" t="n"/>
+      <c r="N23" s="312" t="n"/>
+      <c r="O23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P23" s="10" t="n"/>
-      <c r="Q23" s="10" t="n"/>
-      <c r="R23" s="8" t="inlineStr">
+      <c r="P23" s="312" t="n"/>
+      <c r="Q23" s="312" t="n"/>
+      <c r="R23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S23" s="10" t="n"/>
-      <c r="T23" s="10" t="n"/>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="S23" s="312" t="n"/>
+      <c r="T23" s="312" t="n"/>
+      <c r="U23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V23" s="10" t="n"/>
-      <c r="W23" s="10" t="n"/>
-      <c r="X23" s="8" t="inlineStr">
+      <c r="V23" s="312" t="n"/>
+      <c r="W23" s="312" t="n"/>
+      <c r="X23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y23" s="10" t="n"/>
-      <c r="Z23" s="10" t="n"/>
-      <c r="AA23" s="8" t="inlineStr">
+      <c r="Y23" s="312" t="n"/>
+      <c r="Z23" s="312" t="n"/>
+      <c r="AA23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB23" s="10" t="n"/>
-      <c r="AC23" s="307" t="n"/>
-      <c r="AD23" s="284" t="n"/>
-      <c r="AE23" s="285" t="n"/>
-      <c r="AF23" s="275">
+      <c r="AB23" s="312" t="n"/>
+      <c r="AC23" s="320" t="n"/>
+      <c r="AD23" s="294" t="n"/>
+      <c r="AE23" s="295" t="n"/>
+      <c r="AF23" s="321">
         <f>IF(AE25="","",AE25)</f>
         <v/>
       </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="AG23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH23" s="275">
+      <c r="AH23" s="321">
         <f>IF(AC25="","",AC25)</f>
         <v/>
       </c>
-      <c r="AI23" s="16">
+      <c r="AI23" s="305">
         <f>IF(AE27="","",AE27)</f>
         <v/>
       </c>
-      <c r="AJ23" s="16" t="inlineStr">
+      <c r="AJ23" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK23" s="16">
+      <c r="AK23" s="305">
         <f>IF(AC27="","",AC27)</f>
         <v/>
       </c>
-      <c r="AL23" s="272" t="n"/>
-      <c r="AM23" s="276" t="n"/>
-      <c r="AN23" s="276" t="n"/>
-      <c r="AO23" s="276" t="n"/>
-      <c r="AP23" s="276" t="n"/>
-      <c r="AQ23" s="276" t="n"/>
-      <c r="AR23" s="276" t="n"/>
-      <c r="AS23" s="289" t="n"/>
-      <c r="AV23" s="276" t="n"/>
-      <c r="AW23" s="278" t="n"/>
-      <c r="AX23" s="276" t="n"/>
+      <c r="AL23" s="281" t="n"/>
+      <c r="AM23" s="286" t="n"/>
+      <c r="AN23" s="286" t="n"/>
+      <c r="AO23" s="286" t="n"/>
+      <c r="AP23" s="286" t="n"/>
+      <c r="AQ23" s="286" t="n"/>
+      <c r="AR23" s="286" t="n"/>
+      <c r="AS23" s="298" t="n"/>
+      <c r="AV23" s="286" t="n"/>
+      <c r="AW23" s="288" t="n"/>
+      <c r="AX23" s="286" t="n"/>
     </row>
     <row r="24" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="B24" s="174" t="n">
+      <c r="A24" s="302" t="n"/>
+      <c r="B24" s="303" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="175">
+      <c r="C24" s="304">
         <f>AX24</f>
         <v/>
       </c>
-      <c r="D24" s="264" t="n"/>
-      <c r="E24" s="308">
+      <c r="D24" s="272" t="n"/>
+      <c r="E24" s="303">
         <f>IF(E25="","",IF(E25="☂","☂",IF(E25&gt;G25,"○",IF(E25=G25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F24" s="279" t="n"/>
-      <c r="G24" s="280" t="n"/>
-      <c r="H24" s="39">
+      <c r="F24" s="290" t="n"/>
+      <c r="G24" s="291" t="n"/>
+      <c r="H24" s="305">
         <f>IF(H25="","",IF(H25="☂","☂",IF(H25&gt;J25,"○",IF(H25=J25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I24" s="279" t="n"/>
-      <c r="J24" s="280" t="n"/>
-      <c r="K24" s="39">
+      <c r="I24" s="290" t="n"/>
+      <c r="J24" s="291" t="n"/>
+      <c r="K24" s="305">
         <f>IF(K25="","",IF(K25="☂","☂",IF(K25&gt;M25,"○",IF(K25=M25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L24" s="279" t="n"/>
-      <c r="M24" s="280" t="n"/>
-      <c r="N24" s="309">
+      <c r="L24" s="290" t="n"/>
+      <c r="M24" s="291" t="n"/>
+      <c r="N24" s="306">
         <f>IF(N25="","",IF(N25="☂","☂",IF(N25&gt;P25,"○",IF(N25=P25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O24" s="298" t="n"/>
-      <c r="P24" s="299" t="n"/>
-      <c r="Q24" s="309">
+      <c r="O24" s="300" t="n"/>
+      <c r="P24" s="301" t="n"/>
+      <c r="Q24" s="306">
         <f>IF(Q25="","",IF(Q25="☂","☂",IF(Q25&gt;S25,"○",IF(Q25=S25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R24" s="298" t="n"/>
-      <c r="S24" s="299" t="n"/>
-      <c r="T24" s="309">
+      <c r="R24" s="300" t="n"/>
+      <c r="S24" s="301" t="n"/>
+      <c r="T24" s="306">
         <f>IF(T25="","",IF(T25="☂","☂",IF(T25&gt;V25,"○",IF(T25=V25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U24" s="298" t="n"/>
-      <c r="V24" s="299" t="n"/>
-      <c r="W24" s="309">
+      <c r="U24" s="300" t="n"/>
+      <c r="V24" s="301" t="n"/>
+      <c r="W24" s="306">
         <f>IF(W25="","",IF(W25="☂","☂",IF(W25&gt;Y25,"○",IF(W25=Y25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X24" s="298" t="n"/>
-      <c r="Y24" s="299" t="n"/>
-      <c r="Z24" s="309">
+      <c r="X24" s="300" t="n"/>
+      <c r="Y24" s="301" t="n"/>
+      <c r="Z24" s="306">
         <f>IF(Z25="","",IF(Z25="☂","☂",IF(Z25&gt;AB25,"○",IF(Z25=AB25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA24" s="298" t="n"/>
-      <c r="AB24" s="299" t="n"/>
-      <c r="AC24" s="309">
+      <c r="AA24" s="300" t="n"/>
+      <c r="AB24" s="301" t="n"/>
+      <c r="AC24" s="306">
         <f>IF(AC25="","",IF(AC25="☂","☂",IF(AC25&gt;AE25,"○",IF(AC25=AE25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD24" s="298" t="n"/>
-      <c r="AE24" s="299" t="n"/>
-      <c r="AF24" s="310" t="n"/>
-      <c r="AG24" s="304" t="n"/>
-      <c r="AH24" s="305" t="n"/>
-      <c r="AI24" s="309">
+      <c r="AD24" s="300" t="n"/>
+      <c r="AE24" s="301" t="n"/>
+      <c r="AF24" s="322" t="n"/>
+      <c r="AG24" s="318" t="n"/>
+      <c r="AH24" s="319" t="n"/>
+      <c r="AI24" s="306">
         <f>IF(AI25="","",IF(AI25="☂","☂",IF(AI25&gt;AK25,"○",IF(AI25=AK25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ24" s="298" t="n"/>
-      <c r="AK24" s="299" t="n"/>
-      <c r="AL24" s="311">
+      <c r="AJ24" s="300" t="n"/>
+      <c r="AK24" s="301" t="n"/>
+      <c r="AL24" s="309">
         <f>COUNTIF(E24:AK24,"○")</f>
         <v/>
       </c>
-      <c r="AM24" s="312">
+      <c r="AM24" s="310">
         <f>COUNTIF(E24:AK24,"△")</f>
         <v/>
       </c>
-      <c r="AN24" s="312">
+      <c r="AN24" s="310">
         <f>COUNTIF(E24:AK24,"×")</f>
         <v/>
       </c>
-      <c r="AO24" s="312">
+      <c r="AO24" s="310">
         <f>AL24*3+AM24*1</f>
         <v/>
       </c>
-      <c r="AP24" s="312">
+      <c r="AP24" s="310">
         <f>SUM(G25,M25,P25,S25,V25,Y25,AB25,AK25)</f>
         <v/>
       </c>
-      <c r="AQ24" s="312">
+      <c r="AQ24" s="310">
         <f>SUM(E25,K25,N25,Q25,T25,W25,Z25,AI25)</f>
         <v/>
       </c>
-      <c r="AR24" s="312">
+      <c r="AR24" s="310">
         <f>10-AL24-AM24-AN24</f>
         <v/>
       </c>
-      <c r="AS24" s="288">
+      <c r="AS24" s="311">
         <f>IFERROR(_xlfn.RANK.EQ(AO24,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5414,201 +5720,203 @@
       </c>
     </row>
     <row r="25" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="B25" s="272" t="n"/>
-      <c r="C25" s="273" t="n"/>
-      <c r="D25" s="274" t="n"/>
-      <c r="E25" s="41" t="n"/>
-      <c r="F25" s="39" t="inlineStr">
+      <c r="A25" s="302" t="n"/>
+      <c r="B25" s="281" t="n"/>
+      <c r="C25" s="282" t="n"/>
+      <c r="D25" s="283" t="n"/>
+      <c r="E25" s="323" t="n"/>
+      <c r="F25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="40" t="n"/>
-      <c r="H25" s="40" t="n"/>
-      <c r="I25" s="39" t="inlineStr">
+      <c r="G25" s="312" t="n"/>
+      <c r="H25" s="312" t="n"/>
+      <c r="I25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="40" t="n"/>
-      <c r="K25" s="40" t="n"/>
-      <c r="L25" s="39" t="inlineStr">
+      <c r="J25" s="312" t="n"/>
+      <c r="K25" s="312" t="n"/>
+      <c r="L25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="40" t="n"/>
-      <c r="N25" s="40" t="n"/>
-      <c r="O25" s="39" t="inlineStr">
+      <c r="M25" s="312" t="n"/>
+      <c r="N25" s="312" t="n"/>
+      <c r="O25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P25" s="40" t="n"/>
-      <c r="Q25" s="40" t="n"/>
-      <c r="R25" s="39" t="inlineStr">
+      <c r="P25" s="312" t="n"/>
+      <c r="Q25" s="312" t="n"/>
+      <c r="R25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S25" s="40" t="n"/>
-      <c r="T25" s="40" t="n"/>
-      <c r="U25" s="39" t="inlineStr">
+      <c r="S25" s="312" t="n"/>
+      <c r="T25" s="312" t="n"/>
+      <c r="U25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V25" s="40" t="n"/>
-      <c r="W25" s="40" t="n"/>
-      <c r="X25" s="39" t="inlineStr">
+      <c r="V25" s="312" t="n"/>
+      <c r="W25" s="312" t="n"/>
+      <c r="X25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y25" s="40" t="n"/>
-      <c r="Z25" s="40" t="n"/>
-      <c r="AA25" s="39" t="inlineStr">
+      <c r="Y25" s="312" t="n"/>
+      <c r="Z25" s="312" t="n"/>
+      <c r="AA25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB25" s="40" t="n"/>
-      <c r="AC25" s="40" t="n"/>
-      <c r="AD25" s="39" t="inlineStr">
+      <c r="AB25" s="312" t="n"/>
+      <c r="AC25" s="312" t="n"/>
+      <c r="AD25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE25" s="40" t="n"/>
-      <c r="AF25" s="313" t="n"/>
-      <c r="AG25" s="314" t="n"/>
-      <c r="AH25" s="315" t="n"/>
-      <c r="AI25" s="40">
+      <c r="AE25" s="312" t="n"/>
+      <c r="AF25" s="324" t="n"/>
+      <c r="AG25" s="325" t="n"/>
+      <c r="AH25" s="326" t="n"/>
+      <c r="AI25" s="312">
         <f>IF(AH27="","",AH27)</f>
         <v/>
       </c>
-      <c r="AJ25" s="39" t="inlineStr">
+      <c r="AJ25" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK25" s="42">
+      <c r="AK25" s="327">
         <f>IF(AF27="","",AF27)</f>
         <v/>
       </c>
-      <c r="AL25" s="272" t="n"/>
-      <c r="AM25" s="276" t="n"/>
-      <c r="AN25" s="276" t="n"/>
-      <c r="AO25" s="276" t="n"/>
-      <c r="AP25" s="276" t="n"/>
-      <c r="AQ25" s="276" t="n"/>
-      <c r="AR25" s="276" t="n"/>
-      <c r="AS25" s="289" t="n"/>
-      <c r="AV25" s="276" t="n"/>
-      <c r="AW25" s="278" t="n"/>
-      <c r="AX25" s="276" t="n"/>
+      <c r="AL25" s="281" t="n"/>
+      <c r="AM25" s="286" t="n"/>
+      <c r="AN25" s="286" t="n"/>
+      <c r="AO25" s="286" t="n"/>
+      <c r="AP25" s="286" t="n"/>
+      <c r="AQ25" s="286" t="n"/>
+      <c r="AR25" s="286" t="n"/>
+      <c r="AS25" s="298" t="n"/>
+      <c r="AV25" s="286" t="n"/>
+      <c r="AW25" s="288" t="n"/>
+      <c r="AX25" s="286" t="n"/>
     </row>
     <row r="26" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="B26" s="131" t="n">
+      <c r="A26" s="302" t="n"/>
+      <c r="B26" s="303" t="n">
         <v>11</v>
       </c>
-      <c r="C26" s="163">
+      <c r="C26" s="304">
         <f>AX26</f>
         <v/>
       </c>
-      <c r="D26" s="264" t="n"/>
-      <c r="E26" s="316">
+      <c r="D26" s="272" t="n"/>
+      <c r="E26" s="303">
         <f>IF(E27="","",IF(E27="☂","☂",IF(E27&gt;G27,"○",IF(E27=G27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F26" s="279" t="n"/>
-      <c r="G26" s="280" t="n"/>
-      <c r="H26" s="16">
+      <c r="F26" s="290" t="n"/>
+      <c r="G26" s="291" t="n"/>
+      <c r="H26" s="305">
         <f>IF(H27="","",IF(H27="☂","☂",IF(H27&gt;J27,"○",IF(H27=J27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I26" s="279" t="n"/>
-      <c r="J26" s="280" t="n"/>
-      <c r="K26" s="16">
+      <c r="I26" s="290" t="n"/>
+      <c r="J26" s="291" t="n"/>
+      <c r="K26" s="305">
         <f>IF(K27="","",IF(K27="☂","☂",IF(K27&gt;M27,"○",IF(K27=M27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L26" s="279" t="n"/>
-      <c r="M26" s="280" t="n"/>
-      <c r="N26" s="317">
+      <c r="L26" s="290" t="n"/>
+      <c r="M26" s="291" t="n"/>
+      <c r="N26" s="306">
         <f>IF(N27="","",IF(N27="☂","☂",IF(N27&gt;P27,"○",IF(N27=P27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O26" s="298" t="n"/>
-      <c r="P26" s="299" t="n"/>
-      <c r="Q26" s="317">
+      <c r="O26" s="300" t="n"/>
+      <c r="P26" s="301" t="n"/>
+      <c r="Q26" s="306">
         <f>IF(Q27="","",IF(Q27="☂","☂",IF(Q27&gt;S27,"○",IF(Q27=S27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R26" s="298" t="n"/>
-      <c r="S26" s="299" t="n"/>
-      <c r="T26" s="317">
+      <c r="R26" s="300" t="n"/>
+      <c r="S26" s="301" t="n"/>
+      <c r="T26" s="306">
         <f>IF(T27="","",IF(T27="☂","☂",IF(T27&gt;V27,"○",IF(T27=V27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U26" s="298" t="n"/>
-      <c r="V26" s="299" t="n"/>
-      <c r="W26" s="317">
+      <c r="U26" s="300" t="n"/>
+      <c r="V26" s="301" t="n"/>
+      <c r="W26" s="306">
         <f>IF(W27="","",IF(W27="☂","☂",IF(W27&gt;Y27,"○",IF(W27=Y27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X26" s="298" t="n"/>
-      <c r="Y26" s="299" t="n"/>
-      <c r="Z26" s="317">
+      <c r="X26" s="300" t="n"/>
+      <c r="Y26" s="301" t="n"/>
+      <c r="Z26" s="306">
         <f>IF(Z27="","",IF(Z27="☂","☂",IF(Z27&gt;AB27,"○",IF(Z27=AB27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA26" s="298" t="n"/>
-      <c r="AB26" s="299" t="n"/>
-      <c r="AC26" s="317">
+      <c r="AA26" s="300" t="n"/>
+      <c r="AB26" s="301" t="n"/>
+      <c r="AC26" s="306">
         <f>IF(AC27="","",IF(AC27="☂","☂",IF(AC27&gt;AE27,"○",IF(AC27=AE27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD26" s="298" t="n"/>
-      <c r="AE26" s="299" t="n"/>
-      <c r="AF26" s="317">
+      <c r="AD26" s="300" t="n"/>
+      <c r="AE26" s="301" t="n"/>
+      <c r="AF26" s="306">
         <f>IF(AF27="","",IF(AF27="☂","☂",IF(AF27&gt;AH27,"○",IF(AF27=AH27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG26" s="298" t="n"/>
-      <c r="AH26" s="299" t="n"/>
-      <c r="AI26" s="318" t="n"/>
-      <c r="AJ26" s="314" t="n"/>
-      <c r="AK26" s="319" t="n"/>
-      <c r="AL26" s="293">
+      <c r="AG26" s="300" t="n"/>
+      <c r="AH26" s="301" t="n"/>
+      <c r="AI26" s="328" t="n"/>
+      <c r="AJ26" s="325" t="n"/>
+      <c r="AK26" s="329" t="n"/>
+      <c r="AL26" s="309">
         <f>COUNTIF(E26:AK26,"○")</f>
         <v/>
       </c>
-      <c r="AM26" s="294">
+      <c r="AM26" s="310">
         <f>COUNTIF(E26:AK26,"△")</f>
         <v/>
       </c>
-      <c r="AN26" s="294">
+      <c r="AN26" s="310">
         <f>COUNTIF(E26:AK26,"×")</f>
         <v/>
       </c>
-      <c r="AO26" s="294">
+      <c r="AO26" s="310">
         <f>AL26*3+AM26*1</f>
         <v/>
       </c>
-      <c r="AP26" s="294">
+      <c r="AP26" s="310">
         <f>SUM(G27,M27,P27,S27,V27,Y27,AB27,AK27)</f>
         <v/>
       </c>
-      <c r="AQ26" s="14">
+      <c r="AQ26" s="330">
         <f>SUM(H27,K27,N27,Q27,T27,W27,Z27,AI27,#REF!)</f>
         <v/>
       </c>
-      <c r="AR26" s="14">
+      <c r="AR26" s="330">
         <f>10-AL26-AM26-AN26</f>
         <v/>
       </c>
-      <c r="AS26" s="320">
+      <c r="AS26" s="331">
         <f>IFERROR(_xlfn.RANK.EQ(AO26,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5622,93 +5930,94 @@
       </c>
     </row>
     <row r="27" hidden="1" ht="33.6" customHeight="1" s="257" thickBot="1">
-      <c r="B27" s="272" t="n"/>
-      <c r="C27" s="273" t="n"/>
-      <c r="D27" s="274" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="A27" s="302" t="n"/>
+      <c r="B27" s="281" t="n"/>
+      <c r="C27" s="282" t="n"/>
+      <c r="D27" s="283" t="n"/>
+      <c r="E27" s="332" t="n"/>
+      <c r="F27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="G27" s="333" t="n"/>
+      <c r="H27" s="332" t="n"/>
+      <c r="I27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="J27" s="332" t="n"/>
+      <c r="K27" s="332" t="n"/>
+      <c r="L27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="13" t="n"/>
-      <c r="N27" s="13" t="n"/>
-      <c r="O27" s="14" t="inlineStr">
+      <c r="M27" s="332" t="n"/>
+      <c r="N27" s="332" t="n"/>
+      <c r="O27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P27" s="13" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="14" t="inlineStr">
+      <c r="P27" s="332" t="n"/>
+      <c r="Q27" s="332" t="n"/>
+      <c r="R27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S27" s="13" t="n"/>
-      <c r="T27" s="13" t="n"/>
-      <c r="U27" s="14" t="inlineStr">
+      <c r="S27" s="332" t="n"/>
+      <c r="T27" s="332" t="n"/>
+      <c r="U27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V27" s="13" t="n"/>
-      <c r="W27" s="13" t="n"/>
-      <c r="X27" s="14" t="inlineStr">
+      <c r="V27" s="332" t="n"/>
+      <c r="W27" s="332" t="n"/>
+      <c r="X27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y27" s="13" t="n"/>
-      <c r="Z27" s="13" t="n"/>
-      <c r="AA27" s="14" t="inlineStr">
+      <c r="Y27" s="332" t="n"/>
+      <c r="Z27" s="332" t="n"/>
+      <c r="AA27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB27" s="13" t="n"/>
-      <c r="AC27" s="13" t="n"/>
-      <c r="AD27" s="14" t="inlineStr">
+      <c r="AB27" s="332" t="n"/>
+      <c r="AC27" s="332" t="n"/>
+      <c r="AD27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE27" s="13" t="n"/>
-      <c r="AF27" s="321" t="n"/>
-      <c r="AG27" s="14" t="inlineStr">
+      <c r="AE27" s="332" t="n"/>
+      <c r="AF27" s="334" t="n"/>
+      <c r="AG27" s="330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH27" s="321" t="n"/>
-      <c r="AI27" s="322" t="n"/>
-      <c r="AJ27" s="323" t="n"/>
-      <c r="AK27" s="324" t="n"/>
-      <c r="AL27" s="272" t="n"/>
-      <c r="AM27" s="276" t="n"/>
-      <c r="AN27" s="276" t="n"/>
-      <c r="AO27" s="276" t="n"/>
-      <c r="AP27" s="276" t="n"/>
-      <c r="AQ27" s="325" t="n"/>
-      <c r="AR27" s="325" t="n"/>
-      <c r="AS27" s="326" t="n"/>
-      <c r="AV27" s="276" t="n"/>
-      <c r="AW27" s="278" t="n"/>
-      <c r="AX27" s="276" t="n"/>
+      <c r="AH27" s="334" t="n"/>
+      <c r="AI27" s="335" t="n"/>
+      <c r="AJ27" s="336" t="n"/>
+      <c r="AK27" s="337" t="n"/>
+      <c r="AL27" s="281" t="n"/>
+      <c r="AM27" s="286" t="n"/>
+      <c r="AN27" s="286" t="n"/>
+      <c r="AO27" s="286" t="n"/>
+      <c r="AP27" s="286" t="n"/>
+      <c r="AQ27" s="338" t="n"/>
+      <c r="AR27" s="338" t="n"/>
+      <c r="AS27" s="339" t="n"/>
+      <c r="AV27" s="286" t="n"/>
+      <c r="AW27" s="288" t="n"/>
+      <c r="AX27" s="286" t="n"/>
     </row>
     <row r="28" ht="6.75" customHeight="1" s="257"/>
   </sheetData>
@@ -6056,8 +6365,8 @@
       <c r="T1" s="240" t="n">
         <v>2026</v>
       </c>
-      <c r="U1" s="327" t="n"/>
-      <c r="V1" s="327" t="n"/>
+      <c r="U1" s="340" t="n"/>
+      <c r="V1" s="340" t="n"/>
       <c r="W1" s="238" t="inlineStr">
         <is>
           <t>年</t>
@@ -6066,46 +6375,46 @@
       <c r="X1" s="238" t="n"/>
     </row>
     <row r="2" ht="16.15" customHeight="1" s="257">
-      <c r="A2" s="328" t="inlineStr">
+      <c r="A2" s="341" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="329" t="n"/>
-      <c r="C2" s="329" t="n"/>
-      <c r="D2" s="329" t="n"/>
-      <c r="E2" s="329" t="n"/>
-      <c r="F2" s="330" t="n"/>
-      <c r="G2" s="328" t="inlineStr">
+      <c r="B2" s="342" t="n"/>
+      <c r="C2" s="342" t="n"/>
+      <c r="D2" s="342" t="n"/>
+      <c r="E2" s="342" t="n"/>
+      <c r="F2" s="343" t="n"/>
+      <c r="G2" s="341" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="329" t="n"/>
-      <c r="I2" s="329" t="n"/>
-      <c r="J2" s="329" t="n"/>
-      <c r="K2" s="329" t="n"/>
-      <c r="L2" s="330" t="n"/>
-      <c r="M2" s="328" t="inlineStr">
+      <c r="H2" s="342" t="n"/>
+      <c r="I2" s="342" t="n"/>
+      <c r="J2" s="342" t="n"/>
+      <c r="K2" s="342" t="n"/>
+      <c r="L2" s="343" t="n"/>
+      <c r="M2" s="341" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="329" t="n"/>
-      <c r="O2" s="329" t="n"/>
-      <c r="P2" s="329" t="n"/>
-      <c r="Q2" s="329" t="n"/>
-      <c r="R2" s="330" t="n"/>
+      <c r="N2" s="342" t="n"/>
+      <c r="O2" s="342" t="n"/>
+      <c r="P2" s="342" t="n"/>
+      <c r="Q2" s="342" t="n"/>
+      <c r="R2" s="343" t="n"/>
       <c r="S2" s="246" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="329" t="n"/>
-      <c r="U2" s="329" t="n"/>
-      <c r="V2" s="329" t="n"/>
-      <c r="W2" s="329" t="n"/>
-      <c r="X2" s="330" t="n"/>
+      <c r="T2" s="342" t="n"/>
+      <c r="U2" s="342" t="n"/>
+      <c r="V2" s="342" t="n"/>
+      <c r="W2" s="342" t="n"/>
+      <c r="X2" s="343" t="n"/>
     </row>
     <row r="3" ht="16.15" customHeight="1" s="257">
       <c r="A3" s="53" t="inlineStr">
@@ -6123,8 +6432,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="279" t="n"/>
-      <c r="E3" s="280" t="n"/>
+      <c r="D3" s="290" t="n"/>
+      <c r="E3" s="291" t="n"/>
       <c r="F3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6145,8 +6454,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="279" t="n"/>
-      <c r="K3" s="280" t="n"/>
+      <c r="J3" s="290" t="n"/>
+      <c r="K3" s="291" t="n"/>
       <c r="L3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6167,8 +6476,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="279" t="n"/>
-      <c r="Q3" s="280" t="n"/>
+      <c r="P3" s="290" t="n"/>
+      <c r="Q3" s="291" t="n"/>
       <c r="R3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6189,8 +6498,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="279" t="n"/>
-      <c r="W3" s="280" t="n"/>
+      <c r="V3" s="290" t="n"/>
+      <c r="W3" s="291" t="n"/>
       <c r="X3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6198,7 +6507,7 @@
       </c>
     </row>
     <row r="4" ht="16.15" customHeight="1" s="257">
-      <c r="A4" s="331" t="n">
+      <c r="A4" s="344" t="n">
         <v>45047</v>
       </c>
       <c r="B4" s="69" t="inlineStr">
@@ -6206,15 +6515,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C4" s="332" t="n"/>
+      <c r="C4" s="345" t="n"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="333" t="n"/>
-      <c r="F4" s="334" t="n"/>
-      <c r="G4" s="331" t="n">
+      <c r="E4" s="346" t="n"/>
+      <c r="F4" s="347" t="n"/>
+      <c r="G4" s="344" t="n">
         <v>45078</v>
       </c>
       <c r="H4" s="70" t="inlineStr">
@@ -6222,15 +6531,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I4" s="335" t="n"/>
+      <c r="I4" s="348" t="n"/>
       <c r="J4" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="336" t="n"/>
-      <c r="L4" s="334" t="n"/>
-      <c r="M4" s="331" t="n">
+      <c r="K4" s="349" t="n"/>
+      <c r="L4" s="347" t="n"/>
+      <c r="M4" s="344" t="n">
         <v>45108</v>
       </c>
       <c r="N4" s="69" t="inlineStr">
@@ -6238,7 +6547,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O4" s="335">
+      <c r="O4" s="348">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6247,15 +6556,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="336">
+      <c r="Q4" s="349">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="334">
+      <c r="R4" s="347">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="337" t="n">
+      <c r="S4" s="350" t="n">
         <v>45139</v>
       </c>
       <c r="T4" s="69" t="inlineStr">
@@ -6263,17 +6572,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U4" s="332" t="n"/>
+      <c r="U4" s="345" t="n"/>
       <c r="V4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="333" t="n"/>
-      <c r="X4" s="334" t="n"/>
+      <c r="W4" s="346" t="n"/>
+      <c r="X4" s="347" t="n"/>
     </row>
     <row r="5" ht="16.15" customHeight="1" s="257">
-      <c r="A5" s="331" t="n">
+      <c r="A5" s="344" t="n">
         <v>45048</v>
       </c>
       <c r="B5" s="69" t="inlineStr">
@@ -6281,15 +6590,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C5" s="335" t="n"/>
+      <c r="C5" s="348" t="n"/>
       <c r="D5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="336" t="n"/>
-      <c r="F5" s="334" t="n"/>
-      <c r="G5" s="331" t="n">
+      <c r="E5" s="349" t="n"/>
+      <c r="F5" s="347" t="n"/>
+      <c r="G5" s="344" t="n">
         <v>45079</v>
       </c>
       <c r="H5" s="70" t="inlineStr">
@@ -6297,7 +6606,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I5" s="335">
+      <c r="I5" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -6306,40 +6615,40 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="336">
+      <c r="K5" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="347">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="338" t="n">
+      <c r="M5" s="351" t="n">
         <v>45109</v>
       </c>
-      <c r="N5" s="339" t="inlineStr">
+      <c r="N5" s="352" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="O5" s="340">
+      <c r="O5" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="341" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="342">
+      <c r="P5" s="354" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="355">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="343">
+      <c r="R5" s="356">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="337" t="n">
+      <c r="S5" s="350" t="n">
         <v>45140</v>
       </c>
       <c r="T5" s="69" t="inlineStr">
@@ -6347,17 +6656,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U5" s="335" t="n"/>
+      <c r="U5" s="348" t="n"/>
       <c r="V5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="336" t="n"/>
-      <c r="X5" s="334" t="n"/>
+      <c r="W5" s="349" t="n"/>
+      <c r="X5" s="347" t="n"/>
     </row>
     <row r="6" ht="16.15" customHeight="1" s="257">
-      <c r="A6" s="331" t="n">
+      <c r="A6" s="344" t="n">
         <v>45049</v>
       </c>
       <c r="B6" s="69" t="inlineStr">
@@ -6365,40 +6674,40 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C6" s="335" t="n"/>
+      <c r="C6" s="348" t="n"/>
       <c r="D6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="336" t="n"/>
-      <c r="F6" s="334" t="n"/>
-      <c r="G6" s="338" t="n">
+      <c r="E6" s="349" t="n"/>
+      <c r="F6" s="347" t="n"/>
+      <c r="G6" s="351" t="n">
         <v>45080</v>
       </c>
-      <c r="H6" s="344" t="inlineStr">
+      <c r="H6" s="357" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I6" s="340">
+      <c r="I6" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="341" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="342">
+      <c r="J6" s="354" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="355">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="343">
+      <c r="L6" s="356">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="331" t="n">
+      <c r="M6" s="344" t="n">
         <v>45110</v>
       </c>
       <c r="N6" s="69" t="inlineStr">
@@ -6406,15 +6715,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O6" s="335" t="n"/>
+      <c r="O6" s="348" t="n"/>
       <c r="P6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="336" t="n"/>
-      <c r="R6" s="334" t="n"/>
-      <c r="S6" s="337" t="n">
+      <c r="Q6" s="349" t="n"/>
+      <c r="R6" s="347" t="n"/>
+      <c r="S6" s="350" t="n">
         <v>45141</v>
       </c>
       <c r="T6" s="69" t="inlineStr">
@@ -6422,17 +6731,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U6" s="335" t="n"/>
+      <c r="U6" s="348" t="n"/>
       <c r="V6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="336" t="n"/>
-      <c r="X6" s="334" t="n"/>
+      <c r="W6" s="349" t="n"/>
+      <c r="X6" s="347" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" s="257">
-      <c r="A7" s="331" t="n">
+      <c r="A7" s="344" t="n">
         <v>45050</v>
       </c>
       <c r="B7" s="69" t="inlineStr">
@@ -6440,15 +6749,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C7" s="335" t="n"/>
+      <c r="C7" s="348" t="n"/>
       <c r="D7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="336" t="n"/>
-      <c r="F7" s="334" t="n"/>
-      <c r="G7" s="331" t="n">
+      <c r="E7" s="349" t="n"/>
+      <c r="F7" s="347" t="n"/>
+      <c r="G7" s="344" t="n">
         <v>45081</v>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -6456,7 +6765,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="348">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6465,15 +6774,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="336">
+      <c r="K7" s="349">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="334">
+      <c r="L7" s="347">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="331" t="n">
+      <c r="M7" s="344" t="n">
         <v>45111</v>
       </c>
       <c r="N7" s="69" t="inlineStr">
@@ -6481,15 +6790,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O7" s="335" t="n"/>
+      <c r="O7" s="348" t="n"/>
       <c r="P7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="336" t="n"/>
-      <c r="R7" s="334" t="n"/>
-      <c r="S7" s="337" t="n">
+      <c r="Q7" s="349" t="n"/>
+      <c r="R7" s="347" t="n"/>
+      <c r="S7" s="350" t="n">
         <v>45142</v>
       </c>
       <c r="T7" s="69" t="inlineStr">
@@ -6497,17 +6806,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U7" s="335" t="n"/>
+      <c r="U7" s="348" t="n"/>
       <c r="V7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="336" t="n"/>
-      <c r="X7" s="334" t="n"/>
+      <c r="W7" s="349" t="n"/>
+      <c r="X7" s="347" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" s="257">
-      <c r="A8" s="331" t="n">
+      <c r="A8" s="344" t="n">
         <v>45051</v>
       </c>
       <c r="B8" s="69" t="inlineStr">
@@ -6515,15 +6824,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C8" s="335" t="n"/>
+      <c r="C8" s="348" t="n"/>
       <c r="D8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="336" t="n"/>
-      <c r="F8" s="334" t="n"/>
-      <c r="G8" s="331" t="n">
+      <c r="E8" s="349" t="n"/>
+      <c r="F8" s="347" t="n"/>
+      <c r="G8" s="344" t="n">
         <v>45082</v>
       </c>
       <c r="H8" s="70" t="inlineStr">
@@ -6531,15 +6840,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I8" s="335" t="n"/>
+      <c r="I8" s="348" t="n"/>
       <c r="J8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="336" t="n"/>
-      <c r="L8" s="334" t="n"/>
-      <c r="M8" s="331" t="n">
+      <c r="K8" s="349" t="n"/>
+      <c r="L8" s="347" t="n"/>
+      <c r="M8" s="344" t="n">
         <v>45112</v>
       </c>
       <c r="N8" s="69" t="inlineStr">
@@ -6547,15 +6856,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O8" s="335" t="n"/>
+      <c r="O8" s="348" t="n"/>
       <c r="P8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="336" t="n"/>
-      <c r="R8" s="334" t="n"/>
-      <c r="S8" s="337" t="n">
+      <c r="Q8" s="349" t="n"/>
+      <c r="R8" s="347" t="n"/>
+      <c r="S8" s="350" t="n">
         <v>45143</v>
       </c>
       <c r="T8" s="69" t="inlineStr">
@@ -6563,17 +6872,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U8" s="335" t="n"/>
+      <c r="U8" s="348" t="n"/>
       <c r="V8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="336" t="n"/>
-      <c r="X8" s="334" t="n"/>
+      <c r="W8" s="349" t="n"/>
+      <c r="X8" s="347" t="n"/>
     </row>
     <row r="9" ht="16.15" customHeight="1" s="257">
-      <c r="A9" s="331" t="n">
+      <c r="A9" s="344" t="n">
         <v>45052</v>
       </c>
       <c r="B9" s="69" t="inlineStr">
@@ -6581,15 +6890,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C9" s="335" t="n"/>
+      <c r="C9" s="348" t="n"/>
       <c r="D9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="336" t="n"/>
-      <c r="F9" s="334" t="n"/>
-      <c r="G9" s="331" t="n">
+      <c r="E9" s="349" t="n"/>
+      <c r="F9" s="347" t="n"/>
+      <c r="G9" s="344" t="n">
         <v>45083</v>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -6597,15 +6906,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I9" s="335" t="n"/>
+      <c r="I9" s="348" t="n"/>
       <c r="J9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="336" t="n"/>
-      <c r="L9" s="334" t="n"/>
-      <c r="M9" s="331" t="n">
+      <c r="K9" s="349" t="n"/>
+      <c r="L9" s="347" t="n"/>
+      <c r="M9" s="344" t="n">
         <v>45113</v>
       </c>
       <c r="N9" s="69" t="inlineStr">
@@ -6613,15 +6922,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O9" s="335" t="n"/>
+      <c r="O9" s="348" t="n"/>
       <c r="P9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="336" t="n"/>
-      <c r="R9" s="334" t="n"/>
-      <c r="S9" s="337" t="n">
+      <c r="Q9" s="349" t="n"/>
+      <c r="R9" s="347" t="n"/>
+      <c r="S9" s="350" t="n">
         <v>45144</v>
       </c>
       <c r="T9" s="69" t="inlineStr">
@@ -6629,17 +6938,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U9" s="335" t="n"/>
+      <c r="U9" s="348" t="n"/>
       <c r="V9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="336" t="n"/>
-      <c r="X9" s="334" t="n"/>
+      <c r="W9" s="349" t="n"/>
+      <c r="X9" s="347" t="n"/>
     </row>
     <row r="10" ht="16.15" customHeight="1" s="257">
-      <c r="A10" s="331" t="n">
+      <c r="A10" s="344" t="n">
         <v>45053</v>
       </c>
       <c r="B10" s="69" t="inlineStr">
@@ -6647,15 +6956,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C10" s="335" t="n"/>
+      <c r="C10" s="348" t="n"/>
       <c r="D10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="336" t="n"/>
-      <c r="F10" s="334" t="n"/>
-      <c r="G10" s="331" t="n">
+      <c r="E10" s="349" t="n"/>
+      <c r="F10" s="347" t="n"/>
+      <c r="G10" s="344" t="n">
         <v>45084</v>
       </c>
       <c r="H10" s="70" t="inlineStr">
@@ -6663,15 +6972,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I10" s="335" t="n"/>
+      <c r="I10" s="348" t="n"/>
       <c r="J10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="336" t="n"/>
-      <c r="L10" s="334" t="n"/>
-      <c r="M10" s="331" t="n">
+      <c r="K10" s="349" t="n"/>
+      <c r="L10" s="347" t="n"/>
+      <c r="M10" s="344" t="n">
         <v>45114</v>
       </c>
       <c r="N10" s="69" t="inlineStr">
@@ -6679,15 +6988,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O10" s="335" t="n"/>
+      <c r="O10" s="348" t="n"/>
       <c r="P10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="336" t="n"/>
-      <c r="R10" s="334" t="n"/>
-      <c r="S10" s="337" t="n">
+      <c r="Q10" s="349" t="n"/>
+      <c r="R10" s="347" t="n"/>
+      <c r="S10" s="350" t="n">
         <v>45145</v>
       </c>
       <c r="T10" s="69" t="inlineStr">
@@ -6695,17 +7004,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U10" s="335" t="n"/>
+      <c r="U10" s="348" t="n"/>
       <c r="V10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="336" t="n"/>
-      <c r="X10" s="334" t="n"/>
+      <c r="W10" s="349" t="n"/>
+      <c r="X10" s="347" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" s="257">
-      <c r="A11" s="331" t="n">
+      <c r="A11" s="344" t="n">
         <v>45054</v>
       </c>
       <c r="B11" s="69" t="inlineStr">
@@ -6713,15 +7022,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C11" s="335" t="n"/>
+      <c r="C11" s="348" t="n"/>
       <c r="D11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="336" t="n"/>
-      <c r="F11" s="334" t="n"/>
-      <c r="G11" s="331" t="n">
+      <c r="E11" s="349" t="n"/>
+      <c r="F11" s="347" t="n"/>
+      <c r="G11" s="344" t="n">
         <v>45085</v>
       </c>
       <c r="H11" s="70" t="inlineStr">
@@ -6729,15 +7038,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I11" s="335" t="n"/>
+      <c r="I11" s="348" t="n"/>
       <c r="J11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="336" t="n"/>
-      <c r="L11" s="334" t="n"/>
-      <c r="M11" s="331" t="n">
+      <c r="K11" s="349" t="n"/>
+      <c r="L11" s="347" t="n"/>
+      <c r="M11" s="344" t="n">
         <v>45115</v>
       </c>
       <c r="N11" s="69" t="inlineStr">
@@ -6745,15 +7054,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O11" s="335" t="n"/>
+      <c r="O11" s="348" t="n"/>
       <c r="P11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="336" t="n"/>
-      <c r="R11" s="334" t="n"/>
-      <c r="S11" s="337" t="n">
+      <c r="Q11" s="349" t="n"/>
+      <c r="R11" s="347" t="n"/>
+      <c r="S11" s="350" t="n">
         <v>45146</v>
       </c>
       <c r="T11" s="69" t="inlineStr">
@@ -6761,17 +7070,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U11" s="335" t="n"/>
+      <c r="U11" s="348" t="n"/>
       <c r="V11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="336" t="n"/>
-      <c r="X11" s="334" t="n"/>
+      <c r="W11" s="349" t="n"/>
+      <c r="X11" s="347" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" s="257">
-      <c r="A12" s="331" t="n">
+      <c r="A12" s="344" t="n">
         <v>45055</v>
       </c>
       <c r="B12" s="69" t="inlineStr">
@@ -6779,40 +7088,40 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C12" s="335" t="n"/>
+      <c r="C12" s="348" t="n"/>
       <c r="D12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="336" t="n"/>
-      <c r="F12" s="334" t="n"/>
-      <c r="G12" s="338" t="n">
+      <c r="E12" s="349" t="n"/>
+      <c r="F12" s="347" t="n"/>
+      <c r="G12" s="351" t="n">
         <v>45086</v>
       </c>
-      <c r="H12" s="344" t="inlineStr">
+      <c r="H12" s="357" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I12" s="340">
+      <c r="I12" s="353">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="341" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="342">
+      <c r="J12" s="354" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="355">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="343">
+      <c r="L12" s="356">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="331" t="n">
+      <c r="M12" s="344" t="n">
         <v>45116</v>
       </c>
       <c r="N12" s="69" t="inlineStr">
@@ -6820,15 +7129,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O12" s="335" t="n"/>
+      <c r="O12" s="348" t="n"/>
       <c r="P12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="336" t="n"/>
-      <c r="R12" s="334" t="n"/>
-      <c r="S12" s="337" t="n">
+      <c r="Q12" s="349" t="n"/>
+      <c r="R12" s="347" t="n"/>
+      <c r="S12" s="350" t="n">
         <v>45147</v>
       </c>
       <c r="T12" s="69" t="inlineStr">
@@ -6836,17 +7145,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U12" s="335" t="n"/>
+      <c r="U12" s="348" t="n"/>
       <c r="V12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="336" t="n"/>
-      <c r="X12" s="334" t="n"/>
+      <c r="W12" s="349" t="n"/>
+      <c r="X12" s="347" t="n"/>
     </row>
     <row r="13" ht="16.15" customHeight="1" s="257">
-      <c r="A13" s="331" t="n">
+      <c r="A13" s="344" t="n">
         <v>45056</v>
       </c>
       <c r="B13" s="69" t="inlineStr">
@@ -6854,15 +7163,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C13" s="335" t="n"/>
+      <c r="C13" s="348" t="n"/>
       <c r="D13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="336" t="n"/>
-      <c r="F13" s="334" t="n"/>
-      <c r="G13" s="331" t="n">
+      <c r="E13" s="349" t="n"/>
+      <c r="F13" s="347" t="n"/>
+      <c r="G13" s="344" t="n">
         <v>45087</v>
       </c>
       <c r="H13" s="70" t="inlineStr">
@@ -6870,7 +7179,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I13" s="335">
+      <c r="I13" s="348">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6879,15 +7188,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="336">
+      <c r="K13" s="349">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="334">
+      <c r="L13" s="347">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="331" t="n">
+      <c r="M13" s="344" t="n">
         <v>45117</v>
       </c>
       <c r="N13" s="69" t="inlineStr">
@@ -6895,15 +7204,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O13" s="335" t="n"/>
+      <c r="O13" s="348" t="n"/>
       <c r="P13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="336" t="n"/>
-      <c r="R13" s="334" t="n"/>
-      <c r="S13" s="337" t="n">
+      <c r="Q13" s="349" t="n"/>
+      <c r="R13" s="347" t="n"/>
+      <c r="S13" s="350" t="n">
         <v>45148</v>
       </c>
       <c r="T13" s="69" t="inlineStr">
@@ -6911,17 +7220,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U13" s="335" t="n"/>
+      <c r="U13" s="348" t="n"/>
       <c r="V13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="336" t="n"/>
-      <c r="X13" s="334" t="n"/>
+      <c r="W13" s="349" t="n"/>
+      <c r="X13" s="347" t="n"/>
     </row>
     <row r="14" ht="16.15" customHeight="1" s="257">
-      <c r="A14" s="331" t="n">
+      <c r="A14" s="344" t="n">
         <v>45057</v>
       </c>
       <c r="B14" s="69" t="inlineStr">
@@ -6929,15 +7238,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C14" s="335" t="n"/>
+      <c r="C14" s="348" t="n"/>
       <c r="D14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="336" t="n"/>
-      <c r="F14" s="334" t="n"/>
-      <c r="G14" s="331" t="n">
+      <c r="E14" s="349" t="n"/>
+      <c r="F14" s="347" t="n"/>
+      <c r="G14" s="344" t="n">
         <v>45088</v>
       </c>
       <c r="H14" s="70" t="inlineStr">
@@ -6945,7 +7254,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I14" s="335">
+      <c r="I14" s="348">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6954,15 +7263,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="336">
+      <c r="K14" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="347">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="331" t="n">
+      <c r="M14" s="344" t="n">
         <v>45118</v>
       </c>
       <c r="N14" s="69" t="inlineStr">
@@ -6970,15 +7279,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O14" s="335" t="n"/>
+      <c r="O14" s="348" t="n"/>
       <c r="P14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="336" t="n"/>
-      <c r="R14" s="334" t="n"/>
-      <c r="S14" s="337" t="n">
+      <c r="Q14" s="349" t="n"/>
+      <c r="R14" s="347" t="n"/>
+      <c r="S14" s="350" t="n">
         <v>45149</v>
       </c>
       <c r="T14" s="69" t="inlineStr">
@@ -6986,17 +7295,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U14" s="335" t="n"/>
+      <c r="U14" s="348" t="n"/>
       <c r="V14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W14" s="336" t="n"/>
-      <c r="X14" s="334" t="n"/>
+      <c r="W14" s="349" t="n"/>
+      <c r="X14" s="347" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" s="257">
-      <c r="A15" s="331" t="n">
+      <c r="A15" s="344" t="n">
         <v>45058</v>
       </c>
       <c r="B15" s="69" t="inlineStr">
@@ -7004,15 +7313,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C15" s="335" t="n"/>
+      <c r="C15" s="348" t="n"/>
       <c r="D15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="336" t="n"/>
-      <c r="F15" s="334" t="n"/>
-      <c r="G15" s="331" t="n">
+      <c r="E15" s="349" t="n"/>
+      <c r="F15" s="347" t="n"/>
+      <c r="G15" s="344" t="n">
         <v>45089</v>
       </c>
       <c r="H15" s="70" t="inlineStr">
@@ -7020,15 +7329,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I15" s="335" t="n"/>
+      <c r="I15" s="348" t="n"/>
       <c r="J15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="336" t="n"/>
-      <c r="L15" s="334" t="n"/>
-      <c r="M15" s="331" t="n">
+      <c r="K15" s="349" t="n"/>
+      <c r="L15" s="347" t="n"/>
+      <c r="M15" s="344" t="n">
         <v>45119</v>
       </c>
       <c r="N15" s="69" t="inlineStr">
@@ -7036,15 +7345,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O15" s="335" t="n"/>
+      <c r="O15" s="348" t="n"/>
       <c r="P15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="336" t="n"/>
-      <c r="R15" s="334" t="n"/>
-      <c r="S15" s="337" t="n">
+      <c r="Q15" s="349" t="n"/>
+      <c r="R15" s="347" t="n"/>
+      <c r="S15" s="350" t="n">
         <v>45150</v>
       </c>
       <c r="T15" s="69" t="inlineStr">
@@ -7052,17 +7361,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U15" s="335" t="n"/>
+      <c r="U15" s="348" t="n"/>
       <c r="V15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W15" s="336" t="n"/>
-      <c r="X15" s="334" t="n"/>
+      <c r="W15" s="349" t="n"/>
+      <c r="X15" s="347" t="n"/>
     </row>
     <row r="16" ht="16.15" customHeight="1" s="257">
-      <c r="A16" s="331" t="n">
+      <c r="A16" s="344" t="n">
         <v>45059</v>
       </c>
       <c r="B16" s="69" t="inlineStr">
@@ -7070,15 +7379,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C16" s="335" t="n"/>
+      <c r="C16" s="348" t="n"/>
       <c r="D16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="336" t="n"/>
-      <c r="F16" s="334" t="n"/>
-      <c r="G16" s="331" t="n">
+      <c r="E16" s="349" t="n"/>
+      <c r="F16" s="347" t="n"/>
+      <c r="G16" s="344" t="n">
         <v>45090</v>
       </c>
       <c r="H16" s="70" t="inlineStr">
@@ -7086,15 +7395,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I16" s="335" t="n"/>
+      <c r="I16" s="348" t="n"/>
       <c r="J16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="336" t="n"/>
-      <c r="L16" s="334" t="n"/>
-      <c r="M16" s="331" t="n">
+      <c r="K16" s="349" t="n"/>
+      <c r="L16" s="347" t="n"/>
+      <c r="M16" s="344" t="n">
         <v>45120</v>
       </c>
       <c r="N16" s="69" t="inlineStr">
@@ -7102,15 +7411,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O16" s="335" t="n"/>
+      <c r="O16" s="348" t="n"/>
       <c r="P16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="336" t="n"/>
-      <c r="R16" s="334" t="n"/>
-      <c r="S16" s="337" t="n">
+      <c r="Q16" s="349" t="n"/>
+      <c r="R16" s="347" t="n"/>
+      <c r="S16" s="350" t="n">
         <v>45151</v>
       </c>
       <c r="T16" s="69" t="inlineStr">
@@ -7118,17 +7427,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U16" s="335" t="n"/>
+      <c r="U16" s="348" t="n"/>
       <c r="V16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W16" s="336" t="n"/>
-      <c r="X16" s="334" t="n"/>
+      <c r="W16" s="349" t="n"/>
+      <c r="X16" s="347" t="n"/>
     </row>
     <row r="17" ht="16.15" customHeight="1" s="257">
-      <c r="A17" s="331" t="n">
+      <c r="A17" s="344" t="n">
         <v>45060</v>
       </c>
       <c r="B17" s="69" t="inlineStr">
@@ -7136,15 +7445,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C17" s="335" t="n"/>
+      <c r="C17" s="348" t="n"/>
       <c r="D17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="336" t="n"/>
-      <c r="F17" s="334" t="n"/>
-      <c r="G17" s="331" t="n">
+      <c r="E17" s="349" t="n"/>
+      <c r="F17" s="347" t="n"/>
+      <c r="G17" s="344" t="n">
         <v>45091</v>
       </c>
       <c r="H17" s="70" t="inlineStr">
@@ -7152,15 +7461,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I17" s="335" t="n"/>
+      <c r="I17" s="348" t="n"/>
       <c r="J17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="336" t="n"/>
-      <c r="L17" s="334" t="n"/>
-      <c r="M17" s="331" t="n">
+      <c r="K17" s="349" t="n"/>
+      <c r="L17" s="347" t="n"/>
+      <c r="M17" s="344" t="n">
         <v>45121</v>
       </c>
       <c r="N17" s="69" t="inlineStr">
@@ -7168,15 +7477,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O17" s="335" t="n"/>
+      <c r="O17" s="348" t="n"/>
       <c r="P17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="336" t="n"/>
-      <c r="R17" s="334" t="n"/>
-      <c r="S17" s="337" t="n">
+      <c r="Q17" s="349" t="n"/>
+      <c r="R17" s="347" t="n"/>
+      <c r="S17" s="350" t="n">
         <v>45152</v>
       </c>
       <c r="T17" s="69" t="inlineStr">
@@ -7184,17 +7493,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U17" s="335" t="n"/>
+      <c r="U17" s="348" t="n"/>
       <c r="V17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W17" s="336" t="n"/>
-      <c r="X17" s="334" t="n"/>
+      <c r="W17" s="349" t="n"/>
+      <c r="X17" s="347" t="n"/>
     </row>
     <row r="18" ht="16.15" customHeight="1" s="257">
-      <c r="A18" s="331" t="n">
+      <c r="A18" s="344" t="n">
         <v>45061</v>
       </c>
       <c r="B18" s="69" t="inlineStr">
@@ -7202,15 +7511,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C18" s="335" t="n"/>
+      <c r="C18" s="348" t="n"/>
       <c r="D18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="336" t="n"/>
-      <c r="F18" s="334" t="n"/>
-      <c r="G18" s="331" t="n">
+      <c r="E18" s="349" t="n"/>
+      <c r="F18" s="347" t="n"/>
+      <c r="G18" s="344" t="n">
         <v>45092</v>
       </c>
       <c r="H18" s="70" t="inlineStr">
@@ -7218,15 +7527,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I18" s="335" t="n"/>
+      <c r="I18" s="348" t="n"/>
       <c r="J18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="336" t="n"/>
-      <c r="L18" s="334" t="n"/>
-      <c r="M18" s="331" t="n">
+      <c r="K18" s="349" t="n"/>
+      <c r="L18" s="347" t="n"/>
+      <c r="M18" s="344" t="n">
         <v>45122</v>
       </c>
       <c r="N18" s="69" t="inlineStr">
@@ -7234,15 +7543,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O18" s="335" t="n"/>
+      <c r="O18" s="348" t="n"/>
       <c r="P18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="336" t="n"/>
-      <c r="R18" s="334" t="n"/>
-      <c r="S18" s="337" t="n">
+      <c r="Q18" s="349" t="n"/>
+      <c r="R18" s="347" t="n"/>
+      <c r="S18" s="350" t="n">
         <v>45153</v>
       </c>
       <c r="T18" s="69" t="inlineStr">
@@ -7250,17 +7559,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U18" s="335" t="n"/>
+      <c r="U18" s="348" t="n"/>
       <c r="V18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W18" s="336" t="n"/>
-      <c r="X18" s="334" t="n"/>
+      <c r="W18" s="349" t="n"/>
+      <c r="X18" s="347" t="n"/>
     </row>
     <row r="19" ht="16.15" customHeight="1" s="257">
-      <c r="A19" s="331" t="n">
+      <c r="A19" s="344" t="n">
         <v>45062</v>
       </c>
       <c r="B19" s="69" t="inlineStr">
@@ -7268,15 +7577,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C19" s="335" t="n"/>
+      <c r="C19" s="348" t="n"/>
       <c r="D19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="336" t="n"/>
-      <c r="F19" s="334" t="n"/>
-      <c r="G19" s="331" t="n">
+      <c r="E19" s="349" t="n"/>
+      <c r="F19" s="347" t="n"/>
+      <c r="G19" s="344" t="n">
         <v>45093</v>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -7284,15 +7593,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I19" s="335" t="inlineStr">
+      <c r="I19" s="348" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="50" t="n"/>
-      <c r="K19" s="336" t="n"/>
-      <c r="L19" s="334" t="n"/>
-      <c r="M19" s="331" t="n">
+      <c r="K19" s="349" t="n"/>
+      <c r="L19" s="347" t="n"/>
+      <c r="M19" s="344" t="n">
         <v>45123</v>
       </c>
       <c r="N19" s="69" t="inlineStr">
@@ -7300,15 +7609,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O19" s="335" t="n"/>
+      <c r="O19" s="348" t="n"/>
       <c r="P19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="336" t="n"/>
-      <c r="R19" s="334" t="n"/>
-      <c r="S19" s="337" t="n">
+      <c r="Q19" s="349" t="n"/>
+      <c r="R19" s="347" t="n"/>
+      <c r="S19" s="350" t="n">
         <v>45154</v>
       </c>
       <c r="T19" s="69" t="inlineStr">
@@ -7316,17 +7625,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U19" s="335" t="n"/>
+      <c r="U19" s="348" t="n"/>
       <c r="V19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W19" s="336" t="n"/>
-      <c r="X19" s="334" t="n"/>
+      <c r="W19" s="349" t="n"/>
+      <c r="X19" s="347" t="n"/>
     </row>
     <row r="20" ht="16.15" customHeight="1" s="257">
-      <c r="A20" s="331" t="n">
+      <c r="A20" s="344" t="n">
         <v>45063</v>
       </c>
       <c r="B20" s="69" t="inlineStr">
@@ -7334,15 +7643,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C20" s="335" t="n"/>
+      <c r="C20" s="348" t="n"/>
       <c r="D20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="336" t="n"/>
-      <c r="F20" s="334" t="n"/>
-      <c r="G20" s="331" t="n">
+      <c r="E20" s="349" t="n"/>
+      <c r="F20" s="347" t="n"/>
+      <c r="G20" s="344" t="n">
         <v>45094</v>
       </c>
       <c r="H20" s="70" t="inlineStr">
@@ -7350,15 +7659,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I20" s="335" t="inlineStr">
+      <c r="I20" s="348" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="50" t="n"/>
-      <c r="K20" s="336" t="n"/>
-      <c r="L20" s="334" t="n"/>
-      <c r="M20" s="331" t="n">
+      <c r="K20" s="349" t="n"/>
+      <c r="L20" s="347" t="n"/>
+      <c r="M20" s="344" t="n">
         <v>45124</v>
       </c>
       <c r="N20" s="69" t="inlineStr">
@@ -7366,15 +7675,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O20" s="335" t="n"/>
+      <c r="O20" s="348" t="n"/>
       <c r="P20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="336" t="n"/>
-      <c r="R20" s="334" t="n"/>
-      <c r="S20" s="337" t="n">
+      <c r="Q20" s="349" t="n"/>
+      <c r="R20" s="347" t="n"/>
+      <c r="S20" s="350" t="n">
         <v>45155</v>
       </c>
       <c r="T20" s="69" t="inlineStr">
@@ -7382,17 +7691,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U20" s="335" t="n"/>
+      <c r="U20" s="348" t="n"/>
       <c r="V20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W20" s="336" t="n"/>
-      <c r="X20" s="334" t="n"/>
+      <c r="W20" s="349" t="n"/>
+      <c r="X20" s="347" t="n"/>
     </row>
     <row r="21" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A21" s="331" t="n">
+      <c r="A21" s="344" t="n">
         <v>45064</v>
       </c>
       <c r="B21" s="69" t="inlineStr">
@@ -7400,15 +7709,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C21" s="335" t="n"/>
+      <c r="C21" s="348" t="n"/>
       <c r="D21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="336" t="n"/>
-      <c r="F21" s="334" t="n"/>
-      <c r="G21" s="331" t="n">
+      <c r="E21" s="349" t="n"/>
+      <c r="F21" s="347" t="n"/>
+      <c r="G21" s="344" t="n">
         <v>45095</v>
       </c>
       <c r="H21" s="70" t="inlineStr">
@@ -7416,15 +7725,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I21" s="335" t="inlineStr">
+      <c r="I21" s="348" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="50" t="n"/>
-      <c r="K21" s="336" t="n"/>
-      <c r="L21" s="334" t="n"/>
-      <c r="M21" s="331" t="n">
+      <c r="K21" s="349" t="n"/>
+      <c r="L21" s="347" t="n"/>
+      <c r="M21" s="344" t="n">
         <v>45125</v>
       </c>
       <c r="N21" s="69" t="inlineStr">
@@ -7432,15 +7741,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O21" s="335" t="n"/>
+      <c r="O21" s="348" t="n"/>
       <c r="P21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="336" t="n"/>
-      <c r="R21" s="334" t="n"/>
-      <c r="S21" s="345" t="n">
+      <c r="Q21" s="349" t="n"/>
+      <c r="R21" s="347" t="n"/>
+      <c r="S21" s="358" t="n">
         <v>45156</v>
       </c>
       <c r="T21" s="71" t="inlineStr">
@@ -7448,17 +7757,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U21" s="346" t="n"/>
+      <c r="U21" s="359" t="n"/>
       <c r="V21" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W21" s="347" t="n"/>
-      <c r="X21" s="348" t="n"/>
+      <c r="W21" s="360" t="n"/>
+      <c r="X21" s="361" t="n"/>
     </row>
     <row r="22" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A22" s="331" t="n">
+      <c r="A22" s="344" t="n">
         <v>45065</v>
       </c>
       <c r="B22" s="69" t="inlineStr">
@@ -7466,15 +7775,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C22" s="335" t="n"/>
+      <c r="C22" s="348" t="n"/>
       <c r="D22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="336" t="n"/>
-      <c r="F22" s="334" t="n"/>
-      <c r="G22" s="331" t="n">
+      <c r="E22" s="349" t="n"/>
+      <c r="F22" s="347" t="n"/>
+      <c r="G22" s="344" t="n">
         <v>45096</v>
       </c>
       <c r="H22" s="70" t="inlineStr">
@@ -7482,11 +7791,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I22" s="335" t="n"/>
+      <c r="I22" s="348" t="n"/>
       <c r="J22" s="50" t="n"/>
-      <c r="K22" s="336" t="n"/>
-      <c r="L22" s="334" t="n"/>
-      <c r="M22" s="331" t="n">
+      <c r="K22" s="349" t="n"/>
+      <c r="L22" s="347" t="n"/>
+      <c r="M22" s="344" t="n">
         <v>45126</v>
       </c>
       <c r="N22" s="69" t="inlineStr">
@@ -7494,27 +7803,27 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O22" s="335" t="n"/>
+      <c r="O22" s="348" t="n"/>
       <c r="P22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="336" t="n"/>
-      <c r="R22" s="334" t="n"/>
+      <c r="Q22" s="349" t="n"/>
+      <c r="R22" s="347" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="U22" s="349" t="n"/>
+      <c r="U22" s="362" t="n"/>
       <c r="V22" s="238" t="n"/>
-      <c r="W22" s="350" t="n"/>
-      <c r="X22" s="350" t="n"/>
+      <c r="W22" s="363" t="n"/>
+      <c r="X22" s="363" t="n"/>
     </row>
     <row r="23" ht="16.15" customHeight="1" s="257">
-      <c r="A23" s="331" t="n">
+      <c r="A23" s="344" t="n">
         <v>45066</v>
       </c>
       <c r="B23" s="69" t="inlineStr">
@@ -7522,15 +7831,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C23" s="335" t="n"/>
+      <c r="C23" s="348" t="n"/>
       <c r="D23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="336" t="n"/>
-      <c r="F23" s="334" t="n"/>
-      <c r="G23" s="331" t="n">
+      <c r="E23" s="349" t="n"/>
+      <c r="F23" s="347" t="n"/>
+      <c r="G23" s="344" t="n">
         <v>45097</v>
       </c>
       <c r="H23" s="70" t="inlineStr">
@@ -7538,11 +7847,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I23" s="335" t="n"/>
+      <c r="I23" s="348" t="n"/>
       <c r="J23" s="50" t="n"/>
-      <c r="K23" s="336" t="n"/>
-      <c r="L23" s="334" t="n"/>
-      <c r="M23" s="331" t="n">
+      <c r="K23" s="349" t="n"/>
+      <c r="L23" s="347" t="n"/>
+      <c r="M23" s="344" t="n">
         <v>45127</v>
       </c>
       <c r="N23" s="69" t="inlineStr">
@@ -7550,31 +7859,31 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O23" s="335" t="n"/>
+      <c r="O23" s="348" t="n"/>
       <c r="P23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="336" t="n"/>
-      <c r="R23" s="334" t="n"/>
-      <c r="S23" s="351" t="inlineStr">
+      <c r="Q23" s="349" t="n"/>
+      <c r="R23" s="347" t="n"/>
+      <c r="S23" s="364" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="T23" s="352" t="inlineStr">
+      <c r="T23" s="365" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="U23" s="329" t="n"/>
-      <c r="V23" s="329" t="n"/>
-      <c r="W23" s="329" t="n"/>
-      <c r="X23" s="353" t="n"/>
+      <c r="U23" s="342" t="n"/>
+      <c r="V23" s="342" t="n"/>
+      <c r="W23" s="342" t="n"/>
+      <c r="X23" s="366" t="n"/>
     </row>
     <row r="24" ht="16.15" customHeight="1" s="257">
-      <c r="A24" s="331" t="n">
+      <c r="A24" s="344" t="n">
         <v>45067</v>
       </c>
       <c r="B24" s="69" t="inlineStr">
@@ -7582,15 +7891,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C24" s="335" t="n"/>
+      <c r="C24" s="348" t="n"/>
       <c r="D24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="336" t="n"/>
-      <c r="F24" s="334" t="n"/>
-      <c r="G24" s="331" t="n">
+      <c r="E24" s="349" t="n"/>
+      <c r="F24" s="347" t="n"/>
+      <c r="G24" s="344" t="n">
         <v>45098</v>
       </c>
       <c r="H24" s="70" t="inlineStr">
@@ -7598,11 +7907,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I24" s="335" t="n"/>
+      <c r="I24" s="348" t="n"/>
       <c r="J24" s="50" t="n"/>
-      <c r="K24" s="336" t="n"/>
-      <c r="L24" s="334" t="n"/>
-      <c r="M24" s="331" t="n">
+      <c r="K24" s="349" t="n"/>
+      <c r="L24" s="347" t="n"/>
+      <c r="M24" s="344" t="n">
         <v>45128</v>
       </c>
       <c r="N24" s="69" t="inlineStr">
@@ -7610,14 +7919,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O24" s="335" t="n"/>
+      <c r="O24" s="348" t="n"/>
       <c r="P24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="336" t="n"/>
-      <c r="R24" s="334" t="n"/>
+      <c r="Q24" s="349" t="n"/>
+      <c r="R24" s="347" t="n"/>
       <c r="S24" s="73" t="n">
         <v>1</v>
       </c>
@@ -7626,13 +7935,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U24" s="279" t="n"/>
-      <c r="V24" s="279" t="n"/>
-      <c r="W24" s="279" t="n"/>
-      <c r="X24" s="280" t="n"/>
+      <c r="U24" s="290" t="n"/>
+      <c r="V24" s="290" t="n"/>
+      <c r="W24" s="290" t="n"/>
+      <c r="X24" s="291" t="n"/>
     </row>
     <row r="25" ht="16.15" customHeight="1" s="257">
-      <c r="A25" s="331" t="n">
+      <c r="A25" s="344" t="n">
         <v>45068</v>
       </c>
       <c r="B25" s="69" t="inlineStr">
@@ -7640,15 +7949,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C25" s="335" t="n"/>
+      <c r="C25" s="348" t="n"/>
       <c r="D25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="336" t="n"/>
-      <c r="F25" s="334" t="n"/>
-      <c r="G25" s="331" t="n">
+      <c r="E25" s="349" t="n"/>
+      <c r="F25" s="347" t="n"/>
+      <c r="G25" s="344" t="n">
         <v>45099</v>
       </c>
       <c r="H25" s="70" t="inlineStr">
@@ -7656,11 +7965,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I25" s="335" t="n"/>
+      <c r="I25" s="348" t="n"/>
       <c r="J25" s="50" t="n"/>
-      <c r="K25" s="336" t="n"/>
-      <c r="L25" s="334" t="n"/>
-      <c r="M25" s="331" t="n">
+      <c r="K25" s="349" t="n"/>
+      <c r="L25" s="347" t="n"/>
+      <c r="M25" s="344" t="n">
         <v>45129</v>
       </c>
       <c r="N25" s="69" t="inlineStr">
@@ -7668,14 +7977,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O25" s="335" t="n"/>
+      <c r="O25" s="348" t="n"/>
       <c r="P25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="336" t="n"/>
-      <c r="R25" s="334" t="n"/>
+      <c r="Q25" s="349" t="n"/>
+      <c r="R25" s="347" t="n"/>
       <c r="S25" s="73" t="n">
         <v>2</v>
       </c>
@@ -7684,13 +7993,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U25" s="279" t="n"/>
-      <c r="V25" s="279" t="n"/>
-      <c r="W25" s="279" t="n"/>
-      <c r="X25" s="280" t="n"/>
+      <c r="U25" s="290" t="n"/>
+      <c r="V25" s="290" t="n"/>
+      <c r="W25" s="290" t="n"/>
+      <c r="X25" s="291" t="n"/>
     </row>
     <row r="26" ht="16.15" customHeight="1" s="257">
-      <c r="A26" s="331" t="n">
+      <c r="A26" s="344" t="n">
         <v>45069</v>
       </c>
       <c r="B26" s="69" t="inlineStr">
@@ -7698,36 +8007,36 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C26" s="335" t="n"/>
+      <c r="C26" s="348" t="n"/>
       <c r="D26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="336" t="n"/>
-      <c r="F26" s="334" t="n"/>
-      <c r="G26" s="338" t="n">
+      <c r="E26" s="349" t="n"/>
+      <c r="F26" s="347" t="n"/>
+      <c r="G26" s="351" t="n">
         <v>45100</v>
       </c>
-      <c r="H26" s="344" t="inlineStr">
+      <c r="H26" s="357" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I26" s="340">
+      <c r="I26" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="341" t="n"/>
-      <c r="K26" s="342">
+      <c r="J26" s="354" t="n"/>
+      <c r="K26" s="355">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="343">
+      <c r="L26" s="356">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="331" t="n">
+      <c r="M26" s="344" t="n">
         <v>45130</v>
       </c>
       <c r="N26" s="69" t="inlineStr">
@@ -7735,14 +8044,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O26" s="335" t="n"/>
+      <c r="O26" s="348" t="n"/>
       <c r="P26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="336" t="n"/>
-      <c r="R26" s="334" t="n"/>
+      <c r="Q26" s="349" t="n"/>
+      <c r="R26" s="347" t="n"/>
       <c r="S26" s="73" t="n">
         <v>3</v>
       </c>
@@ -7751,13 +8060,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U26" s="279" t="n"/>
-      <c r="V26" s="279" t="n"/>
-      <c r="W26" s="279" t="n"/>
-      <c r="X26" s="280" t="n"/>
+      <c r="U26" s="290" t="n"/>
+      <c r="V26" s="290" t="n"/>
+      <c r="W26" s="290" t="n"/>
+      <c r="X26" s="291" t="n"/>
     </row>
     <row r="27" ht="16.15" customHeight="1" s="257">
-      <c r="A27" s="331" t="n">
+      <c r="A27" s="344" t="n">
         <v>45070</v>
       </c>
       <c r="B27" s="69" t="inlineStr">
@@ -7765,15 +8074,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C27" s="335" t="n"/>
+      <c r="C27" s="348" t="n"/>
       <c r="D27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="336" t="n"/>
-      <c r="F27" s="334" t="n"/>
-      <c r="G27" s="331" t="n">
+      <c r="E27" s="349" t="n"/>
+      <c r="F27" s="347" t="n"/>
+      <c r="G27" s="344" t="n">
         <v>45101</v>
       </c>
       <c r="H27" s="70" t="inlineStr">
@@ -7781,20 +8090,20 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I27" s="335">
+      <c r="I27" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J27" s="50" t="n"/>
-      <c r="K27" s="336">
+      <c r="K27" s="349">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="334">
+      <c r="L27" s="347">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="331" t="n">
+      <c r="M27" s="344" t="n">
         <v>45131</v>
       </c>
       <c r="N27" s="69" t="inlineStr">
@@ -7802,14 +8111,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O27" s="335" t="n"/>
+      <c r="O27" s="348" t="n"/>
       <c r="P27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="336" t="n"/>
-      <c r="R27" s="334" t="n"/>
+      <c r="Q27" s="349" t="n"/>
+      <c r="R27" s="347" t="n"/>
       <c r="S27" s="73" t="n">
         <v>4</v>
       </c>
@@ -7818,13 +8127,13 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U27" s="279" t="n"/>
-      <c r="V27" s="279" t="n"/>
-      <c r="W27" s="279" t="n"/>
-      <c r="X27" s="280" t="n"/>
+      <c r="U27" s="290" t="n"/>
+      <c r="V27" s="290" t="n"/>
+      <c r="W27" s="290" t="n"/>
+      <c r="X27" s="291" t="n"/>
     </row>
     <row r="28" ht="16.15" customHeight="1" s="257">
-      <c r="A28" s="331" t="n">
+      <c r="A28" s="344" t="n">
         <v>45071</v>
       </c>
       <c r="B28" s="69" t="inlineStr">
@@ -7832,15 +8141,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C28" s="335" t="n"/>
+      <c r="C28" s="348" t="n"/>
       <c r="D28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="336" t="n"/>
-      <c r="F28" s="334" t="n"/>
-      <c r="G28" s="331" t="n">
+      <c r="E28" s="349" t="n"/>
+      <c r="F28" s="347" t="n"/>
+      <c r="G28" s="344" t="n">
         <v>45102</v>
       </c>
       <c r="H28" s="70" t="inlineStr">
@@ -7848,20 +8157,20 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I28" s="335">
+      <c r="I28" s="348">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
       <c r="J28" s="50" t="n"/>
-      <c r="K28" s="336">
+      <c r="K28" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="347">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="331" t="n">
+      <c r="M28" s="344" t="n">
         <v>45132</v>
       </c>
       <c r="N28" s="69" t="inlineStr">
@@ -7869,14 +8178,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O28" s="335" t="n"/>
+      <c r="O28" s="348" t="n"/>
       <c r="P28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="336" t="n"/>
-      <c r="R28" s="334" t="n"/>
+      <c r="Q28" s="349" t="n"/>
+      <c r="R28" s="347" t="n"/>
       <c r="S28" s="73" t="n">
         <v>5</v>
       </c>
@@ -7885,13 +8194,13 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U28" s="279" t="n"/>
-      <c r="V28" s="279" t="n"/>
-      <c r="W28" s="279" t="n"/>
-      <c r="X28" s="280" t="n"/>
+      <c r="U28" s="290" t="n"/>
+      <c r="V28" s="290" t="n"/>
+      <c r="W28" s="290" t="n"/>
+      <c r="X28" s="291" t="n"/>
     </row>
     <row r="29" ht="16.15" customHeight="1" s="257">
-      <c r="A29" s="331" t="n">
+      <c r="A29" s="344" t="n">
         <v>45072</v>
       </c>
       <c r="B29" s="69" t="inlineStr">
@@ -7899,7 +8208,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C29" s="335">
+      <c r="C29" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -7908,15 +8217,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="336">
+      <c r="E29" s="349">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="347">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="331" t="n">
+      <c r="G29" s="344" t="n">
         <v>45103</v>
       </c>
       <c r="H29" s="70" t="inlineStr">
@@ -7924,11 +8233,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I29" s="335" t="n"/>
+      <c r="I29" s="348" t="n"/>
       <c r="J29" s="50" t="n"/>
-      <c r="K29" s="336" t="n"/>
-      <c r="L29" s="334" t="n"/>
-      <c r="M29" s="331" t="n">
+      <c r="K29" s="349" t="n"/>
+      <c r="L29" s="347" t="n"/>
+      <c r="M29" s="344" t="n">
         <v>45133</v>
       </c>
       <c r="N29" s="69" t="inlineStr">
@@ -7936,14 +8245,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O29" s="335" t="n"/>
+      <c r="O29" s="348" t="n"/>
       <c r="P29" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="336" t="n"/>
-      <c r="R29" s="334" t="n"/>
+      <c r="Q29" s="349" t="n"/>
+      <c r="R29" s="347" t="n"/>
       <c r="S29" s="73" t="n">
         <v>6</v>
       </c>
@@ -7952,13 +8261,13 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U29" s="279" t="n"/>
-      <c r="V29" s="279" t="n"/>
-      <c r="W29" s="279" t="n"/>
-      <c r="X29" s="280" t="n"/>
+      <c r="U29" s="290" t="n"/>
+      <c r="V29" s="290" t="n"/>
+      <c r="W29" s="290" t="n"/>
+      <c r="X29" s="291" t="n"/>
     </row>
     <row r="30" ht="16.15" customHeight="1" s="257">
-      <c r="A30" s="331" t="n">
+      <c r="A30" s="344" t="n">
         <v>45073</v>
       </c>
       <c r="B30" s="69" t="inlineStr">
@@ -7966,7 +8275,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C30" s="335">
+      <c r="C30" s="348">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -7975,15 +8284,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="334">
+      <c r="F30" s="347">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="331" t="n">
+      <c r="G30" s="344" t="n">
         <v>45104</v>
       </c>
       <c r="H30" s="70" t="inlineStr">
@@ -7991,11 +8300,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I30" s="335" t="n"/>
+      <c r="I30" s="348" t="n"/>
       <c r="J30" s="50" t="n"/>
-      <c r="K30" s="336" t="n"/>
-      <c r="L30" s="334" t="n"/>
-      <c r="M30" s="331" t="n">
+      <c r="K30" s="349" t="n"/>
+      <c r="L30" s="347" t="n"/>
+      <c r="M30" s="344" t="n">
         <v>45134</v>
       </c>
       <c r="N30" s="69" t="inlineStr">
@@ -8003,14 +8312,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O30" s="335" t="n"/>
+      <c r="O30" s="348" t="n"/>
       <c r="P30" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="336" t="n"/>
-      <c r="R30" s="334" t="n"/>
+      <c r="Q30" s="349" t="n"/>
+      <c r="R30" s="347" t="n"/>
       <c r="S30" s="73" t="n">
         <v>7</v>
       </c>
@@ -8019,38 +8328,38 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U30" s="279" t="n"/>
-      <c r="V30" s="279" t="n"/>
-      <c r="W30" s="279" t="n"/>
-      <c r="X30" s="280" t="n"/>
+      <c r="U30" s="290" t="n"/>
+      <c r="V30" s="290" t="n"/>
+      <c r="W30" s="290" t="n"/>
+      <c r="X30" s="291" t="n"/>
     </row>
     <row r="31" ht="16.15" customHeight="1" s="257">
-      <c r="A31" s="338" t="n">
+      <c r="A31" s="351" t="n">
         <v>45074</v>
       </c>
-      <c r="B31" s="339" t="inlineStr">
+      <c r="B31" s="352" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="C31" s="340">
+      <c r="C31" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="341" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="342">
+      <c r="D31" s="354" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="355">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="343">
+      <c r="F31" s="356">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="331" t="n">
+      <c r="G31" s="344" t="n">
         <v>45105</v>
       </c>
       <c r="H31" s="70" t="inlineStr">
@@ -8058,11 +8367,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I31" s="335" t="n"/>
+      <c r="I31" s="348" t="n"/>
       <c r="J31" s="50" t="n"/>
-      <c r="K31" s="336" t="n"/>
-      <c r="L31" s="334" t="n"/>
-      <c r="M31" s="331" t="n">
+      <c r="K31" s="349" t="n"/>
+      <c r="L31" s="347" t="n"/>
+      <c r="M31" s="344" t="n">
         <v>45135</v>
       </c>
       <c r="N31" s="69" t="inlineStr">
@@ -8070,14 +8379,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O31" s="335" t="n"/>
+      <c r="O31" s="348" t="n"/>
       <c r="P31" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="336" t="n"/>
-      <c r="R31" s="334" t="n"/>
+      <c r="Q31" s="349" t="n"/>
+      <c r="R31" s="347" t="n"/>
       <c r="S31" s="73" t="n">
         <v>8</v>
       </c>
@@ -8086,13 +8395,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U31" s="279" t="n"/>
-      <c r="V31" s="279" t="n"/>
-      <c r="W31" s="279" t="n"/>
-      <c r="X31" s="280" t="n"/>
+      <c r="U31" s="290" t="n"/>
+      <c r="V31" s="290" t="n"/>
+      <c r="W31" s="290" t="n"/>
+      <c r="X31" s="291" t="n"/>
     </row>
     <row r="32" ht="16.15" customHeight="1" s="257">
-      <c r="A32" s="331" t="n">
+      <c r="A32" s="344" t="n">
         <v>45075</v>
       </c>
       <c r="B32" s="69" t="inlineStr">
@@ -8100,15 +8409,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C32" s="335" t="n"/>
+      <c r="C32" s="348" t="n"/>
       <c r="D32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="336" t="n"/>
-      <c r="F32" s="334" t="n"/>
-      <c r="G32" s="331" t="n">
+      <c r="E32" s="349" t="n"/>
+      <c r="F32" s="347" t="n"/>
+      <c r="G32" s="344" t="n">
         <v>45106</v>
       </c>
       <c r="H32" s="70" t="inlineStr">
@@ -8116,11 +8425,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I32" s="335" t="n"/>
+      <c r="I32" s="348" t="n"/>
       <c r="J32" s="50" t="n"/>
-      <c r="K32" s="336" t="n"/>
-      <c r="L32" s="334" t="n"/>
-      <c r="M32" s="331" t="n">
+      <c r="K32" s="349" t="n"/>
+      <c r="L32" s="347" t="n"/>
+      <c r="M32" s="344" t="n">
         <v>45136</v>
       </c>
       <c r="N32" s="69" t="inlineStr">
@@ -8128,14 +8437,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O32" s="335" t="n"/>
+      <c r="O32" s="348" t="n"/>
       <c r="P32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="336" t="n"/>
-      <c r="R32" s="334" t="n"/>
+      <c r="Q32" s="349" t="n"/>
+      <c r="R32" s="347" t="n"/>
       <c r="S32" s="73" t="n">
         <v>9</v>
       </c>
@@ -8144,13 +8453,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U32" s="279" t="n"/>
-      <c r="V32" s="279" t="n"/>
-      <c r="W32" s="279" t="n"/>
-      <c r="X32" s="280" t="n"/>
+      <c r="U32" s="290" t="n"/>
+      <c r="V32" s="290" t="n"/>
+      <c r="W32" s="290" t="n"/>
+      <c r="X32" s="291" t="n"/>
     </row>
     <row r="33" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A33" s="331" t="n">
+      <c r="A33" s="344" t="n">
         <v>45076</v>
       </c>
       <c r="B33" s="69" t="inlineStr">
@@ -8158,15 +8467,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C33" s="335" t="n"/>
+      <c r="C33" s="348" t="n"/>
       <c r="D33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="336" t="n"/>
-      <c r="F33" s="334" t="n"/>
-      <c r="G33" s="354" t="n">
+      <c r="E33" s="349" t="n"/>
+      <c r="F33" s="347" t="n"/>
+      <c r="G33" s="367" t="n">
         <v>45107</v>
       </c>
       <c r="H33" s="82" t="inlineStr">
@@ -8174,20 +8483,20 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I33" s="346">
+      <c r="I33" s="359">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J33" s="60" t="n"/>
-      <c r="K33" s="347">
+      <c r="K33" s="360">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="348">
+      <c r="L33" s="361">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="331" t="n">
+      <c r="M33" s="344" t="n">
         <v>45137</v>
       </c>
       <c r="N33" s="69" t="inlineStr">
@@ -8195,14 +8504,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O33" s="335" t="n"/>
+      <c r="O33" s="348" t="n"/>
       <c r="P33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="336" t="n"/>
-      <c r="R33" s="334" t="n"/>
+      <c r="Q33" s="349" t="n"/>
+      <c r="R33" s="347" t="n"/>
       <c r="S33" s="77" t="n">
         <v>10</v>
       </c>
@@ -8211,13 +8520,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U33" s="355" t="n"/>
-      <c r="V33" s="355" t="n"/>
-      <c r="W33" s="355" t="n"/>
-      <c r="X33" s="356" t="n"/>
+      <c r="U33" s="368" t="n"/>
+      <c r="V33" s="368" t="n"/>
+      <c r="W33" s="368" t="n"/>
+      <c r="X33" s="369" t="n"/>
     </row>
     <row r="34" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A34" s="354" t="n">
+      <c r="A34" s="367" t="n">
         <v>45077</v>
       </c>
       <c r="B34" s="71" t="inlineStr">
@@ -8225,20 +8534,20 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C34" s="346" t="n"/>
+      <c r="C34" s="359" t="n"/>
       <c r="D34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="347" t="n"/>
-      <c r="F34" s="348" t="n"/>
-      <c r="G34" s="357" t="n"/>
-      <c r="I34" s="349" t="n"/>
+      <c r="E34" s="360" t="n"/>
+      <c r="F34" s="361" t="n"/>
+      <c r="G34" s="370" t="n"/>
+      <c r="I34" s="362" t="n"/>
       <c r="J34" s="238" t="n"/>
-      <c r="K34" s="349" t="n"/>
-      <c r="L34" s="349" t="n"/>
-      <c r="M34" s="354" t="n">
+      <c r="K34" s="362" t="n"/>
+      <c r="L34" s="362" t="n"/>
+      <c r="M34" s="367" t="n">
         <v>45138</v>
       </c>
       <c r="N34" s="71" t="inlineStr">
@@ -8246,14 +8555,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O34" s="346" t="n"/>
+      <c r="O34" s="359" t="n"/>
       <c r="P34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="347" t="n"/>
-      <c r="R34" s="348" t="n"/>
+      <c r="Q34" s="360" t="n"/>
+      <c r="R34" s="361" t="n"/>
       <c r="S34" s="238" t="n"/>
       <c r="T34" s="238" t="inlineStr">
         <is>
@@ -8631,8 +8940,8 @@
         <f>日程表１!T1</f>
         <v/>
       </c>
-      <c r="U1" s="327" t="n"/>
-      <c r="V1" s="327" t="n"/>
+      <c r="U1" s="340" t="n"/>
+      <c r="V1" s="340" t="n"/>
       <c r="W1" s="255" t="inlineStr">
         <is>
           <t>年</t>
@@ -8646,41 +8955,41 @@
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="279" t="n"/>
-      <c r="C2" s="279" t="n"/>
-      <c r="D2" s="279" t="n"/>
-      <c r="E2" s="279" t="n"/>
-      <c r="F2" s="280" t="n"/>
+      <c r="B2" s="290" t="n"/>
+      <c r="C2" s="290" t="n"/>
+      <c r="D2" s="290" t="n"/>
+      <c r="E2" s="290" t="n"/>
+      <c r="F2" s="291" t="n"/>
       <c r="G2" s="251" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="279" t="n"/>
-      <c r="I2" s="279" t="n"/>
-      <c r="J2" s="279" t="n"/>
-      <c r="K2" s="279" t="n"/>
-      <c r="L2" s="280" t="n"/>
+      <c r="H2" s="290" t="n"/>
+      <c r="I2" s="290" t="n"/>
+      <c r="J2" s="290" t="n"/>
+      <c r="K2" s="290" t="n"/>
+      <c r="L2" s="291" t="n"/>
       <c r="M2" s="251" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="279" t="n"/>
-      <c r="O2" s="279" t="n"/>
-      <c r="P2" s="279" t="n"/>
-      <c r="Q2" s="279" t="n"/>
-      <c r="R2" s="280" t="n"/>
+      <c r="N2" s="290" t="n"/>
+      <c r="O2" s="290" t="n"/>
+      <c r="P2" s="290" t="n"/>
+      <c r="Q2" s="290" t="n"/>
+      <c r="R2" s="291" t="n"/>
       <c r="S2" s="251" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="279" t="n"/>
-      <c r="U2" s="279" t="n"/>
-      <c r="V2" s="279" t="n"/>
-      <c r="W2" s="279" t="n"/>
-      <c r="X2" s="280" t="n"/>
+      <c r="T2" s="290" t="n"/>
+      <c r="U2" s="290" t="n"/>
+      <c r="V2" s="290" t="n"/>
+      <c r="W2" s="290" t="n"/>
+      <c r="X2" s="291" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="251" t="inlineStr">
@@ -8698,8 +9007,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="279" t="n"/>
-      <c r="E3" s="280" t="n"/>
+      <c r="D3" s="290" t="n"/>
+      <c r="E3" s="291" t="n"/>
       <c r="F3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8720,8 +9029,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="279" t="n"/>
-      <c r="K3" s="280" t="n"/>
+      <c r="J3" s="290" t="n"/>
+      <c r="K3" s="291" t="n"/>
       <c r="L3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8742,8 +9051,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="279" t="n"/>
-      <c r="Q3" s="280" t="n"/>
+      <c r="P3" s="290" t="n"/>
+      <c r="Q3" s="291" t="n"/>
       <c r="R3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8764,8 +9073,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="279" t="n"/>
-      <c r="W3" s="280" t="n"/>
+      <c r="V3" s="290" t="n"/>
+      <c r="W3" s="291" t="n"/>
       <c r="X3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -8773,7 +9082,7 @@
       </c>
     </row>
     <row r="4" ht="20.45" customHeight="1" s="257">
-      <c r="A4" s="358">
+      <c r="A4" s="371">
         <f>日程表１!A4</f>
         <v/>
       </c>
@@ -8781,15 +9090,15 @@
         <f>日程表１!B4</f>
         <v/>
       </c>
-      <c r="C4" s="332" t="n"/>
+      <c r="C4" s="345" t="n"/>
       <c r="D4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="333" t="n"/>
-      <c r="F4" s="359" t="n"/>
-      <c r="G4" s="358">
+      <c r="E4" s="346" t="n"/>
+      <c r="F4" s="372" t="n"/>
+      <c r="G4" s="371">
         <f>日程表１!G4</f>
         <v/>
       </c>
@@ -8797,15 +9106,15 @@
         <f>日程表１!H4</f>
         <v/>
       </c>
-      <c r="I4" s="332" t="n"/>
+      <c r="I4" s="345" t="n"/>
       <c r="J4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="333" t="n"/>
-      <c r="L4" s="359" t="n"/>
-      <c r="M4" s="358">
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="372" t="n"/>
+      <c r="M4" s="371">
         <f>日程表１!M4</f>
         <v/>
       </c>
@@ -8813,7 +9122,7 @@
         <f>日程表１!N4</f>
         <v/>
       </c>
-      <c r="O4" s="332">
+      <c r="O4" s="345">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -8822,15 +9131,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="333">
+      <c r="Q4" s="346">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="359">
+      <c r="R4" s="372">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="358">
+      <c r="S4" s="371">
         <f>日程表１!S5</f>
         <v/>
       </c>
@@ -8838,17 +9147,17 @@
         <f>日程表１!T5</f>
         <v/>
       </c>
-      <c r="U4" s="332" t="n"/>
+      <c r="U4" s="345" t="n"/>
       <c r="V4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="360" t="n"/>
-      <c r="X4" s="361" t="n"/>
+      <c r="W4" s="373" t="n"/>
+      <c r="X4" s="374" t="n"/>
     </row>
     <row r="5" ht="20.45" customHeight="1" s="257">
-      <c r="A5" s="358">
+      <c r="A5" s="371">
         <f>日程表１!A5</f>
         <v/>
       </c>
@@ -8856,15 +9165,15 @@
         <f>日程表１!B5</f>
         <v/>
       </c>
-      <c r="C5" s="335" t="n"/>
+      <c r="C5" s="348" t="n"/>
       <c r="D5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="336" t="n"/>
-      <c r="F5" s="359" t="n"/>
-      <c r="G5" s="358">
+      <c r="E5" s="349" t="n"/>
+      <c r="F5" s="372" t="n"/>
+      <c r="G5" s="371">
         <f>日程表１!G5</f>
         <v/>
       </c>
@@ -8872,7 +9181,7 @@
         <f>日程表１!H5</f>
         <v/>
       </c>
-      <c r="I5" s="335">
+      <c r="I5" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -8881,40 +9190,40 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="336">
+      <c r="K5" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="359">
+      <c r="L5" s="372">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="362">
+      <c r="M5" s="375">
         <f>日程表１!M5</f>
         <v/>
       </c>
-      <c r="N5" s="363">
+      <c r="N5" s="376">
         <f>日程表１!N5</f>
         <v/>
       </c>
-      <c r="O5" s="340">
+      <c r="O5" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="364" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="342">
+      <c r="P5" s="377" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="355">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="365">
+      <c r="R5" s="378">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="358">
+      <c r="S5" s="371">
         <f>日程表１!S6</f>
         <v/>
       </c>
@@ -8922,17 +9231,17 @@
         <f>日程表１!T6</f>
         <v/>
       </c>
-      <c r="U5" s="335" t="n"/>
+      <c r="U5" s="348" t="n"/>
       <c r="V5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="366" t="n"/>
-      <c r="X5" s="361" t="n"/>
+      <c r="W5" s="379" t="n"/>
+      <c r="X5" s="374" t="n"/>
     </row>
     <row r="6" ht="20.45" customHeight="1" s="257">
-      <c r="A6" s="358">
+      <c r="A6" s="371">
         <f>日程表１!A6</f>
         <v/>
       </c>
@@ -8940,40 +9249,40 @@
         <f>日程表１!B6</f>
         <v/>
       </c>
-      <c r="C6" s="335" t="n"/>
+      <c r="C6" s="348" t="n"/>
       <c r="D6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="336" t="n"/>
-      <c r="F6" s="359" t="n"/>
-      <c r="G6" s="362">
+      <c r="E6" s="349" t="n"/>
+      <c r="F6" s="372" t="n"/>
+      <c r="G6" s="375">
         <f>日程表１!G6</f>
         <v/>
       </c>
-      <c r="H6" s="363">
+      <c r="H6" s="376">
         <f>日程表１!H6</f>
         <v/>
       </c>
-      <c r="I6" s="340">
+      <c r="I6" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="364" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="342">
+      <c r="J6" s="377" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="355">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="365">
+      <c r="L6" s="378">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="358">
+      <c r="M6" s="371">
         <f>日程表１!M6</f>
         <v/>
       </c>
@@ -8981,15 +9290,15 @@
         <f>日程表１!N6</f>
         <v/>
       </c>
-      <c r="O6" s="335" t="n"/>
+      <c r="O6" s="348" t="n"/>
       <c r="P6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="336" t="n"/>
-      <c r="R6" s="359" t="n"/>
-      <c r="S6" s="358">
+      <c r="Q6" s="349" t="n"/>
+      <c r="R6" s="372" t="n"/>
+      <c r="S6" s="371">
         <f>日程表１!S7</f>
         <v/>
       </c>
@@ -8997,17 +9306,17 @@
         <f>日程表１!T7</f>
         <v/>
       </c>
-      <c r="U6" s="335" t="n"/>
+      <c r="U6" s="348" t="n"/>
       <c r="V6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="366" t="n"/>
-      <c r="X6" s="361" t="n"/>
+      <c r="W6" s="379" t="n"/>
+      <c r="X6" s="374" t="n"/>
     </row>
     <row r="7" ht="20.45" customHeight="1" s="257">
-      <c r="A7" s="358">
+      <c r="A7" s="371">
         <f>日程表１!A7</f>
         <v/>
       </c>
@@ -9015,15 +9324,15 @@
         <f>日程表１!B7</f>
         <v/>
       </c>
-      <c r="C7" s="335" t="n"/>
+      <c r="C7" s="348" t="n"/>
       <c r="D7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="336" t="n"/>
-      <c r="F7" s="359" t="n"/>
-      <c r="G7" s="358">
+      <c r="E7" s="349" t="n"/>
+      <c r="F7" s="372" t="n"/>
+      <c r="G7" s="371">
         <f>日程表１!G7</f>
         <v/>
       </c>
@@ -9031,7 +9340,7 @@
         <f>日程表１!H7</f>
         <v/>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="348">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9040,15 +9349,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="336">
+      <c r="K7" s="349">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="359">
+      <c r="L7" s="372">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="358">
+      <c r="M7" s="371">
         <f>日程表１!M7</f>
         <v/>
       </c>
@@ -9056,15 +9365,15 @@
         <f>日程表１!N7</f>
         <v/>
       </c>
-      <c r="O7" s="335" t="n"/>
+      <c r="O7" s="348" t="n"/>
       <c r="P7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="336" t="n"/>
-      <c r="R7" s="359" t="n"/>
-      <c r="S7" s="358">
+      <c r="Q7" s="349" t="n"/>
+      <c r="R7" s="372" t="n"/>
+      <c r="S7" s="371">
         <f>日程表１!S8</f>
         <v/>
       </c>
@@ -9072,17 +9381,17 @@
         <f>日程表１!T8</f>
         <v/>
       </c>
-      <c r="U7" s="335" t="n"/>
+      <c r="U7" s="348" t="n"/>
       <c r="V7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="366" t="n"/>
-      <c r="X7" s="361" t="n"/>
+      <c r="W7" s="379" t="n"/>
+      <c r="X7" s="374" t="n"/>
     </row>
     <row r="8" ht="20.45" customHeight="1" s="257">
-      <c r="A8" s="358">
+      <c r="A8" s="371">
         <f>日程表１!A8</f>
         <v/>
       </c>
@@ -9090,15 +9399,15 @@
         <f>日程表１!B8</f>
         <v/>
       </c>
-      <c r="C8" s="335" t="n"/>
+      <c r="C8" s="348" t="n"/>
       <c r="D8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="336" t="n"/>
-      <c r="F8" s="359" t="n"/>
-      <c r="G8" s="358">
+      <c r="E8" s="349" t="n"/>
+      <c r="F8" s="372" t="n"/>
+      <c r="G8" s="371">
         <f>日程表１!G8</f>
         <v/>
       </c>
@@ -9106,15 +9415,15 @@
         <f>日程表１!H8</f>
         <v/>
       </c>
-      <c r="I8" s="335" t="n"/>
+      <c r="I8" s="348" t="n"/>
       <c r="J8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="336" t="n"/>
-      <c r="L8" s="359" t="n"/>
-      <c r="M8" s="358">
+      <c r="K8" s="349" t="n"/>
+      <c r="L8" s="372" t="n"/>
+      <c r="M8" s="371">
         <f>日程表１!M8</f>
         <v/>
       </c>
@@ -9122,15 +9431,15 @@
         <f>日程表１!N8</f>
         <v/>
       </c>
-      <c r="O8" s="335" t="n"/>
+      <c r="O8" s="348" t="n"/>
       <c r="P8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="336" t="n"/>
-      <c r="R8" s="359" t="n"/>
-      <c r="S8" s="358">
+      <c r="Q8" s="349" t="n"/>
+      <c r="R8" s="372" t="n"/>
+      <c r="S8" s="371">
         <f>日程表１!S9</f>
         <v/>
       </c>
@@ -9138,17 +9447,17 @@
         <f>日程表１!T9</f>
         <v/>
       </c>
-      <c r="U8" s="335" t="n"/>
+      <c r="U8" s="348" t="n"/>
       <c r="V8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="366" t="n"/>
-      <c r="X8" s="361" t="n"/>
+      <c r="W8" s="379" t="n"/>
+      <c r="X8" s="374" t="n"/>
     </row>
     <row r="9" ht="20.45" customHeight="1" s="257">
-      <c r="A9" s="358">
+      <c r="A9" s="371">
         <f>日程表１!A9</f>
         <v/>
       </c>
@@ -9156,15 +9465,15 @@
         <f>日程表１!B9</f>
         <v/>
       </c>
-      <c r="C9" s="335" t="n"/>
+      <c r="C9" s="348" t="n"/>
       <c r="D9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="336" t="n"/>
-      <c r="F9" s="359" t="n"/>
-      <c r="G9" s="358">
+      <c r="E9" s="349" t="n"/>
+      <c r="F9" s="372" t="n"/>
+      <c r="G9" s="371">
         <f>日程表１!G9</f>
         <v/>
       </c>
@@ -9172,15 +9481,15 @@
         <f>日程表１!H9</f>
         <v/>
       </c>
-      <c r="I9" s="335" t="n"/>
+      <c r="I9" s="348" t="n"/>
       <c r="J9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="336" t="n"/>
-      <c r="L9" s="359" t="n"/>
-      <c r="M9" s="358">
+      <c r="K9" s="349" t="n"/>
+      <c r="L9" s="372" t="n"/>
+      <c r="M9" s="371">
         <f>日程表１!M9</f>
         <v/>
       </c>
@@ -9188,15 +9497,15 @@
         <f>日程表１!N9</f>
         <v/>
       </c>
-      <c r="O9" s="335" t="n"/>
+      <c r="O9" s="348" t="n"/>
       <c r="P9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="336" t="n"/>
-      <c r="R9" s="359" t="n"/>
-      <c r="S9" s="358">
+      <c r="Q9" s="349" t="n"/>
+      <c r="R9" s="372" t="n"/>
+      <c r="S9" s="371">
         <f>日程表１!S10</f>
         <v/>
       </c>
@@ -9204,17 +9513,17 @@
         <f>日程表１!T10</f>
         <v/>
       </c>
-      <c r="U9" s="335" t="n"/>
+      <c r="U9" s="348" t="n"/>
       <c r="V9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="366" t="n"/>
-      <c r="X9" s="361" t="n"/>
+      <c r="W9" s="379" t="n"/>
+      <c r="X9" s="374" t="n"/>
     </row>
     <row r="10" ht="20.45" customHeight="1" s="257">
-      <c r="A10" s="358">
+      <c r="A10" s="371">
         <f>日程表１!A10</f>
         <v/>
       </c>
@@ -9222,15 +9531,15 @@
         <f>日程表１!B10</f>
         <v/>
       </c>
-      <c r="C10" s="335" t="n"/>
+      <c r="C10" s="348" t="n"/>
       <c r="D10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="336" t="n"/>
-      <c r="F10" s="359" t="n"/>
-      <c r="G10" s="358">
+      <c r="E10" s="349" t="n"/>
+      <c r="F10" s="372" t="n"/>
+      <c r="G10" s="371">
         <f>日程表１!G10</f>
         <v/>
       </c>
@@ -9238,15 +9547,15 @@
         <f>日程表１!H10</f>
         <v/>
       </c>
-      <c r="I10" s="335" t="n"/>
+      <c r="I10" s="348" t="n"/>
       <c r="J10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="336" t="n"/>
-      <c r="L10" s="359" t="n"/>
-      <c r="M10" s="358">
+      <c r="K10" s="349" t="n"/>
+      <c r="L10" s="372" t="n"/>
+      <c r="M10" s="371">
         <f>日程表１!M10</f>
         <v/>
       </c>
@@ -9254,15 +9563,15 @@
         <f>日程表１!N10</f>
         <v/>
       </c>
-      <c r="O10" s="335" t="n"/>
+      <c r="O10" s="348" t="n"/>
       <c r="P10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="336" t="n"/>
-      <c r="R10" s="359" t="n"/>
-      <c r="S10" s="358">
+      <c r="Q10" s="349" t="n"/>
+      <c r="R10" s="372" t="n"/>
+      <c r="S10" s="371">
         <f>日程表１!S11</f>
         <v/>
       </c>
@@ -9270,17 +9579,17 @@
         <f>日程表１!T11</f>
         <v/>
       </c>
-      <c r="U10" s="335" t="n"/>
+      <c r="U10" s="348" t="n"/>
       <c r="V10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="366" t="n"/>
-      <c r="X10" s="361" t="n"/>
+      <c r="W10" s="379" t="n"/>
+      <c r="X10" s="374" t="n"/>
     </row>
     <row r="11" ht="20.45" customHeight="1" s="257">
-      <c r="A11" s="358">
+      <c r="A11" s="371">
         <f>日程表１!A11</f>
         <v/>
       </c>
@@ -9288,15 +9597,15 @@
         <f>日程表１!B11</f>
         <v/>
       </c>
-      <c r="C11" s="335" t="n"/>
+      <c r="C11" s="348" t="n"/>
       <c r="D11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="336" t="n"/>
-      <c r="F11" s="359" t="n"/>
-      <c r="G11" s="358">
+      <c r="E11" s="349" t="n"/>
+      <c r="F11" s="372" t="n"/>
+      <c r="G11" s="371">
         <f>日程表１!G11</f>
         <v/>
       </c>
@@ -9304,15 +9613,15 @@
         <f>日程表１!H11</f>
         <v/>
       </c>
-      <c r="I11" s="335" t="n"/>
+      <c r="I11" s="348" t="n"/>
       <c r="J11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="336" t="n"/>
-      <c r="L11" s="359" t="n"/>
-      <c r="M11" s="358">
+      <c r="K11" s="349" t="n"/>
+      <c r="L11" s="372" t="n"/>
+      <c r="M11" s="371">
         <f>日程表１!M11</f>
         <v/>
       </c>
@@ -9320,15 +9629,15 @@
         <f>日程表１!N11</f>
         <v/>
       </c>
-      <c r="O11" s="335" t="n"/>
+      <c r="O11" s="348" t="n"/>
       <c r="P11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="336" t="n"/>
-      <c r="R11" s="359" t="n"/>
-      <c r="S11" s="358">
+      <c r="Q11" s="349" t="n"/>
+      <c r="R11" s="372" t="n"/>
+      <c r="S11" s="371">
         <f>日程表１!S12</f>
         <v/>
       </c>
@@ -9336,17 +9645,17 @@
         <f>日程表１!T12</f>
         <v/>
       </c>
-      <c r="U11" s="335" t="n"/>
+      <c r="U11" s="348" t="n"/>
       <c r="V11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="366" t="n"/>
-      <c r="X11" s="361" t="n"/>
+      <c r="W11" s="379" t="n"/>
+      <c r="X11" s="374" t="n"/>
     </row>
     <row r="12" ht="20.45" customHeight="1" s="257">
-      <c r="A12" s="358">
+      <c r="A12" s="371">
         <f>日程表１!A12</f>
         <v/>
       </c>
@@ -9354,40 +9663,40 @@
         <f>日程表１!B12</f>
         <v/>
       </c>
-      <c r="C12" s="335" t="n"/>
+      <c r="C12" s="348" t="n"/>
       <c r="D12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="336" t="n"/>
-      <c r="F12" s="359" t="n"/>
-      <c r="G12" s="362">
+      <c r="E12" s="349" t="n"/>
+      <c r="F12" s="372" t="n"/>
+      <c r="G12" s="375">
         <f>日程表１!G12</f>
         <v/>
       </c>
-      <c r="H12" s="363">
+      <c r="H12" s="376">
         <f>日程表１!H12</f>
         <v/>
       </c>
-      <c r="I12" s="340">
+      <c r="I12" s="353">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="364" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="342">
+      <c r="J12" s="377" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="355">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="365">
+      <c r="L12" s="378">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="358">
+      <c r="M12" s="371">
         <f>日程表１!M12</f>
         <v/>
       </c>
@@ -9395,15 +9704,15 @@
         <f>日程表１!N12</f>
         <v/>
       </c>
-      <c r="O12" s="335" t="n"/>
+      <c r="O12" s="348" t="n"/>
       <c r="P12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="336" t="n"/>
-      <c r="R12" s="359" t="n"/>
-      <c r="S12" s="358">
+      <c r="Q12" s="349" t="n"/>
+      <c r="R12" s="372" t="n"/>
+      <c r="S12" s="371">
         <f>日程表１!S13</f>
         <v/>
       </c>
@@ -9411,17 +9720,17 @@
         <f>日程表１!T13</f>
         <v/>
       </c>
-      <c r="U12" s="335" t="n"/>
+      <c r="U12" s="348" t="n"/>
       <c r="V12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="366" t="n"/>
-      <c r="X12" s="361" t="n"/>
+      <c r="W12" s="379" t="n"/>
+      <c r="X12" s="374" t="n"/>
     </row>
     <row r="13" ht="20.45" customHeight="1" s="257">
-      <c r="A13" s="358">
+      <c r="A13" s="371">
         <f>日程表１!A13</f>
         <v/>
       </c>
@@ -9429,15 +9738,15 @@
         <f>日程表１!B13</f>
         <v/>
       </c>
-      <c r="C13" s="335" t="n"/>
+      <c r="C13" s="348" t="n"/>
       <c r="D13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="336" t="n"/>
-      <c r="F13" s="359" t="n"/>
-      <c r="G13" s="358">
+      <c r="E13" s="349" t="n"/>
+      <c r="F13" s="372" t="n"/>
+      <c r="G13" s="371">
         <f>日程表１!G13</f>
         <v/>
       </c>
@@ -9445,7 +9754,7 @@
         <f>日程表１!H13</f>
         <v/>
       </c>
-      <c r="I13" s="335">
+      <c r="I13" s="348">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -9454,15 +9763,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="336">
+      <c r="K13" s="349">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="359">
+      <c r="L13" s="372">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="358">
+      <c r="M13" s="371">
         <f>日程表１!M13</f>
         <v/>
       </c>
@@ -9470,15 +9779,15 @@
         <f>日程表１!N13</f>
         <v/>
       </c>
-      <c r="O13" s="335" t="n"/>
+      <c r="O13" s="348" t="n"/>
       <c r="P13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="336" t="n"/>
-      <c r="R13" s="359" t="n"/>
-      <c r="S13" s="358" t="n">
+      <c r="Q13" s="349" t="n"/>
+      <c r="R13" s="372" t="n"/>
+      <c r="S13" s="371" t="n">
         <v>10</v>
       </c>
       <c r="T13" s="29" t="inlineStr">
@@ -9486,17 +9795,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U13" s="335" t="n"/>
+      <c r="U13" s="348" t="n"/>
       <c r="V13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="366" t="n"/>
-      <c r="X13" s="361" t="n"/>
+      <c r="W13" s="379" t="n"/>
+      <c r="X13" s="374" t="n"/>
     </row>
     <row r="14" ht="20.45" customHeight="1" s="257">
-      <c r="A14" s="358">
+      <c r="A14" s="371">
         <f>日程表１!A14</f>
         <v/>
       </c>
@@ -9504,15 +9813,15 @@
         <f>日程表１!B14</f>
         <v/>
       </c>
-      <c r="C14" s="335" t="n"/>
+      <c r="C14" s="348" t="n"/>
       <c r="D14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="336" t="n"/>
-      <c r="F14" s="359" t="n"/>
-      <c r="G14" s="358">
+      <c r="E14" s="349" t="n"/>
+      <c r="F14" s="372" t="n"/>
+      <c r="G14" s="371">
         <f>日程表１!G14</f>
         <v/>
       </c>
@@ -9520,7 +9829,7 @@
         <f>日程表１!H14</f>
         <v/>
       </c>
-      <c r="I14" s="335">
+      <c r="I14" s="348">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9529,15 +9838,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="336">
+      <c r="K14" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="359">
+      <c r="L14" s="372">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="358">
+      <c r="M14" s="371">
         <f>日程表１!M14</f>
         <v/>
       </c>
@@ -9545,23 +9854,23 @@
         <f>日程表１!N14</f>
         <v/>
       </c>
-      <c r="O14" s="335" t="n"/>
+      <c r="O14" s="348" t="n"/>
       <c r="P14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="336" t="n"/>
-      <c r="R14" s="359" t="n"/>
+      <c r="Q14" s="349" t="n"/>
+      <c r="R14" s="372" t="n"/>
       <c r="S14" s="256" t="n"/>
       <c r="T14" s="256" t="n"/>
-      <c r="U14" s="349" t="n"/>
+      <c r="U14" s="362" t="n"/>
       <c r="V14" s="255" t="n"/>
-      <c r="W14" s="350" t="n"/>
-      <c r="X14" s="350" t="n"/>
+      <c r="W14" s="363" t="n"/>
+      <c r="X14" s="363" t="n"/>
     </row>
     <row r="15" ht="20.45" customHeight="1" s="257">
-      <c r="A15" s="358">
+      <c r="A15" s="371">
         <f>日程表１!A15</f>
         <v/>
       </c>
@@ -9569,15 +9878,15 @@
         <f>日程表１!B15</f>
         <v/>
       </c>
-      <c r="C15" s="335" t="n"/>
+      <c r="C15" s="348" t="n"/>
       <c r="D15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="336" t="n"/>
-      <c r="F15" s="359" t="n"/>
-      <c r="G15" s="358">
+      <c r="E15" s="349" t="n"/>
+      <c r="F15" s="372" t="n"/>
+      <c r="G15" s="371">
         <f>日程表１!G15</f>
         <v/>
       </c>
@@ -9585,15 +9894,15 @@
         <f>日程表１!H15</f>
         <v/>
       </c>
-      <c r="I15" s="335" t="n"/>
+      <c r="I15" s="348" t="n"/>
       <c r="J15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="336" t="n"/>
-      <c r="L15" s="359" t="n"/>
-      <c r="M15" s="358">
+      <c r="K15" s="349" t="n"/>
+      <c r="L15" s="372" t="n"/>
+      <c r="M15" s="371">
         <f>日程表１!M15</f>
         <v/>
       </c>
@@ -9601,23 +9910,23 @@
         <f>日程表１!N15</f>
         <v/>
       </c>
-      <c r="O15" s="335" t="n"/>
+      <c r="O15" s="348" t="n"/>
       <c r="P15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="336" t="n"/>
-      <c r="R15" s="359" t="n"/>
+      <c r="Q15" s="349" t="n"/>
+      <c r="R15" s="372" t="n"/>
       <c r="S15" s="256" t="n"/>
       <c r="T15" s="256" t="n"/>
-      <c r="U15" s="349" t="n"/>
+      <c r="U15" s="362" t="n"/>
       <c r="V15" s="255" t="n"/>
-      <c r="W15" s="350" t="n"/>
-      <c r="X15" s="350" t="n"/>
+      <c r="W15" s="363" t="n"/>
+      <c r="X15" s="363" t="n"/>
     </row>
     <row r="16" ht="20.45" customHeight="1" s="257">
-      <c r="A16" s="358">
+      <c r="A16" s="371">
         <f>日程表１!A16</f>
         <v/>
       </c>
@@ -9625,15 +9934,15 @@
         <f>日程表１!B16</f>
         <v/>
       </c>
-      <c r="C16" s="335" t="n"/>
+      <c r="C16" s="348" t="n"/>
       <c r="D16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="336" t="n"/>
-      <c r="F16" s="359" t="n"/>
-      <c r="G16" s="358">
+      <c r="E16" s="349" t="n"/>
+      <c r="F16" s="372" t="n"/>
+      <c r="G16" s="371">
         <f>日程表１!G16</f>
         <v/>
       </c>
@@ -9641,15 +9950,15 @@
         <f>日程表１!H16</f>
         <v/>
       </c>
-      <c r="I16" s="335" t="n"/>
+      <c r="I16" s="348" t="n"/>
       <c r="J16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="336" t="n"/>
-      <c r="L16" s="359" t="n"/>
-      <c r="M16" s="358">
+      <c r="K16" s="349" t="n"/>
+      <c r="L16" s="372" t="n"/>
+      <c r="M16" s="371">
         <f>日程表１!M16</f>
         <v/>
       </c>
@@ -9657,23 +9966,23 @@
         <f>日程表１!N16</f>
         <v/>
       </c>
-      <c r="O16" s="335" t="n"/>
+      <c r="O16" s="348" t="n"/>
       <c r="P16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="336" t="n"/>
-      <c r="R16" s="359" t="n"/>
+      <c r="Q16" s="349" t="n"/>
+      <c r="R16" s="372" t="n"/>
       <c r="S16" s="256" t="n"/>
       <c r="T16" s="256" t="n"/>
-      <c r="U16" s="349" t="n"/>
+      <c r="U16" s="362" t="n"/>
       <c r="V16" s="255" t="n"/>
-      <c r="W16" s="350" t="n"/>
-      <c r="X16" s="350" t="n"/>
+      <c r="W16" s="363" t="n"/>
+      <c r="X16" s="363" t="n"/>
     </row>
     <row r="17" ht="20.45" customHeight="1" s="257">
-      <c r="A17" s="358">
+      <c r="A17" s="371">
         <f>日程表１!A17</f>
         <v/>
       </c>
@@ -9681,15 +9990,15 @@
         <f>日程表１!B17</f>
         <v/>
       </c>
-      <c r="C17" s="335" t="n"/>
+      <c r="C17" s="348" t="n"/>
       <c r="D17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="336" t="n"/>
-      <c r="F17" s="359" t="n"/>
-      <c r="G17" s="358">
+      <c r="E17" s="349" t="n"/>
+      <c r="F17" s="372" t="n"/>
+      <c r="G17" s="371">
         <f>日程表１!G17</f>
         <v/>
       </c>
@@ -9697,15 +10006,15 @@
         <f>日程表１!H17</f>
         <v/>
       </c>
-      <c r="I17" s="335" t="n"/>
+      <c r="I17" s="348" t="n"/>
       <c r="J17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="336" t="n"/>
-      <c r="L17" s="359" t="n"/>
-      <c r="M17" s="358">
+      <c r="K17" s="349" t="n"/>
+      <c r="L17" s="372" t="n"/>
+      <c r="M17" s="371">
         <f>日程表１!M17</f>
         <v/>
       </c>
@@ -9713,14 +10022,14 @@
         <f>日程表１!N17</f>
         <v/>
       </c>
-      <c r="O17" s="335" t="n"/>
+      <c r="O17" s="348" t="n"/>
       <c r="P17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="336" t="n"/>
-      <c r="R17" s="359" t="n"/>
+      <c r="Q17" s="349" t="n"/>
+      <c r="R17" s="372" t="n"/>
       <c r="S17" s="254" t="inlineStr">
         <is>
           <t>NO.</t>
@@ -9731,13 +10040,13 @@
           <t>team</t>
         </is>
       </c>
-      <c r="U17" s="279" t="n"/>
-      <c r="V17" s="279" t="n"/>
-      <c r="W17" s="279" t="n"/>
-      <c r="X17" s="280" t="n"/>
+      <c r="U17" s="290" t="n"/>
+      <c r="V17" s="290" t="n"/>
+      <c r="W17" s="290" t="n"/>
+      <c r="X17" s="291" t="n"/>
     </row>
     <row r="18" ht="20.45" customHeight="1" s="257">
-      <c r="A18" s="358">
+      <c r="A18" s="371">
         <f>日程表１!A18</f>
         <v/>
       </c>
@@ -9745,15 +10054,15 @@
         <f>日程表１!B18</f>
         <v/>
       </c>
-      <c r="C18" s="335" t="n"/>
+      <c r="C18" s="348" t="n"/>
       <c r="D18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="336" t="n"/>
-      <c r="F18" s="359" t="n"/>
-      <c r="G18" s="358">
+      <c r="E18" s="349" t="n"/>
+      <c r="F18" s="372" t="n"/>
+      <c r="G18" s="371">
         <f>日程表１!G18</f>
         <v/>
       </c>
@@ -9761,15 +10070,15 @@
         <f>日程表１!H18</f>
         <v/>
       </c>
-      <c r="I18" s="335" t="n"/>
+      <c r="I18" s="348" t="n"/>
       <c r="J18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="336" t="n"/>
-      <c r="L18" s="359" t="n"/>
-      <c r="M18" s="358">
+      <c r="K18" s="349" t="n"/>
+      <c r="L18" s="372" t="n"/>
+      <c r="M18" s="371">
         <f>日程表１!M18</f>
         <v/>
       </c>
@@ -9777,14 +10086,14 @@
         <f>日程表１!N18</f>
         <v/>
       </c>
-      <c r="O18" s="335" t="n"/>
+      <c r="O18" s="348" t="n"/>
       <c r="P18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="336" t="n"/>
-      <c r="R18" s="359" t="n"/>
+      <c r="Q18" s="349" t="n"/>
+      <c r="R18" s="372" t="n"/>
       <c r="S18" s="254" t="n">
         <v>1</v>
       </c>
@@ -9792,13 +10101,13 @@
         <f>リーグ勝敗表!AX6</f>
         <v/>
       </c>
-      <c r="U18" s="279" t="n"/>
-      <c r="V18" s="279" t="n"/>
-      <c r="W18" s="279" t="n"/>
-      <c r="X18" s="280" t="n"/>
+      <c r="U18" s="290" t="n"/>
+      <c r="V18" s="290" t="n"/>
+      <c r="W18" s="290" t="n"/>
+      <c r="X18" s="291" t="n"/>
     </row>
     <row r="19" ht="20.45" customHeight="1" s="257">
-      <c r="A19" s="358">
+      <c r="A19" s="371">
         <f>日程表１!A19</f>
         <v/>
       </c>
@@ -9806,15 +10115,15 @@
         <f>日程表１!B19</f>
         <v/>
       </c>
-      <c r="C19" s="335" t="n"/>
+      <c r="C19" s="348" t="n"/>
       <c r="D19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="336" t="n"/>
-      <c r="F19" s="359" t="n"/>
-      <c r="G19" s="358">
+      <c r="E19" s="349" t="n"/>
+      <c r="F19" s="372" t="n"/>
+      <c r="G19" s="371">
         <f>日程表１!G19</f>
         <v/>
       </c>
@@ -9822,15 +10131,15 @@
         <f>日程表１!H19</f>
         <v/>
       </c>
-      <c r="I19" s="335" t="inlineStr">
+      <c r="I19" s="348" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="253" t="n"/>
-      <c r="K19" s="336" t="n"/>
-      <c r="L19" s="359" t="n"/>
-      <c r="M19" s="358">
+      <c r="K19" s="349" t="n"/>
+      <c r="L19" s="372" t="n"/>
+      <c r="M19" s="371">
         <f>日程表１!M19</f>
         <v/>
       </c>
@@ -9838,14 +10147,14 @@
         <f>日程表１!N19</f>
         <v/>
       </c>
-      <c r="O19" s="335" t="n"/>
+      <c r="O19" s="348" t="n"/>
       <c r="P19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="336" t="n"/>
-      <c r="R19" s="359" t="n"/>
+      <c r="Q19" s="349" t="n"/>
+      <c r="R19" s="372" t="n"/>
       <c r="S19" s="254" t="n">
         <v>2</v>
       </c>
@@ -9853,13 +10162,13 @@
         <f>リーグ勝敗表!AX8</f>
         <v/>
       </c>
-      <c r="U19" s="279" t="n"/>
-      <c r="V19" s="279" t="n"/>
-      <c r="W19" s="279" t="n"/>
-      <c r="X19" s="280" t="n"/>
+      <c r="U19" s="290" t="n"/>
+      <c r="V19" s="290" t="n"/>
+      <c r="W19" s="290" t="n"/>
+      <c r="X19" s="291" t="n"/>
     </row>
     <row r="20" ht="20.45" customHeight="1" s="257">
-      <c r="A20" s="358">
+      <c r="A20" s="371">
         <f>日程表１!A20</f>
         <v/>
       </c>
@@ -9867,15 +10176,15 @@
         <f>日程表１!B20</f>
         <v/>
       </c>
-      <c r="C20" s="335" t="n"/>
+      <c r="C20" s="348" t="n"/>
       <c r="D20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="336" t="n"/>
-      <c r="F20" s="359" t="n"/>
-      <c r="G20" s="358">
+      <c r="E20" s="349" t="n"/>
+      <c r="F20" s="372" t="n"/>
+      <c r="G20" s="371">
         <f>日程表１!G20</f>
         <v/>
       </c>
@@ -9883,15 +10192,15 @@
         <f>日程表１!H20</f>
         <v/>
       </c>
-      <c r="I20" s="335" t="inlineStr">
+      <c r="I20" s="348" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="253" t="n"/>
-      <c r="K20" s="336" t="n"/>
-      <c r="L20" s="359" t="n"/>
-      <c r="M20" s="358">
+      <c r="K20" s="349" t="n"/>
+      <c r="L20" s="372" t="n"/>
+      <c r="M20" s="371">
         <f>日程表１!M20</f>
         <v/>
       </c>
@@ -9899,14 +10208,14 @@
         <f>日程表１!N20</f>
         <v/>
       </c>
-      <c r="O20" s="335" t="n"/>
+      <c r="O20" s="348" t="n"/>
       <c r="P20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="336" t="n"/>
-      <c r="R20" s="359" t="n"/>
+      <c r="Q20" s="349" t="n"/>
+      <c r="R20" s="372" t="n"/>
       <c r="S20" s="254" t="n">
         <v>3</v>
       </c>
@@ -9914,13 +10223,13 @@
         <f>リーグ勝敗表!AX10</f>
         <v/>
       </c>
-      <c r="U20" s="279" t="n"/>
-      <c r="V20" s="279" t="n"/>
-      <c r="W20" s="279" t="n"/>
-      <c r="X20" s="280" t="n"/>
+      <c r="U20" s="290" t="n"/>
+      <c r="V20" s="290" t="n"/>
+      <c r="W20" s="290" t="n"/>
+      <c r="X20" s="291" t="n"/>
     </row>
     <row r="21" ht="20.45" customHeight="1" s="257">
-      <c r="A21" s="358">
+      <c r="A21" s="371">
         <f>日程表１!A21</f>
         <v/>
       </c>
@@ -9928,15 +10237,15 @@
         <f>日程表１!B21</f>
         <v/>
       </c>
-      <c r="C21" s="335" t="n"/>
+      <c r="C21" s="348" t="n"/>
       <c r="D21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="336" t="n"/>
-      <c r="F21" s="359" t="n"/>
-      <c r="G21" s="358">
+      <c r="E21" s="349" t="n"/>
+      <c r="F21" s="372" t="n"/>
+      <c r="G21" s="371">
         <f>日程表１!G21</f>
         <v/>
       </c>
@@ -9944,15 +10253,15 @@
         <f>日程表１!H21</f>
         <v/>
       </c>
-      <c r="I21" s="335" t="inlineStr">
+      <c r="I21" s="348" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="253" t="n"/>
-      <c r="K21" s="336" t="n"/>
-      <c r="L21" s="359" t="n"/>
-      <c r="M21" s="358">
+      <c r="K21" s="349" t="n"/>
+      <c r="L21" s="372" t="n"/>
+      <c r="M21" s="371">
         <f>日程表１!M21</f>
         <v/>
       </c>
@@ -9960,14 +10269,14 @@
         <f>日程表１!N21</f>
         <v/>
       </c>
-      <c r="O21" s="335" t="n"/>
+      <c r="O21" s="348" t="n"/>
       <c r="P21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="336" t="n"/>
-      <c r="R21" s="359" t="n"/>
+      <c r="Q21" s="349" t="n"/>
+      <c r="R21" s="372" t="n"/>
       <c r="S21" s="254" t="n">
         <v>4</v>
       </c>
@@ -9975,13 +10284,13 @@
         <f>リーグ勝敗表!AX12</f>
         <v/>
       </c>
-      <c r="U21" s="279" t="n"/>
-      <c r="V21" s="279" t="n"/>
-      <c r="W21" s="279" t="n"/>
-      <c r="X21" s="280" t="n"/>
+      <c r="U21" s="290" t="n"/>
+      <c r="V21" s="290" t="n"/>
+      <c r="W21" s="290" t="n"/>
+      <c r="X21" s="291" t="n"/>
     </row>
     <row r="22" ht="20.45" customHeight="1" s="257">
-      <c r="A22" s="358">
+      <c r="A22" s="371">
         <f>日程表１!A22</f>
         <v/>
       </c>
@@ -9989,15 +10298,15 @@
         <f>日程表１!B22</f>
         <v/>
       </c>
-      <c r="C22" s="335" t="n"/>
+      <c r="C22" s="348" t="n"/>
       <c r="D22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="336" t="n"/>
-      <c r="F22" s="359" t="n"/>
-      <c r="G22" s="358">
+      <c r="E22" s="349" t="n"/>
+      <c r="F22" s="372" t="n"/>
+      <c r="G22" s="371">
         <f>日程表１!G22</f>
         <v/>
       </c>
@@ -10005,15 +10314,15 @@
         <f>日程表１!H22</f>
         <v/>
       </c>
-      <c r="I22" s="335" t="n"/>
+      <c r="I22" s="348" t="n"/>
       <c r="J22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K22" s="336" t="n"/>
-      <c r="L22" s="359" t="n"/>
-      <c r="M22" s="358">
+      <c r="K22" s="349" t="n"/>
+      <c r="L22" s="372" t="n"/>
+      <c r="M22" s="371">
         <f>日程表１!M22</f>
         <v/>
       </c>
@@ -10021,14 +10330,14 @@
         <f>日程表１!N22</f>
         <v/>
       </c>
-      <c r="O22" s="335" t="n"/>
+      <c r="O22" s="348" t="n"/>
       <c r="P22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="336" t="n"/>
-      <c r="R22" s="359" t="n"/>
+      <c r="Q22" s="349" t="n"/>
+      <c r="R22" s="372" t="n"/>
       <c r="S22" s="254" t="n">
         <v>5</v>
       </c>
@@ -10036,13 +10345,13 @@
         <f>リーグ勝敗表!AX14</f>
         <v/>
       </c>
-      <c r="U22" s="279" t="n"/>
-      <c r="V22" s="279" t="n"/>
-      <c r="W22" s="279" t="n"/>
-      <c r="X22" s="280" t="n"/>
+      <c r="U22" s="290" t="n"/>
+      <c r="V22" s="290" t="n"/>
+      <c r="W22" s="290" t="n"/>
+      <c r="X22" s="291" t="n"/>
     </row>
     <row r="23" ht="20.45" customHeight="1" s="257">
-      <c r="A23" s="358">
+      <c r="A23" s="371">
         <f>日程表１!A23</f>
         <v/>
       </c>
@@ -10050,15 +10359,15 @@
         <f>日程表１!B23</f>
         <v/>
       </c>
-      <c r="C23" s="335" t="n"/>
+      <c r="C23" s="348" t="n"/>
       <c r="D23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="336" t="n"/>
-      <c r="F23" s="359" t="n"/>
-      <c r="G23" s="358">
+      <c r="E23" s="349" t="n"/>
+      <c r="F23" s="372" t="n"/>
+      <c r="G23" s="371">
         <f>日程表１!G23</f>
         <v/>
       </c>
@@ -10066,15 +10375,15 @@
         <f>日程表１!H23</f>
         <v/>
       </c>
-      <c r="I23" s="335" t="n"/>
+      <c r="I23" s="348" t="n"/>
       <c r="J23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K23" s="336" t="n"/>
-      <c r="L23" s="359" t="n"/>
-      <c r="M23" s="358">
+      <c r="K23" s="349" t="n"/>
+      <c r="L23" s="372" t="n"/>
+      <c r="M23" s="371">
         <f>日程表１!M23</f>
         <v/>
       </c>
@@ -10082,14 +10391,14 @@
         <f>日程表１!N23</f>
         <v/>
       </c>
-      <c r="O23" s="335" t="n"/>
+      <c r="O23" s="348" t="n"/>
       <c r="P23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="336" t="n"/>
-      <c r="R23" s="359" t="n"/>
+      <c r="Q23" s="349" t="n"/>
+      <c r="R23" s="372" t="n"/>
       <c r="S23" s="254" t="n">
         <v>6</v>
       </c>
@@ -10097,13 +10406,13 @@
         <f>リーグ勝敗表!AX16</f>
         <v/>
       </c>
-      <c r="U23" s="279" t="n"/>
-      <c r="V23" s="279" t="n"/>
-      <c r="W23" s="279" t="n"/>
-      <c r="X23" s="280" t="n"/>
+      <c r="U23" s="290" t="n"/>
+      <c r="V23" s="290" t="n"/>
+      <c r="W23" s="290" t="n"/>
+      <c r="X23" s="291" t="n"/>
     </row>
     <row r="24" ht="20.45" customHeight="1" s="257">
-      <c r="A24" s="358">
+      <c r="A24" s="371">
         <f>日程表１!A24</f>
         <v/>
       </c>
@@ -10111,15 +10420,15 @@
         <f>日程表１!B24</f>
         <v/>
       </c>
-      <c r="C24" s="335" t="n"/>
+      <c r="C24" s="348" t="n"/>
       <c r="D24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="336" t="n"/>
-      <c r="F24" s="359" t="n"/>
-      <c r="G24" s="358">
+      <c r="E24" s="349" t="n"/>
+      <c r="F24" s="372" t="n"/>
+      <c r="G24" s="371">
         <f>日程表１!G24</f>
         <v/>
       </c>
@@ -10127,15 +10436,15 @@
         <f>日程表１!H24</f>
         <v/>
       </c>
-      <c r="I24" s="335" t="n"/>
+      <c r="I24" s="348" t="n"/>
       <c r="J24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K24" s="336" t="n"/>
-      <c r="L24" s="359" t="n"/>
-      <c r="M24" s="358">
+      <c r="K24" s="349" t="n"/>
+      <c r="L24" s="372" t="n"/>
+      <c r="M24" s="371">
         <f>日程表１!M24</f>
         <v/>
       </c>
@@ -10143,14 +10452,14 @@
         <f>日程表１!N24</f>
         <v/>
       </c>
-      <c r="O24" s="335" t="n"/>
+      <c r="O24" s="348" t="n"/>
       <c r="P24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="336" t="n"/>
-      <c r="R24" s="359" t="n"/>
+      <c r="Q24" s="349" t="n"/>
+      <c r="R24" s="372" t="n"/>
       <c r="S24" s="254" t="n">
         <v>7</v>
       </c>
@@ -10158,13 +10467,13 @@
         <f>リーグ勝敗表!AX18</f>
         <v/>
       </c>
-      <c r="U24" s="279" t="n"/>
-      <c r="V24" s="279" t="n"/>
-      <c r="W24" s="279" t="n"/>
-      <c r="X24" s="280" t="n"/>
+      <c r="U24" s="290" t="n"/>
+      <c r="V24" s="290" t="n"/>
+      <c r="W24" s="290" t="n"/>
+      <c r="X24" s="291" t="n"/>
     </row>
     <row r="25" ht="20.45" customHeight="1" s="257">
-      <c r="A25" s="358">
+      <c r="A25" s="371">
         <f>日程表１!A25</f>
         <v/>
       </c>
@@ -10172,15 +10481,15 @@
         <f>日程表１!B25</f>
         <v/>
       </c>
-      <c r="C25" s="335" t="n"/>
+      <c r="C25" s="348" t="n"/>
       <c r="D25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="336" t="n"/>
-      <c r="F25" s="359" t="n"/>
-      <c r="G25" s="358">
+      <c r="E25" s="349" t="n"/>
+      <c r="F25" s="372" t="n"/>
+      <c r="G25" s="371">
         <f>日程表１!G25</f>
         <v/>
       </c>
@@ -10188,15 +10497,15 @@
         <f>日程表１!H25</f>
         <v/>
       </c>
-      <c r="I25" s="335" t="n"/>
+      <c r="I25" s="348" t="n"/>
       <c r="J25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K25" s="336" t="n"/>
-      <c r="L25" s="359" t="n"/>
-      <c r="M25" s="358">
+      <c r="K25" s="349" t="n"/>
+      <c r="L25" s="372" t="n"/>
+      <c r="M25" s="371">
         <f>日程表１!M25</f>
         <v/>
       </c>
@@ -10204,14 +10513,14 @@
         <f>日程表１!N25</f>
         <v/>
       </c>
-      <c r="O25" s="335" t="n"/>
+      <c r="O25" s="348" t="n"/>
       <c r="P25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="336" t="n"/>
-      <c r="R25" s="359" t="n"/>
+      <c r="Q25" s="349" t="n"/>
+      <c r="R25" s="372" t="n"/>
       <c r="S25" s="254" t="n">
         <v>8</v>
       </c>
@@ -10219,13 +10528,13 @@
         <f>リーグ勝敗表!AX20</f>
         <v/>
       </c>
-      <c r="U25" s="279" t="n"/>
-      <c r="V25" s="279" t="n"/>
-      <c r="W25" s="279" t="n"/>
-      <c r="X25" s="280" t="n"/>
+      <c r="U25" s="290" t="n"/>
+      <c r="V25" s="290" t="n"/>
+      <c r="W25" s="290" t="n"/>
+      <c r="X25" s="291" t="n"/>
     </row>
     <row r="26" ht="20.45" customHeight="1" s="257">
-      <c r="A26" s="358">
+      <c r="A26" s="371">
         <f>日程表１!A26</f>
         <v/>
       </c>
@@ -10233,40 +10542,40 @@
         <f>日程表１!B26</f>
         <v/>
       </c>
-      <c r="C26" s="335" t="n"/>
+      <c r="C26" s="348" t="n"/>
       <c r="D26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="336" t="n"/>
-      <c r="F26" s="359" t="n"/>
-      <c r="G26" s="362">
+      <c r="E26" s="349" t="n"/>
+      <c r="F26" s="372" t="n"/>
+      <c r="G26" s="375">
         <f>日程表１!G26</f>
         <v/>
       </c>
-      <c r="H26" s="363">
+      <c r="H26" s="376">
         <f>日程表１!H26</f>
         <v/>
       </c>
-      <c r="I26" s="340">
+      <c r="I26" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="364" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K26" s="342">
+      <c r="J26" s="377" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K26" s="355">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="365">
+      <c r="L26" s="378">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="358">
+      <c r="M26" s="371">
         <f>日程表１!M26</f>
         <v/>
       </c>
@@ -10274,14 +10583,14 @@
         <f>日程表１!N26</f>
         <v/>
       </c>
-      <c r="O26" s="335" t="n"/>
+      <c r="O26" s="348" t="n"/>
       <c r="P26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="336" t="n"/>
-      <c r="R26" s="359" t="n"/>
+      <c r="Q26" s="349" t="n"/>
+      <c r="R26" s="372" t="n"/>
       <c r="S26" s="254" t="n">
         <v>9</v>
       </c>
@@ -10289,13 +10598,13 @@
         <f>リーグ勝敗表!AX22</f>
         <v/>
       </c>
-      <c r="U26" s="279" t="n"/>
-      <c r="V26" s="279" t="n"/>
-      <c r="W26" s="279" t="n"/>
-      <c r="X26" s="280" t="n"/>
+      <c r="U26" s="290" t="n"/>
+      <c r="V26" s="290" t="n"/>
+      <c r="W26" s="290" t="n"/>
+      <c r="X26" s="291" t="n"/>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="257">
-      <c r="A27" s="358">
+      <c r="A27" s="371">
         <f>日程表１!A27</f>
         <v/>
       </c>
@@ -10303,15 +10612,15 @@
         <f>日程表１!B27</f>
         <v/>
       </c>
-      <c r="C27" s="335" t="n"/>
+      <c r="C27" s="348" t="n"/>
       <c r="D27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="336" t="n"/>
-      <c r="F27" s="359" t="n"/>
-      <c r="G27" s="358">
+      <c r="E27" s="349" t="n"/>
+      <c r="F27" s="372" t="n"/>
+      <c r="G27" s="371">
         <f>日程表１!G27</f>
         <v/>
       </c>
@@ -10319,7 +10628,7 @@
         <f>日程表１!H27</f>
         <v/>
       </c>
-      <c r="I27" s="335">
+      <c r="I27" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10328,15 +10637,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K27" s="336">
+      <c r="K27" s="349">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="359">
+      <c r="L27" s="372">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="358">
+      <c r="M27" s="371">
         <f>日程表１!M27</f>
         <v/>
       </c>
@@ -10344,14 +10653,14 @@
         <f>日程表１!N27</f>
         <v/>
       </c>
-      <c r="O27" s="335" t="n"/>
+      <c r="O27" s="348" t="n"/>
       <c r="P27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="336" t="n"/>
-      <c r="R27" s="359" t="n"/>
+      <c r="Q27" s="349" t="n"/>
+      <c r="R27" s="372" t="n"/>
       <c r="S27" s="254" t="n">
         <v>10</v>
       </c>
@@ -10359,13 +10668,13 @@
         <f>リーグ勝敗表!AX24</f>
         <v/>
       </c>
-      <c r="U27" s="279" t="n"/>
-      <c r="V27" s="279" t="n"/>
-      <c r="W27" s="279" t="n"/>
-      <c r="X27" s="280" t="n"/>
+      <c r="U27" s="290" t="n"/>
+      <c r="V27" s="290" t="n"/>
+      <c r="W27" s="290" t="n"/>
+      <c r="X27" s="291" t="n"/>
     </row>
     <row r="28" ht="20.45" customHeight="1" s="257">
-      <c r="A28" s="358">
+      <c r="A28" s="371">
         <f>日程表１!A28</f>
         <v/>
       </c>
@@ -10373,15 +10682,15 @@
         <f>日程表１!B28</f>
         <v/>
       </c>
-      <c r="C28" s="335" t="n"/>
+      <c r="C28" s="348" t="n"/>
       <c r="D28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="336" t="n"/>
-      <c r="F28" s="359" t="n"/>
-      <c r="G28" s="358">
+      <c r="E28" s="349" t="n"/>
+      <c r="F28" s="372" t="n"/>
+      <c r="G28" s="371">
         <f>日程表１!G28</f>
         <v/>
       </c>
@@ -10389,7 +10698,7 @@
         <f>日程表１!H28</f>
         <v/>
       </c>
-      <c r="I28" s="335">
+      <c r="I28" s="348">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -10398,15 +10707,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K28" s="336">
+      <c r="K28" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="359">
+      <c r="L28" s="372">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="358">
+      <c r="M28" s="371">
         <f>日程表１!M28</f>
         <v/>
       </c>
@@ -10414,14 +10723,14 @@
         <f>日程表１!N28</f>
         <v/>
       </c>
-      <c r="O28" s="335" t="n"/>
+      <c r="O28" s="348" t="n"/>
       <c r="P28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="336" t="n"/>
-      <c r="R28" s="359" t="n"/>
+      <c r="Q28" s="349" t="n"/>
+      <c r="R28" s="372" t="n"/>
       <c r="S28" s="254" t="n">
         <v>11</v>
       </c>
@@ -10429,13 +10738,13 @@
         <f>リーグ勝敗表!AX26</f>
         <v/>
       </c>
-      <c r="U28" s="279" t="n"/>
-      <c r="V28" s="279" t="n"/>
-      <c r="W28" s="279" t="n"/>
-      <c r="X28" s="280" t="n"/>
+      <c r="U28" s="290" t="n"/>
+      <c r="V28" s="290" t="n"/>
+      <c r="W28" s="290" t="n"/>
+      <c r="X28" s="291" t="n"/>
     </row>
     <row r="29" ht="20.45" customHeight="1" s="257">
-      <c r="A29" s="358">
+      <c r="A29" s="371">
         <f>日程表１!A29</f>
         <v/>
       </c>
@@ -10443,7 +10752,7 @@
         <f>日程表１!B29</f>
         <v/>
       </c>
-      <c r="C29" s="335">
+      <c r="C29" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10452,15 +10761,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="336">
+      <c r="E29" s="349">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="359">
+      <c r="F29" s="372">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="358">
+      <c r="G29" s="371">
         <f>日程表１!G29</f>
         <v/>
       </c>
@@ -10468,15 +10777,15 @@
         <f>日程表１!H29</f>
         <v/>
       </c>
-      <c r="I29" s="335" t="n"/>
+      <c r="I29" s="348" t="n"/>
       <c r="J29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K29" s="336" t="n"/>
-      <c r="L29" s="359" t="n"/>
-      <c r="M29" s="358">
+      <c r="K29" s="349" t="n"/>
+      <c r="L29" s="372" t="n"/>
+      <c r="M29" s="371">
         <f>日程表１!M29</f>
         <v/>
       </c>
@@ -10484,23 +10793,23 @@
         <f>日程表１!N29</f>
         <v/>
       </c>
-      <c r="O29" s="335" t="n"/>
+      <c r="O29" s="348" t="n"/>
       <c r="P29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="336" t="n"/>
-      <c r="R29" s="359" t="n"/>
+      <c r="Q29" s="349" t="n"/>
+      <c r="R29" s="372" t="n"/>
       <c r="S29" s="255" t="n"/>
       <c r="T29" s="255" t="n"/>
-      <c r="U29" s="350" t="n"/>
+      <c r="U29" s="363" t="n"/>
       <c r="V29" s="255" t="n"/>
-      <c r="W29" s="350" t="n"/>
-      <c r="X29" s="350" t="n"/>
+      <c r="W29" s="363" t="n"/>
+      <c r="X29" s="363" t="n"/>
     </row>
     <row r="30" ht="20.45" customHeight="1" s="257">
-      <c r="A30" s="358">
+      <c r="A30" s="371">
         <f>日程表１!A30</f>
         <v/>
       </c>
@@ -10508,7 +10817,7 @@
         <f>日程表１!B30</f>
         <v/>
       </c>
-      <c r="C30" s="335">
+      <c r="C30" s="348">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -10517,15 +10826,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="349">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="359">
+      <c r="F30" s="372">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="358">
+      <c r="G30" s="371">
         <f>日程表１!G30</f>
         <v/>
       </c>
@@ -10533,15 +10842,15 @@
         <f>日程表１!H30</f>
         <v/>
       </c>
-      <c r="I30" s="335" t="n"/>
+      <c r="I30" s="348" t="n"/>
       <c r="J30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K30" s="336" t="n"/>
-      <c r="L30" s="359" t="n"/>
-      <c r="M30" s="358">
+      <c r="K30" s="349" t="n"/>
+      <c r="L30" s="372" t="n"/>
+      <c r="M30" s="371">
         <f>日程表１!M30</f>
         <v/>
       </c>
@@ -10549,48 +10858,48 @@
         <f>日程表１!N30</f>
         <v/>
       </c>
-      <c r="O30" s="335" t="n"/>
+      <c r="O30" s="348" t="n"/>
       <c r="P30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="336" t="n"/>
-      <c r="R30" s="359" t="n"/>
+      <c r="Q30" s="349" t="n"/>
+      <c r="R30" s="372" t="n"/>
       <c r="S30" s="255" t="n"/>
       <c r="T30" s="255" t="n"/>
-      <c r="U30" s="350" t="n"/>
+      <c r="U30" s="363" t="n"/>
       <c r="V30" s="255" t="n"/>
-      <c r="W30" s="350" t="n"/>
-      <c r="X30" s="350" t="n"/>
+      <c r="W30" s="363" t="n"/>
+      <c r="X30" s="363" t="n"/>
     </row>
     <row r="31" ht="20.45" customHeight="1" s="257">
-      <c r="A31" s="362">
+      <c r="A31" s="375">
         <f>日程表１!A31</f>
         <v/>
       </c>
-      <c r="B31" s="363">
+      <c r="B31" s="376">
         <f>日程表１!B31</f>
         <v/>
       </c>
-      <c r="C31" s="340">
+      <c r="C31" s="353">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="364" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="342">
+      <c r="D31" s="377" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="355">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="365">
+      <c r="F31" s="378">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="358">
+      <c r="G31" s="371">
         <f>日程表１!G31</f>
         <v/>
       </c>
@@ -10598,15 +10907,15 @@
         <f>日程表１!H31</f>
         <v/>
       </c>
-      <c r="I31" s="335" t="n"/>
+      <c r="I31" s="348" t="n"/>
       <c r="J31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K31" s="336" t="n"/>
-      <c r="L31" s="359" t="n"/>
-      <c r="M31" s="358">
+      <c r="K31" s="349" t="n"/>
+      <c r="L31" s="372" t="n"/>
+      <c r="M31" s="371">
         <f>日程表１!M31</f>
         <v/>
       </c>
@@ -10614,23 +10923,23 @@
         <f>日程表１!N31</f>
         <v/>
       </c>
-      <c r="O31" s="335" t="n"/>
+      <c r="O31" s="348" t="n"/>
       <c r="P31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="336" t="n"/>
-      <c r="R31" s="359" t="n"/>
+      <c r="Q31" s="349" t="n"/>
+      <c r="R31" s="372" t="n"/>
       <c r="S31" s="255" t="n"/>
       <c r="T31" s="255" t="n"/>
-      <c r="U31" s="350" t="n"/>
+      <c r="U31" s="363" t="n"/>
       <c r="V31" s="255" t="n"/>
-      <c r="W31" s="350" t="n"/>
-      <c r="X31" s="350" t="n"/>
+      <c r="W31" s="363" t="n"/>
+      <c r="X31" s="363" t="n"/>
     </row>
     <row r="32" ht="20.45" customHeight="1" s="257">
-      <c r="A32" s="358">
+      <c r="A32" s="371">
         <f>日程表１!A32</f>
         <v/>
       </c>
@@ -10638,15 +10947,15 @@
         <f>日程表１!B32</f>
         <v/>
       </c>
-      <c r="C32" s="335" t="n"/>
+      <c r="C32" s="348" t="n"/>
       <c r="D32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="336" t="n"/>
-      <c r="F32" s="359" t="n"/>
-      <c r="G32" s="358">
+      <c r="E32" s="349" t="n"/>
+      <c r="F32" s="372" t="n"/>
+      <c r="G32" s="371">
         <f>日程表１!G32</f>
         <v/>
       </c>
@@ -10654,15 +10963,15 @@
         <f>日程表１!H32</f>
         <v/>
       </c>
-      <c r="I32" s="335" t="n"/>
+      <c r="I32" s="348" t="n"/>
       <c r="J32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K32" s="336" t="n"/>
-      <c r="L32" s="359" t="n"/>
-      <c r="M32" s="358">
+      <c r="K32" s="349" t="n"/>
+      <c r="L32" s="372" t="n"/>
+      <c r="M32" s="371">
         <f>日程表１!M32</f>
         <v/>
       </c>
@@ -10670,23 +10979,23 @@
         <f>日程表１!N32</f>
         <v/>
       </c>
-      <c r="O32" s="335" t="n"/>
+      <c r="O32" s="348" t="n"/>
       <c r="P32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="336" t="n"/>
-      <c r="R32" s="359" t="n"/>
+      <c r="Q32" s="349" t="n"/>
+      <c r="R32" s="372" t="n"/>
       <c r="S32" s="255" t="n"/>
       <c r="T32" s="255" t="n"/>
-      <c r="U32" s="350" t="n"/>
+      <c r="U32" s="363" t="n"/>
       <c r="V32" s="255" t="n"/>
-      <c r="W32" s="350" t="n"/>
-      <c r="X32" s="350" t="n"/>
+      <c r="W32" s="363" t="n"/>
+      <c r="X32" s="363" t="n"/>
     </row>
     <row r="33" ht="20.45" customHeight="1" s="257">
-      <c r="A33" s="358">
+      <c r="A33" s="371">
         <f>日程表１!A33</f>
         <v/>
       </c>
@@ -10694,15 +11003,15 @@
         <f>日程表１!B33</f>
         <v/>
       </c>
-      <c r="C33" s="335" t="n"/>
+      <c r="C33" s="348" t="n"/>
       <c r="D33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="336" t="n"/>
-      <c r="F33" s="359" t="n"/>
-      <c r="G33" s="358">
+      <c r="E33" s="349" t="n"/>
+      <c r="F33" s="372" t="n"/>
+      <c r="G33" s="371">
         <f>日程表１!G33</f>
         <v/>
       </c>
@@ -10710,7 +11019,7 @@
         <f>日程表１!H33</f>
         <v/>
       </c>
-      <c r="I33" s="335">
+      <c r="I33" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10719,15 +11028,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K33" s="336">
+      <c r="K33" s="349">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="359">
+      <c r="L33" s="372">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="358">
+      <c r="M33" s="371">
         <f>日程表１!M33</f>
         <v/>
       </c>
@@ -10735,23 +11044,23 @@
         <f>日程表１!N33</f>
         <v/>
       </c>
-      <c r="O33" s="335" t="n"/>
+      <c r="O33" s="348" t="n"/>
       <c r="P33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="336" t="n"/>
-      <c r="R33" s="359" t="n"/>
+      <c r="Q33" s="349" t="n"/>
+      <c r="R33" s="372" t="n"/>
       <c r="S33" s="255" t="n"/>
       <c r="T33" s="255" t="n"/>
-      <c r="U33" s="350" t="n"/>
+      <c r="U33" s="363" t="n"/>
       <c r="V33" s="255" t="n"/>
-      <c r="W33" s="350" t="n"/>
-      <c r="X33" s="350" t="n"/>
+      <c r="W33" s="363" t="n"/>
+      <c r="X33" s="363" t="n"/>
     </row>
     <row r="34" ht="20.45" customHeight="1" s="257">
-      <c r="A34" s="358">
+      <c r="A34" s="371">
         <f>日程表１!A34</f>
         <v/>
       </c>
@@ -10759,25 +11068,25 @@
         <f>日程表１!B34</f>
         <v/>
       </c>
-      <c r="C34" s="335" t="n"/>
+      <c r="C34" s="348" t="n"/>
       <c r="D34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="366" t="n"/>
-      <c r="F34" s="349" t="n"/>
-      <c r="G34" s="358" t="n"/>
+      <c r="E34" s="379" t="n"/>
+      <c r="F34" s="362" t="n"/>
+      <c r="G34" s="371" t="n"/>
       <c r="H34" s="256" t="n"/>
-      <c r="I34" s="335" t="n"/>
+      <c r="I34" s="348" t="n"/>
       <c r="J34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K34" s="336" t="n"/>
-      <c r="L34" s="359" t="n"/>
-      <c r="M34" s="358">
+      <c r="K34" s="349" t="n"/>
+      <c r="L34" s="372" t="n"/>
+      <c r="M34" s="371">
         <f>日程表１!M34</f>
         <v/>
       </c>
@@ -10785,20 +11094,20 @@
         <f>日程表１!N34</f>
         <v/>
       </c>
-      <c r="O34" s="335" t="n"/>
+      <c r="O34" s="348" t="n"/>
       <c r="P34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="336" t="n"/>
-      <c r="R34" s="359" t="n"/>
+      <c r="Q34" s="349" t="n"/>
+      <c r="R34" s="372" t="n"/>
       <c r="S34" s="255" t="n"/>
       <c r="T34" s="255" t="n"/>
-      <c r="U34" s="350" t="n"/>
+      <c r="U34" s="363" t="n"/>
       <c r="V34" s="255" t="n"/>
-      <c r="W34" s="350" t="n"/>
-      <c r="X34" s="350" t="n"/>
+      <c r="W34" s="363" t="n"/>
+      <c r="X34" s="363" t="n"/>
     </row>
     <row r="35" ht="3" customHeight="1" s="257"/>
   </sheetData>

--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -396,7 +396,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="86">
+  <borders count="89">
     <border>
       <left/>
       <right/>
@@ -1386,8 +1386,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="000D1B2A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B2BABB"/>
+      </right>
+      <top style="medium">
+        <color rgb="000D1B2A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B2BABB"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="00B2BABB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B2BABB"/>
+      </right>
+      <top style="medium">
+        <color rgb="000D1B2A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B2BABB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B2BABB"/>
+      </left>
+      <right style="medium">
+        <color rgb="000D1B2A"/>
+      </right>
+      <top style="medium">
+        <color rgb="000D1B2A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B2BABB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000D1B2A"/>
       </left>
       <right style="thin">
         <color rgb="00B2BABB"/>
@@ -1395,8 +1437,8 @@
       <top style="thin">
         <color rgb="00B2BABB"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00B2BABB"/>
+      <bottom style="medium">
+        <color rgb="000D1B2A"/>
       </bottom>
     </border>
     <border>
@@ -1414,19 +1456,11 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color rgb="00B2BABB"/>
+      </left>
+      <right style="medium">
         <color rgb="000D1B2A"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="000D1B2A"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B2BABB"/>
       </right>
       <top style="thin">
         <color rgb="00B2BABB"/>
@@ -1450,17 +1484,31 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="000D1B2A"/>
+      <left style="thin">
+        <color rgb="00B2BABB"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="00B2BABB"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="00B2BABB"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="00B2BABB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B2BABB"/>
+      </left>
+      <right style="medium">
+        <color rgb="000D1B2A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B2BABB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B2BABB"/>
       </bottom>
     </border>
   </borders>
@@ -1469,7 +1517,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="380">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2340,34 +2388,40 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="14" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2377,25 +2431,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="17" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="17" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="32" fillId="17" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="17" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="17" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="17" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="31" fillId="18" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="31" fillId="18" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2403,13 +2460,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2419,15 +2476,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2437,57 +2494,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="33" fillId="21" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="33" fillId="21" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="21" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2497,16 +2527,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="65" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
+    <xf numFmtId="164" fontId="33" fillId="21" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
@@ -2517,32 +2539,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="74" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="1" hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="21" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="21" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -3155,9 +3165,9 @@
     </row>
     <row r="4" ht="20.25" customHeight="1" s="257" thickBot="1">
       <c r="A4" s="261" t="n"/>
-      <c r="B4" s="261" t="n"/>
-      <c r="C4" s="261" t="n"/>
-      <c r="D4" s="261" t="n"/>
+      <c r="B4" s="262" t="n"/>
+      <c r="C4" s="262" t="n"/>
+      <c r="D4" s="262" t="n"/>
       <c r="E4" s="262" t="n">
         <v>1</v>
       </c>
@@ -3213,126 +3223,126 @@
       </c>
       <c r="AJ4" s="263" t="n"/>
       <c r="AK4" s="263" t="n"/>
-      <c r="AL4" s="264" t="n"/>
-      <c r="AM4" s="261" t="n"/>
-      <c r="AN4" s="261" t="n"/>
-      <c r="AO4" s="261" t="n"/>
-      <c r="AP4" s="261" t="n"/>
-      <c r="AQ4" s="261" t="n"/>
-      <c r="AR4" s="261" t="n"/>
-      <c r="AS4" s="261" t="n"/>
+      <c r="AL4" s="261" t="n"/>
+      <c r="AM4" s="262" t="n"/>
+      <c r="AN4" s="262" t="n"/>
+      <c r="AO4" s="262" t="n"/>
+      <c r="AP4" s="262" t="n"/>
+      <c r="AQ4" s="262" t="n"/>
+      <c r="AR4" s="262" t="n"/>
+      <c r="AS4" s="264" t="n"/>
     </row>
     <row r="5" ht="57" customHeight="1" s="257" thickBot="1">
       <c r="A5" s="265" t="n"/>
-      <c r="B5" s="265" t="inlineStr">
+      <c r="B5" s="266" t="inlineStr">
         <is>
           <t>チーム名</t>
         </is>
       </c>
-      <c r="C5" s="266" t="n"/>
-      <c r="D5" s="267" t="n"/>
-      <c r="E5" s="265">
+      <c r="C5" s="267" t="n"/>
+      <c r="D5" s="268" t="n"/>
+      <c r="E5" s="266">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F5" s="266" t="n"/>
-      <c r="G5" s="267" t="n"/>
-      <c r="H5" s="265">
+      <c r="F5" s="267" t="n"/>
+      <c r="G5" s="268" t="n"/>
+      <c r="H5" s="266">
         <f>C8</f>
         <v/>
       </c>
-      <c r="I5" s="266" t="n"/>
-      <c r="J5" s="267" t="n"/>
-      <c r="K5" s="265">
+      <c r="I5" s="267" t="n"/>
+      <c r="J5" s="268" t="n"/>
+      <c r="K5" s="266">
         <f>C10</f>
         <v/>
       </c>
-      <c r="L5" s="266" t="n"/>
-      <c r="M5" s="267" t="n"/>
-      <c r="N5" s="265">
+      <c r="L5" s="267" t="n"/>
+      <c r="M5" s="268" t="n"/>
+      <c r="N5" s="266">
         <f>C12</f>
         <v/>
       </c>
-      <c r="O5" s="266" t="n"/>
-      <c r="P5" s="267" t="n"/>
-      <c r="Q5" s="265">
+      <c r="O5" s="267" t="n"/>
+      <c r="P5" s="268" t="n"/>
+      <c r="Q5" s="266">
         <f>C14</f>
         <v/>
       </c>
-      <c r="R5" s="266" t="n"/>
-      <c r="S5" s="267" t="n"/>
-      <c r="T5" s="265">
+      <c r="R5" s="267" t="n"/>
+      <c r="S5" s="268" t="n"/>
+      <c r="T5" s="266">
         <f>C16</f>
         <v/>
       </c>
-      <c r="U5" s="266" t="n"/>
-      <c r="V5" s="267" t="n"/>
-      <c r="W5" s="265">
+      <c r="U5" s="267" t="n"/>
+      <c r="V5" s="268" t="n"/>
+      <c r="W5" s="266">
         <f>C18</f>
         <v/>
       </c>
-      <c r="X5" s="266" t="n"/>
-      <c r="Y5" s="267" t="n"/>
-      <c r="Z5" s="265">
+      <c r="X5" s="267" t="n"/>
+      <c r="Y5" s="268" t="n"/>
+      <c r="Z5" s="266">
         <f>C20</f>
         <v/>
       </c>
-      <c r="AA5" s="266" t="n"/>
-      <c r="AB5" s="267" t="n"/>
-      <c r="AC5" s="265">
+      <c r="AA5" s="267" t="n"/>
+      <c r="AB5" s="268" t="n"/>
+      <c r="AC5" s="266">
         <f>C22</f>
         <v/>
       </c>
-      <c r="AD5" s="266" t="n"/>
-      <c r="AE5" s="267" t="n"/>
-      <c r="AF5" s="265">
+      <c r="AD5" s="267" t="n"/>
+      <c r="AE5" s="268" t="n"/>
+      <c r="AF5" s="266">
         <f>C24</f>
         <v/>
       </c>
-      <c r="AG5" s="266" t="n"/>
-      <c r="AH5" s="267" t="n"/>
-      <c r="AI5" s="265">
+      <c r="AG5" s="267" t="n"/>
+      <c r="AH5" s="268" t="n"/>
+      <c r="AI5" s="266">
         <f>C26</f>
         <v/>
       </c>
-      <c r="AJ5" s="266" t="n"/>
-      <c r="AK5" s="267" t="n"/>
-      <c r="AL5" s="268" t="inlineStr">
+      <c r="AJ5" s="267" t="n"/>
+      <c r="AK5" s="268" t="n"/>
+      <c r="AL5" s="265" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
       </c>
-      <c r="AM5" s="265" t="inlineStr">
+      <c r="AM5" s="266" t="inlineStr">
         <is>
           <t>分</t>
         </is>
       </c>
-      <c r="AN5" s="265" t="inlineStr">
+      <c r="AN5" s="266" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
       </c>
-      <c r="AO5" s="265" t="inlineStr">
+      <c r="AO5" s="266" t="inlineStr">
         <is>
           <t>勝点</t>
         </is>
       </c>
-      <c r="AP5" s="265" t="inlineStr">
+      <c r="AP5" s="266" t="inlineStr">
         <is>
           <t>失点</t>
         </is>
       </c>
-      <c r="AQ5" s="265" t="inlineStr">
+      <c r="AQ5" s="266" t="inlineStr">
         <is>
           <t>得点</t>
         </is>
       </c>
-      <c r="AR5" s="265" t="inlineStr">
+      <c r="AR5" s="266" t="inlineStr">
         <is>
           <t>残試</t>
         </is>
       </c>
-      <c r="AS5" s="265" t="inlineStr">
+      <c r="AS5" s="269" t="inlineStr">
         <is>
           <t>順位</t>
         </is>
@@ -3342,115 +3352,115 @@
           <t>チームナンバー</t>
         </is>
       </c>
-      <c r="AX5" s="269" t="n"/>
+      <c r="AX5" s="270" t="n"/>
       <c r="AZ5" s="100" t="inlineStr">
         <is>
           <t>チームリスト</t>
         </is>
       </c>
-      <c r="BA5" s="270" t="n"/>
+      <c r="BA5" s="271" t="n"/>
     </row>
     <row r="6" ht="46.9" customHeight="1" s="257">
-      <c r="A6" s="271" t="n"/>
-      <c r="B6" s="271" t="n">
+      <c r="A6" s="272" t="n"/>
+      <c r="B6" s="273" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="271">
+      <c r="C6" s="273">
         <f>AX6</f>
         <v/>
       </c>
-      <c r="D6" s="272" t="n"/>
-      <c r="E6" s="273" t="n"/>
-      <c r="G6" s="272" t="n"/>
-      <c r="H6" s="274">
+      <c r="D6" s="274" t="n"/>
+      <c r="E6" s="275" t="n"/>
+      <c r="G6" s="274" t="n"/>
+      <c r="H6" s="276">
         <f>IF(H7="","",IF(H7="☂","☂",IF(H7&gt;J7,"○",IF(H7=J7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I6" s="275" t="n"/>
-      <c r="J6" s="276" t="n"/>
-      <c r="K6" s="274">
+      <c r="I6" s="277" t="n"/>
+      <c r="J6" s="278" t="n"/>
+      <c r="K6" s="276">
         <f>IF(K7="","",IF(K7="☂","☂",IF(K7&gt;M7,"○",IF(K7=M7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L6" s="275" t="n"/>
-      <c r="M6" s="276" t="n"/>
-      <c r="N6" s="274">
+      <c r="L6" s="277" t="n"/>
+      <c r="M6" s="278" t="n"/>
+      <c r="N6" s="276">
         <f>IF(N7="","",IF(N7="☂","☂",IF(N7&gt;P7,"○",IF(N7=P7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O6" s="275" t="n"/>
-      <c r="P6" s="276" t="n"/>
-      <c r="Q6" s="274">
+      <c r="O6" s="277" t="n"/>
+      <c r="P6" s="278" t="n"/>
+      <c r="Q6" s="276">
         <f>IF(Q7="","",IF(Q7="☂","☂",IF(Q7&gt;S7,"○",IF(Q7=S7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R6" s="275" t="n"/>
-      <c r="S6" s="276" t="n"/>
-      <c r="T6" s="274">
+      <c r="R6" s="277" t="n"/>
+      <c r="S6" s="278" t="n"/>
+      <c r="T6" s="276">
         <f>IF(T7="","",IF(T7="☂","☂",IF(T7&gt;V7,"○",IF(T7=V7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U6" s="275" t="n"/>
-      <c r="V6" s="276" t="n"/>
-      <c r="W6" s="274">
+      <c r="U6" s="277" t="n"/>
+      <c r="V6" s="278" t="n"/>
+      <c r="W6" s="276">
         <f>IF(W7="","",IF(W7="☂","☂",IF(W7&gt;Y7,"○",IF(W7=Y7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X6" s="275" t="n"/>
-      <c r="Y6" s="276" t="n"/>
-      <c r="Z6" s="274">
+      <c r="X6" s="277" t="n"/>
+      <c r="Y6" s="278" t="n"/>
+      <c r="Z6" s="276">
         <f>IF(Z7="","",IF(Z7="☂","☂",IF(Z7&gt;AB7,"○",IF(Z7=AB7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA6" s="275" t="n"/>
-      <c r="AB6" s="276" t="n"/>
-      <c r="AC6" s="274">
+      <c r="AA6" s="277" t="n"/>
+      <c r="AB6" s="278" t="n"/>
+      <c r="AC6" s="276">
         <f>IF(AC7="","",IF(AC7="☂","☂",IF(AC7&gt;AE7,"○",IF(AC7=AE7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD6" s="275" t="n"/>
-      <c r="AE6" s="276" t="n"/>
-      <c r="AF6" s="274">
+      <c r="AD6" s="277" t="n"/>
+      <c r="AE6" s="278" t="n"/>
+      <c r="AF6" s="276">
         <f>IF(AF7="","",IF(AF7="☂","☂",IF(AF7&gt;AH7,"○",IF(AF7=AH7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG6" s="275" t="n"/>
-      <c r="AH6" s="276" t="n"/>
-      <c r="AI6" s="274">
+      <c r="AG6" s="277" t="n"/>
+      <c r="AH6" s="278" t="n"/>
+      <c r="AI6" s="276">
         <f>IF(AI7="","",IF(AI7="☂","☂",IF(AI7&gt;AK7,"○",IF(AI7=AK7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ6" s="275" t="n"/>
-      <c r="AK6" s="276" t="n"/>
-      <c r="AL6" s="277">
+      <c r="AJ6" s="277" t="n"/>
+      <c r="AK6" s="278" t="n"/>
+      <c r="AL6" s="279">
         <f>COUNTIF(E6:AK6,"○")</f>
         <v/>
       </c>
-      <c r="AM6" s="278">
+      <c r="AM6" s="280">
         <f>COUNTIF(E6:AK6,"△")</f>
         <v/>
       </c>
-      <c r="AN6" s="278">
+      <c r="AN6" s="280">
         <f>COUNTIF(E6:AK6,"×")</f>
         <v/>
       </c>
-      <c r="AO6" s="279">
+      <c r="AO6" s="281">
         <f>AL6*3+AM6*1</f>
         <v/>
       </c>
-      <c r="AP6" s="278">
+      <c r="AP6" s="280">
         <f>SUM(J7,M7,P7,S7,V7,Y7,AB7,AK7)</f>
         <v/>
       </c>
-      <c r="AQ6" s="278">
+      <c r="AQ6" s="280">
         <f>SUM(H7,K7,N7,Q7,T7,W7,Z7,AI7)</f>
         <v/>
       </c>
-      <c r="AR6" s="278">
+      <c r="AR6" s="280">
         <f>$AY$21-AL6-AM6-AN6</f>
         <v/>
       </c>
-      <c r="AS6" s="280">
+      <c r="AS6" s="282">
         <f>IFERROR(_xlfn.RANK.EQ(AO6,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3474,154 +3484,154 @@
       </c>
     </row>
     <row r="7" ht="46.9" customHeight="1" s="257">
-      <c r="A7" s="271" t="n"/>
-      <c r="B7" s="281" t="n"/>
-      <c r="C7" s="282" t="n"/>
-      <c r="D7" s="283" t="n"/>
-      <c r="E7" s="270" t="n"/>
-      <c r="F7" s="270" t="n"/>
-      <c r="G7" s="283" t="n"/>
-      <c r="H7" s="284">
+      <c r="A7" s="283" t="n"/>
+      <c r="B7" s="284" t="n"/>
+      <c r="C7" s="285" t="n"/>
+      <c r="D7" s="286" t="n"/>
+      <c r="E7" s="271" t="n"/>
+      <c r="F7" s="271" t="n"/>
+      <c r="G7" s="286" t="n"/>
+      <c r="H7" s="287">
         <f>IF(G9="","",G9)</f>
         <v/>
       </c>
-      <c r="I7" s="285" t="inlineStr">
+      <c r="I7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="284">
+      <c r="J7" s="287">
         <f>IF(E9="","",E9)</f>
         <v/>
       </c>
-      <c r="K7" s="284">
+      <c r="K7" s="287">
         <f>IF(G11="","",G11)</f>
         <v/>
       </c>
-      <c r="L7" s="285" t="inlineStr">
+      <c r="L7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M7" s="284">
+      <c r="M7" s="287">
         <f>IF(E11="","",E11)</f>
         <v/>
       </c>
-      <c r="N7" s="284">
+      <c r="N7" s="287">
         <f>IF(G13="","",G13)</f>
         <v/>
       </c>
-      <c r="O7" s="285" t="inlineStr">
+      <c r="O7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P7" s="284">
+      <c r="P7" s="287">
         <f>IF(E13="","",E13)</f>
         <v/>
       </c>
-      <c r="Q7" s="284">
+      <c r="Q7" s="287">
         <f>IF(G15="","",G15)</f>
         <v/>
       </c>
-      <c r="R7" s="285" t="inlineStr">
+      <c r="R7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S7" s="284">
+      <c r="S7" s="287">
         <f>IF(E15="","",E15)</f>
         <v/>
       </c>
-      <c r="T7" s="284">
+      <c r="T7" s="287">
         <f>IF(G17="","",G17)</f>
         <v/>
       </c>
-      <c r="U7" s="285" t="inlineStr">
+      <c r="U7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V7" s="284">
+      <c r="V7" s="287">
         <f>IF(E17="","",E17)</f>
         <v/>
       </c>
-      <c r="W7" s="284">
+      <c r="W7" s="287">
         <f>IF(G19="","",G19)</f>
         <v/>
       </c>
-      <c r="X7" s="285" t="inlineStr">
+      <c r="X7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y7" s="284">
+      <c r="Y7" s="287">
         <f>IF(E19="","",E19)</f>
         <v/>
       </c>
-      <c r="Z7" s="284">
+      <c r="Z7" s="287">
         <f>IF(G21="","",G21)</f>
         <v/>
       </c>
-      <c r="AA7" s="285" t="inlineStr">
+      <c r="AA7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB7" s="284">
+      <c r="AB7" s="287">
         <f>IF(E21="","",E21)</f>
         <v/>
       </c>
-      <c r="AC7" s="284">
+      <c r="AC7" s="287">
         <f>IF(G23="","",G23)</f>
         <v/>
       </c>
-      <c r="AD7" s="285" t="inlineStr">
+      <c r="AD7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE7" s="284">
+      <c r="AE7" s="287">
         <f>IF(E23="","",E23)</f>
         <v/>
       </c>
-      <c r="AF7" s="284">
+      <c r="AF7" s="287">
         <f>IF(G25="","",G25)</f>
         <v/>
       </c>
-      <c r="AG7" s="285" t="inlineStr">
+      <c r="AG7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH7" s="284">
+      <c r="AH7" s="287">
         <f>IF(E25="","",E25)</f>
         <v/>
       </c>
-      <c r="AI7" s="284">
+      <c r="AI7" s="287">
         <f>IF(G27="","",G27)</f>
         <v/>
       </c>
-      <c r="AJ7" s="285" t="inlineStr">
+      <c r="AJ7" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK7" s="284">
+      <c r="AK7" s="287">
         <f>IF(E27="","",G27)</f>
         <v/>
       </c>
-      <c r="AL7" s="281" t="n"/>
-      <c r="AM7" s="286" t="n"/>
-      <c r="AN7" s="286" t="n"/>
-      <c r="AO7" s="286" t="n"/>
-      <c r="AP7" s="282" t="n"/>
-      <c r="AQ7" s="286" t="n"/>
-      <c r="AR7" s="286" t="n"/>
-      <c r="AS7" s="287" t="n"/>
-      <c r="AV7" s="286" t="n"/>
-      <c r="AW7" s="288" t="n"/>
-      <c r="AX7" s="286" t="n"/>
+      <c r="AL7" s="284" t="n"/>
+      <c r="AM7" s="289" t="n"/>
+      <c r="AN7" s="289" t="n"/>
+      <c r="AO7" s="289" t="n"/>
+      <c r="AP7" s="285" t="n"/>
+      <c r="AQ7" s="289" t="n"/>
+      <c r="AR7" s="289" t="n"/>
+      <c r="AS7" s="290" t="n"/>
+      <c r="AV7" s="289" t="n"/>
+      <c r="AW7" s="291" t="n"/>
+      <c r="AX7" s="289" t="n"/>
       <c r="AZ7" s="5" t="n">
         <v>2</v>
       </c>
@@ -3632,107 +3642,107 @@
       </c>
     </row>
     <row r="8" ht="46.9" customHeight="1" s="257">
-      <c r="A8" s="271" t="n"/>
-      <c r="B8" s="271" t="n">
+      <c r="A8" s="272" t="n"/>
+      <c r="B8" s="273" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="271">
+      <c r="C8" s="273">
         <f>AX8</f>
         <v/>
       </c>
-      <c r="D8" s="272" t="n"/>
-      <c r="E8" s="289">
+      <c r="D8" s="274" t="n"/>
+      <c r="E8" s="292">
         <f>IF(E9="","",IF(E9="☂","☂",IF(E9&gt;G9,"○",IF(E9=G9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F8" s="290" t="n"/>
-      <c r="G8" s="291" t="n"/>
-      <c r="H8" s="289" t="n"/>
-      <c r="I8" s="292" t="n"/>
-      <c r="J8" s="269" t="n"/>
-      <c r="K8" s="293">
+      <c r="F8" s="293" t="n"/>
+      <c r="G8" s="294" t="n"/>
+      <c r="H8" s="292" t="n"/>
+      <c r="I8" s="295" t="n"/>
+      <c r="J8" s="270" t="n"/>
+      <c r="K8" s="296">
         <f>IF(K9="","",IF(K9="☂","☂",IF(K9&gt;M9,"○",IF(K9=M9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L8" s="294" t="n"/>
-      <c r="M8" s="295" t="n"/>
-      <c r="N8" s="293">
+      <c r="L8" s="297" t="n"/>
+      <c r="M8" s="298" t="n"/>
+      <c r="N8" s="296">
         <f>IF(N9="","",IF(N9="☂","☂",IF(N9&gt;P9,"○",IF(N9=P9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O8" s="294" t="n"/>
-      <c r="P8" s="295" t="n"/>
-      <c r="Q8" s="293">
+      <c r="O8" s="297" t="n"/>
+      <c r="P8" s="298" t="n"/>
+      <c r="Q8" s="296">
         <f>IF(Q9="","",IF(Q9="☂","☂",IF(Q9&gt;S9,"○",IF(Q9=S9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R8" s="294" t="n"/>
-      <c r="S8" s="295" t="n"/>
-      <c r="T8" s="293">
+      <c r="R8" s="297" t="n"/>
+      <c r="S8" s="298" t="n"/>
+      <c r="T8" s="296">
         <f>IF(T9="","",IF(T9="☂","☂",IF(T9&gt;V9,"○",IF(T9=V9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U8" s="294" t="n"/>
-      <c r="V8" s="295" t="n"/>
-      <c r="W8" s="293">
+      <c r="U8" s="297" t="n"/>
+      <c r="V8" s="298" t="n"/>
+      <c r="W8" s="296">
         <f>IF(W9="","",IF(W9="☂","☂",IF(W9&gt;Y9,"○",IF(W9=Y9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X8" s="294" t="n"/>
-      <c r="Y8" s="295" t="n"/>
-      <c r="Z8" s="293">
+      <c r="X8" s="297" t="n"/>
+      <c r="Y8" s="298" t="n"/>
+      <c r="Z8" s="296">
         <f>IF(Z9="","",IF(Z9="☂","☂",IF(Z9&gt;AB9,"○",IF(Z9=AB9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA8" s="294" t="n"/>
-      <c r="AB8" s="295" t="n"/>
-      <c r="AC8" s="293">
+      <c r="AA8" s="297" t="n"/>
+      <c r="AB8" s="298" t="n"/>
+      <c r="AC8" s="296">
         <f>IF(AC9="","",IF(AC9="☂","☂",IF(AC9&gt;AE9,"○",IF(AC9=AE9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD8" s="294" t="n"/>
-      <c r="AE8" s="295" t="n"/>
-      <c r="AF8" s="293">
+      <c r="AD8" s="297" t="n"/>
+      <c r="AE8" s="298" t="n"/>
+      <c r="AF8" s="296">
         <f>IF(AF9="","",IF(AF9="☂","☂",IF(AF9&gt;AH9,"○",IF(AF9=AH9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG8" s="294" t="n"/>
-      <c r="AH8" s="295" t="n"/>
-      <c r="AI8" s="293">
+      <c r="AG8" s="297" t="n"/>
+      <c r="AH8" s="298" t="n"/>
+      <c r="AI8" s="296">
         <f>IF(AI9="","",IF(AI9="☂","☂",IF(AI9&gt;AK9,"○",IF(AI9=AK9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ8" s="294" t="n"/>
-      <c r="AK8" s="295" t="n"/>
-      <c r="AL8" s="277">
+      <c r="AJ8" s="297" t="n"/>
+      <c r="AK8" s="298" t="n"/>
+      <c r="AL8" s="279">
         <f>COUNTIF(E8:AK8,"○")</f>
         <v/>
       </c>
-      <c r="AM8" s="278">
+      <c r="AM8" s="280">
         <f>COUNTIF(E8:AK8,"△")</f>
         <v/>
       </c>
-      <c r="AN8" s="278">
+      <c r="AN8" s="280">
         <f>COUNTIF(E8:AK8,"×")</f>
         <v/>
       </c>
-      <c r="AO8" s="279">
+      <c r="AO8" s="281">
         <f>AL8*3+AM8*1</f>
         <v/>
       </c>
-      <c r="AP8" s="278">
+      <c r="AP8" s="280">
         <f>SUM(G9,M9,P9,S9,V9,Y9,AB9,AK9)</f>
         <v/>
       </c>
-      <c r="AQ8" s="278">
+      <c r="AQ8" s="280">
         <f>SUM(E9,K9,N9,Q9,T9,W9,Z9,AI9)</f>
         <v/>
       </c>
-      <c r="AR8" s="278">
+      <c r="AR8" s="280">
         <f>$AY$21-AL8-AM8-AN8</f>
         <v/>
       </c>
-      <c r="AS8" s="280">
+      <c r="AS8" s="282">
         <f>IFERROR(_xlfn.RANK.EQ(AO8,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3756,148 +3766,148 @@
       </c>
     </row>
     <row r="9" ht="46.9" customHeight="1" s="257">
-      <c r="A9" s="271" t="n"/>
-      <c r="B9" s="281" t="n"/>
-      <c r="C9" s="282" t="n"/>
-      <c r="D9" s="283" t="n"/>
-      <c r="E9" s="296" t="n"/>
-      <c r="F9" s="297" t="inlineStr">
+      <c r="A9" s="283" t="n"/>
+      <c r="B9" s="284" t="n"/>
+      <c r="C9" s="285" t="n"/>
+      <c r="D9" s="286" t="n"/>
+      <c r="E9" s="299" t="n"/>
+      <c r="F9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="296" t="n"/>
-      <c r="H9" s="282" t="n"/>
-      <c r="I9" s="270" t="n"/>
-      <c r="J9" s="283" t="n"/>
-      <c r="K9" s="297">
+      <c r="G9" s="299" t="n"/>
+      <c r="H9" s="285" t="n"/>
+      <c r="I9" s="271" t="n"/>
+      <c r="J9" s="286" t="n"/>
+      <c r="K9" s="300">
         <f>IF(J11="","",J11)</f>
         <v/>
       </c>
-      <c r="L9" s="297" t="inlineStr">
+      <c r="L9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M9" s="297">
+      <c r="M9" s="300">
         <f>IF(H11="","",H11)</f>
         <v/>
       </c>
-      <c r="N9" s="297">
+      <c r="N9" s="300">
         <f>IF(J13="","",J13)</f>
         <v/>
       </c>
-      <c r="O9" s="297" t="inlineStr">
+      <c r="O9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P9" s="297">
+      <c r="P9" s="300">
         <f>IF(H13="","",H13)</f>
         <v/>
       </c>
-      <c r="Q9" s="297">
+      <c r="Q9" s="300">
         <f>IF(J15="","",J15)</f>
         <v/>
       </c>
-      <c r="R9" s="297" t="inlineStr">
+      <c r="R9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S9" s="297">
+      <c r="S9" s="300">
         <f>IF(H15="","",H15)</f>
         <v/>
       </c>
-      <c r="T9" s="297">
+      <c r="T9" s="300">
         <f>IF(J17="","",J17)</f>
         <v/>
       </c>
-      <c r="U9" s="297" t="inlineStr">
+      <c r="U9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V9" s="297">
+      <c r="V9" s="300">
         <f>IF(H17="","",H17)</f>
         <v/>
       </c>
-      <c r="W9" s="297">
+      <c r="W9" s="300">
         <f>IF(J19="","",J19)</f>
         <v/>
       </c>
-      <c r="X9" s="297" t="inlineStr">
+      <c r="X9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y9" s="297">
+      <c r="Y9" s="300">
         <f>IF(H19="","",H19)</f>
         <v/>
       </c>
-      <c r="Z9" s="297">
+      <c r="Z9" s="300">
         <f>IF(J21="","",J21)</f>
         <v/>
       </c>
-      <c r="AA9" s="297" t="inlineStr">
+      <c r="AA9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB9" s="297">
+      <c r="AB9" s="300">
         <f>IF(H21="","",H21)</f>
         <v/>
       </c>
-      <c r="AC9" s="297">
+      <c r="AC9" s="300">
         <f>IF(J23="","",J23)</f>
         <v/>
       </c>
-      <c r="AD9" s="297" t="inlineStr">
+      <c r="AD9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE9" s="297">
+      <c r="AE9" s="300">
         <f>IF(H23="","",H23)</f>
         <v/>
       </c>
-      <c r="AF9" s="297">
+      <c r="AF9" s="300">
         <f>IF(J25="","",J25)</f>
         <v/>
       </c>
-      <c r="AG9" s="297" t="inlineStr">
+      <c r="AG9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH9" s="297">
+      <c r="AH9" s="300">
         <f>IF(H25="","",H25)</f>
         <v/>
       </c>
-      <c r="AI9" s="297">
+      <c r="AI9" s="300">
         <f>IF(J27="","",J27)</f>
         <v/>
       </c>
-      <c r="AJ9" s="297" t="inlineStr">
+      <c r="AJ9" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK9" s="297">
+      <c r="AK9" s="300">
         <f>IF(H27="","",H27)</f>
         <v/>
       </c>
-      <c r="AL9" s="281" t="n"/>
-      <c r="AM9" s="286" t="n"/>
-      <c r="AN9" s="286" t="n"/>
-      <c r="AO9" s="286" t="n"/>
-      <c r="AP9" s="286" t="n"/>
-      <c r="AQ9" s="286" t="n"/>
-      <c r="AR9" s="286" t="n"/>
-      <c r="AS9" s="298" t="n"/>
-      <c r="AV9" s="286" t="n"/>
-      <c r="AW9" s="288" t="n"/>
-      <c r="AX9" s="286" t="n"/>
+      <c r="AL9" s="284" t="n"/>
+      <c r="AM9" s="289" t="n"/>
+      <c r="AN9" s="289" t="n"/>
+      <c r="AO9" s="289" t="n"/>
+      <c r="AP9" s="289" t="n"/>
+      <c r="AQ9" s="289" t="n"/>
+      <c r="AR9" s="289" t="n"/>
+      <c r="AS9" s="301" t="n"/>
+      <c r="AV9" s="289" t="n"/>
+      <c r="AW9" s="291" t="n"/>
+      <c r="AX9" s="289" t="n"/>
       <c r="AZ9" s="5" t="n">
         <v>4</v>
       </c>
@@ -3908,107 +3918,107 @@
       </c>
     </row>
     <row r="10" ht="46.9" customHeight="1" s="257">
-      <c r="A10" s="271" t="n"/>
-      <c r="B10" s="271" t="n">
+      <c r="A10" s="272" t="n"/>
+      <c r="B10" s="273" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="271">
+      <c r="C10" s="273">
         <f>AX10</f>
         <v/>
       </c>
-      <c r="D10" s="272" t="n"/>
-      <c r="E10" s="273">
+      <c r="D10" s="274" t="n"/>
+      <c r="E10" s="275">
         <f>IF(E11="","",IF(E11="☂","☂",IF(E11&gt;G11,"○",IF(E11=G11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F10" s="290" t="n"/>
-      <c r="G10" s="291" t="n"/>
-      <c r="H10" s="273">
+      <c r="F10" s="293" t="n"/>
+      <c r="G10" s="294" t="n"/>
+      <c r="H10" s="275">
         <f>IF(H11="","",IF(H11="☂","☂",IF(H11&gt;J11,"○",IF(H11=J11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I10" s="290" t="n"/>
-      <c r="J10" s="291" t="n"/>
-      <c r="K10" s="273" t="n"/>
-      <c r="L10" s="292" t="n"/>
-      <c r="M10" s="269" t="n"/>
-      <c r="N10" s="274">
+      <c r="I10" s="293" t="n"/>
+      <c r="J10" s="294" t="n"/>
+      <c r="K10" s="275" t="n"/>
+      <c r="L10" s="295" t="n"/>
+      <c r="M10" s="270" t="n"/>
+      <c r="N10" s="276">
         <f>IF(N11="","",IF(N11="☂","☂",IF(N11&gt;P11,"○",IF(N11=P11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O10" s="294" t="n"/>
-      <c r="P10" s="295" t="n"/>
-      <c r="Q10" s="274">
+      <c r="O10" s="297" t="n"/>
+      <c r="P10" s="298" t="n"/>
+      <c r="Q10" s="276">
         <f>IF(Q11="","",IF(Q11="☂","☂",IF(Q11&gt;S11,"○",IF(Q11=S11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R10" s="294" t="n"/>
-      <c r="S10" s="295" t="n"/>
-      <c r="T10" s="274">
+      <c r="R10" s="297" t="n"/>
+      <c r="S10" s="298" t="n"/>
+      <c r="T10" s="276">
         <f>IF(T11="","",IF(T11="☂","☂",IF(T11&gt;V11,"○",IF(T11=V11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U10" s="294" t="n"/>
-      <c r="V10" s="295" t="n"/>
-      <c r="W10" s="274">
+      <c r="U10" s="297" t="n"/>
+      <c r="V10" s="298" t="n"/>
+      <c r="W10" s="276">
         <f>IF(W11="","",IF(W11="☂","☂",IF(W11&gt;Y11,"○",IF(W11=Y11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X10" s="294" t="n"/>
-      <c r="Y10" s="295" t="n"/>
-      <c r="Z10" s="274">
+      <c r="X10" s="297" t="n"/>
+      <c r="Y10" s="298" t="n"/>
+      <c r="Z10" s="276">
         <f>IF(Z11="","",IF(Z11="☂","☂",IF(Z11&gt;AB11,"○",IF(Z11=AB11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA10" s="294" t="n"/>
-      <c r="AB10" s="295" t="n"/>
-      <c r="AC10" s="274">
+      <c r="AA10" s="297" t="n"/>
+      <c r="AB10" s="298" t="n"/>
+      <c r="AC10" s="276">
         <f>IF(AC11="","",IF(AC11="☂","☂",IF(AC11&gt;AE11,"○",IF(AC11=AE11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD10" s="294" t="n"/>
-      <c r="AE10" s="295" t="n"/>
-      <c r="AF10" s="274">
+      <c r="AD10" s="297" t="n"/>
+      <c r="AE10" s="298" t="n"/>
+      <c r="AF10" s="276">
         <f>IF(AF11="","",IF(AF11="☂","☂",IF(AF11&gt;AH11,"○",IF(AF11=AH11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG10" s="294" t="n"/>
-      <c r="AH10" s="295" t="n"/>
-      <c r="AI10" s="274">
+      <c r="AG10" s="297" t="n"/>
+      <c r="AH10" s="298" t="n"/>
+      <c r="AI10" s="276">
         <f>IF(AI11="","",IF(AI11="☂","☂",IF(AI11&gt;AK11,"○",IF(AI11=AK11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ10" s="294" t="n"/>
-      <c r="AK10" s="295" t="n"/>
-      <c r="AL10" s="277">
+      <c r="AJ10" s="297" t="n"/>
+      <c r="AK10" s="298" t="n"/>
+      <c r="AL10" s="279">
         <f>COUNTIF(E10:AK10,"○")</f>
         <v/>
       </c>
-      <c r="AM10" s="278">
+      <c r="AM10" s="280">
         <f>COUNTIF(E10:AK10,"△")</f>
         <v/>
       </c>
-      <c r="AN10" s="278">
+      <c r="AN10" s="280">
         <f>COUNTIF(E10:AK10,"×")</f>
         <v/>
       </c>
-      <c r="AO10" s="279">
+      <c r="AO10" s="281">
         <f>AL10*3+AM10*1</f>
         <v/>
       </c>
-      <c r="AP10" s="278">
+      <c r="AP10" s="280">
         <f>SUM(G11,J11,M11,P11,S11,V11,Y11,AB11,AK11)</f>
         <v/>
       </c>
-      <c r="AQ10" s="278">
+      <c r="AQ10" s="280">
         <f>SUM(E11,H11,K11,N11,Q11,T11,W11,Z11,AI11)</f>
         <v/>
       </c>
-      <c r="AR10" s="278">
+      <c r="AR10" s="280">
         <f>$AY$21-AL10-AM10-AN10</f>
         <v/>
       </c>
-      <c r="AS10" s="280">
+      <c r="AS10" s="282">
         <f>IFERROR(_xlfn.RANK.EQ(AO10,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4032,138 +4042,138 @@
       </c>
     </row>
     <row r="11" ht="46.9" customHeight="1" s="257">
-      <c r="A11" s="271" t="n"/>
-      <c r="B11" s="281" t="n"/>
-      <c r="C11" s="282" t="n"/>
-      <c r="D11" s="283" t="n"/>
-      <c r="E11" s="299" t="n"/>
-      <c r="F11" s="285" t="n"/>
-      <c r="G11" s="299" t="n"/>
-      <c r="H11" s="299" t="n"/>
-      <c r="I11" s="285" t="inlineStr">
+      <c r="A11" s="283" t="n"/>
+      <c r="B11" s="284" t="n"/>
+      <c r="C11" s="285" t="n"/>
+      <c r="D11" s="286" t="n"/>
+      <c r="E11" s="302" t="n"/>
+      <c r="F11" s="288" t="n"/>
+      <c r="G11" s="302" t="n"/>
+      <c r="H11" s="302" t="n"/>
+      <c r="I11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="299" t="n"/>
-      <c r="K11" s="282" t="n"/>
-      <c r="L11" s="270" t="n"/>
-      <c r="M11" s="283" t="n"/>
-      <c r="N11" s="285">
+      <c r="J11" s="302" t="n"/>
+      <c r="K11" s="285" t="n"/>
+      <c r="L11" s="271" t="n"/>
+      <c r="M11" s="286" t="n"/>
+      <c r="N11" s="288">
         <f>IF(M13="","",M13)</f>
         <v/>
       </c>
-      <c r="O11" s="285" t="inlineStr">
+      <c r="O11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="285">
+      <c r="P11" s="288">
         <f>IF(K13="","",K13)</f>
         <v/>
       </c>
-      <c r="Q11" s="285">
+      <c r="Q11" s="288">
         <f>IF(M15="","",M15)</f>
         <v/>
       </c>
-      <c r="R11" s="285" t="inlineStr">
+      <c r="R11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S11" s="285">
+      <c r="S11" s="288">
         <f>IF(K15="","",K15)</f>
         <v/>
       </c>
-      <c r="T11" s="285">
+      <c r="T11" s="288">
         <f>IF(M17="","",M17)</f>
         <v/>
       </c>
-      <c r="U11" s="285" t="inlineStr">
+      <c r="U11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V11" s="285">
+      <c r="V11" s="288">
         <f>IF(K17="","",K17)</f>
         <v/>
       </c>
-      <c r="W11" s="285">
+      <c r="W11" s="288">
         <f>IF(M19="","",M19)</f>
         <v/>
       </c>
-      <c r="X11" s="285" t="inlineStr">
+      <c r="X11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y11" s="285">
+      <c r="Y11" s="288">
         <f>IF(K19="","",K19)</f>
         <v/>
       </c>
-      <c r="Z11" s="285">
+      <c r="Z11" s="288">
         <f>IF(M21="","",M21)</f>
         <v/>
       </c>
-      <c r="AA11" s="285" t="inlineStr">
+      <c r="AA11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB11" s="285">
+      <c r="AB11" s="288">
         <f>IF(K21="","",K21)</f>
         <v/>
       </c>
-      <c r="AC11" s="285">
+      <c r="AC11" s="288">
         <f>IF(M23="","",M23)</f>
         <v/>
       </c>
-      <c r="AD11" s="285" t="inlineStr">
+      <c r="AD11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE11" s="285">
+      <c r="AE11" s="288">
         <f>IF(K23="","",K23)</f>
         <v/>
       </c>
-      <c r="AF11" s="285">
+      <c r="AF11" s="288">
         <f>IF(M25="","",M25)</f>
         <v/>
       </c>
-      <c r="AG11" s="285" t="inlineStr">
+      <c r="AG11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH11" s="285">
+      <c r="AH11" s="288">
         <f>IF(K25="","",K25)</f>
         <v/>
       </c>
-      <c r="AI11" s="285">
+      <c r="AI11" s="288">
         <f>IF(M27="","",M27)</f>
         <v/>
       </c>
-      <c r="AJ11" s="285" t="inlineStr">
+      <c r="AJ11" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK11" s="285">
+      <c r="AK11" s="288">
         <f>IF(K27="","",K27)</f>
         <v/>
       </c>
-      <c r="AL11" s="281" t="n"/>
-      <c r="AM11" s="286" t="n"/>
-      <c r="AN11" s="286" t="n"/>
-      <c r="AO11" s="286" t="n"/>
-      <c r="AP11" s="286" t="n"/>
-      <c r="AQ11" s="286" t="n"/>
-      <c r="AR11" s="286" t="n"/>
-      <c r="AS11" s="298" t="n"/>
-      <c r="AV11" s="286" t="n"/>
-      <c r="AW11" s="288" t="n"/>
-      <c r="AX11" s="286" t="n"/>
+      <c r="AL11" s="284" t="n"/>
+      <c r="AM11" s="289" t="n"/>
+      <c r="AN11" s="289" t="n"/>
+      <c r="AO11" s="289" t="n"/>
+      <c r="AP11" s="289" t="n"/>
+      <c r="AQ11" s="289" t="n"/>
+      <c r="AR11" s="289" t="n"/>
+      <c r="AS11" s="301" t="n"/>
+      <c r="AV11" s="289" t="n"/>
+      <c r="AW11" s="291" t="n"/>
+      <c r="AX11" s="289" t="n"/>
       <c r="AZ11" s="5" t="n">
         <v>6</v>
       </c>
@@ -4174,107 +4184,107 @@
       </c>
     </row>
     <row r="12" ht="46.9" customHeight="1" s="257">
-      <c r="A12" s="271" t="n"/>
-      <c r="B12" s="271" t="n">
+      <c r="A12" s="272" t="n"/>
+      <c r="B12" s="273" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="271">
+      <c r="C12" s="273">
         <f>AX12</f>
         <v/>
       </c>
-      <c r="D12" s="272" t="n"/>
-      <c r="E12" s="289">
+      <c r="D12" s="274" t="n"/>
+      <c r="E12" s="292">
         <f>IF(E13="","",IF(E13="☂","☂",IF(E13&gt;G13,"○",IF(E13=G13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F12" s="290" t="n"/>
-      <c r="G12" s="291" t="n"/>
-      <c r="H12" s="289">
+      <c r="F12" s="293" t="n"/>
+      <c r="G12" s="294" t="n"/>
+      <c r="H12" s="292">
         <f>IF(H13="","",IF(H13="☂","☂",IF(H13&gt;J13,"○",IF(H13=J13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I12" s="290" t="n"/>
-      <c r="J12" s="291" t="n"/>
-      <c r="K12" s="289">
+      <c r="I12" s="293" t="n"/>
+      <c r="J12" s="294" t="n"/>
+      <c r="K12" s="292">
         <f>IF(K13="","",IF(K13="☂","☂",IF(K13&gt;M13,"○",IF(K13=M13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L12" s="290" t="n"/>
-      <c r="M12" s="291" t="n"/>
-      <c r="N12" s="289" t="n"/>
-      <c r="O12" s="292" t="n"/>
-      <c r="P12" s="269" t="n"/>
-      <c r="Q12" s="293">
+      <c r="L12" s="293" t="n"/>
+      <c r="M12" s="294" t="n"/>
+      <c r="N12" s="292" t="n"/>
+      <c r="O12" s="295" t="n"/>
+      <c r="P12" s="270" t="n"/>
+      <c r="Q12" s="296">
         <f>IF(Q13="","",IF(Q13="☂","☂",IF(Q13&gt;S13,"○",IF(Q13=S13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R12" s="294" t="n"/>
-      <c r="S12" s="295" t="n"/>
-      <c r="T12" s="293">
+      <c r="R12" s="297" t="n"/>
+      <c r="S12" s="298" t="n"/>
+      <c r="T12" s="296">
         <f>IF(T13="","",IF(T13="☂","☂",IF(T13&gt;V13,"○",IF(T13=V13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U12" s="294" t="n"/>
-      <c r="V12" s="295" t="n"/>
-      <c r="W12" s="293">
+      <c r="U12" s="297" t="n"/>
+      <c r="V12" s="298" t="n"/>
+      <c r="W12" s="296">
         <f>IF(W13="","",IF(W13="☂","☂",IF(W13&gt;Y13,"○",IF(W13=Y13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X12" s="294" t="n"/>
-      <c r="Y12" s="295" t="n"/>
-      <c r="Z12" s="293">
+      <c r="X12" s="297" t="n"/>
+      <c r="Y12" s="298" t="n"/>
+      <c r="Z12" s="296">
         <f>IF(Z13="","",IF(Z13="☂","☂",IF(Z13&gt;AB13,"○",IF(Z13=AB13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA12" s="294" t="n"/>
-      <c r="AB12" s="295" t="n"/>
-      <c r="AC12" s="293">
+      <c r="AA12" s="297" t="n"/>
+      <c r="AB12" s="298" t="n"/>
+      <c r="AC12" s="296">
         <f>IF(AC13="","",IF(AC13="☂","☂",IF(AC13&gt;AE13,"○",IF(AC13=AE13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD12" s="294" t="n"/>
-      <c r="AE12" s="295" t="n"/>
-      <c r="AF12" s="293">
+      <c r="AD12" s="297" t="n"/>
+      <c r="AE12" s="298" t="n"/>
+      <c r="AF12" s="296">
         <f>IF(AF13="","",IF(AF13="☂","☂",IF(AF13&gt;AH13,"○",IF(AF13=AH13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG12" s="294" t="n"/>
-      <c r="AH12" s="295" t="n"/>
-      <c r="AI12" s="293">
+      <c r="AG12" s="297" t="n"/>
+      <c r="AH12" s="298" t="n"/>
+      <c r="AI12" s="296">
         <f>IF(AI13="","",IF(AI13="☂","☂",IF(AI13&gt;AK13,"○",IF(AI13=AK13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ12" s="294" t="n"/>
-      <c r="AK12" s="295" t="n"/>
-      <c r="AL12" s="277">
+      <c r="AJ12" s="297" t="n"/>
+      <c r="AK12" s="298" t="n"/>
+      <c r="AL12" s="279">
         <f>COUNTIF(E12:AK12,"○")</f>
         <v/>
       </c>
-      <c r="AM12" s="278">
+      <c r="AM12" s="280">
         <f>COUNTIF(E12:AK12,"△")</f>
         <v/>
       </c>
-      <c r="AN12" s="278">
+      <c r="AN12" s="280">
         <f>COUNTIF(E12:AK12,"×")</f>
         <v/>
       </c>
-      <c r="AO12" s="279">
+      <c r="AO12" s="281">
         <f>AL12*3+AM12*1</f>
         <v/>
       </c>
-      <c r="AP12" s="278">
+      <c r="AP12" s="280">
         <f>SUM(G13,J13,M13,P13,S13,V13,Y13,AB13,AK13)</f>
         <v/>
       </c>
-      <c r="AQ12" s="278">
+      <c r="AQ12" s="280">
         <f>SUM(E13,H13,K13,N13,Q13,T13,W13,Z13,AI13)</f>
         <v/>
       </c>
-      <c r="AR12" s="278">
+      <c r="AR12" s="280">
         <f>$AY$21-AL12-AM12-AN12</f>
         <v/>
       </c>
-      <c r="AS12" s="280">
+      <c r="AS12" s="282">
         <f>IFERROR(_xlfn.RANK.EQ(AO12,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4294,243 +4304,243 @@
       <c r="BA12" s="6" t="n"/>
     </row>
     <row r="13" ht="46.9" customHeight="1" s="257">
-      <c r="A13" s="271" t="n"/>
-      <c r="B13" s="281" t="n"/>
-      <c r="C13" s="282" t="n"/>
-      <c r="D13" s="283" t="n"/>
-      <c r="E13" s="296" t="n"/>
-      <c r="F13" s="297" t="inlineStr">
+      <c r="A13" s="283" t="n"/>
+      <c r="B13" s="284" t="n"/>
+      <c r="C13" s="285" t="n"/>
+      <c r="D13" s="286" t="n"/>
+      <c r="E13" s="299" t="n"/>
+      <c r="F13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="296" t="n"/>
-      <c r="H13" s="296" t="n"/>
-      <c r="I13" s="297" t="inlineStr">
+      <c r="G13" s="299" t="n"/>
+      <c r="H13" s="299" t="n"/>
+      <c r="I13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="296" t="n"/>
-      <c r="K13" s="296" t="n"/>
-      <c r="L13" s="297" t="inlineStr">
+      <c r="J13" s="299" t="n"/>
+      <c r="K13" s="299" t="n"/>
+      <c r="L13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M13" s="296" t="n"/>
-      <c r="N13" s="282" t="n"/>
-      <c r="O13" s="270" t="n"/>
-      <c r="P13" s="283" t="n"/>
-      <c r="Q13" s="297">
+      <c r="M13" s="299" t="n"/>
+      <c r="N13" s="285" t="n"/>
+      <c r="O13" s="271" t="n"/>
+      <c r="P13" s="286" t="n"/>
+      <c r="Q13" s="300">
         <f>IF(P15="","",P15)</f>
         <v/>
       </c>
-      <c r="R13" s="297" t="inlineStr">
+      <c r="R13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S13" s="297">
+      <c r="S13" s="300">
         <f>IF(N15="","",N15)</f>
         <v/>
       </c>
-      <c r="T13" s="297">
+      <c r="T13" s="300">
         <f>IF(P17="","",P17)</f>
         <v/>
       </c>
-      <c r="U13" s="297" t="inlineStr">
+      <c r="U13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V13" s="297">
+      <c r="V13" s="300">
         <f>IF(N17="","",N17)</f>
         <v/>
       </c>
-      <c r="W13" s="297">
+      <c r="W13" s="300">
         <f>IF(P19="","",P19)</f>
         <v/>
       </c>
-      <c r="X13" s="297" t="inlineStr">
+      <c r="X13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y13" s="297">
+      <c r="Y13" s="300">
         <f>IF(N19="","",N19)</f>
         <v/>
       </c>
-      <c r="Z13" s="297">
+      <c r="Z13" s="300">
         <f>IF(P21="","",P21)</f>
         <v/>
       </c>
-      <c r="AA13" s="297" t="inlineStr">
+      <c r="AA13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB13" s="297">
+      <c r="AB13" s="300">
         <f>IF(N21="","",N21)</f>
         <v/>
       </c>
-      <c r="AC13" s="297">
+      <c r="AC13" s="300">
         <f>IF(P23="","",P23)</f>
         <v/>
       </c>
-      <c r="AD13" s="297" t="inlineStr">
+      <c r="AD13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE13" s="297">
+      <c r="AE13" s="300">
         <f>IF(N23="","",N23)</f>
         <v/>
       </c>
-      <c r="AF13" s="297">
+      <c r="AF13" s="300">
         <f>IF(P25="","",P25)</f>
         <v/>
       </c>
-      <c r="AG13" s="297" t="inlineStr">
+      <c r="AG13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH13" s="297">
+      <c r="AH13" s="300">
         <f>IF(N25="","",N25)</f>
         <v/>
       </c>
-      <c r="AI13" s="297">
+      <c r="AI13" s="300">
         <f>IF(P27="","",P27)</f>
         <v/>
       </c>
-      <c r="AJ13" s="297" t="inlineStr">
+      <c r="AJ13" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK13" s="297">
+      <c r="AK13" s="300">
         <f>IF(N27="","",N27)</f>
         <v/>
       </c>
-      <c r="AL13" s="281" t="n"/>
-      <c r="AM13" s="286" t="n"/>
-      <c r="AN13" s="286" t="n"/>
-      <c r="AO13" s="286" t="n"/>
-      <c r="AP13" s="286" t="n"/>
-      <c r="AQ13" s="286" t="n"/>
-      <c r="AR13" s="286" t="n"/>
-      <c r="AS13" s="298" t="n"/>
-      <c r="AV13" s="286" t="n"/>
-      <c r="AW13" s="288" t="n"/>
-      <c r="AX13" s="286" t="n"/>
+      <c r="AL13" s="284" t="n"/>
+      <c r="AM13" s="289" t="n"/>
+      <c r="AN13" s="289" t="n"/>
+      <c r="AO13" s="289" t="n"/>
+      <c r="AP13" s="289" t="n"/>
+      <c r="AQ13" s="289" t="n"/>
+      <c r="AR13" s="289" t="n"/>
+      <c r="AS13" s="301" t="n"/>
+      <c r="AV13" s="289" t="n"/>
+      <c r="AW13" s="291" t="n"/>
+      <c r="AX13" s="289" t="n"/>
       <c r="AZ13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="BA13" s="6" t="n"/>
     </row>
     <row r="14" ht="46.9" customHeight="1" s="257">
-      <c r="A14" s="271" t="n"/>
-      <c r="B14" s="271" t="n">
+      <c r="A14" s="272" t="n"/>
+      <c r="B14" s="273" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="271">
+      <c r="C14" s="273">
         <f>AX14</f>
         <v/>
       </c>
-      <c r="D14" s="272" t="n"/>
-      <c r="E14" s="273">
+      <c r="D14" s="274" t="n"/>
+      <c r="E14" s="275">
         <f>IF(E15="","",IF(E15="☂","☂",IF(E15&gt;G15,"○",IF(E15=G15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F14" s="290" t="n"/>
-      <c r="G14" s="291" t="n"/>
-      <c r="H14" s="273">
+      <c r="F14" s="293" t="n"/>
+      <c r="G14" s="294" t="n"/>
+      <c r="H14" s="275">
         <f>IF(H15="","",IF(H15="☂","☂",IF(H15&gt;J15,"○",IF(H15=J15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I14" s="290" t="n"/>
-      <c r="J14" s="291" t="n"/>
-      <c r="K14" s="273">
+      <c r="I14" s="293" t="n"/>
+      <c r="J14" s="294" t="n"/>
+      <c r="K14" s="275">
         <f>IF(K15="","",IF(K15="☂","☂",IF(K15&gt;M15,"○",IF(K15=M15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L14" s="290" t="n"/>
-      <c r="M14" s="291" t="n"/>
-      <c r="N14" s="274">
+      <c r="L14" s="293" t="n"/>
+      <c r="M14" s="294" t="n"/>
+      <c r="N14" s="276">
         <f>IF(N15="","",IF(N15="☂","☂",IF(N15&gt;P15,"○",IF(N15=P15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O14" s="300" t="n"/>
-      <c r="P14" s="301" t="n"/>
-      <c r="Q14" s="273" t="n"/>
-      <c r="R14" s="292" t="n"/>
-      <c r="S14" s="269" t="n"/>
-      <c r="T14" s="274">
+      <c r="O14" s="303" t="n"/>
+      <c r="P14" s="304" t="n"/>
+      <c r="Q14" s="275" t="n"/>
+      <c r="R14" s="295" t="n"/>
+      <c r="S14" s="270" t="n"/>
+      <c r="T14" s="276">
         <f>IF(T15="","",IF(T15="☂","☂",IF(T15&gt;V15,"○",IF(T15=V15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U14" s="294" t="n"/>
-      <c r="V14" s="295" t="n"/>
-      <c r="W14" s="274">
+      <c r="U14" s="297" t="n"/>
+      <c r="V14" s="298" t="n"/>
+      <c r="W14" s="276">
         <f>IF(W15="","",IF(W15="☂","☂",IF(W15&gt;Y15,"○",IF(W15=Y15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X14" s="294" t="n"/>
-      <c r="Y14" s="295" t="n"/>
-      <c r="Z14" s="274">
+      <c r="X14" s="297" t="n"/>
+      <c r="Y14" s="298" t="n"/>
+      <c r="Z14" s="276">
         <f>IF(Z15="","",IF(Z15="☂","☂",IF(Z15&gt;AB15,"○",IF(Z15=AB15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA14" s="294" t="n"/>
-      <c r="AB14" s="295" t="n"/>
-      <c r="AC14" s="274">
+      <c r="AA14" s="297" t="n"/>
+      <c r="AB14" s="298" t="n"/>
+      <c r="AC14" s="276">
         <f>IF(AC15="","",IF(AC15="☂","☂",IF(AC15&gt;AE15,"○",IF(AC15=AE15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD14" s="294" t="n"/>
-      <c r="AE14" s="295" t="n"/>
-      <c r="AF14" s="274">
+      <c r="AD14" s="297" t="n"/>
+      <c r="AE14" s="298" t="n"/>
+      <c r="AF14" s="276">
         <f>IF(AF15="","",IF(AF15="☂","☂",IF(AF15&gt;AH15,"○",IF(AF15=AH15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG14" s="294" t="n"/>
-      <c r="AH14" s="295" t="n"/>
-      <c r="AI14" s="274">
+      <c r="AG14" s="297" t="n"/>
+      <c r="AH14" s="298" t="n"/>
+      <c r="AI14" s="276">
         <f>IF(AI15="","",IF(AI15="☂","☂",IF(AI15&gt;AK15,"○",IF(AI15=AK15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ14" s="294" t="n"/>
-      <c r="AK14" s="295" t="n"/>
-      <c r="AL14" s="277">
+      <c r="AJ14" s="297" t="n"/>
+      <c r="AK14" s="298" t="n"/>
+      <c r="AL14" s="279">
         <f>COUNTIF(E14:AK14,"○")</f>
         <v/>
       </c>
-      <c r="AM14" s="278">
+      <c r="AM14" s="280">
         <f>COUNTIF(E14:AK14,"△")</f>
         <v/>
       </c>
-      <c r="AN14" s="278">
+      <c r="AN14" s="280">
         <f>COUNTIF(E14:AK14,"×")</f>
         <v/>
       </c>
-      <c r="AO14" s="279">
+      <c r="AO14" s="281">
         <f>AL14*3+AM14*1</f>
         <v/>
       </c>
-      <c r="AP14" s="278">
+      <c r="AP14" s="280">
         <f>SUM(G15,J15,M15,P15,S15,V15,Y15,AB15,AK15)</f>
         <v/>
       </c>
-      <c r="AQ14" s="278">
+      <c r="AQ14" s="280">
         <f>SUM(E15,H15,K15,N15,Q15,T15,W15,Z15,AI15)</f>
         <v/>
       </c>
-      <c r="AR14" s="278">
+      <c r="AR14" s="280">
         <f>$AY$21-AL14-AM14-AN14</f>
         <v/>
       </c>
-      <c r="AS14" s="280">
+      <c r="AS14" s="282">
         <f>IFERROR(_xlfn.RANK.EQ(AO14,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4550,237 +4560,237 @@
       <c r="BA14" s="6" t="n"/>
     </row>
     <row r="15" ht="46.9" customHeight="1" s="257">
-      <c r="A15" s="271" t="n"/>
-      <c r="B15" s="281" t="n"/>
-      <c r="C15" s="282" t="n"/>
-      <c r="D15" s="283" t="n"/>
-      <c r="E15" s="299" t="n"/>
-      <c r="F15" s="285" t="inlineStr">
+      <c r="A15" s="283" t="n"/>
+      <c r="B15" s="284" t="n"/>
+      <c r="C15" s="285" t="n"/>
+      <c r="D15" s="286" t="n"/>
+      <c r="E15" s="302" t="n"/>
+      <c r="F15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="299" t="n"/>
-      <c r="H15" s="299" t="n"/>
-      <c r="I15" s="285" t="inlineStr">
+      <c r="G15" s="302" t="n"/>
+      <c r="H15" s="302" t="n"/>
+      <c r="I15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="299" t="n"/>
-      <c r="K15" s="299" t="n"/>
-      <c r="L15" s="285" t="inlineStr">
+      <c r="J15" s="302" t="n"/>
+      <c r="K15" s="302" t="n"/>
+      <c r="L15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="299" t="n"/>
-      <c r="N15" s="299" t="n"/>
-      <c r="O15" s="285" t="inlineStr">
+      <c r="M15" s="302" t="n"/>
+      <c r="N15" s="302" t="n"/>
+      <c r="O15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="299" t="n"/>
-      <c r="Q15" s="282" t="n"/>
-      <c r="R15" s="270" t="n"/>
-      <c r="S15" s="283" t="n"/>
-      <c r="T15" s="285">
+      <c r="P15" s="302" t="n"/>
+      <c r="Q15" s="285" t="n"/>
+      <c r="R15" s="271" t="n"/>
+      <c r="S15" s="286" t="n"/>
+      <c r="T15" s="288">
         <f>IF(S17="","",S17)</f>
         <v/>
       </c>
-      <c r="U15" s="285" t="inlineStr">
+      <c r="U15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V15" s="285">
+      <c r="V15" s="288">
         <f>IF(Q17="","",Q17)</f>
         <v/>
       </c>
-      <c r="W15" s="285">
+      <c r="W15" s="288">
         <f>IF(S19="","",S19)</f>
         <v/>
       </c>
-      <c r="X15" s="285" t="inlineStr">
+      <c r="X15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y15" s="285">
+      <c r="Y15" s="288">
         <f>IF(Q19="","",Q19)</f>
         <v/>
       </c>
-      <c r="Z15" s="285">
+      <c r="Z15" s="288">
         <f>IF(S21="","",S21)</f>
         <v/>
       </c>
-      <c r="AA15" s="285" t="inlineStr">
+      <c r="AA15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB15" s="285">
+      <c r="AB15" s="288">
         <f>IF(Q21="","",Q21)</f>
         <v/>
       </c>
-      <c r="AC15" s="285">
+      <c r="AC15" s="288">
         <f>IF(S23="","",S23)</f>
         <v/>
       </c>
-      <c r="AD15" s="285" t="inlineStr">
+      <c r="AD15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE15" s="285">
+      <c r="AE15" s="288">
         <f>IF(Q31="","",Q31)</f>
         <v/>
       </c>
-      <c r="AF15" s="285">
+      <c r="AF15" s="288">
         <f>IF(S25="","",S25)</f>
         <v/>
       </c>
-      <c r="AG15" s="285" t="inlineStr">
+      <c r="AG15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH15" s="285">
+      <c r="AH15" s="288">
         <f>IF(Q25="","",Q25)</f>
         <v/>
       </c>
-      <c r="AI15" s="285">
+      <c r="AI15" s="288">
         <f>IF(S27="","",S27)</f>
         <v/>
       </c>
-      <c r="AJ15" s="285" t="inlineStr">
+      <c r="AJ15" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK15" s="285">
+      <c r="AK15" s="288">
         <f>IF(Q27="","",Q27)</f>
         <v/>
       </c>
-      <c r="AL15" s="281" t="n"/>
-      <c r="AM15" s="286" t="n"/>
-      <c r="AN15" s="286" t="n"/>
-      <c r="AO15" s="286" t="n"/>
-      <c r="AP15" s="286" t="n"/>
-      <c r="AQ15" s="286" t="n"/>
-      <c r="AR15" s="286" t="n"/>
-      <c r="AS15" s="298" t="n"/>
-      <c r="AV15" s="286" t="n"/>
-      <c r="AW15" s="288" t="n"/>
-      <c r="AX15" s="286" t="n"/>
+      <c r="AL15" s="284" t="n"/>
+      <c r="AM15" s="289" t="n"/>
+      <c r="AN15" s="289" t="n"/>
+      <c r="AO15" s="289" t="n"/>
+      <c r="AP15" s="289" t="n"/>
+      <c r="AQ15" s="289" t="n"/>
+      <c r="AR15" s="289" t="n"/>
+      <c r="AS15" s="301" t="n"/>
+      <c r="AV15" s="289" t="n"/>
+      <c r="AW15" s="291" t="n"/>
+      <c r="AX15" s="289" t="n"/>
       <c r="AZ15" s="5" t="n">
         <v>10</v>
       </c>
       <c r="BA15" s="6" t="n"/>
     </row>
     <row r="16" ht="46.9" customHeight="1" s="257">
-      <c r="A16" s="271" t="n"/>
-      <c r="B16" s="271" t="n">
+      <c r="A16" s="272" t="n"/>
+      <c r="B16" s="273" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="271">
+      <c r="C16" s="273">
         <f>AX16</f>
         <v/>
       </c>
-      <c r="D16" s="272" t="n"/>
-      <c r="E16" s="289">
+      <c r="D16" s="274" t="n"/>
+      <c r="E16" s="292">
         <f>IF(E17="","",IF(E17="☂","☂",IF(E17&gt;G17,"○",IF(E17=G17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F16" s="290" t="n"/>
-      <c r="G16" s="291" t="n"/>
-      <c r="H16" s="289">
+      <c r="F16" s="293" t="n"/>
+      <c r="G16" s="294" t="n"/>
+      <c r="H16" s="292">
         <f>IF(H17="","",IF(H17="☂","☂",IF(H17&gt;J17,"○",IF(H17=J17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I16" s="290" t="n"/>
-      <c r="J16" s="291" t="n"/>
-      <c r="K16" s="289">
+      <c r="I16" s="293" t="n"/>
+      <c r="J16" s="294" t="n"/>
+      <c r="K16" s="292">
         <f>IF(K17="","",IF(K17="☂","☂",IF(K17&gt;M17,"○",IF(K17=M17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L16" s="290" t="n"/>
-      <c r="M16" s="291" t="n"/>
-      <c r="N16" s="293">
+      <c r="L16" s="293" t="n"/>
+      <c r="M16" s="294" t="n"/>
+      <c r="N16" s="296">
         <f>IF(N17="","",IF(N17="☂","☂",IF(N17&gt;P17,"○",IF(N17=P17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O16" s="300" t="n"/>
-      <c r="P16" s="301" t="n"/>
-      <c r="Q16" s="293">
+      <c r="O16" s="303" t="n"/>
+      <c r="P16" s="304" t="n"/>
+      <c r="Q16" s="296">
         <f>IF(Q17="","",IF(Q17="☂","☂",IF(Q17&gt;S17,"○",IF(Q17=S17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R16" s="300" t="n"/>
-      <c r="S16" s="301" t="n"/>
-      <c r="T16" s="289" t="n"/>
-      <c r="U16" s="292" t="n"/>
-      <c r="V16" s="269" t="n"/>
-      <c r="W16" s="293">
+      <c r="R16" s="303" t="n"/>
+      <c r="S16" s="304" t="n"/>
+      <c r="T16" s="292" t="n"/>
+      <c r="U16" s="295" t="n"/>
+      <c r="V16" s="270" t="n"/>
+      <c r="W16" s="296">
         <f>IF(W17="","",IF(W17="☂","☂",IF(W17&gt;Y17,"○",IF(W17=Y17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X16" s="294" t="n"/>
-      <c r="Y16" s="295" t="n"/>
-      <c r="Z16" s="293">
+      <c r="X16" s="297" t="n"/>
+      <c r="Y16" s="298" t="n"/>
+      <c r="Z16" s="296">
         <f>IF(Z17="","",IF(Z17="☂","☂",IF(Z17&gt;AB17,"○",IF(Z17=AB17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA16" s="294" t="n"/>
-      <c r="AB16" s="295" t="n"/>
-      <c r="AC16" s="293">
+      <c r="AA16" s="297" t="n"/>
+      <c r="AB16" s="298" t="n"/>
+      <c r="AC16" s="296">
         <f>IF(AC17="","",IF(AC17="☂","☂",IF(AC17&gt;AE17,"○",IF(AC17=AE17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD16" s="294" t="n"/>
-      <c r="AE16" s="295" t="n"/>
-      <c r="AF16" s="293">
+      <c r="AD16" s="297" t="n"/>
+      <c r="AE16" s="298" t="n"/>
+      <c r="AF16" s="296">
         <f>IF(AF17="","",IF(AF17="☂","☂",IF(AF17&gt;AH17,"○",IF(AF17=AH17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG16" s="294" t="n"/>
-      <c r="AH16" s="295" t="n"/>
-      <c r="AI16" s="293">
+      <c r="AG16" s="297" t="n"/>
+      <c r="AH16" s="298" t="n"/>
+      <c r="AI16" s="296">
         <f>IF(AI17="","",IF(AI17="☂","☂",IF(AI17&gt;AK17,"○",IF(AI17=AK17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ16" s="294" t="n"/>
-      <c r="AK16" s="295" t="n"/>
-      <c r="AL16" s="277">
+      <c r="AJ16" s="297" t="n"/>
+      <c r="AK16" s="298" t="n"/>
+      <c r="AL16" s="279">
         <f>COUNTIF(E16:AK16,"○")</f>
         <v/>
       </c>
-      <c r="AM16" s="278">
+      <c r="AM16" s="280">
         <f>COUNTIF(E16:AK16,"△")</f>
         <v/>
       </c>
-      <c r="AN16" s="278">
+      <c r="AN16" s="280">
         <f>COUNTIF(E16:AK16,"×")</f>
         <v/>
       </c>
-      <c r="AO16" s="279">
+      <c r="AO16" s="281">
         <f>AL16*3+AM16*1</f>
         <v/>
       </c>
-      <c r="AP16" s="278">
+      <c r="AP16" s="280">
         <f>SUM(G17,J17,M17,P17,S17,V17,Y17,AB17,AK17)</f>
         <v/>
       </c>
-      <c r="AQ16" s="278">
+      <c r="AQ16" s="280">
         <f>SUM(E17,H17,K17,N17,Q17,T17,W17,Z17,AI17)</f>
         <v/>
       </c>
-      <c r="AR16" s="278">
+      <c r="AR16" s="280">
         <f>$AY$21-AL16-AM16-AN16</f>
         <v/>
       </c>
-      <c r="AS16" s="280">
+      <c r="AS16" s="282">
         <f>IFERROR(_xlfn.RANK.EQ(AO16,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4800,231 +4810,231 @@
       <c r="BA16" s="6" t="n"/>
     </row>
     <row r="17" ht="46.9" customHeight="1" s="257">
-      <c r="A17" s="271" t="n"/>
-      <c r="B17" s="281" t="n"/>
-      <c r="C17" s="282" t="n"/>
-      <c r="D17" s="283" t="n"/>
-      <c r="E17" s="296" t="n"/>
-      <c r="F17" s="297" t="inlineStr">
+      <c r="A17" s="283" t="n"/>
+      <c r="B17" s="284" t="n"/>
+      <c r="C17" s="285" t="n"/>
+      <c r="D17" s="286" t="n"/>
+      <c r="E17" s="299" t="n"/>
+      <c r="F17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="296" t="n"/>
-      <c r="H17" s="296" t="n"/>
-      <c r="I17" s="297" t="inlineStr">
+      <c r="G17" s="299" t="n"/>
+      <c r="H17" s="299" t="n"/>
+      <c r="I17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="296" t="n"/>
-      <c r="K17" s="296" t="n"/>
-      <c r="L17" s="297" t="inlineStr">
+      <c r="J17" s="299" t="n"/>
+      <c r="K17" s="299" t="n"/>
+      <c r="L17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M17" s="296" t="n"/>
-      <c r="N17" s="296" t="n"/>
-      <c r="O17" s="297" t="inlineStr">
+      <c r="M17" s="299" t="n"/>
+      <c r="N17" s="299" t="n"/>
+      <c r="O17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="296" t="n"/>
-      <c r="Q17" s="296" t="n"/>
-      <c r="R17" s="297" t="inlineStr">
+      <c r="P17" s="299" t="n"/>
+      <c r="Q17" s="299" t="n"/>
+      <c r="R17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S17" s="296" t="n"/>
-      <c r="T17" s="282" t="n"/>
-      <c r="U17" s="270" t="n"/>
-      <c r="V17" s="283" t="n"/>
-      <c r="W17" s="297">
+      <c r="S17" s="299" t="n"/>
+      <c r="T17" s="285" t="n"/>
+      <c r="U17" s="271" t="n"/>
+      <c r="V17" s="286" t="n"/>
+      <c r="W17" s="300">
         <f>IF(V19="","",V19)</f>
         <v/>
       </c>
-      <c r="X17" s="297" t="inlineStr">
+      <c r="X17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y17" s="297">
+      <c r="Y17" s="300">
         <f>IF(T19="","",T19)</f>
         <v/>
       </c>
-      <c r="Z17" s="297">
+      <c r="Z17" s="300">
         <f>IF(V21="","",V21)</f>
         <v/>
       </c>
-      <c r="AA17" s="297" t="inlineStr">
+      <c r="AA17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB17" s="297">
+      <c r="AB17" s="300">
         <f>IF(T21="","",T21)</f>
         <v/>
       </c>
-      <c r="AC17" s="297">
+      <c r="AC17" s="300">
         <f>IF(V23="","",V23)</f>
         <v/>
       </c>
-      <c r="AD17" s="297" t="inlineStr">
+      <c r="AD17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE17" s="297">
+      <c r="AE17" s="300">
         <f>IF(T23="","",T23)</f>
         <v/>
       </c>
-      <c r="AF17" s="297">
+      <c r="AF17" s="300">
         <f>IF(V25="","",V25)</f>
         <v/>
       </c>
-      <c r="AG17" s="297" t="inlineStr">
+      <c r="AG17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH17" s="297">
+      <c r="AH17" s="300">
         <f>IF(T25="","",T25)</f>
         <v/>
       </c>
-      <c r="AI17" s="297">
+      <c r="AI17" s="300">
         <f>IF(V27="","",V27)</f>
         <v/>
       </c>
-      <c r="AJ17" s="297" t="inlineStr">
+      <c r="AJ17" s="300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK17" s="297">
+      <c r="AK17" s="300">
         <f>IF(T27="","",T27)</f>
         <v/>
       </c>
-      <c r="AL17" s="281" t="n"/>
-      <c r="AM17" s="286" t="n"/>
-      <c r="AN17" s="286" t="n"/>
-      <c r="AO17" s="286" t="n"/>
-      <c r="AP17" s="286" t="n"/>
-      <c r="AQ17" s="286" t="n"/>
-      <c r="AR17" s="286" t="n"/>
-      <c r="AS17" s="298" t="n"/>
-      <c r="AV17" s="286" t="n"/>
-      <c r="AW17" s="288" t="n"/>
-      <c r="AX17" s="286" t="n"/>
+      <c r="AL17" s="284" t="n"/>
+      <c r="AM17" s="289" t="n"/>
+      <c r="AN17" s="289" t="n"/>
+      <c r="AO17" s="289" t="n"/>
+      <c r="AP17" s="289" t="n"/>
+      <c r="AQ17" s="289" t="n"/>
+      <c r="AR17" s="289" t="n"/>
+      <c r="AS17" s="301" t="n"/>
+      <c r="AV17" s="289" t="n"/>
+      <c r="AW17" s="291" t="n"/>
+      <c r="AX17" s="289" t="n"/>
       <c r="AZ17" s="5" t="n">
         <v>12</v>
       </c>
       <c r="BA17" s="6" t="n"/>
     </row>
     <row r="18" ht="46.9" customHeight="1" s="257">
-      <c r="A18" s="302" t="n"/>
-      <c r="B18" s="303" t="n">
+      <c r="A18" s="305" t="n"/>
+      <c r="B18" s="306" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="304">
+      <c r="C18" s="306">
         <f>AX18</f>
         <v/>
       </c>
-      <c r="D18" s="272" t="n"/>
-      <c r="E18" s="303">
+      <c r="D18" s="274" t="n"/>
+      <c r="E18" s="306">
         <f>IF(E19="","",IF(E19="☂","☂",IF(E19&gt;G19,"○",IF(E19=G19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F18" s="290" t="n"/>
-      <c r="G18" s="291" t="n"/>
-      <c r="H18" s="305">
+      <c r="F18" s="293" t="n"/>
+      <c r="G18" s="294" t="n"/>
+      <c r="H18" s="306">
         <f>IF(H19="","",IF(H19="☂","☂",IF(H19&gt;J19,"○",IF(H19=J19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I18" s="290" t="n"/>
-      <c r="J18" s="291" t="n"/>
-      <c r="K18" s="305">
+      <c r="I18" s="293" t="n"/>
+      <c r="J18" s="294" t="n"/>
+      <c r="K18" s="306">
         <f>IF(K19="","",IF(K19="☂","☂",IF(K19&gt;M19,"○",IF(K19=M19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L18" s="290" t="n"/>
-      <c r="M18" s="291" t="n"/>
-      <c r="N18" s="306">
+      <c r="L18" s="293" t="n"/>
+      <c r="M18" s="294" t="n"/>
+      <c r="N18" s="307">
         <f>IF(N19="","",IF(N19="☂","☂",IF(N19&gt;P19,"○",IF(N19=P19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O18" s="300" t="n"/>
-      <c r="P18" s="301" t="n"/>
-      <c r="Q18" s="306">
+      <c r="O18" s="303" t="n"/>
+      <c r="P18" s="304" t="n"/>
+      <c r="Q18" s="307">
         <f>IF(Q19="","",IF(Q19="☂","☂",IF(Q19&gt;S19,"○",IF(Q19=S19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R18" s="300" t="n"/>
-      <c r="S18" s="301" t="n"/>
-      <c r="T18" s="306">
+      <c r="R18" s="303" t="n"/>
+      <c r="S18" s="304" t="n"/>
+      <c r="T18" s="307">
         <f>IF(T19="","",IF(T19="☂","☂",IF(T19&gt;V19,"○",IF(T19=V19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U18" s="300" t="n"/>
-      <c r="V18" s="301" t="n"/>
-      <c r="W18" s="307" t="n"/>
-      <c r="X18" s="292" t="n"/>
-      <c r="Y18" s="269" t="n"/>
-      <c r="Z18" s="308">
+      <c r="U18" s="303" t="n"/>
+      <c r="V18" s="304" t="n"/>
+      <c r="W18" s="306" t="n"/>
+      <c r="X18" s="295" t="n"/>
+      <c r="Y18" s="270" t="n"/>
+      <c r="Z18" s="307">
         <f>IF(Z19="","",IF(Z19="☂","☂",IF(Z19&gt;AB19,"○",IF(Z19=AB19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA18" s="294" t="n"/>
-      <c r="AB18" s="295" t="n"/>
-      <c r="AC18" s="308">
+      <c r="AA18" s="297" t="n"/>
+      <c r="AB18" s="298" t="n"/>
+      <c r="AC18" s="307">
         <f>IF(AC19="","",IF(AC19="☂","☂",IF(AC19&gt;AE19,"○",IF(AC19=AE19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD18" s="294" t="n"/>
-      <c r="AE18" s="295" t="n"/>
-      <c r="AF18" s="308">
+      <c r="AD18" s="297" t="n"/>
+      <c r="AE18" s="298" t="n"/>
+      <c r="AF18" s="307">
         <f>IF(AF19="","",IF(AF19="☂","☂",IF(AF19&gt;AH19,"○",IF(AF19=AH19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG18" s="294" t="n"/>
-      <c r="AH18" s="295" t="n"/>
-      <c r="AI18" s="308">
+      <c r="AG18" s="297" t="n"/>
+      <c r="AH18" s="298" t="n"/>
+      <c r="AI18" s="307">
         <f>IF(AI19="","",IF(AI19="☂","☂",IF(AI19&gt;AK19,"○",IF(AI19=AK19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ18" s="294" t="n"/>
-      <c r="AK18" s="295" t="n"/>
-      <c r="AL18" s="309">
+      <c r="AJ18" s="297" t="n"/>
+      <c r="AK18" s="298" t="n"/>
+      <c r="AL18" s="308">
         <f>COUNTIF(E18:AK18,"○")</f>
         <v/>
       </c>
-      <c r="AM18" s="310">
+      <c r="AM18" s="309">
         <f>COUNTIF(E18:AK18,"△")</f>
         <v/>
       </c>
-      <c r="AN18" s="310">
+      <c r="AN18" s="309">
         <f>COUNTIF(E18:AK18,"×")</f>
         <v/>
       </c>
-      <c r="AO18" s="310">
+      <c r="AO18" s="309">
         <f>AL18*3+AM18*1</f>
         <v/>
       </c>
-      <c r="AP18" s="310">
+      <c r="AP18" s="309">
         <f>SUM(G19,J19,M19,P19,S19,V19,Y19,AB19,AK19)</f>
         <v/>
       </c>
-      <c r="AQ18" s="310">
+      <c r="AQ18" s="309">
         <f>SUM(E19,H19,K19,N19,Q19,T19,W19,Z19,AI19)</f>
         <v/>
       </c>
-      <c r="AR18" s="310">
+      <c r="AR18" s="309">
         <f>$AY$21-AL18-AM18-AN18</f>
         <v/>
       </c>
-      <c r="AS18" s="311">
+      <c r="AS18" s="310">
         <f>IFERROR(_xlfn.RANK.EQ(AO18,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5042,225 +5052,225 @@
       <c r="BA18" s="6" t="n"/>
     </row>
     <row r="19" ht="46.9" customHeight="1" s="257">
-      <c r="A19" s="302" t="n"/>
-      <c r="B19" s="281" t="n"/>
-      <c r="C19" s="282" t="n"/>
-      <c r="D19" s="283" t="n"/>
-      <c r="E19" s="312" t="n"/>
-      <c r="F19" s="305" t="inlineStr">
+      <c r="A19" s="305" t="n"/>
+      <c r="B19" s="284" t="n"/>
+      <c r="C19" s="285" t="n"/>
+      <c r="D19" s="286" t="n"/>
+      <c r="E19" s="311" t="n"/>
+      <c r="F19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="312" t="n"/>
-      <c r="H19" s="312" t="n"/>
-      <c r="I19" s="305" t="inlineStr">
+      <c r="G19" s="311" t="n"/>
+      <c r="H19" s="311" t="n"/>
+      <c r="I19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J19" s="312" t="n"/>
-      <c r="K19" s="312" t="n"/>
-      <c r="L19" s="305" t="inlineStr">
+      <c r="J19" s="311" t="n"/>
+      <c r="K19" s="311" t="n"/>
+      <c r="L19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="312" t="n"/>
-      <c r="N19" s="312" t="n"/>
-      <c r="O19" s="305" t="inlineStr">
+      <c r="M19" s="311" t="n"/>
+      <c r="N19" s="311" t="n"/>
+      <c r="O19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="312" t="n"/>
-      <c r="Q19" s="312" t="n"/>
-      <c r="R19" s="305" t="inlineStr">
+      <c r="P19" s="311" t="n"/>
+      <c r="Q19" s="311" t="n"/>
+      <c r="R19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S19" s="312" t="n"/>
-      <c r="T19" s="312" t="n"/>
-      <c r="U19" s="305" t="inlineStr">
+      <c r="S19" s="311" t="n"/>
+      <c r="T19" s="311" t="n"/>
+      <c r="U19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V19" s="312" t="n"/>
-      <c r="W19" s="282" t="n"/>
-      <c r="X19" s="270" t="n"/>
-      <c r="Y19" s="283" t="n"/>
-      <c r="Z19" s="305">
+      <c r="V19" s="311" t="n"/>
+      <c r="W19" s="285" t="n"/>
+      <c r="X19" s="271" t="n"/>
+      <c r="Y19" s="286" t="n"/>
+      <c r="Z19" s="306">
         <f>IF(Y21="","",Y21)</f>
         <v/>
       </c>
-      <c r="AA19" s="305" t="inlineStr">
+      <c r="AA19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB19" s="305">
+      <c r="AB19" s="306">
         <f>IF(W21="","",W21)</f>
         <v/>
       </c>
-      <c r="AC19" s="305">
+      <c r="AC19" s="306">
         <f>IF(Y23="","",Y23)</f>
         <v/>
       </c>
-      <c r="AD19" s="305" t="inlineStr">
+      <c r="AD19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE19" s="305">
+      <c r="AE19" s="306">
         <f>IF(W23="","",W23)</f>
         <v/>
       </c>
-      <c r="AF19" s="305">
+      <c r="AF19" s="306">
         <f>IF(Y25="","",Y25)</f>
         <v/>
       </c>
-      <c r="AG19" s="305" t="inlineStr">
+      <c r="AG19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH19" s="305">
+      <c r="AH19" s="306">
         <f>IF(W25="","",W25)</f>
         <v/>
       </c>
-      <c r="AI19" s="305">
+      <c r="AI19" s="306">
         <f>IF(Y27="","",Y27)</f>
         <v/>
       </c>
-      <c r="AJ19" s="305" t="inlineStr">
+      <c r="AJ19" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK19" s="305">
+      <c r="AK19" s="306">
         <f>IF(W27="","",W27)</f>
         <v/>
       </c>
-      <c r="AL19" s="281" t="n"/>
-      <c r="AM19" s="286" t="n"/>
-      <c r="AN19" s="286" t="n"/>
-      <c r="AO19" s="286" t="n"/>
-      <c r="AP19" s="286" t="n"/>
-      <c r="AQ19" s="286" t="n"/>
-      <c r="AR19" s="286" t="n"/>
-      <c r="AS19" s="298" t="n"/>
-      <c r="AV19" s="286" t="n"/>
-      <c r="AW19" s="288" t="n"/>
-      <c r="AX19" s="286" t="n"/>
+      <c r="AL19" s="284" t="n"/>
+      <c r="AM19" s="289" t="n"/>
+      <c r="AN19" s="289" t="n"/>
+      <c r="AO19" s="289" t="n"/>
+      <c r="AP19" s="289" t="n"/>
+      <c r="AQ19" s="289" t="n"/>
+      <c r="AR19" s="289" t="n"/>
+      <c r="AS19" s="301" t="n"/>
+      <c r="AV19" s="289" t="n"/>
+      <c r="AW19" s="291" t="n"/>
+      <c r="AX19" s="289" t="n"/>
       <c r="AZ19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="BA19" s="6" t="n"/>
     </row>
     <row r="20" ht="46.9" customHeight="1" s="257">
-      <c r="A20" s="302" t="n"/>
-      <c r="B20" s="313" t="n">
+      <c r="A20" s="305" t="n"/>
+      <c r="B20" s="306" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="304">
+      <c r="C20" s="306">
         <f>AX20</f>
         <v/>
       </c>
-      <c r="D20" s="272" t="n"/>
-      <c r="E20" s="314">
+      <c r="D20" s="274" t="n"/>
+      <c r="E20" s="306">
         <f>IF(E21="","",IF(E21="☂","☂",IF(E21&gt;G21,"○",IF(E21=G21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F20" s="290" t="n"/>
-      <c r="G20" s="291" t="n"/>
-      <c r="H20" s="305">
+      <c r="F20" s="293" t="n"/>
+      <c r="G20" s="294" t="n"/>
+      <c r="H20" s="306">
         <f>IF(H21="","",IF(H21="☂","☂",IF(H21&gt;J21,"○",IF(H21=J21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I20" s="290" t="n"/>
-      <c r="J20" s="291" t="n"/>
-      <c r="K20" s="305">
+      <c r="I20" s="293" t="n"/>
+      <c r="J20" s="294" t="n"/>
+      <c r="K20" s="306">
         <f>IF(K21="","",IF(K21="☂","☂",IF(K21&gt;M21,"○",IF(K21=M21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L20" s="290" t="n"/>
-      <c r="M20" s="291" t="n"/>
-      <c r="N20" s="306">
+      <c r="L20" s="293" t="n"/>
+      <c r="M20" s="294" t="n"/>
+      <c r="N20" s="307">
         <f>IF(N21="","",IF(N21="☂","☂",IF(N21&gt;P21,"○",IF(N21=P21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O20" s="300" t="n"/>
-      <c r="P20" s="301" t="n"/>
-      <c r="Q20" s="306">
+      <c r="O20" s="303" t="n"/>
+      <c r="P20" s="304" t="n"/>
+      <c r="Q20" s="307">
         <f>IF(Q21="","",IF(Q21="☂","☂",IF(Q21&gt;S21,"○",IF(Q21=S21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R20" s="300" t="n"/>
-      <c r="S20" s="301" t="n"/>
-      <c r="T20" s="306">
+      <c r="R20" s="303" t="n"/>
+      <c r="S20" s="304" t="n"/>
+      <c r="T20" s="307">
         <f>IF(T21="","",IF(T21="☂","☂",IF(T21&gt;V21,"○",IF(T21=V21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U20" s="300" t="n"/>
-      <c r="V20" s="301" t="n"/>
-      <c r="W20" s="306">
+      <c r="U20" s="303" t="n"/>
+      <c r="V20" s="304" t="n"/>
+      <c r="W20" s="307">
         <f>IF(W21="","",IF(W21="☂","☂",IF(W21&gt;Y21,"○",IF(W21=Y21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X20" s="300" t="n"/>
-      <c r="Y20" s="301" t="n"/>
-      <c r="Z20" s="307" t="n"/>
-      <c r="AA20" s="292" t="n"/>
-      <c r="AB20" s="269" t="n"/>
-      <c r="AC20" s="308">
+      <c r="X20" s="303" t="n"/>
+      <c r="Y20" s="304" t="n"/>
+      <c r="Z20" s="306" t="n"/>
+      <c r="AA20" s="295" t="n"/>
+      <c r="AB20" s="270" t="n"/>
+      <c r="AC20" s="307">
         <f>IF(AC21="","",IF(AC21="☂","☂",IF(AC21&gt;AE21,"○",IF(AC21=AE21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD20" s="294" t="n"/>
-      <c r="AE20" s="295" t="n"/>
-      <c r="AF20" s="308">
+      <c r="AD20" s="297" t="n"/>
+      <c r="AE20" s="298" t="n"/>
+      <c r="AF20" s="307">
         <f>IF(AF21="","",IF(AF21="☂","☂",IF(AF21&gt;AH21,"○",IF(AF21=AH21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG20" s="294" t="n"/>
-      <c r="AH20" s="295" t="n"/>
-      <c r="AI20" s="308">
+      <c r="AG20" s="297" t="n"/>
+      <c r="AH20" s="298" t="n"/>
+      <c r="AI20" s="307">
         <f>IF(AI21="","",IF(AI21="☂","☂",IF(AI21&gt;AK21,"○",IF(AI21=AK21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ20" s="294" t="n"/>
-      <c r="AK20" s="295" t="n"/>
-      <c r="AL20" s="309">
+      <c r="AJ20" s="297" t="n"/>
+      <c r="AK20" s="298" t="n"/>
+      <c r="AL20" s="308">
         <f>COUNTIF(E20:AK20,"○")</f>
         <v/>
       </c>
-      <c r="AM20" s="310">
+      <c r="AM20" s="309">
         <f>COUNTIF(E20:AK20,"△")</f>
         <v/>
       </c>
-      <c r="AN20" s="310">
+      <c r="AN20" s="309">
         <f>COUNTIF(E20:AK20,"×")</f>
         <v/>
       </c>
-      <c r="AO20" s="310">
+      <c r="AO20" s="309">
         <f>AL20*3+AM20*1</f>
         <v/>
       </c>
-      <c r="AP20" s="310">
+      <c r="AP20" s="309">
         <f>SUM(G21,J21,M21,P21,S21,V21,Y21,AB21,AK21)</f>
         <v/>
       </c>
-      <c r="AQ20" s="310">
+      <c r="AQ20" s="309">
         <f>SUM(E21,H21,K21,N21,Q21,T21,W21,Z21,AI21)</f>
         <v/>
       </c>
-      <c r="AR20" s="310">
+      <c r="AR20" s="309">
         <f>$AY$21-AL20-AM20-AN20</f>
         <v/>
       </c>
-      <c r="AS20" s="311">
+      <c r="AS20" s="310">
         <f>IFERROR(_xlfn.RANK.EQ(AO20,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5278,219 +5288,219 @@
       <c r="BA20" s="6" t="n"/>
     </row>
     <row r="21" ht="46.9" customHeight="1" s="257">
-      <c r="A21" s="302" t="n"/>
-      <c r="B21" s="315" t="n"/>
-      <c r="C21" s="282" t="n"/>
-      <c r="D21" s="283" t="n"/>
-      <c r="E21" s="316" t="n"/>
-      <c r="F21" s="305" t="inlineStr">
+      <c r="A21" s="305" t="n"/>
+      <c r="B21" s="312" t="n"/>
+      <c r="C21" s="285" t="n"/>
+      <c r="D21" s="286" t="n"/>
+      <c r="E21" s="311" t="n"/>
+      <c r="F21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="312" t="n"/>
-      <c r="H21" s="312" t="n"/>
-      <c r="I21" s="305" t="inlineStr">
+      <c r="G21" s="311" t="n"/>
+      <c r="H21" s="311" t="n"/>
+      <c r="I21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J21" s="312" t="n"/>
-      <c r="K21" s="312" t="n"/>
-      <c r="L21" s="305" t="inlineStr">
+      <c r="J21" s="311" t="n"/>
+      <c r="K21" s="311" t="n"/>
+      <c r="L21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="312" t="n"/>
-      <c r="N21" s="312" t="n"/>
-      <c r="O21" s="305" t="inlineStr">
+      <c r="M21" s="311" t="n"/>
+      <c r="N21" s="311" t="n"/>
+      <c r="O21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="312" t="n"/>
-      <c r="Q21" s="312" t="n"/>
-      <c r="R21" s="305" t="inlineStr">
+      <c r="P21" s="311" t="n"/>
+      <c r="Q21" s="311" t="n"/>
+      <c r="R21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S21" s="312" t="n"/>
-      <c r="T21" s="312" t="n"/>
-      <c r="U21" s="305" t="inlineStr">
+      <c r="S21" s="311" t="n"/>
+      <c r="T21" s="311" t="n"/>
+      <c r="U21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V21" s="312" t="n"/>
-      <c r="W21" s="312" t="n"/>
-      <c r="X21" s="305" t="inlineStr">
+      <c r="V21" s="311" t="n"/>
+      <c r="W21" s="311" t="n"/>
+      <c r="X21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y21" s="312" t="n"/>
-      <c r="Z21" s="282" t="n"/>
-      <c r="AA21" s="270" t="n"/>
-      <c r="AB21" s="283" t="n"/>
-      <c r="AC21" s="305">
+      <c r="Y21" s="311" t="n"/>
+      <c r="Z21" s="285" t="n"/>
+      <c r="AA21" s="271" t="n"/>
+      <c r="AB21" s="286" t="n"/>
+      <c r="AC21" s="306">
         <f>IF(AB23="","",AB23)</f>
         <v/>
       </c>
-      <c r="AD21" s="305" t="inlineStr">
+      <c r="AD21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE21" s="305">
+      <c r="AE21" s="306">
         <f>IF(Z23="","",Z23)</f>
         <v/>
       </c>
-      <c r="AF21" s="305">
+      <c r="AF21" s="306">
         <f>IF(AB25="","",AB25)</f>
         <v/>
       </c>
-      <c r="AG21" s="305" t="inlineStr">
+      <c r="AG21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH21" s="305">
+      <c r="AH21" s="306">
         <f>IF(Z25="","",Z25)</f>
         <v/>
       </c>
-      <c r="AI21" s="305">
+      <c r="AI21" s="306">
         <f>IF(AB27="","",AB27)</f>
         <v/>
       </c>
-      <c r="AJ21" s="305" t="inlineStr">
+      <c r="AJ21" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK21" s="305">
+      <c r="AK21" s="306">
         <f>IF(Z27="","",Z27)</f>
         <v/>
       </c>
-      <c r="AL21" s="281" t="n"/>
-      <c r="AM21" s="286" t="n"/>
-      <c r="AN21" s="286" t="n"/>
-      <c r="AO21" s="286" t="n"/>
-      <c r="AP21" s="286" t="n"/>
-      <c r="AQ21" s="286" t="n"/>
-      <c r="AR21" s="286" t="n"/>
-      <c r="AS21" s="298" t="n"/>
-      <c r="AV21" s="286" t="n"/>
-      <c r="AW21" s="288" t="n"/>
-      <c r="AX21" s="286" t="n"/>
+      <c r="AL21" s="284" t="n"/>
+      <c r="AM21" s="289" t="n"/>
+      <c r="AN21" s="289" t="n"/>
+      <c r="AO21" s="289" t="n"/>
+      <c r="AP21" s="289" t="n"/>
+      <c r="AQ21" s="289" t="n"/>
+      <c r="AR21" s="289" t="n"/>
+      <c r="AS21" s="301" t="n"/>
+      <c r="AV21" s="289" t="n"/>
+      <c r="AW21" s="291" t="n"/>
+      <c r="AX21" s="289" t="n"/>
       <c r="AY21" s="1">
         <f>COUNTA(AW6:AW21)</f>
         <v/>
       </c>
     </row>
     <row r="22" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A22" s="302" t="n"/>
-      <c r="B22" s="303" t="n">
+      <c r="A22" s="305" t="n"/>
+      <c r="B22" s="306" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="304">
+      <c r="C22" s="306">
         <f>AX22</f>
         <v/>
       </c>
-      <c r="D22" s="272" t="n"/>
-      <c r="E22" s="303">
+      <c r="D22" s="274" t="n"/>
+      <c r="E22" s="306">
         <f>IF(E23="","",IF(E23="☂","☂",IF(E23&gt;G23,"○",IF(E23=G23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F22" s="290" t="n"/>
-      <c r="G22" s="291" t="n"/>
-      <c r="H22" s="305">
+      <c r="F22" s="293" t="n"/>
+      <c r="G22" s="294" t="n"/>
+      <c r="H22" s="306">
         <f>IF(H23="","",IF(H23="☂","☂",IF(H23&gt;J23,"○",IF(H23=J23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I22" s="290" t="n"/>
-      <c r="J22" s="291" t="n"/>
-      <c r="K22" s="305">
+      <c r="I22" s="293" t="n"/>
+      <c r="J22" s="294" t="n"/>
+      <c r="K22" s="306">
         <f>IF(K23="","",IF(K23="☂","☂",IF(K23&gt;M23,"○",IF(K23=M23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L22" s="290" t="n"/>
-      <c r="M22" s="291" t="n"/>
-      <c r="N22" s="306">
+      <c r="L22" s="293" t="n"/>
+      <c r="M22" s="294" t="n"/>
+      <c r="N22" s="307">
         <f>IF(N23="","",IF(N23="☂","☂",IF(N23&gt;P23,"○",IF(N23=P23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O22" s="300" t="n"/>
-      <c r="P22" s="301" t="n"/>
-      <c r="Q22" s="306">
+      <c r="O22" s="303" t="n"/>
+      <c r="P22" s="304" t="n"/>
+      <c r="Q22" s="307">
         <f>IF(Q23="","",IF(Q23="☂","☂",IF(Q23&gt;S23,"○",IF(Q23=S23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R22" s="300" t="n"/>
-      <c r="S22" s="301" t="n"/>
-      <c r="T22" s="306">
+      <c r="R22" s="303" t="n"/>
+      <c r="S22" s="304" t="n"/>
+      <c r="T22" s="307">
         <f>IF(T23="","",IF(T23="☂","☂",IF(T23&gt;V23,"○",IF(T23=V23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U22" s="300" t="n"/>
-      <c r="V22" s="301" t="n"/>
-      <c r="W22" s="306">
+      <c r="U22" s="303" t="n"/>
+      <c r="V22" s="304" t="n"/>
+      <c r="W22" s="307">
         <f>IF(W23="","",IF(W23="☂","☂",IF(W23&gt;Y23,"○",IF(W23=Y23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X22" s="300" t="n"/>
-      <c r="Y22" s="301" t="n"/>
-      <c r="Z22" s="306">
+      <c r="X22" s="303" t="n"/>
+      <c r="Y22" s="304" t="n"/>
+      <c r="Z22" s="307">
         <f>IF(Z23="","",IF(Z23="☂","☂",IF(Z23&gt;AB23,"○",IF(Z23=AB23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA22" s="300" t="n"/>
-      <c r="AB22" s="301" t="n"/>
-      <c r="AC22" s="317" t="n"/>
-      <c r="AD22" s="318" t="n"/>
-      <c r="AE22" s="319" t="n"/>
-      <c r="AF22" s="306">
+      <c r="AA22" s="303" t="n"/>
+      <c r="AB22" s="304" t="n"/>
+      <c r="AC22" s="307" t="n"/>
+      <c r="AD22" s="313" t="n"/>
+      <c r="AE22" s="314" t="n"/>
+      <c r="AF22" s="307">
         <f>IF(AF23="","",IF(AF23="☂","☂",IF(AF23&gt;AH23,"○",IF(AF23=AH23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG22" s="300" t="n"/>
-      <c r="AH22" s="301" t="n"/>
-      <c r="AI22" s="308">
+      <c r="AG22" s="303" t="n"/>
+      <c r="AH22" s="304" t="n"/>
+      <c r="AI22" s="307">
         <f>IF(AI23="","",IF(AI23="☂","☂",IF(AI23&gt;AK23,"○",IF(AI23=AK23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ22" s="294" t="n"/>
-      <c r="AK22" s="295" t="n"/>
-      <c r="AL22" s="309">
+      <c r="AJ22" s="297" t="n"/>
+      <c r="AK22" s="298" t="n"/>
+      <c r="AL22" s="308">
         <f>COUNTIF(E22:AK22,"○")</f>
         <v/>
       </c>
-      <c r="AM22" s="310">
+      <c r="AM22" s="309">
         <f>COUNTIF(E22:AK22,"△")</f>
         <v/>
       </c>
-      <c r="AN22" s="310">
+      <c r="AN22" s="309">
         <f>COUNTIF(E22:AK22,"×")</f>
         <v/>
       </c>
-      <c r="AO22" s="310">
+      <c r="AO22" s="309">
         <f>AL22*3+AM22*1</f>
         <v/>
       </c>
-      <c r="AP22" s="310">
+      <c r="AP22" s="309">
         <f>SUM(G23,M23,P23,S23,V23,Y23,AB23,AK23)</f>
         <v/>
       </c>
-      <c r="AQ22" s="310">
+      <c r="AQ22" s="309">
         <f>SUM(E23,K23,N23,Q23,T23,W23,Z23,AI23)</f>
         <v/>
       </c>
-      <c r="AR22" s="310">
+      <c r="AR22" s="309">
         <f>10-AL22-AM22-AN22</f>
         <v/>
       </c>
-      <c r="AS22" s="311">
+      <c r="AS22" s="310">
         <f>IFERROR(_xlfn.RANK.EQ(AO22,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5504,209 +5514,209 @@
       </c>
     </row>
     <row r="23" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A23" s="302" t="n"/>
-      <c r="B23" s="281" t="n"/>
-      <c r="C23" s="282" t="n"/>
-      <c r="D23" s="283" t="n"/>
-      <c r="E23" s="316" t="n"/>
-      <c r="F23" s="305" t="inlineStr">
+      <c r="A23" s="305" t="n"/>
+      <c r="B23" s="284" t="n"/>
+      <c r="C23" s="285" t="n"/>
+      <c r="D23" s="286" t="n"/>
+      <c r="E23" s="311" t="n"/>
+      <c r="F23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="312" t="n"/>
-      <c r="H23" s="312" t="n"/>
-      <c r="I23" s="305" t="inlineStr">
+      <c r="G23" s="311" t="n"/>
+      <c r="H23" s="311" t="n"/>
+      <c r="I23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J23" s="312" t="n"/>
-      <c r="K23" s="312" t="n"/>
-      <c r="L23" s="305" t="inlineStr">
+      <c r="J23" s="311" t="n"/>
+      <c r="K23" s="311" t="n"/>
+      <c r="L23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="312" t="n"/>
-      <c r="N23" s="312" t="n"/>
-      <c r="O23" s="305" t="inlineStr">
+      <c r="M23" s="311" t="n"/>
+      <c r="N23" s="311" t="n"/>
+      <c r="O23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P23" s="312" t="n"/>
-      <c r="Q23" s="312" t="n"/>
-      <c r="R23" s="305" t="inlineStr">
+      <c r="P23" s="311" t="n"/>
+      <c r="Q23" s="311" t="n"/>
+      <c r="R23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S23" s="312" t="n"/>
-      <c r="T23" s="312" t="n"/>
-      <c r="U23" s="305" t="inlineStr">
+      <c r="S23" s="311" t="n"/>
+      <c r="T23" s="311" t="n"/>
+      <c r="U23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V23" s="312" t="n"/>
-      <c r="W23" s="312" t="n"/>
-      <c r="X23" s="305" t="inlineStr">
+      <c r="V23" s="311" t="n"/>
+      <c r="W23" s="311" t="n"/>
+      <c r="X23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y23" s="312" t="n"/>
-      <c r="Z23" s="312" t="n"/>
-      <c r="AA23" s="305" t="inlineStr">
+      <c r="Y23" s="311" t="n"/>
+      <c r="Z23" s="311" t="n"/>
+      <c r="AA23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB23" s="312" t="n"/>
-      <c r="AC23" s="320" t="n"/>
-      <c r="AD23" s="294" t="n"/>
-      <c r="AE23" s="295" t="n"/>
-      <c r="AF23" s="321">
+      <c r="AB23" s="311" t="n"/>
+      <c r="AC23" s="315" t="n"/>
+      <c r="AD23" s="297" t="n"/>
+      <c r="AE23" s="298" t="n"/>
+      <c r="AF23" s="316">
         <f>IF(AE25="","",AE25)</f>
         <v/>
       </c>
-      <c r="AG23" s="305" t="inlineStr">
+      <c r="AG23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH23" s="321">
+      <c r="AH23" s="316">
         <f>IF(AC25="","",AC25)</f>
         <v/>
       </c>
-      <c r="AI23" s="305">
+      <c r="AI23" s="306">
         <f>IF(AE27="","",AE27)</f>
         <v/>
       </c>
-      <c r="AJ23" s="305" t="inlineStr">
+      <c r="AJ23" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK23" s="305">
+      <c r="AK23" s="306">
         <f>IF(AC27="","",AC27)</f>
         <v/>
       </c>
-      <c r="AL23" s="281" t="n"/>
-      <c r="AM23" s="286" t="n"/>
-      <c r="AN23" s="286" t="n"/>
-      <c r="AO23" s="286" t="n"/>
-      <c r="AP23" s="286" t="n"/>
-      <c r="AQ23" s="286" t="n"/>
-      <c r="AR23" s="286" t="n"/>
-      <c r="AS23" s="298" t="n"/>
-      <c r="AV23" s="286" t="n"/>
-      <c r="AW23" s="288" t="n"/>
-      <c r="AX23" s="286" t="n"/>
+      <c r="AL23" s="284" t="n"/>
+      <c r="AM23" s="289" t="n"/>
+      <c r="AN23" s="289" t="n"/>
+      <c r="AO23" s="289" t="n"/>
+      <c r="AP23" s="289" t="n"/>
+      <c r="AQ23" s="289" t="n"/>
+      <c r="AR23" s="289" t="n"/>
+      <c r="AS23" s="301" t="n"/>
+      <c r="AV23" s="289" t="n"/>
+      <c r="AW23" s="291" t="n"/>
+      <c r="AX23" s="289" t="n"/>
     </row>
     <row r="24" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A24" s="302" t="n"/>
-      <c r="B24" s="303" t="n">
+      <c r="A24" s="305" t="n"/>
+      <c r="B24" s="306" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="304">
+      <c r="C24" s="306">
         <f>AX24</f>
         <v/>
       </c>
-      <c r="D24" s="272" t="n"/>
-      <c r="E24" s="303">
+      <c r="D24" s="274" t="n"/>
+      <c r="E24" s="306">
         <f>IF(E25="","",IF(E25="☂","☂",IF(E25&gt;G25,"○",IF(E25=G25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F24" s="290" t="n"/>
-      <c r="G24" s="291" t="n"/>
-      <c r="H24" s="305">
+      <c r="F24" s="293" t="n"/>
+      <c r="G24" s="294" t="n"/>
+      <c r="H24" s="306">
         <f>IF(H25="","",IF(H25="☂","☂",IF(H25&gt;J25,"○",IF(H25=J25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I24" s="290" t="n"/>
-      <c r="J24" s="291" t="n"/>
-      <c r="K24" s="305">
+      <c r="I24" s="293" t="n"/>
+      <c r="J24" s="294" t="n"/>
+      <c r="K24" s="306">
         <f>IF(K25="","",IF(K25="☂","☂",IF(K25&gt;M25,"○",IF(K25=M25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L24" s="290" t="n"/>
-      <c r="M24" s="291" t="n"/>
-      <c r="N24" s="306">
+      <c r="L24" s="293" t="n"/>
+      <c r="M24" s="294" t="n"/>
+      <c r="N24" s="307">
         <f>IF(N25="","",IF(N25="☂","☂",IF(N25&gt;P25,"○",IF(N25=P25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O24" s="300" t="n"/>
-      <c r="P24" s="301" t="n"/>
-      <c r="Q24" s="306">
+      <c r="O24" s="303" t="n"/>
+      <c r="P24" s="304" t="n"/>
+      <c r="Q24" s="307">
         <f>IF(Q25="","",IF(Q25="☂","☂",IF(Q25&gt;S25,"○",IF(Q25=S25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R24" s="300" t="n"/>
-      <c r="S24" s="301" t="n"/>
-      <c r="T24" s="306">
+      <c r="R24" s="303" t="n"/>
+      <c r="S24" s="304" t="n"/>
+      <c r="T24" s="307">
         <f>IF(T25="","",IF(T25="☂","☂",IF(T25&gt;V25,"○",IF(T25=V25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U24" s="300" t="n"/>
-      <c r="V24" s="301" t="n"/>
-      <c r="W24" s="306">
+      <c r="U24" s="303" t="n"/>
+      <c r="V24" s="304" t="n"/>
+      <c r="W24" s="307">
         <f>IF(W25="","",IF(W25="☂","☂",IF(W25&gt;Y25,"○",IF(W25=Y25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X24" s="300" t="n"/>
-      <c r="Y24" s="301" t="n"/>
-      <c r="Z24" s="306">
+      <c r="X24" s="303" t="n"/>
+      <c r="Y24" s="304" t="n"/>
+      <c r="Z24" s="307">
         <f>IF(Z25="","",IF(Z25="☂","☂",IF(Z25&gt;AB25,"○",IF(Z25=AB25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA24" s="300" t="n"/>
-      <c r="AB24" s="301" t="n"/>
-      <c r="AC24" s="306">
+      <c r="AA24" s="303" t="n"/>
+      <c r="AB24" s="304" t="n"/>
+      <c r="AC24" s="307">
         <f>IF(AC25="","",IF(AC25="☂","☂",IF(AC25&gt;AE25,"○",IF(AC25=AE25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD24" s="300" t="n"/>
-      <c r="AE24" s="301" t="n"/>
-      <c r="AF24" s="322" t="n"/>
-      <c r="AG24" s="318" t="n"/>
-      <c r="AH24" s="319" t="n"/>
-      <c r="AI24" s="306">
+      <c r="AD24" s="303" t="n"/>
+      <c r="AE24" s="304" t="n"/>
+      <c r="AF24" s="307" t="n"/>
+      <c r="AG24" s="313" t="n"/>
+      <c r="AH24" s="314" t="n"/>
+      <c r="AI24" s="307">
         <f>IF(AI25="","",IF(AI25="☂","☂",IF(AI25&gt;AK25,"○",IF(AI25=AK25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ24" s="300" t="n"/>
-      <c r="AK24" s="301" t="n"/>
-      <c r="AL24" s="309">
+      <c r="AJ24" s="303" t="n"/>
+      <c r="AK24" s="304" t="n"/>
+      <c r="AL24" s="308">
         <f>COUNTIF(E24:AK24,"○")</f>
         <v/>
       </c>
-      <c r="AM24" s="310">
+      <c r="AM24" s="309">
         <f>COUNTIF(E24:AK24,"△")</f>
         <v/>
       </c>
-      <c r="AN24" s="310">
+      <c r="AN24" s="309">
         <f>COUNTIF(E24:AK24,"×")</f>
         <v/>
       </c>
-      <c r="AO24" s="310">
+      <c r="AO24" s="309">
         <f>AL24*3+AM24*1</f>
         <v/>
       </c>
-      <c r="AP24" s="310">
+      <c r="AP24" s="309">
         <f>SUM(G25,M25,P25,S25,V25,Y25,AB25,AK25)</f>
         <v/>
       </c>
-      <c r="AQ24" s="310">
+      <c r="AQ24" s="309">
         <f>SUM(E25,K25,N25,Q25,T25,W25,Z25,AI25)</f>
         <v/>
       </c>
-      <c r="AR24" s="310">
+      <c r="AR24" s="309">
         <f>10-AL24-AM24-AN24</f>
         <v/>
       </c>
-      <c r="AS24" s="311">
+      <c r="AS24" s="310">
         <f>IFERROR(_xlfn.RANK.EQ(AO24,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5720,203 +5730,203 @@
       </c>
     </row>
     <row r="25" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A25" s="302" t="n"/>
-      <c r="B25" s="281" t="n"/>
-      <c r="C25" s="282" t="n"/>
-      <c r="D25" s="283" t="n"/>
-      <c r="E25" s="323" t="n"/>
-      <c r="F25" s="305" t="inlineStr">
+      <c r="A25" s="305" t="n"/>
+      <c r="B25" s="284" t="n"/>
+      <c r="C25" s="285" t="n"/>
+      <c r="D25" s="286" t="n"/>
+      <c r="E25" s="311" t="n"/>
+      <c r="F25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="312" t="n"/>
-      <c r="H25" s="312" t="n"/>
-      <c r="I25" s="305" t="inlineStr">
+      <c r="G25" s="311" t="n"/>
+      <c r="H25" s="311" t="n"/>
+      <c r="I25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="312" t="n"/>
-      <c r="K25" s="312" t="n"/>
-      <c r="L25" s="305" t="inlineStr">
+      <c r="J25" s="311" t="n"/>
+      <c r="K25" s="311" t="n"/>
+      <c r="L25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="312" t="n"/>
-      <c r="N25" s="312" t="n"/>
-      <c r="O25" s="305" t="inlineStr">
+      <c r="M25" s="311" t="n"/>
+      <c r="N25" s="311" t="n"/>
+      <c r="O25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P25" s="312" t="n"/>
-      <c r="Q25" s="312" t="n"/>
-      <c r="R25" s="305" t="inlineStr">
+      <c r="P25" s="311" t="n"/>
+      <c r="Q25" s="311" t="n"/>
+      <c r="R25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S25" s="312" t="n"/>
-      <c r="T25" s="312" t="n"/>
-      <c r="U25" s="305" t="inlineStr">
+      <c r="S25" s="311" t="n"/>
+      <c r="T25" s="311" t="n"/>
+      <c r="U25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V25" s="312" t="n"/>
-      <c r="W25" s="312" t="n"/>
-      <c r="X25" s="305" t="inlineStr">
+      <c r="V25" s="311" t="n"/>
+      <c r="W25" s="311" t="n"/>
+      <c r="X25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y25" s="312" t="n"/>
-      <c r="Z25" s="312" t="n"/>
-      <c r="AA25" s="305" t="inlineStr">
+      <c r="Y25" s="311" t="n"/>
+      <c r="Z25" s="311" t="n"/>
+      <c r="AA25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB25" s="312" t="n"/>
-      <c r="AC25" s="312" t="n"/>
-      <c r="AD25" s="305" t="inlineStr">
+      <c r="AB25" s="311" t="n"/>
+      <c r="AC25" s="311" t="n"/>
+      <c r="AD25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE25" s="312" t="n"/>
-      <c r="AF25" s="324" t="n"/>
-      <c r="AG25" s="325" t="n"/>
-      <c r="AH25" s="326" t="n"/>
-      <c r="AI25" s="312">
+      <c r="AE25" s="311" t="n"/>
+      <c r="AF25" s="317" t="n"/>
+      <c r="AG25" s="318" t="n"/>
+      <c r="AH25" s="319" t="n"/>
+      <c r="AI25" s="311">
         <f>IF(AH27="","",AH27)</f>
         <v/>
       </c>
-      <c r="AJ25" s="305" t="inlineStr">
+      <c r="AJ25" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK25" s="327">
+      <c r="AK25" s="311">
         <f>IF(AF27="","",AF27)</f>
         <v/>
       </c>
-      <c r="AL25" s="281" t="n"/>
-      <c r="AM25" s="286" t="n"/>
-      <c r="AN25" s="286" t="n"/>
-      <c r="AO25" s="286" t="n"/>
-      <c r="AP25" s="286" t="n"/>
-      <c r="AQ25" s="286" t="n"/>
-      <c r="AR25" s="286" t="n"/>
-      <c r="AS25" s="298" t="n"/>
-      <c r="AV25" s="286" t="n"/>
-      <c r="AW25" s="288" t="n"/>
-      <c r="AX25" s="286" t="n"/>
+      <c r="AL25" s="284" t="n"/>
+      <c r="AM25" s="289" t="n"/>
+      <c r="AN25" s="289" t="n"/>
+      <c r="AO25" s="289" t="n"/>
+      <c r="AP25" s="289" t="n"/>
+      <c r="AQ25" s="289" t="n"/>
+      <c r="AR25" s="289" t="n"/>
+      <c r="AS25" s="301" t="n"/>
+      <c r="AV25" s="289" t="n"/>
+      <c r="AW25" s="291" t="n"/>
+      <c r="AX25" s="289" t="n"/>
     </row>
     <row r="26" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A26" s="302" t="n"/>
-      <c r="B26" s="303" t="n">
+      <c r="A26" s="305" t="n"/>
+      <c r="B26" s="306" t="n">
         <v>11</v>
       </c>
-      <c r="C26" s="304">
+      <c r="C26" s="306">
         <f>AX26</f>
         <v/>
       </c>
-      <c r="D26" s="272" t="n"/>
-      <c r="E26" s="303">
+      <c r="D26" s="274" t="n"/>
+      <c r="E26" s="306">
         <f>IF(E27="","",IF(E27="☂","☂",IF(E27&gt;G27,"○",IF(E27=G27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F26" s="290" t="n"/>
-      <c r="G26" s="291" t="n"/>
-      <c r="H26" s="305">
+      <c r="F26" s="293" t="n"/>
+      <c r="G26" s="294" t="n"/>
+      <c r="H26" s="306">
         <f>IF(H27="","",IF(H27="☂","☂",IF(H27&gt;J27,"○",IF(H27=J27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I26" s="290" t="n"/>
-      <c r="J26" s="291" t="n"/>
-      <c r="K26" s="305">
+      <c r="I26" s="293" t="n"/>
+      <c r="J26" s="294" t="n"/>
+      <c r="K26" s="306">
         <f>IF(K27="","",IF(K27="☂","☂",IF(K27&gt;M27,"○",IF(K27=M27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L26" s="290" t="n"/>
-      <c r="M26" s="291" t="n"/>
-      <c r="N26" s="306">
+      <c r="L26" s="293" t="n"/>
+      <c r="M26" s="294" t="n"/>
+      <c r="N26" s="307">
         <f>IF(N27="","",IF(N27="☂","☂",IF(N27&gt;P27,"○",IF(N27=P27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O26" s="300" t="n"/>
-      <c r="P26" s="301" t="n"/>
-      <c r="Q26" s="306">
+      <c r="O26" s="303" t="n"/>
+      <c r="P26" s="304" t="n"/>
+      <c r="Q26" s="307">
         <f>IF(Q27="","",IF(Q27="☂","☂",IF(Q27&gt;S27,"○",IF(Q27=S27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R26" s="300" t="n"/>
-      <c r="S26" s="301" t="n"/>
-      <c r="T26" s="306">
+      <c r="R26" s="303" t="n"/>
+      <c r="S26" s="304" t="n"/>
+      <c r="T26" s="307">
         <f>IF(T27="","",IF(T27="☂","☂",IF(T27&gt;V27,"○",IF(T27=V27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U26" s="300" t="n"/>
-      <c r="V26" s="301" t="n"/>
-      <c r="W26" s="306">
+      <c r="U26" s="303" t="n"/>
+      <c r="V26" s="304" t="n"/>
+      <c r="W26" s="307">
         <f>IF(W27="","",IF(W27="☂","☂",IF(W27&gt;Y27,"○",IF(W27=Y27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X26" s="300" t="n"/>
-      <c r="Y26" s="301" t="n"/>
-      <c r="Z26" s="306">
+      <c r="X26" s="303" t="n"/>
+      <c r="Y26" s="304" t="n"/>
+      <c r="Z26" s="307">
         <f>IF(Z27="","",IF(Z27="☂","☂",IF(Z27&gt;AB27,"○",IF(Z27=AB27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA26" s="300" t="n"/>
-      <c r="AB26" s="301" t="n"/>
-      <c r="AC26" s="306">
+      <c r="AA26" s="303" t="n"/>
+      <c r="AB26" s="304" t="n"/>
+      <c r="AC26" s="307">
         <f>IF(AC27="","",IF(AC27="☂","☂",IF(AC27&gt;AE27,"○",IF(AC27=AE27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD26" s="300" t="n"/>
-      <c r="AE26" s="301" t="n"/>
-      <c r="AF26" s="306">
+      <c r="AD26" s="303" t="n"/>
+      <c r="AE26" s="304" t="n"/>
+      <c r="AF26" s="307">
         <f>IF(AF27="","",IF(AF27="☂","☂",IF(AF27&gt;AH27,"○",IF(AF27=AH27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG26" s="300" t="n"/>
-      <c r="AH26" s="301" t="n"/>
-      <c r="AI26" s="328" t="n"/>
-      <c r="AJ26" s="325" t="n"/>
-      <c r="AK26" s="329" t="n"/>
-      <c r="AL26" s="309">
+      <c r="AG26" s="303" t="n"/>
+      <c r="AH26" s="304" t="n"/>
+      <c r="AI26" s="307" t="n"/>
+      <c r="AJ26" s="318" t="n"/>
+      <c r="AK26" s="320" t="n"/>
+      <c r="AL26" s="308">
         <f>COUNTIF(E26:AK26,"○")</f>
         <v/>
       </c>
-      <c r="AM26" s="310">
+      <c r="AM26" s="309">
         <f>COUNTIF(E26:AK26,"△")</f>
         <v/>
       </c>
-      <c r="AN26" s="310">
+      <c r="AN26" s="309">
         <f>COUNTIF(E26:AK26,"×")</f>
         <v/>
       </c>
-      <c r="AO26" s="310">
+      <c r="AO26" s="309">
         <f>AL26*3+AM26*1</f>
         <v/>
       </c>
-      <c r="AP26" s="310">
+      <c r="AP26" s="309">
         <f>SUM(G27,M27,P27,S27,V27,Y27,AB27,AK27)</f>
         <v/>
       </c>
-      <c r="AQ26" s="330">
+      <c r="AQ26" s="306">
         <f>SUM(H27,K27,N27,Q27,T27,W27,Z27,AI27,#REF!)</f>
         <v/>
       </c>
-      <c r="AR26" s="330">
+      <c r="AR26" s="306">
         <f>10-AL26-AM26-AN26</f>
         <v/>
       </c>
-      <c r="AS26" s="331">
+      <c r="AS26" s="310">
         <f>IFERROR(_xlfn.RANK.EQ(AO26,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5930,94 +5940,94 @@
       </c>
     </row>
     <row r="27" hidden="1" ht="33.6" customHeight="1" s="257" thickBot="1">
-      <c r="A27" s="302" t="n"/>
-      <c r="B27" s="281" t="n"/>
-      <c r="C27" s="282" t="n"/>
-      <c r="D27" s="283" t="n"/>
-      <c r="E27" s="332" t="n"/>
-      <c r="F27" s="330" t="inlineStr">
+      <c r="A27" s="321" t="n"/>
+      <c r="B27" s="284" t="n"/>
+      <c r="C27" s="285" t="n"/>
+      <c r="D27" s="286" t="n"/>
+      <c r="E27" s="322" t="n"/>
+      <c r="F27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="333" t="n"/>
-      <c r="H27" s="332" t="n"/>
-      <c r="I27" s="330" t="inlineStr">
+      <c r="G27" s="322" t="n"/>
+      <c r="H27" s="322" t="n"/>
+      <c r="I27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="332" t="n"/>
-      <c r="K27" s="332" t="n"/>
-      <c r="L27" s="330" t="inlineStr">
+      <c r="J27" s="322" t="n"/>
+      <c r="K27" s="322" t="n"/>
+      <c r="L27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="332" t="n"/>
-      <c r="N27" s="332" t="n"/>
-      <c r="O27" s="330" t="inlineStr">
+      <c r="M27" s="322" t="n"/>
+      <c r="N27" s="322" t="n"/>
+      <c r="O27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P27" s="332" t="n"/>
-      <c r="Q27" s="332" t="n"/>
-      <c r="R27" s="330" t="inlineStr">
+      <c r="P27" s="322" t="n"/>
+      <c r="Q27" s="322" t="n"/>
+      <c r="R27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S27" s="332" t="n"/>
-      <c r="T27" s="332" t="n"/>
-      <c r="U27" s="330" t="inlineStr">
+      <c r="S27" s="322" t="n"/>
+      <c r="T27" s="322" t="n"/>
+      <c r="U27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V27" s="332" t="n"/>
-      <c r="W27" s="332" t="n"/>
-      <c r="X27" s="330" t="inlineStr">
+      <c r="V27" s="322" t="n"/>
+      <c r="W27" s="322" t="n"/>
+      <c r="X27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y27" s="332" t="n"/>
-      <c r="Z27" s="332" t="n"/>
-      <c r="AA27" s="330" t="inlineStr">
+      <c r="Y27" s="322" t="n"/>
+      <c r="Z27" s="322" t="n"/>
+      <c r="AA27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB27" s="332" t="n"/>
-      <c r="AC27" s="332" t="n"/>
-      <c r="AD27" s="330" t="inlineStr">
+      <c r="AB27" s="322" t="n"/>
+      <c r="AC27" s="322" t="n"/>
+      <c r="AD27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE27" s="332" t="n"/>
-      <c r="AF27" s="334" t="n"/>
-      <c r="AG27" s="330" t="inlineStr">
+      <c r="AE27" s="322" t="n"/>
+      <c r="AF27" s="324" t="n"/>
+      <c r="AG27" s="323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH27" s="334" t="n"/>
-      <c r="AI27" s="335" t="n"/>
-      <c r="AJ27" s="336" t="n"/>
-      <c r="AK27" s="337" t="n"/>
-      <c r="AL27" s="281" t="n"/>
-      <c r="AM27" s="286" t="n"/>
-      <c r="AN27" s="286" t="n"/>
-      <c r="AO27" s="286" t="n"/>
-      <c r="AP27" s="286" t="n"/>
-      <c r="AQ27" s="338" t="n"/>
-      <c r="AR27" s="338" t="n"/>
-      <c r="AS27" s="339" t="n"/>
-      <c r="AV27" s="286" t="n"/>
-      <c r="AW27" s="288" t="n"/>
-      <c r="AX27" s="286" t="n"/>
+      <c r="AH27" s="324" t="n"/>
+      <c r="AI27" s="325" t="n"/>
+      <c r="AJ27" s="326" t="n"/>
+      <c r="AK27" s="327" t="n"/>
+      <c r="AL27" s="284" t="n"/>
+      <c r="AM27" s="289" t="n"/>
+      <c r="AN27" s="289" t="n"/>
+      <c r="AO27" s="289" t="n"/>
+      <c r="AP27" s="289" t="n"/>
+      <c r="AQ27" s="328" t="n"/>
+      <c r="AR27" s="328" t="n"/>
+      <c r="AS27" s="329" t="n"/>
+      <c r="AV27" s="289" t="n"/>
+      <c r="AW27" s="291" t="n"/>
+      <c r="AX27" s="289" t="n"/>
     </row>
     <row r="28" ht="6.75" customHeight="1" s="257"/>
   </sheetData>
@@ -6365,8 +6375,8 @@
       <c r="T1" s="240" t="n">
         <v>2026</v>
       </c>
-      <c r="U1" s="340" t="n"/>
-      <c r="V1" s="340" t="n"/>
+      <c r="U1" s="330" t="n"/>
+      <c r="V1" s="330" t="n"/>
       <c r="W1" s="238" t="inlineStr">
         <is>
           <t>年</t>
@@ -6375,46 +6385,46 @@
       <c r="X1" s="238" t="n"/>
     </row>
     <row r="2" ht="16.15" customHeight="1" s="257">
-      <c r="A2" s="341" t="inlineStr">
+      <c r="A2" s="331" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="342" t="n"/>
-      <c r="C2" s="342" t="n"/>
-      <c r="D2" s="342" t="n"/>
-      <c r="E2" s="342" t="n"/>
-      <c r="F2" s="343" t="n"/>
-      <c r="G2" s="341" t="inlineStr">
+      <c r="B2" s="332" t="n"/>
+      <c r="C2" s="332" t="n"/>
+      <c r="D2" s="332" t="n"/>
+      <c r="E2" s="332" t="n"/>
+      <c r="F2" s="333" t="n"/>
+      <c r="G2" s="331" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="342" t="n"/>
-      <c r="I2" s="342" t="n"/>
-      <c r="J2" s="342" t="n"/>
-      <c r="K2" s="342" t="n"/>
-      <c r="L2" s="343" t="n"/>
-      <c r="M2" s="341" t="inlineStr">
+      <c r="H2" s="332" t="n"/>
+      <c r="I2" s="332" t="n"/>
+      <c r="J2" s="332" t="n"/>
+      <c r="K2" s="332" t="n"/>
+      <c r="L2" s="333" t="n"/>
+      <c r="M2" s="331" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="342" t="n"/>
-      <c r="O2" s="342" t="n"/>
-      <c r="P2" s="342" t="n"/>
-      <c r="Q2" s="342" t="n"/>
-      <c r="R2" s="343" t="n"/>
+      <c r="N2" s="332" t="n"/>
+      <c r="O2" s="332" t="n"/>
+      <c r="P2" s="332" t="n"/>
+      <c r="Q2" s="332" t="n"/>
+      <c r="R2" s="333" t="n"/>
       <c r="S2" s="246" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="342" t="n"/>
-      <c r="U2" s="342" t="n"/>
-      <c r="V2" s="342" t="n"/>
-      <c r="W2" s="342" t="n"/>
-      <c r="X2" s="343" t="n"/>
+      <c r="T2" s="332" t="n"/>
+      <c r="U2" s="332" t="n"/>
+      <c r="V2" s="332" t="n"/>
+      <c r="W2" s="332" t="n"/>
+      <c r="X2" s="333" t="n"/>
     </row>
     <row r="3" ht="16.15" customHeight="1" s="257">
       <c r="A3" s="53" t="inlineStr">
@@ -6432,8 +6442,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="290" t="n"/>
-      <c r="E3" s="291" t="n"/>
+      <c r="D3" s="293" t="n"/>
+      <c r="E3" s="294" t="n"/>
       <c r="F3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6454,8 +6464,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="290" t="n"/>
-      <c r="K3" s="291" t="n"/>
+      <c r="J3" s="293" t="n"/>
+      <c r="K3" s="294" t="n"/>
       <c r="L3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6476,8 +6486,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="290" t="n"/>
-      <c r="Q3" s="291" t="n"/>
+      <c r="P3" s="293" t="n"/>
+      <c r="Q3" s="294" t="n"/>
       <c r="R3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6498,8 +6508,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="290" t="n"/>
-      <c r="W3" s="291" t="n"/>
+      <c r="V3" s="293" t="n"/>
+      <c r="W3" s="294" t="n"/>
       <c r="X3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6507,7 +6517,7 @@
       </c>
     </row>
     <row r="4" ht="16.15" customHeight="1" s="257">
-      <c r="A4" s="344" t="n">
+      <c r="A4" s="334" t="n">
         <v>45047</v>
       </c>
       <c r="B4" s="69" t="inlineStr">
@@ -6515,15 +6525,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C4" s="345" t="n"/>
+      <c r="C4" s="335" t="n"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="346" t="n"/>
-      <c r="F4" s="347" t="n"/>
-      <c r="G4" s="344" t="n">
+      <c r="E4" s="336" t="n"/>
+      <c r="F4" s="337" t="n"/>
+      <c r="G4" s="334" t="n">
         <v>45078</v>
       </c>
       <c r="H4" s="70" t="inlineStr">
@@ -6531,15 +6541,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I4" s="348" t="n"/>
+      <c r="I4" s="338" t="n"/>
       <c r="J4" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="349" t="n"/>
-      <c r="L4" s="347" t="n"/>
-      <c r="M4" s="344" t="n">
+      <c r="K4" s="339" t="n"/>
+      <c r="L4" s="337" t="n"/>
+      <c r="M4" s="334" t="n">
         <v>45108</v>
       </c>
       <c r="N4" s="69" t="inlineStr">
@@ -6547,7 +6557,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O4" s="348">
+      <c r="O4" s="338">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6556,15 +6566,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="349">
+      <c r="Q4" s="339">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="347">
+      <c r="R4" s="337">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="350" t="n">
+      <c r="S4" s="340" t="n">
         <v>45139</v>
       </c>
       <c r="T4" s="69" t="inlineStr">
@@ -6572,17 +6582,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U4" s="345" t="n"/>
+      <c r="U4" s="335" t="n"/>
       <c r="V4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="346" t="n"/>
-      <c r="X4" s="347" t="n"/>
+      <c r="W4" s="336" t="n"/>
+      <c r="X4" s="337" t="n"/>
     </row>
     <row r="5" ht="16.15" customHeight="1" s="257">
-      <c r="A5" s="344" t="n">
+      <c r="A5" s="334" t="n">
         <v>45048</v>
       </c>
       <c r="B5" s="69" t="inlineStr">
@@ -6590,15 +6600,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C5" s="348" t="n"/>
+      <c r="C5" s="338" t="n"/>
       <c r="D5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="349" t="n"/>
-      <c r="F5" s="347" t="n"/>
-      <c r="G5" s="344" t="n">
+      <c r="E5" s="339" t="n"/>
+      <c r="F5" s="337" t="n"/>
+      <c r="G5" s="334" t="n">
         <v>45079</v>
       </c>
       <c r="H5" s="70" t="inlineStr">
@@ -6606,7 +6616,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I5" s="348">
+      <c r="I5" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -6615,40 +6625,40 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="349">
+      <c r="K5" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="347">
+      <c r="L5" s="337">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="351" t="n">
+      <c r="M5" s="341" t="n">
         <v>45109</v>
       </c>
-      <c r="N5" s="352" t="inlineStr">
+      <c r="N5" s="342" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="O5" s="353">
+      <c r="O5" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="354" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="355">
+      <c r="P5" s="344" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="345">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="356">
+      <c r="R5" s="346">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="350" t="n">
+      <c r="S5" s="340" t="n">
         <v>45140</v>
       </c>
       <c r="T5" s="69" t="inlineStr">
@@ -6656,17 +6666,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U5" s="348" t="n"/>
+      <c r="U5" s="338" t="n"/>
       <c r="V5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="349" t="n"/>
-      <c r="X5" s="347" t="n"/>
+      <c r="W5" s="339" t="n"/>
+      <c r="X5" s="337" t="n"/>
     </row>
     <row r="6" ht="16.15" customHeight="1" s="257">
-      <c r="A6" s="344" t="n">
+      <c r="A6" s="334" t="n">
         <v>45049</v>
       </c>
       <c r="B6" s="69" t="inlineStr">
@@ -6674,40 +6684,40 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C6" s="348" t="n"/>
+      <c r="C6" s="338" t="n"/>
       <c r="D6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="349" t="n"/>
-      <c r="F6" s="347" t="n"/>
-      <c r="G6" s="351" t="n">
+      <c r="E6" s="339" t="n"/>
+      <c r="F6" s="337" t="n"/>
+      <c r="G6" s="341" t="n">
         <v>45080</v>
       </c>
-      <c r="H6" s="357" t="inlineStr">
+      <c r="H6" s="347" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I6" s="353">
+      <c r="I6" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="354" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="355">
+      <c r="J6" s="344" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="345">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="356">
+      <c r="L6" s="346">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="344" t="n">
+      <c r="M6" s="334" t="n">
         <v>45110</v>
       </c>
       <c r="N6" s="69" t="inlineStr">
@@ -6715,15 +6725,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O6" s="348" t="n"/>
+      <c r="O6" s="338" t="n"/>
       <c r="P6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="349" t="n"/>
-      <c r="R6" s="347" t="n"/>
-      <c r="S6" s="350" t="n">
+      <c r="Q6" s="339" t="n"/>
+      <c r="R6" s="337" t="n"/>
+      <c r="S6" s="340" t="n">
         <v>45141</v>
       </c>
       <c r="T6" s="69" t="inlineStr">
@@ -6731,17 +6741,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U6" s="348" t="n"/>
+      <c r="U6" s="338" t="n"/>
       <c r="V6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="349" t="n"/>
-      <c r="X6" s="347" t="n"/>
+      <c r="W6" s="339" t="n"/>
+      <c r="X6" s="337" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" s="257">
-      <c r="A7" s="344" t="n">
+      <c r="A7" s="334" t="n">
         <v>45050</v>
       </c>
       <c r="B7" s="69" t="inlineStr">
@@ -6749,15 +6759,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C7" s="348" t="n"/>
+      <c r="C7" s="338" t="n"/>
       <c r="D7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="349" t="n"/>
-      <c r="F7" s="347" t="n"/>
-      <c r="G7" s="344" t="n">
+      <c r="E7" s="339" t="n"/>
+      <c r="F7" s="337" t="n"/>
+      <c r="G7" s="334" t="n">
         <v>45081</v>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -6765,7 +6775,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I7" s="348">
+      <c r="I7" s="338">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6774,15 +6784,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="349">
+      <c r="K7" s="339">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="347">
+      <c r="L7" s="337">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="344" t="n">
+      <c r="M7" s="334" t="n">
         <v>45111</v>
       </c>
       <c r="N7" s="69" t="inlineStr">
@@ -6790,15 +6800,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O7" s="348" t="n"/>
+      <c r="O7" s="338" t="n"/>
       <c r="P7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="349" t="n"/>
-      <c r="R7" s="347" t="n"/>
-      <c r="S7" s="350" t="n">
+      <c r="Q7" s="339" t="n"/>
+      <c r="R7" s="337" t="n"/>
+      <c r="S7" s="340" t="n">
         <v>45142</v>
       </c>
       <c r="T7" s="69" t="inlineStr">
@@ -6806,17 +6816,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U7" s="348" t="n"/>
+      <c r="U7" s="338" t="n"/>
       <c r="V7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="349" t="n"/>
-      <c r="X7" s="347" t="n"/>
+      <c r="W7" s="339" t="n"/>
+      <c r="X7" s="337" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" s="257">
-      <c r="A8" s="344" t="n">
+      <c r="A8" s="334" t="n">
         <v>45051</v>
       </c>
       <c r="B8" s="69" t="inlineStr">
@@ -6824,15 +6834,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C8" s="348" t="n"/>
+      <c r="C8" s="338" t="n"/>
       <c r="D8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="349" t="n"/>
-      <c r="F8" s="347" t="n"/>
-      <c r="G8" s="344" t="n">
+      <c r="E8" s="339" t="n"/>
+      <c r="F8" s="337" t="n"/>
+      <c r="G8" s="334" t="n">
         <v>45082</v>
       </c>
       <c r="H8" s="70" t="inlineStr">
@@ -6840,15 +6850,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I8" s="348" t="n"/>
+      <c r="I8" s="338" t="n"/>
       <c r="J8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="349" t="n"/>
-      <c r="L8" s="347" t="n"/>
-      <c r="M8" s="344" t="n">
+      <c r="K8" s="339" t="n"/>
+      <c r="L8" s="337" t="n"/>
+      <c r="M8" s="334" t="n">
         <v>45112</v>
       </c>
       <c r="N8" s="69" t="inlineStr">
@@ -6856,15 +6866,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O8" s="348" t="n"/>
+      <c r="O8" s="338" t="n"/>
       <c r="P8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="349" t="n"/>
-      <c r="R8" s="347" t="n"/>
-      <c r="S8" s="350" t="n">
+      <c r="Q8" s="339" t="n"/>
+      <c r="R8" s="337" t="n"/>
+      <c r="S8" s="340" t="n">
         <v>45143</v>
       </c>
       <c r="T8" s="69" t="inlineStr">
@@ -6872,17 +6882,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U8" s="348" t="n"/>
+      <c r="U8" s="338" t="n"/>
       <c r="V8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="349" t="n"/>
-      <c r="X8" s="347" t="n"/>
+      <c r="W8" s="339" t="n"/>
+      <c r="X8" s="337" t="n"/>
     </row>
     <row r="9" ht="16.15" customHeight="1" s="257">
-      <c r="A9" s="344" t="n">
+      <c r="A9" s="334" t="n">
         <v>45052</v>
       </c>
       <c r="B9" s="69" t="inlineStr">
@@ -6890,15 +6900,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C9" s="348" t="n"/>
+      <c r="C9" s="338" t="n"/>
       <c r="D9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="349" t="n"/>
-      <c r="F9" s="347" t="n"/>
-      <c r="G9" s="344" t="n">
+      <c r="E9" s="339" t="n"/>
+      <c r="F9" s="337" t="n"/>
+      <c r="G9" s="334" t="n">
         <v>45083</v>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -6906,15 +6916,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I9" s="348" t="n"/>
+      <c r="I9" s="338" t="n"/>
       <c r="J9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="349" t="n"/>
-      <c r="L9" s="347" t="n"/>
-      <c r="M9" s="344" t="n">
+      <c r="K9" s="339" t="n"/>
+      <c r="L9" s="337" t="n"/>
+      <c r="M9" s="334" t="n">
         <v>45113</v>
       </c>
       <c r="N9" s="69" t="inlineStr">
@@ -6922,15 +6932,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O9" s="348" t="n"/>
+      <c r="O9" s="338" t="n"/>
       <c r="P9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="349" t="n"/>
-      <c r="R9" s="347" t="n"/>
-      <c r="S9" s="350" t="n">
+      <c r="Q9" s="339" t="n"/>
+      <c r="R9" s="337" t="n"/>
+      <c r="S9" s="340" t="n">
         <v>45144</v>
       </c>
       <c r="T9" s="69" t="inlineStr">
@@ -6938,17 +6948,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U9" s="348" t="n"/>
+      <c r="U9" s="338" t="n"/>
       <c r="V9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="349" t="n"/>
-      <c r="X9" s="347" t="n"/>
+      <c r="W9" s="339" t="n"/>
+      <c r="X9" s="337" t="n"/>
     </row>
     <row r="10" ht="16.15" customHeight="1" s="257">
-      <c r="A10" s="344" t="n">
+      <c r="A10" s="334" t="n">
         <v>45053</v>
       </c>
       <c r="B10" s="69" t="inlineStr">
@@ -6956,15 +6966,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C10" s="348" t="n"/>
+      <c r="C10" s="338" t="n"/>
       <c r="D10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="349" t="n"/>
-      <c r="F10" s="347" t="n"/>
-      <c r="G10" s="344" t="n">
+      <c r="E10" s="339" t="n"/>
+      <c r="F10" s="337" t="n"/>
+      <c r="G10" s="334" t="n">
         <v>45084</v>
       </c>
       <c r="H10" s="70" t="inlineStr">
@@ -6972,15 +6982,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I10" s="348" t="n"/>
+      <c r="I10" s="338" t="n"/>
       <c r="J10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="349" t="n"/>
-      <c r="L10" s="347" t="n"/>
-      <c r="M10" s="344" t="n">
+      <c r="K10" s="339" t="n"/>
+      <c r="L10" s="337" t="n"/>
+      <c r="M10" s="334" t="n">
         <v>45114</v>
       </c>
       <c r="N10" s="69" t="inlineStr">
@@ -6988,15 +6998,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O10" s="348" t="n"/>
+      <c r="O10" s="338" t="n"/>
       <c r="P10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="349" t="n"/>
-      <c r="R10" s="347" t="n"/>
-      <c r="S10" s="350" t="n">
+      <c r="Q10" s="339" t="n"/>
+      <c r="R10" s="337" t="n"/>
+      <c r="S10" s="340" t="n">
         <v>45145</v>
       </c>
       <c r="T10" s="69" t="inlineStr">
@@ -7004,17 +7014,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U10" s="348" t="n"/>
+      <c r="U10" s="338" t="n"/>
       <c r="V10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="349" t="n"/>
-      <c r="X10" s="347" t="n"/>
+      <c r="W10" s="339" t="n"/>
+      <c r="X10" s="337" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" s="257">
-      <c r="A11" s="344" t="n">
+      <c r="A11" s="334" t="n">
         <v>45054</v>
       </c>
       <c r="B11" s="69" t="inlineStr">
@@ -7022,15 +7032,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C11" s="348" t="n"/>
+      <c r="C11" s="338" t="n"/>
       <c r="D11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="349" t="n"/>
-      <c r="F11" s="347" t="n"/>
-      <c r="G11" s="344" t="n">
+      <c r="E11" s="339" t="n"/>
+      <c r="F11" s="337" t="n"/>
+      <c r="G11" s="334" t="n">
         <v>45085</v>
       </c>
       <c r="H11" s="70" t="inlineStr">
@@ -7038,15 +7048,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I11" s="348" t="n"/>
+      <c r="I11" s="338" t="n"/>
       <c r="J11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="349" t="n"/>
-      <c r="L11" s="347" t="n"/>
-      <c r="M11" s="344" t="n">
+      <c r="K11" s="339" t="n"/>
+      <c r="L11" s="337" t="n"/>
+      <c r="M11" s="334" t="n">
         <v>45115</v>
       </c>
       <c r="N11" s="69" t="inlineStr">
@@ -7054,15 +7064,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O11" s="348" t="n"/>
+      <c r="O11" s="338" t="n"/>
       <c r="P11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="349" t="n"/>
-      <c r="R11" s="347" t="n"/>
-      <c r="S11" s="350" t="n">
+      <c r="Q11" s="339" t="n"/>
+      <c r="R11" s="337" t="n"/>
+      <c r="S11" s="340" t="n">
         <v>45146</v>
       </c>
       <c r="T11" s="69" t="inlineStr">
@@ -7070,17 +7080,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U11" s="348" t="n"/>
+      <c r="U11" s="338" t="n"/>
       <c r="V11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="349" t="n"/>
-      <c r="X11" s="347" t="n"/>
+      <c r="W11" s="339" t="n"/>
+      <c r="X11" s="337" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" s="257">
-      <c r="A12" s="344" t="n">
+      <c r="A12" s="334" t="n">
         <v>45055</v>
       </c>
       <c r="B12" s="69" t="inlineStr">
@@ -7088,40 +7098,40 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C12" s="348" t="n"/>
+      <c r="C12" s="338" t="n"/>
       <c r="D12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="349" t="n"/>
-      <c r="F12" s="347" t="n"/>
-      <c r="G12" s="351" t="n">
+      <c r="E12" s="339" t="n"/>
+      <c r="F12" s="337" t="n"/>
+      <c r="G12" s="341" t="n">
         <v>45086</v>
       </c>
-      <c r="H12" s="357" t="inlineStr">
+      <c r="H12" s="347" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I12" s="353">
+      <c r="I12" s="343">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="354" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="355">
+      <c r="J12" s="344" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="345">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="356">
+      <c r="L12" s="346">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="344" t="n">
+      <c r="M12" s="334" t="n">
         <v>45116</v>
       </c>
       <c r="N12" s="69" t="inlineStr">
@@ -7129,15 +7139,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O12" s="348" t="n"/>
+      <c r="O12" s="338" t="n"/>
       <c r="P12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="349" t="n"/>
-      <c r="R12" s="347" t="n"/>
-      <c r="S12" s="350" t="n">
+      <c r="Q12" s="339" t="n"/>
+      <c r="R12" s="337" t="n"/>
+      <c r="S12" s="340" t="n">
         <v>45147</v>
       </c>
       <c r="T12" s="69" t="inlineStr">
@@ -7145,17 +7155,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U12" s="348" t="n"/>
+      <c r="U12" s="338" t="n"/>
       <c r="V12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="349" t="n"/>
-      <c r="X12" s="347" t="n"/>
+      <c r="W12" s="339" t="n"/>
+      <c r="X12" s="337" t="n"/>
     </row>
     <row r="13" ht="16.15" customHeight="1" s="257">
-      <c r="A13" s="344" t="n">
+      <c r="A13" s="334" t="n">
         <v>45056</v>
       </c>
       <c r="B13" s="69" t="inlineStr">
@@ -7163,15 +7173,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C13" s="348" t="n"/>
+      <c r="C13" s="338" t="n"/>
       <c r="D13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="349" t="n"/>
-      <c r="F13" s="347" t="n"/>
-      <c r="G13" s="344" t="n">
+      <c r="E13" s="339" t="n"/>
+      <c r="F13" s="337" t="n"/>
+      <c r="G13" s="334" t="n">
         <v>45087</v>
       </c>
       <c r="H13" s="70" t="inlineStr">
@@ -7179,7 +7189,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I13" s="348">
+      <c r="I13" s="338">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -7188,15 +7198,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="349">
+      <c r="K13" s="339">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="347">
+      <c r="L13" s="337">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="344" t="n">
+      <c r="M13" s="334" t="n">
         <v>45117</v>
       </c>
       <c r="N13" s="69" t="inlineStr">
@@ -7204,15 +7214,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O13" s="348" t="n"/>
+      <c r="O13" s="338" t="n"/>
       <c r="P13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="349" t="n"/>
-      <c r="R13" s="347" t="n"/>
-      <c r="S13" s="350" t="n">
+      <c r="Q13" s="339" t="n"/>
+      <c r="R13" s="337" t="n"/>
+      <c r="S13" s="340" t="n">
         <v>45148</v>
       </c>
       <c r="T13" s="69" t="inlineStr">
@@ -7220,17 +7230,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U13" s="348" t="n"/>
+      <c r="U13" s="338" t="n"/>
       <c r="V13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="349" t="n"/>
-      <c r="X13" s="347" t="n"/>
+      <c r="W13" s="339" t="n"/>
+      <c r="X13" s="337" t="n"/>
     </row>
     <row r="14" ht="16.15" customHeight="1" s="257">
-      <c r="A14" s="344" t="n">
+      <c r="A14" s="334" t="n">
         <v>45057</v>
       </c>
       <c r="B14" s="69" t="inlineStr">
@@ -7238,15 +7248,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C14" s="348" t="n"/>
+      <c r="C14" s="338" t="n"/>
       <c r="D14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="349" t="n"/>
-      <c r="F14" s="347" t="n"/>
-      <c r="G14" s="344" t="n">
+      <c r="E14" s="339" t="n"/>
+      <c r="F14" s="337" t="n"/>
+      <c r="G14" s="334" t="n">
         <v>45088</v>
       </c>
       <c r="H14" s="70" t="inlineStr">
@@ -7254,7 +7264,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I14" s="348">
+      <c r="I14" s="338">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -7263,15 +7273,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="349">
+      <c r="K14" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="347">
+      <c r="L14" s="337">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="344" t="n">
+      <c r="M14" s="334" t="n">
         <v>45118</v>
       </c>
       <c r="N14" s="69" t="inlineStr">
@@ -7279,15 +7289,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O14" s="348" t="n"/>
+      <c r="O14" s="338" t="n"/>
       <c r="P14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="349" t="n"/>
-      <c r="R14" s="347" t="n"/>
-      <c r="S14" s="350" t="n">
+      <c r="Q14" s="339" t="n"/>
+      <c r="R14" s="337" t="n"/>
+      <c r="S14" s="340" t="n">
         <v>45149</v>
       </c>
       <c r="T14" s="69" t="inlineStr">
@@ -7295,17 +7305,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U14" s="348" t="n"/>
+      <c r="U14" s="338" t="n"/>
       <c r="V14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W14" s="349" t="n"/>
-      <c r="X14" s="347" t="n"/>
+      <c r="W14" s="339" t="n"/>
+      <c r="X14" s="337" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" s="257">
-      <c r="A15" s="344" t="n">
+      <c r="A15" s="334" t="n">
         <v>45058</v>
       </c>
       <c r="B15" s="69" t="inlineStr">
@@ -7313,15 +7323,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C15" s="348" t="n"/>
+      <c r="C15" s="338" t="n"/>
       <c r="D15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="349" t="n"/>
-      <c r="F15" s="347" t="n"/>
-      <c r="G15" s="344" t="n">
+      <c r="E15" s="339" t="n"/>
+      <c r="F15" s="337" t="n"/>
+      <c r="G15" s="334" t="n">
         <v>45089</v>
       </c>
       <c r="H15" s="70" t="inlineStr">
@@ -7329,15 +7339,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I15" s="348" t="n"/>
+      <c r="I15" s="338" t="n"/>
       <c r="J15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="349" t="n"/>
-      <c r="L15" s="347" t="n"/>
-      <c r="M15" s="344" t="n">
+      <c r="K15" s="339" t="n"/>
+      <c r="L15" s="337" t="n"/>
+      <c r="M15" s="334" t="n">
         <v>45119</v>
       </c>
       <c r="N15" s="69" t="inlineStr">
@@ -7345,15 +7355,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O15" s="348" t="n"/>
+      <c r="O15" s="338" t="n"/>
       <c r="P15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="349" t="n"/>
-      <c r="R15" s="347" t="n"/>
-      <c r="S15" s="350" t="n">
+      <c r="Q15" s="339" t="n"/>
+      <c r="R15" s="337" t="n"/>
+      <c r="S15" s="340" t="n">
         <v>45150</v>
       </c>
       <c r="T15" s="69" t="inlineStr">
@@ -7361,17 +7371,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U15" s="348" t="n"/>
+      <c r="U15" s="338" t="n"/>
       <c r="V15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W15" s="349" t="n"/>
-      <c r="X15" s="347" t="n"/>
+      <c r="W15" s="339" t="n"/>
+      <c r="X15" s="337" t="n"/>
     </row>
     <row r="16" ht="16.15" customHeight="1" s="257">
-      <c r="A16" s="344" t="n">
+      <c r="A16" s="334" t="n">
         <v>45059</v>
       </c>
       <c r="B16" s="69" t="inlineStr">
@@ -7379,15 +7389,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C16" s="348" t="n"/>
+      <c r="C16" s="338" t="n"/>
       <c r="D16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="349" t="n"/>
-      <c r="F16" s="347" t="n"/>
-      <c r="G16" s="344" t="n">
+      <c r="E16" s="339" t="n"/>
+      <c r="F16" s="337" t="n"/>
+      <c r="G16" s="334" t="n">
         <v>45090</v>
       </c>
       <c r="H16" s="70" t="inlineStr">
@@ -7395,15 +7405,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I16" s="348" t="n"/>
+      <c r="I16" s="338" t="n"/>
       <c r="J16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="349" t="n"/>
-      <c r="L16" s="347" t="n"/>
-      <c r="M16" s="344" t="n">
+      <c r="K16" s="339" t="n"/>
+      <c r="L16" s="337" t="n"/>
+      <c r="M16" s="334" t="n">
         <v>45120</v>
       </c>
       <c r="N16" s="69" t="inlineStr">
@@ -7411,15 +7421,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O16" s="348" t="n"/>
+      <c r="O16" s="338" t="n"/>
       <c r="P16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="349" t="n"/>
-      <c r="R16" s="347" t="n"/>
-      <c r="S16" s="350" t="n">
+      <c r="Q16" s="339" t="n"/>
+      <c r="R16" s="337" t="n"/>
+      <c r="S16" s="340" t="n">
         <v>45151</v>
       </c>
       <c r="T16" s="69" t="inlineStr">
@@ -7427,17 +7437,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U16" s="348" t="n"/>
+      <c r="U16" s="338" t="n"/>
       <c r="V16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W16" s="349" t="n"/>
-      <c r="X16" s="347" t="n"/>
+      <c r="W16" s="339" t="n"/>
+      <c r="X16" s="337" t="n"/>
     </row>
     <row r="17" ht="16.15" customHeight="1" s="257">
-      <c r="A17" s="344" t="n">
+      <c r="A17" s="334" t="n">
         <v>45060</v>
       </c>
       <c r="B17" s="69" t="inlineStr">
@@ -7445,15 +7455,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C17" s="348" t="n"/>
+      <c r="C17" s="338" t="n"/>
       <c r="D17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="349" t="n"/>
-      <c r="F17" s="347" t="n"/>
-      <c r="G17" s="344" t="n">
+      <c r="E17" s="339" t="n"/>
+      <c r="F17" s="337" t="n"/>
+      <c r="G17" s="334" t="n">
         <v>45091</v>
       </c>
       <c r="H17" s="70" t="inlineStr">
@@ -7461,15 +7471,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I17" s="348" t="n"/>
+      <c r="I17" s="338" t="n"/>
       <c r="J17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="349" t="n"/>
-      <c r="L17" s="347" t="n"/>
-      <c r="M17" s="344" t="n">
+      <c r="K17" s="339" t="n"/>
+      <c r="L17" s="337" t="n"/>
+      <c r="M17" s="334" t="n">
         <v>45121</v>
       </c>
       <c r="N17" s="69" t="inlineStr">
@@ -7477,15 +7487,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O17" s="348" t="n"/>
+      <c r="O17" s="338" t="n"/>
       <c r="P17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="349" t="n"/>
-      <c r="R17" s="347" t="n"/>
-      <c r="S17" s="350" t="n">
+      <c r="Q17" s="339" t="n"/>
+      <c r="R17" s="337" t="n"/>
+      <c r="S17" s="340" t="n">
         <v>45152</v>
       </c>
       <c r="T17" s="69" t="inlineStr">
@@ -7493,17 +7503,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U17" s="348" t="n"/>
+      <c r="U17" s="338" t="n"/>
       <c r="V17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W17" s="349" t="n"/>
-      <c r="X17" s="347" t="n"/>
+      <c r="W17" s="339" t="n"/>
+      <c r="X17" s="337" t="n"/>
     </row>
     <row r="18" ht="16.15" customHeight="1" s="257">
-      <c r="A18" s="344" t="n">
+      <c r="A18" s="334" t="n">
         <v>45061</v>
       </c>
       <c r="B18" s="69" t="inlineStr">
@@ -7511,15 +7521,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C18" s="348" t="n"/>
+      <c r="C18" s="338" t="n"/>
       <c r="D18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="349" t="n"/>
-      <c r="F18" s="347" t="n"/>
-      <c r="G18" s="344" t="n">
+      <c r="E18" s="339" t="n"/>
+      <c r="F18" s="337" t="n"/>
+      <c r="G18" s="334" t="n">
         <v>45092</v>
       </c>
       <c r="H18" s="70" t="inlineStr">
@@ -7527,15 +7537,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I18" s="348" t="n"/>
+      <c r="I18" s="338" t="n"/>
       <c r="J18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="349" t="n"/>
-      <c r="L18" s="347" t="n"/>
-      <c r="M18" s="344" t="n">
+      <c r="K18" s="339" t="n"/>
+      <c r="L18" s="337" t="n"/>
+      <c r="M18" s="334" t="n">
         <v>45122</v>
       </c>
       <c r="N18" s="69" t="inlineStr">
@@ -7543,15 +7553,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O18" s="348" t="n"/>
+      <c r="O18" s="338" t="n"/>
       <c r="P18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="349" t="n"/>
-      <c r="R18" s="347" t="n"/>
-      <c r="S18" s="350" t="n">
+      <c r="Q18" s="339" t="n"/>
+      <c r="R18" s="337" t="n"/>
+      <c r="S18" s="340" t="n">
         <v>45153</v>
       </c>
       <c r="T18" s="69" t="inlineStr">
@@ -7559,17 +7569,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U18" s="348" t="n"/>
+      <c r="U18" s="338" t="n"/>
       <c r="V18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W18" s="349" t="n"/>
-      <c r="X18" s="347" t="n"/>
+      <c r="W18" s="339" t="n"/>
+      <c r="X18" s="337" t="n"/>
     </row>
     <row r="19" ht="16.15" customHeight="1" s="257">
-      <c r="A19" s="344" t="n">
+      <c r="A19" s="334" t="n">
         <v>45062</v>
       </c>
       <c r="B19" s="69" t="inlineStr">
@@ -7577,15 +7587,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C19" s="348" t="n"/>
+      <c r="C19" s="338" t="n"/>
       <c r="D19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="349" t="n"/>
-      <c r="F19" s="347" t="n"/>
-      <c r="G19" s="344" t="n">
+      <c r="E19" s="339" t="n"/>
+      <c r="F19" s="337" t="n"/>
+      <c r="G19" s="334" t="n">
         <v>45093</v>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -7593,15 +7603,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I19" s="348" t="inlineStr">
+      <c r="I19" s="338" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="50" t="n"/>
-      <c r="K19" s="349" t="n"/>
-      <c r="L19" s="347" t="n"/>
-      <c r="M19" s="344" t="n">
+      <c r="K19" s="339" t="n"/>
+      <c r="L19" s="337" t="n"/>
+      <c r="M19" s="334" t="n">
         <v>45123</v>
       </c>
       <c r="N19" s="69" t="inlineStr">
@@ -7609,15 +7619,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O19" s="348" t="n"/>
+      <c r="O19" s="338" t="n"/>
       <c r="P19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="349" t="n"/>
-      <c r="R19" s="347" t="n"/>
-      <c r="S19" s="350" t="n">
+      <c r="Q19" s="339" t="n"/>
+      <c r="R19" s="337" t="n"/>
+      <c r="S19" s="340" t="n">
         <v>45154</v>
       </c>
       <c r="T19" s="69" t="inlineStr">
@@ -7625,17 +7635,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U19" s="348" t="n"/>
+      <c r="U19" s="338" t="n"/>
       <c r="V19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W19" s="349" t="n"/>
-      <c r="X19" s="347" t="n"/>
+      <c r="W19" s="339" t="n"/>
+      <c r="X19" s="337" t="n"/>
     </row>
     <row r="20" ht="16.15" customHeight="1" s="257">
-      <c r="A20" s="344" t="n">
+      <c r="A20" s="334" t="n">
         <v>45063</v>
       </c>
       <c r="B20" s="69" t="inlineStr">
@@ -7643,15 +7653,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C20" s="348" t="n"/>
+      <c r="C20" s="338" t="n"/>
       <c r="D20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="349" t="n"/>
-      <c r="F20" s="347" t="n"/>
-      <c r="G20" s="344" t="n">
+      <c r="E20" s="339" t="n"/>
+      <c r="F20" s="337" t="n"/>
+      <c r="G20" s="334" t="n">
         <v>45094</v>
       </c>
       <c r="H20" s="70" t="inlineStr">
@@ -7659,15 +7669,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I20" s="348" t="inlineStr">
+      <c r="I20" s="338" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="50" t="n"/>
-      <c r="K20" s="349" t="n"/>
-      <c r="L20" s="347" t="n"/>
-      <c r="M20" s="344" t="n">
+      <c r="K20" s="339" t="n"/>
+      <c r="L20" s="337" t="n"/>
+      <c r="M20" s="334" t="n">
         <v>45124</v>
       </c>
       <c r="N20" s="69" t="inlineStr">
@@ -7675,15 +7685,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O20" s="348" t="n"/>
+      <c r="O20" s="338" t="n"/>
       <c r="P20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="349" t="n"/>
-      <c r="R20" s="347" t="n"/>
-      <c r="S20" s="350" t="n">
+      <c r="Q20" s="339" t="n"/>
+      <c r="R20" s="337" t="n"/>
+      <c r="S20" s="340" t="n">
         <v>45155</v>
       </c>
       <c r="T20" s="69" t="inlineStr">
@@ -7691,17 +7701,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U20" s="348" t="n"/>
+      <c r="U20" s="338" t="n"/>
       <c r="V20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W20" s="349" t="n"/>
-      <c r="X20" s="347" t="n"/>
+      <c r="W20" s="339" t="n"/>
+      <c r="X20" s="337" t="n"/>
     </row>
     <row r="21" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A21" s="344" t="n">
+      <c r="A21" s="334" t="n">
         <v>45064</v>
       </c>
       <c r="B21" s="69" t="inlineStr">
@@ -7709,15 +7719,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C21" s="348" t="n"/>
+      <c r="C21" s="338" t="n"/>
       <c r="D21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="349" t="n"/>
-      <c r="F21" s="347" t="n"/>
-      <c r="G21" s="344" t="n">
+      <c r="E21" s="339" t="n"/>
+      <c r="F21" s="337" t="n"/>
+      <c r="G21" s="334" t="n">
         <v>45095</v>
       </c>
       <c r="H21" s="70" t="inlineStr">
@@ -7725,15 +7735,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I21" s="348" t="inlineStr">
+      <c r="I21" s="338" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="50" t="n"/>
-      <c r="K21" s="349" t="n"/>
-      <c r="L21" s="347" t="n"/>
-      <c r="M21" s="344" t="n">
+      <c r="K21" s="339" t="n"/>
+      <c r="L21" s="337" t="n"/>
+      <c r="M21" s="334" t="n">
         <v>45125</v>
       </c>
       <c r="N21" s="69" t="inlineStr">
@@ -7741,15 +7751,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O21" s="348" t="n"/>
+      <c r="O21" s="338" t="n"/>
       <c r="P21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="349" t="n"/>
-      <c r="R21" s="347" t="n"/>
-      <c r="S21" s="358" t="n">
+      <c r="Q21" s="339" t="n"/>
+      <c r="R21" s="337" t="n"/>
+      <c r="S21" s="348" t="n">
         <v>45156</v>
       </c>
       <c r="T21" s="71" t="inlineStr">
@@ -7757,17 +7767,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U21" s="359" t="n"/>
+      <c r="U21" s="349" t="n"/>
       <c r="V21" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W21" s="360" t="n"/>
-      <c r="X21" s="361" t="n"/>
+      <c r="W21" s="350" t="n"/>
+      <c r="X21" s="351" t="n"/>
     </row>
     <row r="22" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A22" s="344" t="n">
+      <c r="A22" s="334" t="n">
         <v>45065</v>
       </c>
       <c r="B22" s="69" t="inlineStr">
@@ -7775,15 +7785,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C22" s="348" t="n"/>
+      <c r="C22" s="338" t="n"/>
       <c r="D22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="349" t="n"/>
-      <c r="F22" s="347" t="n"/>
-      <c r="G22" s="344" t="n">
+      <c r="E22" s="339" t="n"/>
+      <c r="F22" s="337" t="n"/>
+      <c r="G22" s="334" t="n">
         <v>45096</v>
       </c>
       <c r="H22" s="70" t="inlineStr">
@@ -7791,11 +7801,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I22" s="348" t="n"/>
+      <c r="I22" s="338" t="n"/>
       <c r="J22" s="50" t="n"/>
-      <c r="K22" s="349" t="n"/>
-      <c r="L22" s="347" t="n"/>
-      <c r="M22" s="344" t="n">
+      <c r="K22" s="339" t="n"/>
+      <c r="L22" s="337" t="n"/>
+      <c r="M22" s="334" t="n">
         <v>45126</v>
       </c>
       <c r="N22" s="69" t="inlineStr">
@@ -7803,27 +7813,27 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O22" s="348" t="n"/>
+      <c r="O22" s="338" t="n"/>
       <c r="P22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="349" t="n"/>
-      <c r="R22" s="347" t="n"/>
+      <c r="Q22" s="339" t="n"/>
+      <c r="R22" s="337" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="U22" s="362" t="n"/>
+      <c r="U22" s="352" t="n"/>
       <c r="V22" s="238" t="n"/>
-      <c r="W22" s="363" t="n"/>
-      <c r="X22" s="363" t="n"/>
+      <c r="W22" s="353" t="n"/>
+      <c r="X22" s="353" t="n"/>
     </row>
     <row r="23" ht="16.15" customHeight="1" s="257">
-      <c r="A23" s="344" t="n">
+      <c r="A23" s="334" t="n">
         <v>45066</v>
       </c>
       <c r="B23" s="69" t="inlineStr">
@@ -7831,15 +7841,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C23" s="348" t="n"/>
+      <c r="C23" s="338" t="n"/>
       <c r="D23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="349" t="n"/>
-      <c r="F23" s="347" t="n"/>
-      <c r="G23" s="344" t="n">
+      <c r="E23" s="339" t="n"/>
+      <c r="F23" s="337" t="n"/>
+      <c r="G23" s="334" t="n">
         <v>45097</v>
       </c>
       <c r="H23" s="70" t="inlineStr">
@@ -7847,11 +7857,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I23" s="348" t="n"/>
+      <c r="I23" s="338" t="n"/>
       <c r="J23" s="50" t="n"/>
-      <c r="K23" s="349" t="n"/>
-      <c r="L23" s="347" t="n"/>
-      <c r="M23" s="344" t="n">
+      <c r="K23" s="339" t="n"/>
+      <c r="L23" s="337" t="n"/>
+      <c r="M23" s="334" t="n">
         <v>45127</v>
       </c>
       <c r="N23" s="69" t="inlineStr">
@@ -7859,31 +7869,31 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O23" s="348" t="n"/>
+      <c r="O23" s="338" t="n"/>
       <c r="P23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="349" t="n"/>
-      <c r="R23" s="347" t="n"/>
-      <c r="S23" s="364" t="inlineStr">
+      <c r="Q23" s="339" t="n"/>
+      <c r="R23" s="337" t="n"/>
+      <c r="S23" s="354" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="T23" s="365" t="inlineStr">
+      <c r="T23" s="355" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="U23" s="342" t="n"/>
-      <c r="V23" s="342" t="n"/>
-      <c r="W23" s="342" t="n"/>
-      <c r="X23" s="366" t="n"/>
+      <c r="U23" s="332" t="n"/>
+      <c r="V23" s="332" t="n"/>
+      <c r="W23" s="332" t="n"/>
+      <c r="X23" s="356" t="n"/>
     </row>
     <row r="24" ht="16.15" customHeight="1" s="257">
-      <c r="A24" s="344" t="n">
+      <c r="A24" s="334" t="n">
         <v>45067</v>
       </c>
       <c r="B24" s="69" t="inlineStr">
@@ -7891,15 +7901,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C24" s="348" t="n"/>
+      <c r="C24" s="338" t="n"/>
       <c r="D24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="349" t="n"/>
-      <c r="F24" s="347" t="n"/>
-      <c r="G24" s="344" t="n">
+      <c r="E24" s="339" t="n"/>
+      <c r="F24" s="337" t="n"/>
+      <c r="G24" s="334" t="n">
         <v>45098</v>
       </c>
       <c r="H24" s="70" t="inlineStr">
@@ -7907,11 +7917,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I24" s="348" t="n"/>
+      <c r="I24" s="338" t="n"/>
       <c r="J24" s="50" t="n"/>
-      <c r="K24" s="349" t="n"/>
-      <c r="L24" s="347" t="n"/>
-      <c r="M24" s="344" t="n">
+      <c r="K24" s="339" t="n"/>
+      <c r="L24" s="337" t="n"/>
+      <c r="M24" s="334" t="n">
         <v>45128</v>
       </c>
       <c r="N24" s="69" t="inlineStr">
@@ -7919,14 +7929,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O24" s="348" t="n"/>
+      <c r="O24" s="338" t="n"/>
       <c r="P24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="349" t="n"/>
-      <c r="R24" s="347" t="n"/>
+      <c r="Q24" s="339" t="n"/>
+      <c r="R24" s="337" t="n"/>
       <c r="S24" s="73" t="n">
         <v>1</v>
       </c>
@@ -7935,13 +7945,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U24" s="290" t="n"/>
-      <c r="V24" s="290" t="n"/>
-      <c r="W24" s="290" t="n"/>
-      <c r="X24" s="291" t="n"/>
+      <c r="U24" s="293" t="n"/>
+      <c r="V24" s="293" t="n"/>
+      <c r="W24" s="293" t="n"/>
+      <c r="X24" s="294" t="n"/>
     </row>
     <row r="25" ht="16.15" customHeight="1" s="257">
-      <c r="A25" s="344" t="n">
+      <c r="A25" s="334" t="n">
         <v>45068</v>
       </c>
       <c r="B25" s="69" t="inlineStr">
@@ -7949,15 +7959,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C25" s="348" t="n"/>
+      <c r="C25" s="338" t="n"/>
       <c r="D25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="349" t="n"/>
-      <c r="F25" s="347" t="n"/>
-      <c r="G25" s="344" t="n">
+      <c r="E25" s="339" t="n"/>
+      <c r="F25" s="337" t="n"/>
+      <c r="G25" s="334" t="n">
         <v>45099</v>
       </c>
       <c r="H25" s="70" t="inlineStr">
@@ -7965,11 +7975,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I25" s="348" t="n"/>
+      <c r="I25" s="338" t="n"/>
       <c r="J25" s="50" t="n"/>
-      <c r="K25" s="349" t="n"/>
-      <c r="L25" s="347" t="n"/>
-      <c r="M25" s="344" t="n">
+      <c r="K25" s="339" t="n"/>
+      <c r="L25" s="337" t="n"/>
+      <c r="M25" s="334" t="n">
         <v>45129</v>
       </c>
       <c r="N25" s="69" t="inlineStr">
@@ -7977,14 +7987,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O25" s="348" t="n"/>
+      <c r="O25" s="338" t="n"/>
       <c r="P25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="349" t="n"/>
-      <c r="R25" s="347" t="n"/>
+      <c r="Q25" s="339" t="n"/>
+      <c r="R25" s="337" t="n"/>
       <c r="S25" s="73" t="n">
         <v>2</v>
       </c>
@@ -7993,13 +8003,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U25" s="290" t="n"/>
-      <c r="V25" s="290" t="n"/>
-      <c r="W25" s="290" t="n"/>
-      <c r="X25" s="291" t="n"/>
+      <c r="U25" s="293" t="n"/>
+      <c r="V25" s="293" t="n"/>
+      <c r="W25" s="293" t="n"/>
+      <c r="X25" s="294" t="n"/>
     </row>
     <row r="26" ht="16.15" customHeight="1" s="257">
-      <c r="A26" s="344" t="n">
+      <c r="A26" s="334" t="n">
         <v>45069</v>
       </c>
       <c r="B26" s="69" t="inlineStr">
@@ -8007,36 +8017,36 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C26" s="348" t="n"/>
+      <c r="C26" s="338" t="n"/>
       <c r="D26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="349" t="n"/>
-      <c r="F26" s="347" t="n"/>
-      <c r="G26" s="351" t="n">
+      <c r="E26" s="339" t="n"/>
+      <c r="F26" s="337" t="n"/>
+      <c r="G26" s="341" t="n">
         <v>45100</v>
       </c>
-      <c r="H26" s="357" t="inlineStr">
+      <c r="H26" s="347" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I26" s="353">
+      <c r="I26" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="354" t="n"/>
-      <c r="K26" s="355">
+      <c r="J26" s="344" t="n"/>
+      <c r="K26" s="345">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="356">
+      <c r="L26" s="346">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="344" t="n">
+      <c r="M26" s="334" t="n">
         <v>45130</v>
       </c>
       <c r="N26" s="69" t="inlineStr">
@@ -8044,14 +8054,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O26" s="348" t="n"/>
+      <c r="O26" s="338" t="n"/>
       <c r="P26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="349" t="n"/>
-      <c r="R26" s="347" t="n"/>
+      <c r="Q26" s="339" t="n"/>
+      <c r="R26" s="337" t="n"/>
       <c r="S26" s="73" t="n">
         <v>3</v>
       </c>
@@ -8060,13 +8070,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U26" s="290" t="n"/>
-      <c r="V26" s="290" t="n"/>
-      <c r="W26" s="290" t="n"/>
-      <c r="X26" s="291" t="n"/>
+      <c r="U26" s="293" t="n"/>
+      <c r="V26" s="293" t="n"/>
+      <c r="W26" s="293" t="n"/>
+      <c r="X26" s="294" t="n"/>
     </row>
     <row r="27" ht="16.15" customHeight="1" s="257">
-      <c r="A27" s="344" t="n">
+      <c r="A27" s="334" t="n">
         <v>45070</v>
       </c>
       <c r="B27" s="69" t="inlineStr">
@@ -8074,15 +8084,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C27" s="348" t="n"/>
+      <c r="C27" s="338" t="n"/>
       <c r="D27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="349" t="n"/>
-      <c r="F27" s="347" t="n"/>
-      <c r="G27" s="344" t="n">
+      <c r="E27" s="339" t="n"/>
+      <c r="F27" s="337" t="n"/>
+      <c r="G27" s="334" t="n">
         <v>45101</v>
       </c>
       <c r="H27" s="70" t="inlineStr">
@@ -8090,20 +8100,20 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I27" s="348">
+      <c r="I27" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J27" s="50" t="n"/>
-      <c r="K27" s="349">
+      <c r="K27" s="339">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="347">
+      <c r="L27" s="337">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="344" t="n">
+      <c r="M27" s="334" t="n">
         <v>45131</v>
       </c>
       <c r="N27" s="69" t="inlineStr">
@@ -8111,14 +8121,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O27" s="348" t="n"/>
+      <c r="O27" s="338" t="n"/>
       <c r="P27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="349" t="n"/>
-      <c r="R27" s="347" t="n"/>
+      <c r="Q27" s="339" t="n"/>
+      <c r="R27" s="337" t="n"/>
       <c r="S27" s="73" t="n">
         <v>4</v>
       </c>
@@ -8127,13 +8137,13 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U27" s="290" t="n"/>
-      <c r="V27" s="290" t="n"/>
-      <c r="W27" s="290" t="n"/>
-      <c r="X27" s="291" t="n"/>
+      <c r="U27" s="293" t="n"/>
+      <c r="V27" s="293" t="n"/>
+      <c r="W27" s="293" t="n"/>
+      <c r="X27" s="294" t="n"/>
     </row>
     <row r="28" ht="16.15" customHeight="1" s="257">
-      <c r="A28" s="344" t="n">
+      <c r="A28" s="334" t="n">
         <v>45071</v>
       </c>
       <c r="B28" s="69" t="inlineStr">
@@ -8141,15 +8151,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C28" s="348" t="n"/>
+      <c r="C28" s="338" t="n"/>
       <c r="D28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="349" t="n"/>
-      <c r="F28" s="347" t="n"/>
-      <c r="G28" s="344" t="n">
+      <c r="E28" s="339" t="n"/>
+      <c r="F28" s="337" t="n"/>
+      <c r="G28" s="334" t="n">
         <v>45102</v>
       </c>
       <c r="H28" s="70" t="inlineStr">
@@ -8157,20 +8167,20 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="338">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
       <c r="J28" s="50" t="n"/>
-      <c r="K28" s="349">
+      <c r="K28" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="347">
+      <c r="L28" s="337">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="344" t="n">
+      <c r="M28" s="334" t="n">
         <v>45132</v>
       </c>
       <c r="N28" s="69" t="inlineStr">
@@ -8178,14 +8188,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O28" s="348" t="n"/>
+      <c r="O28" s="338" t="n"/>
       <c r="P28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="349" t="n"/>
-      <c r="R28" s="347" t="n"/>
+      <c r="Q28" s="339" t="n"/>
+      <c r="R28" s="337" t="n"/>
       <c r="S28" s="73" t="n">
         <v>5</v>
       </c>
@@ -8194,13 +8204,13 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U28" s="290" t="n"/>
-      <c r="V28" s="290" t="n"/>
-      <c r="W28" s="290" t="n"/>
-      <c r="X28" s="291" t="n"/>
+      <c r="U28" s="293" t="n"/>
+      <c r="V28" s="293" t="n"/>
+      <c r="W28" s="293" t="n"/>
+      <c r="X28" s="294" t="n"/>
     </row>
     <row r="29" ht="16.15" customHeight="1" s="257">
-      <c r="A29" s="344" t="n">
+      <c r="A29" s="334" t="n">
         <v>45072</v>
       </c>
       <c r="B29" s="69" t="inlineStr">
@@ -8208,7 +8218,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C29" s="348">
+      <c r="C29" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -8217,15 +8227,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="349">
+      <c r="E29" s="339">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="347">
+      <c r="F29" s="337">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="344" t="n">
+      <c r="G29" s="334" t="n">
         <v>45103</v>
       </c>
       <c r="H29" s="70" t="inlineStr">
@@ -8233,11 +8243,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I29" s="348" t="n"/>
+      <c r="I29" s="338" t="n"/>
       <c r="J29" s="50" t="n"/>
-      <c r="K29" s="349" t="n"/>
-      <c r="L29" s="347" t="n"/>
-      <c r="M29" s="344" t="n">
+      <c r="K29" s="339" t="n"/>
+      <c r="L29" s="337" t="n"/>
+      <c r="M29" s="334" t="n">
         <v>45133</v>
       </c>
       <c r="N29" s="69" t="inlineStr">
@@ -8245,14 +8255,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O29" s="348" t="n"/>
+      <c r="O29" s="338" t="n"/>
       <c r="P29" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="349" t="n"/>
-      <c r="R29" s="347" t="n"/>
+      <c r="Q29" s="339" t="n"/>
+      <c r="R29" s="337" t="n"/>
       <c r="S29" s="73" t="n">
         <v>6</v>
       </c>
@@ -8261,13 +8271,13 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U29" s="290" t="n"/>
-      <c r="V29" s="290" t="n"/>
-      <c r="W29" s="290" t="n"/>
-      <c r="X29" s="291" t="n"/>
+      <c r="U29" s="293" t="n"/>
+      <c r="V29" s="293" t="n"/>
+      <c r="W29" s="293" t="n"/>
+      <c r="X29" s="294" t="n"/>
     </row>
     <row r="30" ht="16.15" customHeight="1" s="257">
-      <c r="A30" s="344" t="n">
+      <c r="A30" s="334" t="n">
         <v>45073</v>
       </c>
       <c r="B30" s="69" t="inlineStr">
@@ -8275,7 +8285,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C30" s="348">
+      <c r="C30" s="338">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -8284,15 +8294,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="349">
+      <c r="E30" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="347">
+      <c r="F30" s="337">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="344" t="n">
+      <c r="G30" s="334" t="n">
         <v>45104</v>
       </c>
       <c r="H30" s="70" t="inlineStr">
@@ -8300,11 +8310,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I30" s="348" t="n"/>
+      <c r="I30" s="338" t="n"/>
       <c r="J30" s="50" t="n"/>
-      <c r="K30" s="349" t="n"/>
-      <c r="L30" s="347" t="n"/>
-      <c r="M30" s="344" t="n">
+      <c r="K30" s="339" t="n"/>
+      <c r="L30" s="337" t="n"/>
+      <c r="M30" s="334" t="n">
         <v>45134</v>
       </c>
       <c r="N30" s="69" t="inlineStr">
@@ -8312,14 +8322,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O30" s="348" t="n"/>
+      <c r="O30" s="338" t="n"/>
       <c r="P30" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="349" t="n"/>
-      <c r="R30" s="347" t="n"/>
+      <c r="Q30" s="339" t="n"/>
+      <c r="R30" s="337" t="n"/>
       <c r="S30" s="73" t="n">
         <v>7</v>
       </c>
@@ -8328,38 +8338,38 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U30" s="290" t="n"/>
-      <c r="V30" s="290" t="n"/>
-      <c r="W30" s="290" t="n"/>
-      <c r="X30" s="291" t="n"/>
+      <c r="U30" s="293" t="n"/>
+      <c r="V30" s="293" t="n"/>
+      <c r="W30" s="293" t="n"/>
+      <c r="X30" s="294" t="n"/>
     </row>
     <row r="31" ht="16.15" customHeight="1" s="257">
-      <c r="A31" s="351" t="n">
+      <c r="A31" s="341" t="n">
         <v>45074</v>
       </c>
-      <c r="B31" s="352" t="inlineStr">
+      <c r="B31" s="342" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="C31" s="353">
+      <c r="C31" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="354" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="355">
+      <c r="D31" s="344" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="345">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="356">
+      <c r="F31" s="346">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="344" t="n">
+      <c r="G31" s="334" t="n">
         <v>45105</v>
       </c>
       <c r="H31" s="70" t="inlineStr">
@@ -8367,11 +8377,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I31" s="348" t="n"/>
+      <c r="I31" s="338" t="n"/>
       <c r="J31" s="50" t="n"/>
-      <c r="K31" s="349" t="n"/>
-      <c r="L31" s="347" t="n"/>
-      <c r="M31" s="344" t="n">
+      <c r="K31" s="339" t="n"/>
+      <c r="L31" s="337" t="n"/>
+      <c r="M31" s="334" t="n">
         <v>45135</v>
       </c>
       <c r="N31" s="69" t="inlineStr">
@@ -8379,14 +8389,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O31" s="348" t="n"/>
+      <c r="O31" s="338" t="n"/>
       <c r="P31" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="349" t="n"/>
-      <c r="R31" s="347" t="n"/>
+      <c r="Q31" s="339" t="n"/>
+      <c r="R31" s="337" t="n"/>
       <c r="S31" s="73" t="n">
         <v>8</v>
       </c>
@@ -8395,13 +8405,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U31" s="290" t="n"/>
-      <c r="V31" s="290" t="n"/>
-      <c r="W31" s="290" t="n"/>
-      <c r="X31" s="291" t="n"/>
+      <c r="U31" s="293" t="n"/>
+      <c r="V31" s="293" t="n"/>
+      <c r="W31" s="293" t="n"/>
+      <c r="X31" s="294" t="n"/>
     </row>
     <row r="32" ht="16.15" customHeight="1" s="257">
-      <c r="A32" s="344" t="n">
+      <c r="A32" s="334" t="n">
         <v>45075</v>
       </c>
       <c r="B32" s="69" t="inlineStr">
@@ -8409,15 +8419,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C32" s="348" t="n"/>
+      <c r="C32" s="338" t="n"/>
       <c r="D32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="349" t="n"/>
-      <c r="F32" s="347" t="n"/>
-      <c r="G32" s="344" t="n">
+      <c r="E32" s="339" t="n"/>
+      <c r="F32" s="337" t="n"/>
+      <c r="G32" s="334" t="n">
         <v>45106</v>
       </c>
       <c r="H32" s="70" t="inlineStr">
@@ -8425,11 +8435,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I32" s="348" t="n"/>
+      <c r="I32" s="338" t="n"/>
       <c r="J32" s="50" t="n"/>
-      <c r="K32" s="349" t="n"/>
-      <c r="L32" s="347" t="n"/>
-      <c r="M32" s="344" t="n">
+      <c r="K32" s="339" t="n"/>
+      <c r="L32" s="337" t="n"/>
+      <c r="M32" s="334" t="n">
         <v>45136</v>
       </c>
       <c r="N32" s="69" t="inlineStr">
@@ -8437,14 +8447,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O32" s="348" t="n"/>
+      <c r="O32" s="338" t="n"/>
       <c r="P32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="349" t="n"/>
-      <c r="R32" s="347" t="n"/>
+      <c r="Q32" s="339" t="n"/>
+      <c r="R32" s="337" t="n"/>
       <c r="S32" s="73" t="n">
         <v>9</v>
       </c>
@@ -8453,13 +8463,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U32" s="290" t="n"/>
-      <c r="V32" s="290" t="n"/>
-      <c r="W32" s="290" t="n"/>
-      <c r="X32" s="291" t="n"/>
+      <c r="U32" s="293" t="n"/>
+      <c r="V32" s="293" t="n"/>
+      <c r="W32" s="293" t="n"/>
+      <c r="X32" s="294" t="n"/>
     </row>
     <row r="33" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A33" s="344" t="n">
+      <c r="A33" s="334" t="n">
         <v>45076</v>
       </c>
       <c r="B33" s="69" t="inlineStr">
@@ -8467,15 +8477,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C33" s="348" t="n"/>
+      <c r="C33" s="338" t="n"/>
       <c r="D33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="349" t="n"/>
-      <c r="F33" s="347" t="n"/>
-      <c r="G33" s="367" t="n">
+      <c r="E33" s="339" t="n"/>
+      <c r="F33" s="337" t="n"/>
+      <c r="G33" s="357" t="n">
         <v>45107</v>
       </c>
       <c r="H33" s="82" t="inlineStr">
@@ -8483,20 +8493,20 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I33" s="359">
+      <c r="I33" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J33" s="60" t="n"/>
-      <c r="K33" s="360">
+      <c r="K33" s="350">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="361">
+      <c r="L33" s="351">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="344" t="n">
+      <c r="M33" s="334" t="n">
         <v>45137</v>
       </c>
       <c r="N33" s="69" t="inlineStr">
@@ -8504,14 +8514,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O33" s="348" t="n"/>
+      <c r="O33" s="338" t="n"/>
       <c r="P33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="349" t="n"/>
-      <c r="R33" s="347" t="n"/>
+      <c r="Q33" s="339" t="n"/>
+      <c r="R33" s="337" t="n"/>
       <c r="S33" s="77" t="n">
         <v>10</v>
       </c>
@@ -8520,13 +8530,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U33" s="368" t="n"/>
-      <c r="V33" s="368" t="n"/>
-      <c r="W33" s="368" t="n"/>
-      <c r="X33" s="369" t="n"/>
+      <c r="U33" s="358" t="n"/>
+      <c r="V33" s="358" t="n"/>
+      <c r="W33" s="358" t="n"/>
+      <c r="X33" s="359" t="n"/>
     </row>
     <row r="34" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A34" s="367" t="n">
+      <c r="A34" s="357" t="n">
         <v>45077</v>
       </c>
       <c r="B34" s="71" t="inlineStr">
@@ -8534,20 +8544,20 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C34" s="359" t="n"/>
+      <c r="C34" s="349" t="n"/>
       <c r="D34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="360" t="n"/>
-      <c r="F34" s="361" t="n"/>
-      <c r="G34" s="370" t="n"/>
-      <c r="I34" s="362" t="n"/>
+      <c r="E34" s="350" t="n"/>
+      <c r="F34" s="351" t="n"/>
+      <c r="G34" s="360" t="n"/>
+      <c r="I34" s="352" t="n"/>
       <c r="J34" s="238" t="n"/>
-      <c r="K34" s="362" t="n"/>
-      <c r="L34" s="362" t="n"/>
-      <c r="M34" s="367" t="n">
+      <c r="K34" s="352" t="n"/>
+      <c r="L34" s="352" t="n"/>
+      <c r="M34" s="357" t="n">
         <v>45138</v>
       </c>
       <c r="N34" s="71" t="inlineStr">
@@ -8555,14 +8565,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O34" s="359" t="n"/>
+      <c r="O34" s="349" t="n"/>
       <c r="P34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="360" t="n"/>
-      <c r="R34" s="361" t="n"/>
+      <c r="Q34" s="350" t="n"/>
+      <c r="R34" s="351" t="n"/>
       <c r="S34" s="238" t="n"/>
       <c r="T34" s="238" t="inlineStr">
         <is>
@@ -8940,8 +8950,8 @@
         <f>日程表１!T1</f>
         <v/>
       </c>
-      <c r="U1" s="340" t="n"/>
-      <c r="V1" s="340" t="n"/>
+      <c r="U1" s="330" t="n"/>
+      <c r="V1" s="330" t="n"/>
       <c r="W1" s="255" t="inlineStr">
         <is>
           <t>年</t>
@@ -8955,41 +8965,41 @@
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="290" t="n"/>
-      <c r="C2" s="290" t="n"/>
-      <c r="D2" s="290" t="n"/>
-      <c r="E2" s="290" t="n"/>
-      <c r="F2" s="291" t="n"/>
+      <c r="B2" s="293" t="n"/>
+      <c r="C2" s="293" t="n"/>
+      <c r="D2" s="293" t="n"/>
+      <c r="E2" s="293" t="n"/>
+      <c r="F2" s="294" t="n"/>
       <c r="G2" s="251" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="290" t="n"/>
-      <c r="I2" s="290" t="n"/>
-      <c r="J2" s="290" t="n"/>
-      <c r="K2" s="290" t="n"/>
-      <c r="L2" s="291" t="n"/>
+      <c r="H2" s="293" t="n"/>
+      <c r="I2" s="293" t="n"/>
+      <c r="J2" s="293" t="n"/>
+      <c r="K2" s="293" t="n"/>
+      <c r="L2" s="294" t="n"/>
       <c r="M2" s="251" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="290" t="n"/>
-      <c r="O2" s="290" t="n"/>
-      <c r="P2" s="290" t="n"/>
-      <c r="Q2" s="290" t="n"/>
-      <c r="R2" s="291" t="n"/>
+      <c r="N2" s="293" t="n"/>
+      <c r="O2" s="293" t="n"/>
+      <c r="P2" s="293" t="n"/>
+      <c r="Q2" s="293" t="n"/>
+      <c r="R2" s="294" t="n"/>
       <c r="S2" s="251" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="290" t="n"/>
-      <c r="U2" s="290" t="n"/>
-      <c r="V2" s="290" t="n"/>
-      <c r="W2" s="290" t="n"/>
-      <c r="X2" s="291" t="n"/>
+      <c r="T2" s="293" t="n"/>
+      <c r="U2" s="293" t="n"/>
+      <c r="V2" s="293" t="n"/>
+      <c r="W2" s="293" t="n"/>
+      <c r="X2" s="294" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="251" t="inlineStr">
@@ -9007,8 +9017,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="290" t="n"/>
-      <c r="E3" s="291" t="n"/>
+      <c r="D3" s="293" t="n"/>
+      <c r="E3" s="294" t="n"/>
       <c r="F3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9029,8 +9039,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="290" t="n"/>
-      <c r="K3" s="291" t="n"/>
+      <c r="J3" s="293" t="n"/>
+      <c r="K3" s="294" t="n"/>
       <c r="L3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9051,8 +9061,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="290" t="n"/>
-      <c r="Q3" s="291" t="n"/>
+      <c r="P3" s="293" t="n"/>
+      <c r="Q3" s="294" t="n"/>
       <c r="R3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9073,8 +9083,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="290" t="n"/>
-      <c r="W3" s="291" t="n"/>
+      <c r="V3" s="293" t="n"/>
+      <c r="W3" s="294" t="n"/>
       <c r="X3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9082,7 +9092,7 @@
       </c>
     </row>
     <row r="4" ht="20.45" customHeight="1" s="257">
-      <c r="A4" s="371">
+      <c r="A4" s="361">
         <f>日程表１!A4</f>
         <v/>
       </c>
@@ -9090,15 +9100,15 @@
         <f>日程表１!B4</f>
         <v/>
       </c>
-      <c r="C4" s="345" t="n"/>
+      <c r="C4" s="335" t="n"/>
       <c r="D4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="346" t="n"/>
-      <c r="F4" s="372" t="n"/>
-      <c r="G4" s="371">
+      <c r="E4" s="336" t="n"/>
+      <c r="F4" s="362" t="n"/>
+      <c r="G4" s="361">
         <f>日程表１!G4</f>
         <v/>
       </c>
@@ -9106,15 +9116,15 @@
         <f>日程表１!H4</f>
         <v/>
       </c>
-      <c r="I4" s="345" t="n"/>
+      <c r="I4" s="335" t="n"/>
       <c r="J4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="346" t="n"/>
-      <c r="L4" s="372" t="n"/>
-      <c r="M4" s="371">
+      <c r="K4" s="336" t="n"/>
+      <c r="L4" s="362" t="n"/>
+      <c r="M4" s="361">
         <f>日程表１!M4</f>
         <v/>
       </c>
@@ -9122,7 +9132,7 @@
         <f>日程表１!N4</f>
         <v/>
       </c>
-      <c r="O4" s="345">
+      <c r="O4" s="335">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -9131,15 +9141,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="346">
+      <c r="Q4" s="336">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="372">
+      <c r="R4" s="362">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="371">
+      <c r="S4" s="361">
         <f>日程表１!S5</f>
         <v/>
       </c>
@@ -9147,17 +9157,17 @@
         <f>日程表１!T5</f>
         <v/>
       </c>
-      <c r="U4" s="345" t="n"/>
+      <c r="U4" s="335" t="n"/>
       <c r="V4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="373" t="n"/>
-      <c r="X4" s="374" t="n"/>
+      <c r="W4" s="363" t="n"/>
+      <c r="X4" s="364" t="n"/>
     </row>
     <row r="5" ht="20.45" customHeight="1" s="257">
-      <c r="A5" s="371">
+      <c r="A5" s="361">
         <f>日程表１!A5</f>
         <v/>
       </c>
@@ -9165,15 +9175,15 @@
         <f>日程表１!B5</f>
         <v/>
       </c>
-      <c r="C5" s="348" t="n"/>
+      <c r="C5" s="338" t="n"/>
       <c r="D5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="349" t="n"/>
-      <c r="F5" s="372" t="n"/>
-      <c r="G5" s="371">
+      <c r="E5" s="339" t="n"/>
+      <c r="F5" s="362" t="n"/>
+      <c r="G5" s="361">
         <f>日程表１!G5</f>
         <v/>
       </c>
@@ -9181,7 +9191,7 @@
         <f>日程表１!H5</f>
         <v/>
       </c>
-      <c r="I5" s="348">
+      <c r="I5" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -9190,40 +9200,40 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="349">
+      <c r="K5" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="372">
+      <c r="L5" s="362">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="375">
+      <c r="M5" s="365">
         <f>日程表１!M5</f>
         <v/>
       </c>
-      <c r="N5" s="376">
+      <c r="N5" s="366">
         <f>日程表１!N5</f>
         <v/>
       </c>
-      <c r="O5" s="353">
+      <c r="O5" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="377" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="355">
+      <c r="P5" s="367" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="345">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="378">
+      <c r="R5" s="368">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="371">
+      <c r="S5" s="361">
         <f>日程表１!S6</f>
         <v/>
       </c>
@@ -9231,17 +9241,17 @@
         <f>日程表１!T6</f>
         <v/>
       </c>
-      <c r="U5" s="348" t="n"/>
+      <c r="U5" s="338" t="n"/>
       <c r="V5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="379" t="n"/>
-      <c r="X5" s="374" t="n"/>
+      <c r="W5" s="369" t="n"/>
+      <c r="X5" s="364" t="n"/>
     </row>
     <row r="6" ht="20.45" customHeight="1" s="257">
-      <c r="A6" s="371">
+      <c r="A6" s="361">
         <f>日程表１!A6</f>
         <v/>
       </c>
@@ -9249,40 +9259,40 @@
         <f>日程表１!B6</f>
         <v/>
       </c>
-      <c r="C6" s="348" t="n"/>
+      <c r="C6" s="338" t="n"/>
       <c r="D6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="349" t="n"/>
-      <c r="F6" s="372" t="n"/>
-      <c r="G6" s="375">
+      <c r="E6" s="339" t="n"/>
+      <c r="F6" s="362" t="n"/>
+      <c r="G6" s="365">
         <f>日程表１!G6</f>
         <v/>
       </c>
-      <c r="H6" s="376">
+      <c r="H6" s="366">
         <f>日程表１!H6</f>
         <v/>
       </c>
-      <c r="I6" s="353">
+      <c r="I6" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="377" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="355">
+      <c r="J6" s="367" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="345">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="378">
+      <c r="L6" s="368">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="371">
+      <c r="M6" s="361">
         <f>日程表１!M6</f>
         <v/>
       </c>
@@ -9290,15 +9300,15 @@
         <f>日程表１!N6</f>
         <v/>
       </c>
-      <c r="O6" s="348" t="n"/>
+      <c r="O6" s="338" t="n"/>
       <c r="P6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="349" t="n"/>
-      <c r="R6" s="372" t="n"/>
-      <c r="S6" s="371">
+      <c r="Q6" s="339" t="n"/>
+      <c r="R6" s="362" t="n"/>
+      <c r="S6" s="361">
         <f>日程表１!S7</f>
         <v/>
       </c>
@@ -9306,17 +9316,17 @@
         <f>日程表１!T7</f>
         <v/>
       </c>
-      <c r="U6" s="348" t="n"/>
+      <c r="U6" s="338" t="n"/>
       <c r="V6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="379" t="n"/>
-      <c r="X6" s="374" t="n"/>
+      <c r="W6" s="369" t="n"/>
+      <c r="X6" s="364" t="n"/>
     </row>
     <row r="7" ht="20.45" customHeight="1" s="257">
-      <c r="A7" s="371">
+      <c r="A7" s="361">
         <f>日程表１!A7</f>
         <v/>
       </c>
@@ -9324,15 +9334,15 @@
         <f>日程表１!B7</f>
         <v/>
       </c>
-      <c r="C7" s="348" t="n"/>
+      <c r="C7" s="338" t="n"/>
       <c r="D7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="349" t="n"/>
-      <c r="F7" s="372" t="n"/>
-      <c r="G7" s="371">
+      <c r="E7" s="339" t="n"/>
+      <c r="F7" s="362" t="n"/>
+      <c r="G7" s="361">
         <f>日程表１!G7</f>
         <v/>
       </c>
@@ -9340,7 +9350,7 @@
         <f>日程表１!H7</f>
         <v/>
       </c>
-      <c r="I7" s="348">
+      <c r="I7" s="338">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9349,15 +9359,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="349">
+      <c r="K7" s="339">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="372">
+      <c r="L7" s="362">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="371">
+      <c r="M7" s="361">
         <f>日程表１!M7</f>
         <v/>
       </c>
@@ -9365,15 +9375,15 @@
         <f>日程表１!N7</f>
         <v/>
       </c>
-      <c r="O7" s="348" t="n"/>
+      <c r="O7" s="338" t="n"/>
       <c r="P7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="349" t="n"/>
-      <c r="R7" s="372" t="n"/>
-      <c r="S7" s="371">
+      <c r="Q7" s="339" t="n"/>
+      <c r="R7" s="362" t="n"/>
+      <c r="S7" s="361">
         <f>日程表１!S8</f>
         <v/>
       </c>
@@ -9381,17 +9391,17 @@
         <f>日程表１!T8</f>
         <v/>
       </c>
-      <c r="U7" s="348" t="n"/>
+      <c r="U7" s="338" t="n"/>
       <c r="V7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="379" t="n"/>
-      <c r="X7" s="374" t="n"/>
+      <c r="W7" s="369" t="n"/>
+      <c r="X7" s="364" t="n"/>
     </row>
     <row r="8" ht="20.45" customHeight="1" s="257">
-      <c r="A8" s="371">
+      <c r="A8" s="361">
         <f>日程表１!A8</f>
         <v/>
       </c>
@@ -9399,15 +9409,15 @@
         <f>日程表１!B8</f>
         <v/>
       </c>
-      <c r="C8" s="348" t="n"/>
+      <c r="C8" s="338" t="n"/>
       <c r="D8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="349" t="n"/>
-      <c r="F8" s="372" t="n"/>
-      <c r="G8" s="371">
+      <c r="E8" s="339" t="n"/>
+      <c r="F8" s="362" t="n"/>
+      <c r="G8" s="361">
         <f>日程表１!G8</f>
         <v/>
       </c>
@@ -9415,15 +9425,15 @@
         <f>日程表１!H8</f>
         <v/>
       </c>
-      <c r="I8" s="348" t="n"/>
+      <c r="I8" s="338" t="n"/>
       <c r="J8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="349" t="n"/>
-      <c r="L8" s="372" t="n"/>
-      <c r="M8" s="371">
+      <c r="K8" s="339" t="n"/>
+      <c r="L8" s="362" t="n"/>
+      <c r="M8" s="361">
         <f>日程表１!M8</f>
         <v/>
       </c>
@@ -9431,15 +9441,15 @@
         <f>日程表１!N8</f>
         <v/>
       </c>
-      <c r="O8" s="348" t="n"/>
+      <c r="O8" s="338" t="n"/>
       <c r="P8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="349" t="n"/>
-      <c r="R8" s="372" t="n"/>
-      <c r="S8" s="371">
+      <c r="Q8" s="339" t="n"/>
+      <c r="R8" s="362" t="n"/>
+      <c r="S8" s="361">
         <f>日程表１!S9</f>
         <v/>
       </c>
@@ -9447,17 +9457,17 @@
         <f>日程表１!T9</f>
         <v/>
       </c>
-      <c r="U8" s="348" t="n"/>
+      <c r="U8" s="338" t="n"/>
       <c r="V8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="379" t="n"/>
-      <c r="X8" s="374" t="n"/>
+      <c r="W8" s="369" t="n"/>
+      <c r="X8" s="364" t="n"/>
     </row>
     <row r="9" ht="20.45" customHeight="1" s="257">
-      <c r="A9" s="371">
+      <c r="A9" s="361">
         <f>日程表１!A9</f>
         <v/>
       </c>
@@ -9465,15 +9475,15 @@
         <f>日程表１!B9</f>
         <v/>
       </c>
-      <c r="C9" s="348" t="n"/>
+      <c r="C9" s="338" t="n"/>
       <c r="D9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="349" t="n"/>
-      <c r="F9" s="372" t="n"/>
-      <c r="G9" s="371">
+      <c r="E9" s="339" t="n"/>
+      <c r="F9" s="362" t="n"/>
+      <c r="G9" s="361">
         <f>日程表１!G9</f>
         <v/>
       </c>
@@ -9481,15 +9491,15 @@
         <f>日程表１!H9</f>
         <v/>
       </c>
-      <c r="I9" s="348" t="n"/>
+      <c r="I9" s="338" t="n"/>
       <c r="J9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="349" t="n"/>
-      <c r="L9" s="372" t="n"/>
-      <c r="M9" s="371">
+      <c r="K9" s="339" t="n"/>
+      <c r="L9" s="362" t="n"/>
+      <c r="M9" s="361">
         <f>日程表１!M9</f>
         <v/>
       </c>
@@ -9497,15 +9507,15 @@
         <f>日程表１!N9</f>
         <v/>
       </c>
-      <c r="O9" s="348" t="n"/>
+      <c r="O9" s="338" t="n"/>
       <c r="P9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="349" t="n"/>
-      <c r="R9" s="372" t="n"/>
-      <c r="S9" s="371">
+      <c r="Q9" s="339" t="n"/>
+      <c r="R9" s="362" t="n"/>
+      <c r="S9" s="361">
         <f>日程表１!S10</f>
         <v/>
       </c>
@@ -9513,17 +9523,17 @@
         <f>日程表１!T10</f>
         <v/>
       </c>
-      <c r="U9" s="348" t="n"/>
+      <c r="U9" s="338" t="n"/>
       <c r="V9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="379" t="n"/>
-      <c r="X9" s="374" t="n"/>
+      <c r="W9" s="369" t="n"/>
+      <c r="X9" s="364" t="n"/>
     </row>
     <row r="10" ht="20.45" customHeight="1" s="257">
-      <c r="A10" s="371">
+      <c r="A10" s="361">
         <f>日程表１!A10</f>
         <v/>
       </c>
@@ -9531,15 +9541,15 @@
         <f>日程表１!B10</f>
         <v/>
       </c>
-      <c r="C10" s="348" t="n"/>
+      <c r="C10" s="338" t="n"/>
       <c r="D10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="349" t="n"/>
-      <c r="F10" s="372" t="n"/>
-      <c r="G10" s="371">
+      <c r="E10" s="339" t="n"/>
+      <c r="F10" s="362" t="n"/>
+      <c r="G10" s="361">
         <f>日程表１!G10</f>
         <v/>
       </c>
@@ -9547,15 +9557,15 @@
         <f>日程表１!H10</f>
         <v/>
       </c>
-      <c r="I10" s="348" t="n"/>
+      <c r="I10" s="338" t="n"/>
       <c r="J10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="349" t="n"/>
-      <c r="L10" s="372" t="n"/>
-      <c r="M10" s="371">
+      <c r="K10" s="339" t="n"/>
+      <c r="L10" s="362" t="n"/>
+      <c r="M10" s="361">
         <f>日程表１!M10</f>
         <v/>
       </c>
@@ -9563,15 +9573,15 @@
         <f>日程表１!N10</f>
         <v/>
       </c>
-      <c r="O10" s="348" t="n"/>
+      <c r="O10" s="338" t="n"/>
       <c r="P10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="349" t="n"/>
-      <c r="R10" s="372" t="n"/>
-      <c r="S10" s="371">
+      <c r="Q10" s="339" t="n"/>
+      <c r="R10" s="362" t="n"/>
+      <c r="S10" s="361">
         <f>日程表１!S11</f>
         <v/>
       </c>
@@ -9579,17 +9589,17 @@
         <f>日程表１!T11</f>
         <v/>
       </c>
-      <c r="U10" s="348" t="n"/>
+      <c r="U10" s="338" t="n"/>
       <c r="V10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="379" t="n"/>
-      <c r="X10" s="374" t="n"/>
+      <c r="W10" s="369" t="n"/>
+      <c r="X10" s="364" t="n"/>
     </row>
     <row r="11" ht="20.45" customHeight="1" s="257">
-      <c r="A11" s="371">
+      <c r="A11" s="361">
         <f>日程表１!A11</f>
         <v/>
       </c>
@@ -9597,15 +9607,15 @@
         <f>日程表１!B11</f>
         <v/>
       </c>
-      <c r="C11" s="348" t="n"/>
+      <c r="C11" s="338" t="n"/>
       <c r="D11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="349" t="n"/>
-      <c r="F11" s="372" t="n"/>
-      <c r="G11" s="371">
+      <c r="E11" s="339" t="n"/>
+      <c r="F11" s="362" t="n"/>
+      <c r="G11" s="361">
         <f>日程表１!G11</f>
         <v/>
       </c>
@@ -9613,15 +9623,15 @@
         <f>日程表１!H11</f>
         <v/>
       </c>
-      <c r="I11" s="348" t="n"/>
+      <c r="I11" s="338" t="n"/>
       <c r="J11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="349" t="n"/>
-      <c r="L11" s="372" t="n"/>
-      <c r="M11" s="371">
+      <c r="K11" s="339" t="n"/>
+      <c r="L11" s="362" t="n"/>
+      <c r="M11" s="361">
         <f>日程表１!M11</f>
         <v/>
       </c>
@@ -9629,15 +9639,15 @@
         <f>日程表１!N11</f>
         <v/>
       </c>
-      <c r="O11" s="348" t="n"/>
+      <c r="O11" s="338" t="n"/>
       <c r="P11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="349" t="n"/>
-      <c r="R11" s="372" t="n"/>
-      <c r="S11" s="371">
+      <c r="Q11" s="339" t="n"/>
+      <c r="R11" s="362" t="n"/>
+      <c r="S11" s="361">
         <f>日程表１!S12</f>
         <v/>
       </c>
@@ -9645,17 +9655,17 @@
         <f>日程表１!T12</f>
         <v/>
       </c>
-      <c r="U11" s="348" t="n"/>
+      <c r="U11" s="338" t="n"/>
       <c r="V11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="379" t="n"/>
-      <c r="X11" s="374" t="n"/>
+      <c r="W11" s="369" t="n"/>
+      <c r="X11" s="364" t="n"/>
     </row>
     <row r="12" ht="20.45" customHeight="1" s="257">
-      <c r="A12" s="371">
+      <c r="A12" s="361">
         <f>日程表１!A12</f>
         <v/>
       </c>
@@ -9663,40 +9673,40 @@
         <f>日程表１!B12</f>
         <v/>
       </c>
-      <c r="C12" s="348" t="n"/>
+      <c r="C12" s="338" t="n"/>
       <c r="D12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="349" t="n"/>
-      <c r="F12" s="372" t="n"/>
-      <c r="G12" s="375">
+      <c r="E12" s="339" t="n"/>
+      <c r="F12" s="362" t="n"/>
+      <c r="G12" s="365">
         <f>日程表１!G12</f>
         <v/>
       </c>
-      <c r="H12" s="376">
+      <c r="H12" s="366">
         <f>日程表１!H12</f>
         <v/>
       </c>
-      <c r="I12" s="353">
+      <c r="I12" s="343">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="377" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="355">
+      <c r="J12" s="367" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="345">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="378">
+      <c r="L12" s="368">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="371">
+      <c r="M12" s="361">
         <f>日程表１!M12</f>
         <v/>
       </c>
@@ -9704,15 +9714,15 @@
         <f>日程表１!N12</f>
         <v/>
       </c>
-      <c r="O12" s="348" t="n"/>
+      <c r="O12" s="338" t="n"/>
       <c r="P12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="349" t="n"/>
-      <c r="R12" s="372" t="n"/>
-      <c r="S12" s="371">
+      <c r="Q12" s="339" t="n"/>
+      <c r="R12" s="362" t="n"/>
+      <c r="S12" s="361">
         <f>日程表１!S13</f>
         <v/>
       </c>
@@ -9720,17 +9730,17 @@
         <f>日程表１!T13</f>
         <v/>
       </c>
-      <c r="U12" s="348" t="n"/>
+      <c r="U12" s="338" t="n"/>
       <c r="V12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="379" t="n"/>
-      <c r="X12" s="374" t="n"/>
+      <c r="W12" s="369" t="n"/>
+      <c r="X12" s="364" t="n"/>
     </row>
     <row r="13" ht="20.45" customHeight="1" s="257">
-      <c r="A13" s="371">
+      <c r="A13" s="361">
         <f>日程表１!A13</f>
         <v/>
       </c>
@@ -9738,15 +9748,15 @@
         <f>日程表１!B13</f>
         <v/>
       </c>
-      <c r="C13" s="348" t="n"/>
+      <c r="C13" s="338" t="n"/>
       <c r="D13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="349" t="n"/>
-      <c r="F13" s="372" t="n"/>
-      <c r="G13" s="371">
+      <c r="E13" s="339" t="n"/>
+      <c r="F13" s="362" t="n"/>
+      <c r="G13" s="361">
         <f>日程表１!G13</f>
         <v/>
       </c>
@@ -9754,7 +9764,7 @@
         <f>日程表１!H13</f>
         <v/>
       </c>
-      <c r="I13" s="348">
+      <c r="I13" s="338">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -9763,15 +9773,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="349">
+      <c r="K13" s="339">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="372">
+      <c r="L13" s="362">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="371">
+      <c r="M13" s="361">
         <f>日程表１!M13</f>
         <v/>
       </c>
@@ -9779,15 +9789,15 @@
         <f>日程表１!N13</f>
         <v/>
       </c>
-      <c r="O13" s="348" t="n"/>
+      <c r="O13" s="338" t="n"/>
       <c r="P13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="349" t="n"/>
-      <c r="R13" s="372" t="n"/>
-      <c r="S13" s="371" t="n">
+      <c r="Q13" s="339" t="n"/>
+      <c r="R13" s="362" t="n"/>
+      <c r="S13" s="361" t="n">
         <v>10</v>
       </c>
       <c r="T13" s="29" t="inlineStr">
@@ -9795,17 +9805,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U13" s="348" t="n"/>
+      <c r="U13" s="338" t="n"/>
       <c r="V13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="379" t="n"/>
-      <c r="X13" s="374" t="n"/>
+      <c r="W13" s="369" t="n"/>
+      <c r="X13" s="364" t="n"/>
     </row>
     <row r="14" ht="20.45" customHeight="1" s="257">
-      <c r="A14" s="371">
+      <c r="A14" s="361">
         <f>日程表１!A14</f>
         <v/>
       </c>
@@ -9813,15 +9823,15 @@
         <f>日程表１!B14</f>
         <v/>
       </c>
-      <c r="C14" s="348" t="n"/>
+      <c r="C14" s="338" t="n"/>
       <c r="D14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="349" t="n"/>
-      <c r="F14" s="372" t="n"/>
-      <c r="G14" s="371">
+      <c r="E14" s="339" t="n"/>
+      <c r="F14" s="362" t="n"/>
+      <c r="G14" s="361">
         <f>日程表１!G14</f>
         <v/>
       </c>
@@ -9829,7 +9839,7 @@
         <f>日程表１!H14</f>
         <v/>
       </c>
-      <c r="I14" s="348">
+      <c r="I14" s="338">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9838,15 +9848,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="349">
+      <c r="K14" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="372">
+      <c r="L14" s="362">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="371">
+      <c r="M14" s="361">
         <f>日程表１!M14</f>
         <v/>
       </c>
@@ -9854,23 +9864,23 @@
         <f>日程表１!N14</f>
         <v/>
       </c>
-      <c r="O14" s="348" t="n"/>
+      <c r="O14" s="338" t="n"/>
       <c r="P14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="349" t="n"/>
-      <c r="R14" s="372" t="n"/>
+      <c r="Q14" s="339" t="n"/>
+      <c r="R14" s="362" t="n"/>
       <c r="S14" s="256" t="n"/>
       <c r="T14" s="256" t="n"/>
-      <c r="U14" s="362" t="n"/>
+      <c r="U14" s="352" t="n"/>
       <c r="V14" s="255" t="n"/>
-      <c r="W14" s="363" t="n"/>
-      <c r="X14" s="363" t="n"/>
+      <c r="W14" s="353" t="n"/>
+      <c r="X14" s="353" t="n"/>
     </row>
     <row r="15" ht="20.45" customHeight="1" s="257">
-      <c r="A15" s="371">
+      <c r="A15" s="361">
         <f>日程表１!A15</f>
         <v/>
       </c>
@@ -9878,15 +9888,15 @@
         <f>日程表１!B15</f>
         <v/>
       </c>
-      <c r="C15" s="348" t="n"/>
+      <c r="C15" s="338" t="n"/>
       <c r="D15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="349" t="n"/>
-      <c r="F15" s="372" t="n"/>
-      <c r="G15" s="371">
+      <c r="E15" s="339" t="n"/>
+      <c r="F15" s="362" t="n"/>
+      <c r="G15" s="361">
         <f>日程表１!G15</f>
         <v/>
       </c>
@@ -9894,15 +9904,15 @@
         <f>日程表１!H15</f>
         <v/>
       </c>
-      <c r="I15" s="348" t="n"/>
+      <c r="I15" s="338" t="n"/>
       <c r="J15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="349" t="n"/>
-      <c r="L15" s="372" t="n"/>
-      <c r="M15" s="371">
+      <c r="K15" s="339" t="n"/>
+      <c r="L15" s="362" t="n"/>
+      <c r="M15" s="361">
         <f>日程表１!M15</f>
         <v/>
       </c>
@@ -9910,23 +9920,23 @@
         <f>日程表１!N15</f>
         <v/>
       </c>
-      <c r="O15" s="348" t="n"/>
+      <c r="O15" s="338" t="n"/>
       <c r="P15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="349" t="n"/>
-      <c r="R15" s="372" t="n"/>
+      <c r="Q15" s="339" t="n"/>
+      <c r="R15" s="362" t="n"/>
       <c r="S15" s="256" t="n"/>
       <c r="T15" s="256" t="n"/>
-      <c r="U15" s="362" t="n"/>
+      <c r="U15" s="352" t="n"/>
       <c r="V15" s="255" t="n"/>
-      <c r="W15" s="363" t="n"/>
-      <c r="X15" s="363" t="n"/>
+      <c r="W15" s="353" t="n"/>
+      <c r="X15" s="353" t="n"/>
     </row>
     <row r="16" ht="20.45" customHeight="1" s="257">
-      <c r="A16" s="371">
+      <c r="A16" s="361">
         <f>日程表１!A16</f>
         <v/>
       </c>
@@ -9934,15 +9944,15 @@
         <f>日程表１!B16</f>
         <v/>
       </c>
-      <c r="C16" s="348" t="n"/>
+      <c r="C16" s="338" t="n"/>
       <c r="D16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="349" t="n"/>
-      <c r="F16" s="372" t="n"/>
-      <c r="G16" s="371">
+      <c r="E16" s="339" t="n"/>
+      <c r="F16" s="362" t="n"/>
+      <c r="G16" s="361">
         <f>日程表１!G16</f>
         <v/>
       </c>
@@ -9950,15 +9960,15 @@
         <f>日程表１!H16</f>
         <v/>
       </c>
-      <c r="I16" s="348" t="n"/>
+      <c r="I16" s="338" t="n"/>
       <c r="J16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="349" t="n"/>
-      <c r="L16" s="372" t="n"/>
-      <c r="M16" s="371">
+      <c r="K16" s="339" t="n"/>
+      <c r="L16" s="362" t="n"/>
+      <c r="M16" s="361">
         <f>日程表１!M16</f>
         <v/>
       </c>
@@ -9966,23 +9976,23 @@
         <f>日程表１!N16</f>
         <v/>
       </c>
-      <c r="O16" s="348" t="n"/>
+      <c r="O16" s="338" t="n"/>
       <c r="P16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="349" t="n"/>
-      <c r="R16" s="372" t="n"/>
+      <c r="Q16" s="339" t="n"/>
+      <c r="R16" s="362" t="n"/>
       <c r="S16" s="256" t="n"/>
       <c r="T16" s="256" t="n"/>
-      <c r="U16" s="362" t="n"/>
+      <c r="U16" s="352" t="n"/>
       <c r="V16" s="255" t="n"/>
-      <c r="W16" s="363" t="n"/>
-      <c r="X16" s="363" t="n"/>
+      <c r="W16" s="353" t="n"/>
+      <c r="X16" s="353" t="n"/>
     </row>
     <row r="17" ht="20.45" customHeight="1" s="257">
-      <c r="A17" s="371">
+      <c r="A17" s="361">
         <f>日程表１!A17</f>
         <v/>
       </c>
@@ -9990,15 +10000,15 @@
         <f>日程表１!B17</f>
         <v/>
       </c>
-      <c r="C17" s="348" t="n"/>
+      <c r="C17" s="338" t="n"/>
       <c r="D17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="349" t="n"/>
-      <c r="F17" s="372" t="n"/>
-      <c r="G17" s="371">
+      <c r="E17" s="339" t="n"/>
+      <c r="F17" s="362" t="n"/>
+      <c r="G17" s="361">
         <f>日程表１!G17</f>
         <v/>
       </c>
@@ -10006,15 +10016,15 @@
         <f>日程表１!H17</f>
         <v/>
       </c>
-      <c r="I17" s="348" t="n"/>
+      <c r="I17" s="338" t="n"/>
       <c r="J17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="349" t="n"/>
-      <c r="L17" s="372" t="n"/>
-      <c r="M17" s="371">
+      <c r="K17" s="339" t="n"/>
+      <c r="L17" s="362" t="n"/>
+      <c r="M17" s="361">
         <f>日程表１!M17</f>
         <v/>
       </c>
@@ -10022,14 +10032,14 @@
         <f>日程表１!N17</f>
         <v/>
       </c>
-      <c r="O17" s="348" t="n"/>
+      <c r="O17" s="338" t="n"/>
       <c r="P17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="349" t="n"/>
-      <c r="R17" s="372" t="n"/>
+      <c r="Q17" s="339" t="n"/>
+      <c r="R17" s="362" t="n"/>
       <c r="S17" s="254" t="inlineStr">
         <is>
           <t>NO.</t>
@@ -10040,13 +10050,13 @@
           <t>team</t>
         </is>
       </c>
-      <c r="U17" s="290" t="n"/>
-      <c r="V17" s="290" t="n"/>
-      <c r="W17" s="290" t="n"/>
-      <c r="X17" s="291" t="n"/>
+      <c r="U17" s="293" t="n"/>
+      <c r="V17" s="293" t="n"/>
+      <c r="W17" s="293" t="n"/>
+      <c r="X17" s="294" t="n"/>
     </row>
     <row r="18" ht="20.45" customHeight="1" s="257">
-      <c r="A18" s="371">
+      <c r="A18" s="361">
         <f>日程表１!A18</f>
         <v/>
       </c>
@@ -10054,15 +10064,15 @@
         <f>日程表１!B18</f>
         <v/>
       </c>
-      <c r="C18" s="348" t="n"/>
+      <c r="C18" s="338" t="n"/>
       <c r="D18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="349" t="n"/>
-      <c r="F18" s="372" t="n"/>
-      <c r="G18" s="371">
+      <c r="E18" s="339" t="n"/>
+      <c r="F18" s="362" t="n"/>
+      <c r="G18" s="361">
         <f>日程表１!G18</f>
         <v/>
       </c>
@@ -10070,15 +10080,15 @@
         <f>日程表１!H18</f>
         <v/>
       </c>
-      <c r="I18" s="348" t="n"/>
+      <c r="I18" s="338" t="n"/>
       <c r="J18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="349" t="n"/>
-      <c r="L18" s="372" t="n"/>
-      <c r="M18" s="371">
+      <c r="K18" s="339" t="n"/>
+      <c r="L18" s="362" t="n"/>
+      <c r="M18" s="361">
         <f>日程表１!M18</f>
         <v/>
       </c>
@@ -10086,14 +10096,14 @@
         <f>日程表１!N18</f>
         <v/>
       </c>
-      <c r="O18" s="348" t="n"/>
+      <c r="O18" s="338" t="n"/>
       <c r="P18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="349" t="n"/>
-      <c r="R18" s="372" t="n"/>
+      <c r="Q18" s="339" t="n"/>
+      <c r="R18" s="362" t="n"/>
       <c r="S18" s="254" t="n">
         <v>1</v>
       </c>
@@ -10101,13 +10111,13 @@
         <f>リーグ勝敗表!AX6</f>
         <v/>
       </c>
-      <c r="U18" s="290" t="n"/>
-      <c r="V18" s="290" t="n"/>
-      <c r="W18" s="290" t="n"/>
-      <c r="X18" s="291" t="n"/>
+      <c r="U18" s="293" t="n"/>
+      <c r="V18" s="293" t="n"/>
+      <c r="W18" s="293" t="n"/>
+      <c r="X18" s="294" t="n"/>
     </row>
     <row r="19" ht="20.45" customHeight="1" s="257">
-      <c r="A19" s="371">
+      <c r="A19" s="361">
         <f>日程表１!A19</f>
         <v/>
       </c>
@@ -10115,15 +10125,15 @@
         <f>日程表１!B19</f>
         <v/>
       </c>
-      <c r="C19" s="348" t="n"/>
+      <c r="C19" s="338" t="n"/>
       <c r="D19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="349" t="n"/>
-      <c r="F19" s="372" t="n"/>
-      <c r="G19" s="371">
+      <c r="E19" s="339" t="n"/>
+      <c r="F19" s="362" t="n"/>
+      <c r="G19" s="361">
         <f>日程表１!G19</f>
         <v/>
       </c>
@@ -10131,15 +10141,15 @@
         <f>日程表１!H19</f>
         <v/>
       </c>
-      <c r="I19" s="348" t="inlineStr">
+      <c r="I19" s="338" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="253" t="n"/>
-      <c r="K19" s="349" t="n"/>
-      <c r="L19" s="372" t="n"/>
-      <c r="M19" s="371">
+      <c r="K19" s="339" t="n"/>
+      <c r="L19" s="362" t="n"/>
+      <c r="M19" s="361">
         <f>日程表１!M19</f>
         <v/>
       </c>
@@ -10147,14 +10157,14 @@
         <f>日程表１!N19</f>
         <v/>
       </c>
-      <c r="O19" s="348" t="n"/>
+      <c r="O19" s="338" t="n"/>
       <c r="P19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="349" t="n"/>
-      <c r="R19" s="372" t="n"/>
+      <c r="Q19" s="339" t="n"/>
+      <c r="R19" s="362" t="n"/>
       <c r="S19" s="254" t="n">
         <v>2</v>
       </c>
@@ -10162,13 +10172,13 @@
         <f>リーグ勝敗表!AX8</f>
         <v/>
       </c>
-      <c r="U19" s="290" t="n"/>
-      <c r="V19" s="290" t="n"/>
-      <c r="W19" s="290" t="n"/>
-      <c r="X19" s="291" t="n"/>
+      <c r="U19" s="293" t="n"/>
+      <c r="V19" s="293" t="n"/>
+      <c r="W19" s="293" t="n"/>
+      <c r="X19" s="294" t="n"/>
     </row>
     <row r="20" ht="20.45" customHeight="1" s="257">
-      <c r="A20" s="371">
+      <c r="A20" s="361">
         <f>日程表１!A20</f>
         <v/>
       </c>
@@ -10176,15 +10186,15 @@
         <f>日程表１!B20</f>
         <v/>
       </c>
-      <c r="C20" s="348" t="n"/>
+      <c r="C20" s="338" t="n"/>
       <c r="D20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="349" t="n"/>
-      <c r="F20" s="372" t="n"/>
-      <c r="G20" s="371">
+      <c r="E20" s="339" t="n"/>
+      <c r="F20" s="362" t="n"/>
+      <c r="G20" s="361">
         <f>日程表１!G20</f>
         <v/>
       </c>
@@ -10192,15 +10202,15 @@
         <f>日程表１!H20</f>
         <v/>
       </c>
-      <c r="I20" s="348" t="inlineStr">
+      <c r="I20" s="338" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="253" t="n"/>
-      <c r="K20" s="349" t="n"/>
-      <c r="L20" s="372" t="n"/>
-      <c r="M20" s="371">
+      <c r="K20" s="339" t="n"/>
+      <c r="L20" s="362" t="n"/>
+      <c r="M20" s="361">
         <f>日程表１!M20</f>
         <v/>
       </c>
@@ -10208,14 +10218,14 @@
         <f>日程表１!N20</f>
         <v/>
       </c>
-      <c r="O20" s="348" t="n"/>
+      <c r="O20" s="338" t="n"/>
       <c r="P20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="349" t="n"/>
-      <c r="R20" s="372" t="n"/>
+      <c r="Q20" s="339" t="n"/>
+      <c r="R20" s="362" t="n"/>
       <c r="S20" s="254" t="n">
         <v>3</v>
       </c>
@@ -10223,13 +10233,13 @@
         <f>リーグ勝敗表!AX10</f>
         <v/>
       </c>
-      <c r="U20" s="290" t="n"/>
-      <c r="V20" s="290" t="n"/>
-      <c r="W20" s="290" t="n"/>
-      <c r="X20" s="291" t="n"/>
+      <c r="U20" s="293" t="n"/>
+      <c r="V20" s="293" t="n"/>
+      <c r="W20" s="293" t="n"/>
+      <c r="X20" s="294" t="n"/>
     </row>
     <row r="21" ht="20.45" customHeight="1" s="257">
-      <c r="A21" s="371">
+      <c r="A21" s="361">
         <f>日程表１!A21</f>
         <v/>
       </c>
@@ -10237,15 +10247,15 @@
         <f>日程表１!B21</f>
         <v/>
       </c>
-      <c r="C21" s="348" t="n"/>
+      <c r="C21" s="338" t="n"/>
       <c r="D21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="349" t="n"/>
-      <c r="F21" s="372" t="n"/>
-      <c r="G21" s="371">
+      <c r="E21" s="339" t="n"/>
+      <c r="F21" s="362" t="n"/>
+      <c r="G21" s="361">
         <f>日程表１!G21</f>
         <v/>
       </c>
@@ -10253,15 +10263,15 @@
         <f>日程表１!H21</f>
         <v/>
       </c>
-      <c r="I21" s="348" t="inlineStr">
+      <c r="I21" s="338" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="253" t="n"/>
-      <c r="K21" s="349" t="n"/>
-      <c r="L21" s="372" t="n"/>
-      <c r="M21" s="371">
+      <c r="K21" s="339" t="n"/>
+      <c r="L21" s="362" t="n"/>
+      <c r="M21" s="361">
         <f>日程表１!M21</f>
         <v/>
       </c>
@@ -10269,14 +10279,14 @@
         <f>日程表１!N21</f>
         <v/>
       </c>
-      <c r="O21" s="348" t="n"/>
+      <c r="O21" s="338" t="n"/>
       <c r="P21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="349" t="n"/>
-      <c r="R21" s="372" t="n"/>
+      <c r="Q21" s="339" t="n"/>
+      <c r="R21" s="362" t="n"/>
       <c r="S21" s="254" t="n">
         <v>4</v>
       </c>
@@ -10284,13 +10294,13 @@
         <f>リーグ勝敗表!AX12</f>
         <v/>
       </c>
-      <c r="U21" s="290" t="n"/>
-      <c r="V21" s="290" t="n"/>
-      <c r="W21" s="290" t="n"/>
-      <c r="X21" s="291" t="n"/>
+      <c r="U21" s="293" t="n"/>
+      <c r="V21" s="293" t="n"/>
+      <c r="W21" s="293" t="n"/>
+      <c r="X21" s="294" t="n"/>
     </row>
     <row r="22" ht="20.45" customHeight="1" s="257">
-      <c r="A22" s="371">
+      <c r="A22" s="361">
         <f>日程表１!A22</f>
         <v/>
       </c>
@@ -10298,15 +10308,15 @@
         <f>日程表１!B22</f>
         <v/>
       </c>
-      <c r="C22" s="348" t="n"/>
+      <c r="C22" s="338" t="n"/>
       <c r="D22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="349" t="n"/>
-      <c r="F22" s="372" t="n"/>
-      <c r="G22" s="371">
+      <c r="E22" s="339" t="n"/>
+      <c r="F22" s="362" t="n"/>
+      <c r="G22" s="361">
         <f>日程表１!G22</f>
         <v/>
       </c>
@@ -10314,15 +10324,15 @@
         <f>日程表１!H22</f>
         <v/>
       </c>
-      <c r="I22" s="348" t="n"/>
+      <c r="I22" s="338" t="n"/>
       <c r="J22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K22" s="349" t="n"/>
-      <c r="L22" s="372" t="n"/>
-      <c r="M22" s="371">
+      <c r="K22" s="339" t="n"/>
+      <c r="L22" s="362" t="n"/>
+      <c r="M22" s="361">
         <f>日程表１!M22</f>
         <v/>
       </c>
@@ -10330,14 +10340,14 @@
         <f>日程表１!N22</f>
         <v/>
       </c>
-      <c r="O22" s="348" t="n"/>
+      <c r="O22" s="338" t="n"/>
       <c r="P22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="349" t="n"/>
-      <c r="R22" s="372" t="n"/>
+      <c r="Q22" s="339" t="n"/>
+      <c r="R22" s="362" t="n"/>
       <c r="S22" s="254" t="n">
         <v>5</v>
       </c>
@@ -10345,13 +10355,13 @@
         <f>リーグ勝敗表!AX14</f>
         <v/>
       </c>
-      <c r="U22" s="290" t="n"/>
-      <c r="V22" s="290" t="n"/>
-      <c r="W22" s="290" t="n"/>
-      <c r="X22" s="291" t="n"/>
+      <c r="U22" s="293" t="n"/>
+      <c r="V22" s="293" t="n"/>
+      <c r="W22" s="293" t="n"/>
+      <c r="X22" s="294" t="n"/>
     </row>
     <row r="23" ht="20.45" customHeight="1" s="257">
-      <c r="A23" s="371">
+      <c r="A23" s="361">
         <f>日程表１!A23</f>
         <v/>
       </c>
@@ -10359,15 +10369,15 @@
         <f>日程表１!B23</f>
         <v/>
       </c>
-      <c r="C23" s="348" t="n"/>
+      <c r="C23" s="338" t="n"/>
       <c r="D23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="349" t="n"/>
-      <c r="F23" s="372" t="n"/>
-      <c r="G23" s="371">
+      <c r="E23" s="339" t="n"/>
+      <c r="F23" s="362" t="n"/>
+      <c r="G23" s="361">
         <f>日程表１!G23</f>
         <v/>
       </c>
@@ -10375,15 +10385,15 @@
         <f>日程表１!H23</f>
         <v/>
       </c>
-      <c r="I23" s="348" t="n"/>
+      <c r="I23" s="338" t="n"/>
       <c r="J23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K23" s="349" t="n"/>
-      <c r="L23" s="372" t="n"/>
-      <c r="M23" s="371">
+      <c r="K23" s="339" t="n"/>
+      <c r="L23" s="362" t="n"/>
+      <c r="M23" s="361">
         <f>日程表１!M23</f>
         <v/>
       </c>
@@ -10391,14 +10401,14 @@
         <f>日程表１!N23</f>
         <v/>
       </c>
-      <c r="O23" s="348" t="n"/>
+      <c r="O23" s="338" t="n"/>
       <c r="P23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="349" t="n"/>
-      <c r="R23" s="372" t="n"/>
+      <c r="Q23" s="339" t="n"/>
+      <c r="R23" s="362" t="n"/>
       <c r="S23" s="254" t="n">
         <v>6</v>
       </c>
@@ -10406,13 +10416,13 @@
         <f>リーグ勝敗表!AX16</f>
         <v/>
       </c>
-      <c r="U23" s="290" t="n"/>
-      <c r="V23" s="290" t="n"/>
-      <c r="W23" s="290" t="n"/>
-      <c r="X23" s="291" t="n"/>
+      <c r="U23" s="293" t="n"/>
+      <c r="V23" s="293" t="n"/>
+      <c r="W23" s="293" t="n"/>
+      <c r="X23" s="294" t="n"/>
     </row>
     <row r="24" ht="20.45" customHeight="1" s="257">
-      <c r="A24" s="371">
+      <c r="A24" s="361">
         <f>日程表１!A24</f>
         <v/>
       </c>
@@ -10420,15 +10430,15 @@
         <f>日程表１!B24</f>
         <v/>
       </c>
-      <c r="C24" s="348" t="n"/>
+      <c r="C24" s="338" t="n"/>
       <c r="D24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="349" t="n"/>
-      <c r="F24" s="372" t="n"/>
-      <c r="G24" s="371">
+      <c r="E24" s="339" t="n"/>
+      <c r="F24" s="362" t="n"/>
+      <c r="G24" s="361">
         <f>日程表１!G24</f>
         <v/>
       </c>
@@ -10436,15 +10446,15 @@
         <f>日程表１!H24</f>
         <v/>
       </c>
-      <c r="I24" s="348" t="n"/>
+      <c r="I24" s="338" t="n"/>
       <c r="J24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K24" s="349" t="n"/>
-      <c r="L24" s="372" t="n"/>
-      <c r="M24" s="371">
+      <c r="K24" s="339" t="n"/>
+      <c r="L24" s="362" t="n"/>
+      <c r="M24" s="361">
         <f>日程表１!M24</f>
         <v/>
       </c>
@@ -10452,14 +10462,14 @@
         <f>日程表１!N24</f>
         <v/>
       </c>
-      <c r="O24" s="348" t="n"/>
+      <c r="O24" s="338" t="n"/>
       <c r="P24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="349" t="n"/>
-      <c r="R24" s="372" t="n"/>
+      <c r="Q24" s="339" t="n"/>
+      <c r="R24" s="362" t="n"/>
       <c r="S24" s="254" t="n">
         <v>7</v>
       </c>
@@ -10467,13 +10477,13 @@
         <f>リーグ勝敗表!AX18</f>
         <v/>
       </c>
-      <c r="U24" s="290" t="n"/>
-      <c r="V24" s="290" t="n"/>
-      <c r="W24" s="290" t="n"/>
-      <c r="X24" s="291" t="n"/>
+      <c r="U24" s="293" t="n"/>
+      <c r="V24" s="293" t="n"/>
+      <c r="W24" s="293" t="n"/>
+      <c r="X24" s="294" t="n"/>
     </row>
     <row r="25" ht="20.45" customHeight="1" s="257">
-      <c r="A25" s="371">
+      <c r="A25" s="361">
         <f>日程表１!A25</f>
         <v/>
       </c>
@@ -10481,15 +10491,15 @@
         <f>日程表１!B25</f>
         <v/>
       </c>
-      <c r="C25" s="348" t="n"/>
+      <c r="C25" s="338" t="n"/>
       <c r="D25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="349" t="n"/>
-      <c r="F25" s="372" t="n"/>
-      <c r="G25" s="371">
+      <c r="E25" s="339" t="n"/>
+      <c r="F25" s="362" t="n"/>
+      <c r="G25" s="361">
         <f>日程表１!G25</f>
         <v/>
       </c>
@@ -10497,15 +10507,15 @@
         <f>日程表１!H25</f>
         <v/>
       </c>
-      <c r="I25" s="348" t="n"/>
+      <c r="I25" s="338" t="n"/>
       <c r="J25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K25" s="349" t="n"/>
-      <c r="L25" s="372" t="n"/>
-      <c r="M25" s="371">
+      <c r="K25" s="339" t="n"/>
+      <c r="L25" s="362" t="n"/>
+      <c r="M25" s="361">
         <f>日程表１!M25</f>
         <v/>
       </c>
@@ -10513,14 +10523,14 @@
         <f>日程表１!N25</f>
         <v/>
       </c>
-      <c r="O25" s="348" t="n"/>
+      <c r="O25" s="338" t="n"/>
       <c r="P25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="349" t="n"/>
-      <c r="R25" s="372" t="n"/>
+      <c r="Q25" s="339" t="n"/>
+      <c r="R25" s="362" t="n"/>
       <c r="S25" s="254" t="n">
         <v>8</v>
       </c>
@@ -10528,13 +10538,13 @@
         <f>リーグ勝敗表!AX20</f>
         <v/>
       </c>
-      <c r="U25" s="290" t="n"/>
-      <c r="V25" s="290" t="n"/>
-      <c r="W25" s="290" t="n"/>
-      <c r="X25" s="291" t="n"/>
+      <c r="U25" s="293" t="n"/>
+      <c r="V25" s="293" t="n"/>
+      <c r="W25" s="293" t="n"/>
+      <c r="X25" s="294" t="n"/>
     </row>
     <row r="26" ht="20.45" customHeight="1" s="257">
-      <c r="A26" s="371">
+      <c r="A26" s="361">
         <f>日程表１!A26</f>
         <v/>
       </c>
@@ -10542,40 +10552,40 @@
         <f>日程表１!B26</f>
         <v/>
       </c>
-      <c r="C26" s="348" t="n"/>
+      <c r="C26" s="338" t="n"/>
       <c r="D26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="349" t="n"/>
-      <c r="F26" s="372" t="n"/>
-      <c r="G26" s="375">
+      <c r="E26" s="339" t="n"/>
+      <c r="F26" s="362" t="n"/>
+      <c r="G26" s="365">
         <f>日程表１!G26</f>
         <v/>
       </c>
-      <c r="H26" s="376">
+      <c r="H26" s="366">
         <f>日程表１!H26</f>
         <v/>
       </c>
-      <c r="I26" s="353">
+      <c r="I26" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="377" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K26" s="355">
+      <c r="J26" s="367" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K26" s="345">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="378">
+      <c r="L26" s="368">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="371">
+      <c r="M26" s="361">
         <f>日程表１!M26</f>
         <v/>
       </c>
@@ -10583,14 +10593,14 @@
         <f>日程表１!N26</f>
         <v/>
       </c>
-      <c r="O26" s="348" t="n"/>
+      <c r="O26" s="338" t="n"/>
       <c r="P26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="349" t="n"/>
-      <c r="R26" s="372" t="n"/>
+      <c r="Q26" s="339" t="n"/>
+      <c r="R26" s="362" t="n"/>
       <c r="S26" s="254" t="n">
         <v>9</v>
       </c>
@@ -10598,13 +10608,13 @@
         <f>リーグ勝敗表!AX22</f>
         <v/>
       </c>
-      <c r="U26" s="290" t="n"/>
-      <c r="V26" s="290" t="n"/>
-      <c r="W26" s="290" t="n"/>
-      <c r="X26" s="291" t="n"/>
+      <c r="U26" s="293" t="n"/>
+      <c r="V26" s="293" t="n"/>
+      <c r="W26" s="293" t="n"/>
+      <c r="X26" s="294" t="n"/>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="257">
-      <c r="A27" s="371">
+      <c r="A27" s="361">
         <f>日程表１!A27</f>
         <v/>
       </c>
@@ -10612,15 +10622,15 @@
         <f>日程表１!B27</f>
         <v/>
       </c>
-      <c r="C27" s="348" t="n"/>
+      <c r="C27" s="338" t="n"/>
       <c r="D27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="349" t="n"/>
-      <c r="F27" s="372" t="n"/>
-      <c r="G27" s="371">
+      <c r="E27" s="339" t="n"/>
+      <c r="F27" s="362" t="n"/>
+      <c r="G27" s="361">
         <f>日程表１!G27</f>
         <v/>
       </c>
@@ -10628,7 +10638,7 @@
         <f>日程表１!H27</f>
         <v/>
       </c>
-      <c r="I27" s="348">
+      <c r="I27" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10637,15 +10647,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K27" s="349">
+      <c r="K27" s="339">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="372">
+      <c r="L27" s="362">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="371">
+      <c r="M27" s="361">
         <f>日程表１!M27</f>
         <v/>
       </c>
@@ -10653,14 +10663,14 @@
         <f>日程表１!N27</f>
         <v/>
       </c>
-      <c r="O27" s="348" t="n"/>
+      <c r="O27" s="338" t="n"/>
       <c r="P27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="349" t="n"/>
-      <c r="R27" s="372" t="n"/>
+      <c r="Q27" s="339" t="n"/>
+      <c r="R27" s="362" t="n"/>
       <c r="S27" s="254" t="n">
         <v>10</v>
       </c>
@@ -10668,13 +10678,13 @@
         <f>リーグ勝敗表!AX24</f>
         <v/>
       </c>
-      <c r="U27" s="290" t="n"/>
-      <c r="V27" s="290" t="n"/>
-      <c r="W27" s="290" t="n"/>
-      <c r="X27" s="291" t="n"/>
+      <c r="U27" s="293" t="n"/>
+      <c r="V27" s="293" t="n"/>
+      <c r="W27" s="293" t="n"/>
+      <c r="X27" s="294" t="n"/>
     </row>
     <row r="28" ht="20.45" customHeight="1" s="257">
-      <c r="A28" s="371">
+      <c r="A28" s="361">
         <f>日程表１!A28</f>
         <v/>
       </c>
@@ -10682,15 +10692,15 @@
         <f>日程表１!B28</f>
         <v/>
       </c>
-      <c r="C28" s="348" t="n"/>
+      <c r="C28" s="338" t="n"/>
       <c r="D28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="349" t="n"/>
-      <c r="F28" s="372" t="n"/>
-      <c r="G28" s="371">
+      <c r="E28" s="339" t="n"/>
+      <c r="F28" s="362" t="n"/>
+      <c r="G28" s="361">
         <f>日程表１!G28</f>
         <v/>
       </c>
@@ -10698,7 +10708,7 @@
         <f>日程表１!H28</f>
         <v/>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="338">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -10707,15 +10717,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="372">
+      <c r="L28" s="362">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="371">
+      <c r="M28" s="361">
         <f>日程表１!M28</f>
         <v/>
       </c>
@@ -10723,14 +10733,14 @@
         <f>日程表１!N28</f>
         <v/>
       </c>
-      <c r="O28" s="348" t="n"/>
+      <c r="O28" s="338" t="n"/>
       <c r="P28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="349" t="n"/>
-      <c r="R28" s="372" t="n"/>
+      <c r="Q28" s="339" t="n"/>
+      <c r="R28" s="362" t="n"/>
       <c r="S28" s="254" t="n">
         <v>11</v>
       </c>
@@ -10738,13 +10748,13 @@
         <f>リーグ勝敗表!AX26</f>
         <v/>
       </c>
-      <c r="U28" s="290" t="n"/>
-      <c r="V28" s="290" t="n"/>
-      <c r="W28" s="290" t="n"/>
-      <c r="X28" s="291" t="n"/>
+      <c r="U28" s="293" t="n"/>
+      <c r="V28" s="293" t="n"/>
+      <c r="W28" s="293" t="n"/>
+      <c r="X28" s="294" t="n"/>
     </row>
     <row r="29" ht="20.45" customHeight="1" s="257">
-      <c r="A29" s="371">
+      <c r="A29" s="361">
         <f>日程表１!A29</f>
         <v/>
       </c>
@@ -10752,7 +10762,7 @@
         <f>日程表１!B29</f>
         <v/>
       </c>
-      <c r="C29" s="348">
+      <c r="C29" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10761,15 +10771,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="349">
+      <c r="E29" s="339">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="372">
+      <c r="F29" s="362">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="371">
+      <c r="G29" s="361">
         <f>日程表１!G29</f>
         <v/>
       </c>
@@ -10777,15 +10787,15 @@
         <f>日程表１!H29</f>
         <v/>
       </c>
-      <c r="I29" s="348" t="n"/>
+      <c r="I29" s="338" t="n"/>
       <c r="J29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K29" s="349" t="n"/>
-      <c r="L29" s="372" t="n"/>
-      <c r="M29" s="371">
+      <c r="K29" s="339" t="n"/>
+      <c r="L29" s="362" t="n"/>
+      <c r="M29" s="361">
         <f>日程表１!M29</f>
         <v/>
       </c>
@@ -10793,23 +10803,23 @@
         <f>日程表１!N29</f>
         <v/>
       </c>
-      <c r="O29" s="348" t="n"/>
+      <c r="O29" s="338" t="n"/>
       <c r="P29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="349" t="n"/>
-      <c r="R29" s="372" t="n"/>
+      <c r="Q29" s="339" t="n"/>
+      <c r="R29" s="362" t="n"/>
       <c r="S29" s="255" t="n"/>
       <c r="T29" s="255" t="n"/>
-      <c r="U29" s="363" t="n"/>
+      <c r="U29" s="353" t="n"/>
       <c r="V29" s="255" t="n"/>
-      <c r="W29" s="363" t="n"/>
-      <c r="X29" s="363" t="n"/>
+      <c r="W29" s="353" t="n"/>
+      <c r="X29" s="353" t="n"/>
     </row>
     <row r="30" ht="20.45" customHeight="1" s="257">
-      <c r="A30" s="371">
+      <c r="A30" s="361">
         <f>日程表１!A30</f>
         <v/>
       </c>
@@ -10817,7 +10827,7 @@
         <f>日程表１!B30</f>
         <v/>
       </c>
-      <c r="C30" s="348">
+      <c r="C30" s="338">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -10826,15 +10836,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="349">
+      <c r="E30" s="339">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="372">
+      <c r="F30" s="362">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="371">
+      <c r="G30" s="361">
         <f>日程表１!G30</f>
         <v/>
       </c>
@@ -10842,15 +10852,15 @@
         <f>日程表１!H30</f>
         <v/>
       </c>
-      <c r="I30" s="348" t="n"/>
+      <c r="I30" s="338" t="n"/>
       <c r="J30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K30" s="349" t="n"/>
-      <c r="L30" s="372" t="n"/>
-      <c r="M30" s="371">
+      <c r="K30" s="339" t="n"/>
+      <c r="L30" s="362" t="n"/>
+      <c r="M30" s="361">
         <f>日程表１!M30</f>
         <v/>
       </c>
@@ -10858,48 +10868,48 @@
         <f>日程表１!N30</f>
         <v/>
       </c>
-      <c r="O30" s="348" t="n"/>
+      <c r="O30" s="338" t="n"/>
       <c r="P30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="349" t="n"/>
-      <c r="R30" s="372" t="n"/>
+      <c r="Q30" s="339" t="n"/>
+      <c r="R30" s="362" t="n"/>
       <c r="S30" s="255" t="n"/>
       <c r="T30" s="255" t="n"/>
-      <c r="U30" s="363" t="n"/>
+      <c r="U30" s="353" t="n"/>
       <c r="V30" s="255" t="n"/>
-      <c r="W30" s="363" t="n"/>
-      <c r="X30" s="363" t="n"/>
+      <c r="W30" s="353" t="n"/>
+      <c r="X30" s="353" t="n"/>
     </row>
     <row r="31" ht="20.45" customHeight="1" s="257">
-      <c r="A31" s="375">
+      <c r="A31" s="365">
         <f>日程表１!A31</f>
         <v/>
       </c>
-      <c r="B31" s="376">
+      <c r="B31" s="366">
         <f>日程表１!B31</f>
         <v/>
       </c>
-      <c r="C31" s="353">
+      <c r="C31" s="343">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="377" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="355">
+      <c r="D31" s="367" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="345">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="378">
+      <c r="F31" s="368">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="371">
+      <c r="G31" s="361">
         <f>日程表１!G31</f>
         <v/>
       </c>
@@ -10907,15 +10917,15 @@
         <f>日程表１!H31</f>
         <v/>
       </c>
-      <c r="I31" s="348" t="n"/>
+      <c r="I31" s="338" t="n"/>
       <c r="J31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K31" s="349" t="n"/>
-      <c r="L31" s="372" t="n"/>
-      <c r="M31" s="371">
+      <c r="K31" s="339" t="n"/>
+      <c r="L31" s="362" t="n"/>
+      <c r="M31" s="361">
         <f>日程表１!M31</f>
         <v/>
       </c>
@@ -10923,23 +10933,23 @@
         <f>日程表１!N31</f>
         <v/>
       </c>
-      <c r="O31" s="348" t="n"/>
+      <c r="O31" s="338" t="n"/>
       <c r="P31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="349" t="n"/>
-      <c r="R31" s="372" t="n"/>
+      <c r="Q31" s="339" t="n"/>
+      <c r="R31" s="362" t="n"/>
       <c r="S31" s="255" t="n"/>
       <c r="T31" s="255" t="n"/>
-      <c r="U31" s="363" t="n"/>
+      <c r="U31" s="353" t="n"/>
       <c r="V31" s="255" t="n"/>
-      <c r="W31" s="363" t="n"/>
-      <c r="X31" s="363" t="n"/>
+      <c r="W31" s="353" t="n"/>
+      <c r="X31" s="353" t="n"/>
     </row>
     <row r="32" ht="20.45" customHeight="1" s="257">
-      <c r="A32" s="371">
+      <c r="A32" s="361">
         <f>日程表１!A32</f>
         <v/>
       </c>
@@ -10947,15 +10957,15 @@
         <f>日程表１!B32</f>
         <v/>
       </c>
-      <c r="C32" s="348" t="n"/>
+      <c r="C32" s="338" t="n"/>
       <c r="D32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="349" t="n"/>
-      <c r="F32" s="372" t="n"/>
-      <c r="G32" s="371">
+      <c r="E32" s="339" t="n"/>
+      <c r="F32" s="362" t="n"/>
+      <c r="G32" s="361">
         <f>日程表１!G32</f>
         <v/>
       </c>
@@ -10963,15 +10973,15 @@
         <f>日程表１!H32</f>
         <v/>
       </c>
-      <c r="I32" s="348" t="n"/>
+      <c r="I32" s="338" t="n"/>
       <c r="J32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K32" s="349" t="n"/>
-      <c r="L32" s="372" t="n"/>
-      <c r="M32" s="371">
+      <c r="K32" s="339" t="n"/>
+      <c r="L32" s="362" t="n"/>
+      <c r="M32" s="361">
         <f>日程表１!M32</f>
         <v/>
       </c>
@@ -10979,23 +10989,23 @@
         <f>日程表１!N32</f>
         <v/>
       </c>
-      <c r="O32" s="348" t="n"/>
+      <c r="O32" s="338" t="n"/>
       <c r="P32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="349" t="n"/>
-      <c r="R32" s="372" t="n"/>
+      <c r="Q32" s="339" t="n"/>
+      <c r="R32" s="362" t="n"/>
       <c r="S32" s="255" t="n"/>
       <c r="T32" s="255" t="n"/>
-      <c r="U32" s="363" t="n"/>
+      <c r="U32" s="353" t="n"/>
       <c r="V32" s="255" t="n"/>
-      <c r="W32" s="363" t="n"/>
-      <c r="X32" s="363" t="n"/>
+      <c r="W32" s="353" t="n"/>
+      <c r="X32" s="353" t="n"/>
     </row>
     <row r="33" ht="20.45" customHeight="1" s="257">
-      <c r="A33" s="371">
+      <c r="A33" s="361">
         <f>日程表１!A33</f>
         <v/>
       </c>
@@ -11003,15 +11013,15 @@
         <f>日程表１!B33</f>
         <v/>
       </c>
-      <c r="C33" s="348" t="n"/>
+      <c r="C33" s="338" t="n"/>
       <c r="D33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="349" t="n"/>
-      <c r="F33" s="372" t="n"/>
-      <c r="G33" s="371">
+      <c r="E33" s="339" t="n"/>
+      <c r="F33" s="362" t="n"/>
+      <c r="G33" s="361">
         <f>日程表１!G33</f>
         <v/>
       </c>
@@ -11019,7 +11029,7 @@
         <f>日程表１!H33</f>
         <v/>
       </c>
-      <c r="I33" s="348">
+      <c r="I33" s="338">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -11028,15 +11038,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K33" s="349">
+      <c r="K33" s="339">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="372">
+      <c r="L33" s="362">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="371">
+      <c r="M33" s="361">
         <f>日程表１!M33</f>
         <v/>
       </c>
@@ -11044,23 +11054,23 @@
         <f>日程表１!N33</f>
         <v/>
       </c>
-      <c r="O33" s="348" t="n"/>
+      <c r="O33" s="338" t="n"/>
       <c r="P33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="349" t="n"/>
-      <c r="R33" s="372" t="n"/>
+      <c r="Q33" s="339" t="n"/>
+      <c r="R33" s="362" t="n"/>
       <c r="S33" s="255" t="n"/>
       <c r="T33" s="255" t="n"/>
-      <c r="U33" s="363" t="n"/>
+      <c r="U33" s="353" t="n"/>
       <c r="V33" s="255" t="n"/>
-      <c r="W33" s="363" t="n"/>
-      <c r="X33" s="363" t="n"/>
+      <c r="W33" s="353" t="n"/>
+      <c r="X33" s="353" t="n"/>
     </row>
     <row r="34" ht="20.45" customHeight="1" s="257">
-      <c r="A34" s="371">
+      <c r="A34" s="361">
         <f>日程表１!A34</f>
         <v/>
       </c>
@@ -11068,25 +11078,25 @@
         <f>日程表１!B34</f>
         <v/>
       </c>
-      <c r="C34" s="348" t="n"/>
+      <c r="C34" s="338" t="n"/>
       <c r="D34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="379" t="n"/>
-      <c r="F34" s="362" t="n"/>
-      <c r="G34" s="371" t="n"/>
+      <c r="E34" s="369" t="n"/>
+      <c r="F34" s="352" t="n"/>
+      <c r="G34" s="361" t="n"/>
       <c r="H34" s="256" t="n"/>
-      <c r="I34" s="348" t="n"/>
+      <c r="I34" s="338" t="n"/>
       <c r="J34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K34" s="349" t="n"/>
-      <c r="L34" s="372" t="n"/>
-      <c r="M34" s="371">
+      <c r="K34" s="339" t="n"/>
+      <c r="L34" s="362" t="n"/>
+      <c r="M34" s="361">
         <f>日程表１!M34</f>
         <v/>
       </c>
@@ -11094,20 +11104,20 @@
         <f>日程表１!N34</f>
         <v/>
       </c>
-      <c r="O34" s="348" t="n"/>
+      <c r="O34" s="338" t="n"/>
       <c r="P34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="349" t="n"/>
-      <c r="R34" s="372" t="n"/>
+      <c r="Q34" s="339" t="n"/>
+      <c r="R34" s="362" t="n"/>
       <c r="S34" s="255" t="n"/>
       <c r="T34" s="255" t="n"/>
-      <c r="U34" s="363" t="n"/>
+      <c r="U34" s="353" t="n"/>
       <c r="V34" s="255" t="n"/>
-      <c r="W34" s="363" t="n"/>
-      <c r="X34" s="363" t="n"/>
+      <c r="W34" s="353" t="n"/>
+      <c r="X34" s="353" t="n"/>
     </row>
     <row r="35" ht="3" customHeight="1" s="257"/>
   </sheetData>

--- a/schedule_R8.xlsx
+++ b/schedule_R8.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <name val="メイリオ"/>
       <charset val="128"/>
@@ -246,7 +246,7 @@
       <name val="メイリオ"/>
       <b val="1"/>
       <color rgb="00FFD700"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="メイリオ"/>
@@ -258,26 +258,38 @@
       <name val="メイリオ"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="メイリオ"/>
-      <color rgb="001A252F"/>
+      <color rgb="00212121"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="メイリオ"/>
       <b val="1"/>
-      <color rgb="001A252F"/>
+      <color rgb="00212121"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="メイリオ"/>
-      <color rgb="00D5D8DC"/>
+      <b val="1"/>
+      <color rgb="00BF360C"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <color rgb="009E9E9E"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -352,47 +364,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1B2A"/>
+        <fgColor rgb="00102A43"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B4F72"/>
+        <fgColor rgb="001565C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002471A3"/>
+        <fgColor rgb="000D47A1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="001A237E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E8F5"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF5FB"/>
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F4F8"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FBFD"/>
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F3F4"/>
+        <fgColor rgb="00283593"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8ECF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1387,128 +1414,128 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="000D1B2A"/>
+        <color rgb="00102A43"/>
       </left>
       <right style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </right>
       <top style="medium">
-        <color rgb="000D1B2A"/>
+        <color rgb="00102A43"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </left>
       <right style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </right>
       <top style="medium">
-        <color rgb="000D1B2A"/>
+        <color rgb="00102A43"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00102A43"/>
+      </left>
+      <right style="medium">
+        <color rgb="00102A43"/>
+      </right>
+      <top style="medium">
+        <color rgb="00102A43"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00102A43"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00102A43"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </left>
-      <right style="medium">
-        <color rgb="000D1B2A"/>
+      <right style="thin">
+        <color rgb="00BDBDBD"/>
       </right>
-      <top style="medium">
-        <color rgb="000D1B2A"/>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00B2BABB"/>
+      <bottom style="medium">
+        <color rgb="00102A43"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="000D1B2A"/>
+        <color rgb="00102A43"/>
+      </left>
+      <right style="medium">
+        <color rgb="00102A43"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00102A43"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00102A43"/>
       </left>
       <right style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </right>
       <top style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </top>
-      <bottom style="medium">
-        <color rgb="000D1B2A"/>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </left>
       <right style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </right>
       <top style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </top>
-      <bottom style="medium">
-        <color rgb="000D1B2A"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B2BABB"/>
-      </left>
-      <right style="medium">
-        <color rgb="000D1B2A"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B2BABB"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="000D1B2A"/>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="000D1B2A"/>
+        <color rgb="00102A43"/>
       </left>
-      <right style="thin">
-        <color rgb="00B2BABB"/>
+      <right style="medium">
+        <color rgb="00102A43"/>
       </right>
       <top style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B2BABB"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B2BABB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B2BABB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B2BABB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B2BABB"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B2BABB"/>
-      </left>
-      <right style="medium">
-        <color rgb="000D1B2A"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B2BABB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B2BABB"/>
+        <color rgb="00BDBDBD"/>
       </bottom>
     </border>
   </borders>
@@ -1517,7 +1544,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="381">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2406,22 +2433,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2431,28 +2464,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="17" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="17" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="32" fillId="17" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="32" fillId="18" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="18" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="18" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="31" fillId="18" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="32" fillId="20" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2460,13 +2493,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
@@ -2476,15 +2518,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="83" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="83" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2494,26 +2550,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="21" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="33" fillId="21" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="35" fillId="24" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="35" fillId="24" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="86" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2527,7 +2587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="21" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="35" fillId="24" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2542,17 +2602,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="83" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="21" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="24" borderId="84" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -3061,14 +3125,14 @@
     <col hidden="1" width="4.6640625" customWidth="1" style="1" min="61" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" s="257">
+    <row r="1" ht="36" customHeight="1" s="257">
       <c r="A1" s="258" t="inlineStr">
         <is>
           <t>令和8年 朝野球リーグ勝敗表</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="6" customHeight="1" s="257">
+    <row r="2" ht="4" customHeight="1" s="257">
       <c r="A2" s="259" t="n"/>
       <c r="B2" s="260" t="n"/>
       <c r="C2" s="260" t="n"/>
@@ -3116,7 +3180,7 @@
       <c r="AS2" s="259" t="n"/>
       <c r="AU2" s="255" t="n"/>
     </row>
-    <row r="3" ht="6" customHeight="1" s="257">
+    <row r="3" ht="4" customHeight="1" s="257">
       <c r="A3" s="259" t="n"/>
       <c r="B3" s="259" t="n"/>
       <c r="C3" s="259" t="n"/>
@@ -3168,7 +3232,7 @@
       <c r="B4" s="262" t="n"/>
       <c r="C4" s="262" t="n"/>
       <c r="D4" s="262" t="n"/>
-      <c r="E4" s="262" t="n">
+      <c r="E4" s="261" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="263" t="n"/>
@@ -3241,7 +3305,7 @@
       </c>
       <c r="C5" s="267" t="n"/>
       <c r="D5" s="268" t="n"/>
-      <c r="E5" s="266">
+      <c r="E5" s="265">
         <f>C6</f>
         <v/>
       </c>
@@ -3307,42 +3371,42 @@
       </c>
       <c r="AJ5" s="267" t="n"/>
       <c r="AK5" s="268" t="n"/>
-      <c r="AL5" s="265" t="inlineStr">
+      <c r="AL5" s="269" t="inlineStr">
         <is>
           <t>勝</t>
         </is>
       </c>
-      <c r="AM5" s="266" t="inlineStr">
+      <c r="AM5" s="270" t="inlineStr">
         <is>
           <t>分</t>
         </is>
       </c>
-      <c r="AN5" s="266" t="inlineStr">
+      <c r="AN5" s="270" t="inlineStr">
         <is>
           <t>敗</t>
         </is>
       </c>
-      <c r="AO5" s="266" t="inlineStr">
+      <c r="AO5" s="270" t="inlineStr">
         <is>
           <t>勝点</t>
         </is>
       </c>
-      <c r="AP5" s="266" t="inlineStr">
+      <c r="AP5" s="270" t="inlineStr">
         <is>
           <t>失点</t>
         </is>
       </c>
-      <c r="AQ5" s="266" t="inlineStr">
+      <c r="AQ5" s="270" t="inlineStr">
         <is>
           <t>得点</t>
         </is>
       </c>
-      <c r="AR5" s="266" t="inlineStr">
+      <c r="AR5" s="270" t="inlineStr">
         <is>
           <t>残試</t>
         </is>
       </c>
-      <c r="AS5" s="269" t="inlineStr">
+      <c r="AS5" s="271" t="inlineStr">
         <is>
           <t>順位</t>
         </is>
@@ -3352,115 +3416,115 @@
           <t>チームナンバー</t>
         </is>
       </c>
-      <c r="AX5" s="270" t="n"/>
+      <c r="AX5" s="272" t="n"/>
       <c r="AZ5" s="100" t="inlineStr">
         <is>
           <t>チームリスト</t>
         </is>
       </c>
-      <c r="BA5" s="271" t="n"/>
+      <c r="BA5" s="273" t="n"/>
     </row>
     <row r="6" ht="46.9" customHeight="1" s="257">
-      <c r="A6" s="272" t="n"/>
-      <c r="B6" s="273" t="n">
+      <c r="A6" s="274" t="n"/>
+      <c r="B6" s="275" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="273">
+      <c r="C6" s="275">
         <f>AX6</f>
         <v/>
       </c>
-      <c r="D6" s="274" t="n"/>
-      <c r="E6" s="275" t="n"/>
-      <c r="G6" s="274" t="n"/>
-      <c r="H6" s="276">
+      <c r="D6" s="276" t="n"/>
+      <c r="E6" s="277" t="n"/>
+      <c r="G6" s="276" t="n"/>
+      <c r="H6" s="278">
         <f>IF(H7="","",IF(H7="☂","☂",IF(H7&gt;J7,"○",IF(H7=J7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I6" s="277" t="n"/>
-      <c r="J6" s="278" t="n"/>
-      <c r="K6" s="276">
+      <c r="I6" s="279" t="n"/>
+      <c r="J6" s="280" t="n"/>
+      <c r="K6" s="278">
         <f>IF(K7="","",IF(K7="☂","☂",IF(K7&gt;M7,"○",IF(K7=M7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L6" s="277" t="n"/>
-      <c r="M6" s="278" t="n"/>
-      <c r="N6" s="276">
+      <c r="L6" s="279" t="n"/>
+      <c r="M6" s="280" t="n"/>
+      <c r="N6" s="278">
         <f>IF(N7="","",IF(N7="☂","☂",IF(N7&gt;P7,"○",IF(N7=P7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O6" s="277" t="n"/>
-      <c r="P6" s="278" t="n"/>
-      <c r="Q6" s="276">
+      <c r="O6" s="279" t="n"/>
+      <c r="P6" s="280" t="n"/>
+      <c r="Q6" s="278">
         <f>IF(Q7="","",IF(Q7="☂","☂",IF(Q7&gt;S7,"○",IF(Q7=S7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R6" s="277" t="n"/>
-      <c r="S6" s="278" t="n"/>
-      <c r="T6" s="276">
+      <c r="R6" s="279" t="n"/>
+      <c r="S6" s="280" t="n"/>
+      <c r="T6" s="278">
         <f>IF(T7="","",IF(T7="☂","☂",IF(T7&gt;V7,"○",IF(T7=V7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U6" s="277" t="n"/>
-      <c r="V6" s="278" t="n"/>
-      <c r="W6" s="276">
+      <c r="U6" s="279" t="n"/>
+      <c r="V6" s="280" t="n"/>
+      <c r="W6" s="278">
         <f>IF(W7="","",IF(W7="☂","☂",IF(W7&gt;Y7,"○",IF(W7=Y7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X6" s="277" t="n"/>
-      <c r="Y6" s="278" t="n"/>
-      <c r="Z6" s="276">
+      <c r="X6" s="279" t="n"/>
+      <c r="Y6" s="280" t="n"/>
+      <c r="Z6" s="278">
         <f>IF(Z7="","",IF(Z7="☂","☂",IF(Z7&gt;AB7,"○",IF(Z7=AB7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA6" s="277" t="n"/>
-      <c r="AB6" s="278" t="n"/>
-      <c r="AC6" s="276">
+      <c r="AA6" s="279" t="n"/>
+      <c r="AB6" s="280" t="n"/>
+      <c r="AC6" s="278">
         <f>IF(AC7="","",IF(AC7="☂","☂",IF(AC7&gt;AE7,"○",IF(AC7=AE7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD6" s="277" t="n"/>
-      <c r="AE6" s="278" t="n"/>
-      <c r="AF6" s="276">
+      <c r="AD6" s="279" t="n"/>
+      <c r="AE6" s="280" t="n"/>
+      <c r="AF6" s="278">
         <f>IF(AF7="","",IF(AF7="☂","☂",IF(AF7&gt;AH7,"○",IF(AF7=AH7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG6" s="277" t="n"/>
-      <c r="AH6" s="278" t="n"/>
-      <c r="AI6" s="276">
+      <c r="AG6" s="279" t="n"/>
+      <c r="AH6" s="280" t="n"/>
+      <c r="AI6" s="278">
         <f>IF(AI7="","",IF(AI7="☂","☂",IF(AI7&gt;AK7,"○",IF(AI7=AK7,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ6" s="277" t="n"/>
-      <c r="AK6" s="278" t="n"/>
-      <c r="AL6" s="279">
+      <c r="AJ6" s="279" t="n"/>
+      <c r="AK6" s="280" t="n"/>
+      <c r="AL6" s="281">
         <f>COUNTIF(E6:AK6,"○")</f>
         <v/>
       </c>
-      <c r="AM6" s="280">
+      <c r="AM6" s="282">
         <f>COUNTIF(E6:AK6,"△")</f>
         <v/>
       </c>
-      <c r="AN6" s="280">
+      <c r="AN6" s="282">
         <f>COUNTIF(E6:AK6,"×")</f>
         <v/>
       </c>
-      <c r="AO6" s="281">
+      <c r="AO6" s="283">
         <f>AL6*3+AM6*1</f>
         <v/>
       </c>
-      <c r="AP6" s="280">
+      <c r="AP6" s="282">
         <f>SUM(J7,M7,P7,S7,V7,Y7,AB7,AK7)</f>
         <v/>
       </c>
-      <c r="AQ6" s="280">
+      <c r="AQ6" s="282">
         <f>SUM(H7,K7,N7,Q7,T7,W7,Z7,AI7)</f>
         <v/>
       </c>
-      <c r="AR6" s="280">
+      <c r="AR6" s="282">
         <f>$AY$21-AL6-AM6-AN6</f>
         <v/>
       </c>
-      <c r="AS6" s="282">
+      <c r="AS6" s="284">
         <f>IFERROR(_xlfn.RANK.EQ(AO6,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3484,154 +3548,154 @@
       </c>
     </row>
     <row r="7" ht="46.9" customHeight="1" s="257">
-      <c r="A7" s="283" t="n"/>
-      <c r="B7" s="284" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="286" t="n"/>
-      <c r="E7" s="271" t="n"/>
-      <c r="F7" s="271" t="n"/>
-      <c r="G7" s="286" t="n"/>
-      <c r="H7" s="287">
+      <c r="A7" s="285" t="n"/>
+      <c r="B7" s="286" t="n"/>
+      <c r="C7" s="287" t="n"/>
+      <c r="D7" s="288" t="n"/>
+      <c r="E7" s="273" t="n"/>
+      <c r="F7" s="273" t="n"/>
+      <c r="G7" s="288" t="n"/>
+      <c r="H7" s="289">
         <f>IF(G9="","",G9)</f>
         <v/>
       </c>
-      <c r="I7" s="288" t="inlineStr">
+      <c r="I7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="287">
+      <c r="J7" s="289">
         <f>IF(E9="","",E9)</f>
         <v/>
       </c>
-      <c r="K7" s="287">
+      <c r="K7" s="289">
         <f>IF(G11="","",G11)</f>
         <v/>
       </c>
-      <c r="L7" s="288" t="inlineStr">
+      <c r="L7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M7" s="287">
+      <c r="M7" s="289">
         <f>IF(E11="","",E11)</f>
         <v/>
       </c>
-      <c r="N7" s="287">
+      <c r="N7" s="289">
         <f>IF(G13="","",G13)</f>
         <v/>
       </c>
-      <c r="O7" s="288" t="inlineStr">
+      <c r="O7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P7" s="287">
+      <c r="P7" s="289">
         <f>IF(E13="","",E13)</f>
         <v/>
       </c>
-      <c r="Q7" s="287">
+      <c r="Q7" s="289">
         <f>IF(G15="","",G15)</f>
         <v/>
       </c>
-      <c r="R7" s="288" t="inlineStr">
+      <c r="R7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S7" s="287">
+      <c r="S7" s="289">
         <f>IF(E15="","",E15)</f>
         <v/>
       </c>
-      <c r="T7" s="287">
+      <c r="T7" s="289">
         <f>IF(G17="","",G17)</f>
         <v/>
       </c>
-      <c r="U7" s="288" t="inlineStr">
+      <c r="U7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V7" s="287">
+      <c r="V7" s="289">
         <f>IF(E17="","",E17)</f>
         <v/>
       </c>
-      <c r="W7" s="287">
+      <c r="W7" s="289">
         <f>IF(G19="","",G19)</f>
         <v/>
       </c>
-      <c r="X7" s="288" t="inlineStr">
+      <c r="X7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y7" s="287">
+      <c r="Y7" s="289">
         <f>IF(E19="","",E19)</f>
         <v/>
       </c>
-      <c r="Z7" s="287">
+      <c r="Z7" s="289">
         <f>IF(G21="","",G21)</f>
         <v/>
       </c>
-      <c r="AA7" s="288" t="inlineStr">
+      <c r="AA7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB7" s="287">
+      <c r="AB7" s="289">
         <f>IF(E21="","",E21)</f>
         <v/>
       </c>
-      <c r="AC7" s="287">
+      <c r="AC7" s="289">
         <f>IF(G23="","",G23)</f>
         <v/>
       </c>
-      <c r="AD7" s="288" t="inlineStr">
+      <c r="AD7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE7" s="287">
+      <c r="AE7" s="289">
         <f>IF(E23="","",E23)</f>
         <v/>
       </c>
-      <c r="AF7" s="287">
+      <c r="AF7" s="289">
         <f>IF(G25="","",G25)</f>
         <v/>
       </c>
-      <c r="AG7" s="288" t="inlineStr">
+      <c r="AG7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH7" s="287">
+      <c r="AH7" s="289">
         <f>IF(E25="","",E25)</f>
         <v/>
       </c>
-      <c r="AI7" s="287">
+      <c r="AI7" s="289">
         <f>IF(G27="","",G27)</f>
         <v/>
       </c>
-      <c r="AJ7" s="288" t="inlineStr">
+      <c r="AJ7" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK7" s="287">
+      <c r="AK7" s="289">
         <f>IF(E27="","",G27)</f>
         <v/>
       </c>
-      <c r="AL7" s="284" t="n"/>
-      <c r="AM7" s="289" t="n"/>
-      <c r="AN7" s="289" t="n"/>
-      <c r="AO7" s="289" t="n"/>
-      <c r="AP7" s="285" t="n"/>
-      <c r="AQ7" s="289" t="n"/>
-      <c r="AR7" s="289" t="n"/>
-      <c r="AS7" s="290" t="n"/>
-      <c r="AV7" s="289" t="n"/>
-      <c r="AW7" s="291" t="n"/>
-      <c r="AX7" s="289" t="n"/>
+      <c r="AL7" s="286" t="n"/>
+      <c r="AM7" s="291" t="n"/>
+      <c r="AN7" s="291" t="n"/>
+      <c r="AO7" s="291" t="n"/>
+      <c r="AP7" s="287" t="n"/>
+      <c r="AQ7" s="291" t="n"/>
+      <c r="AR7" s="291" t="n"/>
+      <c r="AS7" s="292" t="n"/>
+      <c r="AV7" s="291" t="n"/>
+      <c r="AW7" s="293" t="n"/>
+      <c r="AX7" s="291" t="n"/>
       <c r="AZ7" s="5" t="n">
         <v>2</v>
       </c>
@@ -3642,107 +3706,107 @@
       </c>
     </row>
     <row r="8" ht="46.9" customHeight="1" s="257">
-      <c r="A8" s="272" t="n"/>
-      <c r="B8" s="273" t="n">
+      <c r="A8" s="294" t="n"/>
+      <c r="B8" s="295" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="273">
+      <c r="C8" s="295">
         <f>AX8</f>
         <v/>
       </c>
-      <c r="D8" s="274" t="n"/>
-      <c r="E8" s="292">
+      <c r="D8" s="276" t="n"/>
+      <c r="E8" s="296">
         <f>IF(E9="","",IF(E9="☂","☂",IF(E9&gt;G9,"○",IF(E9=G9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F8" s="293" t="n"/>
-      <c r="G8" s="294" t="n"/>
-      <c r="H8" s="292" t="n"/>
-      <c r="I8" s="295" t="n"/>
-      <c r="J8" s="270" t="n"/>
-      <c r="K8" s="296">
+      <c r="F8" s="297" t="n"/>
+      <c r="G8" s="298" t="n"/>
+      <c r="H8" s="299" t="n"/>
+      <c r="I8" s="300" t="n"/>
+      <c r="J8" s="272" t="n"/>
+      <c r="K8" s="301">
         <f>IF(K9="","",IF(K9="☂","☂",IF(K9&gt;M9,"○",IF(K9=M9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L8" s="297" t="n"/>
-      <c r="M8" s="298" t="n"/>
-      <c r="N8" s="296">
+      <c r="L8" s="302" t="n"/>
+      <c r="M8" s="303" t="n"/>
+      <c r="N8" s="301">
         <f>IF(N9="","",IF(N9="☂","☂",IF(N9&gt;P9,"○",IF(N9=P9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O8" s="297" t="n"/>
-      <c r="P8" s="298" t="n"/>
-      <c r="Q8" s="296">
+      <c r="O8" s="302" t="n"/>
+      <c r="P8" s="303" t="n"/>
+      <c r="Q8" s="301">
         <f>IF(Q9="","",IF(Q9="☂","☂",IF(Q9&gt;S9,"○",IF(Q9=S9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R8" s="297" t="n"/>
-      <c r="S8" s="298" t="n"/>
-      <c r="T8" s="296">
+      <c r="R8" s="302" t="n"/>
+      <c r="S8" s="303" t="n"/>
+      <c r="T8" s="301">
         <f>IF(T9="","",IF(T9="☂","☂",IF(T9&gt;V9,"○",IF(T9=V9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U8" s="297" t="n"/>
-      <c r="V8" s="298" t="n"/>
-      <c r="W8" s="296">
+      <c r="U8" s="302" t="n"/>
+      <c r="V8" s="303" t="n"/>
+      <c r="W8" s="301">
         <f>IF(W9="","",IF(W9="☂","☂",IF(W9&gt;Y9,"○",IF(W9=Y9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X8" s="297" t="n"/>
-      <c r="Y8" s="298" t="n"/>
-      <c r="Z8" s="296">
+      <c r="X8" s="302" t="n"/>
+      <c r="Y8" s="303" t="n"/>
+      <c r="Z8" s="301">
         <f>IF(Z9="","",IF(Z9="☂","☂",IF(Z9&gt;AB9,"○",IF(Z9=AB9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA8" s="297" t="n"/>
-      <c r="AB8" s="298" t="n"/>
-      <c r="AC8" s="296">
+      <c r="AA8" s="302" t="n"/>
+      <c r="AB8" s="303" t="n"/>
+      <c r="AC8" s="301">
         <f>IF(AC9="","",IF(AC9="☂","☂",IF(AC9&gt;AE9,"○",IF(AC9=AE9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD8" s="297" t="n"/>
-      <c r="AE8" s="298" t="n"/>
-      <c r="AF8" s="296">
+      <c r="AD8" s="302" t="n"/>
+      <c r="AE8" s="303" t="n"/>
+      <c r="AF8" s="301">
         <f>IF(AF9="","",IF(AF9="☂","☂",IF(AF9&gt;AH9,"○",IF(AF9=AH9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG8" s="297" t="n"/>
-      <c r="AH8" s="298" t="n"/>
-      <c r="AI8" s="296">
+      <c r="AG8" s="302" t="n"/>
+      <c r="AH8" s="303" t="n"/>
+      <c r="AI8" s="301">
         <f>IF(AI9="","",IF(AI9="☂","☂",IF(AI9&gt;AK9,"○",IF(AI9=AK9,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ8" s="297" t="n"/>
-      <c r="AK8" s="298" t="n"/>
-      <c r="AL8" s="279">
+      <c r="AJ8" s="302" t="n"/>
+      <c r="AK8" s="303" t="n"/>
+      <c r="AL8" s="281">
         <f>COUNTIF(E8:AK8,"○")</f>
         <v/>
       </c>
-      <c r="AM8" s="280">
+      <c r="AM8" s="282">
         <f>COUNTIF(E8:AK8,"△")</f>
         <v/>
       </c>
-      <c r="AN8" s="280">
+      <c r="AN8" s="282">
         <f>COUNTIF(E8:AK8,"×")</f>
         <v/>
       </c>
-      <c r="AO8" s="281">
+      <c r="AO8" s="283">
         <f>AL8*3+AM8*1</f>
         <v/>
       </c>
-      <c r="AP8" s="280">
+      <c r="AP8" s="282">
         <f>SUM(G9,M9,P9,S9,V9,Y9,AB9,AK9)</f>
         <v/>
       </c>
-      <c r="AQ8" s="280">
+      <c r="AQ8" s="282">
         <f>SUM(E9,K9,N9,Q9,T9,W9,Z9,AI9)</f>
         <v/>
       </c>
-      <c r="AR8" s="280">
+      <c r="AR8" s="282">
         <f>$AY$21-AL8-AM8-AN8</f>
         <v/>
       </c>
-      <c r="AS8" s="282">
+      <c r="AS8" s="284">
         <f>IFERROR(_xlfn.RANK.EQ(AO8,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -3766,148 +3830,148 @@
       </c>
     </row>
     <row r="9" ht="46.9" customHeight="1" s="257">
-      <c r="A9" s="283" t="n"/>
-      <c r="B9" s="284" t="n"/>
-      <c r="C9" s="285" t="n"/>
-      <c r="D9" s="286" t="n"/>
-      <c r="E9" s="299" t="n"/>
-      <c r="F9" s="300" t="inlineStr">
+      <c r="A9" s="304" t="n"/>
+      <c r="B9" s="286" t="n"/>
+      <c r="C9" s="287" t="n"/>
+      <c r="D9" s="288" t="n"/>
+      <c r="E9" s="305" t="n"/>
+      <c r="F9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="299" t="n"/>
-      <c r="H9" s="285" t="n"/>
-      <c r="I9" s="271" t="n"/>
-      <c r="J9" s="286" t="n"/>
-      <c r="K9" s="300">
+      <c r="G9" s="307" t="n"/>
+      <c r="H9" s="287" t="n"/>
+      <c r="I9" s="273" t="n"/>
+      <c r="J9" s="288" t="n"/>
+      <c r="K9" s="306">
         <f>IF(J11="","",J11)</f>
         <v/>
       </c>
-      <c r="L9" s="300" t="inlineStr">
+      <c r="L9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M9" s="300">
+      <c r="M9" s="306">
         <f>IF(H11="","",H11)</f>
         <v/>
       </c>
-      <c r="N9" s="300">
+      <c r="N9" s="306">
         <f>IF(J13="","",J13)</f>
         <v/>
       </c>
-      <c r="O9" s="300" t="inlineStr">
+      <c r="O9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P9" s="300">
+      <c r="P9" s="306">
         <f>IF(H13="","",H13)</f>
         <v/>
       </c>
-      <c r="Q9" s="300">
+      <c r="Q9" s="306">
         <f>IF(J15="","",J15)</f>
         <v/>
       </c>
-      <c r="R9" s="300" t="inlineStr">
+      <c r="R9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S9" s="300">
+      <c r="S9" s="306">
         <f>IF(H15="","",H15)</f>
         <v/>
       </c>
-      <c r="T9" s="300">
+      <c r="T9" s="306">
         <f>IF(J17="","",J17)</f>
         <v/>
       </c>
-      <c r="U9" s="300" t="inlineStr">
+      <c r="U9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V9" s="300">
+      <c r="V9" s="306">
         <f>IF(H17="","",H17)</f>
         <v/>
       </c>
-      <c r="W9" s="300">
+      <c r="W9" s="306">
         <f>IF(J19="","",J19)</f>
         <v/>
       </c>
-      <c r="X9" s="300" t="inlineStr">
+      <c r="X9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y9" s="300">
+      <c r="Y9" s="306">
         <f>IF(H19="","",H19)</f>
         <v/>
       </c>
-      <c r="Z9" s="300">
+      <c r="Z9" s="306">
         <f>IF(J21="","",J21)</f>
         <v/>
       </c>
-      <c r="AA9" s="300" t="inlineStr">
+      <c r="AA9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB9" s="300">
+      <c r="AB9" s="306">
         <f>IF(H21="","",H21)</f>
         <v/>
       </c>
-      <c r="AC9" s="300">
+      <c r="AC9" s="306">
         <f>IF(J23="","",J23)</f>
         <v/>
       </c>
-      <c r="AD9" s="300" t="inlineStr">
+      <c r="AD9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE9" s="300">
+      <c r="AE9" s="306">
         <f>IF(H23="","",H23)</f>
         <v/>
       </c>
-      <c r="AF9" s="300">
+      <c r="AF9" s="306">
         <f>IF(J25="","",J25)</f>
         <v/>
       </c>
-      <c r="AG9" s="300" t="inlineStr">
+      <c r="AG9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH9" s="300">
+      <c r="AH9" s="306">
         <f>IF(H25="","",H25)</f>
         <v/>
       </c>
-      <c r="AI9" s="300">
+      <c r="AI9" s="306">
         <f>IF(J27="","",J27)</f>
         <v/>
       </c>
-      <c r="AJ9" s="300" t="inlineStr">
+      <c r="AJ9" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK9" s="300">
+      <c r="AK9" s="306">
         <f>IF(H27="","",H27)</f>
         <v/>
       </c>
-      <c r="AL9" s="284" t="n"/>
-      <c r="AM9" s="289" t="n"/>
-      <c r="AN9" s="289" t="n"/>
-      <c r="AO9" s="289" t="n"/>
-      <c r="AP9" s="289" t="n"/>
-      <c r="AQ9" s="289" t="n"/>
-      <c r="AR9" s="289" t="n"/>
-      <c r="AS9" s="301" t="n"/>
-      <c r="AV9" s="289" t="n"/>
-      <c r="AW9" s="291" t="n"/>
-      <c r="AX9" s="289" t="n"/>
+      <c r="AL9" s="286" t="n"/>
+      <c r="AM9" s="291" t="n"/>
+      <c r="AN9" s="291" t="n"/>
+      <c r="AO9" s="291" t="n"/>
+      <c r="AP9" s="291" t="n"/>
+      <c r="AQ9" s="291" t="n"/>
+      <c r="AR9" s="291" t="n"/>
+      <c r="AS9" s="308" t="n"/>
+      <c r="AV9" s="291" t="n"/>
+      <c r="AW9" s="293" t="n"/>
+      <c r="AX9" s="291" t="n"/>
       <c r="AZ9" s="5" t="n">
         <v>4</v>
       </c>
@@ -3918,107 +3982,107 @@
       </c>
     </row>
     <row r="10" ht="46.9" customHeight="1" s="257">
-      <c r="A10" s="272" t="n"/>
-      <c r="B10" s="273" t="n">
+      <c r="A10" s="274" t="n"/>
+      <c r="B10" s="275" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="273">
+      <c r="C10" s="275">
         <f>AX10</f>
         <v/>
       </c>
-      <c r="D10" s="274" t="n"/>
-      <c r="E10" s="275">
+      <c r="D10" s="276" t="n"/>
+      <c r="E10" s="277">
         <f>IF(E11="","",IF(E11="☂","☂",IF(E11&gt;G11,"○",IF(E11=G11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F10" s="293" t="n"/>
-      <c r="G10" s="294" t="n"/>
-      <c r="H10" s="275">
+      <c r="F10" s="297" t="n"/>
+      <c r="G10" s="298" t="n"/>
+      <c r="H10" s="309">
         <f>IF(H11="","",IF(H11="☂","☂",IF(H11&gt;J11,"○",IF(H11=J11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I10" s="293" t="n"/>
-      <c r="J10" s="294" t="n"/>
-      <c r="K10" s="275" t="n"/>
-      <c r="L10" s="295" t="n"/>
-      <c r="M10" s="270" t="n"/>
-      <c r="N10" s="276">
+      <c r="I10" s="297" t="n"/>
+      <c r="J10" s="298" t="n"/>
+      <c r="K10" s="309" t="n"/>
+      <c r="L10" s="300" t="n"/>
+      <c r="M10" s="272" t="n"/>
+      <c r="N10" s="278">
         <f>IF(N11="","",IF(N11="☂","☂",IF(N11&gt;P11,"○",IF(N11=P11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O10" s="297" t="n"/>
-      <c r="P10" s="298" t="n"/>
-      <c r="Q10" s="276">
+      <c r="O10" s="302" t="n"/>
+      <c r="P10" s="303" t="n"/>
+      <c r="Q10" s="278">
         <f>IF(Q11="","",IF(Q11="☂","☂",IF(Q11&gt;S11,"○",IF(Q11=S11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R10" s="297" t="n"/>
-      <c r="S10" s="298" t="n"/>
-      <c r="T10" s="276">
+      <c r="R10" s="302" t="n"/>
+      <c r="S10" s="303" t="n"/>
+      <c r="T10" s="278">
         <f>IF(T11="","",IF(T11="☂","☂",IF(T11&gt;V11,"○",IF(T11=V11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U10" s="297" t="n"/>
-      <c r="V10" s="298" t="n"/>
-      <c r="W10" s="276">
+      <c r="U10" s="302" t="n"/>
+      <c r="V10" s="303" t="n"/>
+      <c r="W10" s="278">
         <f>IF(W11="","",IF(W11="☂","☂",IF(W11&gt;Y11,"○",IF(W11=Y11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X10" s="297" t="n"/>
-      <c r="Y10" s="298" t="n"/>
-      <c r="Z10" s="276">
+      <c r="X10" s="302" t="n"/>
+      <c r="Y10" s="303" t="n"/>
+      <c r="Z10" s="278">
         <f>IF(Z11="","",IF(Z11="☂","☂",IF(Z11&gt;AB11,"○",IF(Z11=AB11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA10" s="297" t="n"/>
-      <c r="AB10" s="298" t="n"/>
-      <c r="AC10" s="276">
+      <c r="AA10" s="302" t="n"/>
+      <c r="AB10" s="303" t="n"/>
+      <c r="AC10" s="278">
         <f>IF(AC11="","",IF(AC11="☂","☂",IF(AC11&gt;AE11,"○",IF(AC11=AE11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD10" s="297" t="n"/>
-      <c r="AE10" s="298" t="n"/>
-      <c r="AF10" s="276">
+      <c r="AD10" s="302" t="n"/>
+      <c r="AE10" s="303" t="n"/>
+      <c r="AF10" s="278">
         <f>IF(AF11="","",IF(AF11="☂","☂",IF(AF11&gt;AH11,"○",IF(AF11=AH11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG10" s="297" t="n"/>
-      <c r="AH10" s="298" t="n"/>
-      <c r="AI10" s="276">
+      <c r="AG10" s="302" t="n"/>
+      <c r="AH10" s="303" t="n"/>
+      <c r="AI10" s="278">
         <f>IF(AI11="","",IF(AI11="☂","☂",IF(AI11&gt;AK11,"○",IF(AI11=AK11,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ10" s="297" t="n"/>
-      <c r="AK10" s="298" t="n"/>
-      <c r="AL10" s="279">
+      <c r="AJ10" s="302" t="n"/>
+      <c r="AK10" s="303" t="n"/>
+      <c r="AL10" s="281">
         <f>COUNTIF(E10:AK10,"○")</f>
         <v/>
       </c>
-      <c r="AM10" s="280">
+      <c r="AM10" s="282">
         <f>COUNTIF(E10:AK10,"△")</f>
         <v/>
       </c>
-      <c r="AN10" s="280">
+      <c r="AN10" s="282">
         <f>COUNTIF(E10:AK10,"×")</f>
         <v/>
       </c>
-      <c r="AO10" s="281">
+      <c r="AO10" s="283">
         <f>AL10*3+AM10*1</f>
         <v/>
       </c>
-      <c r="AP10" s="280">
+      <c r="AP10" s="282">
         <f>SUM(G11,J11,M11,P11,S11,V11,Y11,AB11,AK11)</f>
         <v/>
       </c>
-      <c r="AQ10" s="280">
+      <c r="AQ10" s="282">
         <f>SUM(E11,H11,K11,N11,Q11,T11,W11,Z11,AI11)</f>
         <v/>
       </c>
-      <c r="AR10" s="280">
+      <c r="AR10" s="282">
         <f>$AY$21-AL10-AM10-AN10</f>
         <v/>
       </c>
-      <c r="AS10" s="282">
+      <c r="AS10" s="284">
         <f>IFERROR(_xlfn.RANK.EQ(AO10,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4042,138 +4106,138 @@
       </c>
     </row>
     <row r="11" ht="46.9" customHeight="1" s="257">
-      <c r="A11" s="283" t="n"/>
-      <c r="B11" s="284" t="n"/>
-      <c r="C11" s="285" t="n"/>
-      <c r="D11" s="286" t="n"/>
-      <c r="E11" s="302" t="n"/>
-      <c r="F11" s="288" t="n"/>
-      <c r="G11" s="302" t="n"/>
-      <c r="H11" s="302" t="n"/>
-      <c r="I11" s="288" t="inlineStr">
+      <c r="A11" s="285" t="n"/>
+      <c r="B11" s="286" t="n"/>
+      <c r="C11" s="287" t="n"/>
+      <c r="D11" s="288" t="n"/>
+      <c r="E11" s="310" t="n"/>
+      <c r="F11" s="290" t="n"/>
+      <c r="G11" s="311" t="n"/>
+      <c r="H11" s="311" t="n"/>
+      <c r="I11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="302" t="n"/>
-      <c r="K11" s="285" t="n"/>
-      <c r="L11" s="271" t="n"/>
-      <c r="M11" s="286" t="n"/>
-      <c r="N11" s="288">
+      <c r="J11" s="311" t="n"/>
+      <c r="K11" s="287" t="n"/>
+      <c r="L11" s="273" t="n"/>
+      <c r="M11" s="288" t="n"/>
+      <c r="N11" s="290">
         <f>IF(M13="","",M13)</f>
         <v/>
       </c>
-      <c r="O11" s="288" t="inlineStr">
+      <c r="O11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P11" s="288">
+      <c r="P11" s="290">
         <f>IF(K13="","",K13)</f>
         <v/>
       </c>
-      <c r="Q11" s="288">
+      <c r="Q11" s="290">
         <f>IF(M15="","",M15)</f>
         <v/>
       </c>
-      <c r="R11" s="288" t="inlineStr">
+      <c r="R11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S11" s="288">
+      <c r="S11" s="290">
         <f>IF(K15="","",K15)</f>
         <v/>
       </c>
-      <c r="T11" s="288">
+      <c r="T11" s="290">
         <f>IF(M17="","",M17)</f>
         <v/>
       </c>
-      <c r="U11" s="288" t="inlineStr">
+      <c r="U11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V11" s="288">
+      <c r="V11" s="290">
         <f>IF(K17="","",K17)</f>
         <v/>
       </c>
-      <c r="W11" s="288">
+      <c r="W11" s="290">
         <f>IF(M19="","",M19)</f>
         <v/>
       </c>
-      <c r="X11" s="288" t="inlineStr">
+      <c r="X11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y11" s="288">
+      <c r="Y11" s="290">
         <f>IF(K19="","",K19)</f>
         <v/>
       </c>
-      <c r="Z11" s="288">
+      <c r="Z11" s="290">
         <f>IF(M21="","",M21)</f>
         <v/>
       </c>
-      <c r="AA11" s="288" t="inlineStr">
+      <c r="AA11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB11" s="288">
+      <c r="AB11" s="290">
         <f>IF(K21="","",K21)</f>
         <v/>
       </c>
-      <c r="AC11" s="288">
+      <c r="AC11" s="290">
         <f>IF(M23="","",M23)</f>
         <v/>
       </c>
-      <c r="AD11" s="288" t="inlineStr">
+      <c r="AD11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE11" s="288">
+      <c r="AE11" s="290">
         <f>IF(K23="","",K23)</f>
         <v/>
       </c>
-      <c r="AF11" s="288">
+      <c r="AF11" s="290">
         <f>IF(M25="","",M25)</f>
         <v/>
       </c>
-      <c r="AG11" s="288" t="inlineStr">
+      <c r="AG11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH11" s="288">
+      <c r="AH11" s="290">
         <f>IF(K25="","",K25)</f>
         <v/>
       </c>
-      <c r="AI11" s="288">
+      <c r="AI11" s="290">
         <f>IF(M27="","",M27)</f>
         <v/>
       </c>
-      <c r="AJ11" s="288" t="inlineStr">
+      <c r="AJ11" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK11" s="288">
+      <c r="AK11" s="290">
         <f>IF(K27="","",K27)</f>
         <v/>
       </c>
-      <c r="AL11" s="284" t="n"/>
-      <c r="AM11" s="289" t="n"/>
-      <c r="AN11" s="289" t="n"/>
-      <c r="AO11" s="289" t="n"/>
-      <c r="AP11" s="289" t="n"/>
-      <c r="AQ11" s="289" t="n"/>
-      <c r="AR11" s="289" t="n"/>
-      <c r="AS11" s="301" t="n"/>
-      <c r="AV11" s="289" t="n"/>
-      <c r="AW11" s="291" t="n"/>
-      <c r="AX11" s="289" t="n"/>
+      <c r="AL11" s="286" t="n"/>
+      <c r="AM11" s="291" t="n"/>
+      <c r="AN11" s="291" t="n"/>
+      <c r="AO11" s="291" t="n"/>
+      <c r="AP11" s="291" t="n"/>
+      <c r="AQ11" s="291" t="n"/>
+      <c r="AR11" s="291" t="n"/>
+      <c r="AS11" s="308" t="n"/>
+      <c r="AV11" s="291" t="n"/>
+      <c r="AW11" s="293" t="n"/>
+      <c r="AX11" s="291" t="n"/>
       <c r="AZ11" s="5" t="n">
         <v>6</v>
       </c>
@@ -4184,107 +4248,107 @@
       </c>
     </row>
     <row r="12" ht="46.9" customHeight="1" s="257">
-      <c r="A12" s="272" t="n"/>
-      <c r="B12" s="273" t="n">
+      <c r="A12" s="294" t="n"/>
+      <c r="B12" s="295" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="273">
+      <c r="C12" s="295">
         <f>AX12</f>
         <v/>
       </c>
-      <c r="D12" s="274" t="n"/>
-      <c r="E12" s="292">
+      <c r="D12" s="276" t="n"/>
+      <c r="E12" s="296">
         <f>IF(E13="","",IF(E13="☂","☂",IF(E13&gt;G13,"○",IF(E13=G13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F12" s="293" t="n"/>
-      <c r="G12" s="294" t="n"/>
-      <c r="H12" s="292">
+      <c r="F12" s="297" t="n"/>
+      <c r="G12" s="298" t="n"/>
+      <c r="H12" s="299">
         <f>IF(H13="","",IF(H13="☂","☂",IF(H13&gt;J13,"○",IF(H13=J13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I12" s="293" t="n"/>
-      <c r="J12" s="294" t="n"/>
-      <c r="K12" s="292">
+      <c r="I12" s="297" t="n"/>
+      <c r="J12" s="298" t="n"/>
+      <c r="K12" s="299">
         <f>IF(K13="","",IF(K13="☂","☂",IF(K13&gt;M13,"○",IF(K13=M13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L12" s="293" t="n"/>
-      <c r="M12" s="294" t="n"/>
-      <c r="N12" s="292" t="n"/>
-      <c r="O12" s="295" t="n"/>
-      <c r="P12" s="270" t="n"/>
-      <c r="Q12" s="296">
+      <c r="L12" s="297" t="n"/>
+      <c r="M12" s="298" t="n"/>
+      <c r="N12" s="299" t="n"/>
+      <c r="O12" s="300" t="n"/>
+      <c r="P12" s="272" t="n"/>
+      <c r="Q12" s="301">
         <f>IF(Q13="","",IF(Q13="☂","☂",IF(Q13&gt;S13,"○",IF(Q13=S13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R12" s="297" t="n"/>
-      <c r="S12" s="298" t="n"/>
-      <c r="T12" s="296">
+      <c r="R12" s="302" t="n"/>
+      <c r="S12" s="303" t="n"/>
+      <c r="T12" s="301">
         <f>IF(T13="","",IF(T13="☂","☂",IF(T13&gt;V13,"○",IF(T13=V13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U12" s="297" t="n"/>
-      <c r="V12" s="298" t="n"/>
-      <c r="W12" s="296">
+      <c r="U12" s="302" t="n"/>
+      <c r="V12" s="303" t="n"/>
+      <c r="W12" s="301">
         <f>IF(W13="","",IF(W13="☂","☂",IF(W13&gt;Y13,"○",IF(W13=Y13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X12" s="297" t="n"/>
-      <c r="Y12" s="298" t="n"/>
-      <c r="Z12" s="296">
+      <c r="X12" s="302" t="n"/>
+      <c r="Y12" s="303" t="n"/>
+      <c r="Z12" s="301">
         <f>IF(Z13="","",IF(Z13="☂","☂",IF(Z13&gt;AB13,"○",IF(Z13=AB13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA12" s="297" t="n"/>
-      <c r="AB12" s="298" t="n"/>
-      <c r="AC12" s="296">
+      <c r="AA12" s="302" t="n"/>
+      <c r="AB12" s="303" t="n"/>
+      <c r="AC12" s="301">
         <f>IF(AC13="","",IF(AC13="☂","☂",IF(AC13&gt;AE13,"○",IF(AC13=AE13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD12" s="297" t="n"/>
-      <c r="AE12" s="298" t="n"/>
-      <c r="AF12" s="296">
+      <c r="AD12" s="302" t="n"/>
+      <c r="AE12" s="303" t="n"/>
+      <c r="AF12" s="301">
         <f>IF(AF13="","",IF(AF13="☂","☂",IF(AF13&gt;AH13,"○",IF(AF13=AH13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG12" s="297" t="n"/>
-      <c r="AH12" s="298" t="n"/>
-      <c r="AI12" s="296">
+      <c r="AG12" s="302" t="n"/>
+      <c r="AH12" s="303" t="n"/>
+      <c r="AI12" s="301">
         <f>IF(AI13="","",IF(AI13="☂","☂",IF(AI13&gt;AK13,"○",IF(AI13=AK13,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ12" s="297" t="n"/>
-      <c r="AK12" s="298" t="n"/>
-      <c r="AL12" s="279">
+      <c r="AJ12" s="302" t="n"/>
+      <c r="AK12" s="303" t="n"/>
+      <c r="AL12" s="281">
         <f>COUNTIF(E12:AK12,"○")</f>
         <v/>
       </c>
-      <c r="AM12" s="280">
+      <c r="AM12" s="282">
         <f>COUNTIF(E12:AK12,"△")</f>
         <v/>
       </c>
-      <c r="AN12" s="280">
+      <c r="AN12" s="282">
         <f>COUNTIF(E12:AK12,"×")</f>
         <v/>
       </c>
-      <c r="AO12" s="281">
+      <c r="AO12" s="283">
         <f>AL12*3+AM12*1</f>
         <v/>
       </c>
-      <c r="AP12" s="280">
+      <c r="AP12" s="282">
         <f>SUM(G13,J13,M13,P13,S13,V13,Y13,AB13,AK13)</f>
         <v/>
       </c>
-      <c r="AQ12" s="280">
+      <c r="AQ12" s="282">
         <f>SUM(E13,H13,K13,N13,Q13,T13,W13,Z13,AI13)</f>
         <v/>
       </c>
-      <c r="AR12" s="280">
+      <c r="AR12" s="282">
         <f>$AY$21-AL12-AM12-AN12</f>
         <v/>
       </c>
-      <c r="AS12" s="282">
+      <c r="AS12" s="284">
         <f>IFERROR(_xlfn.RANK.EQ(AO12,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4304,243 +4368,243 @@
       <c r="BA12" s="6" t="n"/>
     </row>
     <row r="13" ht="46.9" customHeight="1" s="257">
-      <c r="A13" s="283" t="n"/>
-      <c r="B13" s="284" t="n"/>
-      <c r="C13" s="285" t="n"/>
-      <c r="D13" s="286" t="n"/>
-      <c r="E13" s="299" t="n"/>
-      <c r="F13" s="300" t="inlineStr">
+      <c r="A13" s="304" t="n"/>
+      <c r="B13" s="286" t="n"/>
+      <c r="C13" s="287" t="n"/>
+      <c r="D13" s="288" t="n"/>
+      <c r="E13" s="305" t="n"/>
+      <c r="F13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="299" t="n"/>
-      <c r="H13" s="299" t="n"/>
-      <c r="I13" s="300" t="inlineStr">
+      <c r="G13" s="307" t="n"/>
+      <c r="H13" s="307" t="n"/>
+      <c r="I13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="299" t="n"/>
-      <c r="K13" s="299" t="n"/>
-      <c r="L13" s="300" t="inlineStr">
+      <c r="J13" s="307" t="n"/>
+      <c r="K13" s="307" t="n"/>
+      <c r="L13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M13" s="299" t="n"/>
-      <c r="N13" s="285" t="n"/>
-      <c r="O13" s="271" t="n"/>
-      <c r="P13" s="286" t="n"/>
-      <c r="Q13" s="300">
+      <c r="M13" s="307" t="n"/>
+      <c r="N13" s="287" t="n"/>
+      <c r="O13" s="273" t="n"/>
+      <c r="P13" s="288" t="n"/>
+      <c r="Q13" s="306">
         <f>IF(P15="","",P15)</f>
         <v/>
       </c>
-      <c r="R13" s="300" t="inlineStr">
+      <c r="R13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S13" s="300">
+      <c r="S13" s="306">
         <f>IF(N15="","",N15)</f>
         <v/>
       </c>
-      <c r="T13" s="300">
+      <c r="T13" s="306">
         <f>IF(P17="","",P17)</f>
         <v/>
       </c>
-      <c r="U13" s="300" t="inlineStr">
+      <c r="U13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V13" s="300">
+      <c r="V13" s="306">
         <f>IF(N17="","",N17)</f>
         <v/>
       </c>
-      <c r="W13" s="300">
+      <c r="W13" s="306">
         <f>IF(P19="","",P19)</f>
         <v/>
       </c>
-      <c r="X13" s="300" t="inlineStr">
+      <c r="X13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y13" s="300">
+      <c r="Y13" s="306">
         <f>IF(N19="","",N19)</f>
         <v/>
       </c>
-      <c r="Z13" s="300">
+      <c r="Z13" s="306">
         <f>IF(P21="","",P21)</f>
         <v/>
       </c>
-      <c r="AA13" s="300" t="inlineStr">
+      <c r="AA13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB13" s="300">
+      <c r="AB13" s="306">
         <f>IF(N21="","",N21)</f>
         <v/>
       </c>
-      <c r="AC13" s="300">
+      <c r="AC13" s="306">
         <f>IF(P23="","",P23)</f>
         <v/>
       </c>
-      <c r="AD13" s="300" t="inlineStr">
+      <c r="AD13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE13" s="300">
+      <c r="AE13" s="306">
         <f>IF(N23="","",N23)</f>
         <v/>
       </c>
-      <c r="AF13" s="300">
+      <c r="AF13" s="306">
         <f>IF(P25="","",P25)</f>
         <v/>
       </c>
-      <c r="AG13" s="300" t="inlineStr">
+      <c r="AG13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH13" s="300">
+      <c r="AH13" s="306">
         <f>IF(N25="","",N25)</f>
         <v/>
       </c>
-      <c r="AI13" s="300">
+      <c r="AI13" s="306">
         <f>IF(P27="","",P27)</f>
         <v/>
       </c>
-      <c r="AJ13" s="300" t="inlineStr">
+      <c r="AJ13" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK13" s="300">
+      <c r="AK13" s="306">
         <f>IF(N27="","",N27)</f>
         <v/>
       </c>
-      <c r="AL13" s="284" t="n"/>
-      <c r="AM13" s="289" t="n"/>
-      <c r="AN13" s="289" t="n"/>
-      <c r="AO13" s="289" t="n"/>
-      <c r="AP13" s="289" t="n"/>
-      <c r="AQ13" s="289" t="n"/>
-      <c r="AR13" s="289" t="n"/>
-      <c r="AS13" s="301" t="n"/>
-      <c r="AV13" s="289" t="n"/>
-      <c r="AW13" s="291" t="n"/>
-      <c r="AX13" s="289" t="n"/>
+      <c r="AL13" s="286" t="n"/>
+      <c r="AM13" s="291" t="n"/>
+      <c r="AN13" s="291" t="n"/>
+      <c r="AO13" s="291" t="n"/>
+      <c r="AP13" s="291" t="n"/>
+      <c r="AQ13" s="291" t="n"/>
+      <c r="AR13" s="291" t="n"/>
+      <c r="AS13" s="308" t="n"/>
+      <c r="AV13" s="291" t="n"/>
+      <c r="AW13" s="293" t="n"/>
+      <c r="AX13" s="291" t="n"/>
       <c r="AZ13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="BA13" s="6" t="n"/>
     </row>
     <row r="14" ht="46.9" customHeight="1" s="257">
-      <c r="A14" s="272" t="n"/>
-      <c r="B14" s="273" t="n">
+      <c r="A14" s="274" t="n"/>
+      <c r="B14" s="275" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="273">
+      <c r="C14" s="275">
         <f>AX14</f>
         <v/>
       </c>
-      <c r="D14" s="274" t="n"/>
-      <c r="E14" s="275">
+      <c r="D14" s="276" t="n"/>
+      <c r="E14" s="277">
         <f>IF(E15="","",IF(E15="☂","☂",IF(E15&gt;G15,"○",IF(E15=G15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F14" s="293" t="n"/>
-      <c r="G14" s="294" t="n"/>
-      <c r="H14" s="275">
+      <c r="F14" s="297" t="n"/>
+      <c r="G14" s="298" t="n"/>
+      <c r="H14" s="309">
         <f>IF(H15="","",IF(H15="☂","☂",IF(H15&gt;J15,"○",IF(H15=J15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I14" s="293" t="n"/>
-      <c r="J14" s="294" t="n"/>
-      <c r="K14" s="275">
+      <c r="I14" s="297" t="n"/>
+      <c r="J14" s="298" t="n"/>
+      <c r="K14" s="309">
         <f>IF(K15="","",IF(K15="☂","☂",IF(K15&gt;M15,"○",IF(K15=M15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L14" s="293" t="n"/>
-      <c r="M14" s="294" t="n"/>
-      <c r="N14" s="276">
+      <c r="L14" s="297" t="n"/>
+      <c r="M14" s="298" t="n"/>
+      <c r="N14" s="278">
         <f>IF(N15="","",IF(N15="☂","☂",IF(N15&gt;P15,"○",IF(N15=P15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O14" s="303" t="n"/>
-      <c r="P14" s="304" t="n"/>
-      <c r="Q14" s="275" t="n"/>
-      <c r="R14" s="295" t="n"/>
-      <c r="S14" s="270" t="n"/>
-      <c r="T14" s="276">
+      <c r="O14" s="312" t="n"/>
+      <c r="P14" s="313" t="n"/>
+      <c r="Q14" s="309" t="n"/>
+      <c r="R14" s="300" t="n"/>
+      <c r="S14" s="272" t="n"/>
+      <c r="T14" s="278">
         <f>IF(T15="","",IF(T15="☂","☂",IF(T15&gt;V15,"○",IF(T15=V15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U14" s="297" t="n"/>
-      <c r="V14" s="298" t="n"/>
-      <c r="W14" s="276">
+      <c r="U14" s="302" t="n"/>
+      <c r="V14" s="303" t="n"/>
+      <c r="W14" s="278">
         <f>IF(W15="","",IF(W15="☂","☂",IF(W15&gt;Y15,"○",IF(W15=Y15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X14" s="297" t="n"/>
-      <c r="Y14" s="298" t="n"/>
-      <c r="Z14" s="276">
+      <c r="X14" s="302" t="n"/>
+      <c r="Y14" s="303" t="n"/>
+      <c r="Z14" s="278">
         <f>IF(Z15="","",IF(Z15="☂","☂",IF(Z15&gt;AB15,"○",IF(Z15=AB15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA14" s="297" t="n"/>
-      <c r="AB14" s="298" t="n"/>
-      <c r="AC14" s="276">
+      <c r="AA14" s="302" t="n"/>
+      <c r="AB14" s="303" t="n"/>
+      <c r="AC14" s="278">
         <f>IF(AC15="","",IF(AC15="☂","☂",IF(AC15&gt;AE15,"○",IF(AC15=AE15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD14" s="297" t="n"/>
-      <c r="AE14" s="298" t="n"/>
-      <c r="AF14" s="276">
+      <c r="AD14" s="302" t="n"/>
+      <c r="AE14" s="303" t="n"/>
+      <c r="AF14" s="278">
         <f>IF(AF15="","",IF(AF15="☂","☂",IF(AF15&gt;AH15,"○",IF(AF15=AH15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG14" s="297" t="n"/>
-      <c r="AH14" s="298" t="n"/>
-      <c r="AI14" s="276">
+      <c r="AG14" s="302" t="n"/>
+      <c r="AH14" s="303" t="n"/>
+      <c r="AI14" s="278">
         <f>IF(AI15="","",IF(AI15="☂","☂",IF(AI15&gt;AK15,"○",IF(AI15=AK15,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ14" s="297" t="n"/>
-      <c r="AK14" s="298" t="n"/>
-      <c r="AL14" s="279">
+      <c r="AJ14" s="302" t="n"/>
+      <c r="AK14" s="303" t="n"/>
+      <c r="AL14" s="281">
         <f>COUNTIF(E14:AK14,"○")</f>
         <v/>
       </c>
-      <c r="AM14" s="280">
+      <c r="AM14" s="282">
         <f>COUNTIF(E14:AK14,"△")</f>
         <v/>
       </c>
-      <c r="AN14" s="280">
+      <c r="AN14" s="282">
         <f>COUNTIF(E14:AK14,"×")</f>
         <v/>
       </c>
-      <c r="AO14" s="281">
+      <c r="AO14" s="283">
         <f>AL14*3+AM14*1</f>
         <v/>
       </c>
-      <c r="AP14" s="280">
+      <c r="AP14" s="282">
         <f>SUM(G15,J15,M15,P15,S15,V15,Y15,AB15,AK15)</f>
         <v/>
       </c>
-      <c r="AQ14" s="280">
+      <c r="AQ14" s="282">
         <f>SUM(E15,H15,K15,N15,Q15,T15,W15,Z15,AI15)</f>
         <v/>
       </c>
-      <c r="AR14" s="280">
+      <c r="AR14" s="282">
         <f>$AY$21-AL14-AM14-AN14</f>
         <v/>
       </c>
-      <c r="AS14" s="282">
+      <c r="AS14" s="284">
         <f>IFERROR(_xlfn.RANK.EQ(AO14,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4560,237 +4624,237 @@
       <c r="BA14" s="6" t="n"/>
     </row>
     <row r="15" ht="46.9" customHeight="1" s="257">
-      <c r="A15" s="283" t="n"/>
-      <c r="B15" s="284" t="n"/>
-      <c r="C15" s="285" t="n"/>
-      <c r="D15" s="286" t="n"/>
-      <c r="E15" s="302" t="n"/>
-      <c r="F15" s="288" t="inlineStr">
+      <c r="A15" s="285" t="n"/>
+      <c r="B15" s="286" t="n"/>
+      <c r="C15" s="287" t="n"/>
+      <c r="D15" s="288" t="n"/>
+      <c r="E15" s="310" t="n"/>
+      <c r="F15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="302" t="n"/>
-      <c r="H15" s="302" t="n"/>
-      <c r="I15" s="288" t="inlineStr">
+      <c r="G15" s="311" t="n"/>
+      <c r="H15" s="311" t="n"/>
+      <c r="I15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="302" t="n"/>
-      <c r="K15" s="302" t="n"/>
-      <c r="L15" s="288" t="inlineStr">
+      <c r="J15" s="311" t="n"/>
+      <c r="K15" s="311" t="n"/>
+      <c r="L15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="302" t="n"/>
-      <c r="N15" s="302" t="n"/>
-      <c r="O15" s="288" t="inlineStr">
+      <c r="M15" s="311" t="n"/>
+      <c r="N15" s="311" t="n"/>
+      <c r="O15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P15" s="302" t="n"/>
-      <c r="Q15" s="285" t="n"/>
-      <c r="R15" s="271" t="n"/>
-      <c r="S15" s="286" t="n"/>
-      <c r="T15" s="288">
+      <c r="P15" s="311" t="n"/>
+      <c r="Q15" s="287" t="n"/>
+      <c r="R15" s="273" t="n"/>
+      <c r="S15" s="288" t="n"/>
+      <c r="T15" s="290">
         <f>IF(S17="","",S17)</f>
         <v/>
       </c>
-      <c r="U15" s="288" t="inlineStr">
+      <c r="U15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V15" s="288">
+      <c r="V15" s="290">
         <f>IF(Q17="","",Q17)</f>
         <v/>
       </c>
-      <c r="W15" s="288">
+      <c r="W15" s="290">
         <f>IF(S19="","",S19)</f>
         <v/>
       </c>
-      <c r="X15" s="288" t="inlineStr">
+      <c r="X15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y15" s="288">
+      <c r="Y15" s="290">
         <f>IF(Q19="","",Q19)</f>
         <v/>
       </c>
-      <c r="Z15" s="288">
+      <c r="Z15" s="290">
         <f>IF(S21="","",S21)</f>
         <v/>
       </c>
-      <c r="AA15" s="288" t="inlineStr">
+      <c r="AA15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB15" s="288">
+      <c r="AB15" s="290">
         <f>IF(Q21="","",Q21)</f>
         <v/>
       </c>
-      <c r="AC15" s="288">
+      <c r="AC15" s="290">
         <f>IF(S23="","",S23)</f>
         <v/>
       </c>
-      <c r="AD15" s="288" t="inlineStr">
+      <c r="AD15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE15" s="288">
+      <c r="AE15" s="290">
         <f>IF(Q31="","",Q31)</f>
         <v/>
       </c>
-      <c r="AF15" s="288">
+      <c r="AF15" s="290">
         <f>IF(S25="","",S25)</f>
         <v/>
       </c>
-      <c r="AG15" s="288" t="inlineStr">
+      <c r="AG15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH15" s="288">
+      <c r="AH15" s="290">
         <f>IF(Q25="","",Q25)</f>
         <v/>
       </c>
-      <c r="AI15" s="288">
+      <c r="AI15" s="290">
         <f>IF(S27="","",S27)</f>
         <v/>
       </c>
-      <c r="AJ15" s="288" t="inlineStr">
+      <c r="AJ15" s="290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK15" s="288">
+      <c r="AK15" s="290">
         <f>IF(Q27="","",Q27)</f>
         <v/>
       </c>
-      <c r="AL15" s="284" t="n"/>
-      <c r="AM15" s="289" t="n"/>
-      <c r="AN15" s="289" t="n"/>
-      <c r="AO15" s="289" t="n"/>
-      <c r="AP15" s="289" t="n"/>
-      <c r="AQ15" s="289" t="n"/>
-      <c r="AR15" s="289" t="n"/>
-      <c r="AS15" s="301" t="n"/>
-      <c r="AV15" s="289" t="n"/>
-      <c r="AW15" s="291" t="n"/>
-      <c r="AX15" s="289" t="n"/>
+      <c r="AL15" s="286" t="n"/>
+      <c r="AM15" s="291" t="n"/>
+      <c r="AN15" s="291" t="n"/>
+      <c r="AO15" s="291" t="n"/>
+      <c r="AP15" s="291" t="n"/>
+      <c r="AQ15" s="291" t="n"/>
+      <c r="AR15" s="291" t="n"/>
+      <c r="AS15" s="308" t="n"/>
+      <c r="AV15" s="291" t="n"/>
+      <c r="AW15" s="293" t="n"/>
+      <c r="AX15" s="291" t="n"/>
       <c r="AZ15" s="5" t="n">
         <v>10</v>
       </c>
       <c r="BA15" s="6" t="n"/>
     </row>
     <row r="16" ht="46.9" customHeight="1" s="257">
-      <c r="A16" s="272" t="n"/>
-      <c r="B16" s="273" t="n">
+      <c r="A16" s="294" t="n"/>
+      <c r="B16" s="295" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="273">
+      <c r="C16" s="295">
         <f>AX16</f>
         <v/>
       </c>
-      <c r="D16" s="274" t="n"/>
-      <c r="E16" s="292">
+      <c r="D16" s="276" t="n"/>
+      <c r="E16" s="296">
         <f>IF(E17="","",IF(E17="☂","☂",IF(E17&gt;G17,"○",IF(E17=G17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F16" s="293" t="n"/>
-      <c r="G16" s="294" t="n"/>
-      <c r="H16" s="292">
+      <c r="F16" s="297" t="n"/>
+      <c r="G16" s="298" t="n"/>
+      <c r="H16" s="299">
         <f>IF(H17="","",IF(H17="☂","☂",IF(H17&gt;J17,"○",IF(H17=J17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I16" s="293" t="n"/>
-      <c r="J16" s="294" t="n"/>
-      <c r="K16" s="292">
+      <c r="I16" s="297" t="n"/>
+      <c r="J16" s="298" t="n"/>
+      <c r="K16" s="299">
         <f>IF(K17="","",IF(K17="☂","☂",IF(K17&gt;M17,"○",IF(K17=M17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L16" s="293" t="n"/>
-      <c r="M16" s="294" t="n"/>
-      <c r="N16" s="296">
+      <c r="L16" s="297" t="n"/>
+      <c r="M16" s="298" t="n"/>
+      <c r="N16" s="301">
         <f>IF(N17="","",IF(N17="☂","☂",IF(N17&gt;P17,"○",IF(N17=P17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O16" s="303" t="n"/>
-      <c r="P16" s="304" t="n"/>
-      <c r="Q16" s="296">
+      <c r="O16" s="312" t="n"/>
+      <c r="P16" s="313" t="n"/>
+      <c r="Q16" s="301">
         <f>IF(Q17="","",IF(Q17="☂","☂",IF(Q17&gt;S17,"○",IF(Q17=S17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R16" s="303" t="n"/>
-      <c r="S16" s="304" t="n"/>
-      <c r="T16" s="292" t="n"/>
-      <c r="U16" s="295" t="n"/>
-      <c r="V16" s="270" t="n"/>
-      <c r="W16" s="296">
+      <c r="R16" s="312" t="n"/>
+      <c r="S16" s="313" t="n"/>
+      <c r="T16" s="299" t="n"/>
+      <c r="U16" s="300" t="n"/>
+      <c r="V16" s="272" t="n"/>
+      <c r="W16" s="301">
         <f>IF(W17="","",IF(W17="☂","☂",IF(W17&gt;Y17,"○",IF(W17=Y17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X16" s="297" t="n"/>
-      <c r="Y16" s="298" t="n"/>
-      <c r="Z16" s="296">
+      <c r="X16" s="302" t="n"/>
+      <c r="Y16" s="303" t="n"/>
+      <c r="Z16" s="301">
         <f>IF(Z17="","",IF(Z17="☂","☂",IF(Z17&gt;AB17,"○",IF(Z17=AB17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA16" s="297" t="n"/>
-      <c r="AB16" s="298" t="n"/>
-      <c r="AC16" s="296">
+      <c r="AA16" s="302" t="n"/>
+      <c r="AB16" s="303" t="n"/>
+      <c r="AC16" s="301">
         <f>IF(AC17="","",IF(AC17="☂","☂",IF(AC17&gt;AE17,"○",IF(AC17=AE17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD16" s="297" t="n"/>
-      <c r="AE16" s="298" t="n"/>
-      <c r="AF16" s="296">
+      <c r="AD16" s="302" t="n"/>
+      <c r="AE16" s="303" t="n"/>
+      <c r="AF16" s="301">
         <f>IF(AF17="","",IF(AF17="☂","☂",IF(AF17&gt;AH17,"○",IF(AF17=AH17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG16" s="297" t="n"/>
-      <c r="AH16" s="298" t="n"/>
-      <c r="AI16" s="296">
+      <c r="AG16" s="302" t="n"/>
+      <c r="AH16" s="303" t="n"/>
+      <c r="AI16" s="301">
         <f>IF(AI17="","",IF(AI17="☂","☂",IF(AI17&gt;AK17,"○",IF(AI17=AK17,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ16" s="297" t="n"/>
-      <c r="AK16" s="298" t="n"/>
-      <c r="AL16" s="279">
+      <c r="AJ16" s="302" t="n"/>
+      <c r="AK16" s="303" t="n"/>
+      <c r="AL16" s="281">
         <f>COUNTIF(E16:AK16,"○")</f>
         <v/>
       </c>
-      <c r="AM16" s="280">
+      <c r="AM16" s="282">
         <f>COUNTIF(E16:AK16,"△")</f>
         <v/>
       </c>
-      <c r="AN16" s="280">
+      <c r="AN16" s="282">
         <f>COUNTIF(E16:AK16,"×")</f>
         <v/>
       </c>
-      <c r="AO16" s="281">
+      <c r="AO16" s="283">
         <f>AL16*3+AM16*1</f>
         <v/>
       </c>
-      <c r="AP16" s="280">
+      <c r="AP16" s="282">
         <f>SUM(G17,J17,M17,P17,S17,V17,Y17,AB17,AK17)</f>
         <v/>
       </c>
-      <c r="AQ16" s="280">
+      <c r="AQ16" s="282">
         <f>SUM(E17,H17,K17,N17,Q17,T17,W17,Z17,AI17)</f>
         <v/>
       </c>
-      <c r="AR16" s="280">
+      <c r="AR16" s="282">
         <f>$AY$21-AL16-AM16-AN16</f>
         <v/>
       </c>
-      <c r="AS16" s="282">
+      <c r="AS16" s="284">
         <f>IFERROR(_xlfn.RANK.EQ(AO16,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -4810,231 +4874,231 @@
       <c r="BA16" s="6" t="n"/>
     </row>
     <row r="17" ht="46.9" customHeight="1" s="257">
-      <c r="A17" s="283" t="n"/>
-      <c r="B17" s="284" t="n"/>
-      <c r="C17" s="285" t="n"/>
-      <c r="D17" s="286" t="n"/>
-      <c r="E17" s="299" t="n"/>
-      <c r="F17" s="300" t="inlineStr">
+      <c r="A17" s="304" t="n"/>
+      <c r="B17" s="286" t="n"/>
+      <c r="C17" s="287" t="n"/>
+      <c r="D17" s="288" t="n"/>
+      <c r="E17" s="305" t="n"/>
+      <c r="F17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="299" t="n"/>
-      <c r="H17" s="299" t="n"/>
-      <c r="I17" s="300" t="inlineStr">
+      <c r="G17" s="307" t="n"/>
+      <c r="H17" s="307" t="n"/>
+      <c r="I17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="299" t="n"/>
-      <c r="K17" s="299" t="n"/>
-      <c r="L17" s="300" t="inlineStr">
+      <c r="J17" s="307" t="n"/>
+      <c r="K17" s="307" t="n"/>
+      <c r="L17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M17" s="299" t="n"/>
-      <c r="N17" s="299" t="n"/>
-      <c r="O17" s="300" t="inlineStr">
+      <c r="M17" s="307" t="n"/>
+      <c r="N17" s="307" t="n"/>
+      <c r="O17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P17" s="299" t="n"/>
-      <c r="Q17" s="299" t="n"/>
-      <c r="R17" s="300" t="inlineStr">
+      <c r="P17" s="307" t="n"/>
+      <c r="Q17" s="307" t="n"/>
+      <c r="R17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S17" s="299" t="n"/>
-      <c r="T17" s="285" t="n"/>
-      <c r="U17" s="271" t="n"/>
-      <c r="V17" s="286" t="n"/>
-      <c r="W17" s="300">
+      <c r="S17" s="307" t="n"/>
+      <c r="T17" s="287" t="n"/>
+      <c r="U17" s="273" t="n"/>
+      <c r="V17" s="288" t="n"/>
+      <c r="W17" s="306">
         <f>IF(V19="","",V19)</f>
         <v/>
       </c>
-      <c r="X17" s="300" t="inlineStr">
+      <c r="X17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y17" s="300">
+      <c r="Y17" s="306">
         <f>IF(T19="","",T19)</f>
         <v/>
       </c>
-      <c r="Z17" s="300">
+      <c r="Z17" s="306">
         <f>IF(V21="","",V21)</f>
         <v/>
       </c>
-      <c r="AA17" s="300" t="inlineStr">
+      <c r="AA17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB17" s="300">
+      <c r="AB17" s="306">
         <f>IF(T21="","",T21)</f>
         <v/>
       </c>
-      <c r="AC17" s="300">
+      <c r="AC17" s="306">
         <f>IF(V23="","",V23)</f>
         <v/>
       </c>
-      <c r="AD17" s="300" t="inlineStr">
+      <c r="AD17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE17" s="300">
+      <c r="AE17" s="306">
         <f>IF(T23="","",T23)</f>
         <v/>
       </c>
-      <c r="AF17" s="300">
+      <c r="AF17" s="306">
         <f>IF(V25="","",V25)</f>
         <v/>
       </c>
-      <c r="AG17" s="300" t="inlineStr">
+      <c r="AG17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH17" s="300">
+      <c r="AH17" s="306">
         <f>IF(T25="","",T25)</f>
         <v/>
       </c>
-      <c r="AI17" s="300">
+      <c r="AI17" s="306">
         <f>IF(V27="","",V27)</f>
         <v/>
       </c>
-      <c r="AJ17" s="300" t="inlineStr">
+      <c r="AJ17" s="306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK17" s="300">
+      <c r="AK17" s="306">
         <f>IF(T27="","",T27)</f>
         <v/>
       </c>
-      <c r="AL17" s="284" t="n"/>
-      <c r="AM17" s="289" t="n"/>
-      <c r="AN17" s="289" t="n"/>
-      <c r="AO17" s="289" t="n"/>
-      <c r="AP17" s="289" t="n"/>
-      <c r="AQ17" s="289" t="n"/>
-      <c r="AR17" s="289" t="n"/>
-      <c r="AS17" s="301" t="n"/>
-      <c r="AV17" s="289" t="n"/>
-      <c r="AW17" s="291" t="n"/>
-      <c r="AX17" s="289" t="n"/>
+      <c r="AL17" s="286" t="n"/>
+      <c r="AM17" s="291" t="n"/>
+      <c r="AN17" s="291" t="n"/>
+      <c r="AO17" s="291" t="n"/>
+      <c r="AP17" s="291" t="n"/>
+      <c r="AQ17" s="291" t="n"/>
+      <c r="AR17" s="291" t="n"/>
+      <c r="AS17" s="308" t="n"/>
+      <c r="AV17" s="291" t="n"/>
+      <c r="AW17" s="293" t="n"/>
+      <c r="AX17" s="291" t="n"/>
       <c r="AZ17" s="5" t="n">
         <v>12</v>
       </c>
       <c r="BA17" s="6" t="n"/>
     </row>
     <row r="18" ht="46.9" customHeight="1" s="257">
-      <c r="A18" s="305" t="n"/>
-      <c r="B18" s="306" t="n">
+      <c r="A18" s="314" t="n"/>
+      <c r="B18" s="315" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="306">
+      <c r="C18" s="315">
         <f>AX18</f>
         <v/>
       </c>
-      <c r="D18" s="274" t="n"/>
-      <c r="E18" s="306">
+      <c r="D18" s="276" t="n"/>
+      <c r="E18" s="314">
         <f>IF(E19="","",IF(E19="☂","☂",IF(E19&gt;G19,"○",IF(E19=G19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F18" s="293" t="n"/>
-      <c r="G18" s="294" t="n"/>
-      <c r="H18" s="306">
+      <c r="F18" s="297" t="n"/>
+      <c r="G18" s="298" t="n"/>
+      <c r="H18" s="315">
         <f>IF(H19="","",IF(H19="☂","☂",IF(H19&gt;J19,"○",IF(H19=J19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I18" s="293" t="n"/>
-      <c r="J18" s="294" t="n"/>
-      <c r="K18" s="306">
+      <c r="I18" s="297" t="n"/>
+      <c r="J18" s="298" t="n"/>
+      <c r="K18" s="315">
         <f>IF(K19="","",IF(K19="☂","☂",IF(K19&gt;M19,"○",IF(K19=M19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L18" s="293" t="n"/>
-      <c r="M18" s="294" t="n"/>
-      <c r="N18" s="307">
+      <c r="L18" s="297" t="n"/>
+      <c r="M18" s="298" t="n"/>
+      <c r="N18" s="316">
         <f>IF(N19="","",IF(N19="☂","☂",IF(N19&gt;P19,"○",IF(N19=P19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O18" s="303" t="n"/>
-      <c r="P18" s="304" t="n"/>
-      <c r="Q18" s="307">
+      <c r="O18" s="312" t="n"/>
+      <c r="P18" s="313" t="n"/>
+      <c r="Q18" s="316">
         <f>IF(Q19="","",IF(Q19="☂","☂",IF(Q19&gt;S19,"○",IF(Q19=S19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R18" s="303" t="n"/>
-      <c r="S18" s="304" t="n"/>
-      <c r="T18" s="307">
+      <c r="R18" s="312" t="n"/>
+      <c r="S18" s="313" t="n"/>
+      <c r="T18" s="316">
         <f>IF(T19="","",IF(T19="☂","☂",IF(T19&gt;V19,"○",IF(T19=V19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U18" s="303" t="n"/>
-      <c r="V18" s="304" t="n"/>
-      <c r="W18" s="306" t="n"/>
-      <c r="X18" s="295" t="n"/>
-      <c r="Y18" s="270" t="n"/>
-      <c r="Z18" s="307">
+      <c r="U18" s="312" t="n"/>
+      <c r="V18" s="313" t="n"/>
+      <c r="W18" s="315" t="n"/>
+      <c r="X18" s="300" t="n"/>
+      <c r="Y18" s="272" t="n"/>
+      <c r="Z18" s="316">
         <f>IF(Z19="","",IF(Z19="☂","☂",IF(Z19&gt;AB19,"○",IF(Z19=AB19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA18" s="297" t="n"/>
-      <c r="AB18" s="298" t="n"/>
-      <c r="AC18" s="307">
+      <c r="AA18" s="302" t="n"/>
+      <c r="AB18" s="303" t="n"/>
+      <c r="AC18" s="316">
         <f>IF(AC19="","",IF(AC19="☂","☂",IF(AC19&gt;AE19,"○",IF(AC19=AE19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD18" s="297" t="n"/>
-      <c r="AE18" s="298" t="n"/>
-      <c r="AF18" s="307">
+      <c r="AD18" s="302" t="n"/>
+      <c r="AE18" s="303" t="n"/>
+      <c r="AF18" s="316">
         <f>IF(AF19="","",IF(AF19="☂","☂",IF(AF19&gt;AH19,"○",IF(AF19=AH19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG18" s="297" t="n"/>
-      <c r="AH18" s="298" t="n"/>
-      <c r="AI18" s="307">
+      <c r="AG18" s="302" t="n"/>
+      <c r="AH18" s="303" t="n"/>
+      <c r="AI18" s="316">
         <f>IF(AI19="","",IF(AI19="☂","☂",IF(AI19&gt;AK19,"○",IF(AI19=AK19,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ18" s="297" t="n"/>
-      <c r="AK18" s="298" t="n"/>
-      <c r="AL18" s="308">
+      <c r="AJ18" s="302" t="n"/>
+      <c r="AK18" s="303" t="n"/>
+      <c r="AL18" s="317">
         <f>COUNTIF(E18:AK18,"○")</f>
         <v/>
       </c>
-      <c r="AM18" s="309">
+      <c r="AM18" s="318">
         <f>COUNTIF(E18:AK18,"△")</f>
         <v/>
       </c>
-      <c r="AN18" s="309">
+      <c r="AN18" s="318">
         <f>COUNTIF(E18:AK18,"×")</f>
         <v/>
       </c>
-      <c r="AO18" s="309">
+      <c r="AO18" s="318">
         <f>AL18*3+AM18*1</f>
         <v/>
       </c>
-      <c r="AP18" s="309">
+      <c r="AP18" s="318">
         <f>SUM(G19,J19,M19,P19,S19,V19,Y19,AB19,AK19)</f>
         <v/>
       </c>
-      <c r="AQ18" s="309">
+      <c r="AQ18" s="318">
         <f>SUM(E19,H19,K19,N19,Q19,T19,W19,Z19,AI19)</f>
         <v/>
       </c>
-      <c r="AR18" s="309">
+      <c r="AR18" s="318">
         <f>$AY$21-AL18-AM18-AN18</f>
         <v/>
       </c>
-      <c r="AS18" s="310">
+      <c r="AS18" s="319">
         <f>IFERROR(_xlfn.RANK.EQ(AO18,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5052,225 +5116,225 @@
       <c r="BA18" s="6" t="n"/>
     </row>
     <row r="19" ht="46.9" customHeight="1" s="257">
-      <c r="A19" s="305" t="n"/>
-      <c r="B19" s="284" t="n"/>
-      <c r="C19" s="285" t="n"/>
-      <c r="D19" s="286" t="n"/>
-      <c r="E19" s="311" t="n"/>
-      <c r="F19" s="306" t="inlineStr">
+      <c r="A19" s="314" t="n"/>
+      <c r="B19" s="286" t="n"/>
+      <c r="C19" s="287" t="n"/>
+      <c r="D19" s="288" t="n"/>
+      <c r="E19" s="320" t="n"/>
+      <c r="F19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="311" t="n"/>
-      <c r="H19" s="311" t="n"/>
-      <c r="I19" s="306" t="inlineStr">
+      <c r="G19" s="321" t="n"/>
+      <c r="H19" s="321" t="n"/>
+      <c r="I19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J19" s="311" t="n"/>
-      <c r="K19" s="311" t="n"/>
-      <c r="L19" s="306" t="inlineStr">
+      <c r="J19" s="321" t="n"/>
+      <c r="K19" s="321" t="n"/>
+      <c r="L19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="311" t="n"/>
-      <c r="N19" s="311" t="n"/>
-      <c r="O19" s="306" t="inlineStr">
+      <c r="M19" s="321" t="n"/>
+      <c r="N19" s="321" t="n"/>
+      <c r="O19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P19" s="311" t="n"/>
-      <c r="Q19" s="311" t="n"/>
-      <c r="R19" s="306" t="inlineStr">
+      <c r="P19" s="321" t="n"/>
+      <c r="Q19" s="321" t="n"/>
+      <c r="R19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S19" s="311" t="n"/>
-      <c r="T19" s="311" t="n"/>
-      <c r="U19" s="306" t="inlineStr">
+      <c r="S19" s="321" t="n"/>
+      <c r="T19" s="321" t="n"/>
+      <c r="U19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V19" s="311" t="n"/>
-      <c r="W19" s="285" t="n"/>
-      <c r="X19" s="271" t="n"/>
-      <c r="Y19" s="286" t="n"/>
-      <c r="Z19" s="306">
+      <c r="V19" s="321" t="n"/>
+      <c r="W19" s="287" t="n"/>
+      <c r="X19" s="273" t="n"/>
+      <c r="Y19" s="288" t="n"/>
+      <c r="Z19" s="315">
         <f>IF(Y21="","",Y21)</f>
         <v/>
       </c>
-      <c r="AA19" s="306" t="inlineStr">
+      <c r="AA19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB19" s="306">
+      <c r="AB19" s="315">
         <f>IF(W21="","",W21)</f>
         <v/>
       </c>
-      <c r="AC19" s="306">
+      <c r="AC19" s="315">
         <f>IF(Y23="","",Y23)</f>
         <v/>
       </c>
-      <c r="AD19" s="306" t="inlineStr">
+      <c r="AD19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE19" s="306">
+      <c r="AE19" s="315">
         <f>IF(W23="","",W23)</f>
         <v/>
       </c>
-      <c r="AF19" s="306">
+      <c r="AF19" s="315">
         <f>IF(Y25="","",Y25)</f>
         <v/>
       </c>
-      <c r="AG19" s="306" t="inlineStr">
+      <c r="AG19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH19" s="306">
+      <c r="AH19" s="315">
         <f>IF(W25="","",W25)</f>
         <v/>
       </c>
-      <c r="AI19" s="306">
+      <c r="AI19" s="315">
         <f>IF(Y27="","",Y27)</f>
         <v/>
       </c>
-      <c r="AJ19" s="306" t="inlineStr">
+      <c r="AJ19" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK19" s="306">
+      <c r="AK19" s="315">
         <f>IF(W27="","",W27)</f>
         <v/>
       </c>
-      <c r="AL19" s="284" t="n"/>
-      <c r="AM19" s="289" t="n"/>
-      <c r="AN19" s="289" t="n"/>
-      <c r="AO19" s="289" t="n"/>
-      <c r="AP19" s="289" t="n"/>
-      <c r="AQ19" s="289" t="n"/>
-      <c r="AR19" s="289" t="n"/>
-      <c r="AS19" s="301" t="n"/>
-      <c r="AV19" s="289" t="n"/>
-      <c r="AW19" s="291" t="n"/>
-      <c r="AX19" s="289" t="n"/>
+      <c r="AL19" s="286" t="n"/>
+      <c r="AM19" s="291" t="n"/>
+      <c r="AN19" s="291" t="n"/>
+      <c r="AO19" s="291" t="n"/>
+      <c r="AP19" s="291" t="n"/>
+      <c r="AQ19" s="291" t="n"/>
+      <c r="AR19" s="291" t="n"/>
+      <c r="AS19" s="308" t="n"/>
+      <c r="AV19" s="291" t="n"/>
+      <c r="AW19" s="293" t="n"/>
+      <c r="AX19" s="291" t="n"/>
       <c r="AZ19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="BA19" s="6" t="n"/>
     </row>
     <row r="20" ht="46.9" customHeight="1" s="257">
-      <c r="A20" s="305" t="n"/>
-      <c r="B20" s="306" t="n">
+      <c r="A20" s="314" t="n"/>
+      <c r="B20" s="315" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="306">
+      <c r="C20" s="315">
         <f>AX20</f>
         <v/>
       </c>
-      <c r="D20" s="274" t="n"/>
-      <c r="E20" s="306">
+      <c r="D20" s="276" t="n"/>
+      <c r="E20" s="314">
         <f>IF(E21="","",IF(E21="☂","☂",IF(E21&gt;G21,"○",IF(E21=G21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F20" s="293" t="n"/>
-      <c r="G20" s="294" t="n"/>
-      <c r="H20" s="306">
+      <c r="F20" s="297" t="n"/>
+      <c r="G20" s="298" t="n"/>
+      <c r="H20" s="315">
         <f>IF(H21="","",IF(H21="☂","☂",IF(H21&gt;J21,"○",IF(H21=J21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I20" s="293" t="n"/>
-      <c r="J20" s="294" t="n"/>
-      <c r="K20" s="306">
+      <c r="I20" s="297" t="n"/>
+      <c r="J20" s="298" t="n"/>
+      <c r="K20" s="315">
         <f>IF(K21="","",IF(K21="☂","☂",IF(K21&gt;M21,"○",IF(K21=M21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L20" s="293" t="n"/>
-      <c r="M20" s="294" t="n"/>
-      <c r="N20" s="307">
+      <c r="L20" s="297" t="n"/>
+      <c r="M20" s="298" t="n"/>
+      <c r="N20" s="316">
         <f>IF(N21="","",IF(N21="☂","☂",IF(N21&gt;P21,"○",IF(N21=P21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O20" s="303" t="n"/>
-      <c r="P20" s="304" t="n"/>
-      <c r="Q20" s="307">
+      <c r="O20" s="312" t="n"/>
+      <c r="P20" s="313" t="n"/>
+      <c r="Q20" s="316">
         <f>IF(Q21="","",IF(Q21="☂","☂",IF(Q21&gt;S21,"○",IF(Q21=S21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R20" s="303" t="n"/>
-      <c r="S20" s="304" t="n"/>
-      <c r="T20" s="307">
+      <c r="R20" s="312" t="n"/>
+      <c r="S20" s="313" t="n"/>
+      <c r="T20" s="316">
         <f>IF(T21="","",IF(T21="☂","☂",IF(T21&gt;V21,"○",IF(T21=V21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U20" s="303" t="n"/>
-      <c r="V20" s="304" t="n"/>
-      <c r="W20" s="307">
+      <c r="U20" s="312" t="n"/>
+      <c r="V20" s="313" t="n"/>
+      <c r="W20" s="316">
         <f>IF(W21="","",IF(W21="☂","☂",IF(W21&gt;Y21,"○",IF(W21=Y21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X20" s="303" t="n"/>
-      <c r="Y20" s="304" t="n"/>
-      <c r="Z20" s="306" t="n"/>
-      <c r="AA20" s="295" t="n"/>
-      <c r="AB20" s="270" t="n"/>
-      <c r="AC20" s="307">
+      <c r="X20" s="312" t="n"/>
+      <c r="Y20" s="313" t="n"/>
+      <c r="Z20" s="315" t="n"/>
+      <c r="AA20" s="300" t="n"/>
+      <c r="AB20" s="272" t="n"/>
+      <c r="AC20" s="316">
         <f>IF(AC21="","",IF(AC21="☂","☂",IF(AC21&gt;AE21,"○",IF(AC21=AE21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD20" s="297" t="n"/>
-      <c r="AE20" s="298" t="n"/>
-      <c r="AF20" s="307">
+      <c r="AD20" s="302" t="n"/>
+      <c r="AE20" s="303" t="n"/>
+      <c r="AF20" s="316">
         <f>IF(AF21="","",IF(AF21="☂","☂",IF(AF21&gt;AH21,"○",IF(AF21=AH21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG20" s="297" t="n"/>
-      <c r="AH20" s="298" t="n"/>
-      <c r="AI20" s="307">
+      <c r="AG20" s="302" t="n"/>
+      <c r="AH20" s="303" t="n"/>
+      <c r="AI20" s="316">
         <f>IF(AI21="","",IF(AI21="☂","☂",IF(AI21&gt;AK21,"○",IF(AI21=AK21,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ20" s="297" t="n"/>
-      <c r="AK20" s="298" t="n"/>
-      <c r="AL20" s="308">
+      <c r="AJ20" s="302" t="n"/>
+      <c r="AK20" s="303" t="n"/>
+      <c r="AL20" s="317">
         <f>COUNTIF(E20:AK20,"○")</f>
         <v/>
       </c>
-      <c r="AM20" s="309">
+      <c r="AM20" s="318">
         <f>COUNTIF(E20:AK20,"△")</f>
         <v/>
       </c>
-      <c r="AN20" s="309">
+      <c r="AN20" s="318">
         <f>COUNTIF(E20:AK20,"×")</f>
         <v/>
       </c>
-      <c r="AO20" s="309">
+      <c r="AO20" s="318">
         <f>AL20*3+AM20*1</f>
         <v/>
       </c>
-      <c r="AP20" s="309">
+      <c r="AP20" s="318">
         <f>SUM(G21,J21,M21,P21,S21,V21,Y21,AB21,AK21)</f>
         <v/>
       </c>
-      <c r="AQ20" s="309">
+      <c r="AQ20" s="318">
         <f>SUM(E21,H21,K21,N21,Q21,T21,W21,Z21,AI21)</f>
         <v/>
       </c>
-      <c r="AR20" s="309">
+      <c r="AR20" s="318">
         <f>$AY$21-AL20-AM20-AN20</f>
         <v/>
       </c>
-      <c r="AS20" s="310">
+      <c r="AS20" s="319">
         <f>IFERROR(_xlfn.RANK.EQ(AO20,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5288,219 +5352,219 @@
       <c r="BA20" s="6" t="n"/>
     </row>
     <row r="21" ht="46.9" customHeight="1" s="257">
-      <c r="A21" s="305" t="n"/>
-      <c r="B21" s="312" t="n"/>
-      <c r="C21" s="285" t="n"/>
-      <c r="D21" s="286" t="n"/>
-      <c r="E21" s="311" t="n"/>
-      <c r="F21" s="306" t="inlineStr">
+      <c r="A21" s="314" t="n"/>
+      <c r="B21" s="322" t="n"/>
+      <c r="C21" s="287" t="n"/>
+      <c r="D21" s="288" t="n"/>
+      <c r="E21" s="320" t="n"/>
+      <c r="F21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="311" t="n"/>
-      <c r="H21" s="311" t="n"/>
-      <c r="I21" s="306" t="inlineStr">
+      <c r="G21" s="321" t="n"/>
+      <c r="H21" s="321" t="n"/>
+      <c r="I21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J21" s="311" t="n"/>
-      <c r="K21" s="311" t="n"/>
-      <c r="L21" s="306" t="inlineStr">
+      <c r="J21" s="321" t="n"/>
+      <c r="K21" s="321" t="n"/>
+      <c r="L21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="311" t="n"/>
-      <c r="N21" s="311" t="n"/>
-      <c r="O21" s="306" t="inlineStr">
+      <c r="M21" s="321" t="n"/>
+      <c r="N21" s="321" t="n"/>
+      <c r="O21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P21" s="311" t="n"/>
-      <c r="Q21" s="311" t="n"/>
-      <c r="R21" s="306" t="inlineStr">
+      <c r="P21" s="321" t="n"/>
+      <c r="Q21" s="321" t="n"/>
+      <c r="R21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S21" s="311" t="n"/>
-      <c r="T21" s="311" t="n"/>
-      <c r="U21" s="306" t="inlineStr">
+      <c r="S21" s="321" t="n"/>
+      <c r="T21" s="321" t="n"/>
+      <c r="U21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V21" s="311" t="n"/>
-      <c r="W21" s="311" t="n"/>
-      <c r="X21" s="306" t="inlineStr">
+      <c r="V21" s="321" t="n"/>
+      <c r="W21" s="321" t="n"/>
+      <c r="X21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y21" s="311" t="n"/>
-      <c r="Z21" s="285" t="n"/>
-      <c r="AA21" s="271" t="n"/>
-      <c r="AB21" s="286" t="n"/>
-      <c r="AC21" s="306">
+      <c r="Y21" s="321" t="n"/>
+      <c r="Z21" s="287" t="n"/>
+      <c r="AA21" s="273" t="n"/>
+      <c r="AB21" s="288" t="n"/>
+      <c r="AC21" s="315">
         <f>IF(AB23="","",AB23)</f>
         <v/>
       </c>
-      <c r="AD21" s="306" t="inlineStr">
+      <c r="AD21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE21" s="306">
+      <c r="AE21" s="315">
         <f>IF(Z23="","",Z23)</f>
         <v/>
       </c>
-      <c r="AF21" s="306">
+      <c r="AF21" s="315">
         <f>IF(AB25="","",AB25)</f>
         <v/>
       </c>
-      <c r="AG21" s="306" t="inlineStr">
+      <c r="AG21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH21" s="306">
+      <c r="AH21" s="315">
         <f>IF(Z25="","",Z25)</f>
         <v/>
       </c>
-      <c r="AI21" s="306">
+      <c r="AI21" s="315">
         <f>IF(AB27="","",AB27)</f>
         <v/>
       </c>
-      <c r="AJ21" s="306" t="inlineStr">
+      <c r="AJ21" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK21" s="306">
+      <c r="AK21" s="315">
         <f>IF(Z27="","",Z27)</f>
         <v/>
       </c>
-      <c r="AL21" s="284" t="n"/>
-      <c r="AM21" s="289" t="n"/>
-      <c r="AN21" s="289" t="n"/>
-      <c r="AO21" s="289" t="n"/>
-      <c r="AP21" s="289" t="n"/>
-      <c r="AQ21" s="289" t="n"/>
-      <c r="AR21" s="289" t="n"/>
-      <c r="AS21" s="301" t="n"/>
-      <c r="AV21" s="289" t="n"/>
-      <c r="AW21" s="291" t="n"/>
-      <c r="AX21" s="289" t="n"/>
+      <c r="AL21" s="286" t="n"/>
+      <c r="AM21" s="291" t="n"/>
+      <c r="AN21" s="291" t="n"/>
+      <c r="AO21" s="291" t="n"/>
+      <c r="AP21" s="291" t="n"/>
+      <c r="AQ21" s="291" t="n"/>
+      <c r="AR21" s="291" t="n"/>
+      <c r="AS21" s="308" t="n"/>
+      <c r="AV21" s="291" t="n"/>
+      <c r="AW21" s="293" t="n"/>
+      <c r="AX21" s="291" t="n"/>
       <c r="AY21" s="1">
         <f>COUNTA(AW6:AW21)</f>
         <v/>
       </c>
     </row>
     <row r="22" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A22" s="305" t="n"/>
-      <c r="B22" s="306" t="n">
+      <c r="A22" s="314" t="n"/>
+      <c r="B22" s="315" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="306">
+      <c r="C22" s="315">
         <f>AX22</f>
         <v/>
       </c>
-      <c r="D22" s="274" t="n"/>
-      <c r="E22" s="306">
+      <c r="D22" s="276" t="n"/>
+      <c r="E22" s="314">
         <f>IF(E23="","",IF(E23="☂","☂",IF(E23&gt;G23,"○",IF(E23=G23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F22" s="293" t="n"/>
-      <c r="G22" s="294" t="n"/>
-      <c r="H22" s="306">
+      <c r="F22" s="297" t="n"/>
+      <c r="G22" s="298" t="n"/>
+      <c r="H22" s="315">
         <f>IF(H23="","",IF(H23="☂","☂",IF(H23&gt;J23,"○",IF(H23=J23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I22" s="293" t="n"/>
-      <c r="J22" s="294" t="n"/>
-      <c r="K22" s="306">
+      <c r="I22" s="297" t="n"/>
+      <c r="J22" s="298" t="n"/>
+      <c r="K22" s="315">
         <f>IF(K23="","",IF(K23="☂","☂",IF(K23&gt;M23,"○",IF(K23=M23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L22" s="293" t="n"/>
-      <c r="M22" s="294" t="n"/>
-      <c r="N22" s="307">
+      <c r="L22" s="297" t="n"/>
+      <c r="M22" s="298" t="n"/>
+      <c r="N22" s="316">
         <f>IF(N23="","",IF(N23="☂","☂",IF(N23&gt;P23,"○",IF(N23=P23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O22" s="303" t="n"/>
-      <c r="P22" s="304" t="n"/>
-      <c r="Q22" s="307">
+      <c r="O22" s="312" t="n"/>
+      <c r="P22" s="313" t="n"/>
+      <c r="Q22" s="316">
         <f>IF(Q23="","",IF(Q23="☂","☂",IF(Q23&gt;S23,"○",IF(Q23=S23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R22" s="303" t="n"/>
-      <c r="S22" s="304" t="n"/>
-      <c r="T22" s="307">
+      <c r="R22" s="312" t="n"/>
+      <c r="S22" s="313" t="n"/>
+      <c r="T22" s="316">
         <f>IF(T23="","",IF(T23="☂","☂",IF(T23&gt;V23,"○",IF(T23=V23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U22" s="303" t="n"/>
-      <c r="V22" s="304" t="n"/>
-      <c r="W22" s="307">
+      <c r="U22" s="312" t="n"/>
+      <c r="V22" s="313" t="n"/>
+      <c r="W22" s="316">
         <f>IF(W23="","",IF(W23="☂","☂",IF(W23&gt;Y23,"○",IF(W23=Y23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X22" s="303" t="n"/>
-      <c r="Y22" s="304" t="n"/>
-      <c r="Z22" s="307">
+      <c r="X22" s="312" t="n"/>
+      <c r="Y22" s="313" t="n"/>
+      <c r="Z22" s="316">
         <f>IF(Z23="","",IF(Z23="☂","☂",IF(Z23&gt;AB23,"○",IF(Z23=AB23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA22" s="303" t="n"/>
-      <c r="AB22" s="304" t="n"/>
-      <c r="AC22" s="307" t="n"/>
-      <c r="AD22" s="313" t="n"/>
-      <c r="AE22" s="314" t="n"/>
-      <c r="AF22" s="307">
+      <c r="AA22" s="312" t="n"/>
+      <c r="AB22" s="313" t="n"/>
+      <c r="AC22" s="316" t="n"/>
+      <c r="AD22" s="323" t="n"/>
+      <c r="AE22" s="324" t="n"/>
+      <c r="AF22" s="316">
         <f>IF(AF23="","",IF(AF23="☂","☂",IF(AF23&gt;AH23,"○",IF(AF23=AH23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG22" s="303" t="n"/>
-      <c r="AH22" s="304" t="n"/>
-      <c r="AI22" s="307">
+      <c r="AG22" s="312" t="n"/>
+      <c r="AH22" s="313" t="n"/>
+      <c r="AI22" s="316">
         <f>IF(AI23="","",IF(AI23="☂","☂",IF(AI23&gt;AK23,"○",IF(AI23=AK23,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ22" s="297" t="n"/>
-      <c r="AK22" s="298" t="n"/>
-      <c r="AL22" s="308">
+      <c r="AJ22" s="302" t="n"/>
+      <c r="AK22" s="303" t="n"/>
+      <c r="AL22" s="317">
         <f>COUNTIF(E22:AK22,"○")</f>
         <v/>
       </c>
-      <c r="AM22" s="309">
+      <c r="AM22" s="318">
         <f>COUNTIF(E22:AK22,"△")</f>
         <v/>
       </c>
-      <c r="AN22" s="309">
+      <c r="AN22" s="318">
         <f>COUNTIF(E22:AK22,"×")</f>
         <v/>
       </c>
-      <c r="AO22" s="309">
+      <c r="AO22" s="318">
         <f>AL22*3+AM22*1</f>
         <v/>
       </c>
-      <c r="AP22" s="309">
+      <c r="AP22" s="318">
         <f>SUM(G23,M23,P23,S23,V23,Y23,AB23,AK23)</f>
         <v/>
       </c>
-      <c r="AQ22" s="309">
+      <c r="AQ22" s="318">
         <f>SUM(E23,K23,N23,Q23,T23,W23,Z23,AI23)</f>
         <v/>
       </c>
-      <c r="AR22" s="309">
+      <c r="AR22" s="318">
         <f>10-AL22-AM22-AN22</f>
         <v/>
       </c>
-      <c r="AS22" s="310">
+      <c r="AS22" s="319">
         <f>IFERROR(_xlfn.RANK.EQ(AO22,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5514,209 +5578,209 @@
       </c>
     </row>
     <row r="23" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A23" s="305" t="n"/>
-      <c r="B23" s="284" t="n"/>
-      <c r="C23" s="285" t="n"/>
-      <c r="D23" s="286" t="n"/>
-      <c r="E23" s="311" t="n"/>
-      <c r="F23" s="306" t="inlineStr">
+      <c r="A23" s="314" t="n"/>
+      <c r="B23" s="286" t="n"/>
+      <c r="C23" s="287" t="n"/>
+      <c r="D23" s="288" t="n"/>
+      <c r="E23" s="320" t="n"/>
+      <c r="F23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="311" t="n"/>
-      <c r="H23" s="311" t="n"/>
-      <c r="I23" s="306" t="inlineStr">
+      <c r="G23" s="321" t="n"/>
+      <c r="H23" s="321" t="n"/>
+      <c r="I23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J23" s="311" t="n"/>
-      <c r="K23" s="311" t="n"/>
-      <c r="L23" s="306" t="inlineStr">
+      <c r="J23" s="321" t="n"/>
+      <c r="K23" s="321" t="n"/>
+      <c r="L23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="311" t="n"/>
-      <c r="N23" s="311" t="n"/>
-      <c r="O23" s="306" t="inlineStr">
+      <c r="M23" s="321" t="n"/>
+      <c r="N23" s="321" t="n"/>
+      <c r="O23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P23" s="311" t="n"/>
-      <c r="Q23" s="311" t="n"/>
-      <c r="R23" s="306" t="inlineStr">
+      <c r="P23" s="321" t="n"/>
+      <c r="Q23" s="321" t="n"/>
+      <c r="R23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S23" s="311" t="n"/>
-      <c r="T23" s="311" t="n"/>
-      <c r="U23" s="306" t="inlineStr">
+      <c r="S23" s="321" t="n"/>
+      <c r="T23" s="321" t="n"/>
+      <c r="U23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V23" s="311" t="n"/>
-      <c r="W23" s="311" t="n"/>
-      <c r="X23" s="306" t="inlineStr">
+      <c r="V23" s="321" t="n"/>
+      <c r="W23" s="321" t="n"/>
+      <c r="X23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y23" s="311" t="n"/>
-      <c r="Z23" s="311" t="n"/>
-      <c r="AA23" s="306" t="inlineStr">
+      <c r="Y23" s="321" t="n"/>
+      <c r="Z23" s="321" t="n"/>
+      <c r="AA23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB23" s="311" t="n"/>
-      <c r="AC23" s="315" t="n"/>
-      <c r="AD23" s="297" t="n"/>
-      <c r="AE23" s="298" t="n"/>
-      <c r="AF23" s="316">
+      <c r="AB23" s="321" t="n"/>
+      <c r="AC23" s="325" t="n"/>
+      <c r="AD23" s="302" t="n"/>
+      <c r="AE23" s="303" t="n"/>
+      <c r="AF23" s="326">
         <f>IF(AE25="","",AE25)</f>
         <v/>
       </c>
-      <c r="AG23" s="306" t="inlineStr">
+      <c r="AG23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH23" s="316">
+      <c r="AH23" s="326">
         <f>IF(AC25="","",AC25)</f>
         <v/>
       </c>
-      <c r="AI23" s="306">
+      <c r="AI23" s="315">
         <f>IF(AE27="","",AE27)</f>
         <v/>
       </c>
-      <c r="AJ23" s="306" t="inlineStr">
+      <c r="AJ23" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK23" s="306">
+      <c r="AK23" s="315">
         <f>IF(AC27="","",AC27)</f>
         <v/>
       </c>
-      <c r="AL23" s="284" t="n"/>
-      <c r="AM23" s="289" t="n"/>
-      <c r="AN23" s="289" t="n"/>
-      <c r="AO23" s="289" t="n"/>
-      <c r="AP23" s="289" t="n"/>
-      <c r="AQ23" s="289" t="n"/>
-      <c r="AR23" s="289" t="n"/>
-      <c r="AS23" s="301" t="n"/>
-      <c r="AV23" s="289" t="n"/>
-      <c r="AW23" s="291" t="n"/>
-      <c r="AX23" s="289" t="n"/>
+      <c r="AL23" s="286" t="n"/>
+      <c r="AM23" s="291" t="n"/>
+      <c r="AN23" s="291" t="n"/>
+      <c r="AO23" s="291" t="n"/>
+      <c r="AP23" s="291" t="n"/>
+      <c r="AQ23" s="291" t="n"/>
+      <c r="AR23" s="291" t="n"/>
+      <c r="AS23" s="308" t="n"/>
+      <c r="AV23" s="291" t="n"/>
+      <c r="AW23" s="293" t="n"/>
+      <c r="AX23" s="291" t="n"/>
     </row>
     <row r="24" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A24" s="305" t="n"/>
-      <c r="B24" s="306" t="n">
+      <c r="A24" s="314" t="n"/>
+      <c r="B24" s="315" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="306">
+      <c r="C24" s="315">
         <f>AX24</f>
         <v/>
       </c>
-      <c r="D24" s="274" t="n"/>
-      <c r="E24" s="306">
+      <c r="D24" s="276" t="n"/>
+      <c r="E24" s="314">
         <f>IF(E25="","",IF(E25="☂","☂",IF(E25&gt;G25,"○",IF(E25=G25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F24" s="293" t="n"/>
-      <c r="G24" s="294" t="n"/>
-      <c r="H24" s="306">
+      <c r="F24" s="297" t="n"/>
+      <c r="G24" s="298" t="n"/>
+      <c r="H24" s="315">
         <f>IF(H25="","",IF(H25="☂","☂",IF(H25&gt;J25,"○",IF(H25=J25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I24" s="293" t="n"/>
-      <c r="J24" s="294" t="n"/>
-      <c r="K24" s="306">
+      <c r="I24" s="297" t="n"/>
+      <c r="J24" s="298" t="n"/>
+      <c r="K24" s="315">
         <f>IF(K25="","",IF(K25="☂","☂",IF(K25&gt;M25,"○",IF(K25=M25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L24" s="293" t="n"/>
-      <c r="M24" s="294" t="n"/>
-      <c r="N24" s="307">
+      <c r="L24" s="297" t="n"/>
+      <c r="M24" s="298" t="n"/>
+      <c r="N24" s="316">
         <f>IF(N25="","",IF(N25="☂","☂",IF(N25&gt;P25,"○",IF(N25=P25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O24" s="303" t="n"/>
-      <c r="P24" s="304" t="n"/>
-      <c r="Q24" s="307">
+      <c r="O24" s="312" t="n"/>
+      <c r="P24" s="313" t="n"/>
+      <c r="Q24" s="316">
         <f>IF(Q25="","",IF(Q25="☂","☂",IF(Q25&gt;S25,"○",IF(Q25=S25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R24" s="303" t="n"/>
-      <c r="S24" s="304" t="n"/>
-      <c r="T24" s="307">
+      <c r="R24" s="312" t="n"/>
+      <c r="S24" s="313" t="n"/>
+      <c r="T24" s="316">
         <f>IF(T25="","",IF(T25="☂","☂",IF(T25&gt;V25,"○",IF(T25=V25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U24" s="303" t="n"/>
-      <c r="V24" s="304" t="n"/>
-      <c r="W24" s="307">
+      <c r="U24" s="312" t="n"/>
+      <c r="V24" s="313" t="n"/>
+      <c r="W24" s="316">
         <f>IF(W25="","",IF(W25="☂","☂",IF(W25&gt;Y25,"○",IF(W25=Y25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X24" s="303" t="n"/>
-      <c r="Y24" s="304" t="n"/>
-      <c r="Z24" s="307">
+      <c r="X24" s="312" t="n"/>
+      <c r="Y24" s="313" t="n"/>
+      <c r="Z24" s="316">
         <f>IF(Z25="","",IF(Z25="☂","☂",IF(Z25&gt;AB25,"○",IF(Z25=AB25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA24" s="303" t="n"/>
-      <c r="AB24" s="304" t="n"/>
-      <c r="AC24" s="307">
+      <c r="AA24" s="312" t="n"/>
+      <c r="AB24" s="313" t="n"/>
+      <c r="AC24" s="316">
         <f>IF(AC25="","",IF(AC25="☂","☂",IF(AC25&gt;AE25,"○",IF(AC25=AE25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD24" s="303" t="n"/>
-      <c r="AE24" s="304" t="n"/>
-      <c r="AF24" s="307" t="n"/>
-      <c r="AG24" s="313" t="n"/>
-      <c r="AH24" s="314" t="n"/>
-      <c r="AI24" s="307">
+      <c r="AD24" s="312" t="n"/>
+      <c r="AE24" s="313" t="n"/>
+      <c r="AF24" s="316" t="n"/>
+      <c r="AG24" s="323" t="n"/>
+      <c r="AH24" s="324" t="n"/>
+      <c r="AI24" s="316">
         <f>IF(AI25="","",IF(AI25="☂","☂",IF(AI25&gt;AK25,"○",IF(AI25=AK25,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AJ24" s="303" t="n"/>
-      <c r="AK24" s="304" t="n"/>
-      <c r="AL24" s="308">
+      <c r="AJ24" s="312" t="n"/>
+      <c r="AK24" s="313" t="n"/>
+      <c r="AL24" s="317">
         <f>COUNTIF(E24:AK24,"○")</f>
         <v/>
       </c>
-      <c r="AM24" s="309">
+      <c r="AM24" s="318">
         <f>COUNTIF(E24:AK24,"△")</f>
         <v/>
       </c>
-      <c r="AN24" s="309">
+      <c r="AN24" s="318">
         <f>COUNTIF(E24:AK24,"×")</f>
         <v/>
       </c>
-      <c r="AO24" s="309">
+      <c r="AO24" s="318">
         <f>AL24*3+AM24*1</f>
         <v/>
       </c>
-      <c r="AP24" s="309">
+      <c r="AP24" s="318">
         <f>SUM(G25,M25,P25,S25,V25,Y25,AB25,AK25)</f>
         <v/>
       </c>
-      <c r="AQ24" s="309">
+      <c r="AQ24" s="318">
         <f>SUM(E25,K25,N25,Q25,T25,W25,Z25,AI25)</f>
         <v/>
       </c>
-      <c r="AR24" s="309">
+      <c r="AR24" s="318">
         <f>10-AL24-AM24-AN24</f>
         <v/>
       </c>
-      <c r="AS24" s="310">
+      <c r="AS24" s="319">
         <f>IFERROR(_xlfn.RANK.EQ(AO24,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5730,203 +5794,203 @@
       </c>
     </row>
     <row r="25" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A25" s="305" t="n"/>
-      <c r="B25" s="284" t="n"/>
-      <c r="C25" s="285" t="n"/>
-      <c r="D25" s="286" t="n"/>
-      <c r="E25" s="311" t="n"/>
-      <c r="F25" s="306" t="inlineStr">
+      <c r="A25" s="314" t="n"/>
+      <c r="B25" s="286" t="n"/>
+      <c r="C25" s="287" t="n"/>
+      <c r="D25" s="288" t="n"/>
+      <c r="E25" s="320" t="n"/>
+      <c r="F25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="311" t="n"/>
-      <c r="H25" s="311" t="n"/>
-      <c r="I25" s="306" t="inlineStr">
+      <c r="G25" s="321" t="n"/>
+      <c r="H25" s="321" t="n"/>
+      <c r="I25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="311" t="n"/>
-      <c r="K25" s="311" t="n"/>
-      <c r="L25" s="306" t="inlineStr">
+      <c r="J25" s="321" t="n"/>
+      <c r="K25" s="321" t="n"/>
+      <c r="L25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="311" t="n"/>
-      <c r="N25" s="311" t="n"/>
-      <c r="O25" s="306" t="inlineStr">
+      <c r="M25" s="321" t="n"/>
+      <c r="N25" s="321" t="n"/>
+      <c r="O25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P25" s="311" t="n"/>
-      <c r="Q25" s="311" t="n"/>
-      <c r="R25" s="306" t="inlineStr">
+      <c r="P25" s="321" t="n"/>
+      <c r="Q25" s="321" t="n"/>
+      <c r="R25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S25" s="311" t="n"/>
-      <c r="T25" s="311" t="n"/>
-      <c r="U25" s="306" t="inlineStr">
+      <c r="S25" s="321" t="n"/>
+      <c r="T25" s="321" t="n"/>
+      <c r="U25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V25" s="311" t="n"/>
-      <c r="W25" s="311" t="n"/>
-      <c r="X25" s="306" t="inlineStr">
+      <c r="V25" s="321" t="n"/>
+      <c r="W25" s="321" t="n"/>
+      <c r="X25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y25" s="311" t="n"/>
-      <c r="Z25" s="311" t="n"/>
-      <c r="AA25" s="306" t="inlineStr">
+      <c r="Y25" s="321" t="n"/>
+      <c r="Z25" s="321" t="n"/>
+      <c r="AA25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB25" s="311" t="n"/>
-      <c r="AC25" s="311" t="n"/>
-      <c r="AD25" s="306" t="inlineStr">
+      <c r="AB25" s="321" t="n"/>
+      <c r="AC25" s="321" t="n"/>
+      <c r="AD25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE25" s="311" t="n"/>
-      <c r="AF25" s="317" t="n"/>
-      <c r="AG25" s="318" t="n"/>
-      <c r="AH25" s="319" t="n"/>
-      <c r="AI25" s="311">
+      <c r="AE25" s="321" t="n"/>
+      <c r="AF25" s="327" t="n"/>
+      <c r="AG25" s="328" t="n"/>
+      <c r="AH25" s="329" t="n"/>
+      <c r="AI25" s="321">
         <f>IF(AH27="","",AH27)</f>
         <v/>
       </c>
-      <c r="AJ25" s="306" t="inlineStr">
+      <c r="AJ25" s="315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK25" s="311">
+      <c r="AK25" s="321">
         <f>IF(AF27="","",AF27)</f>
         <v/>
       </c>
-      <c r="AL25" s="284" t="n"/>
-      <c r="AM25" s="289" t="n"/>
-      <c r="AN25" s="289" t="n"/>
-      <c r="AO25" s="289" t="n"/>
-      <c r="AP25" s="289" t="n"/>
-      <c r="AQ25" s="289" t="n"/>
-      <c r="AR25" s="289" t="n"/>
-      <c r="AS25" s="301" t="n"/>
-      <c r="AV25" s="289" t="n"/>
-      <c r="AW25" s="291" t="n"/>
-      <c r="AX25" s="289" t="n"/>
+      <c r="AL25" s="286" t="n"/>
+      <c r="AM25" s="291" t="n"/>
+      <c r="AN25" s="291" t="n"/>
+      <c r="AO25" s="291" t="n"/>
+      <c r="AP25" s="291" t="n"/>
+      <c r="AQ25" s="291" t="n"/>
+      <c r="AR25" s="291" t="n"/>
+      <c r="AS25" s="308" t="n"/>
+      <c r="AV25" s="291" t="n"/>
+      <c r="AW25" s="293" t="n"/>
+      <c r="AX25" s="291" t="n"/>
     </row>
     <row r="26" hidden="1" ht="33.6" customHeight="1" s="257">
-      <c r="A26" s="305" t="n"/>
-      <c r="B26" s="306" t="n">
+      <c r="A26" s="314" t="n"/>
+      <c r="B26" s="315" t="n">
         <v>11</v>
       </c>
-      <c r="C26" s="306">
+      <c r="C26" s="315">
         <f>AX26</f>
         <v/>
       </c>
-      <c r="D26" s="274" t="n"/>
-      <c r="E26" s="306">
+      <c r="D26" s="276" t="n"/>
+      <c r="E26" s="314">
         <f>IF(E27="","",IF(E27="☂","☂",IF(E27&gt;G27,"○",IF(E27=G27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="F26" s="293" t="n"/>
-      <c r="G26" s="294" t="n"/>
-      <c r="H26" s="306">
+      <c r="F26" s="297" t="n"/>
+      <c r="G26" s="298" t="n"/>
+      <c r="H26" s="315">
         <f>IF(H27="","",IF(H27="☂","☂",IF(H27&gt;J27,"○",IF(H27=J27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="I26" s="293" t="n"/>
-      <c r="J26" s="294" t="n"/>
-      <c r="K26" s="306">
+      <c r="I26" s="297" t="n"/>
+      <c r="J26" s="298" t="n"/>
+      <c r="K26" s="315">
         <f>IF(K27="","",IF(K27="☂","☂",IF(K27&gt;M27,"○",IF(K27=M27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="L26" s="293" t="n"/>
-      <c r="M26" s="294" t="n"/>
-      <c r="N26" s="307">
+      <c r="L26" s="297" t="n"/>
+      <c r="M26" s="298" t="n"/>
+      <c r="N26" s="316">
         <f>IF(N27="","",IF(N27="☂","☂",IF(N27&gt;P27,"○",IF(N27=P27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="O26" s="303" t="n"/>
-      <c r="P26" s="304" t="n"/>
-      <c r="Q26" s="307">
+      <c r="O26" s="312" t="n"/>
+      <c r="P26" s="313" t="n"/>
+      <c r="Q26" s="316">
         <f>IF(Q27="","",IF(Q27="☂","☂",IF(Q27&gt;S27,"○",IF(Q27=S27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="R26" s="303" t="n"/>
-      <c r="S26" s="304" t="n"/>
-      <c r="T26" s="307">
+      <c r="R26" s="312" t="n"/>
+      <c r="S26" s="313" t="n"/>
+      <c r="T26" s="316">
         <f>IF(T27="","",IF(T27="☂","☂",IF(T27&gt;V27,"○",IF(T27=V27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="U26" s="303" t="n"/>
-      <c r="V26" s="304" t="n"/>
-      <c r="W26" s="307">
+      <c r="U26" s="312" t="n"/>
+      <c r="V26" s="313" t="n"/>
+      <c r="W26" s="316">
         <f>IF(W27="","",IF(W27="☂","☂",IF(W27&gt;Y27,"○",IF(W27=Y27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="X26" s="303" t="n"/>
-      <c r="Y26" s="304" t="n"/>
-      <c r="Z26" s="307">
+      <c r="X26" s="312" t="n"/>
+      <c r="Y26" s="313" t="n"/>
+      <c r="Z26" s="316">
         <f>IF(Z27="","",IF(Z27="☂","☂",IF(Z27&gt;AB27,"○",IF(Z27=AB27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AA26" s="303" t="n"/>
-      <c r="AB26" s="304" t="n"/>
-      <c r="AC26" s="307">
+      <c r="AA26" s="312" t="n"/>
+      <c r="AB26" s="313" t="n"/>
+      <c r="AC26" s="316">
         <f>IF(AC27="","",IF(AC27="☂","☂",IF(AC27&gt;AE27,"○",IF(AC27=AE27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AD26" s="303" t="n"/>
-      <c r="AE26" s="304" t="n"/>
-      <c r="AF26" s="307">
+      <c r="AD26" s="312" t="n"/>
+      <c r="AE26" s="313" t="n"/>
+      <c r="AF26" s="316">
         <f>IF(AF27="","",IF(AF27="☂","☂",IF(AF27&gt;AH27,"○",IF(AF27=AH27,"△","×"))))</f>
         <v/>
       </c>
-      <c r="AG26" s="303" t="n"/>
-      <c r="AH26" s="304" t="n"/>
-      <c r="AI26" s="307" t="n"/>
-      <c r="AJ26" s="318" t="n"/>
-      <c r="AK26" s="320" t="n"/>
-      <c r="AL26" s="308">
+      <c r="AG26" s="312" t="n"/>
+      <c r="AH26" s="313" t="n"/>
+      <c r="AI26" s="316" t="n"/>
+      <c r="AJ26" s="328" t="n"/>
+      <c r="AK26" s="330" t="n"/>
+      <c r="AL26" s="317">
         <f>COUNTIF(E26:AK26,"○")</f>
         <v/>
       </c>
-      <c r="AM26" s="309">
+      <c r="AM26" s="318">
         <f>COUNTIF(E26:AK26,"△")</f>
         <v/>
       </c>
-      <c r="AN26" s="309">
+      <c r="AN26" s="318">
         <f>COUNTIF(E26:AK26,"×")</f>
         <v/>
       </c>
-      <c r="AO26" s="309">
+      <c r="AO26" s="318">
         <f>AL26*3+AM26*1</f>
         <v/>
       </c>
-      <c r="AP26" s="309">
+      <c r="AP26" s="318">
         <f>SUM(G27,M27,P27,S27,V27,Y27,AB27,AK27)</f>
         <v/>
       </c>
-      <c r="AQ26" s="306">
+      <c r="AQ26" s="315">
         <f>SUM(H27,K27,N27,Q27,T27,W27,Z27,AI27,#REF!)</f>
         <v/>
       </c>
-      <c r="AR26" s="306">
+      <c r="AR26" s="315">
         <f>10-AL26-AM26-AN26</f>
         <v/>
       </c>
-      <c r="AS26" s="310">
+      <c r="AS26" s="319">
         <f>IFERROR(_xlfn.RANK.EQ(AO26,$AO$6:$AO$27),"")</f>
         <v/>
       </c>
@@ -5940,94 +6004,94 @@
       </c>
     </row>
     <row r="27" hidden="1" ht="33.6" customHeight="1" s="257" thickBot="1">
-      <c r="A27" s="321" t="n"/>
-      <c r="B27" s="284" t="n"/>
-      <c r="C27" s="285" t="n"/>
-      <c r="D27" s="286" t="n"/>
-      <c r="E27" s="322" t="n"/>
-      <c r="F27" s="323" t="inlineStr">
+      <c r="A27" s="331" t="n"/>
+      <c r="B27" s="286" t="n"/>
+      <c r="C27" s="287" t="n"/>
+      <c r="D27" s="288" t="n"/>
+      <c r="E27" s="332" t="n"/>
+      <c r="F27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="322" t="n"/>
-      <c r="H27" s="322" t="n"/>
-      <c r="I27" s="323" t="inlineStr">
+      <c r="G27" s="334" t="n"/>
+      <c r="H27" s="334" t="n"/>
+      <c r="I27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="322" t="n"/>
-      <c r="K27" s="322" t="n"/>
-      <c r="L27" s="323" t="inlineStr">
+      <c r="J27" s="334" t="n"/>
+      <c r="K27" s="334" t="n"/>
+      <c r="L27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="322" t="n"/>
-      <c r="N27" s="322" t="n"/>
-      <c r="O27" s="323" t="inlineStr">
+      <c r="M27" s="334" t="n"/>
+      <c r="N27" s="334" t="n"/>
+      <c r="O27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P27" s="322" t="n"/>
-      <c r="Q27" s="322" t="n"/>
-      <c r="R27" s="323" t="inlineStr">
+      <c r="P27" s="334" t="n"/>
+      <c r="Q27" s="334" t="n"/>
+      <c r="R27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S27" s="322" t="n"/>
-      <c r="T27" s="322" t="n"/>
-      <c r="U27" s="323" t="inlineStr">
+      <c r="S27" s="334" t="n"/>
+      <c r="T27" s="334" t="n"/>
+      <c r="U27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V27" s="322" t="n"/>
-      <c r="W27" s="322" t="n"/>
-      <c r="X27" s="323" t="inlineStr">
+      <c r="V27" s="334" t="n"/>
+      <c r="W27" s="334" t="n"/>
+      <c r="X27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y27" s="322" t="n"/>
-      <c r="Z27" s="322" t="n"/>
-      <c r="AA27" s="323" t="inlineStr">
+      <c r="Y27" s="334" t="n"/>
+      <c r="Z27" s="334" t="n"/>
+      <c r="AA27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB27" s="322" t="n"/>
-      <c r="AC27" s="322" t="n"/>
-      <c r="AD27" s="323" t="inlineStr">
+      <c r="AB27" s="334" t="n"/>
+      <c r="AC27" s="334" t="n"/>
+      <c r="AD27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE27" s="322" t="n"/>
-      <c r="AF27" s="324" t="n"/>
-      <c r="AG27" s="323" t="inlineStr">
+      <c r="AE27" s="334" t="n"/>
+      <c r="AF27" s="335" t="n"/>
+      <c r="AG27" s="333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AH27" s="324" t="n"/>
-      <c r="AI27" s="325" t="n"/>
-      <c r="AJ27" s="326" t="n"/>
-      <c r="AK27" s="327" t="n"/>
-      <c r="AL27" s="284" t="n"/>
-      <c r="AM27" s="289" t="n"/>
-      <c r="AN27" s="289" t="n"/>
-      <c r="AO27" s="289" t="n"/>
-      <c r="AP27" s="289" t="n"/>
-      <c r="AQ27" s="328" t="n"/>
-      <c r="AR27" s="328" t="n"/>
-      <c r="AS27" s="329" t="n"/>
-      <c r="AV27" s="289" t="n"/>
-      <c r="AW27" s="291" t="n"/>
-      <c r="AX27" s="289" t="n"/>
+      <c r="AH27" s="335" t="n"/>
+      <c r="AI27" s="336" t="n"/>
+      <c r="AJ27" s="337" t="n"/>
+      <c r="AK27" s="338" t="n"/>
+      <c r="AL27" s="286" t="n"/>
+      <c r="AM27" s="291" t="n"/>
+      <c r="AN27" s="291" t="n"/>
+      <c r="AO27" s="291" t="n"/>
+      <c r="AP27" s="291" t="n"/>
+      <c r="AQ27" s="339" t="n"/>
+      <c r="AR27" s="339" t="n"/>
+      <c r="AS27" s="340" t="n"/>
+      <c r="AV27" s="291" t="n"/>
+      <c r="AW27" s="293" t="n"/>
+      <c r="AX27" s="291" t="n"/>
     </row>
     <row r="28" ht="6.75" customHeight="1" s="257"/>
   </sheetData>
@@ -6375,8 +6439,8 @@
       <c r="T1" s="240" t="n">
         <v>2026</v>
       </c>
-      <c r="U1" s="330" t="n"/>
-      <c r="V1" s="330" t="n"/>
+      <c r="U1" s="341" t="n"/>
+      <c r="V1" s="341" t="n"/>
       <c r="W1" s="238" t="inlineStr">
         <is>
           <t>年</t>
@@ -6385,46 +6449,46 @@
       <c r="X1" s="238" t="n"/>
     </row>
     <row r="2" ht="16.15" customHeight="1" s="257">
-      <c r="A2" s="331" t="inlineStr">
+      <c r="A2" s="342" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="332" t="n"/>
-      <c r="C2" s="332" t="n"/>
-      <c r="D2" s="332" t="n"/>
-      <c r="E2" s="332" t="n"/>
-      <c r="F2" s="333" t="n"/>
-      <c r="G2" s="331" t="inlineStr">
+      <c r="B2" s="343" t="n"/>
+      <c r="C2" s="343" t="n"/>
+      <c r="D2" s="343" t="n"/>
+      <c r="E2" s="343" t="n"/>
+      <c r="F2" s="344" t="n"/>
+      <c r="G2" s="342" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="332" t="n"/>
-      <c r="I2" s="332" t="n"/>
-      <c r="J2" s="332" t="n"/>
-      <c r="K2" s="332" t="n"/>
-      <c r="L2" s="333" t="n"/>
-      <c r="M2" s="331" t="inlineStr">
+      <c r="H2" s="343" t="n"/>
+      <c r="I2" s="343" t="n"/>
+      <c r="J2" s="343" t="n"/>
+      <c r="K2" s="343" t="n"/>
+      <c r="L2" s="344" t="n"/>
+      <c r="M2" s="342" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="332" t="n"/>
-      <c r="O2" s="332" t="n"/>
-      <c r="P2" s="332" t="n"/>
-      <c r="Q2" s="332" t="n"/>
-      <c r="R2" s="333" t="n"/>
+      <c r="N2" s="343" t="n"/>
+      <c r="O2" s="343" t="n"/>
+      <c r="P2" s="343" t="n"/>
+      <c r="Q2" s="343" t="n"/>
+      <c r="R2" s="344" t="n"/>
       <c r="S2" s="246" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="332" t="n"/>
-      <c r="U2" s="332" t="n"/>
-      <c r="V2" s="332" t="n"/>
-      <c r="W2" s="332" t="n"/>
-      <c r="X2" s="333" t="n"/>
+      <c r="T2" s="343" t="n"/>
+      <c r="U2" s="343" t="n"/>
+      <c r="V2" s="343" t="n"/>
+      <c r="W2" s="343" t="n"/>
+      <c r="X2" s="344" t="n"/>
     </row>
     <row r="3" ht="16.15" customHeight="1" s="257">
       <c r="A3" s="53" t="inlineStr">
@@ -6442,8 +6506,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="293" t="n"/>
-      <c r="E3" s="294" t="n"/>
+      <c r="D3" s="297" t="n"/>
+      <c r="E3" s="298" t="n"/>
       <c r="F3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6464,8 +6528,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="293" t="n"/>
-      <c r="K3" s="294" t="n"/>
+      <c r="J3" s="297" t="n"/>
+      <c r="K3" s="298" t="n"/>
       <c r="L3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6486,8 +6550,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="293" t="n"/>
-      <c r="Q3" s="294" t="n"/>
+      <c r="P3" s="297" t="n"/>
+      <c r="Q3" s="298" t="n"/>
       <c r="R3" s="58" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6508,8 +6572,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="293" t="n"/>
-      <c r="W3" s="294" t="n"/>
+      <c r="V3" s="297" t="n"/>
+      <c r="W3" s="298" t="n"/>
       <c r="X3" s="241" t="inlineStr">
         <is>
           <t>審判</t>
@@ -6517,7 +6581,7 @@
       </c>
     </row>
     <row r="4" ht="16.15" customHeight="1" s="257">
-      <c r="A4" s="334" t="n">
+      <c r="A4" s="345" t="n">
         <v>45047</v>
       </c>
       <c r="B4" s="69" t="inlineStr">
@@ -6525,15 +6589,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C4" s="335" t="n"/>
+      <c r="C4" s="346" t="n"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="336" t="n"/>
-      <c r="F4" s="337" t="n"/>
-      <c r="G4" s="334" t="n">
+      <c r="E4" s="347" t="n"/>
+      <c r="F4" s="348" t="n"/>
+      <c r="G4" s="345" t="n">
         <v>45078</v>
       </c>
       <c r="H4" s="70" t="inlineStr">
@@ -6541,15 +6605,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I4" s="338" t="n"/>
+      <c r="I4" s="349" t="n"/>
       <c r="J4" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="339" t="n"/>
-      <c r="L4" s="337" t="n"/>
-      <c r="M4" s="334" t="n">
+      <c r="K4" s="350" t="n"/>
+      <c r="L4" s="348" t="n"/>
+      <c r="M4" s="345" t="n">
         <v>45108</v>
       </c>
       <c r="N4" s="69" t="inlineStr">
@@ -6557,7 +6621,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O4" s="338">
+      <c r="O4" s="349">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -6566,15 +6630,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="339">
+      <c r="Q4" s="350">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="337">
+      <c r="R4" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="340" t="n">
+      <c r="S4" s="351" t="n">
         <v>45139</v>
       </c>
       <c r="T4" s="69" t="inlineStr">
@@ -6582,17 +6646,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U4" s="335" t="n"/>
+      <c r="U4" s="346" t="n"/>
       <c r="V4" s="20" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="336" t="n"/>
-      <c r="X4" s="337" t="n"/>
+      <c r="W4" s="347" t="n"/>
+      <c r="X4" s="348" t="n"/>
     </row>
     <row r="5" ht="16.15" customHeight="1" s="257">
-      <c r="A5" s="334" t="n">
+      <c r="A5" s="345" t="n">
         <v>45048</v>
       </c>
       <c r="B5" s="69" t="inlineStr">
@@ -6600,15 +6664,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C5" s="338" t="n"/>
+      <c r="C5" s="349" t="n"/>
       <c r="D5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="339" t="n"/>
-      <c r="F5" s="337" t="n"/>
-      <c r="G5" s="334" t="n">
+      <c r="E5" s="350" t="n"/>
+      <c r="F5" s="348" t="n"/>
+      <c r="G5" s="345" t="n">
         <v>45079</v>
       </c>
       <c r="H5" s="70" t="inlineStr">
@@ -6616,7 +6680,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I5" s="338">
+      <c r="I5" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -6625,40 +6689,40 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="339">
+      <c r="K5" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="337">
+      <c r="L5" s="348">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="341" t="n">
+      <c r="M5" s="352" t="n">
         <v>45109</v>
       </c>
-      <c r="N5" s="342" t="inlineStr">
+      <c r="N5" s="353" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="O5" s="343">
+      <c r="O5" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="344" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="345">
+      <c r="P5" s="355" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="356">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="346">
+      <c r="R5" s="357">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="340" t="n">
+      <c r="S5" s="351" t="n">
         <v>45140</v>
       </c>
       <c r="T5" s="69" t="inlineStr">
@@ -6666,17 +6730,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U5" s="338" t="n"/>
+      <c r="U5" s="349" t="n"/>
       <c r="V5" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="339" t="n"/>
-      <c r="X5" s="337" t="n"/>
+      <c r="W5" s="350" t="n"/>
+      <c r="X5" s="348" t="n"/>
     </row>
     <row r="6" ht="16.15" customHeight="1" s="257">
-      <c r="A6" s="334" t="n">
+      <c r="A6" s="345" t="n">
         <v>45049</v>
       </c>
       <c r="B6" s="69" t="inlineStr">
@@ -6684,40 +6748,40 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C6" s="338" t="n"/>
+      <c r="C6" s="349" t="n"/>
       <c r="D6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="339" t="n"/>
-      <c r="F6" s="337" t="n"/>
-      <c r="G6" s="341" t="n">
+      <c r="E6" s="350" t="n"/>
+      <c r="F6" s="348" t="n"/>
+      <c r="G6" s="352" t="n">
         <v>45080</v>
       </c>
-      <c r="H6" s="347" t="inlineStr">
+      <c r="H6" s="358" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="I6" s="343">
+      <c r="I6" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="344" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="345">
+      <c r="J6" s="355" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="356">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="346">
+      <c r="L6" s="357">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="334" t="n">
+      <c r="M6" s="345" t="n">
         <v>45110</v>
       </c>
       <c r="N6" s="69" t="inlineStr">
@@ -6725,15 +6789,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O6" s="338" t="n"/>
+      <c r="O6" s="349" t="n"/>
       <c r="P6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="339" t="n"/>
-      <c r="R6" s="337" t="n"/>
-      <c r="S6" s="340" t="n">
+      <c r="Q6" s="350" t="n"/>
+      <c r="R6" s="348" t="n"/>
+      <c r="S6" s="351" t="n">
         <v>45141</v>
       </c>
       <c r="T6" s="69" t="inlineStr">
@@ -6741,17 +6805,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U6" s="338" t="n"/>
+      <c r="U6" s="349" t="n"/>
       <c r="V6" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="339" t="n"/>
-      <c r="X6" s="337" t="n"/>
+      <c r="W6" s="350" t="n"/>
+      <c r="X6" s="348" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" s="257">
-      <c r="A7" s="334" t="n">
+      <c r="A7" s="345" t="n">
         <v>45050</v>
       </c>
       <c r="B7" s="69" t="inlineStr">
@@ -6759,15 +6823,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C7" s="338" t="n"/>
+      <c r="C7" s="349" t="n"/>
       <c r="D7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="339" t="n"/>
-      <c r="F7" s="337" t="n"/>
-      <c r="G7" s="334" t="n">
+      <c r="E7" s="350" t="n"/>
+      <c r="F7" s="348" t="n"/>
+      <c r="G7" s="345" t="n">
         <v>45081</v>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -6775,7 +6839,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I7" s="338">
+      <c r="I7" s="349">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -6784,15 +6848,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="339">
+      <c r="K7" s="350">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="337">
+      <c r="L7" s="348">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="334" t="n">
+      <c r="M7" s="345" t="n">
         <v>45111</v>
       </c>
       <c r="N7" s="69" t="inlineStr">
@@ -6800,15 +6864,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O7" s="338" t="n"/>
+      <c r="O7" s="349" t="n"/>
       <c r="P7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="339" t="n"/>
-      <c r="R7" s="337" t="n"/>
-      <c r="S7" s="340" t="n">
+      <c r="Q7" s="350" t="n"/>
+      <c r="R7" s="348" t="n"/>
+      <c r="S7" s="351" t="n">
         <v>45142</v>
       </c>
       <c r="T7" s="69" t="inlineStr">
@@ -6816,17 +6880,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U7" s="338" t="n"/>
+      <c r="U7" s="349" t="n"/>
       <c r="V7" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="339" t="n"/>
-      <c r="X7" s="337" t="n"/>
+      <c r="W7" s="350" t="n"/>
+      <c r="X7" s="348" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" s="257">
-      <c r="A8" s="334" t="n">
+      <c r="A8" s="345" t="n">
         <v>45051</v>
       </c>
       <c r="B8" s="69" t="inlineStr">
@@ -6834,15 +6898,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C8" s="338" t="n"/>
+      <c r="C8" s="349" t="n"/>
       <c r="D8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="339" t="n"/>
-      <c r="F8" s="337" t="n"/>
-      <c r="G8" s="334" t="n">
+      <c r="E8" s="350" t="n"/>
+      <c r="F8" s="348" t="n"/>
+      <c r="G8" s="345" t="n">
         <v>45082</v>
       </c>
       <c r="H8" s="70" t="inlineStr">
@@ -6850,15 +6914,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I8" s="338" t="n"/>
+      <c r="I8" s="349" t="n"/>
       <c r="J8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="339" t="n"/>
-      <c r="L8" s="337" t="n"/>
-      <c r="M8" s="334" t="n">
+      <c r="K8" s="350" t="n"/>
+      <c r="L8" s="348" t="n"/>
+      <c r="M8" s="345" t="n">
         <v>45112</v>
       </c>
       <c r="N8" s="69" t="inlineStr">
@@ -6866,15 +6930,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O8" s="338" t="n"/>
+      <c r="O8" s="349" t="n"/>
       <c r="P8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="339" t="n"/>
-      <c r="R8" s="337" t="n"/>
-      <c r="S8" s="340" t="n">
+      <c r="Q8" s="350" t="n"/>
+      <c r="R8" s="348" t="n"/>
+      <c r="S8" s="351" t="n">
         <v>45143</v>
       </c>
       <c r="T8" s="69" t="inlineStr">
@@ -6882,17 +6946,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U8" s="338" t="n"/>
+      <c r="U8" s="349" t="n"/>
       <c r="V8" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="339" t="n"/>
-      <c r="X8" s="337" t="n"/>
+      <c r="W8" s="350" t="n"/>
+      <c r="X8" s="348" t="n"/>
     </row>
     <row r="9" ht="16.15" customHeight="1" s="257">
-      <c r="A9" s="334" t="n">
+      <c r="A9" s="345" t="n">
         <v>45052</v>
       </c>
       <c r="B9" s="69" t="inlineStr">
@@ -6900,15 +6964,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C9" s="338" t="n"/>
+      <c r="C9" s="349" t="n"/>
       <c r="D9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="339" t="n"/>
-      <c r="F9" s="337" t="n"/>
-      <c r="G9" s="334" t="n">
+      <c r="E9" s="350" t="n"/>
+      <c r="F9" s="348" t="n"/>
+      <c r="G9" s="345" t="n">
         <v>45083</v>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -6916,15 +6980,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I9" s="338" t="n"/>
+      <c r="I9" s="349" t="n"/>
       <c r="J9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="339" t="n"/>
-      <c r="L9" s="337" t="n"/>
-      <c r="M9" s="334" t="n">
+      <c r="K9" s="350" t="n"/>
+      <c r="L9" s="348" t="n"/>
+      <c r="M9" s="345" t="n">
         <v>45113</v>
       </c>
       <c r="N9" s="69" t="inlineStr">
@@ -6932,15 +6996,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O9" s="338" t="n"/>
+      <c r="O9" s="349" t="n"/>
       <c r="P9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="339" t="n"/>
-      <c r="R9" s="337" t="n"/>
-      <c r="S9" s="340" t="n">
+      <c r="Q9" s="350" t="n"/>
+      <c r="R9" s="348" t="n"/>
+      <c r="S9" s="351" t="n">
         <v>45144</v>
       </c>
       <c r="T9" s="69" t="inlineStr">
@@ -6948,17 +7012,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U9" s="338" t="n"/>
+      <c r="U9" s="349" t="n"/>
       <c r="V9" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="339" t="n"/>
-      <c r="X9" s="337" t="n"/>
+      <c r="W9" s="350" t="n"/>
+      <c r="X9" s="348" t="n"/>
     </row>
     <row r="10" ht="16.15" customHeight="1" s="257">
-      <c r="A10" s="334" t="n">
+      <c r="A10" s="345" t="n">
         <v>45053</v>
       </c>
       <c r="B10" s="69" t="inlineStr">
@@ -6966,15 +7030,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C10" s="338" t="n"/>
+      <c r="C10" s="349" t="n"/>
       <c r="D10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="339" t="n"/>
-      <c r="F10" s="337" t="n"/>
-      <c r="G10" s="334" t="n">
+      <c r="E10" s="350" t="n"/>
+      <c r="F10" s="348" t="n"/>
+      <c r="G10" s="345" t="n">
         <v>45084</v>
       </c>
       <c r="H10" s="70" t="inlineStr">
@@ -6982,15 +7046,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I10" s="338" t="n"/>
+      <c r="I10" s="349" t="n"/>
       <c r="J10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="339" t="n"/>
-      <c r="L10" s="337" t="n"/>
-      <c r="M10" s="334" t="n">
+      <c r="K10" s="350" t="n"/>
+      <c r="L10" s="348" t="n"/>
+      <c r="M10" s="345" t="n">
         <v>45114</v>
       </c>
       <c r="N10" s="69" t="inlineStr">
@@ -6998,15 +7062,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O10" s="338" t="n"/>
+      <c r="O10" s="349" t="n"/>
       <c r="P10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="339" t="n"/>
-      <c r="R10" s="337" t="n"/>
-      <c r="S10" s="340" t="n">
+      <c r="Q10" s="350" t="n"/>
+      <c r="R10" s="348" t="n"/>
+      <c r="S10" s="351" t="n">
         <v>45145</v>
       </c>
       <c r="T10" s="69" t="inlineStr">
@@ -7014,17 +7078,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U10" s="338" t="n"/>
+      <c r="U10" s="349" t="n"/>
       <c r="V10" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="339" t="n"/>
-      <c r="X10" s="337" t="n"/>
+      <c r="W10" s="350" t="n"/>
+      <c r="X10" s="348" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" s="257">
-      <c r="A11" s="334" t="n">
+      <c r="A11" s="345" t="n">
         <v>45054</v>
       </c>
       <c r="B11" s="69" t="inlineStr">
@@ -7032,15 +7096,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C11" s="338" t="n"/>
+      <c r="C11" s="349" t="n"/>
       <c r="D11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="339" t="n"/>
-      <c r="F11" s="337" t="n"/>
-      <c r="G11" s="334" t="n">
+      <c r="E11" s="350" t="n"/>
+      <c r="F11" s="348" t="n"/>
+      <c r="G11" s="345" t="n">
         <v>45085</v>
       </c>
       <c r="H11" s="70" t="inlineStr">
@@ -7048,15 +7112,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I11" s="338" t="n"/>
+      <c r="I11" s="349" t="n"/>
       <c r="J11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="339" t="n"/>
-      <c r="L11" s="337" t="n"/>
-      <c r="M11" s="334" t="n">
+      <c r="K11" s="350" t="n"/>
+      <c r="L11" s="348" t="n"/>
+      <c r="M11" s="345" t="n">
         <v>45115</v>
       </c>
       <c r="N11" s="69" t="inlineStr">
@@ -7064,15 +7128,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O11" s="338" t="n"/>
+      <c r="O11" s="349" t="n"/>
       <c r="P11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="339" t="n"/>
-      <c r="R11" s="337" t="n"/>
-      <c r="S11" s="340" t="n">
+      <c r="Q11" s="350" t="n"/>
+      <c r="R11" s="348" t="n"/>
+      <c r="S11" s="351" t="n">
         <v>45146</v>
       </c>
       <c r="T11" s="69" t="inlineStr">
@@ -7080,17 +7144,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U11" s="338" t="n"/>
+      <c r="U11" s="349" t="n"/>
       <c r="V11" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="339" t="n"/>
-      <c r="X11" s="337" t="n"/>
+      <c r="W11" s="350" t="n"/>
+      <c r="X11" s="348" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" s="257">
-      <c r="A12" s="334" t="n">
+      <c r="A12" s="345" t="n">
         <v>45055</v>
       </c>
       <c r="B12" s="69" t="inlineStr">
@@ -7098,40 +7162,40 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C12" s="338" t="n"/>
+      <c r="C12" s="349" t="n"/>
       <c r="D12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="339" t="n"/>
-      <c r="F12" s="337" t="n"/>
-      <c r="G12" s="341" t="n">
+      <c r="E12" s="350" t="n"/>
+      <c r="F12" s="348" t="n"/>
+      <c r="G12" s="352" t="n">
         <v>45086</v>
       </c>
-      <c r="H12" s="347" t="inlineStr">
+      <c r="H12" s="358" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I12" s="343">
+      <c r="I12" s="354">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="344" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="345">
+      <c r="J12" s="355" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="356">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="346">
+      <c r="L12" s="357">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="334" t="n">
+      <c r="M12" s="345" t="n">
         <v>45116</v>
       </c>
       <c r="N12" s="69" t="inlineStr">
@@ -7139,15 +7203,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O12" s="338" t="n"/>
+      <c r="O12" s="349" t="n"/>
       <c r="P12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="339" t="n"/>
-      <c r="R12" s="337" t="n"/>
-      <c r="S12" s="340" t="n">
+      <c r="Q12" s="350" t="n"/>
+      <c r="R12" s="348" t="n"/>
+      <c r="S12" s="351" t="n">
         <v>45147</v>
       </c>
       <c r="T12" s="69" t="inlineStr">
@@ -7155,17 +7219,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U12" s="338" t="n"/>
+      <c r="U12" s="349" t="n"/>
       <c r="V12" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="339" t="n"/>
-      <c r="X12" s="337" t="n"/>
+      <c r="W12" s="350" t="n"/>
+      <c r="X12" s="348" t="n"/>
     </row>
     <row r="13" ht="16.15" customHeight="1" s="257">
-      <c r="A13" s="334" t="n">
+      <c r="A13" s="345" t="n">
         <v>45056</v>
       </c>
       <c r="B13" s="69" t="inlineStr">
@@ -7173,15 +7237,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C13" s="338" t="n"/>
+      <c r="C13" s="349" t="n"/>
       <c r="D13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="339" t="n"/>
-      <c r="F13" s="337" t="n"/>
-      <c r="G13" s="334" t="n">
+      <c r="E13" s="350" t="n"/>
+      <c r="F13" s="348" t="n"/>
+      <c r="G13" s="345" t="n">
         <v>45087</v>
       </c>
       <c r="H13" s="70" t="inlineStr">
@@ -7189,7 +7253,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I13" s="338">
+      <c r="I13" s="349">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -7198,15 +7262,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="339">
+      <c r="K13" s="350">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="337">
+      <c r="L13" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="334" t="n">
+      <c r="M13" s="345" t="n">
         <v>45117</v>
       </c>
       <c r="N13" s="69" t="inlineStr">
@@ -7214,15 +7278,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O13" s="338" t="n"/>
+      <c r="O13" s="349" t="n"/>
       <c r="P13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="339" t="n"/>
-      <c r="R13" s="337" t="n"/>
-      <c r="S13" s="340" t="n">
+      <c r="Q13" s="350" t="n"/>
+      <c r="R13" s="348" t="n"/>
+      <c r="S13" s="351" t="n">
         <v>45148</v>
       </c>
       <c r="T13" s="69" t="inlineStr">
@@ -7230,17 +7294,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U13" s="338" t="n"/>
+      <c r="U13" s="349" t="n"/>
       <c r="V13" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="339" t="n"/>
-      <c r="X13" s="337" t="n"/>
+      <c r="W13" s="350" t="n"/>
+      <c r="X13" s="348" t="n"/>
     </row>
     <row r="14" ht="16.15" customHeight="1" s="257">
-      <c r="A14" s="334" t="n">
+      <c r="A14" s="345" t="n">
         <v>45057</v>
       </c>
       <c r="B14" s="69" t="inlineStr">
@@ -7248,15 +7312,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C14" s="338" t="n"/>
+      <c r="C14" s="349" t="n"/>
       <c r="D14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="339" t="n"/>
-      <c r="F14" s="337" t="n"/>
-      <c r="G14" s="334" t="n">
+      <c r="E14" s="350" t="n"/>
+      <c r="F14" s="348" t="n"/>
+      <c r="G14" s="345" t="n">
         <v>45088</v>
       </c>
       <c r="H14" s="70" t="inlineStr">
@@ -7264,7 +7328,7 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I14" s="338">
+      <c r="I14" s="349">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -7273,15 +7337,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="339">
+      <c r="K14" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="337">
+      <c r="L14" s="348">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="334" t="n">
+      <c r="M14" s="345" t="n">
         <v>45118</v>
       </c>
       <c r="N14" s="69" t="inlineStr">
@@ -7289,15 +7353,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O14" s="338" t="n"/>
+      <c r="O14" s="349" t="n"/>
       <c r="P14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="339" t="n"/>
-      <c r="R14" s="337" t="n"/>
-      <c r="S14" s="340" t="n">
+      <c r="Q14" s="350" t="n"/>
+      <c r="R14" s="348" t="n"/>
+      <c r="S14" s="351" t="n">
         <v>45149</v>
       </c>
       <c r="T14" s="69" t="inlineStr">
@@ -7305,17 +7369,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U14" s="338" t="n"/>
+      <c r="U14" s="349" t="n"/>
       <c r="V14" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W14" s="339" t="n"/>
-      <c r="X14" s="337" t="n"/>
+      <c r="W14" s="350" t="n"/>
+      <c r="X14" s="348" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" s="257">
-      <c r="A15" s="334" t="n">
+      <c r="A15" s="345" t="n">
         <v>45058</v>
       </c>
       <c r="B15" s="69" t="inlineStr">
@@ -7323,15 +7387,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C15" s="338" t="n"/>
+      <c r="C15" s="349" t="n"/>
       <c r="D15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="339" t="n"/>
-      <c r="F15" s="337" t="n"/>
-      <c r="G15" s="334" t="n">
+      <c r="E15" s="350" t="n"/>
+      <c r="F15" s="348" t="n"/>
+      <c r="G15" s="345" t="n">
         <v>45089</v>
       </c>
       <c r="H15" s="70" t="inlineStr">
@@ -7339,15 +7403,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I15" s="338" t="n"/>
+      <c r="I15" s="349" t="n"/>
       <c r="J15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="339" t="n"/>
-      <c r="L15" s="337" t="n"/>
-      <c r="M15" s="334" t="n">
+      <c r="K15" s="350" t="n"/>
+      <c r="L15" s="348" t="n"/>
+      <c r="M15" s="345" t="n">
         <v>45119</v>
       </c>
       <c r="N15" s="69" t="inlineStr">
@@ -7355,15 +7419,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O15" s="338" t="n"/>
+      <c r="O15" s="349" t="n"/>
       <c r="P15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="339" t="n"/>
-      <c r="R15" s="337" t="n"/>
-      <c r="S15" s="340" t="n">
+      <c r="Q15" s="350" t="n"/>
+      <c r="R15" s="348" t="n"/>
+      <c r="S15" s="351" t="n">
         <v>45150</v>
       </c>
       <c r="T15" s="69" t="inlineStr">
@@ -7371,17 +7435,17 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U15" s="338" t="n"/>
+      <c r="U15" s="349" t="n"/>
       <c r="V15" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W15" s="339" t="n"/>
-      <c r="X15" s="337" t="n"/>
+      <c r="W15" s="350" t="n"/>
+      <c r="X15" s="348" t="n"/>
     </row>
     <row r="16" ht="16.15" customHeight="1" s="257">
-      <c r="A16" s="334" t="n">
+      <c r="A16" s="345" t="n">
         <v>45059</v>
       </c>
       <c r="B16" s="69" t="inlineStr">
@@ -7389,15 +7453,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C16" s="338" t="n"/>
+      <c r="C16" s="349" t="n"/>
       <c r="D16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="339" t="n"/>
-      <c r="F16" s="337" t="n"/>
-      <c r="G16" s="334" t="n">
+      <c r="E16" s="350" t="n"/>
+      <c r="F16" s="348" t="n"/>
+      <c r="G16" s="345" t="n">
         <v>45090</v>
       </c>
       <c r="H16" s="70" t="inlineStr">
@@ -7405,15 +7469,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I16" s="338" t="n"/>
+      <c r="I16" s="349" t="n"/>
       <c r="J16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="339" t="n"/>
-      <c r="L16" s="337" t="n"/>
-      <c r="M16" s="334" t="n">
+      <c r="K16" s="350" t="n"/>
+      <c r="L16" s="348" t="n"/>
+      <c r="M16" s="345" t="n">
         <v>45120</v>
       </c>
       <c r="N16" s="69" t="inlineStr">
@@ -7421,15 +7485,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O16" s="338" t="n"/>
+      <c r="O16" s="349" t="n"/>
       <c r="P16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="339" t="n"/>
-      <c r="R16" s="337" t="n"/>
-      <c r="S16" s="340" t="n">
+      <c r="Q16" s="350" t="n"/>
+      <c r="R16" s="348" t="n"/>
+      <c r="S16" s="351" t="n">
         <v>45151</v>
       </c>
       <c r="T16" s="69" t="inlineStr">
@@ -7437,17 +7501,17 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U16" s="338" t="n"/>
+      <c r="U16" s="349" t="n"/>
       <c r="V16" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W16" s="339" t="n"/>
-      <c r="X16" s="337" t="n"/>
+      <c r="W16" s="350" t="n"/>
+      <c r="X16" s="348" t="n"/>
     </row>
     <row r="17" ht="16.15" customHeight="1" s="257">
-      <c r="A17" s="334" t="n">
+      <c r="A17" s="345" t="n">
         <v>45060</v>
       </c>
       <c r="B17" s="69" t="inlineStr">
@@ -7455,15 +7519,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C17" s="338" t="n"/>
+      <c r="C17" s="349" t="n"/>
       <c r="D17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="339" t="n"/>
-      <c r="F17" s="337" t="n"/>
-      <c r="G17" s="334" t="n">
+      <c r="E17" s="350" t="n"/>
+      <c r="F17" s="348" t="n"/>
+      <c r="G17" s="345" t="n">
         <v>45091</v>
       </c>
       <c r="H17" s="70" t="inlineStr">
@@ -7471,15 +7535,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I17" s="338" t="n"/>
+      <c r="I17" s="349" t="n"/>
       <c r="J17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="339" t="n"/>
-      <c r="L17" s="337" t="n"/>
-      <c r="M17" s="334" t="n">
+      <c r="K17" s="350" t="n"/>
+      <c r="L17" s="348" t="n"/>
+      <c r="M17" s="345" t="n">
         <v>45121</v>
       </c>
       <c r="N17" s="69" t="inlineStr">
@@ -7487,15 +7551,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O17" s="338" t="n"/>
+      <c r="O17" s="349" t="n"/>
       <c r="P17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="339" t="n"/>
-      <c r="R17" s="337" t="n"/>
-      <c r="S17" s="340" t="n">
+      <c r="Q17" s="350" t="n"/>
+      <c r="R17" s="348" t="n"/>
+      <c r="S17" s="351" t="n">
         <v>45152</v>
       </c>
       <c r="T17" s="69" t="inlineStr">
@@ -7503,17 +7567,17 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U17" s="338" t="n"/>
+      <c r="U17" s="349" t="n"/>
       <c r="V17" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W17" s="339" t="n"/>
-      <c r="X17" s="337" t="n"/>
+      <c r="W17" s="350" t="n"/>
+      <c r="X17" s="348" t="n"/>
     </row>
     <row r="18" ht="16.15" customHeight="1" s="257">
-      <c r="A18" s="334" t="n">
+      <c r="A18" s="345" t="n">
         <v>45061</v>
       </c>
       <c r="B18" s="69" t="inlineStr">
@@ -7521,15 +7585,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C18" s="338" t="n"/>
+      <c r="C18" s="349" t="n"/>
       <c r="D18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="339" t="n"/>
-      <c r="F18" s="337" t="n"/>
-      <c r="G18" s="334" t="n">
+      <c r="E18" s="350" t="n"/>
+      <c r="F18" s="348" t="n"/>
+      <c r="G18" s="345" t="n">
         <v>45092</v>
       </c>
       <c r="H18" s="70" t="inlineStr">
@@ -7537,15 +7601,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I18" s="338" t="n"/>
+      <c r="I18" s="349" t="n"/>
       <c r="J18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="339" t="n"/>
-      <c r="L18" s="337" t="n"/>
-      <c r="M18" s="334" t="n">
+      <c r="K18" s="350" t="n"/>
+      <c r="L18" s="348" t="n"/>
+      <c r="M18" s="345" t="n">
         <v>45122</v>
       </c>
       <c r="N18" s="69" t="inlineStr">
@@ -7553,15 +7617,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O18" s="338" t="n"/>
+      <c r="O18" s="349" t="n"/>
       <c r="P18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="339" t="n"/>
-      <c r="R18" s="337" t="n"/>
-      <c r="S18" s="340" t="n">
+      <c r="Q18" s="350" t="n"/>
+      <c r="R18" s="348" t="n"/>
+      <c r="S18" s="351" t="n">
         <v>45153</v>
       </c>
       <c r="T18" s="69" t="inlineStr">
@@ -7569,17 +7633,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U18" s="338" t="n"/>
+      <c r="U18" s="349" t="n"/>
       <c r="V18" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W18" s="339" t="n"/>
-      <c r="X18" s="337" t="n"/>
+      <c r="W18" s="350" t="n"/>
+      <c r="X18" s="348" t="n"/>
     </row>
     <row r="19" ht="16.15" customHeight="1" s="257">
-      <c r="A19" s="334" t="n">
+      <c r="A19" s="345" t="n">
         <v>45062</v>
       </c>
       <c r="B19" s="69" t="inlineStr">
@@ -7587,15 +7651,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C19" s="338" t="n"/>
+      <c r="C19" s="349" t="n"/>
       <c r="D19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="339" t="n"/>
-      <c r="F19" s="337" t="n"/>
-      <c r="G19" s="334" t="n">
+      <c r="E19" s="350" t="n"/>
+      <c r="F19" s="348" t="n"/>
+      <c r="G19" s="345" t="n">
         <v>45093</v>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -7603,15 +7667,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I19" s="338" t="inlineStr">
+      <c r="I19" s="349" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="50" t="n"/>
-      <c r="K19" s="339" t="n"/>
-      <c r="L19" s="337" t="n"/>
-      <c r="M19" s="334" t="n">
+      <c r="K19" s="350" t="n"/>
+      <c r="L19" s="348" t="n"/>
+      <c r="M19" s="345" t="n">
         <v>45123</v>
       </c>
       <c r="N19" s="69" t="inlineStr">
@@ -7619,15 +7683,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O19" s="338" t="n"/>
+      <c r="O19" s="349" t="n"/>
       <c r="P19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="339" t="n"/>
-      <c r="R19" s="337" t="n"/>
-      <c r="S19" s="340" t="n">
+      <c r="Q19" s="350" t="n"/>
+      <c r="R19" s="348" t="n"/>
+      <c r="S19" s="351" t="n">
         <v>45154</v>
       </c>
       <c r="T19" s="69" t="inlineStr">
@@ -7635,17 +7699,17 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U19" s="338" t="n"/>
+      <c r="U19" s="349" t="n"/>
       <c r="V19" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W19" s="339" t="n"/>
-      <c r="X19" s="337" t="n"/>
+      <c r="W19" s="350" t="n"/>
+      <c r="X19" s="348" t="n"/>
     </row>
     <row r="20" ht="16.15" customHeight="1" s="257">
-      <c r="A20" s="334" t="n">
+      <c r="A20" s="345" t="n">
         <v>45063</v>
       </c>
       <c r="B20" s="69" t="inlineStr">
@@ -7653,15 +7717,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C20" s="338" t="n"/>
+      <c r="C20" s="349" t="n"/>
       <c r="D20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="339" t="n"/>
-      <c r="F20" s="337" t="n"/>
-      <c r="G20" s="334" t="n">
+      <c r="E20" s="350" t="n"/>
+      <c r="F20" s="348" t="n"/>
+      <c r="G20" s="345" t="n">
         <v>45094</v>
       </c>
       <c r="H20" s="70" t="inlineStr">
@@ -7669,15 +7733,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I20" s="338" t="inlineStr">
+      <c r="I20" s="349" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="50" t="n"/>
-      <c r="K20" s="339" t="n"/>
-      <c r="L20" s="337" t="n"/>
-      <c r="M20" s="334" t="n">
+      <c r="K20" s="350" t="n"/>
+      <c r="L20" s="348" t="n"/>
+      <c r="M20" s="345" t="n">
         <v>45124</v>
       </c>
       <c r="N20" s="69" t="inlineStr">
@@ -7685,15 +7749,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O20" s="338" t="n"/>
+      <c r="O20" s="349" t="n"/>
       <c r="P20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="339" t="n"/>
-      <c r="R20" s="337" t="n"/>
-      <c r="S20" s="340" t="n">
+      <c r="Q20" s="350" t="n"/>
+      <c r="R20" s="348" t="n"/>
+      <c r="S20" s="351" t="n">
         <v>45155</v>
       </c>
       <c r="T20" s="69" t="inlineStr">
@@ -7701,17 +7765,17 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U20" s="338" t="n"/>
+      <c r="U20" s="349" t="n"/>
       <c r="V20" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W20" s="339" t="n"/>
-      <c r="X20" s="337" t="n"/>
+      <c r="W20" s="350" t="n"/>
+      <c r="X20" s="348" t="n"/>
     </row>
     <row r="21" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A21" s="334" t="n">
+      <c r="A21" s="345" t="n">
         <v>45064</v>
       </c>
       <c r="B21" s="69" t="inlineStr">
@@ -7719,15 +7783,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C21" s="338" t="n"/>
+      <c r="C21" s="349" t="n"/>
       <c r="D21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="339" t="n"/>
-      <c r="F21" s="337" t="n"/>
-      <c r="G21" s="334" t="n">
+      <c r="E21" s="350" t="n"/>
+      <c r="F21" s="348" t="n"/>
+      <c r="G21" s="345" t="n">
         <v>45095</v>
       </c>
       <c r="H21" s="70" t="inlineStr">
@@ -7735,15 +7799,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I21" s="338" t="inlineStr">
+      <c r="I21" s="349" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="50" t="n"/>
-      <c r="K21" s="339" t="n"/>
-      <c r="L21" s="337" t="n"/>
-      <c r="M21" s="334" t="n">
+      <c r="K21" s="350" t="n"/>
+      <c r="L21" s="348" t="n"/>
+      <c r="M21" s="345" t="n">
         <v>45125</v>
       </c>
       <c r="N21" s="69" t="inlineStr">
@@ -7751,15 +7815,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O21" s="338" t="n"/>
+      <c r="O21" s="349" t="n"/>
       <c r="P21" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="339" t="n"/>
-      <c r="R21" s="337" t="n"/>
-      <c r="S21" s="348" t="n">
+      <c r="Q21" s="350" t="n"/>
+      <c r="R21" s="348" t="n"/>
+      <c r="S21" s="359" t="n">
         <v>45156</v>
       </c>
       <c r="T21" s="71" t="inlineStr">
@@ -7767,17 +7831,17 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U21" s="349" t="n"/>
+      <c r="U21" s="360" t="n"/>
       <c r="V21" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W21" s="350" t="n"/>
-      <c r="X21" s="351" t="n"/>
+      <c r="W21" s="361" t="n"/>
+      <c r="X21" s="362" t="n"/>
     </row>
     <row r="22" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A22" s="334" t="n">
+      <c r="A22" s="345" t="n">
         <v>45065</v>
       </c>
       <c r="B22" s="69" t="inlineStr">
@@ -7785,15 +7849,15 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C22" s="338" t="n"/>
+      <c r="C22" s="349" t="n"/>
       <c r="D22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="339" t="n"/>
-      <c r="F22" s="337" t="n"/>
-      <c r="G22" s="334" t="n">
+      <c r="E22" s="350" t="n"/>
+      <c r="F22" s="348" t="n"/>
+      <c r="G22" s="345" t="n">
         <v>45096</v>
       </c>
       <c r="H22" s="70" t="inlineStr">
@@ -7801,11 +7865,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I22" s="338" t="n"/>
+      <c r="I22" s="349" t="n"/>
       <c r="J22" s="50" t="n"/>
-      <c r="K22" s="339" t="n"/>
-      <c r="L22" s="337" t="n"/>
-      <c r="M22" s="334" t="n">
+      <c r="K22" s="350" t="n"/>
+      <c r="L22" s="348" t="n"/>
+      <c r="M22" s="345" t="n">
         <v>45126</v>
       </c>
       <c r="N22" s="69" t="inlineStr">
@@ -7813,27 +7877,27 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O22" s="338" t="n"/>
+      <c r="O22" s="349" t="n"/>
       <c r="P22" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="339" t="n"/>
-      <c r="R22" s="337" t="n"/>
+      <c r="Q22" s="350" t="n"/>
+      <c r="R22" s="348" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="U22" s="352" t="n"/>
+      <c r="U22" s="363" t="n"/>
       <c r="V22" s="238" t="n"/>
-      <c r="W22" s="353" t="n"/>
-      <c r="X22" s="353" t="n"/>
+      <c r="W22" s="364" t="n"/>
+      <c r="X22" s="364" t="n"/>
     </row>
     <row r="23" ht="16.15" customHeight="1" s="257">
-      <c r="A23" s="334" t="n">
+      <c r="A23" s="345" t="n">
         <v>45066</v>
       </c>
       <c r="B23" s="69" t="inlineStr">
@@ -7841,15 +7905,15 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C23" s="338" t="n"/>
+      <c r="C23" s="349" t="n"/>
       <c r="D23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="339" t="n"/>
-      <c r="F23" s="337" t="n"/>
-      <c r="G23" s="334" t="n">
+      <c r="E23" s="350" t="n"/>
+      <c r="F23" s="348" t="n"/>
+      <c r="G23" s="345" t="n">
         <v>45097</v>
       </c>
       <c r="H23" s="70" t="inlineStr">
@@ -7857,11 +7921,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I23" s="338" t="n"/>
+      <c r="I23" s="349" t="n"/>
       <c r="J23" s="50" t="n"/>
-      <c r="K23" s="339" t="n"/>
-      <c r="L23" s="337" t="n"/>
-      <c r="M23" s="334" t="n">
+      <c r="K23" s="350" t="n"/>
+      <c r="L23" s="348" t="n"/>
+      <c r="M23" s="345" t="n">
         <v>45127</v>
       </c>
       <c r="N23" s="69" t="inlineStr">
@@ -7869,31 +7933,31 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O23" s="338" t="n"/>
+      <c r="O23" s="349" t="n"/>
       <c r="P23" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="339" t="n"/>
-      <c r="R23" s="337" t="n"/>
-      <c r="S23" s="354" t="inlineStr">
+      <c r="Q23" s="350" t="n"/>
+      <c r="R23" s="348" t="n"/>
+      <c r="S23" s="365" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="T23" s="355" t="inlineStr">
+      <c r="T23" s="366" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="U23" s="332" t="n"/>
-      <c r="V23" s="332" t="n"/>
-      <c r="W23" s="332" t="n"/>
-      <c r="X23" s="356" t="n"/>
+      <c r="U23" s="343" t="n"/>
+      <c r="V23" s="343" t="n"/>
+      <c r="W23" s="343" t="n"/>
+      <c r="X23" s="367" t="n"/>
     </row>
     <row r="24" ht="16.15" customHeight="1" s="257">
-      <c r="A24" s="334" t="n">
+      <c r="A24" s="345" t="n">
         <v>45067</v>
       </c>
       <c r="B24" s="69" t="inlineStr">
@@ -7901,15 +7965,15 @@
           <t>木</t>
         </is>
       </c>
-      <c r="C24" s="338" t="n"/>
+      <c r="C24" s="349" t="n"/>
       <c r="D24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="339" t="n"/>
-      <c r="F24" s="337" t="n"/>
-      <c r="G24" s="334" t="n">
+      <c r="E24" s="350" t="n"/>
+      <c r="F24" s="348" t="n"/>
+      <c r="G24" s="345" t="n">
         <v>45098</v>
       </c>
       <c r="H24" s="70" t="inlineStr">
@@ -7917,11 +7981,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I24" s="338" t="n"/>
+      <c r="I24" s="349" t="n"/>
       <c r="J24" s="50" t="n"/>
-      <c r="K24" s="339" t="n"/>
-      <c r="L24" s="337" t="n"/>
-      <c r="M24" s="334" t="n">
+      <c r="K24" s="350" t="n"/>
+      <c r="L24" s="348" t="n"/>
+      <c r="M24" s="345" t="n">
         <v>45128</v>
       </c>
       <c r="N24" s="69" t="inlineStr">
@@ -7929,14 +7993,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O24" s="338" t="n"/>
+      <c r="O24" s="349" t="n"/>
       <c r="P24" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="339" t="n"/>
-      <c r="R24" s="337" t="n"/>
+      <c r="Q24" s="350" t="n"/>
+      <c r="R24" s="348" t="n"/>
       <c r="S24" s="73" t="n">
         <v>1</v>
       </c>
@@ -7945,13 +8009,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U24" s="293" t="n"/>
-      <c r="V24" s="293" t="n"/>
-      <c r="W24" s="293" t="n"/>
-      <c r="X24" s="294" t="n"/>
+      <c r="U24" s="297" t="n"/>
+      <c r="V24" s="297" t="n"/>
+      <c r="W24" s="297" t="n"/>
+      <c r="X24" s="298" t="n"/>
     </row>
     <row r="25" ht="16.15" customHeight="1" s="257">
-      <c r="A25" s="334" t="n">
+      <c r="A25" s="345" t="n">
         <v>45068</v>
       </c>
       <c r="B25" s="69" t="inlineStr">
@@ -7959,15 +8023,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C25" s="338" t="n"/>
+      <c r="C25" s="349" t="n"/>
       <c r="D25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="339" t="n"/>
-      <c r="F25" s="337" t="n"/>
-      <c r="G25" s="334" t="n">
+      <c r="E25" s="350" t="n"/>
+      <c r="F25" s="348" t="n"/>
+      <c r="G25" s="345" t="n">
         <v>45099</v>
       </c>
       <c r="H25" s="70" t="inlineStr">
@@ -7975,11 +8039,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I25" s="338" t="n"/>
+      <c r="I25" s="349" t="n"/>
       <c r="J25" s="50" t="n"/>
-      <c r="K25" s="339" t="n"/>
-      <c r="L25" s="337" t="n"/>
-      <c r="M25" s="334" t="n">
+      <c r="K25" s="350" t="n"/>
+      <c r="L25" s="348" t="n"/>
+      <c r="M25" s="345" t="n">
         <v>45129</v>
       </c>
       <c r="N25" s="69" t="inlineStr">
@@ -7987,14 +8051,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O25" s="338" t="n"/>
+      <c r="O25" s="349" t="n"/>
       <c r="P25" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="339" t="n"/>
-      <c r="R25" s="337" t="n"/>
+      <c r="Q25" s="350" t="n"/>
+      <c r="R25" s="348" t="n"/>
       <c r="S25" s="73" t="n">
         <v>2</v>
       </c>
@@ -8003,13 +8067,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U25" s="293" t="n"/>
-      <c r="V25" s="293" t="n"/>
-      <c r="W25" s="293" t="n"/>
-      <c r="X25" s="294" t="n"/>
+      <c r="U25" s="297" t="n"/>
+      <c r="V25" s="297" t="n"/>
+      <c r="W25" s="297" t="n"/>
+      <c r="X25" s="298" t="n"/>
     </row>
     <row r="26" ht="16.15" customHeight="1" s="257">
-      <c r="A26" s="334" t="n">
+      <c r="A26" s="345" t="n">
         <v>45069</v>
       </c>
       <c r="B26" s="69" t="inlineStr">
@@ -8017,36 +8081,36 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C26" s="338" t="n"/>
+      <c r="C26" s="349" t="n"/>
       <c r="D26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="339" t="n"/>
-      <c r="F26" s="337" t="n"/>
-      <c r="G26" s="341" t="n">
+      <c r="E26" s="350" t="n"/>
+      <c r="F26" s="348" t="n"/>
+      <c r="G26" s="352" t="n">
         <v>45100</v>
       </c>
-      <c r="H26" s="347" t="inlineStr">
+      <c r="H26" s="358" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="I26" s="343">
+      <c r="I26" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="344" t="n"/>
-      <c r="K26" s="345">
+      <c r="J26" s="355" t="n"/>
+      <c r="K26" s="356">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="346">
+      <c r="L26" s="357">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="334" t="n">
+      <c r="M26" s="345" t="n">
         <v>45130</v>
       </c>
       <c r="N26" s="69" t="inlineStr">
@@ -8054,14 +8118,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O26" s="338" t="n"/>
+      <c r="O26" s="349" t="n"/>
       <c r="P26" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="339" t="n"/>
-      <c r="R26" s="337" t="n"/>
+      <c r="Q26" s="350" t="n"/>
+      <c r="R26" s="348" t="n"/>
       <c r="S26" s="73" t="n">
         <v>3</v>
       </c>
@@ -8070,13 +8134,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U26" s="293" t="n"/>
-      <c r="V26" s="293" t="n"/>
-      <c r="W26" s="293" t="n"/>
-      <c r="X26" s="294" t="n"/>
+      <c r="U26" s="297" t="n"/>
+      <c r="V26" s="297" t="n"/>
+      <c r="W26" s="297" t="n"/>
+      <c r="X26" s="298" t="n"/>
     </row>
     <row r="27" ht="16.15" customHeight="1" s="257">
-      <c r="A27" s="334" t="n">
+      <c r="A27" s="345" t="n">
         <v>45070</v>
       </c>
       <c r="B27" s="69" t="inlineStr">
@@ -8084,15 +8148,15 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C27" s="338" t="n"/>
+      <c r="C27" s="349" t="n"/>
       <c r="D27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="339" t="n"/>
-      <c r="F27" s="337" t="n"/>
-      <c r="G27" s="334" t="n">
+      <c r="E27" s="350" t="n"/>
+      <c r="F27" s="348" t="n"/>
+      <c r="G27" s="345" t="n">
         <v>45101</v>
       </c>
       <c r="H27" s="70" t="inlineStr">
@@ -8100,20 +8164,20 @@
           <t>水</t>
         </is>
       </c>
-      <c r="I27" s="338">
+      <c r="I27" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J27" s="50" t="n"/>
-      <c r="K27" s="339">
+      <c r="K27" s="350">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="348">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="334" t="n">
+      <c r="M27" s="345" t="n">
         <v>45131</v>
       </c>
       <c r="N27" s="69" t="inlineStr">
@@ -8121,14 +8185,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O27" s="338" t="n"/>
+      <c r="O27" s="349" t="n"/>
       <c r="P27" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="339" t="n"/>
-      <c r="R27" s="337" t="n"/>
+      <c r="Q27" s="350" t="n"/>
+      <c r="R27" s="348" t="n"/>
       <c r="S27" s="73" t="n">
         <v>4</v>
       </c>
@@ -8137,13 +8201,13 @@
           <t>月</t>
         </is>
       </c>
-      <c r="U27" s="293" t="n"/>
-      <c r="V27" s="293" t="n"/>
-      <c r="W27" s="293" t="n"/>
-      <c r="X27" s="294" t="n"/>
+      <c r="U27" s="297" t="n"/>
+      <c r="V27" s="297" t="n"/>
+      <c r="W27" s="297" t="n"/>
+      <c r="X27" s="298" t="n"/>
     </row>
     <row r="28" ht="16.15" customHeight="1" s="257">
-      <c r="A28" s="334" t="n">
+      <c r="A28" s="345" t="n">
         <v>45071</v>
       </c>
       <c r="B28" s="69" t="inlineStr">
@@ -8151,15 +8215,15 @@
           <t>月</t>
         </is>
       </c>
-      <c r="C28" s="338" t="n"/>
+      <c r="C28" s="349" t="n"/>
       <c r="D28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="339" t="n"/>
-      <c r="F28" s="337" t="n"/>
-      <c r="G28" s="334" t="n">
+      <c r="E28" s="350" t="n"/>
+      <c r="F28" s="348" t="n"/>
+      <c r="G28" s="345" t="n">
         <v>45102</v>
       </c>
       <c r="H28" s="70" t="inlineStr">
@@ -8167,20 +8231,20 @@
           <t>木</t>
         </is>
       </c>
-      <c r="I28" s="338">
+      <c r="I28" s="349">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
       <c r="J28" s="50" t="n"/>
-      <c r="K28" s="339">
+      <c r="K28" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="337">
+      <c r="L28" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="334" t="n">
+      <c r="M28" s="345" t="n">
         <v>45132</v>
       </c>
       <c r="N28" s="69" t="inlineStr">
@@ -8188,14 +8252,14 @@
           <t>土</t>
         </is>
       </c>
-      <c r="O28" s="338" t="n"/>
+      <c r="O28" s="349" t="n"/>
       <c r="P28" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="339" t="n"/>
-      <c r="R28" s="337" t="n"/>
+      <c r="Q28" s="350" t="n"/>
+      <c r="R28" s="348" t="n"/>
       <c r="S28" s="73" t="n">
         <v>5</v>
       </c>
@@ -8204,13 +8268,13 @@
           <t>火</t>
         </is>
       </c>
-      <c r="U28" s="293" t="n"/>
-      <c r="V28" s="293" t="n"/>
-      <c r="W28" s="293" t="n"/>
-      <c r="X28" s="294" t="n"/>
+      <c r="U28" s="297" t="n"/>
+      <c r="V28" s="297" t="n"/>
+      <c r="W28" s="297" t="n"/>
+      <c r="X28" s="298" t="n"/>
     </row>
     <row r="29" ht="16.15" customHeight="1" s="257">
-      <c r="A29" s="334" t="n">
+      <c r="A29" s="345" t="n">
         <v>45072</v>
       </c>
       <c r="B29" s="69" t="inlineStr">
@@ -8218,7 +8282,7 @@
           <t>火</t>
         </is>
       </c>
-      <c r="C29" s="338">
+      <c r="C29" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -8227,15 +8291,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="339">
+      <c r="E29" s="350">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="337">
+      <c r="F29" s="348">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="334" t="n">
+      <c r="G29" s="345" t="n">
         <v>45103</v>
       </c>
       <c r="H29" s="70" t="inlineStr">
@@ -8243,11 +8307,11 @@
           <t>金</t>
         </is>
       </c>
-      <c r="I29" s="338" t="n"/>
+      <c r="I29" s="349" t="n"/>
       <c r="J29" s="50" t="n"/>
-      <c r="K29" s="339" t="n"/>
-      <c r="L29" s="337" t="n"/>
-      <c r="M29" s="334" t="n">
+      <c r="K29" s="350" t="n"/>
+      <c r="L29" s="348" t="n"/>
+      <c r="M29" s="345" t="n">
         <v>45133</v>
       </c>
       <c r="N29" s="69" t="inlineStr">
@@ -8255,14 +8319,14 @@
           <t>日</t>
         </is>
       </c>
-      <c r="O29" s="338" t="n"/>
+      <c r="O29" s="349" t="n"/>
       <c r="P29" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="339" t="n"/>
-      <c r="R29" s="337" t="n"/>
+      <c r="Q29" s="350" t="n"/>
+      <c r="R29" s="348" t="n"/>
       <c r="S29" s="73" t="n">
         <v>6</v>
       </c>
@@ -8271,13 +8335,13 @@
           <t>水</t>
         </is>
       </c>
-      <c r="U29" s="293" t="n"/>
-      <c r="V29" s="293" t="n"/>
-      <c r="W29" s="293" t="n"/>
-      <c r="X29" s="294" t="n"/>
+      <c r="U29" s="297" t="n"/>
+      <c r="V29" s="297" t="n"/>
+      <c r="W29" s="297" t="n"/>
+      <c r="X29" s="298" t="n"/>
     </row>
     <row r="30" ht="16.15" customHeight="1" s="257">
-      <c r="A30" s="334" t="n">
+      <c r="A30" s="345" t="n">
         <v>45073</v>
       </c>
       <c r="B30" s="69" t="inlineStr">
@@ -8285,7 +8349,7 @@
           <t>水</t>
         </is>
       </c>
-      <c r="C30" s="338">
+      <c r="C30" s="349">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -8294,15 +8358,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="339">
+      <c r="E30" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="337">
+      <c r="F30" s="348">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="334" t="n">
+      <c r="G30" s="345" t="n">
         <v>45104</v>
       </c>
       <c r="H30" s="70" t="inlineStr">
@@ -8310,11 +8374,11 @@
           <t>土</t>
         </is>
       </c>
-      <c r="I30" s="338" t="n"/>
+      <c r="I30" s="349" t="n"/>
       <c r="J30" s="50" t="n"/>
-      <c r="K30" s="339" t="n"/>
-      <c r="L30" s="337" t="n"/>
-      <c r="M30" s="334" t="n">
+      <c r="K30" s="350" t="n"/>
+      <c r="L30" s="348" t="n"/>
+      <c r="M30" s="345" t="n">
         <v>45134</v>
       </c>
       <c r="N30" s="69" t="inlineStr">
@@ -8322,14 +8386,14 @@
           <t>月</t>
         </is>
       </c>
-      <c r="O30" s="338" t="n"/>
+      <c r="O30" s="349" t="n"/>
       <c r="P30" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="339" t="n"/>
-      <c r="R30" s="337" t="n"/>
+      <c r="Q30" s="350" t="n"/>
+      <c r="R30" s="348" t="n"/>
       <c r="S30" s="73" t="n">
         <v>7</v>
       </c>
@@ -8338,38 +8402,38 @@
           <t>木</t>
         </is>
       </c>
-      <c r="U30" s="293" t="n"/>
-      <c r="V30" s="293" t="n"/>
-      <c r="W30" s="293" t="n"/>
-      <c r="X30" s="294" t="n"/>
+      <c r="U30" s="297" t="n"/>
+      <c r="V30" s="297" t="n"/>
+      <c r="W30" s="297" t="n"/>
+      <c r="X30" s="298" t="n"/>
     </row>
     <row r="31" ht="16.15" customHeight="1" s="257">
-      <c r="A31" s="341" t="n">
+      <c r="A31" s="352" t="n">
         <v>45074</v>
       </c>
-      <c r="B31" s="342" t="inlineStr">
+      <c r="B31" s="353" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="C31" s="343">
+      <c r="C31" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="344" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="345">
+      <c r="D31" s="355" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="356">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="346">
+      <c r="F31" s="357">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="334" t="n">
+      <c r="G31" s="345" t="n">
         <v>45105</v>
       </c>
       <c r="H31" s="70" t="inlineStr">
@@ -8377,11 +8441,11 @@
           <t>日</t>
         </is>
       </c>
-      <c r="I31" s="338" t="n"/>
+      <c r="I31" s="349" t="n"/>
       <c r="J31" s="50" t="n"/>
-      <c r="K31" s="339" t="n"/>
-      <c r="L31" s="337" t="n"/>
-      <c r="M31" s="334" t="n">
+      <c r="K31" s="350" t="n"/>
+      <c r="L31" s="348" t="n"/>
+      <c r="M31" s="345" t="n">
         <v>45135</v>
       </c>
       <c r="N31" s="69" t="inlineStr">
@@ -8389,14 +8453,14 @@
           <t>火</t>
         </is>
       </c>
-      <c r="O31" s="338" t="n"/>
+      <c r="O31" s="349" t="n"/>
       <c r="P31" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="339" t="n"/>
-      <c r="R31" s="337" t="n"/>
+      <c r="Q31" s="350" t="n"/>
+      <c r="R31" s="348" t="n"/>
       <c r="S31" s="73" t="n">
         <v>8</v>
       </c>
@@ -8405,13 +8469,13 @@
           <t>金</t>
         </is>
       </c>
-      <c r="U31" s="293" t="n"/>
-      <c r="V31" s="293" t="n"/>
-      <c r="W31" s="293" t="n"/>
-      <c r="X31" s="294" t="n"/>
+      <c r="U31" s="297" t="n"/>
+      <c r="V31" s="297" t="n"/>
+      <c r="W31" s="297" t="n"/>
+      <c r="X31" s="298" t="n"/>
     </row>
     <row r="32" ht="16.15" customHeight="1" s="257">
-      <c r="A32" s="334" t="n">
+      <c r="A32" s="345" t="n">
         <v>45075</v>
       </c>
       <c r="B32" s="69" t="inlineStr">
@@ -8419,15 +8483,15 @@
           <t>金</t>
         </is>
       </c>
-      <c r="C32" s="338" t="n"/>
+      <c r="C32" s="349" t="n"/>
       <c r="D32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="339" t="n"/>
-      <c r="F32" s="337" t="n"/>
-      <c r="G32" s="334" t="n">
+      <c r="E32" s="350" t="n"/>
+      <c r="F32" s="348" t="n"/>
+      <c r="G32" s="345" t="n">
         <v>45106</v>
       </c>
       <c r="H32" s="70" t="inlineStr">
@@ -8435,11 +8499,11 @@
           <t>月</t>
         </is>
       </c>
-      <c r="I32" s="338" t="n"/>
+      <c r="I32" s="349" t="n"/>
       <c r="J32" s="50" t="n"/>
-      <c r="K32" s="339" t="n"/>
-      <c r="L32" s="337" t="n"/>
-      <c r="M32" s="334" t="n">
+      <c r="K32" s="350" t="n"/>
+      <c r="L32" s="348" t="n"/>
+      <c r="M32" s="345" t="n">
         <v>45136</v>
       </c>
       <c r="N32" s="69" t="inlineStr">
@@ -8447,14 +8511,14 @@
           <t>水</t>
         </is>
       </c>
-      <c r="O32" s="338" t="n"/>
+      <c r="O32" s="349" t="n"/>
       <c r="P32" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="339" t="n"/>
-      <c r="R32" s="337" t="n"/>
+      <c r="Q32" s="350" t="n"/>
+      <c r="R32" s="348" t="n"/>
       <c r="S32" s="73" t="n">
         <v>9</v>
       </c>
@@ -8463,13 +8527,13 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U32" s="293" t="n"/>
-      <c r="V32" s="293" t="n"/>
-      <c r="W32" s="293" t="n"/>
-      <c r="X32" s="294" t="n"/>
+      <c r="U32" s="297" t="n"/>
+      <c r="V32" s="297" t="n"/>
+      <c r="W32" s="297" t="n"/>
+      <c r="X32" s="298" t="n"/>
     </row>
     <row r="33" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A33" s="334" t="n">
+      <c r="A33" s="345" t="n">
         <v>45076</v>
       </c>
       <c r="B33" s="69" t="inlineStr">
@@ -8477,15 +8541,15 @@
           <t>土</t>
         </is>
       </c>
-      <c r="C33" s="338" t="n"/>
+      <c r="C33" s="349" t="n"/>
       <c r="D33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="339" t="n"/>
-      <c r="F33" s="337" t="n"/>
-      <c r="G33" s="357" t="n">
+      <c r="E33" s="350" t="n"/>
+      <c r="F33" s="348" t="n"/>
+      <c r="G33" s="368" t="n">
         <v>45107</v>
       </c>
       <c r="H33" s="82" t="inlineStr">
@@ -8493,20 +8557,20 @@
           <t>火</t>
         </is>
       </c>
-      <c r="I33" s="349">
+      <c r="I33" s="360">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
       <c r="J33" s="60" t="n"/>
-      <c r="K33" s="350">
+      <c r="K33" s="361">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="351">
+      <c r="L33" s="362">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="334" t="n">
+      <c r="M33" s="345" t="n">
         <v>45137</v>
       </c>
       <c r="N33" s="69" t="inlineStr">
@@ -8514,14 +8578,14 @@
           <t>木</t>
         </is>
       </c>
-      <c r="O33" s="338" t="n"/>
+      <c r="O33" s="349" t="n"/>
       <c r="P33" s="50" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="339" t="n"/>
-      <c r="R33" s="337" t="n"/>
+      <c r="Q33" s="350" t="n"/>
+      <c r="R33" s="348" t="n"/>
       <c r="S33" s="77" t="n">
         <v>10</v>
       </c>
@@ -8530,13 +8594,13 @@
           <t>日</t>
         </is>
       </c>
-      <c r="U33" s="358" t="n"/>
-      <c r="V33" s="358" t="n"/>
-      <c r="W33" s="358" t="n"/>
-      <c r="X33" s="359" t="n"/>
+      <c r="U33" s="369" t="n"/>
+      <c r="V33" s="369" t="n"/>
+      <c r="W33" s="369" t="n"/>
+      <c r="X33" s="370" t="n"/>
     </row>
     <row r="34" ht="16.15" customHeight="1" s="257" thickBot="1">
-      <c r="A34" s="357" t="n">
+      <c r="A34" s="368" t="n">
         <v>45077</v>
       </c>
       <c r="B34" s="71" t="inlineStr">
@@ -8544,20 +8608,20 @@
           <t>日</t>
         </is>
       </c>
-      <c r="C34" s="349" t="n"/>
+      <c r="C34" s="360" t="n"/>
       <c r="D34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="350" t="n"/>
-      <c r="F34" s="351" t="n"/>
-      <c r="G34" s="360" t="n"/>
-      <c r="I34" s="352" t="n"/>
+      <c r="E34" s="361" t="n"/>
+      <c r="F34" s="362" t="n"/>
+      <c r="G34" s="371" t="n"/>
+      <c r="I34" s="363" t="n"/>
       <c r="J34" s="238" t="n"/>
-      <c r="K34" s="352" t="n"/>
-      <c r="L34" s="352" t="n"/>
-      <c r="M34" s="357" t="n">
+      <c r="K34" s="363" t="n"/>
+      <c r="L34" s="363" t="n"/>
+      <c r="M34" s="368" t="n">
         <v>45138</v>
       </c>
       <c r="N34" s="71" t="inlineStr">
@@ -8565,14 +8629,14 @@
           <t>金</t>
         </is>
       </c>
-      <c r="O34" s="349" t="n"/>
+      <c r="O34" s="360" t="n"/>
       <c r="P34" s="60" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="350" t="n"/>
-      <c r="R34" s="351" t="n"/>
+      <c r="Q34" s="361" t="n"/>
+      <c r="R34" s="362" t="n"/>
       <c r="S34" s="238" t="n"/>
       <c r="T34" s="238" t="inlineStr">
         <is>
@@ -8950,8 +9014,8 @@
         <f>日程表１!T1</f>
         <v/>
       </c>
-      <c r="U1" s="330" t="n"/>
-      <c r="V1" s="330" t="n"/>
+      <c r="U1" s="341" t="n"/>
+      <c r="V1" s="341" t="n"/>
       <c r="W1" s="255" t="inlineStr">
         <is>
           <t>年</t>
@@ -8965,41 +9029,41 @@
           <t>5月</t>
         </is>
       </c>
-      <c r="B2" s="293" t="n"/>
-      <c r="C2" s="293" t="n"/>
-      <c r="D2" s="293" t="n"/>
-      <c r="E2" s="293" t="n"/>
-      <c r="F2" s="294" t="n"/>
+      <c r="B2" s="297" t="n"/>
+      <c r="C2" s="297" t="n"/>
+      <c r="D2" s="297" t="n"/>
+      <c r="E2" s="297" t="n"/>
+      <c r="F2" s="298" t="n"/>
       <c r="G2" s="251" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="H2" s="293" t="n"/>
-      <c r="I2" s="293" t="n"/>
-      <c r="J2" s="293" t="n"/>
-      <c r="K2" s="293" t="n"/>
-      <c r="L2" s="294" t="n"/>
+      <c r="H2" s="297" t="n"/>
+      <c r="I2" s="297" t="n"/>
+      <c r="J2" s="297" t="n"/>
+      <c r="K2" s="297" t="n"/>
+      <c r="L2" s="298" t="n"/>
       <c r="M2" s="251" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N2" s="293" t="n"/>
-      <c r="O2" s="293" t="n"/>
-      <c r="P2" s="293" t="n"/>
-      <c r="Q2" s="293" t="n"/>
-      <c r="R2" s="294" t="n"/>
+      <c r="N2" s="297" t="n"/>
+      <c r="O2" s="297" t="n"/>
+      <c r="P2" s="297" t="n"/>
+      <c r="Q2" s="297" t="n"/>
+      <c r="R2" s="298" t="n"/>
       <c r="S2" s="251" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="T2" s="293" t="n"/>
-      <c r="U2" s="293" t="n"/>
-      <c r="V2" s="293" t="n"/>
-      <c r="W2" s="293" t="n"/>
-      <c r="X2" s="294" t="n"/>
+      <c r="T2" s="297" t="n"/>
+      <c r="U2" s="297" t="n"/>
+      <c r="V2" s="297" t="n"/>
+      <c r="W2" s="297" t="n"/>
+      <c r="X2" s="298" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="251" t="inlineStr">
@@ -9017,8 +9081,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="D3" s="293" t="n"/>
-      <c r="E3" s="294" t="n"/>
+      <c r="D3" s="297" t="n"/>
+      <c r="E3" s="298" t="n"/>
       <c r="F3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9039,8 +9103,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="J3" s="293" t="n"/>
-      <c r="K3" s="294" t="n"/>
+      <c r="J3" s="297" t="n"/>
+      <c r="K3" s="298" t="n"/>
       <c r="L3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9061,8 +9125,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="P3" s="293" t="n"/>
-      <c r="Q3" s="294" t="n"/>
+      <c r="P3" s="297" t="n"/>
+      <c r="Q3" s="298" t="n"/>
       <c r="R3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9083,8 +9147,8 @@
           <t>対戦チーム</t>
         </is>
       </c>
-      <c r="V3" s="293" t="n"/>
-      <c r="W3" s="294" t="n"/>
+      <c r="V3" s="297" t="n"/>
+      <c r="W3" s="298" t="n"/>
       <c r="X3" s="251" t="inlineStr">
         <is>
           <t>審判</t>
@@ -9092,7 +9156,7 @@
       </c>
     </row>
     <row r="4" ht="20.45" customHeight="1" s="257">
-      <c r="A4" s="361">
+      <c r="A4" s="372">
         <f>日程表１!A4</f>
         <v/>
       </c>
@@ -9100,15 +9164,15 @@
         <f>日程表１!B4</f>
         <v/>
       </c>
-      <c r="C4" s="335" t="n"/>
+      <c r="C4" s="346" t="n"/>
       <c r="D4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E4" s="336" t="n"/>
-      <c r="F4" s="362" t="n"/>
-      <c r="G4" s="361">
+      <c r="E4" s="347" t="n"/>
+      <c r="F4" s="373" t="n"/>
+      <c r="G4" s="372">
         <f>日程表１!G4</f>
         <v/>
       </c>
@@ -9116,15 +9180,15 @@
         <f>日程表１!H4</f>
         <v/>
       </c>
-      <c r="I4" s="335" t="n"/>
+      <c r="I4" s="346" t="n"/>
       <c r="J4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K4" s="336" t="n"/>
-      <c r="L4" s="362" t="n"/>
-      <c r="M4" s="361">
+      <c r="K4" s="347" t="n"/>
+      <c r="L4" s="373" t="n"/>
+      <c r="M4" s="372">
         <f>日程表１!M4</f>
         <v/>
       </c>
@@ -9132,7 +9196,7 @@
         <f>日程表１!N4</f>
         <v/>
       </c>
-      <c r="O4" s="335">
+      <c r="O4" s="346">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -9141,15 +9205,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="Q4" s="336">
+      <c r="Q4" s="347">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="R4" s="362">
+      <c r="R4" s="373">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="S4" s="361">
+      <c r="S4" s="372">
         <f>日程表１!S5</f>
         <v/>
       </c>
@@ -9157,17 +9221,17 @@
         <f>日程表１!T5</f>
         <v/>
       </c>
-      <c r="U4" s="335" t="n"/>
+      <c r="U4" s="346" t="n"/>
       <c r="V4" s="27" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W4" s="363" t="n"/>
-      <c r="X4" s="364" t="n"/>
+      <c r="W4" s="374" t="n"/>
+      <c r="X4" s="375" t="n"/>
     </row>
     <row r="5" ht="20.45" customHeight="1" s="257">
-      <c r="A5" s="361">
+      <c r="A5" s="372">
         <f>日程表１!A5</f>
         <v/>
       </c>
@@ -9175,15 +9239,15 @@
         <f>日程表１!B5</f>
         <v/>
       </c>
-      <c r="C5" s="338" t="n"/>
+      <c r="C5" s="349" t="n"/>
       <c r="D5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E5" s="339" t="n"/>
-      <c r="F5" s="362" t="n"/>
-      <c r="G5" s="361">
+      <c r="E5" s="350" t="n"/>
+      <c r="F5" s="373" t="n"/>
+      <c r="G5" s="372">
         <f>日程表１!G5</f>
         <v/>
       </c>
@@ -9191,7 +9255,7 @@
         <f>日程表１!H5</f>
         <v/>
       </c>
-      <c r="I5" s="338">
+      <c r="I5" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -9200,40 +9264,40 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K5" s="339">
+      <c r="K5" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L5" s="362">
+      <c r="L5" s="373">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M5" s="365">
+      <c r="M5" s="376">
         <f>日程表１!M5</f>
         <v/>
       </c>
-      <c r="N5" s="366">
+      <c r="N5" s="377">
         <f>日程表１!N5</f>
         <v/>
       </c>
-      <c r="O5" s="343">
+      <c r="O5" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="P5" s="367" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="Q5" s="345">
+      <c r="P5" s="378" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="Q5" s="356">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="R5" s="368">
+      <c r="R5" s="379">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="S5" s="361">
+      <c r="S5" s="372">
         <f>日程表１!S6</f>
         <v/>
       </c>
@@ -9241,17 +9305,17 @@
         <f>日程表１!T6</f>
         <v/>
       </c>
-      <c r="U5" s="338" t="n"/>
+      <c r="U5" s="349" t="n"/>
       <c r="V5" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W5" s="369" t="n"/>
-      <c r="X5" s="364" t="n"/>
+      <c r="W5" s="380" t="n"/>
+      <c r="X5" s="375" t="n"/>
     </row>
     <row r="6" ht="20.45" customHeight="1" s="257">
-      <c r="A6" s="361">
+      <c r="A6" s="372">
         <f>日程表１!A6</f>
         <v/>
       </c>
@@ -9259,40 +9323,40 @@
         <f>日程表１!B6</f>
         <v/>
       </c>
-      <c r="C6" s="338" t="n"/>
+      <c r="C6" s="349" t="n"/>
       <c r="D6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E6" s="339" t="n"/>
-      <c r="F6" s="362" t="n"/>
-      <c r="G6" s="365">
+      <c r="E6" s="350" t="n"/>
+      <c r="F6" s="373" t="n"/>
+      <c r="G6" s="376">
         <f>日程表１!G6</f>
         <v/>
       </c>
-      <c r="H6" s="366">
+      <c r="H6" s="377">
         <f>日程表１!H6</f>
         <v/>
       </c>
-      <c r="I6" s="343">
+      <c r="I6" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J6" s="367" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K6" s="345">
+      <c r="J6" s="378" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K6" s="356">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="L6" s="368">
+      <c r="L6" s="379">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M6" s="361">
+      <c r="M6" s="372">
         <f>日程表１!M6</f>
         <v/>
       </c>
@@ -9300,15 +9364,15 @@
         <f>日程表１!N6</f>
         <v/>
       </c>
-      <c r="O6" s="338" t="n"/>
+      <c r="O6" s="349" t="n"/>
       <c r="P6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q6" s="339" t="n"/>
-      <c r="R6" s="362" t="n"/>
-      <c r="S6" s="361">
+      <c r="Q6" s="350" t="n"/>
+      <c r="R6" s="373" t="n"/>
+      <c r="S6" s="372">
         <f>日程表１!S7</f>
         <v/>
       </c>
@@ -9316,17 +9380,17 @@
         <f>日程表１!T7</f>
         <v/>
       </c>
-      <c r="U6" s="338" t="n"/>
+      <c r="U6" s="349" t="n"/>
       <c r="V6" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W6" s="369" t="n"/>
-      <c r="X6" s="364" t="n"/>
+      <c r="W6" s="380" t="n"/>
+      <c r="X6" s="375" t="n"/>
     </row>
     <row r="7" ht="20.45" customHeight="1" s="257">
-      <c r="A7" s="361">
+      <c r="A7" s="372">
         <f>日程表１!A7</f>
         <v/>
       </c>
@@ -9334,15 +9398,15 @@
         <f>日程表１!B7</f>
         <v/>
       </c>
-      <c r="C7" s="338" t="n"/>
+      <c r="C7" s="349" t="n"/>
       <c r="D7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E7" s="339" t="n"/>
-      <c r="F7" s="362" t="n"/>
-      <c r="G7" s="361">
+      <c r="E7" s="350" t="n"/>
+      <c r="F7" s="373" t="n"/>
+      <c r="G7" s="372">
         <f>日程表１!G7</f>
         <v/>
       </c>
@@ -9350,7 +9414,7 @@
         <f>日程表１!H7</f>
         <v/>
       </c>
-      <c r="I7" s="338">
+      <c r="I7" s="349">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9359,15 +9423,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K7" s="339">
+      <c r="K7" s="350">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L7" s="362">
+      <c r="L7" s="373">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="M7" s="361">
+      <c r="M7" s="372">
         <f>日程表１!M7</f>
         <v/>
       </c>
@@ -9375,15 +9439,15 @@
         <f>日程表１!N7</f>
         <v/>
       </c>
-      <c r="O7" s="338" t="n"/>
+      <c r="O7" s="349" t="n"/>
       <c r="P7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q7" s="339" t="n"/>
-      <c r="R7" s="362" t="n"/>
-      <c r="S7" s="361">
+      <c r="Q7" s="350" t="n"/>
+      <c r="R7" s="373" t="n"/>
+      <c r="S7" s="372">
         <f>日程表１!S8</f>
         <v/>
       </c>
@@ -9391,17 +9455,17 @@
         <f>日程表１!T8</f>
         <v/>
       </c>
-      <c r="U7" s="338" t="n"/>
+      <c r="U7" s="349" t="n"/>
       <c r="V7" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W7" s="369" t="n"/>
-      <c r="X7" s="364" t="n"/>
+      <c r="W7" s="380" t="n"/>
+      <c r="X7" s="375" t="n"/>
     </row>
     <row r="8" ht="20.45" customHeight="1" s="257">
-      <c r="A8" s="361">
+      <c r="A8" s="372">
         <f>日程表１!A8</f>
         <v/>
       </c>
@@ -9409,15 +9473,15 @@
         <f>日程表１!B8</f>
         <v/>
       </c>
-      <c r="C8" s="338" t="n"/>
+      <c r="C8" s="349" t="n"/>
       <c r="D8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E8" s="339" t="n"/>
-      <c r="F8" s="362" t="n"/>
-      <c r="G8" s="361">
+      <c r="E8" s="350" t="n"/>
+      <c r="F8" s="373" t="n"/>
+      <c r="G8" s="372">
         <f>日程表１!G8</f>
         <v/>
       </c>
@@ -9425,15 +9489,15 @@
         <f>日程表１!H8</f>
         <v/>
       </c>
-      <c r="I8" s="338" t="n"/>
+      <c r="I8" s="349" t="n"/>
       <c r="J8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K8" s="339" t="n"/>
-      <c r="L8" s="362" t="n"/>
-      <c r="M8" s="361">
+      <c r="K8" s="350" t="n"/>
+      <c r="L8" s="373" t="n"/>
+      <c r="M8" s="372">
         <f>日程表１!M8</f>
         <v/>
       </c>
@@ -9441,15 +9505,15 @@
         <f>日程表１!N8</f>
         <v/>
       </c>
-      <c r="O8" s="338" t="n"/>
+      <c r="O8" s="349" t="n"/>
       <c r="P8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q8" s="339" t="n"/>
-      <c r="R8" s="362" t="n"/>
-      <c r="S8" s="361">
+      <c r="Q8" s="350" t="n"/>
+      <c r="R8" s="373" t="n"/>
+      <c r="S8" s="372">
         <f>日程表１!S9</f>
         <v/>
       </c>
@@ -9457,17 +9521,17 @@
         <f>日程表１!T9</f>
         <v/>
       </c>
-      <c r="U8" s="338" t="n"/>
+      <c r="U8" s="349" t="n"/>
       <c r="V8" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W8" s="369" t="n"/>
-      <c r="X8" s="364" t="n"/>
+      <c r="W8" s="380" t="n"/>
+      <c r="X8" s="375" t="n"/>
     </row>
     <row r="9" ht="20.45" customHeight="1" s="257">
-      <c r="A9" s="361">
+      <c r="A9" s="372">
         <f>日程表１!A9</f>
         <v/>
       </c>
@@ -9475,15 +9539,15 @@
         <f>日程表１!B9</f>
         <v/>
       </c>
-      <c r="C9" s="338" t="n"/>
+      <c r="C9" s="349" t="n"/>
       <c r="D9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E9" s="339" t="n"/>
-      <c r="F9" s="362" t="n"/>
-      <c r="G9" s="361">
+      <c r="E9" s="350" t="n"/>
+      <c r="F9" s="373" t="n"/>
+      <c r="G9" s="372">
         <f>日程表１!G9</f>
         <v/>
       </c>
@@ -9491,15 +9555,15 @@
         <f>日程表１!H9</f>
         <v/>
       </c>
-      <c r="I9" s="338" t="n"/>
+      <c r="I9" s="349" t="n"/>
       <c r="J9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K9" s="339" t="n"/>
-      <c r="L9" s="362" t="n"/>
-      <c r="M9" s="361">
+      <c r="K9" s="350" t="n"/>
+      <c r="L9" s="373" t="n"/>
+      <c r="M9" s="372">
         <f>日程表１!M9</f>
         <v/>
       </c>
@@ -9507,15 +9571,15 @@
         <f>日程表１!N9</f>
         <v/>
       </c>
-      <c r="O9" s="338" t="n"/>
+      <c r="O9" s="349" t="n"/>
       <c r="P9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q9" s="339" t="n"/>
-      <c r="R9" s="362" t="n"/>
-      <c r="S9" s="361">
+      <c r="Q9" s="350" t="n"/>
+      <c r="R9" s="373" t="n"/>
+      <c r="S9" s="372">
         <f>日程表１!S10</f>
         <v/>
       </c>
@@ -9523,17 +9587,17 @@
         <f>日程表１!T10</f>
         <v/>
       </c>
-      <c r="U9" s="338" t="n"/>
+      <c r="U9" s="349" t="n"/>
       <c r="V9" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W9" s="369" t="n"/>
-      <c r="X9" s="364" t="n"/>
+      <c r="W9" s="380" t="n"/>
+      <c r="X9" s="375" t="n"/>
     </row>
     <row r="10" ht="20.45" customHeight="1" s="257">
-      <c r="A10" s="361">
+      <c r="A10" s="372">
         <f>日程表１!A10</f>
         <v/>
       </c>
@@ -9541,15 +9605,15 @@
         <f>日程表１!B10</f>
         <v/>
       </c>
-      <c r="C10" s="338" t="n"/>
+      <c r="C10" s="349" t="n"/>
       <c r="D10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E10" s="339" t="n"/>
-      <c r="F10" s="362" t="n"/>
-      <c r="G10" s="361">
+      <c r="E10" s="350" t="n"/>
+      <c r="F10" s="373" t="n"/>
+      <c r="G10" s="372">
         <f>日程表１!G10</f>
         <v/>
       </c>
@@ -9557,15 +9621,15 @@
         <f>日程表１!H10</f>
         <v/>
       </c>
-      <c r="I10" s="338" t="n"/>
+      <c r="I10" s="349" t="n"/>
       <c r="J10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K10" s="339" t="n"/>
-      <c r="L10" s="362" t="n"/>
-      <c r="M10" s="361">
+      <c r="K10" s="350" t="n"/>
+      <c r="L10" s="373" t="n"/>
+      <c r="M10" s="372">
         <f>日程表１!M10</f>
         <v/>
       </c>
@@ -9573,15 +9637,15 @@
         <f>日程表１!N10</f>
         <v/>
       </c>
-      <c r="O10" s="338" t="n"/>
+      <c r="O10" s="349" t="n"/>
       <c r="P10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q10" s="339" t="n"/>
-      <c r="R10" s="362" t="n"/>
-      <c r="S10" s="361">
+      <c r="Q10" s="350" t="n"/>
+      <c r="R10" s="373" t="n"/>
+      <c r="S10" s="372">
         <f>日程表１!S11</f>
         <v/>
       </c>
@@ -9589,17 +9653,17 @@
         <f>日程表１!T11</f>
         <v/>
       </c>
-      <c r="U10" s="338" t="n"/>
+      <c r="U10" s="349" t="n"/>
       <c r="V10" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W10" s="369" t="n"/>
-      <c r="X10" s="364" t="n"/>
+      <c r="W10" s="380" t="n"/>
+      <c r="X10" s="375" t="n"/>
     </row>
     <row r="11" ht="20.45" customHeight="1" s="257">
-      <c r="A11" s="361">
+      <c r="A11" s="372">
         <f>日程表１!A11</f>
         <v/>
       </c>
@@ -9607,15 +9671,15 @@
         <f>日程表１!B11</f>
         <v/>
       </c>
-      <c r="C11" s="338" t="n"/>
+      <c r="C11" s="349" t="n"/>
       <c r="D11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E11" s="339" t="n"/>
-      <c r="F11" s="362" t="n"/>
-      <c r="G11" s="361">
+      <c r="E11" s="350" t="n"/>
+      <c r="F11" s="373" t="n"/>
+      <c r="G11" s="372">
         <f>日程表１!G11</f>
         <v/>
       </c>
@@ -9623,15 +9687,15 @@
         <f>日程表１!H11</f>
         <v/>
       </c>
-      <c r="I11" s="338" t="n"/>
+      <c r="I11" s="349" t="n"/>
       <c r="J11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K11" s="339" t="n"/>
-      <c r="L11" s="362" t="n"/>
-      <c r="M11" s="361">
+      <c r="K11" s="350" t="n"/>
+      <c r="L11" s="373" t="n"/>
+      <c r="M11" s="372">
         <f>日程表１!M11</f>
         <v/>
       </c>
@@ -9639,15 +9703,15 @@
         <f>日程表１!N11</f>
         <v/>
       </c>
-      <c r="O11" s="338" t="n"/>
+      <c r="O11" s="349" t="n"/>
       <c r="P11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q11" s="339" t="n"/>
-      <c r="R11" s="362" t="n"/>
-      <c r="S11" s="361">
+      <c r="Q11" s="350" t="n"/>
+      <c r="R11" s="373" t="n"/>
+      <c r="S11" s="372">
         <f>日程表１!S12</f>
         <v/>
       </c>
@@ -9655,17 +9719,17 @@
         <f>日程表１!T12</f>
         <v/>
       </c>
-      <c r="U11" s="338" t="n"/>
+      <c r="U11" s="349" t="n"/>
       <c r="V11" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W11" s="369" t="n"/>
-      <c r="X11" s="364" t="n"/>
+      <c r="W11" s="380" t="n"/>
+      <c r="X11" s="375" t="n"/>
     </row>
     <row r="12" ht="20.45" customHeight="1" s="257">
-      <c r="A12" s="361">
+      <c r="A12" s="372">
         <f>日程表１!A12</f>
         <v/>
       </c>
@@ -9673,40 +9737,40 @@
         <f>日程表１!B12</f>
         <v/>
       </c>
-      <c r="C12" s="338" t="n"/>
+      <c r="C12" s="349" t="n"/>
       <c r="D12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E12" s="339" t="n"/>
-      <c r="F12" s="362" t="n"/>
-      <c r="G12" s="365">
+      <c r="E12" s="350" t="n"/>
+      <c r="F12" s="373" t="n"/>
+      <c r="G12" s="376">
         <f>日程表１!G12</f>
         <v/>
       </c>
-      <c r="H12" s="366">
+      <c r="H12" s="377">
         <f>日程表１!H12</f>
         <v/>
       </c>
-      <c r="I12" s="343">
+      <c r="I12" s="354">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
-      <c r="J12" s="367" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K12" s="345">
+      <c r="J12" s="378" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K12" s="356">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="L12" s="368">
+      <c r="L12" s="379">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M12" s="361">
+      <c r="M12" s="372">
         <f>日程表１!M12</f>
         <v/>
       </c>
@@ -9714,15 +9778,15 @@
         <f>日程表１!N12</f>
         <v/>
       </c>
-      <c r="O12" s="338" t="n"/>
+      <c r="O12" s="349" t="n"/>
       <c r="P12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q12" s="339" t="n"/>
-      <c r="R12" s="362" t="n"/>
-      <c r="S12" s="361">
+      <c r="Q12" s="350" t="n"/>
+      <c r="R12" s="373" t="n"/>
+      <c r="S12" s="372">
         <f>日程表１!S13</f>
         <v/>
       </c>
@@ -9730,17 +9794,17 @@
         <f>日程表１!T13</f>
         <v/>
       </c>
-      <c r="U12" s="338" t="n"/>
+      <c r="U12" s="349" t="n"/>
       <c r="V12" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W12" s="369" t="n"/>
-      <c r="X12" s="364" t="n"/>
+      <c r="W12" s="380" t="n"/>
+      <c r="X12" s="375" t="n"/>
     </row>
     <row r="13" ht="20.45" customHeight="1" s="257">
-      <c r="A13" s="361">
+      <c r="A13" s="372">
         <f>日程表１!A13</f>
         <v/>
       </c>
@@ -9748,15 +9812,15 @@
         <f>日程表１!B13</f>
         <v/>
       </c>
-      <c r="C13" s="338" t="n"/>
+      <c r="C13" s="349" t="n"/>
       <c r="D13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E13" s="339" t="n"/>
-      <c r="F13" s="362" t="n"/>
-      <c r="G13" s="361">
+      <c r="E13" s="350" t="n"/>
+      <c r="F13" s="373" t="n"/>
+      <c r="G13" s="372">
         <f>日程表１!G13</f>
         <v/>
       </c>
@@ -9764,7 +9828,7 @@
         <f>日程表１!H13</f>
         <v/>
       </c>
-      <c r="I13" s="338">
+      <c r="I13" s="349">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -9773,15 +9837,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K13" s="339">
+      <c r="K13" s="350">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L13" s="362">
+      <c r="L13" s="373">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="M13" s="361">
+      <c r="M13" s="372">
         <f>日程表１!M13</f>
         <v/>
       </c>
@@ -9789,15 +9853,15 @@
         <f>日程表１!N13</f>
         <v/>
       </c>
-      <c r="O13" s="338" t="n"/>
+      <c r="O13" s="349" t="n"/>
       <c r="P13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q13" s="339" t="n"/>
-      <c r="R13" s="362" t="n"/>
-      <c r="S13" s="361" t="n">
+      <c r="Q13" s="350" t="n"/>
+      <c r="R13" s="373" t="n"/>
+      <c r="S13" s="372" t="n">
         <v>10</v>
       </c>
       <c r="T13" s="29" t="inlineStr">
@@ -9805,17 +9869,17 @@
           <t>土</t>
         </is>
       </c>
-      <c r="U13" s="338" t="n"/>
+      <c r="U13" s="349" t="n"/>
       <c r="V13" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="W13" s="369" t="n"/>
-      <c r="X13" s="364" t="n"/>
+      <c r="W13" s="380" t="n"/>
+      <c r="X13" s="375" t="n"/>
     </row>
     <row r="14" ht="20.45" customHeight="1" s="257">
-      <c r="A14" s="361">
+      <c r="A14" s="372">
         <f>日程表１!A14</f>
         <v/>
       </c>
@@ -9823,15 +9887,15 @@
         <f>日程表１!B14</f>
         <v/>
       </c>
-      <c r="C14" s="338" t="n"/>
+      <c r="C14" s="349" t="n"/>
       <c r="D14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E14" s="339" t="n"/>
-      <c r="F14" s="362" t="n"/>
-      <c r="G14" s="361">
+      <c r="E14" s="350" t="n"/>
+      <c r="F14" s="373" t="n"/>
+      <c r="G14" s="372">
         <f>日程表１!G14</f>
         <v/>
       </c>
@@ -9839,7 +9903,7 @@
         <f>日程表１!H14</f>
         <v/>
       </c>
-      <c r="I14" s="338">
+      <c r="I14" s="349">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
@@ -9848,15 +9912,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K14" s="339">
+      <c r="K14" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L14" s="362">
+      <c r="L14" s="373">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M14" s="361">
+      <c r="M14" s="372">
         <f>日程表１!M14</f>
         <v/>
       </c>
@@ -9864,23 +9928,23 @@
         <f>日程表１!N14</f>
         <v/>
       </c>
-      <c r="O14" s="338" t="n"/>
+      <c r="O14" s="349" t="n"/>
       <c r="P14" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q14" s="339" t="n"/>
-      <c r="R14" s="362" t="n"/>
+      <c r="Q14" s="350" t="n"/>
+      <c r="R14" s="373" t="n"/>
       <c r="S14" s="256" t="n"/>
       <c r="T14" s="256" t="n"/>
-      <c r="U14" s="352" t="n"/>
+      <c r="U14" s="363" t="n"/>
       <c r="V14" s="255" t="n"/>
-      <c r="W14" s="353" t="n"/>
-      <c r="X14" s="353" t="n"/>
+      <c r="W14" s="364" t="n"/>
+      <c r="X14" s="364" t="n"/>
     </row>
     <row r="15" ht="20.45" customHeight="1" s="257">
-      <c r="A15" s="361">
+      <c r="A15" s="372">
         <f>日程表１!A15</f>
         <v/>
       </c>
@@ -9888,15 +9952,15 @@
         <f>日程表１!B15</f>
         <v/>
       </c>
-      <c r="C15" s="338" t="n"/>
+      <c r="C15" s="349" t="n"/>
       <c r="D15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E15" s="339" t="n"/>
-      <c r="F15" s="362" t="n"/>
-      <c r="G15" s="361">
+      <c r="E15" s="350" t="n"/>
+      <c r="F15" s="373" t="n"/>
+      <c r="G15" s="372">
         <f>日程表１!G15</f>
         <v/>
       </c>
@@ -9904,15 +9968,15 @@
         <f>日程表１!H15</f>
         <v/>
       </c>
-      <c r="I15" s="338" t="n"/>
+      <c r="I15" s="349" t="n"/>
       <c r="J15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K15" s="339" t="n"/>
-      <c r="L15" s="362" t="n"/>
-      <c r="M15" s="361">
+      <c r="K15" s="350" t="n"/>
+      <c r="L15" s="373" t="n"/>
+      <c r="M15" s="372">
         <f>日程表１!M15</f>
         <v/>
       </c>
@@ -9920,23 +9984,23 @@
         <f>日程表１!N15</f>
         <v/>
       </c>
-      <c r="O15" s="338" t="n"/>
+      <c r="O15" s="349" t="n"/>
       <c r="P15" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q15" s="339" t="n"/>
-      <c r="R15" s="362" t="n"/>
+      <c r="Q15" s="350" t="n"/>
+      <c r="R15" s="373" t="n"/>
       <c r="S15" s="256" t="n"/>
       <c r="T15" s="256" t="n"/>
-      <c r="U15" s="352" t="n"/>
+      <c r="U15" s="363" t="n"/>
       <c r="V15" s="255" t="n"/>
-      <c r="W15" s="353" t="n"/>
-      <c r="X15" s="353" t="n"/>
+      <c r="W15" s="364" t="n"/>
+      <c r="X15" s="364" t="n"/>
     </row>
     <row r="16" ht="20.45" customHeight="1" s="257">
-      <c r="A16" s="361">
+      <c r="A16" s="372">
         <f>日程表１!A16</f>
         <v/>
       </c>
@@ -9944,15 +10008,15 @@
         <f>日程表１!B16</f>
         <v/>
       </c>
-      <c r="C16" s="338" t="n"/>
+      <c r="C16" s="349" t="n"/>
       <c r="D16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E16" s="339" t="n"/>
-      <c r="F16" s="362" t="n"/>
-      <c r="G16" s="361">
+      <c r="E16" s="350" t="n"/>
+      <c r="F16" s="373" t="n"/>
+      <c r="G16" s="372">
         <f>日程表１!G16</f>
         <v/>
       </c>
@@ -9960,15 +10024,15 @@
         <f>日程表１!H16</f>
         <v/>
       </c>
-      <c r="I16" s="338" t="n"/>
+      <c r="I16" s="349" t="n"/>
       <c r="J16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K16" s="339" t="n"/>
-      <c r="L16" s="362" t="n"/>
-      <c r="M16" s="361">
+      <c r="K16" s="350" t="n"/>
+      <c r="L16" s="373" t="n"/>
+      <c r="M16" s="372">
         <f>日程表１!M16</f>
         <v/>
       </c>
@@ -9976,23 +10040,23 @@
         <f>日程表１!N16</f>
         <v/>
       </c>
-      <c r="O16" s="338" t="n"/>
+      <c r="O16" s="349" t="n"/>
       <c r="P16" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q16" s="339" t="n"/>
-      <c r="R16" s="362" t="n"/>
+      <c r="Q16" s="350" t="n"/>
+      <c r="R16" s="373" t="n"/>
       <c r="S16" s="256" t="n"/>
       <c r="T16" s="256" t="n"/>
-      <c r="U16" s="352" t="n"/>
+      <c r="U16" s="363" t="n"/>
       <c r="V16" s="255" t="n"/>
-      <c r="W16" s="353" t="n"/>
-      <c r="X16" s="353" t="n"/>
+      <c r="W16" s="364" t="n"/>
+      <c r="X16" s="364" t="n"/>
     </row>
     <row r="17" ht="20.45" customHeight="1" s="257">
-      <c r="A17" s="361">
+      <c r="A17" s="372">
         <f>日程表１!A17</f>
         <v/>
       </c>
@@ -10000,15 +10064,15 @@
         <f>日程表１!B17</f>
         <v/>
       </c>
-      <c r="C17" s="338" t="n"/>
+      <c r="C17" s="349" t="n"/>
       <c r="D17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E17" s="339" t="n"/>
-      <c r="F17" s="362" t="n"/>
-      <c r="G17" s="361">
+      <c r="E17" s="350" t="n"/>
+      <c r="F17" s="373" t="n"/>
+      <c r="G17" s="372">
         <f>日程表１!G17</f>
         <v/>
       </c>
@@ -10016,15 +10080,15 @@
         <f>日程表１!H17</f>
         <v/>
       </c>
-      <c r="I17" s="338" t="n"/>
+      <c r="I17" s="349" t="n"/>
       <c r="J17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K17" s="339" t="n"/>
-      <c r="L17" s="362" t="n"/>
-      <c r="M17" s="361">
+      <c r="K17" s="350" t="n"/>
+      <c r="L17" s="373" t="n"/>
+      <c r="M17" s="372">
         <f>日程表１!M17</f>
         <v/>
       </c>
@@ -10032,14 +10096,14 @@
         <f>日程表１!N17</f>
         <v/>
       </c>
-      <c r="O17" s="338" t="n"/>
+      <c r="O17" s="349" t="n"/>
       <c r="P17" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q17" s="339" t="n"/>
-      <c r="R17" s="362" t="n"/>
+      <c r="Q17" s="350" t="n"/>
+      <c r="R17" s="373" t="n"/>
       <c r="S17" s="254" t="inlineStr">
         <is>
           <t>NO.</t>
@@ -10050,13 +10114,13 @@
           <t>team</t>
         </is>
       </c>
-      <c r="U17" s="293" t="n"/>
-      <c r="V17" s="293" t="n"/>
-      <c r="W17" s="293" t="n"/>
-      <c r="X17" s="294" t="n"/>
+      <c r="U17" s="297" t="n"/>
+      <c r="V17" s="297" t="n"/>
+      <c r="W17" s="297" t="n"/>
+      <c r="X17" s="298" t="n"/>
     </row>
     <row r="18" ht="20.45" customHeight="1" s="257">
-      <c r="A18" s="361">
+      <c r="A18" s="372">
         <f>日程表１!A18</f>
         <v/>
       </c>
@@ -10064,15 +10128,15 @@
         <f>日程表１!B18</f>
         <v/>
       </c>
-      <c r="C18" s="338" t="n"/>
+      <c r="C18" s="349" t="n"/>
       <c r="D18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E18" s="339" t="n"/>
-      <c r="F18" s="362" t="n"/>
-      <c r="G18" s="361">
+      <c r="E18" s="350" t="n"/>
+      <c r="F18" s="373" t="n"/>
+      <c r="G18" s="372">
         <f>日程表１!G18</f>
         <v/>
       </c>
@@ -10080,15 +10144,15 @@
         <f>日程表１!H18</f>
         <v/>
       </c>
-      <c r="I18" s="338" t="n"/>
+      <c r="I18" s="349" t="n"/>
       <c r="J18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K18" s="339" t="n"/>
-      <c r="L18" s="362" t="n"/>
-      <c r="M18" s="361">
+      <c r="K18" s="350" t="n"/>
+      <c r="L18" s="373" t="n"/>
+      <c r="M18" s="372">
         <f>日程表１!M18</f>
         <v/>
       </c>
@@ -10096,14 +10160,14 @@
         <f>日程表１!N18</f>
         <v/>
       </c>
-      <c r="O18" s="338" t="n"/>
+      <c r="O18" s="349" t="n"/>
       <c r="P18" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q18" s="339" t="n"/>
-      <c r="R18" s="362" t="n"/>
+      <c r="Q18" s="350" t="n"/>
+      <c r="R18" s="373" t="n"/>
       <c r="S18" s="254" t="n">
         <v>1</v>
       </c>
@@ -10111,13 +10175,13 @@
         <f>リーグ勝敗表!AX6</f>
         <v/>
       </c>
-      <c r="U18" s="293" t="n"/>
-      <c r="V18" s="293" t="n"/>
-      <c r="W18" s="293" t="n"/>
-      <c r="X18" s="294" t="n"/>
+      <c r="U18" s="297" t="n"/>
+      <c r="V18" s="297" t="n"/>
+      <c r="W18" s="297" t="n"/>
+      <c r="X18" s="298" t="n"/>
     </row>
     <row r="19" ht="20.45" customHeight="1" s="257">
-      <c r="A19" s="361">
+      <c r="A19" s="372">
         <f>日程表１!A19</f>
         <v/>
       </c>
@@ -10125,15 +10189,15 @@
         <f>日程表１!B19</f>
         <v/>
       </c>
-      <c r="C19" s="338" t="n"/>
+      <c r="C19" s="349" t="n"/>
       <c r="D19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E19" s="339" t="n"/>
-      <c r="F19" s="362" t="n"/>
-      <c r="G19" s="361">
+      <c r="E19" s="350" t="n"/>
+      <c r="F19" s="373" t="n"/>
+      <c r="G19" s="372">
         <f>日程表１!G19</f>
         <v/>
       </c>
@@ -10141,15 +10205,15 @@
         <f>日程表１!H19</f>
         <v/>
       </c>
-      <c r="I19" s="338" t="inlineStr">
+      <c r="I19" s="349" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J19" s="253" t="n"/>
-      <c r="K19" s="339" t="n"/>
-      <c r="L19" s="362" t="n"/>
-      <c r="M19" s="361">
+      <c r="K19" s="350" t="n"/>
+      <c r="L19" s="373" t="n"/>
+      <c r="M19" s="372">
         <f>日程表１!M19</f>
         <v/>
       </c>
@@ -10157,14 +10221,14 @@
         <f>日程表１!N19</f>
         <v/>
       </c>
-      <c r="O19" s="338" t="n"/>
+      <c r="O19" s="349" t="n"/>
       <c r="P19" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q19" s="339" t="n"/>
-      <c r="R19" s="362" t="n"/>
+      <c r="Q19" s="350" t="n"/>
+      <c r="R19" s="373" t="n"/>
       <c r="S19" s="254" t="n">
         <v>2</v>
       </c>
@@ -10172,13 +10236,13 @@
         <f>リーグ勝敗表!AX8</f>
         <v/>
       </c>
-      <c r="U19" s="293" t="n"/>
-      <c r="V19" s="293" t="n"/>
-      <c r="W19" s="293" t="n"/>
-      <c r="X19" s="294" t="n"/>
+      <c r="U19" s="297" t="n"/>
+      <c r="V19" s="297" t="n"/>
+      <c r="W19" s="297" t="n"/>
+      <c r="X19" s="298" t="n"/>
     </row>
     <row r="20" ht="20.45" customHeight="1" s="257">
-      <c r="A20" s="361">
+      <c r="A20" s="372">
         <f>日程表１!A20</f>
         <v/>
       </c>
@@ -10186,15 +10250,15 @@
         <f>日程表１!B20</f>
         <v/>
       </c>
-      <c r="C20" s="338" t="n"/>
+      <c r="C20" s="349" t="n"/>
       <c r="D20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E20" s="339" t="n"/>
-      <c r="F20" s="362" t="n"/>
-      <c r="G20" s="361">
+      <c r="E20" s="350" t="n"/>
+      <c r="F20" s="373" t="n"/>
+      <c r="G20" s="372">
         <f>日程表１!G20</f>
         <v/>
       </c>
@@ -10202,15 +10266,15 @@
         <f>日程表１!H20</f>
         <v/>
       </c>
-      <c r="I20" s="338" t="inlineStr">
+      <c r="I20" s="349" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J20" s="253" t="n"/>
-      <c r="K20" s="339" t="n"/>
-      <c r="L20" s="362" t="n"/>
-      <c r="M20" s="361">
+      <c r="K20" s="350" t="n"/>
+      <c r="L20" s="373" t="n"/>
+      <c r="M20" s="372">
         <f>日程表１!M20</f>
         <v/>
       </c>
@@ -10218,14 +10282,14 @@
         <f>日程表１!N20</f>
         <v/>
       </c>
-      <c r="O20" s="338" t="n"/>
+      <c r="O20" s="349" t="n"/>
       <c r="P20" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q20" s="339" t="n"/>
-      <c r="R20" s="362" t="n"/>
+      <c r="Q20" s="350" t="n"/>
+      <c r="R20" s="373" t="n"/>
       <c r="S20" s="254" t="n">
         <v>3</v>
       </c>
@@ -10233,13 +10297,13 @@
         <f>リーグ勝敗表!AX10</f>
         <v/>
       </c>
-      <c r="U20" s="293" t="n"/>
-      <c r="V20" s="293" t="n"/>
-      <c r="W20" s="293" t="n"/>
-      <c r="X20" s="294" t="n"/>
+      <c r="U20" s="297" t="n"/>
+      <c r="V20" s="297" t="n"/>
+      <c r="W20" s="297" t="n"/>
+      <c r="X20" s="298" t="n"/>
     </row>
     <row r="21" ht="20.45" customHeight="1" s="257">
-      <c r="A21" s="361">
+      <c r="A21" s="372">
         <f>日程表１!A21</f>
         <v/>
       </c>
@@ -10247,15 +10311,15 @@
         <f>日程表１!B21</f>
         <v/>
       </c>
-      <c r="C21" s="338" t="n"/>
+      <c r="C21" s="349" t="n"/>
       <c r="D21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E21" s="339" t="n"/>
-      <c r="F21" s="362" t="n"/>
-      <c r="G21" s="361">
+      <c r="E21" s="350" t="n"/>
+      <c r="F21" s="373" t="n"/>
+      <c r="G21" s="372">
         <f>日程表１!G21</f>
         <v/>
       </c>
@@ -10263,15 +10327,15 @@
         <f>日程表１!H21</f>
         <v/>
       </c>
-      <c r="I21" s="338" t="inlineStr">
+      <c r="I21" s="349" t="inlineStr">
         <is>
           <t>予備日</t>
         </is>
       </c>
       <c r="J21" s="253" t="n"/>
-      <c r="K21" s="339" t="n"/>
-      <c r="L21" s="362" t="n"/>
-      <c r="M21" s="361">
+      <c r="K21" s="350" t="n"/>
+      <c r="L21" s="373" t="n"/>
+      <c r="M21" s="372">
         <f>日程表１!M21</f>
         <v/>
       </c>
@@ -10279,14 +10343,14 @@
         <f>日程表１!N21</f>
         <v/>
       </c>
-      <c r="O21" s="338" t="n"/>
+      <c r="O21" s="349" t="n"/>
       <c r="P21" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q21" s="339" t="n"/>
-      <c r="R21" s="362" t="n"/>
+      <c r="Q21" s="350" t="n"/>
+      <c r="R21" s="373" t="n"/>
       <c r="S21" s="254" t="n">
         <v>4</v>
       </c>
@@ -10294,13 +10358,13 @@
         <f>リーグ勝敗表!AX12</f>
         <v/>
       </c>
-      <c r="U21" s="293" t="n"/>
-      <c r="V21" s="293" t="n"/>
-      <c r="W21" s="293" t="n"/>
-      <c r="X21" s="294" t="n"/>
+      <c r="U21" s="297" t="n"/>
+      <c r="V21" s="297" t="n"/>
+      <c r="W21" s="297" t="n"/>
+      <c r="X21" s="298" t="n"/>
     </row>
     <row r="22" ht="20.45" customHeight="1" s="257">
-      <c r="A22" s="361">
+      <c r="A22" s="372">
         <f>日程表１!A22</f>
         <v/>
       </c>
@@ -10308,15 +10372,15 @@
         <f>日程表１!B22</f>
         <v/>
       </c>
-      <c r="C22" s="338" t="n"/>
+      <c r="C22" s="349" t="n"/>
       <c r="D22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E22" s="339" t="n"/>
-      <c r="F22" s="362" t="n"/>
-      <c r="G22" s="361">
+      <c r="E22" s="350" t="n"/>
+      <c r="F22" s="373" t="n"/>
+      <c r="G22" s="372">
         <f>日程表１!G22</f>
         <v/>
       </c>
@@ -10324,15 +10388,15 @@
         <f>日程表１!H22</f>
         <v/>
       </c>
-      <c r="I22" s="338" t="n"/>
+      <c r="I22" s="349" t="n"/>
       <c r="J22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K22" s="339" t="n"/>
-      <c r="L22" s="362" t="n"/>
-      <c r="M22" s="361">
+      <c r="K22" s="350" t="n"/>
+      <c r="L22" s="373" t="n"/>
+      <c r="M22" s="372">
         <f>日程表１!M22</f>
         <v/>
       </c>
@@ -10340,14 +10404,14 @@
         <f>日程表１!N22</f>
         <v/>
       </c>
-      <c r="O22" s="338" t="n"/>
+      <c r="O22" s="349" t="n"/>
       <c r="P22" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q22" s="339" t="n"/>
-      <c r="R22" s="362" t="n"/>
+      <c r="Q22" s="350" t="n"/>
+      <c r="R22" s="373" t="n"/>
       <c r="S22" s="254" t="n">
         <v>5</v>
       </c>
@@ -10355,13 +10419,13 @@
         <f>リーグ勝敗表!AX14</f>
         <v/>
       </c>
-      <c r="U22" s="293" t="n"/>
-      <c r="V22" s="293" t="n"/>
-      <c r="W22" s="293" t="n"/>
-      <c r="X22" s="294" t="n"/>
+      <c r="U22" s="297" t="n"/>
+      <c r="V22" s="297" t="n"/>
+      <c r="W22" s="297" t="n"/>
+      <c r="X22" s="298" t="n"/>
     </row>
     <row r="23" ht="20.45" customHeight="1" s="257">
-      <c r="A23" s="361">
+      <c r="A23" s="372">
         <f>日程表１!A23</f>
         <v/>
       </c>
@@ -10369,15 +10433,15 @@
         <f>日程表１!B23</f>
         <v/>
       </c>
-      <c r="C23" s="338" t="n"/>
+      <c r="C23" s="349" t="n"/>
       <c r="D23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E23" s="339" t="n"/>
-      <c r="F23" s="362" t="n"/>
-      <c r="G23" s="361">
+      <c r="E23" s="350" t="n"/>
+      <c r="F23" s="373" t="n"/>
+      <c r="G23" s="372">
         <f>日程表１!G23</f>
         <v/>
       </c>
@@ -10385,15 +10449,15 @@
         <f>日程表１!H23</f>
         <v/>
       </c>
-      <c r="I23" s="338" t="n"/>
+      <c r="I23" s="349" t="n"/>
       <c r="J23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K23" s="339" t="n"/>
-      <c r="L23" s="362" t="n"/>
-      <c r="M23" s="361">
+      <c r="K23" s="350" t="n"/>
+      <c r="L23" s="373" t="n"/>
+      <c r="M23" s="372">
         <f>日程表１!M23</f>
         <v/>
       </c>
@@ -10401,14 +10465,14 @@
         <f>日程表１!N23</f>
         <v/>
       </c>
-      <c r="O23" s="338" t="n"/>
+      <c r="O23" s="349" t="n"/>
       <c r="P23" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q23" s="339" t="n"/>
-      <c r="R23" s="362" t="n"/>
+      <c r="Q23" s="350" t="n"/>
+      <c r="R23" s="373" t="n"/>
       <c r="S23" s="254" t="n">
         <v>6</v>
       </c>
@@ -10416,13 +10480,13 @@
         <f>リーグ勝敗表!AX16</f>
         <v/>
       </c>
-      <c r="U23" s="293" t="n"/>
-      <c r="V23" s="293" t="n"/>
-      <c r="W23" s="293" t="n"/>
-      <c r="X23" s="294" t="n"/>
+      <c r="U23" s="297" t="n"/>
+      <c r="V23" s="297" t="n"/>
+      <c r="W23" s="297" t="n"/>
+      <c r="X23" s="298" t="n"/>
     </row>
     <row r="24" ht="20.45" customHeight="1" s="257">
-      <c r="A24" s="361">
+      <c r="A24" s="372">
         <f>日程表１!A24</f>
         <v/>
       </c>
@@ -10430,15 +10494,15 @@
         <f>日程表１!B24</f>
         <v/>
       </c>
-      <c r="C24" s="338" t="n"/>
+      <c r="C24" s="349" t="n"/>
       <c r="D24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E24" s="339" t="n"/>
-      <c r="F24" s="362" t="n"/>
-      <c r="G24" s="361">
+      <c r="E24" s="350" t="n"/>
+      <c r="F24" s="373" t="n"/>
+      <c r="G24" s="372">
         <f>日程表１!G24</f>
         <v/>
       </c>
@@ -10446,15 +10510,15 @@
         <f>日程表１!H24</f>
         <v/>
       </c>
-      <c r="I24" s="338" t="n"/>
+      <c r="I24" s="349" t="n"/>
       <c r="J24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K24" s="339" t="n"/>
-      <c r="L24" s="362" t="n"/>
-      <c r="M24" s="361">
+      <c r="K24" s="350" t="n"/>
+      <c r="L24" s="373" t="n"/>
+      <c r="M24" s="372">
         <f>日程表１!M24</f>
         <v/>
       </c>
@@ -10462,14 +10526,14 @@
         <f>日程表１!N24</f>
         <v/>
       </c>
-      <c r="O24" s="338" t="n"/>
+      <c r="O24" s="349" t="n"/>
       <c r="P24" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q24" s="339" t="n"/>
-      <c r="R24" s="362" t="n"/>
+      <c r="Q24" s="350" t="n"/>
+      <c r="R24" s="373" t="n"/>
       <c r="S24" s="254" t="n">
         <v>7</v>
       </c>
@@ -10477,13 +10541,13 @@
         <f>リーグ勝敗表!AX18</f>
         <v/>
       </c>
-      <c r="U24" s="293" t="n"/>
-      <c r="V24" s="293" t="n"/>
-      <c r="W24" s="293" t="n"/>
-      <c r="X24" s="294" t="n"/>
+      <c r="U24" s="297" t="n"/>
+      <c r="V24" s="297" t="n"/>
+      <c r="W24" s="297" t="n"/>
+      <c r="X24" s="298" t="n"/>
     </row>
     <row r="25" ht="20.45" customHeight="1" s="257">
-      <c r="A25" s="361">
+      <c r="A25" s="372">
         <f>日程表１!A25</f>
         <v/>
       </c>
@@ -10491,15 +10555,15 @@
         <f>日程表１!B25</f>
         <v/>
       </c>
-      <c r="C25" s="338" t="n"/>
+      <c r="C25" s="349" t="n"/>
       <c r="D25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E25" s="339" t="n"/>
-      <c r="F25" s="362" t="n"/>
-      <c r="G25" s="361">
+      <c r="E25" s="350" t="n"/>
+      <c r="F25" s="373" t="n"/>
+      <c r="G25" s="372">
         <f>日程表１!G25</f>
         <v/>
       </c>
@@ -10507,15 +10571,15 @@
         <f>日程表１!H25</f>
         <v/>
       </c>
-      <c r="I25" s="338" t="n"/>
+      <c r="I25" s="349" t="n"/>
       <c r="J25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K25" s="339" t="n"/>
-      <c r="L25" s="362" t="n"/>
-      <c r="M25" s="361">
+      <c r="K25" s="350" t="n"/>
+      <c r="L25" s="373" t="n"/>
+      <c r="M25" s="372">
         <f>日程表１!M25</f>
         <v/>
       </c>
@@ -10523,14 +10587,14 @@
         <f>日程表１!N25</f>
         <v/>
       </c>
-      <c r="O25" s="338" t="n"/>
+      <c r="O25" s="349" t="n"/>
       <c r="P25" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q25" s="339" t="n"/>
-      <c r="R25" s="362" t="n"/>
+      <c r="Q25" s="350" t="n"/>
+      <c r="R25" s="373" t="n"/>
       <c r="S25" s="254" t="n">
         <v>8</v>
       </c>
@@ -10538,13 +10602,13 @@
         <f>リーグ勝敗表!AX20</f>
         <v/>
       </c>
-      <c r="U25" s="293" t="n"/>
-      <c r="V25" s="293" t="n"/>
-      <c r="W25" s="293" t="n"/>
-      <c r="X25" s="294" t="n"/>
+      <c r="U25" s="297" t="n"/>
+      <c r="V25" s="297" t="n"/>
+      <c r="W25" s="297" t="n"/>
+      <c r="X25" s="298" t="n"/>
     </row>
     <row r="26" ht="20.45" customHeight="1" s="257">
-      <c r="A26" s="361">
+      <c r="A26" s="372">
         <f>日程表１!A26</f>
         <v/>
       </c>
@@ -10552,40 +10616,40 @@
         <f>日程表１!B26</f>
         <v/>
       </c>
-      <c r="C26" s="338" t="n"/>
+      <c r="C26" s="349" t="n"/>
       <c r="D26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E26" s="339" t="n"/>
-      <c r="F26" s="362" t="n"/>
-      <c r="G26" s="365">
+      <c r="E26" s="350" t="n"/>
+      <c r="F26" s="373" t="n"/>
+      <c r="G26" s="376">
         <f>日程表１!G26</f>
         <v/>
       </c>
-      <c r="H26" s="366">
+      <c r="H26" s="377">
         <f>日程表１!H26</f>
         <v/>
       </c>
-      <c r="I26" s="343">
+      <c r="I26" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="J26" s="367" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="K26" s="345">
+      <c r="J26" s="378" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="K26" s="356">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L26" s="368">
+      <c r="L26" s="379">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M26" s="361">
+      <c r="M26" s="372">
         <f>日程表１!M26</f>
         <v/>
       </c>
@@ -10593,14 +10657,14 @@
         <f>日程表１!N26</f>
         <v/>
       </c>
-      <c r="O26" s="338" t="n"/>
+      <c r="O26" s="349" t="n"/>
       <c r="P26" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q26" s="339" t="n"/>
-      <c r="R26" s="362" t="n"/>
+      <c r="Q26" s="350" t="n"/>
+      <c r="R26" s="373" t="n"/>
       <c r="S26" s="254" t="n">
         <v>9</v>
       </c>
@@ -10608,13 +10672,13 @@
         <f>リーグ勝敗表!AX22</f>
         <v/>
       </c>
-      <c r="U26" s="293" t="n"/>
-      <c r="V26" s="293" t="n"/>
-      <c r="W26" s="293" t="n"/>
-      <c r="X26" s="294" t="n"/>
+      <c r="U26" s="297" t="n"/>
+      <c r="V26" s="297" t="n"/>
+      <c r="W26" s="297" t="n"/>
+      <c r="X26" s="298" t="n"/>
     </row>
     <row r="27" ht="20.45" customHeight="1" s="257">
-      <c r="A27" s="361">
+      <c r="A27" s="372">
         <f>日程表１!A27</f>
         <v/>
       </c>
@@ -10622,15 +10686,15 @@
         <f>日程表１!B27</f>
         <v/>
       </c>
-      <c r="C27" s="338" t="n"/>
+      <c r="C27" s="349" t="n"/>
       <c r="D27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E27" s="339" t="n"/>
-      <c r="F27" s="362" t="n"/>
-      <c r="G27" s="361">
+      <c r="E27" s="350" t="n"/>
+      <c r="F27" s="373" t="n"/>
+      <c r="G27" s="372">
         <f>日程表１!G27</f>
         <v/>
       </c>
@@ -10638,7 +10702,7 @@
         <f>日程表１!H27</f>
         <v/>
       </c>
-      <c r="I27" s="338">
+      <c r="I27" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10647,15 +10711,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K27" s="339">
+      <c r="K27" s="350">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="L27" s="362">
+      <c r="L27" s="373">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="M27" s="361">
+      <c r="M27" s="372">
         <f>日程表１!M27</f>
         <v/>
       </c>
@@ -10663,14 +10727,14 @@
         <f>日程表１!N27</f>
         <v/>
       </c>
-      <c r="O27" s="338" t="n"/>
+      <c r="O27" s="349" t="n"/>
       <c r="P27" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q27" s="339" t="n"/>
-      <c r="R27" s="362" t="n"/>
+      <c r="Q27" s="350" t="n"/>
+      <c r="R27" s="373" t="n"/>
       <c r="S27" s="254" t="n">
         <v>10</v>
       </c>
@@ -10678,13 +10742,13 @@
         <f>リーグ勝敗表!AX24</f>
         <v/>
       </c>
-      <c r="U27" s="293" t="n"/>
-      <c r="V27" s="293" t="n"/>
-      <c r="W27" s="293" t="n"/>
-      <c r="X27" s="294" t="n"/>
+      <c r="U27" s="297" t="n"/>
+      <c r="V27" s="297" t="n"/>
+      <c r="W27" s="297" t="n"/>
+      <c r="X27" s="298" t="n"/>
     </row>
     <row r="28" ht="20.45" customHeight="1" s="257">
-      <c r="A28" s="361">
+      <c r="A28" s="372">
         <f>日程表１!A28</f>
         <v/>
       </c>
@@ -10692,15 +10756,15 @@
         <f>日程表１!B28</f>
         <v/>
       </c>
-      <c r="C28" s="338" t="n"/>
+      <c r="C28" s="349" t="n"/>
       <c r="D28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E28" s="339" t="n"/>
-      <c r="F28" s="362" t="n"/>
-      <c r="G28" s="361">
+      <c r="E28" s="350" t="n"/>
+      <c r="F28" s="373" t="n"/>
+      <c r="G28" s="372">
         <f>日程表１!G28</f>
         <v/>
       </c>
@@ -10708,7 +10772,7 @@
         <f>日程表１!H28</f>
         <v/>
       </c>
-      <c r="I28" s="338">
+      <c r="I28" s="349">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
@@ -10717,15 +10781,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K28" s="339">
+      <c r="K28" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="L28" s="362">
+      <c r="L28" s="373">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="M28" s="361">
+      <c r="M28" s="372">
         <f>日程表１!M28</f>
         <v/>
       </c>
@@ -10733,14 +10797,14 @@
         <f>日程表１!N28</f>
         <v/>
       </c>
-      <c r="O28" s="338" t="n"/>
+      <c r="O28" s="349" t="n"/>
       <c r="P28" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q28" s="339" t="n"/>
-      <c r="R28" s="362" t="n"/>
+      <c r="Q28" s="350" t="n"/>
+      <c r="R28" s="373" t="n"/>
       <c r="S28" s="254" t="n">
         <v>11</v>
       </c>
@@ -10748,13 +10812,13 @@
         <f>リーグ勝敗表!AX26</f>
         <v/>
       </c>
-      <c r="U28" s="293" t="n"/>
-      <c r="V28" s="293" t="n"/>
-      <c r="W28" s="293" t="n"/>
-      <c r="X28" s="294" t="n"/>
+      <c r="U28" s="297" t="n"/>
+      <c r="V28" s="297" t="n"/>
+      <c r="W28" s="297" t="n"/>
+      <c r="X28" s="298" t="n"/>
     </row>
     <row r="29" ht="20.45" customHeight="1" s="257">
-      <c r="A29" s="361">
+      <c r="A29" s="372">
         <f>日程表１!A29</f>
         <v/>
       </c>
@@ -10762,7 +10826,7 @@
         <f>日程表１!B29</f>
         <v/>
       </c>
-      <c r="C29" s="338">
+      <c r="C29" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -10771,15 +10835,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E29" s="339">
+      <c r="E29" s="350">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="F29" s="362">
+      <c r="F29" s="373">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G29" s="361">
+      <c r="G29" s="372">
         <f>日程表１!G29</f>
         <v/>
       </c>
@@ -10787,15 +10851,15 @@
         <f>日程表１!H29</f>
         <v/>
       </c>
-      <c r="I29" s="338" t="n"/>
+      <c r="I29" s="349" t="n"/>
       <c r="J29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K29" s="339" t="n"/>
-      <c r="L29" s="362" t="n"/>
-      <c r="M29" s="361">
+      <c r="K29" s="350" t="n"/>
+      <c r="L29" s="373" t="n"/>
+      <c r="M29" s="372">
         <f>日程表１!M29</f>
         <v/>
       </c>
@@ -10803,23 +10867,23 @@
         <f>日程表１!N29</f>
         <v/>
       </c>
-      <c r="O29" s="338" t="n"/>
+      <c r="O29" s="349" t="n"/>
       <c r="P29" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q29" s="339" t="n"/>
-      <c r="R29" s="362" t="n"/>
+      <c r="Q29" s="350" t="n"/>
+      <c r="R29" s="373" t="n"/>
       <c r="S29" s="255" t="n"/>
       <c r="T29" s="255" t="n"/>
-      <c r="U29" s="353" t="n"/>
+      <c r="U29" s="364" t="n"/>
       <c r="V29" s="255" t="n"/>
-      <c r="W29" s="353" t="n"/>
-      <c r="X29" s="353" t="n"/>
+      <c r="W29" s="364" t="n"/>
+      <c r="X29" s="364" t="n"/>
     </row>
     <row r="30" ht="20.45" customHeight="1" s="257">
-      <c r="A30" s="361">
+      <c r="A30" s="372">
         <f>日程表１!A30</f>
         <v/>
       </c>
@@ -10827,7 +10891,7 @@
         <f>日程表１!B30</f>
         <v/>
       </c>
-      <c r="C30" s="338">
+      <c r="C30" s="349">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
@@ -10836,15 +10900,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="E30" s="339">
+      <c r="E30" s="350">
         <f>IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="F30" s="362">
+      <c r="F30" s="373">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")&amp;"-"&amp;IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")</f>
         <v/>
       </c>
-      <c r="G30" s="361">
+      <c r="G30" s="372">
         <f>日程表１!G30</f>
         <v/>
       </c>
@@ -10852,15 +10916,15 @@
         <f>日程表１!H30</f>
         <v/>
       </c>
-      <c r="I30" s="338" t="n"/>
+      <c r="I30" s="349" t="n"/>
       <c r="J30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K30" s="339" t="n"/>
-      <c r="L30" s="362" t="n"/>
-      <c r="M30" s="361">
+      <c r="K30" s="350" t="n"/>
+      <c r="L30" s="373" t="n"/>
+      <c r="M30" s="372">
         <f>日程表１!M30</f>
         <v/>
       </c>
@@ -10868,48 +10932,48 @@
         <f>日程表１!N30</f>
         <v/>
       </c>
-      <c r="O30" s="338" t="n"/>
+      <c r="O30" s="349" t="n"/>
       <c r="P30" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q30" s="339" t="n"/>
-      <c r="R30" s="362" t="n"/>
+      <c r="Q30" s="350" t="n"/>
+      <c r="R30" s="373" t="n"/>
       <c r="S30" s="255" t="n"/>
       <c r="T30" s="255" t="n"/>
-      <c r="U30" s="353" t="n"/>
+      <c r="U30" s="364" t="n"/>
       <c r="V30" s="255" t="n"/>
-      <c r="W30" s="353" t="n"/>
-      <c r="X30" s="353" t="n"/>
+      <c r="W30" s="364" t="n"/>
+      <c r="X30" s="364" t="n"/>
     </row>
     <row r="31" ht="20.45" customHeight="1" s="257">
-      <c r="A31" s="365">
+      <c r="A31" s="376">
         <f>日程表１!A31</f>
         <v/>
       </c>
-      <c r="B31" s="366">
+      <c r="B31" s="377">
         <f>日程表１!B31</f>
         <v/>
       </c>
-      <c r="C31" s="343">
+      <c r="C31" s="354">
         <f>IFERROR(VLOOKUP(2,リーグ勝敗表!$AZ$6:$BA$11,2,0),"2")</f>
         <v/>
       </c>
-      <c r="D31" s="367" t="inlineStr">
-        <is>
-          <t>ー</t>
-        </is>
-      </c>
-      <c r="E31" s="345">
+      <c r="D31" s="378" t="inlineStr">
+        <is>
+          <t>ー</t>
+        </is>
+      </c>
+      <c r="E31" s="356">
         <f>IFERROR(VLOOKUP(4,リーグ勝敗表!$AZ$6:$BA$11,2,0),"4")</f>
         <v/>
       </c>
-      <c r="F31" s="368">
+      <c r="F31" s="379">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="G31" s="361">
+      <c r="G31" s="372">
         <f>日程表１!G31</f>
         <v/>
       </c>
@@ -10917,15 +10981,15 @@
         <f>日程表１!H31</f>
         <v/>
       </c>
-      <c r="I31" s="338" t="n"/>
+      <c r="I31" s="349" t="n"/>
       <c r="J31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K31" s="339" t="n"/>
-      <c r="L31" s="362" t="n"/>
-      <c r="M31" s="361">
+      <c r="K31" s="350" t="n"/>
+      <c r="L31" s="373" t="n"/>
+      <c r="M31" s="372">
         <f>日程表１!M31</f>
         <v/>
       </c>
@@ -10933,23 +10997,23 @@
         <f>日程表１!N31</f>
         <v/>
       </c>
-      <c r="O31" s="338" t="n"/>
+      <c r="O31" s="349" t="n"/>
       <c r="P31" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q31" s="339" t="n"/>
-      <c r="R31" s="362" t="n"/>
+      <c r="Q31" s="350" t="n"/>
+      <c r="R31" s="373" t="n"/>
       <c r="S31" s="255" t="n"/>
       <c r="T31" s="255" t="n"/>
-      <c r="U31" s="353" t="n"/>
+      <c r="U31" s="364" t="n"/>
       <c r="V31" s="255" t="n"/>
-      <c r="W31" s="353" t="n"/>
-      <c r="X31" s="353" t="n"/>
+      <c r="W31" s="364" t="n"/>
+      <c r="X31" s="364" t="n"/>
     </row>
     <row r="32" ht="20.45" customHeight="1" s="257">
-      <c r="A32" s="361">
+      <c r="A32" s="372">
         <f>日程表１!A32</f>
         <v/>
       </c>
@@ -10957,15 +11021,15 @@
         <f>日程表１!B32</f>
         <v/>
       </c>
-      <c r="C32" s="338" t="n"/>
+      <c r="C32" s="349" t="n"/>
       <c r="D32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E32" s="339" t="n"/>
-      <c r="F32" s="362" t="n"/>
-      <c r="G32" s="361">
+      <c r="E32" s="350" t="n"/>
+      <c r="F32" s="373" t="n"/>
+      <c r="G32" s="372">
         <f>日程表１!G32</f>
         <v/>
       </c>
@@ -10973,15 +11037,15 @@
         <f>日程表１!H32</f>
         <v/>
       </c>
-      <c r="I32" s="338" t="n"/>
+      <c r="I32" s="349" t="n"/>
       <c r="J32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K32" s="339" t="n"/>
-      <c r="L32" s="362" t="n"/>
-      <c r="M32" s="361">
+      <c r="K32" s="350" t="n"/>
+      <c r="L32" s="373" t="n"/>
+      <c r="M32" s="372">
         <f>日程表１!M32</f>
         <v/>
       </c>
@@ -10989,23 +11053,23 @@
         <f>日程表１!N32</f>
         <v/>
       </c>
-      <c r="O32" s="338" t="n"/>
+      <c r="O32" s="349" t="n"/>
       <c r="P32" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q32" s="339" t="n"/>
-      <c r="R32" s="362" t="n"/>
+      <c r="Q32" s="350" t="n"/>
+      <c r="R32" s="373" t="n"/>
       <c r="S32" s="255" t="n"/>
       <c r="T32" s="255" t="n"/>
-      <c r="U32" s="353" t="n"/>
+      <c r="U32" s="364" t="n"/>
       <c r="V32" s="255" t="n"/>
-      <c r="W32" s="353" t="n"/>
-      <c r="X32" s="353" t="n"/>
+      <c r="W32" s="364" t="n"/>
+      <c r="X32" s="364" t="n"/>
     </row>
     <row r="33" ht="20.45" customHeight="1" s="257">
-      <c r="A33" s="361">
+      <c r="A33" s="372">
         <f>日程表１!A33</f>
         <v/>
       </c>
@@ -11013,15 +11077,15 @@
         <f>日程表１!B33</f>
         <v/>
       </c>
-      <c r="C33" s="338" t="n"/>
+      <c r="C33" s="349" t="n"/>
       <c r="D33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E33" s="339" t="n"/>
-      <c r="F33" s="362" t="n"/>
-      <c r="G33" s="361">
+      <c r="E33" s="350" t="n"/>
+      <c r="F33" s="373" t="n"/>
+      <c r="G33" s="372">
         <f>日程表１!G33</f>
         <v/>
       </c>
@@ -11029,7 +11093,7 @@
         <f>日程表１!H33</f>
         <v/>
       </c>
-      <c r="I33" s="338">
+      <c r="I33" s="349">
         <f>IFERROR(VLOOKUP(1,リーグ勝敗表!$AZ$6:$BA$11,2,0),"1")</f>
         <v/>
       </c>
@@ -11038,15 +11102,15 @@
           <t>ー</t>
         </is>
       </c>
-      <c r="K33" s="339">
+      <c r="K33" s="350">
         <f>IFERROR(VLOOKUP(5,リーグ勝敗表!$AZ$6:$BA$11,2,0),"5")</f>
         <v/>
       </c>
-      <c r="L33" s="362">
+      <c r="L33" s="373">
         <f>IFERROR(VLOOKUP(3,リーグ勝敗表!$AZ$6:$BA$11,2,0),"3")&amp;"-"&amp;IFERROR(VLOOKUP(6,リーグ勝敗表!$AZ$6:$BA$11,2,0),"6")</f>
         <v/>
       </c>
-      <c r="M33" s="361">
+      <c r="M33" s="372">
         <f>日程表１!M33</f>
         <v/>
       </c>
@@ -11054,23 +11118,23 @@
         <f>日程表１!N33</f>
         <v/>
       </c>
-      <c r="O33" s="338" t="n"/>
+      <c r="O33" s="349" t="n"/>
       <c r="P33" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q33" s="339" t="n"/>
-      <c r="R33" s="362" t="n"/>
+      <c r="Q33" s="350" t="n"/>
+      <c r="R33" s="373" t="n"/>
       <c r="S33" s="255" t="n"/>
       <c r="T33" s="255" t="n"/>
-      <c r="U33" s="353" t="n"/>
+      <c r="U33" s="364" t="n"/>
       <c r="V33" s="255" t="n"/>
-      <c r="W33" s="353" t="n"/>
-      <c r="X33" s="353" t="n"/>
+      <c r="W33" s="364" t="n"/>
+      <c r="X33" s="364" t="n"/>
     </row>
     <row r="34" ht="20.45" customHeight="1" s="257">
-      <c r="A34" s="361">
+      <c r="A34" s="372">
         <f>日程表１!A34</f>
         <v/>
       </c>
@@ -11078,25 +11142,25 @@
         <f>日程表１!B34</f>
         <v/>
       </c>
-      <c r="C34" s="338" t="n"/>
+      <c r="C34" s="349" t="n"/>
       <c r="D34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="E34" s="369" t="n"/>
-      <c r="F34" s="352" t="n"/>
-      <c r="G34" s="361" t="n"/>
+      <c r="E34" s="380" t="n"/>
+      <c r="F34" s="363" t="n"/>
+      <c r="G34" s="372" t="n"/>
       <c r="H34" s="256" t="n"/>
-      <c r="I34" s="338" t="n"/>
+      <c r="I34" s="349" t="n"/>
       <c r="J34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="K34" s="339" t="n"/>
-      <c r="L34" s="362" t="n"/>
-      <c r="M34" s="361">
+      <c r="K34" s="350" t="n"/>
+      <c r="L34" s="373" t="n"/>
+      <c r="M34" s="372">
         <f>日程表１!M34</f>
         <v/>
       </c>
@@ -11104,20 +11168,20 @@
         <f>日程表１!N34</f>
         <v/>
       </c>
-      <c r="O34" s="338" t="n"/>
+      <c r="O34" s="349" t="n"/>
       <c r="P34" s="253" t="inlineStr">
         <is>
           <t>ー</t>
         </is>
       </c>
-      <c r="Q34" s="339" t="n"/>
-      <c r="R34" s="362" t="n"/>
+      <c r="Q34" s="350" t="n"/>
+      <c r="R34" s="373" t="n"/>
       <c r="S34" s="255" t="n"/>
       <c r="T34" s="255" t="n"/>
-      <c r="U34" s="353" t="n"/>
+      <c r="U34" s="364" t="n"/>
       <c r="V34" s="255" t="n"/>
-      <c r="W34" s="353" t="n"/>
-      <c r="X34" s="353" t="n"/>
+      <c r="W34" s="364" t="n"/>
+      <c r="X34" s="364" t="n"/>
     </row>
     <row r="35" ht="3" customHeight="1" s="257"/>
   </sheetData>
